--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/Stocks/Data/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACF1E84-1922-FA42-8641-F97A6963C449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA234FB8-2C16-AD41-952A-C3E2058C6728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1062,6 +1062,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1071,7 +1072,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,20 +1098,19 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>43.87</v>
+            <v>68.5</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1520,8 +1519,8 @@
         <v>95</v>
       </c>
       <c r="C3" s="1">
-        <f ca="1">[1]Sheet1!$C$5</f>
-        <v>43.87</v>
+        <f>[1]Sheet1!$C$5</f>
+        <v>68.5</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -1539,9 +1538,9 @@
       <c r="B10" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="105">
-        <f ca="1">C3*'Statement Q'!J141</f>
-        <v>219130.65</v>
+      <c r="C10" s="102">
+        <f>C3*'Statement Q'!J141</f>
+        <v>342157.5</v>
       </c>
     </row>
   </sheetData>
@@ -7456,11 +7455,11 @@
         <v>96</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="102" t="s">
+      <c r="P4" s="103" t="s">
         <v>97</v>
       </c>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="104"/>
+      <c r="Q4" s="104"/>
+      <c r="R4" s="105"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA234FB8-2C16-AD41-952A-C3E2058C6728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D390F21-78CC-8645-AA5A-9F373DF5F231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -321,9 +321,6 @@
     <t>Q</t>
   </si>
   <si>
-    <t>Q1 2024</t>
-  </si>
-  <si>
     <t>Q1 2025</t>
   </si>
   <si>
@@ -594,9 +591,6 @@
     <t>29.03.2025</t>
   </si>
   <si>
-    <t>30.03.2024</t>
-  </si>
-  <si>
     <t>27.12.2025</t>
   </si>
   <si>
@@ -613,6 +607,12 @@
   </si>
   <si>
     <t>Market cap</t>
+  </si>
+  <si>
+    <t>Q1 2026</t>
+  </si>
+  <si>
+    <t>28.03.2026</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1106,7 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>68.5</v>
+            <v>99.61</v>
           </cell>
         </row>
       </sheetData>
@@ -1511,16 +1511,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="1">
         <f>[1]Sheet1!$C$5</f>
-        <v>68.5</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -1536,11 +1536,11 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C10" s="102">
         <f>C3*'Statement Q'!J141</f>
-        <v>342157.5</v>
+        <v>500639.86</v>
       </c>
     </row>
   </sheetData>
@@ -1573,34 +1573,34 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1848,7 +1848,7 @@
     </row>
     <row r="10" spans="1:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="27">
         <v>1744</v>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="11" spans="1:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" s="27">
         <v>294</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="14" spans="1:14" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="27">
         <v>506</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="17" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="27">
         <v>-2620</v>
@@ -2151,7 +2151,7 @@
     <row r="18" spans="1:19" s="98" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C18" s="35">
         <v>10316</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="28" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C28" s="27">
         <v>3225</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="29" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C29" s="27">
         <v>8314</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="37" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C37" s="27">
         <v>4716</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="39" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C39" s="27">
         <v>9494</v>
@@ -3075,7 +3075,7 @@
     </row>
     <row r="45" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C45" s="27">
         <v>3465</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="46" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C46" s="27">
         <v>0</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="47" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C47" s="27">
         <v>1718</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="52" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B52" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C52" s="27">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="53" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B53" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C53" s="27">
         <v>0</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="54" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B54" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C54" s="27">
         <v>1730</v>
@@ -3729,7 +3729,7 @@
     </row>
     <row r="63" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B63" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C63" s="27">
         <v>882</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="64" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B64" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C64" s="36">
         <f>C62+C63</f>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="65" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B65" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C65" s="27">
         <v>0</v>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="71" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B71" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C71" s="27">
         <v>6266</v>
@@ -4049,7 +4049,7 @@
     </row>
     <row r="73" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B73" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C73" s="27">
         <v>1524</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="75" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B75" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C75" s="27">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="76" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B76" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C76" s="27">
         <v>0</v>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="77" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C77" s="27">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="78" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B78" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C78" s="27">
         <v>257</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="79" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B79" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C79" s="27">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="80" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B80" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C80" s="27">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="84" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B84" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C84" s="27">
         <v>291</v>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="85" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B85" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C85" s="27">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="86" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B86" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C86" s="27">
         <v>1382</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="87" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B87" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C87" s="27">
         <v>394</v>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="90" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B90" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C90" s="27">
         <v>-15470</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="91" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B91" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C91" s="27">
         <v>0</v>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="92" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B92" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C92" s="27">
         <v>-9269</v>
@@ -4750,7 +4750,7 @@
     </row>
     <row r="93" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B93" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C93" s="27">
         <v>2847</v>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="94" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B94" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C94" s="27">
         <v>5654</v>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="95" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B95" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C95" s="27">
         <v>-12237</v>
@@ -4855,7 +4855,7 @@
     </row>
     <row r="96" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B96" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C96" s="27">
         <v>10898</v>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="97" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B97" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C97" s="27">
         <v>-963</v>
@@ -4925,7 +4925,7 @@
     </row>
     <row r="98" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B98" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C98" s="27">
         <v>1080</v>
@@ -4960,7 +4960,7 @@
     </row>
     <row r="99" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B99" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C99" s="27">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     </row>
     <row r="100" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B100" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C100" s="27">
         <v>1268</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="102" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B102" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C102" s="27">
         <v>-15</v>
@@ -5101,7 +5101,7 @@
     </row>
     <row r="103" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B103" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C103" s="27">
         <v>0</v>
@@ -5136,7 +5136,7 @@
     </row>
     <row r="104" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B104" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C104" s="27">
         <v>0</v>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="105" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B105" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C105" s="27">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     </row>
     <row r="106" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B106" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C106" s="27">
         <v>0</v>
@@ -5241,7 +5241,7 @@
     </row>
     <row r="107" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B107" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C107" s="27">
         <v>0</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="108" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B108" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C108" s="27">
         <v>2734</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="109" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B109" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C109" s="27">
         <v>-1500</v>
@@ -5346,7 +5346,7 @@
     </row>
     <row r="110" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B110" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C110" s="27">
         <v>1108</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="111" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B111" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C111" s="27">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="112" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B112" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C112" s="27">
         <v>0</v>
@@ -5451,7 +5451,7 @@
     </row>
     <row r="113" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B113" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C113" s="27">
         <v>-2587</v>
@@ -6563,7 +6563,7 @@
     </row>
     <row r="143" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B143" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C143" s="30">
         <v>1.04</v>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="144" spans="1:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B144" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C144" s="36">
         <f>C71</f>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="145" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B145" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C145" s="36">
         <f>C73</f>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="146" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B146" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C146" s="97">
         <f t="shared" ref="C146:L146" si="28">(-1*C17)/C16</f>
@@ -6734,7 +6734,7 @@
     </row>
     <row r="147" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B147" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C147" s="27">
         <v>106000</v>
@@ -6774,7 +6774,7 @@
     <row r="150" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4"/>
       <c r="B150" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="151" spans="1:12" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -7178,12 +7178,12 @@
     <row r="161" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4"/>
       <c r="B161" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="162" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B162" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C162" s="87">
         <f t="shared" ref="C162:L162" si="33">C7/C5</f>
@@ -7228,7 +7228,7 @@
     </row>
     <row r="163" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B163" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C163" s="87">
         <f t="shared" ref="C163:L163" si="34">C13/C5</f>
@@ -7274,7 +7274,7 @@
     <row r="164" spans="1:12" s="96" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="94" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C164" s="95">
         <f t="shared" ref="C164:L164" si="35">C18/C5</f>
@@ -7332,15 +7332,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB41336-2E39-7442-9864-91E9B0A07818}">
-  <dimension ref="A1:S153"/>
+  <dimension ref="A1:S152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="9" customWidth="1"/>
-    <col min="3" max="3" width="12" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="10" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="12" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="10" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="2" style="1" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="10.33203125" style="1" customWidth="1" outlineLevel="1"/>
     <col min="13" max="13" width="2.33203125" style="1" customWidth="1"/>
@@ -7361,28 +7360,28 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="I2" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>172</v>
-      </c>
       <c r="J2" s="40" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -7400,25 +7399,25 @@
         <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>88</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="40" t="s">
         <v>90</v>
       </c>
       <c r="I3" s="40" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="J3" s="40" t="s">
         <v>182</v>
@@ -7430,14 +7429,14 @@
       <c r="O3" s="4"/>
       <c r="P3" s="56" t="str">
         <f>I3</f>
-        <v>Q3 2025</v>
+        <v>Q4 2025</v>
       </c>
       <c r="Q3" s="5" t="str">
         <f>J3</f>
-        <v>Q4 2025</v>
+        <v>Q1 2026</v>
       </c>
       <c r="R3" s="57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S3" s="4"/>
     </row>
@@ -7446,977 +7445,979 @@
       <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="H4" s="41"/>
       <c r="I4" s="41"/>
       <c r="J4" s="41"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="103" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q4" s="104"/>
       <c r="R4" s="105"/>
       <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="60">
-        <v>12724</v>
+        <v>12833</v>
       </c>
       <c r="D5" s="60">
-        <v>12833</v>
+        <v>13284</v>
       </c>
       <c r="E5" s="60">
-        <v>13284</v>
+        <v>14260</v>
       </c>
       <c r="F5" s="60">
-        <v>14260</v>
+        <v>12667</v>
       </c>
       <c r="G5" s="60">
-        <v>12667</v>
-      </c>
-      <c r="H5" s="60">
         <v>12859</v>
       </c>
+      <c r="H5" s="69">
+        <v>13653</v>
+      </c>
       <c r="I5" s="69">
-        <v>13653</v>
+        <v>13674</v>
       </c>
       <c r="J5" s="69">
-        <v>13674</v>
+        <v>13577</v>
       </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
       <c r="N5" s="68">
         <f t="shared" ref="N5:N19" si="0">SUM(G5:J5)</f>
-        <v>52853</v>
+        <v>53763</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="79">
         <f t="shared" ref="P5:P23" si="1">I5</f>
-        <v>13653</v>
+        <v>13674</v>
       </c>
       <c r="Q5" s="63">
         <f t="shared" ref="Q5:Q23" si="2">J5</f>
-        <v>13674</v>
+        <v>13577</v>
       </c>
       <c r="R5" s="75">
         <f t="shared" ref="R5:R23" si="3">IF(P5=0,
 IF(Q5=0,0,IF(Q5&gt;0,1,-1)),
 (Q5-P5)/ABS(P5)
 )</f>
-        <v>1.5381234893430016E-3</v>
+        <v>-7.0937545707181514E-3</v>
       </c>
       <c r="S5" s="7"/>
     </row>
-    <row r="6" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="27">
-        <v>7507</v>
+        <v>8286</v>
       </c>
       <c r="D6" s="27">
-        <v>8286</v>
+        <v>11287</v>
       </c>
       <c r="E6" s="27">
-        <v>11287</v>
+        <v>8676</v>
       </c>
       <c r="F6" s="27">
-        <v>8676</v>
+        <v>7995</v>
       </c>
       <c r="G6" s="27">
-        <v>7995</v>
-      </c>
-      <c r="H6" s="27">
         <v>9317</v>
       </c>
+      <c r="H6" s="42">
+        <v>8435</v>
+      </c>
       <c r="I6" s="42">
-        <v>8435</v>
+        <v>8731</v>
       </c>
       <c r="J6" s="42">
-        <v>8731</v>
+        <v>8230</v>
       </c>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
       <c r="N6" s="48">
         <f>SUM(G6:J6)</f>
-        <v>34478</v>
+        <v>34713</v>
       </c>
       <c r="P6" s="58">
         <f t="shared" si="1"/>
-        <v>8435</v>
+        <v>8731</v>
       </c>
       <c r="Q6" s="20">
         <f t="shared" si="2"/>
-        <v>8731</v>
+        <v>8230</v>
       </c>
       <c r="R6" s="59">
         <f t="shared" si="3"/>
-        <v>3.5091879075281565E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>-5.7381743213835761E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="63">
-        <f t="shared" ref="C7" si="4">C5-C6</f>
-        <v>5217</v>
+        <f>C5-C6</f>
+        <v>4547</v>
       </c>
       <c r="D7" s="63">
-        <f>D5-D6</f>
-        <v>4547</v>
+        <f t="shared" ref="D7:H7" si="4">D5-D6</f>
+        <v>1997</v>
       </c>
       <c r="E7" s="63">
-        <f t="shared" ref="E7:I7" si="5">E5-E6</f>
-        <v>1997</v>
+        <f t="shared" si="4"/>
+        <v>5584</v>
       </c>
       <c r="F7" s="63">
+        <f t="shared" si="4"/>
+        <v>4672</v>
+      </c>
+      <c r="G7" s="63">
+        <f t="shared" si="4"/>
+        <v>3542</v>
+      </c>
+      <c r="H7" s="70">
+        <f t="shared" si="4"/>
+        <v>5218</v>
+      </c>
+      <c r="I7" s="70">
+        <f t="shared" ref="I7:J7" si="5">I5-I6</f>
+        <v>4943</v>
+      </c>
+      <c r="J7" s="70">
         <f t="shared" si="5"/>
-        <v>5584</v>
-      </c>
-      <c r="G7" s="63">
-        <f t="shared" si="5"/>
-        <v>4672</v>
-      </c>
-      <c r="H7" s="63">
-        <f t="shared" si="5"/>
-        <v>3542</v>
-      </c>
-      <c r="I7" s="70">
-        <f t="shared" si="5"/>
-        <v>5218</v>
-      </c>
-      <c r="J7" s="70">
-        <f t="shared" ref="J7" si="6">J5-J6</f>
-        <v>4943</v>
+        <v>5347</v>
       </c>
       <c r="K7" s="21"/>
       <c r="L7" s="21"/>
       <c r="M7" s="21"/>
       <c r="N7" s="68">
         <f t="shared" si="0"/>
-        <v>18375</v>
+        <v>19050</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="79">
         <f t="shared" si="1"/>
-        <v>5218</v>
+        <v>4943</v>
       </c>
       <c r="Q7" s="63">
         <f t="shared" si="2"/>
-        <v>4943</v>
+        <v>5347</v>
       </c>
       <c r="R7" s="75">
         <f t="shared" si="3"/>
-        <v>-5.2702184745113068E-2</v>
+        <v>8.1731741857171761E-2</v>
       </c>
       <c r="S7" s="7"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="27">
-        <v>4382</v>
+        <v>4239</v>
       </c>
       <c r="D8" s="27">
-        <v>4239</v>
+        <v>4049</v>
       </c>
       <c r="E8" s="27">
-        <v>4049</v>
+        <v>3876</v>
       </c>
       <c r="F8" s="27">
-        <v>3876</v>
+        <v>3640</v>
       </c>
       <c r="G8" s="27">
-        <v>3640</v>
-      </c>
-      <c r="H8" s="27">
         <v>3684</v>
       </c>
+      <c r="H8" s="42">
+        <v>3231</v>
+      </c>
       <c r="I8" s="42">
-        <v>3231</v>
+        <v>3219</v>
       </c>
       <c r="J8" s="42">
-        <v>3219</v>
+        <v>3375</v>
       </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="48">
         <f t="shared" si="0"/>
-        <v>13774</v>
+        <v>13509</v>
       </c>
       <c r="P8" s="58">
         <f t="shared" si="1"/>
-        <v>3231</v>
+        <v>3219</v>
       </c>
       <c r="Q8" s="20">
         <f t="shared" si="2"/>
-        <v>3219</v>
+        <v>3375</v>
       </c>
       <c r="R8" s="59">
         <f t="shared" si="3"/>
-        <v>-3.7140204271123491E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>4.8462255358807084E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="27">
-        <v>1556</v>
+        <v>1329</v>
       </c>
       <c r="D9" s="27">
-        <v>1329</v>
+        <v>1383</v>
       </c>
       <c r="E9" s="27">
-        <v>1383</v>
+        <v>1239</v>
       </c>
       <c r="F9" s="27">
-        <v>1239</v>
+        <v>1177</v>
       </c>
       <c r="G9" s="27">
-        <v>1177</v>
-      </c>
-      <c r="H9" s="27">
         <v>1144</v>
       </c>
+      <c r="H9" s="42">
+        <v>1129</v>
+      </c>
       <c r="I9" s="42">
-        <v>1129</v>
+        <v>1174</v>
       </c>
       <c r="J9" s="42">
-        <v>1174</v>
+        <v>1038</v>
       </c>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="48">
         <f t="shared" si="0"/>
-        <v>4624</v>
+        <v>4485</v>
       </c>
       <c r="P9" s="80">
         <f t="shared" si="1"/>
-        <v>1129</v>
+        <v>1174</v>
       </c>
       <c r="Q9" s="36">
         <f t="shared" si="2"/>
-        <v>1174</v>
+        <v>1038</v>
       </c>
       <c r="R9" s="76">
         <f t="shared" si="3"/>
-        <v>3.9858281665190433E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>-0.11584327086882454</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="27">
-        <v>348</v>
+        <v>943</v>
       </c>
       <c r="D10" s="27">
-        <v>943</v>
+        <v>5622</v>
       </c>
       <c r="E10" s="27">
-        <v>5622</v>
+        <v>57</v>
       </c>
       <c r="F10" s="27">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="G10" s="27">
-        <v>156</v>
-      </c>
-      <c r="H10" s="27">
         <v>1890</v>
       </c>
+      <c r="H10" s="42">
+        <v>175</v>
+      </c>
       <c r="I10" s="42">
-        <v>175</v>
+        <v>-30</v>
       </c>
       <c r="J10" s="42">
-        <v>-30</v>
+        <v>4070</v>
       </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
       <c r="N10" s="48">
         <f t="shared" si="0"/>
-        <v>2191</v>
+        <v>6105</v>
       </c>
       <c r="P10" s="58">
         <f t="shared" si="1"/>
-        <v>175</v>
+        <v>-30</v>
       </c>
       <c r="Q10" s="20">
         <f t="shared" si="2"/>
-        <v>-30</v>
+        <v>4070</v>
       </c>
       <c r="R10" s="59">
         <f t="shared" si="3"/>
-        <v>-1.1714285714285715</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>136.66666666666666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="20">
-        <f t="shared" ref="C11:I11" si="7">SUM(C8:C10)</f>
-        <v>6286</v>
+        <f t="shared" ref="C11:I11" si="6">SUM(C8:C10)</f>
+        <v>6511</v>
       </c>
       <c r="D11" s="20">
+        <f t="shared" si="6"/>
+        <v>11054</v>
+      </c>
+      <c r="E11" s="20">
+        <f t="shared" si="6"/>
+        <v>5172</v>
+      </c>
+      <c r="F11" s="20">
+        <f t="shared" si="6"/>
+        <v>4973</v>
+      </c>
+      <c r="G11" s="20">
+        <f t="shared" si="6"/>
+        <v>6718</v>
+      </c>
+      <c r="H11" s="43">
+        <f t="shared" si="6"/>
+        <v>4535</v>
+      </c>
+      <c r="I11" s="43">
+        <f t="shared" ref="I11:J11" si="7">SUM(I8:I10)</f>
+        <v>4363</v>
+      </c>
+      <c r="J11" s="43">
         <f t="shared" si="7"/>
-        <v>6511</v>
-      </c>
-      <c r="E11" s="20">
-        <f t="shared" si="7"/>
-        <v>11054</v>
-      </c>
-      <c r="F11" s="20">
-        <f t="shared" si="7"/>
-        <v>5172</v>
-      </c>
-      <c r="G11" s="20">
-        <f t="shared" si="7"/>
-        <v>4973</v>
-      </c>
-      <c r="H11" s="20">
-        <f t="shared" si="7"/>
-        <v>6718</v>
-      </c>
-      <c r="I11" s="43">
-        <f t="shared" si="7"/>
-        <v>4535</v>
-      </c>
-      <c r="J11" s="43">
-        <f t="shared" ref="J11" si="8">SUM(J8:J10)</f>
-        <v>4363</v>
+        <v>8483</v>
       </c>
       <c r="K11" s="20"/>
       <c r="L11" s="20"/>
       <c r="M11" s="20"/>
       <c r="N11" s="48">
         <f t="shared" si="0"/>
-        <v>20589</v>
+        <v>24099</v>
       </c>
       <c r="P11" s="58">
         <f t="shared" si="1"/>
-        <v>4535</v>
+        <v>4363</v>
       </c>
       <c r="Q11" s="20">
         <f>J11</f>
-        <v>4363</v>
+        <v>8483</v>
       </c>
       <c r="R11" s="59">
         <f t="shared" si="3"/>
-        <v>-3.7927232635060641E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>0.94430437772175113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="17" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="60">
-        <v>-1069</v>
+        <v>-1964</v>
       </c>
       <c r="D12" s="60">
-        <v>-1964</v>
+        <v>-9057</v>
       </c>
       <c r="E12" s="60">
-        <v>-9057</v>
+        <v>412</v>
       </c>
       <c r="F12" s="60">
-        <v>412</v>
+        <v>-301</v>
       </c>
       <c r="G12" s="60">
-        <v>-301</v>
-      </c>
-      <c r="H12" s="60">
         <v>-3176</v>
       </c>
+      <c r="H12" s="69">
+        <v>683</v>
+      </c>
       <c r="I12" s="69">
-        <v>683</v>
+        <v>580</v>
       </c>
       <c r="J12" s="69">
-        <v>580</v>
+        <v>-3136</v>
       </c>
       <c r="K12" s="21"/>
       <c r="L12" s="21"/>
       <c r="M12" s="21"/>
       <c r="N12" s="68">
         <f t="shared" si="0"/>
-        <v>-2214</v>
+        <v>-5049</v>
       </c>
       <c r="O12" s="7"/>
       <c r="P12" s="79">
         <f t="shared" si="1"/>
-        <v>683</v>
+        <v>580</v>
       </c>
       <c r="Q12" s="63">
         <f t="shared" si="2"/>
-        <v>580</v>
+        <v>-3136</v>
       </c>
       <c r="R12" s="75">
         <f t="shared" si="3"/>
-        <v>-0.15080527086383602</v>
+        <v>-6.4068965517241381</v>
       </c>
       <c r="S12" s="7"/>
     </row>
-    <row r="13" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C13" s="27">
-        <v>205</v>
+        <v>-120</v>
       </c>
       <c r="D13" s="27">
-        <v>-120</v>
+        <v>-159</v>
       </c>
       <c r="E13" s="27">
-        <v>-159</v>
+        <v>316</v>
       </c>
       <c r="F13" s="27">
-        <v>316</v>
+        <v>-112</v>
       </c>
       <c r="G13" s="27">
-        <v>-112</v>
-      </c>
-      <c r="H13" s="27">
         <v>502</v>
       </c>
+      <c r="H13" s="42">
+        <v>221</v>
+      </c>
       <c r="I13" s="42">
-        <v>221</v>
+        <v>-97</v>
       </c>
       <c r="J13" s="42">
-        <v>-97</v>
+        <v>-72</v>
       </c>
       <c r="K13" s="20"/>
       <c r="L13" s="20"/>
       <c r="M13" s="20"/>
       <c r="N13" s="48">
         <f t="shared" si="0"/>
-        <v>514</v>
+        <v>554</v>
       </c>
       <c r="P13" s="58">
         <f t="shared" si="1"/>
-        <v>221</v>
+        <v>-97</v>
       </c>
       <c r="Q13" s="20">
         <f t="shared" si="2"/>
-        <v>-97</v>
+        <v>-72</v>
       </c>
       <c r="R13" s="59">
         <f t="shared" si="3"/>
-        <v>-1.4389140271493213</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>0.25773195876288657</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="27">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="D14" s="27">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E14" s="27">
-        <v>130</v>
+        <v>-129</v>
       </c>
       <c r="F14" s="27">
-        <v>-129</v>
+        <v>-173</v>
       </c>
       <c r="G14" s="27">
-        <v>-173</v>
-      </c>
-      <c r="H14" s="27">
         <v>-95</v>
       </c>
+      <c r="H14" s="42">
+        <v>3670</v>
+      </c>
       <c r="I14" s="42">
-        <v>3670</v>
+        <v>-145</v>
       </c>
       <c r="J14" s="42">
-        <v>-145</v>
+        <v>-738</v>
       </c>
       <c r="K14" s="20"/>
       <c r="L14" s="20"/>
       <c r="M14" s="20"/>
       <c r="N14" s="48">
         <f t="shared" si="0"/>
-        <v>3257</v>
+        <v>2692</v>
       </c>
       <c r="P14" s="58">
         <f t="shared" si="1"/>
-        <v>3670</v>
+        <v>-145</v>
       </c>
       <c r="Q14" s="20">
         <f t="shared" si="2"/>
-        <v>-145</v>
+        <v>-738</v>
       </c>
       <c r="R14" s="59">
         <f t="shared" si="3"/>
-        <v>-1.0395095367847411</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>-4.0896551724137931</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="60">
-        <v>-719</v>
+        <v>-2004</v>
       </c>
       <c r="D15" s="60">
-        <v>-2004</v>
+        <v>-9086</v>
       </c>
       <c r="E15" s="60">
-        <v>-9086</v>
+        <v>599</v>
       </c>
       <c r="F15" s="60">
-        <v>599</v>
+        <v>-586</v>
       </c>
       <c r="G15" s="60">
-        <v>-586</v>
-      </c>
-      <c r="H15" s="60">
         <v>-2769</v>
       </c>
+      <c r="H15" s="69">
+        <v>4574</v>
+      </c>
       <c r="I15" s="69">
-        <v>4574</v>
+        <v>338</v>
       </c>
       <c r="J15" s="69">
-        <v>338</v>
+        <v>-3946</v>
       </c>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="21"/>
       <c r="N15" s="68">
         <f t="shared" si="0"/>
-        <v>1557</v>
+        <v>-1803</v>
       </c>
       <c r="O15" s="7"/>
       <c r="P15" s="79">
         <f t="shared" si="1"/>
-        <v>4574</v>
+        <v>338</v>
       </c>
       <c r="Q15" s="63">
         <f t="shared" si="2"/>
-        <v>338</v>
+        <v>-3946</v>
       </c>
       <c r="R15" s="75">
         <f t="shared" si="3"/>
-        <v>-0.92610406646261478</v>
+        <v>-12.674556213017752</v>
       </c>
       <c r="S15" s="7"/>
     </row>
-    <row r="16" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="27">
-        <v>282</v>
+        <v>350</v>
       </c>
       <c r="D16" s="27">
-        <v>350</v>
+        <v>-7903</v>
       </c>
       <c r="E16" s="27">
-        <v>-7903</v>
+        <v>-752</v>
       </c>
       <c r="F16" s="27">
-        <v>-752</v>
+        <v>-301</v>
       </c>
       <c r="G16" s="27">
-        <v>-301</v>
-      </c>
-      <c r="H16" s="27">
         <v>-255</v>
       </c>
+      <c r="H16" s="42">
+        <v>-304</v>
+      </c>
       <c r="I16" s="42">
-        <v>-304</v>
+        <v>-671</v>
       </c>
       <c r="J16" s="42">
-        <v>-671</v>
+        <v>-335</v>
       </c>
       <c r="K16" s="20"/>
       <c r="L16" s="20"/>
       <c r="M16" s="20"/>
       <c r="N16" s="48">
         <f t="shared" si="0"/>
-        <v>-1531</v>
+        <v>-1565</v>
       </c>
       <c r="P16" s="58">
         <f t="shared" si="1"/>
-        <v>-304</v>
+        <v>-671</v>
       </c>
       <c r="Q16" s="20">
         <f t="shared" si="2"/>
-        <v>-671</v>
+        <v>-335</v>
       </c>
       <c r="R16" s="59">
         <f t="shared" si="3"/>
-        <v>-1.2072368421052631</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>0.50074515648286144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C17" s="35">
-        <v>-437</v>
+        <v>-1654</v>
       </c>
       <c r="D17" s="35">
-        <v>-1654</v>
+        <v>-16989</v>
       </c>
       <c r="E17" s="35">
-        <v>-16989</v>
+        <v>-153</v>
       </c>
       <c r="F17" s="35">
-        <v>-153</v>
+        <v>-887</v>
       </c>
       <c r="G17" s="35">
-        <v>-887</v>
-      </c>
-      <c r="H17" s="35">
         <v>-3024</v>
       </c>
+      <c r="H17" s="44">
+        <v>4270</v>
+      </c>
       <c r="I17" s="44">
-        <v>4270</v>
+        <v>-333</v>
       </c>
       <c r="J17" s="44">
-        <v>-333</v>
+        <v>-4281</v>
       </c>
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
       <c r="N17" s="100">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>-3368</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="81">
         <f t="shared" si="1"/>
-        <v>4270</v>
+        <v>-333</v>
       </c>
       <c r="Q17" s="82">
         <f t="shared" si="2"/>
-        <v>-333</v>
+        <v>-4281</v>
       </c>
       <c r="R17" s="77">
         <f t="shared" si="3"/>
-        <v>-1.0779859484777519</v>
+        <v>-11.855855855855856</v>
       </c>
       <c r="S17" s="7"/>
     </row>
-    <row r="18" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="12" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="27">
-        <v>-56</v>
+        <v>-44</v>
       </c>
       <c r="D18" s="27">
-        <v>-44</v>
+        <v>-350</v>
       </c>
       <c r="E18" s="27">
-        <v>-350</v>
+        <v>-27</v>
       </c>
       <c r="F18" s="27">
-        <v>-27</v>
+        <v>-66</v>
       </c>
       <c r="G18" s="27">
-        <v>-66</v>
-      </c>
-      <c r="H18" s="27">
         <v>-106</v>
       </c>
+      <c r="H18" s="42">
+        <v>207</v>
+      </c>
       <c r="I18" s="42">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="J18" s="42">
-        <v>258</v>
+        <v>553</v>
       </c>
       <c r="K18" s="20"/>
       <c r="L18" s="20"/>
       <c r="M18" s="20"/>
       <c r="N18" s="48">
         <f t="shared" si="0"/>
-        <v>293</v>
+        <v>912</v>
       </c>
       <c r="P18" s="58">
         <f t="shared" si="1"/>
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="Q18" s="20">
         <f t="shared" si="2"/>
-        <v>258</v>
+        <v>553</v>
       </c>
       <c r="R18" s="59">
         <f t="shared" si="3"/>
-        <v>0.24637681159420291</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>1.1434108527131783</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="60">
-        <v>-381</v>
+        <v>-1610</v>
       </c>
       <c r="D19" s="60">
-        <v>-1610</v>
+        <v>-16639</v>
       </c>
       <c r="E19" s="60">
-        <v>-16639</v>
+        <v>-126</v>
       </c>
       <c r="F19" s="60">
-        <v>-126</v>
+        <v>-821</v>
       </c>
       <c r="G19" s="60">
-        <v>-821</v>
-      </c>
-      <c r="H19" s="60">
         <v>-2918</v>
       </c>
+      <c r="H19" s="69">
+        <v>4063</v>
+      </c>
       <c r="I19" s="69">
-        <v>4063</v>
+        <v>-591</v>
       </c>
       <c r="J19" s="69">
-        <v>-591</v>
+        <v>-3728</v>
       </c>
       <c r="K19" s="21"/>
       <c r="L19" s="21"/>
       <c r="M19" s="21"/>
       <c r="N19" s="68">
         <f t="shared" si="0"/>
-        <v>-267</v>
+        <v>-3174</v>
       </c>
       <c r="O19" s="7"/>
       <c r="P19" s="79">
         <f t="shared" si="1"/>
-        <v>4063</v>
+        <v>-591</v>
       </c>
       <c r="Q19" s="63">
         <f t="shared" si="2"/>
-        <v>-591</v>
+        <v>-3728</v>
       </c>
       <c r="R19" s="75">
         <f t="shared" si="3"/>
-        <v>-1.1454590204282551</v>
+        <v>-5.3079526226734348</v>
       </c>
       <c r="S19" s="7"/>
     </row>
-    <row r="20" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="27">
-        <v>4242</v>
+        <v>4267</v>
       </c>
       <c r="D20" s="27">
-        <v>4267</v>
+        <v>4292</v>
       </c>
       <c r="E20" s="27">
-        <v>4292</v>
+        <v>4319</v>
       </c>
       <c r="F20" s="27">
-        <v>4319</v>
+        <v>4343</v>
       </c>
       <c r="G20" s="27">
-        <v>4343</v>
-      </c>
-      <c r="H20" s="27">
         <v>4369</v>
       </c>
+      <c r="H20" s="42">
+        <v>4514</v>
+      </c>
       <c r="I20" s="42">
-        <v>4514</v>
+        <v>4856</v>
       </c>
       <c r="J20" s="42">
-        <v>4856</v>
+        <v>5083</v>
       </c>
       <c r="K20" s="20"/>
       <c r="L20" s="20"/>
       <c r="M20" s="20"/>
       <c r="N20" s="48">
         <f>AVERAGE(G20:J20)</f>
-        <v>4520.5</v>
+        <v>4705.5</v>
       </c>
       <c r="P20" s="58">
         <f t="shared" si="1"/>
-        <v>4514</v>
+        <v>4856</v>
       </c>
       <c r="Q20" s="20">
         <f t="shared" si="2"/>
-        <v>4856</v>
+        <v>5083</v>
       </c>
       <c r="R20" s="59">
         <f t="shared" si="3"/>
-        <v>7.5764288879042976E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>4.6746293245469521E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="12" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="27">
-        <v>4242</v>
+        <v>4267</v>
       </c>
       <c r="D21" s="27">
-        <v>4267</v>
+        <v>4292</v>
       </c>
       <c r="E21" s="27">
-        <v>4292</v>
+        <v>4319</v>
       </c>
       <c r="F21" s="27">
-        <v>4319</v>
+        <v>4343</v>
       </c>
       <c r="G21" s="27">
-        <v>4343</v>
-      </c>
-      <c r="H21" s="27">
         <v>4369</v>
       </c>
+      <c r="H21" s="42">
+        <v>4531</v>
+      </c>
       <c r="I21" s="42">
-        <v>4531</v>
+        <v>4856</v>
       </c>
       <c r="J21" s="42">
-        <v>4856</v>
+        <v>5083</v>
       </c>
       <c r="K21" s="20"/>
       <c r="L21" s="20"/>
       <c r="M21" s="20"/>
       <c r="N21" s="48">
         <f>AVERAGE((G21:J21))</f>
-        <v>4524.75</v>
+        <v>4709.75</v>
       </c>
       <c r="P21" s="58">
         <f t="shared" si="1"/>
-        <v>4531</v>
+        <v>4856</v>
       </c>
       <c r="Q21" s="20">
         <f t="shared" si="2"/>
-        <v>4856</v>
+        <v>5083</v>
       </c>
       <c r="R21" s="59">
         <f t="shared" si="3"/>
-        <v>7.1728095343191342E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>4.6746293245469521E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="12" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="31">
-        <v>-0.09</v>
+        <v>-0.38</v>
       </c>
       <c r="D22" s="31">
-        <v>-0.38</v>
+        <v>-3.88</v>
       </c>
       <c r="E22" s="31">
-        <v>-3.88</v>
+        <v>-0.03</v>
       </c>
       <c r="F22" s="31">
-        <v>-0.03</v>
+        <v>-0.19</v>
       </c>
       <c r="G22" s="31">
-        <v>-0.19</v>
-      </c>
-      <c r="H22" s="31">
         <v>-0.67</v>
       </c>
+      <c r="H22" s="45">
+        <v>0.9</v>
+      </c>
       <c r="I22" s="45">
-        <v>0.9</v>
+        <v>-0.12</v>
       </c>
       <c r="J22" s="45">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
       <c r="N22" s="49">
         <f>N19/N20</f>
-        <v>-5.9064262802787301E-2</v>
+        <v>-0.67452980554670072</v>
       </c>
       <c r="P22" s="83">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>-0.12</v>
       </c>
       <c r="Q22" s="84">
         <f t="shared" si="2"/>
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="R22" s="59">
         <f t="shared" si="3"/>
-        <v>-1.1333333333333333</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" s="16" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>-5.083333333333333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" s="16" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="32">
-        <v>-0.09</v>
+        <v>-0.38</v>
       </c>
       <c r="D23" s="32">
-        <v>-0.38</v>
+        <v>-3.88</v>
       </c>
       <c r="E23" s="32">
-        <v>-3.88</v>
+        <v>-0.03</v>
       </c>
       <c r="F23" s="32">
-        <v>-0.03</v>
+        <v>-0.19</v>
       </c>
       <c r="G23" s="32">
-        <v>-0.19</v>
-      </c>
-      <c r="H23" s="32">
         <v>-0.67</v>
       </c>
+      <c r="H23" s="46">
+        <v>0.9</v>
+      </c>
       <c r="I23" s="46">
-        <v>0.9</v>
+        <v>-0.12</v>
       </c>
       <c r="J23" s="46">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
       <c r="M23" s="25"/>
       <c r="N23" s="50">
         <f>N19/N21</f>
-        <v>-5.9008785015746724E-2</v>
+        <v>-0.67392112107861346</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="85">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>-0.12</v>
       </c>
       <c r="Q23" s="86">
         <f t="shared" si="2"/>
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="R23" s="78">
         <f t="shared" si="3"/>
-        <v>-1.1333333333333333</v>
+        <v>-5.083333333333333</v>
       </c>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" s="16" customFormat="1" ht="17" collapsed="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" s="16" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="6"/>
+      <c r="D24" s="6"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -8440,73 +8441,73 @@
       <c r="O25" s="4"/>
       <c r="S25" s="4"/>
     </row>
-    <row r="26" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C26" s="27">
-        <v>6923</v>
+        <v>11287</v>
       </c>
       <c r="D26" s="27">
-        <v>11287</v>
+        <v>8785</v>
       </c>
       <c r="E26" s="27">
-        <v>8785</v>
+        <v>8249</v>
       </c>
       <c r="F26" s="27">
-        <v>8249</v>
+        <v>8947</v>
       </c>
       <c r="G26" s="27">
-        <v>8947</v>
+        <v>9643</v>
       </c>
       <c r="H26" s="27">
-        <v>9643</v>
+        <v>11141</v>
       </c>
       <c r="I26" s="27">
-        <v>11141</v>
+        <v>14265</v>
       </c>
       <c r="J26" s="27">
-        <v>14265</v>
+        <v>17247</v>
       </c>
       <c r="K26" s="20"/>
       <c r="L26" s="20"/>
       <c r="M26" s="20"/>
     </row>
-    <row r="27" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C27" s="27">
-        <v>14388</v>
+        <v>17986</v>
       </c>
       <c r="D27" s="27">
-        <v>17986</v>
+        <v>15301</v>
       </c>
       <c r="E27" s="27">
-        <v>15301</v>
+        <v>13813</v>
       </c>
       <c r="F27" s="27">
-        <v>13813</v>
+        <v>12101</v>
       </c>
       <c r="G27" s="27">
-        <v>12101</v>
+        <v>11563</v>
       </c>
       <c r="H27" s="27">
-        <v>11563</v>
+        <v>19794</v>
       </c>
       <c r="I27" s="27">
-        <v>19794</v>
+        <v>23151</v>
       </c>
       <c r="J27" s="27">
-        <v>23151</v>
+        <v>15542</v>
       </c>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
       <c r="M27" s="20"/>
     </row>
-    <row r="28" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C28" s="27">
         <v>0</v>
@@ -8536,71 +8537,71 @@
       <c r="L28" s="20"/>
       <c r="M28" s="20"/>
     </row>
-    <row r="29" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="27">
-        <v>3323</v>
+        <v>3131</v>
       </c>
       <c r="D29" s="27">
-        <v>3131</v>
+        <v>3121</v>
       </c>
       <c r="E29" s="27">
-        <v>3121</v>
+        <v>3478</v>
       </c>
       <c r="F29" s="27">
-        <v>3478</v>
+        <v>3064</v>
       </c>
       <c r="G29" s="27">
-        <v>3064</v>
+        <v>2360</v>
       </c>
       <c r="H29" s="27">
-        <v>2360</v>
+        <v>3202</v>
       </c>
       <c r="I29" s="27">
-        <v>3202</v>
+        <v>3839</v>
       </c>
       <c r="J29" s="27">
-        <v>3839</v>
+        <v>4066</v>
       </c>
       <c r="K29" s="20"/>
       <c r="L29" s="20"/>
       <c r="M29" s="20"/>
     </row>
-    <row r="30" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="27">
-        <v>11494</v>
+        <v>11244</v>
       </c>
       <c r="D30" s="27">
-        <v>11244</v>
+        <v>12062</v>
       </c>
       <c r="E30" s="27">
-        <v>12062</v>
+        <v>12198</v>
       </c>
       <c r="F30" s="27">
-        <v>12198</v>
+        <v>12281</v>
       </c>
       <c r="G30" s="27">
-        <v>12281</v>
+        <v>11377</v>
       </c>
       <c r="H30" s="27">
-        <v>11377</v>
+        <v>11489</v>
       </c>
       <c r="I30" s="27">
-        <v>11489</v>
+        <v>11618</v>
       </c>
       <c r="J30" s="27">
-        <v>11618</v>
+        <v>12426</v>
       </c>
       <c r="K30" s="20"/>
       <c r="L30" s="20"/>
       <c r="M30" s="20"/>
     </row>
-    <row r="31" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
         <v>49</v>
       </c>
@@ -8632,137 +8633,137 @@
       <c r="L31" s="20"/>
       <c r="M31" s="20"/>
     </row>
-    <row r="32" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C32" s="27">
-        <v>6480</v>
+        <v>7181</v>
       </c>
       <c r="D32" s="27">
-        <v>7181</v>
+        <v>6868</v>
       </c>
       <c r="E32" s="27">
-        <v>6868</v>
+        <v>9586</v>
       </c>
       <c r="F32" s="27">
-        <v>9586</v>
+        <v>5741</v>
       </c>
       <c r="G32" s="27">
-        <v>5741</v>
+        <v>8432</v>
       </c>
       <c r="H32" s="27">
-        <v>8432</v>
+        <v>6105</v>
       </c>
       <c r="I32" s="27">
-        <v>6105</v>
+        <v>10815</v>
       </c>
       <c r="J32" s="27">
-        <v>10815</v>
+        <v>12876</v>
       </c>
       <c r="K32" s="20"/>
       <c r="L32" s="20"/>
       <c r="M32" s="20"/>
     </row>
-    <row r="33" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B33" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="64">
-        <v>42608</v>
+        <v>50829</v>
       </c>
       <c r="D33" s="64">
-        <v>50829</v>
+        <v>46137</v>
       </c>
       <c r="E33" s="64">
-        <v>46137</v>
+        <v>47324</v>
       </c>
       <c r="F33" s="64">
-        <v>47324</v>
+        <v>42134</v>
       </c>
       <c r="G33" s="64">
-        <v>42134</v>
+        <v>43375</v>
       </c>
       <c r="H33" s="64">
-        <v>43375</v>
+        <v>51731</v>
       </c>
       <c r="I33" s="64">
-        <v>51731</v>
+        <v>63688</v>
       </c>
       <c r="J33" s="64">
-        <v>63688</v>
+        <v>62157</v>
       </c>
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
       <c r="M33" s="21"/>
     </row>
-    <row r="34" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="99" t="s">
         <v>28</v>
       </c>
       <c r="C34" s="27">
-        <v>99924</v>
+        <v>103398</v>
       </c>
       <c r="D34" s="27">
-        <v>103398</v>
+        <v>104248</v>
       </c>
       <c r="E34" s="27">
-        <v>104248</v>
+        <v>107919</v>
       </c>
       <c r="F34" s="27">
-        <v>107919</v>
+        <v>109763</v>
       </c>
       <c r="G34" s="27">
-        <v>109763</v>
+        <v>109510</v>
       </c>
       <c r="H34" s="27">
-        <v>109510</v>
+        <v>105047</v>
       </c>
       <c r="I34" s="27">
-        <v>105047</v>
+        <v>105414</v>
       </c>
       <c r="J34" s="27">
-        <v>105414</v>
+        <v>104458</v>
       </c>
       <c r="K34" s="20"/>
       <c r="L34" s="20"/>
       <c r="M34" s="20"/>
     </row>
-    <row r="35" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C35" s="27">
-        <v>6139</v>
+        <v>5824</v>
       </c>
       <c r="D35" s="27">
-        <v>5824</v>
+        <v>5496</v>
       </c>
       <c r="E35" s="27">
-        <v>5496</v>
+        <v>5383</v>
       </c>
       <c r="F35" s="27">
+        <v>5027</v>
+      </c>
+      <c r="G35" s="27">
         <v>5383</v>
       </c>
-      <c r="G35" s="27">
-        <v>5027</v>
-      </c>
       <c r="H35" s="27">
-        <v>5383</v>
+        <v>8667</v>
       </c>
       <c r="I35" s="27">
-        <v>8667</v>
+        <v>8512</v>
       </c>
       <c r="J35" s="27">
-        <v>8512</v>
+        <v>8481</v>
       </c>
       <c r="K35" s="20"/>
       <c r="L35" s="20"/>
       <c r="M35" s="20"/>
     </row>
-    <row r="36" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C36" s="27">
         <v>0</v>
@@ -8792,24 +8793,24 @@
       <c r="L36" s="20"/>
       <c r="M36" s="20"/>
     </row>
-    <row r="37" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="27">
-        <v>27440</v>
+        <v>27442</v>
       </c>
       <c r="D37" s="27">
-        <v>27442</v>
+        <v>24680</v>
       </c>
       <c r="E37" s="27">
-        <v>24680</v>
+        <v>24693</v>
       </c>
       <c r="F37" s="27">
         <v>24693</v>
       </c>
       <c r="G37" s="27">
-        <v>24693</v>
+        <v>23912</v>
       </c>
       <c r="H37" s="27">
         <v>23912</v>
@@ -8818,144 +8819,144 @@
         <v>23912</v>
       </c>
       <c r="J37" s="27">
-        <v>23912</v>
+        <v>20465</v>
       </c>
       <c r="K37" s="20"/>
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
     </row>
-    <row r="38" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C38" s="27">
-        <v>4675</v>
+        <v>4383</v>
       </c>
       <c r="D38" s="27">
-        <v>4383</v>
+        <v>3975</v>
       </c>
       <c r="E38" s="27">
-        <v>3975</v>
+        <v>3691</v>
       </c>
       <c r="F38" s="27">
-        <v>3691</v>
+        <v>3568</v>
       </c>
       <c r="G38" s="27">
-        <v>3568</v>
+        <v>3057</v>
       </c>
       <c r="H38" s="27">
-        <v>3057</v>
+        <v>2877</v>
       </c>
       <c r="I38" s="27">
-        <v>2877</v>
+        <v>2772</v>
       </c>
       <c r="J38" s="27">
-        <v>2772</v>
+        <v>2722</v>
       </c>
       <c r="K38" s="20"/>
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
     </row>
-    <row r="39" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="27">
-        <v>11947</v>
+        <v>14329</v>
       </c>
       <c r="D39" s="27">
-        <v>14329</v>
+        <v>9006</v>
       </c>
       <c r="E39" s="27">
-        <v>9006</v>
+        <v>7475</v>
       </c>
       <c r="F39" s="27">
-        <v>7475</v>
+        <v>7057</v>
       </c>
       <c r="G39" s="27">
-        <v>7057</v>
+        <v>7283</v>
       </c>
       <c r="H39" s="27">
-        <v>7283</v>
+        <v>12280</v>
       </c>
       <c r="I39" s="27">
-        <v>12280</v>
+        <v>7131</v>
       </c>
       <c r="J39" s="27">
-        <v>7131</v>
+        <v>7049</v>
       </c>
       <c r="K39" s="20"/>
       <c r="L39" s="20"/>
       <c r="M39" s="20"/>
     </row>
-    <row r="40" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="65">
-        <f t="shared" ref="C40:I40" si="9">SUM(C34:C39)</f>
-        <v>150125</v>
+        <f t="shared" ref="C40:I40" si="8">SUM(C34:C39)</f>
+        <v>155376</v>
       </c>
       <c r="D40" s="65">
+        <f t="shared" si="8"/>
+        <v>147405</v>
+      </c>
+      <c r="E40" s="65">
+        <f t="shared" si="8"/>
+        <v>149161</v>
+      </c>
+      <c r="F40" s="65">
+        <f t="shared" si="8"/>
+        <v>150108</v>
+      </c>
+      <c r="G40" s="65">
+        <f t="shared" si="8"/>
+        <v>149145</v>
+      </c>
+      <c r="H40" s="65">
+        <f t="shared" si="8"/>
+        <v>152783</v>
+      </c>
+      <c r="I40" s="65">
+        <f t="shared" ref="I40:J40" si="9">SUM(I34:I39)</f>
+        <v>147741</v>
+      </c>
+      <c r="J40" s="65">
         <f t="shared" si="9"/>
-        <v>155376</v>
-      </c>
-      <c r="E40" s="65">
-        <f t="shared" si="9"/>
-        <v>147405</v>
-      </c>
-      <c r="F40" s="65">
-        <f t="shared" si="9"/>
-        <v>149161</v>
-      </c>
-      <c r="G40" s="65">
-        <f t="shared" si="9"/>
-        <v>150108</v>
-      </c>
-      <c r="H40" s="65">
-        <f t="shared" si="9"/>
-        <v>149145</v>
-      </c>
-      <c r="I40" s="65">
-        <f t="shared" si="9"/>
-        <v>152783</v>
-      </c>
-      <c r="J40" s="65">
-        <f t="shared" ref="J40" si="10">SUM(J34:J39)</f>
-        <v>147741</v>
+        <v>143175</v>
       </c>
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
       <c r="M40" s="21"/>
     </row>
-    <row r="41" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
       <c r="B41" s="17" t="s">
         <v>32</v>
       </c>
       <c r="C41" s="60">
-        <v>192733</v>
+        <v>206205</v>
       </c>
       <c r="D41" s="60">
-        <v>206205</v>
+        <v>193542</v>
       </c>
       <c r="E41" s="60">
-        <v>193542</v>
+        <v>196485</v>
       </c>
       <c r="F41" s="60">
-        <v>196485</v>
+        <v>192242</v>
       </c>
       <c r="G41" s="60">
-        <v>192242</v>
+        <v>192520</v>
       </c>
       <c r="H41" s="60">
-        <v>192520</v>
+        <v>204514</v>
       </c>
       <c r="I41" s="60">
-        <v>204514</v>
+        <v>211429</v>
       </c>
       <c r="J41" s="60">
-        <v>211429</v>
+        <v>205332</v>
       </c>
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
@@ -8963,137 +8964,137 @@
       <c r="O41" s="7"/>
       <c r="S41" s="7"/>
     </row>
-    <row r="42" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C42" s="27">
-        <v>4581</v>
+        <v>4695</v>
       </c>
       <c r="D42" s="27">
-        <v>4695</v>
+        <v>3765</v>
       </c>
       <c r="E42" s="27">
-        <v>3765</v>
+        <v>3729</v>
       </c>
       <c r="F42" s="27">
-        <v>3729</v>
+        <v>5240</v>
       </c>
       <c r="G42" s="27">
-        <v>5240</v>
+        <v>6731</v>
       </c>
       <c r="H42" s="27">
-        <v>6731</v>
+        <v>2496</v>
       </c>
       <c r="I42" s="27">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="J42" s="27">
-        <v>2499</v>
+        <v>2004</v>
       </c>
       <c r="K42" s="20"/>
       <c r="L42" s="20"/>
       <c r="M42" s="20"/>
     </row>
-    <row r="43" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C43" s="27">
-        <v>8559</v>
+        <v>9618</v>
       </c>
       <c r="D43" s="27">
-        <v>9618</v>
+        <v>11074</v>
       </c>
       <c r="E43" s="27">
-        <v>11074</v>
+        <v>12556</v>
       </c>
       <c r="F43" s="27">
-        <v>12556</v>
+        <v>10896</v>
       </c>
       <c r="G43" s="27">
-        <v>10896</v>
+        <v>10666</v>
       </c>
       <c r="H43" s="27">
-        <v>10666</v>
+        <v>10268</v>
       </c>
       <c r="I43" s="27">
-        <v>10268</v>
+        <v>9882</v>
       </c>
       <c r="J43" s="27">
-        <v>9882</v>
+        <v>7159</v>
       </c>
       <c r="K43" s="20"/>
       <c r="L43" s="20"/>
       <c r="M43" s="20"/>
     </row>
-    <row r="44" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C44" s="27">
-        <v>2506</v>
+        <v>2651</v>
       </c>
       <c r="D44" s="27">
-        <v>2651</v>
+        <v>5015</v>
       </c>
       <c r="E44" s="27">
-        <v>5015</v>
+        <v>3343</v>
       </c>
       <c r="F44" s="27">
-        <v>3343</v>
+        <v>2652</v>
       </c>
       <c r="G44" s="27">
-        <v>2652</v>
+        <v>4249</v>
       </c>
       <c r="H44" s="27">
-        <v>4249</v>
+        <v>3756</v>
       </c>
       <c r="I44" s="27">
-        <v>3756</v>
+        <v>3990</v>
       </c>
       <c r="J44" s="27">
-        <v>3990</v>
+        <v>2824</v>
       </c>
       <c r="K44" s="20"/>
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
     </row>
-    <row r="45" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C45" s="27">
-        <v>346</v>
+        <v>1856</v>
       </c>
       <c r="D45" s="27">
-        <v>1856</v>
+        <v>2440</v>
       </c>
       <c r="E45" s="27">
-        <v>2440</v>
+        <v>1756</v>
       </c>
       <c r="F45" s="27">
-        <v>1756</v>
+        <v>1873</v>
       </c>
       <c r="G45" s="27">
-        <v>1873</v>
+        <v>887</v>
       </c>
       <c r="H45" s="27">
-        <v>887</v>
+        <v>825</v>
       </c>
       <c r="I45" s="27">
-        <v>825</v>
+        <v>604</v>
       </c>
       <c r="J45" s="27">
-        <v>604</v>
+        <v>0</v>
       </c>
       <c r="K45" s="20"/>
       <c r="L45" s="20"/>
       <c r="M45" s="20"/>
     </row>
-    <row r="46" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="27">
         <v>0</v>
@@ -9123,7 +9124,7 @@
       <c r="L46" s="20"/>
       <c r="M46" s="20"/>
     </row>
-    <row r="47" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
         <v>49</v>
       </c>
@@ -9155,105 +9156,105 @@
       <c r="L47" s="20"/>
       <c r="M47" s="20"/>
     </row>
-    <row r="48" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C48" s="27">
-        <v>11221</v>
+        <v>13207</v>
       </c>
       <c r="D48" s="27">
-        <v>13207</v>
+        <v>12865</v>
       </c>
       <c r="E48" s="27">
-        <v>12865</v>
+        <v>14282</v>
       </c>
       <c r="F48" s="27">
-        <v>14282</v>
+        <v>11513</v>
       </c>
       <c r="G48" s="27">
-        <v>11513</v>
+        <v>12433</v>
       </c>
       <c r="H48" s="27">
-        <v>12433</v>
+        <v>14952</v>
       </c>
       <c r="I48" s="27">
-        <v>14952</v>
+        <v>14600</v>
       </c>
       <c r="J48" s="27">
-        <v>14600</v>
+        <v>14898</v>
       </c>
       <c r="K48" s="20"/>
       <c r="L48" s="20"/>
       <c r="M48" s="20"/>
     </row>
-    <row r="49" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B49" s="11" t="s">
         <v>40</v>
       </c>
       <c r="C49" s="64">
-        <v>27213</v>
+        <v>32027</v>
       </c>
       <c r="D49" s="64">
-        <v>32027</v>
+        <v>35159</v>
       </c>
       <c r="E49" s="64">
-        <v>35159</v>
+        <v>35666</v>
       </c>
       <c r="F49" s="64">
-        <v>35666</v>
+        <v>32174</v>
       </c>
       <c r="G49" s="64">
-        <v>32174</v>
+        <v>34966</v>
       </c>
       <c r="H49" s="64">
-        <v>34966</v>
+        <v>32297</v>
       </c>
       <c r="I49" s="64">
-        <v>32297</v>
+        <v>31575</v>
       </c>
       <c r="J49" s="64">
-        <v>31575</v>
+        <v>26885</v>
       </c>
       <c r="K49" s="21"/>
       <c r="L49" s="21"/>
       <c r="M49" s="21"/>
     </row>
-    <row r="50" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B50" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C50" s="27">
-        <v>47869</v>
+        <v>48334</v>
       </c>
       <c r="D50" s="27">
-        <v>48334</v>
+        <v>46471</v>
       </c>
       <c r="E50" s="27">
-        <v>46471</v>
+        <v>46282</v>
       </c>
       <c r="F50" s="27">
-        <v>46282</v>
+        <v>44911</v>
       </c>
       <c r="G50" s="27">
-        <v>44911</v>
+        <v>44026</v>
       </c>
       <c r="H50" s="27">
-        <v>44026</v>
+        <v>44057</v>
       </c>
       <c r="I50" s="27">
-        <v>44057</v>
+        <v>44086</v>
       </c>
       <c r="J50" s="27">
-        <v>44086</v>
+        <v>43027</v>
       </c>
       <c r="K50" s="20"/>
       <c r="L50" s="20"/>
       <c r="M50" s="20"/>
     </row>
-    <row r="51" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B51" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C51" s="27">
         <v>0</v>
@@ -9283,9 +9284,9 @@
       <c r="L51" s="20"/>
       <c r="M51" s="20"/>
     </row>
-    <row r="52" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B52" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C52" s="27">
         <v>0</v>
@@ -9315,9 +9316,9 @@
       <c r="L52" s="20"/>
       <c r="M52" s="20"/>
     </row>
-    <row r="53" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B53" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C53" s="27">
         <v>0</v>
@@ -9347,114 +9348,114 @@
       <c r="L53" s="20"/>
       <c r="M53" s="20"/>
     </row>
-    <row r="54" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B54" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C54" s="27">
-        <v>6895</v>
+        <v>5410</v>
       </c>
       <c r="D54" s="27">
-        <v>5410</v>
+        <v>7048</v>
       </c>
       <c r="E54" s="27">
-        <v>7048</v>
+        <v>9505</v>
       </c>
       <c r="F54" s="27">
-        <v>9505</v>
+        <v>8744</v>
       </c>
       <c r="G54" s="27">
-        <v>8744</v>
+        <v>7777</v>
       </c>
       <c r="H54" s="27">
-        <v>7777</v>
+        <v>11430</v>
       </c>
       <c r="I54" s="27">
-        <v>11430</v>
+        <v>9408</v>
       </c>
       <c r="J54" s="27">
-        <v>9408</v>
+        <v>10431</v>
       </c>
       <c r="K54" s="20"/>
       <c r="L54" s="20"/>
       <c r="M54" s="20"/>
     </row>
-    <row r="55" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="11" t="s">
         <v>38</v>
       </c>
       <c r="C55" s="65">
-        <f>SUM(C50:C54)</f>
-        <v>54764</v>
+        <f t="shared" ref="C55:H55" si="10">SUM(C50:C54)</f>
+        <v>53744</v>
       </c>
       <c r="D55" s="65">
-        <f t="shared" ref="D55:I55" si="11">SUM(D50:D54)</f>
-        <v>53744</v>
+        <f t="shared" si="10"/>
+        <v>53519</v>
       </c>
       <c r="E55" s="65">
+        <f t="shared" si="10"/>
+        <v>55787</v>
+      </c>
+      <c r="F55" s="65">
+        <f t="shared" si="10"/>
+        <v>53655</v>
+      </c>
+      <c r="G55" s="65">
+        <f t="shared" si="10"/>
+        <v>51803</v>
+      </c>
+      <c r="H55" s="65">
+        <f t="shared" si="10"/>
+        <v>55487</v>
+      </c>
+      <c r="I55" s="65">
+        <f t="shared" ref="I55:J55" si="11">SUM(I50:I54)</f>
+        <v>53494</v>
+      </c>
+      <c r="J55" s="65">
         <f t="shared" si="11"/>
-        <v>53519</v>
-      </c>
-      <c r="F55" s="65">
-        <f t="shared" si="11"/>
-        <v>55787</v>
-      </c>
-      <c r="G55" s="65">
-        <f t="shared" si="11"/>
-        <v>53655</v>
-      </c>
-      <c r="H55" s="65">
-        <f t="shared" si="11"/>
-        <v>51803</v>
-      </c>
-      <c r="I55" s="65">
-        <f t="shared" si="11"/>
-        <v>55487</v>
-      </c>
-      <c r="J55" s="65">
-        <f t="shared" ref="J55" si="12">SUM(J50:J54)</f>
-        <v>53494</v>
+        <v>53458</v>
       </c>
       <c r="K55" s="21"/>
       <c r="L55" s="21"/>
       <c r="M55" s="21"/>
     </row>
-    <row r="56" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7"/>
       <c r="B56" s="17" t="s">
         <v>39</v>
       </c>
       <c r="C56" s="63">
-        <f t="shared" ref="C56:H56" si="13">C49+C55</f>
-        <v>81977</v>
+        <f t="shared" ref="C56:H56" si="12">C49+C55</f>
+        <v>85771</v>
       </c>
       <c r="D56" s="63">
-        <f t="shared" si="13"/>
-        <v>85771</v>
+        <f t="shared" si="12"/>
+        <v>88678</v>
       </c>
       <c r="E56" s="63">
-        <f t="shared" si="13"/>
-        <v>88678</v>
+        <f t="shared" si="12"/>
+        <v>91453</v>
       </c>
       <c r="F56" s="63">
-        <f t="shared" si="13"/>
-        <v>91453</v>
+        <f t="shared" si="12"/>
+        <v>85829</v>
       </c>
       <c r="G56" s="63">
-        <f t="shared" si="13"/>
-        <v>85829</v>
+        <f t="shared" si="12"/>
+        <v>86769</v>
       </c>
       <c r="H56" s="63">
-        <f t="shared" si="13"/>
-        <v>86769</v>
+        <f>H49+H55</f>
+        <v>87784</v>
       </c>
       <c r="I56" s="63">
         <f>I49+I55</f>
-        <v>87784</v>
+        <v>85069</v>
       </c>
       <c r="J56" s="63">
         <f>J49+J55</f>
-        <v>85069</v>
+        <v>80343</v>
       </c>
       <c r="K56" s="21"/>
       <c r="L56" s="21"/>
@@ -9462,7 +9463,7 @@
       <c r="O56" s="7"/>
       <c r="S56" s="7"/>
     </row>
-    <row r="57" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B57" s="9" t="s">
         <v>41</v>
       </c>
@@ -9494,137 +9495,137 @@
       <c r="L57" s="20"/>
       <c r="M57" s="20"/>
     </row>
-    <row r="58" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B58" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C58" s="27">
-        <v>38291</v>
+        <v>49763</v>
       </c>
       <c r="D58" s="27">
-        <v>49763</v>
+        <v>50665</v>
       </c>
       <c r="E58" s="27">
-        <v>50665</v>
+        <v>50949</v>
       </c>
       <c r="F58" s="27">
-        <v>50949</v>
+        <v>51920</v>
       </c>
       <c r="G58" s="27">
-        <v>51920</v>
+        <v>52334</v>
       </c>
       <c r="H58" s="27">
-        <v>52334</v>
+        <v>56755</v>
       </c>
       <c r="I58" s="27">
-        <v>56755</v>
+        <v>65185</v>
       </c>
       <c r="J58" s="27">
-        <v>65185</v>
+        <v>66259</v>
       </c>
       <c r="K58" s="20"/>
       <c r="L58" s="20"/>
       <c r="M58" s="20"/>
     </row>
-    <row r="59" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B59" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C59" s="27">
-        <v>-542</v>
+        <v>-696</v>
       </c>
       <c r="D59" s="27">
-        <v>-696</v>
+        <v>-185</v>
       </c>
       <c r="E59" s="27">
-        <v>-185</v>
+        <v>-711</v>
       </c>
       <c r="F59" s="27">
-        <v>-711</v>
+        <v>-486</v>
       </c>
       <c r="G59" s="27">
-        <v>-486</v>
+        <v>65</v>
       </c>
       <c r="H59" s="27">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="I59" s="27">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="J59" s="27">
-        <v>113</v>
+        <v>-44</v>
       </c>
       <c r="K59" s="20"/>
       <c r="L59" s="20"/>
       <c r="M59" s="20"/>
     </row>
-    <row r="60" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B60" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C60" s="27">
-        <v>68224</v>
+        <v>66162</v>
       </c>
       <c r="D60" s="27">
-        <v>66162</v>
+        <v>49052</v>
       </c>
       <c r="E60" s="27">
-        <v>49052</v>
+        <v>49032</v>
       </c>
       <c r="F60" s="27">
-        <v>49032</v>
+        <v>48322</v>
       </c>
       <c r="G60" s="27">
-        <v>48322</v>
+        <v>45484</v>
       </c>
       <c r="H60" s="27">
-        <v>45484</v>
+        <v>49602</v>
       </c>
       <c r="I60" s="27">
-        <v>49602</v>
+        <v>48983</v>
       </c>
       <c r="J60" s="27">
-        <v>48983</v>
+        <v>45179</v>
       </c>
       <c r="K60" s="20"/>
       <c r="L60" s="20"/>
       <c r="M60" s="20"/>
     </row>
-    <row r="61" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B61" s="11" t="s">
         <v>45</v>
       </c>
       <c r="C61" s="64">
-        <v>105973</v>
+        <v>115229</v>
       </c>
       <c r="D61" s="64">
-        <v>115229</v>
+        <v>99532</v>
       </c>
       <c r="E61" s="64">
-        <v>99532</v>
+        <v>99270</v>
       </c>
       <c r="F61" s="64">
-        <v>99270</v>
+        <v>99756</v>
       </c>
       <c r="G61" s="64">
-        <v>99756</v>
+        <v>97883</v>
       </c>
       <c r="H61" s="64">
-        <v>97883</v>
+        <v>106376</v>
       </c>
       <c r="I61" s="64">
-        <v>106376</v>
+        <v>114281</v>
       </c>
       <c r="J61" s="64">
-        <v>114281</v>
+        <v>111394</v>
       </c>
       <c r="K61" s="21"/>
       <c r="L61" s="21"/>
       <c r="M61" s="21"/>
     </row>
-    <row r="62" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B62" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C62" s="27">
         <v>0</v>
@@ -9654,146 +9655,146 @@
       <c r="L62" s="20"/>
       <c r="M62" s="20"/>
     </row>
-    <row r="63" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B63" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C63" s="36">
-        <f t="shared" ref="C63:H63" si="14">C61+C62</f>
-        <v>105973</v>
+        <f t="shared" ref="C63:H63" si="13">C61+C62</f>
+        <v>115229</v>
       </c>
       <c r="D63" s="36">
-        <f t="shared" si="14"/>
-        <v>115229</v>
+        <f t="shared" si="13"/>
+        <v>99532</v>
       </c>
       <c r="E63" s="36">
-        <f t="shared" si="14"/>
-        <v>99532</v>
+        <f t="shared" si="13"/>
+        <v>99270</v>
       </c>
       <c r="F63" s="36">
-        <f t="shared" si="14"/>
-        <v>99270</v>
+        <f t="shared" si="13"/>
+        <v>99756</v>
       </c>
       <c r="G63" s="36">
-        <f t="shared" si="14"/>
-        <v>99756</v>
+        <f t="shared" si="13"/>
+        <v>97883</v>
       </c>
       <c r="H63" s="36">
-        <f t="shared" si="14"/>
-        <v>97883</v>
+        <f>H61+H62</f>
+        <v>106376</v>
       </c>
       <c r="I63" s="36">
         <f>I61+I62</f>
-        <v>106376</v>
+        <v>114281</v>
       </c>
       <c r="J63" s="36">
         <f>J61+J62</f>
-        <v>114281</v>
+        <v>111394</v>
       </c>
       <c r="K63" s="20"/>
       <c r="L63" s="20"/>
       <c r="M63" s="20"/>
     </row>
-    <row r="64" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B64" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C64" s="27">
-        <v>4783</v>
+        <v>5205</v>
       </c>
       <c r="D64" s="27">
-        <v>5205</v>
+        <v>5332</v>
       </c>
       <c r="E64" s="27">
-        <v>5332</v>
+        <v>5762</v>
       </c>
       <c r="F64" s="27">
-        <v>5762</v>
+        <v>6657</v>
       </c>
       <c r="G64" s="27">
-        <v>6657</v>
+        <v>7868</v>
       </c>
       <c r="H64" s="27">
-        <v>7868</v>
+        <v>10354</v>
       </c>
       <c r="I64" s="27">
-        <v>10354</v>
+        <v>12079</v>
       </c>
       <c r="J64" s="27">
-        <v>12079</v>
+        <v>13595</v>
       </c>
       <c r="K64" s="20"/>
       <c r="L64" s="20"/>
       <c r="M64" s="20"/>
     </row>
-    <row r="65" spans="1:19" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B65" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C65" s="36">
-        <f t="shared" ref="C65:H65" si="15">C63+C64</f>
-        <v>110756</v>
+        <f t="shared" ref="C65:H65" si="14">C63+C64</f>
+        <v>120434</v>
       </c>
       <c r="D65" s="36">
-        <f t="shared" si="15"/>
-        <v>120434</v>
+        <f t="shared" si="14"/>
+        <v>104864</v>
       </c>
       <c r="E65" s="36">
-        <f t="shared" si="15"/>
-        <v>104864</v>
+        <f t="shared" si="14"/>
+        <v>105032</v>
       </c>
       <c r="F65" s="36">
-        <f t="shared" si="15"/>
-        <v>105032</v>
+        <f t="shared" si="14"/>
+        <v>106413</v>
       </c>
       <c r="G65" s="36">
-        <f t="shared" si="15"/>
-        <v>106413</v>
+        <f t="shared" si="14"/>
+        <v>105751</v>
       </c>
       <c r="H65" s="36">
-        <f t="shared" si="15"/>
-        <v>105751</v>
+        <f>H63+H64</f>
+        <v>116730</v>
       </c>
       <c r="I65" s="36">
         <f>I63+I64</f>
-        <v>116730</v>
+        <v>126360</v>
       </c>
       <c r="J65" s="36">
         <f>J63+J64</f>
-        <v>126360</v>
+        <v>124989</v>
       </c>
       <c r="K65" s="20"/>
       <c r="L65" s="20"/>
       <c r="M65" s="20"/>
     </row>
-    <row r="66" spans="1:19" s="13" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" s="13" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7"/>
       <c r="B66" s="19" t="s">
         <v>47</v>
       </c>
       <c r="C66" s="67">
-        <v>192733</v>
+        <v>206205</v>
       </c>
       <c r="D66" s="67">
-        <v>206205</v>
+        <v>193542</v>
       </c>
       <c r="E66" s="67">
-        <v>193542</v>
+        <v>196485</v>
       </c>
       <c r="F66" s="67">
-        <v>196485</v>
+        <v>192242</v>
       </c>
       <c r="G66" s="67">
-        <v>192242</v>
+        <v>192520</v>
       </c>
       <c r="H66" s="67">
-        <v>192520</v>
+        <v>204514</v>
       </c>
       <c r="I66" s="67">
-        <v>204514</v>
+        <v>211429</v>
       </c>
       <c r="J66" s="67">
-        <v>211429</v>
+        <v>204332</v>
       </c>
       <c r="K66" s="21"/>
       <c r="L66" s="21"/>
@@ -9801,7 +9802,7 @@
       <c r="O66" s="7"/>
       <c r="S66" s="7"/>
     </row>
-    <row r="67" spans="1:19" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -9815,177 +9816,177 @@
       <c r="O68" s="4"/>
       <c r="S68" s="4"/>
     </row>
-    <row r="69" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B69" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C69" s="20">
-        <f t="shared" ref="C69:I69" si="16">C17</f>
-        <v>-437</v>
+        <f t="shared" ref="C69:I69" si="15">C17</f>
+        <v>-1654</v>
       </c>
       <c r="D69" s="20">
+        <f t="shared" si="15"/>
+        <v>-16989</v>
+      </c>
+      <c r="E69" s="20">
+        <f t="shared" si="15"/>
+        <v>-153</v>
+      </c>
+      <c r="F69" s="20">
+        <f t="shared" si="15"/>
+        <v>-887</v>
+      </c>
+      <c r="G69" s="20">
+        <f t="shared" si="15"/>
+        <v>-3024</v>
+      </c>
+      <c r="H69" s="20">
+        <f t="shared" si="15"/>
+        <v>4270</v>
+      </c>
+      <c r="I69" s="20">
+        <f t="shared" ref="I69:J69" si="16">I17</f>
+        <v>-333</v>
+      </c>
+      <c r="J69" s="20">
         <f t="shared" si="16"/>
-        <v>-1654</v>
-      </c>
-      <c r="E69" s="20">
-        <f t="shared" si="16"/>
-        <v>-16989</v>
-      </c>
-      <c r="F69" s="20">
-        <f t="shared" si="16"/>
-        <v>-153</v>
-      </c>
-      <c r="G69" s="20">
-        <f t="shared" si="16"/>
-        <v>-887</v>
-      </c>
-      <c r="H69" s="20">
-        <f t="shared" si="16"/>
-        <v>-3024</v>
-      </c>
-      <c r="I69" s="20">
-        <f t="shared" si="16"/>
-        <v>4270</v>
-      </c>
-      <c r="J69" s="20">
-        <f t="shared" ref="J69" si="17">J17</f>
-        <v>-333</v>
+        <v>-4281</v>
       </c>
       <c r="K69" s="20"/>
       <c r="L69" s="20"/>
       <c r="M69" s="20"/>
     </row>
-    <row r="70" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B70" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C70" s="27">
-        <v>2200</v>
+        <v>2203</v>
       </c>
       <c r="D70" s="27">
-        <v>2203</v>
+        <v>3248</v>
       </c>
       <c r="E70" s="27">
-        <v>3248</v>
+        <v>2300</v>
       </c>
       <c r="F70" s="27">
-        <v>2300</v>
+        <v>2425</v>
       </c>
       <c r="G70" s="27">
-        <v>2425</v>
+        <v>2788</v>
       </c>
       <c r="H70" s="27">
-        <v>2788</v>
+        <v>2758</v>
       </c>
       <c r="I70" s="27">
-        <v>2758</v>
+        <v>2786</v>
       </c>
       <c r="J70" s="27">
-        <v>2786</v>
+        <v>2902</v>
       </c>
       <c r="K70" s="20"/>
       <c r="L70" s="27"/>
       <c r="M70" s="20"/>
     </row>
-    <row r="71" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B71" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C71" s="27">
-        <v>1179</v>
+        <v>780</v>
       </c>
       <c r="D71" s="27">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="E71" s="27">
-        <v>800</v>
+        <v>651</v>
       </c>
       <c r="F71" s="27">
-        <v>651</v>
+        <v>684</v>
       </c>
       <c r="G71" s="27">
-        <v>684</v>
+        <v>664</v>
       </c>
       <c r="H71" s="27">
-        <v>664</v>
+        <v>548</v>
       </c>
       <c r="I71" s="27">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="J71" s="27">
-        <v>538</v>
+        <v>621</v>
       </c>
       <c r="K71" s="27"/>
       <c r="L71" s="27"/>
       <c r="M71" s="20"/>
     </row>
-    <row r="72" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B72" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C72" s="27">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="D72" s="27">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E72" s="27">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="F72" s="27">
-        <v>347</v>
+        <v>249</v>
       </c>
       <c r="G72" s="27">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="H72" s="27">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="I72" s="27">
+        <v>241</v>
+      </c>
+      <c r="J72" s="27">
         <v>234</v>
-      </c>
-      <c r="J72" s="27">
-        <v>241</v>
       </c>
       <c r="K72" s="27"/>
       <c r="L72" s="27"/>
       <c r="M72" s="20"/>
     </row>
-    <row r="73" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B73" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C73" s="27">
-        <v>-208</v>
+        <v>124</v>
       </c>
       <c r="D73" s="27">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="E73" s="27">
-        <v>159</v>
+        <v>-321</v>
       </c>
       <c r="F73" s="27">
-        <v>-321</v>
+        <v>112</v>
       </c>
       <c r="G73" s="27">
-        <v>112</v>
+        <v>-502</v>
       </c>
       <c r="H73" s="27">
-        <v>-502</v>
+        <v>-221</v>
       </c>
       <c r="I73" s="27">
-        <v>-221</v>
+        <v>97</v>
       </c>
       <c r="J73" s="27">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="K73" s="27"/>
       <c r="L73" s="27"/>
       <c r="M73" s="20"/>
     </row>
-    <row r="74" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B74" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C74" s="27">
         <v>0</v>
@@ -10015,9 +10016,9 @@
       <c r="L74" s="27"/>
       <c r="M74" s="20"/>
     </row>
-    <row r="75" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B75" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C75" s="27">
         <v>0</v>
@@ -10038,18 +10039,18 @@
         <v>0</v>
       </c>
       <c r="I75" s="27">
-        <v>0</v>
+        <v>1796</v>
       </c>
       <c r="J75" s="27">
-        <v>1796</v>
+        <v>1090</v>
       </c>
       <c r="K75" s="27"/>
       <c r="L75" s="27"/>
       <c r="M75" s="20"/>
     </row>
-    <row r="76" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B76" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C76" s="27">
         <v>0</v>
@@ -10067,83 +10068,83 @@
         <v>0</v>
       </c>
       <c r="H76" s="27">
-        <v>0</v>
+        <v>-5355</v>
       </c>
       <c r="I76" s="27">
-        <v>-5355</v>
+        <v>32</v>
       </c>
       <c r="J76" s="27">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K76" s="27"/>
       <c r="L76" s="27"/>
       <c r="M76" s="20"/>
     </row>
-    <row r="77" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C77" s="27">
-        <v>-346</v>
+        <v>-993</v>
       </c>
       <c r="D77" s="27">
-        <v>-993</v>
+        <v>7707</v>
       </c>
       <c r="E77" s="27">
-        <v>7707</v>
+        <v>-236</v>
       </c>
       <c r="F77" s="27">
-        <v>-236</v>
+        <v>19</v>
       </c>
       <c r="G77" s="27">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="H77" s="27">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="I77" s="27">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="J77" s="27">
-        <v>205</v>
+        <v>-9</v>
       </c>
       <c r="K77" s="27"/>
       <c r="L77" s="27"/>
       <c r="M77" s="20"/>
     </row>
-    <row r="78" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B78" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C78" s="27">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="D78" s="27">
-        <v>126</v>
+        <v>2164</v>
       </c>
       <c r="E78" s="27">
-        <v>2164</v>
+        <v>-38</v>
       </c>
       <c r="F78" s="27">
-        <v>-38</v>
+        <v>0</v>
       </c>
       <c r="G78" s="27">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="H78" s="27">
-        <v>482</v>
+        <v>-17</v>
       </c>
       <c r="I78" s="27">
-        <v>-17</v>
+        <v>50</v>
       </c>
       <c r="J78" s="27">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K78" s="27"/>
       <c r="L78" s="27"/>
       <c r="M78" s="20"/>
     </row>
-    <row r="79" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B79" s="9" t="s">
         <v>52</v>
       </c>
@@ -10151,161 +10152,161 @@
         <v>0</v>
       </c>
       <c r="D79" s="27">
-        <v>0</v>
+        <v>3626</v>
       </c>
       <c r="E79" s="27">
-        <v>3626</v>
+        <v>-135</v>
       </c>
       <c r="F79" s="27">
-        <v>-135</v>
+        <v>0</v>
       </c>
       <c r="G79" s="27">
         <v>0</v>
       </c>
       <c r="H79" s="27">
-        <v>0</v>
+        <v>2059</v>
       </c>
       <c r="I79" s="27">
-        <v>2059</v>
+        <v>-1583</v>
       </c>
       <c r="J79" s="27">
-        <v>-1583</v>
+        <v>3965</v>
       </c>
       <c r="K79" s="27"/>
       <c r="L79" s="27"/>
       <c r="M79" s="20"/>
     </row>
-    <row r="80" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B80" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C80" s="27">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="D80" s="27">
-        <v>192</v>
+        <v>10</v>
       </c>
       <c r="E80" s="27">
-        <v>10</v>
+        <v>-357</v>
       </c>
       <c r="F80" s="27">
-        <v>-357</v>
+        <v>414</v>
       </c>
       <c r="G80" s="27">
-        <v>414</v>
+        <v>590</v>
       </c>
       <c r="H80" s="27">
-        <v>590</v>
+        <v>-842</v>
       </c>
       <c r="I80" s="27">
-        <v>-842</v>
+        <v>-611</v>
       </c>
       <c r="J80" s="27">
-        <v>-611</v>
+        <v>-217</v>
       </c>
       <c r="K80" s="27"/>
       <c r="L80" s="27"/>
       <c r="M80" s="20"/>
     </row>
-    <row r="81" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B81" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C81" s="27">
-        <v>-366</v>
+        <v>250</v>
       </c>
       <c r="D81" s="27">
-        <v>250</v>
+        <v>-853</v>
       </c>
       <c r="E81" s="27">
-        <v>-853</v>
+        <v>-136</v>
       </c>
       <c r="F81" s="27">
-        <v>-136</v>
+        <v>-83</v>
       </c>
       <c r="G81" s="27">
-        <v>-83</v>
+        <v>182</v>
       </c>
       <c r="H81" s="27">
-        <v>182</v>
+        <v>-108</v>
       </c>
       <c r="I81" s="27">
-        <v>-108</v>
+        <v>-129</v>
       </c>
       <c r="J81" s="27">
-        <v>-129</v>
+        <v>-808</v>
       </c>
       <c r="K81" s="27"/>
       <c r="L81" s="27"/>
       <c r="M81" s="20"/>
     </row>
-    <row r="82" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B82" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C82" s="27">
-        <v>-386</v>
+        <v>567</v>
       </c>
       <c r="D82" s="27">
-        <v>567</v>
+        <v>385</v>
       </c>
       <c r="E82" s="27">
-        <v>385</v>
+        <v>68</v>
       </c>
       <c r="F82" s="27">
-        <v>68</v>
+        <v>-240</v>
       </c>
       <c r="G82" s="27">
-        <v>-240</v>
+        <v>354</v>
       </c>
       <c r="H82" s="27">
-        <v>354</v>
+        <v>-395</v>
       </c>
       <c r="I82" s="27">
-        <v>-395</v>
+        <v>578</v>
       </c>
       <c r="J82" s="27">
-        <v>578</v>
+        <v>-142</v>
       </c>
       <c r="K82" s="27"/>
       <c r="L82" s="27"/>
       <c r="M82" s="20"/>
     </row>
-    <row r="83" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B83" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C83" s="27">
         <v>145</v>
       </c>
-      <c r="C83" s="27">
-        <v>-1160</v>
-      </c>
       <c r="D83" s="27">
-        <v>145</v>
+        <v>2399</v>
       </c>
       <c r="E83" s="27">
-        <v>2399</v>
+        <v>-1602</v>
       </c>
       <c r="F83" s="27">
-        <v>-1602</v>
+        <v>-741</v>
       </c>
       <c r="G83" s="27">
-        <v>-741</v>
+        <v>1763</v>
       </c>
       <c r="H83" s="27">
-        <v>1763</v>
+        <v>-481</v>
       </c>
       <c r="I83" s="27">
-        <v>-481</v>
+        <v>247</v>
       </c>
       <c r="J83" s="27">
-        <v>247</v>
+        <v>-1175</v>
       </c>
       <c r="K83" s="27"/>
       <c r="L83" s="27"/>
       <c r="M83" s="20"/>
     </row>
-    <row r="84" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B84" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C84" s="27">
         <v>0</v>
@@ -10335,98 +10336,98 @@
       <c r="L84" s="27"/>
       <c r="M84" s="20"/>
     </row>
-    <row r="85" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B85" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C85" s="27">
-        <v>-245</v>
+        <v>-590</v>
       </c>
       <c r="D85" s="27">
-        <v>-590</v>
+        <v>-95</v>
       </c>
       <c r="E85" s="27">
-        <v>-95</v>
+        <v>574</v>
       </c>
       <c r="F85" s="27">
-        <v>574</v>
+        <v>67</v>
       </c>
       <c r="G85" s="27">
-        <v>67</v>
+        <v>-1405</v>
       </c>
       <c r="H85" s="27">
-        <v>-1405</v>
+        <v>142</v>
       </c>
       <c r="I85" s="27">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="J85" s="27">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="K85" s="27"/>
       <c r="L85" s="27"/>
       <c r="M85" s="20"/>
     </row>
-    <row r="86" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B86" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C86" s="27">
-        <v>-1885</v>
+        <v>776</v>
       </c>
       <c r="D86" s="27">
-        <v>776</v>
+        <v>1129</v>
       </c>
       <c r="E86" s="27">
-        <v>1129</v>
+        <v>2203</v>
       </c>
       <c r="F86" s="27">
-        <v>2203</v>
+        <v>-1206</v>
       </c>
       <c r="G86" s="27">
-        <v>-1206</v>
+        <v>-154</v>
       </c>
       <c r="H86" s="27">
-        <v>-154</v>
+        <v>-63</v>
       </c>
       <c r="I86" s="27">
-        <v>-63</v>
+        <v>173</v>
       </c>
       <c r="J86" s="27">
-        <v>173</v>
+        <v>-1325</v>
       </c>
       <c r="K86" s="27"/>
       <c r="L86" s="27"/>
       <c r="M86" s="20"/>
     </row>
-    <row r="87" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A87" s="7"/>
       <c r="B87" s="17" t="s">
         <v>56</v>
       </c>
       <c r="C87" s="60">
-        <v>-1223</v>
+        <v>2292</v>
       </c>
       <c r="D87" s="60">
-        <v>2292</v>
+        <v>4054</v>
       </c>
       <c r="E87" s="60">
-        <v>4054</v>
+        <v>3165</v>
       </c>
       <c r="F87" s="60">
-        <v>3165</v>
+        <v>813</v>
       </c>
       <c r="G87" s="60">
-        <v>813</v>
+        <v>2050</v>
       </c>
       <c r="H87" s="60">
-        <v>2050</v>
+        <v>2546</v>
       </c>
       <c r="I87" s="60">
-        <v>2546</v>
+        <v>4288</v>
       </c>
       <c r="J87" s="60">
-        <v>4288</v>
+        <v>1096</v>
       </c>
       <c r="K87" s="33"/>
       <c r="L87" s="33"/>
@@ -10434,41 +10435,41 @@
       <c r="O87" s="7"/>
       <c r="S87" s="7"/>
     </row>
-    <row r="88" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B88" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C88" s="27">
-        <v>-5970</v>
+        <v>-5682</v>
       </c>
       <c r="D88" s="27">
-        <v>-5682</v>
+        <v>-6458</v>
       </c>
       <c r="E88" s="27">
-        <v>-6458</v>
+        <v>-5834</v>
       </c>
       <c r="F88" s="27">
-        <v>-5834</v>
+        <v>-5183</v>
       </c>
       <c r="G88" s="27">
-        <v>-5183</v>
+        <v>-3550</v>
       </c>
       <c r="H88" s="27">
-        <v>-3550</v>
+        <v>-2425</v>
       </c>
       <c r="I88" s="27">
-        <v>-2425</v>
+        <v>-3488</v>
       </c>
       <c r="J88" s="27">
-        <v>-3488</v>
+        <v>-3636</v>
       </c>
       <c r="K88" s="27"/>
       <c r="L88" s="27"/>
       <c r="M88" s="20"/>
     </row>
-    <row r="89" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B89" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C89" s="27">
         <v>0</v>
@@ -10477,10 +10478,10 @@
         <v>0</v>
       </c>
       <c r="E89" s="27">
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="F89" s="27">
-        <v>-82</v>
+        <v>0</v>
       </c>
       <c r="G89" s="27">
         <v>0</v>
@@ -10492,79 +10493,79 @@
         <v>0</v>
       </c>
       <c r="J89" s="27">
-        <v>0</v>
+        <v>-596</v>
       </c>
       <c r="K89" s="27"/>
       <c r="L89" s="27"/>
       <c r="M89" s="20"/>
     </row>
-    <row r="90" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B90" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C90" s="27">
-        <v>592</v>
+        <v>107</v>
       </c>
       <c r="D90" s="27">
+        <v>26</v>
+      </c>
+      <c r="E90" s="27">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="27">
+        <v>803</v>
+      </c>
+      <c r="G90" s="27">
+        <v>161</v>
+      </c>
+      <c r="H90" s="27">
+        <v>54</v>
+      </c>
+      <c r="I90" s="27">
+        <v>559</v>
+      </c>
+      <c r="J90" s="27">
         <v>107</v>
-      </c>
-      <c r="E90" s="27">
-        <v>26</v>
-      </c>
-      <c r="F90" s="27">
-        <v>1211</v>
-      </c>
-      <c r="G90" s="27">
-        <v>803</v>
-      </c>
-      <c r="H90" s="27">
-        <v>161</v>
-      </c>
-      <c r="I90" s="27">
-        <v>54</v>
-      </c>
-      <c r="J90" s="27">
-        <v>559</v>
       </c>
       <c r="K90" s="27"/>
       <c r="L90" s="27"/>
       <c r="M90" s="20"/>
     </row>
-    <row r="91" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B91" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C91" s="27">
-        <v>-6460</v>
+        <v>-11174</v>
       </c>
       <c r="D91" s="27">
-        <v>-11174</v>
+        <v>-13885</v>
       </c>
       <c r="E91" s="27">
-        <v>-13885</v>
+        <v>-6421</v>
       </c>
       <c r="F91" s="27">
-        <v>-6421</v>
+        <v>-3386</v>
       </c>
       <c r="G91" s="27">
-        <v>-3386</v>
+        <v>-2344</v>
       </c>
       <c r="H91" s="27">
-        <v>-2344</v>
+        <v>-10671</v>
       </c>
       <c r="I91" s="27">
-        <v>-10671</v>
+        <v>-7918</v>
       </c>
       <c r="J91" s="27">
-        <v>-7918</v>
+        <v>-7190</v>
       </c>
       <c r="K91" s="27"/>
       <c r="L91" s="27"/>
       <c r="M91" s="20"/>
     </row>
-    <row r="92" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B92" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C92" s="27">
         <v>0</v>
@@ -10573,10 +10574,10 @@
         <v>0</v>
       </c>
       <c r="E92" s="27">
-        <v>0</v>
+        <v>41463</v>
       </c>
       <c r="F92" s="27">
-        <v>41463</v>
+        <v>0</v>
       </c>
       <c r="G92" s="27">
         <v>0</v>
@@ -10585,50 +10586,50 @@
         <v>0</v>
       </c>
       <c r="I92" s="27">
-        <v>0</v>
+        <v>15387</v>
       </c>
       <c r="J92" s="27">
-        <v>15387</v>
+        <v>9221</v>
       </c>
       <c r="K92" s="27"/>
       <c r="L92" s="27"/>
       <c r="M92" s="20"/>
     </row>
-    <row r="93" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B93" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C93" s="27">
-        <v>9598</v>
+        <v>7616</v>
       </c>
       <c r="D93" s="27">
-        <v>7616</v>
+        <v>17054</v>
       </c>
       <c r="E93" s="27">
-        <v>17054</v>
+        <v>-34268</v>
       </c>
       <c r="F93" s="27">
-        <v>-34268</v>
+        <v>5327</v>
       </c>
       <c r="G93" s="27">
-        <v>5327</v>
+        <v>3248</v>
       </c>
       <c r="H93" s="27">
-        <v>3248</v>
+        <v>2389</v>
       </c>
       <c r="I93" s="27">
-        <v>2389</v>
+        <v>-10964</v>
       </c>
       <c r="J93" s="27">
-        <v>-10964</v>
+        <v>5227</v>
       </c>
       <c r="K93" s="27"/>
       <c r="L93" s="27"/>
       <c r="M93" s="20"/>
     </row>
-    <row r="94" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B94" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C94" s="27">
         <v>0</v>
@@ -10658,9 +10659,9 @@
       <c r="L94" s="27"/>
       <c r="M94" s="20"/>
     </row>
-    <row r="95" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B95" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C95" s="27">
         <v>0</v>
@@ -10690,9 +10691,9 @@
       <c r="L95" s="27"/>
       <c r="M95" s="20"/>
     </row>
-    <row r="96" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B96" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C96" s="27">
         <v>0</v>
@@ -10722,41 +10723,41 @@
       <c r="L96" s="27"/>
       <c r="M96" s="20"/>
     </row>
-    <row r="97" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B97" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C97" s="27">
         <v>0</v>
       </c>
       <c r="D97" s="27">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="E97" s="27">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="F97" s="27">
-        <v>544</v>
+        <v>0</v>
       </c>
       <c r="G97" s="27">
         <v>0</v>
       </c>
       <c r="H97" s="27">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="I97" s="27">
-        <v>642</v>
+        <v>29</v>
       </c>
       <c r="J97" s="27">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K97" s="27"/>
       <c r="L97" s="27"/>
       <c r="M97" s="20"/>
     </row>
-    <row r="98" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B98" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C98" s="27">
         <v>0</v>
@@ -10768,84 +10769,84 @@
         <v>0</v>
       </c>
       <c r="F98" s="27">
-        <v>0</v>
+        <v>1935</v>
       </c>
       <c r="G98" s="27">
-        <v>1935</v>
+        <v>0</v>
       </c>
       <c r="H98" s="27">
-        <v>0</v>
+        <v>4251</v>
       </c>
       <c r="I98" s="27">
-        <v>4251</v>
+        <v>-29</v>
       </c>
       <c r="J98" s="27">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="K98" s="27"/>
       <c r="L98" s="27"/>
       <c r="M98" s="20"/>
     </row>
-    <row r="99" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B99" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C99" s="27">
-        <v>-323</v>
+        <v>-32</v>
       </c>
       <c r="D99" s="27">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="E99" s="27">
-        <v>-4</v>
+        <v>-377</v>
       </c>
       <c r="F99" s="27">
-        <v>-377</v>
+        <v>585</v>
       </c>
       <c r="G99" s="27">
-        <v>585</v>
+        <v>399</v>
       </c>
       <c r="H99" s="27">
-        <v>399</v>
+        <v>-490</v>
       </c>
       <c r="I99" s="27">
-        <v>-490</v>
+        <v>-142</v>
       </c>
       <c r="J99" s="27">
-        <v>-142</v>
+        <v>-40</v>
       </c>
       <c r="K99" s="27"/>
       <c r="L99" s="27"/>
       <c r="M99" s="20"/>
     </row>
-    <row r="100" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7"/>
       <c r="B100" s="17" t="s">
         <v>58</v>
       </c>
       <c r="C100" s="60">
-        <v>-2563</v>
+        <v>-9165</v>
       </c>
       <c r="D100" s="60">
-        <v>-9165</v>
+        <v>-2764</v>
       </c>
       <c r="E100" s="60">
-        <v>-2764</v>
+        <v>-3764</v>
       </c>
       <c r="F100" s="60">
-        <v>-3764</v>
+        <v>81</v>
       </c>
       <c r="G100" s="60">
-        <v>81</v>
+        <v>-2086</v>
       </c>
       <c r="H100" s="60">
-        <v>-2086</v>
+        <v>-6250</v>
       </c>
       <c r="I100" s="60">
-        <v>-6250</v>
+        <v>-6566</v>
       </c>
       <c r="J100" s="60">
-        <v>-6566</v>
+        <v>3093</v>
       </c>
       <c r="K100" s="33"/>
       <c r="L100" s="33"/>
@@ -10853,9 +10854,9 @@
       <c r="O100" s="7"/>
       <c r="S100" s="7"/>
     </row>
-    <row r="101" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B101" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C101" s="27">
         <v>0</v>
@@ -10885,27 +10886,27 @@
       <c r="L101" s="27"/>
       <c r="M101" s="20"/>
     </row>
-    <row r="102" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B102" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C102" s="27">
-        <v>793</v>
+        <v>5011</v>
       </c>
       <c r="D102" s="27">
-        <v>5011</v>
+        <v>1545</v>
       </c>
       <c r="E102" s="27">
-        <v>1545</v>
+        <v>0</v>
       </c>
       <c r="F102" s="27">
-        <v>0</v>
+        <v>1496</v>
       </c>
       <c r="G102" s="27">
-        <v>1496</v>
+        <v>1997</v>
       </c>
       <c r="H102" s="27">
-        <v>1997</v>
+        <v>0</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -10917,30 +10918,30 @@
       <c r="L102" s="27"/>
       <c r="M102" s="20"/>
     </row>
-    <row r="103" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B103" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C103" s="27">
-        <v>0</v>
+        <v>-2609</v>
       </c>
       <c r="D103" s="27">
-        <v>-2609</v>
+        <v>-4740</v>
       </c>
       <c r="E103" s="27">
-        <v>-4740</v>
+        <v>0</v>
       </c>
       <c r="F103" s="27">
         <v>0</v>
       </c>
       <c r="G103" s="27">
-        <v>0</v>
+        <v>-1496</v>
       </c>
       <c r="H103" s="27">
-        <v>-1496</v>
+        <v>-1997</v>
       </c>
       <c r="I103" s="27">
-        <v>-1997</v>
+        <v>0</v>
       </c>
       <c r="J103" s="27">
         <v>0</v>
@@ -10949,41 +10950,41 @@
       <c r="L103" s="27"/>
       <c r="M103" s="20"/>
     </row>
-    <row r="104" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B104" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C104" s="27">
-        <v>423</v>
+        <v>11438</v>
       </c>
       <c r="D104" s="27">
-        <v>11438</v>
+        <v>417</v>
       </c>
       <c r="E104" s="27">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="F104" s="27">
-        <v>436</v>
+        <v>955</v>
       </c>
       <c r="G104" s="27">
-        <v>955</v>
+        <v>1283</v>
       </c>
       <c r="H104" s="27">
-        <v>1283</v>
+        <v>1414</v>
       </c>
       <c r="I104" s="27">
-        <v>1414</v>
+        <v>1456</v>
       </c>
       <c r="J104" s="27">
-        <v>1456</v>
+        <v>2064</v>
       </c>
       <c r="K104" s="27"/>
       <c r="L104" s="27"/>
       <c r="M104" s="20"/>
     </row>
-    <row r="105" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B105" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C105" s="27">
         <v>0</v>
@@ -11001,59 +11002,59 @@
         <v>0</v>
       </c>
       <c r="H105" s="27">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="I105" s="27">
-        <v>922</v>
+        <v>-1</v>
       </c>
       <c r="J105" s="27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K105" s="27"/>
       <c r="L105" s="27"/>
       <c r="M105" s="20"/>
     </row>
-    <row r="106" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B106" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C106" s="27">
         <v>0</v>
       </c>
       <c r="D106" s="27">
-        <v>0</v>
+        <v>-741</v>
       </c>
       <c r="E106" s="27">
-        <v>-741</v>
+        <v>-437</v>
       </c>
       <c r="F106" s="27">
-        <v>-437</v>
+        <v>-1020</v>
       </c>
       <c r="G106" s="27">
-        <v>-1020</v>
+        <v>-942</v>
       </c>
       <c r="H106" s="27">
-        <v>-942</v>
+        <v>-531</v>
       </c>
       <c r="I106" s="27">
-        <v>-531</v>
+        <v>-533</v>
       </c>
       <c r="J106" s="27">
-        <v>-533</v>
+        <v>-1327</v>
       </c>
       <c r="K106" s="27"/>
       <c r="L106" s="27"/>
       <c r="M106" s="20"/>
     </row>
-    <row r="107" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B107" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C107" s="27">
-        <v>2537</v>
+        <v>438</v>
       </c>
       <c r="D107" s="27">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="E107" s="27">
         <v>0</v>
@@ -11077,73 +11078,73 @@
       <c r="L107" s="27"/>
       <c r="M107" s="20"/>
     </row>
-    <row r="108" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B108" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C108" s="27">
-        <v>0</v>
+        <v>-2288</v>
       </c>
       <c r="D108" s="27">
-        <v>-2288</v>
+        <v>0</v>
       </c>
       <c r="E108" s="27">
         <v>0</v>
       </c>
       <c r="F108" s="27">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="G108" s="27">
+        <v>0</v>
+      </c>
+      <c r="H108" s="27">
+        <v>-2250</v>
+      </c>
+      <c r="I108" s="27">
+        <v>0</v>
+      </c>
+      <c r="J108" s="27">
         <v>-1500</v>
-      </c>
-      <c r="H108" s="27">
-        <v>0</v>
-      </c>
-      <c r="I108" s="27">
-        <v>-2250</v>
-      </c>
-      <c r="J108" s="27">
-        <v>0</v>
       </c>
       <c r="K108" s="27"/>
       <c r="L108" s="27"/>
       <c r="M108" s="20"/>
     </row>
-    <row r="109" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B109" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C109" s="27">
-        <v>626</v>
+        <v>5</v>
       </c>
       <c r="D109" s="27">
-        <v>5</v>
+        <v>355</v>
       </c>
       <c r="E109" s="27">
-        <v>355</v>
+        <v>1</v>
       </c>
       <c r="F109" s="27">
-        <v>1</v>
+        <v>491</v>
       </c>
       <c r="G109" s="27">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="H109" s="27">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="I109" s="27">
-        <v>286</v>
+        <v>-6</v>
       </c>
       <c r="J109" s="27">
-        <v>-6</v>
+        <v>427</v>
       </c>
       <c r="K109" s="27"/>
       <c r="L109" s="27"/>
       <c r="M109" s="20"/>
     </row>
-    <row r="110" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B110" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C110" s="27">
         <v>0</v>
@@ -11152,10 +11153,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="27">
-        <v>0</v>
+        <v>-631</v>
       </c>
       <c r="F110" s="27">
-        <v>-631</v>
+        <v>0</v>
       </c>
       <c r="G110" s="27">
         <v>0</v>
@@ -11164,18 +11165,18 @@
         <v>0</v>
       </c>
       <c r="I110" s="27">
-        <v>0</v>
+        <v>-423</v>
       </c>
       <c r="J110" s="27">
-        <v>-423</v>
+        <v>0</v>
       </c>
       <c r="K110" s="27"/>
       <c r="L110" s="27"/>
       <c r="M110" s="20"/>
     </row>
-    <row r="111" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B111" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C111" s="27">
         <v>0</v>
@@ -11196,18 +11197,18 @@
         <v>0</v>
       </c>
       <c r="I111" s="27">
-        <v>0</v>
+        <v>12706</v>
       </c>
       <c r="J111" s="27">
-        <v>12706</v>
+        <v>0</v>
       </c>
       <c r="K111" s="27"/>
       <c r="L111" s="27"/>
       <c r="M111" s="20"/>
     </row>
-    <row r="112" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B112" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C112" s="27">
         <v>0</v>
@@ -11237,18 +11238,18 @@
       <c r="L112" s="27"/>
       <c r="M112" s="20"/>
     </row>
-    <row r="113" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B113" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C113" s="27">
-        <v>-529</v>
+        <v>-534</v>
       </c>
       <c r="D113" s="27">
-        <v>-534</v>
+        <v>-536</v>
       </c>
       <c r="E113" s="27">
-        <v>-536</v>
+        <v>0</v>
       </c>
       <c r="F113" s="27">
         <v>0</v>
@@ -11269,66 +11270,66 @@
       <c r="L113" s="27"/>
       <c r="M113" s="20"/>
     </row>
-    <row r="114" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B114" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C114" s="27">
-        <v>-220</v>
+        <v>-224</v>
       </c>
       <c r="D114" s="27">
-        <v>-224</v>
+        <v>-92</v>
       </c>
       <c r="E114" s="27">
-        <v>-92</v>
+        <v>694</v>
       </c>
       <c r="F114" s="27">
-        <v>694</v>
+        <v>-618</v>
       </c>
       <c r="G114" s="27">
-        <v>-618</v>
+        <v>-60</v>
       </c>
       <c r="H114" s="27">
-        <v>-60</v>
+        <v>7308</v>
       </c>
       <c r="I114" s="27">
-        <v>7308</v>
+        <v>-7350</v>
       </c>
       <c r="J114" s="27">
-        <v>-7350</v>
+        <v>-870</v>
       </c>
       <c r="K114" s="27"/>
       <c r="L114" s="27"/>
       <c r="M114" s="20"/>
     </row>
-    <row r="115" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A115" s="7"/>
       <c r="B115" s="17" t="s">
         <v>60</v>
       </c>
       <c r="C115" s="60">
-        <v>3630</v>
+        <v>11237</v>
       </c>
       <c r="D115" s="60">
-        <v>11237</v>
+        <v>-3792</v>
       </c>
       <c r="E115" s="60">
-        <v>-3792</v>
+        <v>63</v>
       </c>
       <c r="F115" s="60">
-        <v>63</v>
+        <v>-196</v>
       </c>
       <c r="G115" s="60">
-        <v>-196</v>
+        <v>782</v>
       </c>
       <c r="H115" s="60">
-        <v>782</v>
+        <v>5152</v>
       </c>
       <c r="I115" s="60">
-        <v>5152</v>
+        <v>5849</v>
       </c>
       <c r="J115" s="60">
-        <v>5849</v>
+        <v>-1206</v>
       </c>
       <c r="K115" s="33"/>
       <c r="L115" s="33"/>
@@ -11336,7 +11337,7 @@
       <c r="O115" s="7"/>
       <c r="S115" s="7"/>
     </row>
-    <row r="116" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B116" s="9" t="s">
         <v>61</v>
       </c>
@@ -11368,99 +11369,99 @@
       <c r="L116" s="27"/>
       <c r="M116" s="20"/>
     </row>
-    <row r="117" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B117" s="11" t="s">
         <v>62</v>
       </c>
       <c r="C117" s="64">
-        <v>-156</v>
+        <v>4364</v>
       </c>
       <c r="D117" s="64">
-        <v>4364</v>
+        <v>-3132</v>
       </c>
       <c r="E117" s="64">
-        <v>-3132</v>
+        <v>-536</v>
       </c>
       <c r="F117" s="64">
-        <v>-536</v>
+        <v>698</v>
       </c>
       <c r="G117" s="64">
-        <v>698</v>
+        <v>746</v>
       </c>
       <c r="H117" s="64">
-        <v>746</v>
+        <v>2892</v>
       </c>
       <c r="I117" s="64">
-        <v>2892</v>
+        <v>3571</v>
       </c>
       <c r="J117" s="64">
-        <v>3571</v>
+        <v>2983</v>
       </c>
       <c r="K117" s="33"/>
       <c r="L117" s="33"/>
       <c r="M117" s="21"/>
     </row>
-    <row r="118" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B118" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C118" s="64">
-        <v>7079</v>
+        <v>6923</v>
       </c>
       <c r="D118" s="64">
-        <v>6923</v>
+        <v>11287</v>
       </c>
       <c r="E118" s="64">
-        <v>11287</v>
+        <v>8785</v>
       </c>
       <c r="F118" s="64">
-        <v>8785</v>
+        <v>8249</v>
       </c>
       <c r="G118" s="64">
-        <v>8249</v>
+        <v>8947</v>
       </c>
       <c r="H118" s="64">
-        <v>8947</v>
+        <v>9693</v>
       </c>
       <c r="I118" s="64">
-        <v>9693</v>
+        <v>11141</v>
       </c>
       <c r="J118" s="64">
-        <v>11141</v>
+        <v>14712</v>
       </c>
       <c r="K118" s="21"/>
       <c r="L118" s="21"/>
       <c r="M118" s="21"/>
     </row>
-    <row r="119" spans="1:19" s="13" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" s="13" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A119" s="7"/>
       <c r="B119" s="19" t="s">
         <v>64</v>
       </c>
       <c r="C119" s="60">
-        <v>6923</v>
+        <v>11287</v>
       </c>
       <c r="D119" s="60">
-        <v>11287</v>
+        <v>8785</v>
       </c>
       <c r="E119" s="60">
-        <v>8785</v>
+        <v>8249</v>
       </c>
       <c r="F119" s="60">
-        <v>8249</v>
+        <v>8947</v>
       </c>
       <c r="G119" s="60">
-        <v>8947</v>
+        <v>9693</v>
       </c>
       <c r="H119" s="60">
-        <v>9693</v>
+        <v>11141</v>
       </c>
       <c r="I119" s="60">
-        <v>11141</v>
+        <f>I118+I117</f>
+        <v>14712</v>
       </c>
       <c r="J119" s="60">
-        <f>J118+J117</f>
-        <v>14712</v>
+        <v>17695</v>
       </c>
       <c r="K119" s="21"/>
       <c r="L119" s="21"/>
@@ -11468,7 +11469,7 @@
       <c r="O119" s="7"/>
       <c r="S119" s="7"/>
     </row>
-    <row r="120" spans="1:19" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B120" s="1"/>
     </row>
     <row r="121" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -11487,76 +11488,76 @@
         <v>67</v>
       </c>
       <c r="C122" s="20">
-        <f t="shared" ref="C122:I122" si="18">C5-C6-C11+C13+C14+C16-C18</f>
-        <v>-381</v>
+        <f t="shared" ref="C122:I122" si="17">C5-C6-C11+C13+C14+C16-C18</f>
+        <v>-1610</v>
       </c>
       <c r="D122" s="20">
-        <f t="shared" si="18"/>
-        <v>-1610</v>
+        <f t="shared" si="17"/>
+        <v>-16639</v>
       </c>
       <c r="E122" s="20">
-        <f t="shared" si="18"/>
-        <v>-16639</v>
+        <f t="shared" si="17"/>
+        <v>-126</v>
       </c>
       <c r="F122" s="20">
-        <f t="shared" si="18"/>
-        <v>-126</v>
+        <f t="shared" si="17"/>
+        <v>-821</v>
       </c>
       <c r="G122" s="20">
-        <f t="shared" si="18"/>
-        <v>-821</v>
+        <f t="shared" si="17"/>
+        <v>-2918</v>
       </c>
       <c r="H122" s="20">
-        <f t="shared" si="18"/>
-        <v>-2918</v>
+        <f t="shared" si="17"/>
+        <v>4063</v>
       </c>
       <c r="I122" s="20">
-        <f t="shared" si="18"/>
-        <v>4063</v>
+        <f t="shared" ref="I122:J122" si="18">I5-I6-I11+I13+I14+I16-I18</f>
+        <v>-591</v>
       </c>
       <c r="J122" s="20">
-        <f t="shared" ref="J122" si="19">J5-J6-J11+J13+J14+J16-J18</f>
-        <v>-591</v>
+        <f>J5-J6-J11+J13+J14+J16+J18</f>
+        <v>-3728</v>
       </c>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
       <c r="M122" s="20"/>
     </row>
-    <row r="123" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:19" s="18" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A123" s="7"/>
       <c r="B123" s="17" t="s">
         <v>68</v>
       </c>
       <c r="C123" s="24">
-        <f t="shared" ref="C123:I123" si="20">C19-C122</f>
+        <f t="shared" ref="C123:I123" si="19">C19-C122</f>
         <v>0</v>
       </c>
       <c r="D123" s="24">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="E123" s="24">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F123" s="24">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="G123" s="24">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H123" s="24">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I123" s="24">
+        <f t="shared" ref="I123:J123" si="20">I19-I122</f>
+        <v>0</v>
+      </c>
+      <c r="J123" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E123" s="24">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="F123" s="24">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="G123" s="24">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="H123" s="24">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I123" s="24">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J123" s="24">
-        <f t="shared" ref="J123" si="21">J19-J122</f>
         <v>0</v>
       </c>
       <c r="K123" s="26"/>
@@ -11570,75 +11571,75 @@
         <v>69</v>
       </c>
       <c r="C124" s="20">
-        <f t="shared" ref="C124:I124" si="22">SUM(C26:C32)+SUM(C34:C39)</f>
-        <v>192733</v>
+        <f t="shared" ref="C124:I124" si="21">SUM(C26:C32)+SUM(C34:C39)</f>
+        <v>206205</v>
       </c>
       <c r="D124" s="20">
+        <f t="shared" si="21"/>
+        <v>193542</v>
+      </c>
+      <c r="E124" s="20">
+        <f t="shared" si="21"/>
+        <v>196485</v>
+      </c>
+      <c r="F124" s="20">
+        <f t="shared" si="21"/>
+        <v>192242</v>
+      </c>
+      <c r="G124" s="20">
+        <f t="shared" si="21"/>
+        <v>192520</v>
+      </c>
+      <c r="H124" s="20">
+        <f t="shared" si="21"/>
+        <v>204514</v>
+      </c>
+      <c r="I124" s="20">
+        <f t="shared" ref="I124:J124" si="22">SUM(I26:I32)+SUM(I34:I39)</f>
+        <v>211429</v>
+      </c>
+      <c r="J124" s="20">
         <f t="shared" si="22"/>
-        <v>206205</v>
-      </c>
-      <c r="E124" s="20">
-        <f t="shared" si="22"/>
-        <v>193542</v>
-      </c>
-      <c r="F124" s="20">
-        <f t="shared" si="22"/>
-        <v>196485</v>
-      </c>
-      <c r="G124" s="20">
-        <f t="shared" si="22"/>
-        <v>192242</v>
-      </c>
-      <c r="H124" s="20">
-        <f t="shared" si="22"/>
-        <v>192520</v>
-      </c>
-      <c r="I124" s="20">
-        <f t="shared" si="22"/>
-        <v>204514</v>
-      </c>
-      <c r="J124" s="20">
-        <f t="shared" ref="J124" si="23">SUM(J26:J32)+SUM(J34:J39)</f>
-        <v>211429</v>
+        <v>205332</v>
       </c>
       <c r="K124" s="20"/>
       <c r="L124" s="20"/>
       <c r="M124" s="20"/>
     </row>
-    <row r="125" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B125" s="11" t="s">
         <v>70</v>
       </c>
       <c r="C125" s="23">
-        <f t="shared" ref="C125:I125" si="24">C41-C124</f>
+        <f t="shared" ref="C125:I125" si="23">C41-C124</f>
         <v>0</v>
       </c>
       <c r="D125" s="23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="E125" s="23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F125" s="23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G125" s="23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="H125" s="23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I125" s="23">
+        <f t="shared" ref="I125:J125" si="24">I41-I124</f>
+        <v>0</v>
+      </c>
+      <c r="J125" s="23">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="E125" s="23">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="F125" s="23">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="G125" s="23">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="H125" s="23">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="I125" s="23">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="J125" s="23">
-        <f t="shared" ref="J125" si="25">J41-J124</f>
         <v>0</v>
       </c>
       <c r="K125" s="26"/>
@@ -11650,75 +11651,75 @@
         <v>71</v>
       </c>
       <c r="C126" s="20">
-        <f t="shared" ref="C126:I126" si="26">SUM(C42:C48)+SUM(C50:C54)</f>
-        <v>81977</v>
+        <f t="shared" ref="C126:I126" si="25">SUM(C42:C48)+SUM(C50:C54)</f>
+        <v>85771</v>
       </c>
       <c r="D126" s="20">
+        <f t="shared" si="25"/>
+        <v>88678</v>
+      </c>
+      <c r="E126" s="20">
+        <f t="shared" si="25"/>
+        <v>91453</v>
+      </c>
+      <c r="F126" s="20">
+        <f t="shared" si="25"/>
+        <v>85829</v>
+      </c>
+      <c r="G126" s="20">
+        <f t="shared" si="25"/>
+        <v>86769</v>
+      </c>
+      <c r="H126" s="20">
+        <f t="shared" si="25"/>
+        <v>87784</v>
+      </c>
+      <c r="I126" s="20">
+        <f t="shared" ref="I126:J126" si="26">SUM(I42:I48)+SUM(I50:I54)</f>
+        <v>85069</v>
+      </c>
+      <c r="J126" s="20">
         <f t="shared" si="26"/>
-        <v>85771</v>
-      </c>
-      <c r="E126" s="20">
-        <f t="shared" si="26"/>
-        <v>88678</v>
-      </c>
-      <c r="F126" s="20">
-        <f t="shared" si="26"/>
-        <v>91453</v>
-      </c>
-      <c r="G126" s="20">
-        <f t="shared" si="26"/>
-        <v>85829</v>
-      </c>
-      <c r="H126" s="20">
-        <f t="shared" si="26"/>
-        <v>86769</v>
-      </c>
-      <c r="I126" s="20">
-        <f t="shared" si="26"/>
-        <v>87784</v>
-      </c>
-      <c r="J126" s="20">
-        <f t="shared" ref="J126" si="27">SUM(J42:J48)+SUM(J50:J54)</f>
-        <v>85069</v>
+        <v>80343</v>
       </c>
       <c r="K126" s="20"/>
       <c r="L126" s="20"/>
       <c r="M126" s="20"/>
     </row>
-    <row r="127" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B127" s="11" t="s">
         <v>72</v>
       </c>
       <c r="C127" s="23">
-        <f t="shared" ref="C127:I127" si="28">C56-C126</f>
+        <f t="shared" ref="C127:I127" si="27">C56-C126</f>
         <v>0</v>
       </c>
       <c r="D127" s="23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="E127" s="23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G127" s="23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="H127" s="23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="I127" s="23">
+        <f t="shared" ref="I127:J127" si="28">I56-I126</f>
+        <v>0</v>
+      </c>
+      <c r="J127" s="23">
         <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="E127" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="F127" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="G127" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="H127" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="I127" s="23">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="J127" s="23">
-        <f t="shared" ref="J127" si="29">J56-J126</f>
         <v>0</v>
       </c>
       <c r="K127" s="26"/>
@@ -11730,116 +11731,116 @@
         <v>73</v>
       </c>
       <c r="C128" s="20">
-        <f t="shared" ref="C128:I128" si="30">SUM(C57:C60)+C62+C64</f>
-        <v>110756</v>
+        <f t="shared" ref="C128:I128" si="29">SUM(C57:C60)+C62+C64</f>
+        <v>120434</v>
       </c>
       <c r="D128" s="20">
+        <f t="shared" si="29"/>
+        <v>104864</v>
+      </c>
+      <c r="E128" s="20">
+        <f t="shared" si="29"/>
+        <v>105032</v>
+      </c>
+      <c r="F128" s="20">
+        <f t="shared" si="29"/>
+        <v>106413</v>
+      </c>
+      <c r="G128" s="20">
+        <f t="shared" si="29"/>
+        <v>105751</v>
+      </c>
+      <c r="H128" s="20">
+        <f t="shared" si="29"/>
+        <v>116730</v>
+      </c>
+      <c r="I128" s="20">
+        <f t="shared" ref="I128:J128" si="30">SUM(I57:I60)+I62+I64</f>
+        <v>126360</v>
+      </c>
+      <c r="J128" s="20">
         <f t="shared" si="30"/>
-        <v>120434</v>
-      </c>
-      <c r="E128" s="20">
-        <f t="shared" si="30"/>
-        <v>104864</v>
-      </c>
-      <c r="F128" s="20">
-        <f t="shared" si="30"/>
-        <v>105032</v>
-      </c>
-      <c r="G128" s="20">
-        <f t="shared" si="30"/>
-        <v>106413</v>
-      </c>
-      <c r="H128" s="20">
-        <f t="shared" si="30"/>
-        <v>105751</v>
-      </c>
-      <c r="I128" s="20">
-        <f t="shared" si="30"/>
-        <v>116730</v>
-      </c>
-      <c r="J128" s="20">
-        <f t="shared" ref="J128" si="31">SUM(J57:J60)+J62+J64</f>
-        <v>126360</v>
+        <v>124989</v>
       </c>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
       <c r="M128" s="20"/>
     </row>
-    <row r="129" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B129" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C129" s="23">
-        <f t="shared" ref="C129:I129" si="32">C65-C128</f>
+        <f t="shared" ref="C129:I129" si="31">C65-C128</f>
         <v>0</v>
       </c>
       <c r="D129" s="23">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="E129" s="23">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="F129" s="23">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="G129" s="23">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="H129" s="23">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="I129" s="23">
+        <f t="shared" ref="I129:J129" si="32">I65-I128</f>
+        <v>0</v>
+      </c>
+      <c r="J129" s="23">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="E129" s="23">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="F129" s="23">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="G129" s="23">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H129" s="23">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="I129" s="23">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J129" s="23">
-        <f t="shared" ref="J129" si="33">J65-J128</f>
         <v>0</v>
       </c>
       <c r="K129" s="26"/>
       <c r="L129" s="26"/>
       <c r="M129" s="26"/>
     </row>
-    <row r="130" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="17" t="s">
         <v>84</v>
       </c>
       <c r="C130" s="22">
-        <f t="shared" ref="C130:I130" si="34">C41-(C56+C65)</f>
+        <f t="shared" ref="C130:I130" si="33">C41-(C56+C65)</f>
         <v>0</v>
       </c>
       <c r="D130" s="22">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="E130" s="22">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="F130" s="22">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G130" s="22">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="H130" s="22">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="I130" s="22">
+        <f t="shared" ref="I130:J130" si="34">I41-(I56+I65)</f>
+        <v>0</v>
+      </c>
+      <c r="J130" s="22">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="E130" s="22">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="F130" s="22">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="G130" s="22">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H130" s="22">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="I130" s="22">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="J130" s="22">
-        <f t="shared" ref="J130" si="35">J41-(J56+J65)</f>
         <v>0</v>
       </c>
       <c r="K130" s="26"/>
@@ -11853,75 +11854,75 @@
         <v>75</v>
       </c>
       <c r="C131" s="20">
-        <f t="shared" ref="C131:I131" si="36">SUM(C69:C86)</f>
-        <v>-1223</v>
+        <f t="shared" ref="C131:I131" si="35">SUM(C69:C86)</f>
+        <v>2292</v>
       </c>
       <c r="D131" s="20">
+        <f t="shared" si="35"/>
+        <v>4054</v>
+      </c>
+      <c r="E131" s="20">
+        <f t="shared" si="35"/>
+        <v>3165</v>
+      </c>
+      <c r="F131" s="20">
+        <f t="shared" si="35"/>
+        <v>813</v>
+      </c>
+      <c r="G131" s="20">
+        <f t="shared" si="35"/>
+        <v>2050</v>
+      </c>
+      <c r="H131" s="20">
+        <f t="shared" si="35"/>
+        <v>2546</v>
+      </c>
+      <c r="I131" s="20">
+        <f t="shared" ref="I131:J131" si="36">SUM(I69:I86)</f>
+        <v>4288</v>
+      </c>
+      <c r="J131" s="20">
         <f t="shared" si="36"/>
-        <v>2292</v>
-      </c>
-      <c r="E131" s="20">
-        <f t="shared" si="36"/>
-        <v>4054</v>
-      </c>
-      <c r="F131" s="20">
-        <f t="shared" si="36"/>
-        <v>3165</v>
-      </c>
-      <c r="G131" s="20">
-        <f t="shared" si="36"/>
-        <v>813</v>
-      </c>
-      <c r="H131" s="20">
-        <f t="shared" si="36"/>
-        <v>2050</v>
-      </c>
-      <c r="I131" s="20">
-        <f t="shared" si="36"/>
-        <v>2546</v>
-      </c>
-      <c r="J131" s="20">
-        <f t="shared" ref="J131" si="37">SUM(J69:J86)</f>
-        <v>4288</v>
+        <v>1096</v>
       </c>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
       <c r="M131" s="20"/>
     </row>
-    <row r="132" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B132" s="11" t="s">
         <v>76</v>
       </c>
       <c r="C132" s="23">
-        <f t="shared" ref="C132:I132" si="38">C87-C131</f>
+        <f t="shared" ref="C132:I132" si="37">C87-C131</f>
         <v>0</v>
       </c>
       <c r="D132" s="23">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="E132" s="23">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="23">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="G132" s="23">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H132" s="23">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="I132" s="23">
+        <f t="shared" ref="I132:J132" si="38">I87-I131</f>
+        <v>0</v>
+      </c>
+      <c r="J132" s="23">
         <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="E132" s="23">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="F132" s="23">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="G132" s="23">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="H132" s="23">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="I132" s="23">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="J132" s="23">
-        <f t="shared" ref="J132" si="39">J87-J131</f>
         <v>0</v>
       </c>
       <c r="K132" s="26"/>
@@ -11933,75 +11934,75 @@
         <v>77</v>
       </c>
       <c r="C133" s="20">
-        <f t="shared" ref="C133:I133" si="40">SUM(C88:C99)</f>
-        <v>-2563</v>
+        <f t="shared" ref="C133:I133" si="39">SUM(C88:C99)</f>
+        <v>-9165</v>
       </c>
       <c r="D133" s="20">
+        <f t="shared" si="39"/>
+        <v>-2764</v>
+      </c>
+      <c r="E133" s="20">
+        <f t="shared" si="39"/>
+        <v>-3764</v>
+      </c>
+      <c r="F133" s="20">
+        <f t="shared" si="39"/>
+        <v>81</v>
+      </c>
+      <c r="G133" s="20">
+        <f t="shared" si="39"/>
+        <v>-2086</v>
+      </c>
+      <c r="H133" s="20">
+        <f t="shared" si="39"/>
+        <v>-6250</v>
+      </c>
+      <c r="I133" s="20">
+        <f t="shared" ref="I133:J133" si="40">SUM(I88:I99)</f>
+        <v>-6566</v>
+      </c>
+      <c r="J133" s="20">
         <f t="shared" si="40"/>
-        <v>-9165</v>
-      </c>
-      <c r="E133" s="20">
-        <f t="shared" si="40"/>
-        <v>-2764</v>
-      </c>
-      <c r="F133" s="20">
-        <f t="shared" si="40"/>
-        <v>-3764</v>
-      </c>
-      <c r="G133" s="20">
-        <f t="shared" si="40"/>
-        <v>81</v>
-      </c>
-      <c r="H133" s="20">
-        <f t="shared" si="40"/>
-        <v>-2086</v>
-      </c>
-      <c r="I133" s="20">
-        <f t="shared" si="40"/>
-        <v>-6250</v>
-      </c>
-      <c r="J133" s="20">
-        <f t="shared" ref="J133" si="41">SUM(J88:J99)</f>
-        <v>-6566</v>
+        <v>3093</v>
       </c>
       <c r="K133" s="20"/>
       <c r="L133" s="20"/>
       <c r="M133" s="20"/>
     </row>
-    <row r="134" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B134" s="11" t="s">
         <v>78</v>
       </c>
       <c r="C134" s="23">
-        <f t="shared" ref="C134:I134" si="42">C100-C133</f>
+        <f t="shared" ref="C134:I134" si="41">C100-C133</f>
         <v>0</v>
       </c>
       <c r="D134" s="23">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="E134" s="23">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="F134" s="23">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="G134" s="23">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="H134" s="23">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="I134" s="23">
+        <f t="shared" ref="I134:J134" si="42">I100-I133</f>
+        <v>0</v>
+      </c>
+      <c r="J134" s="23">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="E134" s="23">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="F134" s="23">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="G134" s="23">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="H134" s="23">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="I134" s="23">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="J134" s="23">
-        <f t="shared" ref="J134" si="43">J100-J133</f>
         <v>0</v>
       </c>
       <c r="K134" s="26"/>
@@ -12013,75 +12014,75 @@
         <v>79</v>
       </c>
       <c r="C135" s="20">
-        <f t="shared" ref="C135:I135" si="44">SUM(C101:C114)</f>
-        <v>3630</v>
+        <f t="shared" ref="C135:I135" si="43">SUM(C101:C114)</f>
+        <v>11237</v>
       </c>
       <c r="D135" s="20">
+        <f t="shared" si="43"/>
+        <v>-3792</v>
+      </c>
+      <c r="E135" s="20">
+        <f t="shared" si="43"/>
+        <v>63</v>
+      </c>
+      <c r="F135" s="20">
+        <f t="shared" si="43"/>
+        <v>-196</v>
+      </c>
+      <c r="G135" s="20">
+        <f t="shared" si="43"/>
+        <v>782</v>
+      </c>
+      <c r="H135" s="20">
+        <f t="shared" si="43"/>
+        <v>5152</v>
+      </c>
+      <c r="I135" s="20">
+        <f t="shared" ref="I135:J135" si="44">SUM(I101:I114)</f>
+        <v>5849</v>
+      </c>
+      <c r="J135" s="20">
         <f t="shared" si="44"/>
-        <v>11237</v>
-      </c>
-      <c r="E135" s="20">
-        <f t="shared" si="44"/>
-        <v>-3792</v>
-      </c>
-      <c r="F135" s="20">
-        <f t="shared" si="44"/>
-        <v>63</v>
-      </c>
-      <c r="G135" s="20">
-        <f t="shared" si="44"/>
-        <v>-196</v>
-      </c>
-      <c r="H135" s="20">
-        <f t="shared" si="44"/>
-        <v>782</v>
-      </c>
-      <c r="I135" s="20">
-        <f t="shared" si="44"/>
-        <v>5152</v>
-      </c>
-      <c r="J135" s="20">
-        <f t="shared" ref="J135" si="45">SUM(J101:J114)</f>
-        <v>5849</v>
+        <v>-1206</v>
       </c>
       <c r="K135" s="20"/>
       <c r="L135" s="20"/>
       <c r="M135" s="20"/>
     </row>
-    <row r="136" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B136" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C136" s="23">
-        <f t="shared" ref="C136:I136" si="46">C115-C135</f>
+        <f t="shared" ref="C136:I136" si="45">C115-C135</f>
         <v>0</v>
       </c>
       <c r="D136" s="23">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="E136" s="23">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="F136" s="23">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="G136" s="23">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="H136" s="23">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="I136" s="23">
+        <f t="shared" ref="I136:J136" si="46">I115-I135</f>
+        <v>0</v>
+      </c>
+      <c r="J136" s="23">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="E136" s="23">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F136" s="23">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="G136" s="23">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="H136" s="23">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="I136" s="23">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="J136" s="23">
-        <f t="shared" ref="J136" si="47">J115-J135</f>
         <v>0</v>
       </c>
       <c r="K136" s="26"/>
@@ -12093,76 +12094,76 @@
         <v>82</v>
       </c>
       <c r="C137" s="20">
-        <f t="shared" ref="C137:I137" si="48">C87+C100+C115+C116+C118</f>
-        <v>6923</v>
+        <f t="shared" ref="C137:I137" si="47">C87+C100+C115+C116+C118</f>
+        <v>11287</v>
       </c>
       <c r="D137" s="20">
+        <f t="shared" si="47"/>
+        <v>8785</v>
+      </c>
+      <c r="E137" s="20">
+        <f t="shared" si="47"/>
+        <v>8249</v>
+      </c>
+      <c r="F137" s="20">
+        <f t="shared" si="47"/>
+        <v>8947</v>
+      </c>
+      <c r="G137" s="20">
+        <f t="shared" si="47"/>
+        <v>9693</v>
+      </c>
+      <c r="H137" s="20">
+        <f t="shared" si="47"/>
+        <v>11141</v>
+      </c>
+      <c r="I137" s="20">
+        <f t="shared" ref="I137:J137" si="48">I87+I100+I115+I116+I118</f>
+        <v>14712</v>
+      </c>
+      <c r="J137" s="20">
         <f t="shared" si="48"/>
-        <v>11287</v>
-      </c>
-      <c r="E137" s="20">
-        <f t="shared" si="48"/>
-        <v>8785</v>
-      </c>
-      <c r="F137" s="20">
-        <f t="shared" si="48"/>
-        <v>8249</v>
-      </c>
-      <c r="G137" s="20">
-        <f t="shared" si="48"/>
-        <v>8947</v>
-      </c>
-      <c r="H137" s="20">
-        <f t="shared" si="48"/>
-        <v>9693</v>
-      </c>
-      <c r="I137" s="20">
-        <f t="shared" si="48"/>
-        <v>11141</v>
-      </c>
-      <c r="J137" s="20">
-        <f t="shared" ref="J137" si="49">J87+J100+J115+J116+J118</f>
-        <v>14712</v>
+        <v>17695</v>
       </c>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
       <c r="M137" s="20"/>
     </row>
-    <row r="138" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:19" s="18" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="17" t="s">
         <v>81</v>
       </c>
       <c r="C138" s="22">
-        <f t="shared" ref="C138:I138" si="50">C119-C137</f>
+        <f t="shared" ref="C138:I138" si="49">C119-C137</f>
         <v>0</v>
       </c>
       <c r="D138" s="22">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="E138" s="22">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="F138" s="22">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="G138" s="22">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="H138" s="22">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I138" s="22">
+        <f t="shared" ref="I138:J138" si="50">I119-I137</f>
+        <v>0</v>
+      </c>
+      <c r="J138" s="22">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="E138" s="22">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="F138" s="22">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="G138" s="22">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="H138" s="22">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="I138" s="22">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="J138" s="22">
-        <f t="shared" ref="J138" si="51">J119-J137</f>
         <v>0</v>
       </c>
       <c r="K138" s="26"/>
@@ -12171,8 +12172,9 @@
       <c r="O138" s="7"/>
       <c r="S138" s="7"/>
     </row>
-    <row r="139" spans="1:19" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B139" s="8"/>
+      <c r="D139" s="8"/>
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
@@ -12199,28 +12201,28 @@
         <v>4</v>
       </c>
       <c r="C141" s="27">
-        <v>4257</v>
+        <v>4276</v>
       </c>
       <c r="D141" s="27">
-        <v>4276</v>
+        <v>4313</v>
       </c>
       <c r="E141" s="27">
-        <v>4313</v>
+        <v>4330</v>
       </c>
       <c r="F141" s="27">
-        <v>4330</v>
+        <v>4362</v>
       </c>
       <c r="G141" s="27">
-        <v>4362</v>
+        <v>4377</v>
       </c>
       <c r="H141" s="27">
-        <v>4377</v>
+        <v>4770</v>
       </c>
       <c r="I141" s="27">
-        <v>4770</v>
+        <v>4995</v>
       </c>
       <c r="J141" s="27">
-        <v>4995</v>
+        <v>5026</v>
       </c>
       <c r="K141" s="20"/>
       <c r="L141" s="20"/>
@@ -12228,16 +12230,16 @@
     </row>
     <row r="142" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B142" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C142" s="28">
         <v>0.125</v>
       </c>
       <c r="D142" s="28">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="E142" s="28">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="F142" s="28">
         <v>0</v>
@@ -12264,7 +12266,7 @@
     <row r="144" spans="1:19" s="73" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C144" s="74"/>
       <c r="D144" s="74"/>
@@ -12280,277 +12282,276 @@
       <c r="O144" s="4"/>
       <c r="S144" s="4"/>
     </row>
-    <row r="145" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B145" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C145" s="27">
         <v>12500</v>
       </c>
       <c r="D145" s="27">
-        <v>12500</v>
+        <v>13300</v>
       </c>
       <c r="E145" s="27">
-        <v>13300</v>
+        <v>11700</v>
       </c>
       <c r="F145" s="27">
+        <v>11200</v>
+      </c>
+      <c r="G145" s="27">
+        <v>12600</v>
+      </c>
+      <c r="H145" s="27">
+        <v>12800</v>
+      </c>
+      <c r="I145" s="27">
         <v>11700</v>
       </c>
-      <c r="G145" s="27">
-        <v>11200</v>
-      </c>
-      <c r="H145" s="27">
-        <v>12600</v>
-      </c>
-      <c r="I145" s="27">
-        <v>12800</v>
-      </c>
       <c r="J145" s="27">
-        <v>11700</v>
-      </c>
-    </row>
-    <row r="146" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="146" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B146" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C146" s="27">
         <v>13500</v>
       </c>
       <c r="D146" s="27">
-        <v>13500</v>
+        <v>14300</v>
       </c>
       <c r="E146" s="27">
-        <v>14300</v>
+        <v>12700</v>
       </c>
       <c r="F146" s="27">
+        <v>12400</v>
+      </c>
+      <c r="G146" s="27">
+        <v>13600</v>
+      </c>
+      <c r="H146" s="27">
+        <v>13800</v>
+      </c>
+      <c r="I146" s="27">
         <v>12700</v>
       </c>
-      <c r="G146" s="27">
-        <v>12400</v>
-      </c>
-      <c r="H146" s="27">
-        <v>13600</v>
-      </c>
-      <c r="I146" s="27">
-        <v>13800</v>
-      </c>
       <c r="J146" s="27">
-        <v>12700</v>
-      </c>
-    </row>
-    <row r="147" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="147" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B147" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C147" s="36">
-        <f t="shared" ref="C147" si="52">D5</f>
-        <v>12833</v>
+        <f t="shared" ref="C147" si="51">D5</f>
+        <v>13284</v>
       </c>
       <c r="D147" s="36">
-        <f t="shared" ref="D147" si="53">E5</f>
-        <v>13284</v>
+        <f t="shared" ref="D147" si="52">E5</f>
+        <v>14260</v>
       </c>
       <c r="E147" s="36">
-        <f t="shared" ref="E147" si="54">F5</f>
-        <v>14260</v>
+        <f t="shared" ref="E147" si="53">F5</f>
+        <v>12667</v>
       </c>
       <c r="F147" s="36">
-        <f t="shared" ref="F147" si="55">G5</f>
-        <v>12667</v>
+        <f t="shared" ref="F147" si="54">G5</f>
+        <v>12859</v>
       </c>
       <c r="G147" s="36">
-        <f t="shared" ref="G147" si="56">H5</f>
-        <v>12859</v>
+        <f t="shared" ref="G147" si="55">H5</f>
+        <v>13653</v>
       </c>
       <c r="H147" s="36">
-        <f t="shared" ref="H147" si="57">I5</f>
-        <v>13653</v>
+        <f t="shared" ref="H147" si="56">I5</f>
+        <v>13674</v>
       </c>
       <c r="I147" s="36">
-        <f t="shared" ref="I147" si="58">J5</f>
-        <v>13674</v>
+        <f t="shared" ref="I147" si="57">J5</f>
+        <v>13577</v>
       </c>
       <c r="J147" s="36">
-        <f t="shared" ref="J147" si="59">K5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="J147" si="58">K5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B148" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C148" s="101" t="str">
+        <f t="shared" ref="C148" si="59">IF(D5&gt;C146, "BEAT", IF(D5&lt;C145, "MISSED", "MET"))</f>
+        <v>MET</v>
+      </c>
+      <c r="D148" s="101" t="str">
+        <f t="shared" ref="D148" si="60">IF(E5&gt;D146, "BEAT", IF(E5&lt;D145, "MISSED", "MET"))</f>
+        <v>MET</v>
+      </c>
+      <c r="E148" s="101" t="str">
+        <f t="shared" ref="E148" si="61">IF(F5&gt;E146, "BEAT", IF(F5&lt;E145, "MISSED", "MET"))</f>
+        <v>MET</v>
+      </c>
+      <c r="F148" s="101" t="str">
+        <f t="shared" ref="F148" si="62">IF(G5&gt;F146, "BEAT", IF(G5&lt;F145, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="G148" s="101" t="str">
+        <f t="shared" ref="G148" si="63">IF(H5&gt;G146, "BEAT", IF(H5&lt;G145, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="H148" s="101" t="str">
+        <f t="shared" ref="H148" si="64">IF(I5&gt;H146, "BEAT", IF(I5&lt;H145, "MISSED", "MET"))</f>
+        <v>MET</v>
+      </c>
+      <c r="I148" s="101" t="str">
+        <f t="shared" ref="I148" si="65">IF(J5&gt;I146, "BEAT", IF(J5&lt;I145, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="J148" s="101" t="str">
+        <f t="shared" ref="J148" si="66">IF(K5&gt;J146, "BEAT", IF(K5&lt;J145, "MISSED", "MET"))</f>
+        <v>MISSED</v>
+      </c>
+    </row>
+    <row r="149" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B149" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C148" s="101" t="str">
-        <f t="shared" ref="C148" si="60">IF(D5&gt;C146, "BEAT", IF(D5&lt;C145, "MISSED", "MET"))</f>
-        <v>MET</v>
-      </c>
-      <c r="D148" s="101" t="str">
-        <f t="shared" ref="D148" si="61">IF(E5&gt;D146, "BEAT", IF(E5&lt;D145, "MISSED", "MET"))</f>
-        <v>MET</v>
-      </c>
-      <c r="E148" s="101" t="str">
-        <f t="shared" ref="E148" si="62">IF(F5&gt;E146, "BEAT", IF(F5&lt;E145, "MISSED", "MET"))</f>
-        <v>MET</v>
-      </c>
-      <c r="F148" s="101" t="str">
-        <f t="shared" ref="F148" si="63">IF(G5&gt;F146, "BEAT", IF(G5&lt;F145, "MISSED", "MET"))</f>
-        <v>MET</v>
-      </c>
-      <c r="G148" s="101" t="str">
-        <f t="shared" ref="G148" si="64">IF(H5&gt;G146, "BEAT", IF(H5&lt;G145, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="H148" s="101" t="str">
-        <f t="shared" ref="H148" si="65">IF(I5&gt;H146, "BEAT", IF(I5&lt;H145, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="I148" s="101" t="str">
-        <f t="shared" ref="I148" si="66">IF(J5&gt;I146, "BEAT", IF(J5&lt;I145, "MISSED", "MET"))</f>
-        <v>MET</v>
-      </c>
-      <c r="J148" s="101" t="str">
-        <f t="shared" ref="J148" si="67">IF(K5&gt;J146, "BEAT", IF(K5&lt;J145, "MISSED", "MET"))</f>
-        <v>MISSED</v>
-      </c>
-    </row>
-    <row r="149" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B149" s="9" t="s">
-        <v>102</v>
-      </c>
       <c r="C149" s="31">
-        <v>-0.05</v>
+        <v>-0.24</v>
       </c>
       <c r="D149" s="31">
         <v>-0.24</v>
       </c>
       <c r="E149" s="31">
+        <v>-0.27</v>
+      </c>
+      <c r="F149" s="31">
+        <v>-0.32</v>
+      </c>
+      <c r="G149" s="31">
         <v>-0.24</v>
       </c>
-      <c r="F149" s="31">
-        <v>-0.27</v>
-      </c>
-      <c r="G149" s="31">
-        <v>-0.32</v>
-      </c>
       <c r="H149" s="31">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="I149" s="31">
+        <v>-0.21</v>
+      </c>
+      <c r="J149" s="31">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="150" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B150" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C150" s="31">
         <v>-0.24</v>
-      </c>
-      <c r="I149" s="31">
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="J149" s="31">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="150" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C150" s="31">
-        <v>-0.05</v>
       </c>
       <c r="D150" s="31">
         <v>-0.24</v>
       </c>
       <c r="E150" s="31">
+        <v>-0.27</v>
+      </c>
+      <c r="F150" s="31">
+        <v>-0.32</v>
+      </c>
+      <c r="G150" s="31">
         <v>-0.24</v>
       </c>
-      <c r="F150" s="31">
-        <v>-0.27</v>
-      </c>
-      <c r="G150" s="31">
-        <v>-0.32</v>
-      </c>
       <c r="H150" s="31">
-        <v>-0.24</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="I150" s="31">
-        <v>-0.14000000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="J150" s="31">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="151" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="151" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B151" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C151" s="25">
-        <f t="shared" ref="C151" si="68">D23</f>
-        <v>-0.38</v>
+        <f t="shared" ref="C151" si="67">D23</f>
+        <v>-3.88</v>
       </c>
       <c r="D151" s="25">
-        <f t="shared" ref="D151" si="69">E23</f>
-        <v>-3.88</v>
+        <f t="shared" ref="D151" si="68">E23</f>
+        <v>-0.03</v>
       </c>
       <c r="E151" s="25">
-        <f t="shared" ref="E151" si="70">F23</f>
-        <v>-0.03</v>
+        <f t="shared" ref="E151" si="69">F23</f>
+        <v>-0.19</v>
       </c>
       <c r="F151" s="25">
-        <f t="shared" ref="F151" si="71">G23</f>
-        <v>-0.19</v>
+        <f t="shared" ref="F151" si="70">G23</f>
+        <v>-0.67</v>
       </c>
       <c r="G151" s="25">
-        <f t="shared" ref="G151" si="72">H23</f>
-        <v>-0.67</v>
+        <f t="shared" ref="G151" si="71">H23</f>
+        <v>0.9</v>
       </c>
       <c r="H151" s="25">
-        <f t="shared" ref="H151" si="73">I23</f>
-        <v>0.9</v>
+        <f t="shared" ref="H151" si="72">I23</f>
+        <v>-0.12</v>
       </c>
       <c r="I151" s="25">
-        <f t="shared" ref="I151" si="74">J23</f>
-        <v>-0.12</v>
+        <f t="shared" ref="I151" si="73">J23</f>
+        <v>-0.73</v>
       </c>
       <c r="J151" s="25">
-        <f t="shared" ref="J151" si="75">K23</f>
+        <f t="shared" ref="J151" si="74">K23</f>
         <v>0</v>
       </c>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
       <c r="M151" s="20"/>
     </row>
-    <row r="152" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B152" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C152" s="101" t="str">
-        <f t="shared" ref="C152" si="76">IF(D23&gt;C150, "BEAT", IF(D23&lt;C149, "MISSED", "MET"))</f>
+        <f t="shared" ref="C152" si="75">IF(D23&gt;C150, "BEAT", IF(D23&lt;C149, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="D152" s="101" t="str">
-        <f t="shared" ref="D152" si="77">IF(E23&gt;D150, "BEAT", IF(E23&lt;D149, "MISSED", "MET"))</f>
+        <f t="shared" ref="D152" si="76">IF(E23&gt;D150, "BEAT", IF(E23&lt;D149, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="E152" s="101" t="str">
+        <f t="shared" ref="E152" si="77">IF(F23&gt;E150, "BEAT", IF(F23&lt;E149, "MISSED", "MET"))</f>
+        <v>BEAT</v>
+      </c>
+      <c r="F152" s="101" t="str">
+        <f t="shared" ref="F152" si="78">IF(G23&gt;F150, "BEAT", IF(G23&lt;F149, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
-      <c r="E152" s="101" t="str">
-        <f t="shared" ref="E152" si="78">IF(F23&gt;E150, "BEAT", IF(F23&lt;E149, "MISSED", "MET"))</f>
+      <c r="G152" s="101" t="str">
+        <f t="shared" ref="G152" si="79">IF(H23&gt;G150, "BEAT", IF(H23&lt;G149, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
-      <c r="F152" s="101" t="str">
-        <f t="shared" ref="F152" si="79">IF(G23&gt;F150, "BEAT", IF(G23&lt;F149, "MISSED", "MET"))</f>
+      <c r="H152" s="101" t="str">
+        <f t="shared" ref="H152" si="80">IF(I23&gt;H150, "BEAT", IF(I23&lt;H149, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
-      <c r="G152" s="101" t="str">
-        <f t="shared" ref="G152" si="80">IF(H23&gt;G150, "BEAT", IF(H23&lt;G149, "MISSED", "MET"))</f>
+      <c r="I152" s="101" t="str">
+        <f t="shared" ref="I152" si="81">IF(J23&gt;I150, "BEAT", IF(J23&lt;I149, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
-      <c r="H152" s="101" t="str">
-        <f t="shared" ref="H152" si="81">IF(I23&gt;H150, "BEAT", IF(I23&lt;H149, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
-      <c r="I152" s="101" t="str">
-        <f t="shared" ref="I152" si="82">IF(J23&gt;I150, "BEAT", IF(J23&lt;I149, "MISSED", "MET"))</f>
-        <v>BEAT</v>
-      </c>
       <c r="J152" s="101" t="str">
-        <f t="shared" ref="J152" si="83">IF(K23&gt;J150, "BEAT", IF(K23&lt;J149, "MISSED", "MET"))</f>
-        <v>BEAT</v>
+        <f t="shared" ref="J152" si="82">IF(K23&gt;J150, "BEAT", IF(K23&lt;J149, "MISSED", "MET"))</f>
+        <v>MISSED</v>
       </c>
       <c r="K152" s="8"/>
       <c r="L152" s="8"/>
       <c r="M152" s="8"/>
     </row>
-    <row r="153" spans="2:13" collapsed="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="P4:R4"/>
@@ -12558,7 +12559,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="J55 J133 J135 J40 N5:N6 N8:N10 N12:N19 N20:N21 C135:I135" formulaRange="1"/>
+    <ignoredError sqref="J55 J133 J135 J40 N5:N6 N8:N10 N12:N19 N20:N21" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4C4FF3-FE53-9044-97D0-0BA4944191DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546458A5-898E-8A44-B4BF-C4B914BEC026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="6" activeTab="15" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="392">
   <si>
     <t>Ticker</t>
   </si>
@@ -1355,6 +1355,9 @@
   </si>
   <si>
     <t>Percentage</t>
+  </si>
+  <si>
+    <t>Last market price for period adjusted</t>
   </si>
 </sst>
 </file>
@@ -2259,6 +2262,10 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2271,12 +2278,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2284,6 +2285,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2313,10 +2320,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="39" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11721,8 +11724,8 @@
     <v>132.75</v>
     <v>18.965</v>
     <v>2.2317999999999998</v>
-    <v>4.1550000000000002</v>
-    <v>3.8496999999999997E-2</v>
+    <v>3.355</v>
+    <v>3.1084999999999998E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -11733,20 +11736,20 @@
     <v>118.29</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46176.704395034372</v>
+    <v>46176.724033205472</v>
     <v>0</v>
     <v>110.86</v>
-    <v>563339210000</v>
+    <v>559318410000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
     <v>116.43</v>
     <v>0</v>
     <v>107.93</v>
-    <v>112.08499999999999</v>
+    <v>111.285</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>81220077</v>
+    <v>84379814</v>
     <v>145048030</v>
     <v>1989</v>
   </rv>
@@ -12581,18 +12584,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="227" t="s">
+      <c r="B2" s="229" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="228"/>
-      <c r="E2" s="227" t="s">
+      <c r="C2" s="230"/>
+      <c r="E2" s="229" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="228"/>
-      <c r="H2" s="227" t="s">
+      <c r="F2" s="230"/>
+      <c r="H2" s="229" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="228"/>
+      <c r="I2" s="230"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="187" t="s">
@@ -12606,8 +12609,8 @@
         <v>242</v>
       </c>
       <c r="F3" s="189">
-        <f ca="1">Statement!AC170</f>
-        <v>563339.21</v>
+        <f ca="1">Statement!AC171</f>
+        <v>559318.41</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -12615,7 +12618,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-8.8062398504652677</v>
+        <v>-8.808241809556387</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -12630,8 +12633,8 @@
         <v>184</v>
       </c>
       <c r="F4" s="190">
-        <f ca="1">Statement!AC171</f>
-        <v>589176.21</v>
+        <f ca="1">Statement!AC172</f>
+        <v>585155.41</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -12639,7 +12642,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>32.32676090415854</v>
+        <v>32.333922448813013</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -12648,7 +12651,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>112.08499999999999</v>
+        <v>111.285</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>246</v>
@@ -12663,7 +12666,7 @@
       </c>
       <c r="I5" s="213">
         <f ca="1">'AVG target price'!C7</f>
-        <v>36.47521819576469</v>
+        <v>36.483298773483725</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -12678,8 +12681,8 @@
         <v>240</v>
       </c>
       <c r="F6" s="192">
-        <f ca="1">Statement!AC167</f>
-        <v>-180.78225806451613</v>
+        <f ca="1">Statement!AC168</f>
+        <v>-179.49193548387098</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -12687,7 +12690,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-10.98645044949315</v>
+        <v>-10.988884344918722</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -12696,14 +12699,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>4.1550000000000002</v>
+        <v>3.355</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="193">
-        <f ca="1">Statement!AC168</f>
-        <v>9.8100174376429887</v>
+        <f ca="1">Statement!AC169</f>
+        <v>9.7399990234919915</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -12711,7 +12714,7 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>12.252322199991204</v>
+        <v>12.255023766955407</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -12726,8 +12729,8 @@
         <v>268</v>
       </c>
       <c r="F8" s="194">
-        <f ca="1">Statement!AC178</f>
-        <v>-9.7454604659952572E-3</v>
+        <f ca="1">Statement!AC179</f>
+        <v>-9.8155181410889015E-3</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -12735,7 +12738,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.89068722665841815</v>
+        <v>-0.88987712839146871</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12744,14 +12747,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.8496999999999997E-2</v>
+        <v>3.1084999999999998E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="194">
-        <f ca="1">Statement!AC179</f>
-        <v>-5.5315162599812642E-3</v>
+        <f ca="1">Statement!AC180</f>
+        <v>-5.5712809453205732E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -12766,7 +12769,7 @@
         <v>297</v>
       </c>
       <c r="F10" s="194">
-        <f ca="1">Statement!AC181</f>
+        <f ca="1">Statement!AC182</f>
         <v>0</v>
       </c>
     </row>
@@ -12782,7 +12785,7 @@
         <v>293</v>
       </c>
       <c r="F11" s="195">
-        <f ca="1">Statement!AC180</f>
+        <f ca="1">Statement!AC181</f>
         <v>0</v>
       </c>
     </row>
@@ -12798,7 +12801,7 @@
         <v>97</v>
       </c>
       <c r="F12" s="194">
-        <f>Statement!AC135</f>
+        <f>Statement!AC136</f>
         <v>-1.6402703913661776E-2</v>
       </c>
     </row>
@@ -12814,7 +12817,7 @@
         <v>99</v>
       </c>
       <c r="F13" s="194">
-        <f>Statement!AC137</f>
+        <f>Statement!AC138</f>
         <v>-3.0235021634917498E-2</v>
       </c>
     </row>
@@ -12830,7 +12833,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="195">
-        <f>Statement!AC157</f>
+        <f>Statement!AC158</f>
         <v>-3.6791978488825414E-2</v>
       </c>
     </row>
@@ -12839,8 +12842,8 @@
         <v>294</v>
       </c>
       <c r="F15" s="194">
-        <f ca="1">Statement!AC192</f>
-        <v>-2.1731134248581776E-2</v>
+        <f ca="1">Statement!AC193</f>
+        <v>-2.1887353931368002E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -12848,20 +12851,20 @@
         <v>299</v>
       </c>
       <c r="F16" s="193">
-        <f>Statement!AC191</f>
+        <f>Statement!AC192</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="229" t="s">
+      <c r="B17" s="231" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="229"/>
+      <c r="C17" s="231"/>
       <c r="E17" s="186" t="s">
         <v>300</v>
       </c>
       <c r="F17" s="196">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>5.9689614007162755E-4</v>
       </c>
     </row>
@@ -12876,7 +12879,7 @@
         <v>301</v>
       </c>
       <c r="F18" s="192">
-        <f>Statement!AC161</f>
+        <f>Statement!AC162</f>
         <v>82.9857136586363</v>
       </c>
       <c r="I18" s="50"/>
@@ -12892,7 +12895,7 @@
         <v>261</v>
       </c>
       <c r="F19" s="192">
-        <f>Statement!AC163</f>
+        <f>Statement!AC164</f>
         <v>0.10989819918487531</v>
       </c>
     </row>
@@ -12907,7 +12910,7 @@
         <v>302</v>
       </c>
       <c r="F20" s="193">
-        <f>Statement!AC164</f>
+        <f>Statement!AC165</f>
         <v>1.3708387576715642</v>
       </c>
     </row>
@@ -12929,14 +12932,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="229" t="s">
+      <c r="B25" s="231" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="229"/>
-      <c r="E25" s="227" t="s">
+      <c r="C25" s="231"/>
+      <c r="E25" s="229" t="s">
         <v>389</v>
       </c>
-      <c r="F25" s="228"/>
+      <c r="F25" s="230"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="186" t="s">
@@ -12948,7 +12951,7 @@
       <c r="E26" s="187" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="244" cm="1">
+      <c r="F26" s="226" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
         <v>44.55</v>
       </c>
@@ -12963,21 +12966,21 @@
       <c r="E27" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="F27" s="245">
+      <c r="F27" s="227">
         <f ca="1">F26/1000</f>
         <v>4.4549999999999999E-2</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="226" t="s">
+      <c r="B31" s="228" t="s">
         <v>357</v>
       </c>
-      <c r="C31" s="226"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="226"/>
-      <c r="H31" s="226"/>
+      <c r="C31" s="228"/>
+      <c r="D31" s="228"/>
+      <c r="E31" s="228"/>
+      <c r="F31" s="228"/>
+      <c r="G31" s="228"/>
+      <c r="H31" s="228"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
@@ -12996,24 +12999,24 @@
       </c>
     </row>
     <row r="37" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="226"/>
-      <c r="C37" s="226"/>
-      <c r="D37" s="226"/>
-      <c r="E37" s="226"/>
-      <c r="F37" s="226"/>
-      <c r="G37" s="226"/>
-      <c r="H37" s="226"/>
+      <c r="B37" s="228"/>
+      <c r="C37" s="228"/>
+      <c r="D37" s="228"/>
+      <c r="E37" s="228"/>
+      <c r="F37" s="228"/>
+      <c r="G37" s="228"/>
+      <c r="H37" s="228"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="226" t="s">
+      <c r="B40" s="228" t="s">
         <v>360</v>
       </c>
-      <c r="C40" s="226"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="226"/>
-      <c r="F40" s="226"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="226"/>
+      <c r="C40" s="228"/>
+      <c r="D40" s="228"/>
+      <c r="E40" s="228"/>
+      <c r="F40" s="228"/>
+      <c r="G40" s="228"/>
+      <c r="H40" s="228"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="41" t="s">
@@ -13038,13 +13041,13 @@
       </c>
     </row>
     <row r="47" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="226"/>
-      <c r="C47" s="226"/>
-      <c r="D47" s="226"/>
-      <c r="E47" s="226"/>
-      <c r="F47" s="226"/>
-      <c r="G47" s="226"/>
-      <c r="H47" s="226"/>
+      <c r="B47" s="228"/>
+      <c r="C47" s="228"/>
+      <c r="D47" s="228"/>
+      <c r="E47" s="228"/>
+      <c r="F47" s="228"/>
+      <c r="G47" s="228"/>
+      <c r="H47" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -13127,36 +13130,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="228"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="226" t="s">
+      <c r="S2" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="226"/>
-      <c r="U2" s="226"/>
-      <c r="V2" s="226"/>
-      <c r="W2" s="226"/>
-      <c r="X2" s="226"/>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="226"/>
-      <c r="AA2" s="226" t="s">
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="228" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="226"/>
-      <c r="AC2" s="226"/>
+      <c r="AB2" s="228"/>
+      <c r="AC2" s="228"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -13167,32 +13170,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="237" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
+      <c r="D4" s="237"/>
+      <c r="E4" s="237"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
+      <c r="H4" s="237"/>
+      <c r="I4" s="237"/>
+      <c r="J4" s="237"/>
+      <c r="K4" s="237"/>
+      <c r="L4" s="237"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="236" t="s">
+      <c r="S4" s="238" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="237"/>
-      <c r="U4" s="237"/>
-      <c r="V4" s="237"/>
-      <c r="W4" s="237"/>
-      <c r="X4" s="237"/>
-      <c r="Y4" s="237"/>
-      <c r="Z4" s="237"/>
-      <c r="AA4" s="237"/>
-      <c r="AB4" s="237"/>
-      <c r="AC4" s="237"/>
+      <c r="T4" s="239"/>
+      <c r="U4" s="239"/>
+      <c r="V4" s="239"/>
+      <c r="W4" s="239"/>
+      <c r="X4" s="239"/>
+      <c r="Y4" s="239"/>
+      <c r="Z4" s="239"/>
+      <c r="AA4" s="239"/>
+      <c r="AB4" s="239"/>
+      <c r="AC4" s="239"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13588,27 +13591,27 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="str">
-        <f>Statement!B142</f>
+        <f>Statement!B143</f>
         <v>External Foundry revenue</v>
       </c>
       <c r="C9" s="87">
-        <f>Statement!M142</f>
+        <f>Statement!M143</f>
         <v>0</v>
       </c>
       <c r="D9" s="87">
-        <f>Statement!N142</f>
+        <f>Statement!N143</f>
         <v>0</v>
       </c>
       <c r="E9" s="87">
-        <f>Statement!O142</f>
+        <f>Statement!O143</f>
         <v>0</v>
       </c>
       <c r="F9" s="87">
-        <f>Statement!P142</f>
+        <f>Statement!P143</f>
         <v>29</v>
       </c>
       <c r="G9" s="88">
-        <f>Statement!Q142</f>
+        <f>Statement!Q143</f>
         <v>143</v>
       </c>
       <c r="H9" s="63">
@@ -13643,35 +13646,35 @@
         <v>External Foundry revenue</v>
       </c>
       <c r="S9" s="87">
-        <f>Statement!T142</f>
+        <f>Statement!T143</f>
         <v>4</v>
       </c>
       <c r="T9" s="87">
-        <f>Statement!U142</f>
+        <f>Statement!U143</f>
         <v>18</v>
       </c>
       <c r="U9" s="87">
-        <f>Statement!V142</f>
+        <f>Statement!V143</f>
         <v>27</v>
       </c>
       <c r="V9" s="87">
-        <f>Statement!W142</f>
+        <f>Statement!W143</f>
         <v>-31</v>
       </c>
       <c r="W9" s="87">
-        <f>Statement!X142</f>
+        <f>Statement!X143</f>
         <v>-4</v>
       </c>
       <c r="X9" s="87">
-        <f>Statement!Y142</f>
+        <f>Statement!Y143</f>
         <v>8</v>
       </c>
       <c r="Y9" s="87">
-        <f>Statement!Z142</f>
+        <f>Statement!Z143</f>
         <v>170</v>
       </c>
       <c r="Z9" s="88">
-        <f>Statement!AA142</f>
+        <f>Statement!AA143</f>
         <v>170</v>
       </c>
       <c r="AA9" s="63">
@@ -13880,33 +13883,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="235" t="s">
+      <c r="C13" s="237" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="235"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="235"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="235"/>
-      <c r="L13" s="235"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="237"/>
+      <c r="F13" s="237"/>
+      <c r="G13" s="237"/>
+      <c r="H13" s="237"/>
+      <c r="I13" s="237"/>
+      <c r="J13" s="237"/>
+      <c r="K13" s="237"/>
+      <c r="L13" s="237"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="236" t="s">
+      <c r="S13" s="238" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="237"/>
-      <c r="U13" s="237"/>
-      <c r="V13" s="237"/>
-      <c r="W13" s="237"/>
-      <c r="X13" s="237"/>
-      <c r="Y13" s="237"/>
-      <c r="Z13" s="237"/>
-      <c r="AA13" s="237"/>
-      <c r="AB13" s="237"/>
-      <c r="AC13" s="237"/>
+      <c r="T13" s="239"/>
+      <c r="U13" s="239"/>
+      <c r="V13" s="239"/>
+      <c r="W13" s="239"/>
+      <c r="X13" s="239"/>
+      <c r="Y13" s="239"/>
+      <c r="Z13" s="239"/>
+      <c r="AA13" s="239"/>
+      <c r="AB13" s="239"/>
+      <c r="AC13" s="239"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -14543,35 +14546,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
-      <c r="P2" s="226" t="s">
+      <c r="I2" s="228"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
+      <c r="P2" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="226"/>
-      <c r="R2" s="226"/>
-      <c r="S2" s="226"/>
-      <c r="T2" s="226"/>
-      <c r="U2" s="226"/>
-      <c r="V2" s="226"/>
-      <c r="W2" s="226"/>
-      <c r="X2" s="226" t="s">
+      <c r="Q2" s="228"/>
+      <c r="R2" s="228"/>
+      <c r="S2" s="228"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="226"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="228"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14580,31 +14583,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="237" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
-      <c r="P4" s="237" t="s">
+      <c r="D4" s="237"/>
+      <c r="E4" s="237"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
+      <c r="H4" s="237"/>
+      <c r="I4" s="237"/>
+      <c r="J4" s="237"/>
+      <c r="K4" s="237"/>
+      <c r="L4" s="237"/>
+      <c r="P4" s="239" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="237"/>
-      <c r="R4" s="237"/>
-      <c r="S4" s="237"/>
-      <c r="T4" s="237"/>
-      <c r="U4" s="237"/>
-      <c r="V4" s="237"/>
-      <c r="W4" s="237"/>
-      <c r="X4" s="237"/>
-      <c r="Y4" s="237"/>
-      <c r="Z4" s="237"/>
+      <c r="Q4" s="239"/>
+      <c r="R4" s="239"/>
+      <c r="S4" s="239"/>
+      <c r="T4" s="239"/>
+      <c r="U4" s="239"/>
+      <c r="V4" s="239"/>
+      <c r="W4" s="239"/>
+      <c r="X4" s="239"/>
+      <c r="Y4" s="239"/>
+      <c r="Z4" s="239"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -14799,32 +14802,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="235" t="s">
+      <c r="C9" s="237" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="237"/>
+      <c r="F9" s="237"/>
+      <c r="G9" s="237"/>
+      <c r="H9" s="237"/>
+      <c r="I9" s="237"/>
+      <c r="J9" s="237"/>
+      <c r="K9" s="237"/>
+      <c r="L9" s="237"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="237" t="s">
+      <c r="P9" s="239" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="237"/>
-      <c r="R9" s="237"/>
-      <c r="S9" s="237"/>
-      <c r="T9" s="237"/>
-      <c r="U9" s="237"/>
-      <c r="V9" s="237"/>
-      <c r="W9" s="237"/>
-      <c r="X9" s="237"/>
-      <c r="Y9" s="237"/>
-      <c r="Z9" s="237"/>
+      <c r="Q9" s="239"/>
+      <c r="R9" s="239"/>
+      <c r="S9" s="239"/>
+      <c r="T9" s="239"/>
+      <c r="U9" s="239"/>
+      <c r="V9" s="239"/>
+      <c r="W9" s="239"/>
+      <c r="X9" s="239"/>
+      <c r="Y9" s="239"/>
+      <c r="Z9" s="239"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -15394,31 +15397,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="235" t="s">
+      <c r="C18" s="237" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
-      <c r="P18" s="237" t="s">
+      <c r="D18" s="237"/>
+      <c r="E18" s="237"/>
+      <c r="F18" s="237"/>
+      <c r="G18" s="237"/>
+      <c r="H18" s="237"/>
+      <c r="I18" s="237"/>
+      <c r="J18" s="237"/>
+      <c r="K18" s="237"/>
+      <c r="L18" s="237"/>
+      <c r="P18" s="239" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="237"/>
-      <c r="R18" s="237"/>
-      <c r="S18" s="237"/>
-      <c r="T18" s="237"/>
-      <c r="U18" s="237"/>
-      <c r="V18" s="237"/>
-      <c r="W18" s="237"/>
-      <c r="X18" s="237"/>
-      <c r="Y18" s="237"/>
-      <c r="Z18" s="237"/>
+      <c r="Q18" s="239"/>
+      <c r="R18" s="239"/>
+      <c r="S18" s="239"/>
+      <c r="T18" s="239"/>
+      <c r="U18" s="239"/>
+      <c r="V18" s="239"/>
+      <c r="W18" s="239"/>
+      <c r="X18" s="239"/>
+      <c r="Y18" s="239"/>
+      <c r="Z18" s="239"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -15978,60 +15981,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="228"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="240"/>
+      <c r="H3" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="228"/>
+      <c r="J3" s="228"/>
+      <c r="K3" s="228"/>
+      <c r="L3" s="228"/>
+      <c r="P3" s="242"/>
+      <c r="Q3" s="242"/>
+      <c r="R3" s="242"/>
+      <c r="S3" s="242"/>
+      <c r="T3" s="242"/>
+      <c r="U3" s="242"/>
+      <c r="V3" s="242"/>
+      <c r="W3" s="242"/>
+      <c r="X3" s="242"/>
+      <c r="Y3" s="242"/>
+      <c r="Z3" s="242"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="237" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="237"/>
+      <c r="E5" s="237"/>
+      <c r="F5" s="237"/>
+      <c r="G5" s="237"/>
+      <c r="H5" s="237"/>
+      <c r="I5" s="237"/>
+      <c r="J5" s="237"/>
+      <c r="K5" s="237"/>
+      <c r="L5" s="237"/>
+      <c r="P5" s="242"/>
+      <c r="Q5" s="242"/>
+      <c r="R5" s="242"/>
+      <c r="S5" s="242"/>
+      <c r="T5" s="242"/>
+      <c r="U5" s="242"/>
+      <c r="V5" s="242"/>
+      <c r="W5" s="242"/>
+      <c r="X5" s="242"/>
+      <c r="Y5" s="242"/>
+      <c r="Z5" s="242"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -16217,30 +16220,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="235" t="s">
+      <c r="C11" s="237" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="235"/>
-      <c r="E11" s="235"/>
-      <c r="F11" s="235"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="235"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
-      <c r="K11" s="235"/>
-      <c r="L11" s="235"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="237"/>
+      <c r="F11" s="237"/>
+      <c r="G11" s="237"/>
+      <c r="H11" s="237"/>
+      <c r="I11" s="237"/>
+      <c r="J11" s="237"/>
+      <c r="K11" s="237"/>
+      <c r="L11" s="237"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="240"/>
-      <c r="Q11" s="240"/>
-      <c r="R11" s="240"/>
-      <c r="S11" s="240"/>
-      <c r="T11" s="240"/>
-      <c r="U11" s="240"/>
-      <c r="V11" s="240"/>
-      <c r="W11" s="240"/>
-      <c r="X11" s="240"/>
-      <c r="Y11" s="240"/>
-      <c r="Z11" s="240"/>
+      <c r="P11" s="242"/>
+      <c r="Q11" s="242"/>
+      <c r="R11" s="242"/>
+      <c r="S11" s="242"/>
+      <c r="T11" s="242"/>
+      <c r="U11" s="242"/>
+      <c r="V11" s="242"/>
+      <c r="W11" s="242"/>
+      <c r="X11" s="242"/>
+      <c r="Y11" s="242"/>
+      <c r="Z11" s="242"/>
       <c r="AB11" s="109"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -16482,18 +16485,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="235" t="s">
+      <c r="C18" s="237" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
+      <c r="D18" s="237"/>
+      <c r="E18" s="237"/>
+      <c r="F18" s="237"/>
+      <c r="G18" s="237"/>
+      <c r="H18" s="237"/>
+      <c r="I18" s="237"/>
+      <c r="J18" s="237"/>
+      <c r="K18" s="237"/>
+      <c r="L18" s="237"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -16706,23 +16709,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="240"/>
-      <c r="C25" s="240"/>
+      <c r="B25" s="242"/>
+      <c r="C25" s="242"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="235" t="s">
+      <c r="C26" s="237" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="235"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="235"/>
-      <c r="G26" s="235"/>
-      <c r="H26" s="235"/>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
-      <c r="K26" s="235"/>
-      <c r="L26" s="235"/>
+      <c r="D26" s="237"/>
+      <c r="E26" s="237"/>
+      <c r="F26" s="237"/>
+      <c r="G26" s="237"/>
+      <c r="H26" s="237"/>
+      <c r="I26" s="237"/>
+      <c r="J26" s="237"/>
+      <c r="K26" s="237"/>
+      <c r="L26" s="237"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -16914,18 +16917,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="235" t="s">
+      <c r="C33" s="237" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
-      <c r="I33" s="235"/>
-      <c r="J33" s="235"/>
-      <c r="K33" s="235"/>
-      <c r="L33" s="235"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
+      <c r="I33" s="237"/>
+      <c r="J33" s="237"/>
+      <c r="K33" s="237"/>
+      <c r="L33" s="237"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17109,18 +17112,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="235" t="s">
+      <c r="C40" s="237" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="235"/>
-      <c r="E40" s="235"/>
-      <c r="F40" s="235"/>
-      <c r="G40" s="235"/>
-      <c r="H40" s="235"/>
-      <c r="I40" s="235"/>
-      <c r="J40" s="235"/>
-      <c r="K40" s="235"/>
-      <c r="L40" s="235"/>
+      <c r="D40" s="237"/>
+      <c r="E40" s="237"/>
+      <c r="F40" s="237"/>
+      <c r="G40" s="237"/>
+      <c r="H40" s="237"/>
+      <c r="I40" s="237"/>
+      <c r="J40" s="237"/>
+      <c r="K40" s="237"/>
+      <c r="L40" s="237"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -17384,12 +17387,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -17397,6 +17394,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17434,60 +17437,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240"/>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="I2" s="228"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="108"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="237" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
-      <c r="S4" s="240"/>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
-      <c r="AA4" s="240"/>
-      <c r="AB4" s="240"/>
-      <c r="AC4" s="240"/>
+      <c r="D4" s="237"/>
+      <c r="E4" s="237"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
+      <c r="H4" s="237"/>
+      <c r="I4" s="237"/>
+      <c r="J4" s="237"/>
+      <c r="K4" s="237"/>
+      <c r="L4" s="237"/>
+      <c r="S4" s="242"/>
+      <c r="T4" s="242"/>
+      <c r="U4" s="242"/>
+      <c r="V4" s="242"/>
+      <c r="W4" s="242"/>
+      <c r="X4" s="242"/>
+      <c r="Y4" s="242"/>
+      <c r="Z4" s="242"/>
+      <c r="AA4" s="242"/>
+      <c r="AB4" s="242"/>
+      <c r="AC4" s="242"/>
       <c r="AE4" s="109"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17850,18 +17853,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="235" t="s">
+      <c r="C13" s="237" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="235"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="235"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="235"/>
-      <c r="L13" s="235"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="237"/>
+      <c r="F13" s="237"/>
+      <c r="G13" s="237"/>
+      <c r="H13" s="237"/>
+      <c r="I13" s="237"/>
+      <c r="J13" s="237"/>
+      <c r="K13" s="237"/>
+      <c r="L13" s="237"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -17954,18 +17957,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="235" t="s">
+      <c r="C18" s="237" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
+      <c r="D18" s="237"/>
+      <c r="E18" s="237"/>
+      <c r="F18" s="237"/>
+      <c r="G18" s="237"/>
+      <c r="H18" s="237"/>
+      <c r="I18" s="237"/>
+      <c r="J18" s="237"/>
+      <c r="K18" s="237"/>
+      <c r="L18" s="237"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18157,18 +18160,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="235" t="s">
+      <c r="C25" s="237" t="s">
         <v>157</v>
       </c>
-      <c r="D25" s="235"/>
-      <c r="E25" s="235"/>
-      <c r="F25" s="235"/>
-      <c r="G25" s="235"/>
-      <c r="H25" s="235"/>
-      <c r="I25" s="235"/>
-      <c r="J25" s="235"/>
-      <c r="K25" s="235"/>
-      <c r="L25" s="235"/>
+      <c r="D25" s="237"/>
+      <c r="E25" s="237"/>
+      <c r="F25" s="237"/>
+      <c r="G25" s="237"/>
+      <c r="H25" s="237"/>
+      <c r="I25" s="237"/>
+      <c r="J25" s="237"/>
+      <c r="K25" s="237"/>
+      <c r="L25" s="237"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -18306,18 +18309,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="235" t="s">
+      <c r="C31" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="235"/>
-      <c r="E31" s="235"/>
-      <c r="F31" s="235"/>
-      <c r="G31" s="235"/>
-      <c r="H31" s="235"/>
-      <c r="I31" s="235"/>
-      <c r="J31" s="235"/>
-      <c r="K31" s="235"/>
-      <c r="L31" s="235"/>
+      <c r="D31" s="237"/>
+      <c r="E31" s="237"/>
+      <c r="F31" s="237"/>
+      <c r="G31" s="237"/>
+      <c r="H31" s="237"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="237"/>
+      <c r="K31" s="237"/>
+      <c r="L31" s="237"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -18456,16 +18459,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -18528,10 +18531,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="228" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="226"/>
+      <c r="C4" s="228"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -18548,7 +18551,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>112.08499999999999</v>
+        <v>111.285</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18557,7 +18560,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>563339.21</v>
+        <v>559318.41</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18616,10 +18619,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="226" t="s">
+      <c r="B15" s="228" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="226"/>
+      <c r="C15" s="228"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -18627,7 +18630,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.4019074668366824E-2</v>
+        <v>7.4511531334166436E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18636,7 +18639,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92598092533163323</v>
+        <v>0.92548846866583356</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18663,7 +18666,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13740729426085804</v>
+        <v>0.13735690560235675</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18716,60 +18719,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="228"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="240"/>
+      <c r="H3" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="228"/>
+      <c r="J3" s="228"/>
+      <c r="K3" s="228"/>
+      <c r="L3" s="228"/>
+      <c r="P3" s="242"/>
+      <c r="Q3" s="242"/>
+      <c r="R3" s="242"/>
+      <c r="S3" s="242"/>
+      <c r="T3" s="242"/>
+      <c r="U3" s="242"/>
+      <c r="V3" s="242"/>
+      <c r="W3" s="242"/>
+      <c r="X3" s="242"/>
+      <c r="Y3" s="242"/>
+      <c r="Z3" s="242"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="237" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="237"/>
+      <c r="E5" s="237"/>
+      <c r="F5" s="237"/>
+      <c r="G5" s="237"/>
+      <c r="H5" s="237"/>
+      <c r="I5" s="237"/>
+      <c r="J5" s="237"/>
+      <c r="K5" s="237"/>
+      <c r="L5" s="237"/>
+      <c r="P5" s="242"/>
+      <c r="Q5" s="242"/>
+      <c r="R5" s="242"/>
+      <c r="S5" s="242"/>
+      <c r="T5" s="242"/>
+      <c r="U5" s="242"/>
+      <c r="V5" s="242"/>
+      <c r="W5" s="242"/>
+      <c r="X5" s="242"/>
+      <c r="Y5" s="242"/>
+      <c r="Z5" s="242"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18922,7 +18925,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23281.936265269174</v>
+        <v>-23291.932656446141</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -18976,23 +18979,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6494.0162771069063</v>
+        <v>-6494.3039834257206</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5057.4210272064993</v>
+        <v>-5057.8691579644583</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3564.6263361643</v>
+        <v>-3565.1001312306958</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3263.9658992162194</v>
+        <v>-3264.5443554323961</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1407.7773010196877</v>
+        <v>-1408.0891745177687</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -19011,14 +19014,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12230.354647724826</v>
+        <v>-12238.316532259363</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="226" t="s">
+      <c r="B13" s="228" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="226"/>
+      <c r="C13" s="228"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19034,14 +19037,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13740729426085804</v>
+        <v>0.13735690560235675</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="226" t="s">
+      <c r="B18" s="228" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="226"/>
+      <c r="C18" s="228"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19049,7 +19052,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19787.806840713612</v>
+        <v>-19789.90680257104</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19058,7 +19061,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12230.354647724826</v>
+        <v>-12238.316532259363</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19067,7 +19070,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-32018.16148843844</v>
+        <v>-32028.223334830403</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19094,7 +19097,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-44260.16148843844</v>
+        <v>-44270.2233348304</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19112,7 +19115,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>-8.8062398504652677</v>
+        <v>-8.808241809556387</v>
       </c>
     </row>
   </sheetData>
@@ -19155,37 +19158,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239" t="s">
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="240"/>
+      <c r="H2" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
+      <c r="I2" s="228"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="237" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
+      <c r="D4" s="237"/>
+      <c r="E4" s="237"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
+      <c r="H4" s="237"/>
+      <c r="I4" s="237"/>
+      <c r="J4" s="237"/>
+      <c r="K4" s="237"/>
+      <c r="L4" s="237"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -19374,18 +19377,18 @@
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="235" t="s">
+      <c r="C10" s="237" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="237"/>
+      <c r="G10" s="237"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="237"/>
+      <c r="J10" s="237"/>
+      <c r="K10" s="237"/>
+      <c r="L10" s="237"/>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -19579,18 +19582,18 @@
       <c r="N15" s="90"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="235" t="s">
+      <c r="C16" s="237" t="s">
         <v>192</v>
       </c>
-      <c r="D16" s="235"/>
-      <c r="E16" s="235"/>
-      <c r="F16" s="235"/>
-      <c r="G16" s="235"/>
-      <c r="H16" s="235"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="235"/>
-      <c r="L16" s="235"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="237"/>
+      <c r="J16" s="237"/>
+      <c r="K16" s="237"/>
+      <c r="L16" s="237"/>
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -19724,18 +19727,18 @@
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="235" t="s">
+      <c r="C21" s="237" t="s">
         <v>195</v>
       </c>
-      <c r="D21" s="235"/>
-      <c r="E21" s="235"/>
-      <c r="F21" s="235"/>
-      <c r="G21" s="235"/>
-      <c r="H21" s="235"/>
-      <c r="I21" s="235"/>
-      <c r="J21" s="235"/>
-      <c r="K21" s="235"/>
-      <c r="L21" s="235"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="237"/>
+      <c r="F21" s="237"/>
+      <c r="G21" s="237"/>
+      <c r="H21" s="237"/>
+      <c r="I21" s="237"/>
+      <c r="J21" s="237"/>
+      <c r="K21" s="237"/>
+      <c r="L21" s="237"/>
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -19819,18 +19822,18 @@
       <c r="N25" s="90"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="235" t="s">
+      <c r="C26" s="237" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="235"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="235"/>
-      <c r="G26" s="235"/>
-      <c r="H26" s="235"/>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
-      <c r="K26" s="235"/>
-      <c r="L26" s="235"/>
+      <c r="D26" s="237"/>
+      <c r="E26" s="237"/>
+      <c r="F26" s="237"/>
+      <c r="G26" s="237"/>
+      <c r="H26" s="237"/>
+      <c r="I26" s="237"/>
+      <c r="J26" s="237"/>
+      <c r="K26" s="237"/>
+      <c r="L26" s="237"/>
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -20100,10 +20103,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="226" t="s">
+      <c r="B37" s="228" t="s">
         <v>201</v>
       </c>
-      <c r="C37" s="226"/>
+      <c r="C37" s="228"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20121,7 +20124,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13740729426085804</v>
+        <v>0.13735690560235675</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -20165,14 +20168,14 @@
       </c>
       <c r="C44" s="142">
         <f ca="1">C43/(1+C48)^5</f>
-        <v>32.32676090415854</v>
+        <v>32.333922448813013</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="226" t="s">
+      <c r="B46" s="228" t="s">
         <v>206</v>
       </c>
-      <c r="C46" s="226"/>
+      <c r="C46" s="228"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -20189,7 +20192,7 @@
       </c>
       <c r="C48" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13740729426085804</v>
+        <v>0.13735690560235675</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -20224,14 +20227,14 @@
       </c>
       <c r="C52" s="142">
         <f ca="1">C51/(1+C48)^5</f>
-        <v>36.47521819576469</v>
+        <v>36.483298773483725</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="226" t="s">
+      <c r="B54" s="228" t="s">
         <v>326</v>
       </c>
-      <c r="C54" s="226"/>
+      <c r="C54" s="228"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -20248,7 +20251,7 @@
       </c>
       <c r="C56" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13740729426085804</v>
+        <v>0.13735690560235675</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -20292,7 +20295,7 @@
       </c>
       <c r="C61" s="142">
         <f ca="1">C60/(1+C56)^5</f>
-        <v>-10.98645044949315</v>
+        <v>-10.988884344918722</v>
       </c>
     </row>
   </sheetData>
@@ -20344,10 +20347,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="228" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="226"/>
+      <c r="C4" s="228"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20356,7 +20359,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-8.8062398504652677</v>
+        <v>-8.808241809556387</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -20365,7 +20368,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C44</f>
-        <v>32.32676090415854</v>
+        <v>32.333922448813013</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -20374,7 +20377,7 @@
       </c>
       <c r="C7" s="132">
         <f ca="1">Multiples!C52</f>
-        <v>36.47521819576469</v>
+        <v>36.483298773483725</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -20383,7 +20386,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C61</f>
-        <v>-10.98645044949315</v>
+        <v>-10.988884344918722</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -20392,7 +20395,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>12.252322199991204</v>
+        <v>12.255023766955407</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20401,7 +20404,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>112.08499999999999</v>
+        <v>111.285</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20410,7 +20413,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.89068722665841815</v>
+        <v>-0.88987712839146871</v>
       </c>
     </row>
   </sheetData>
@@ -20475,60 +20478,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="228" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="239" t="s">
+      <c r="D3" s="228"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="240"/>
+      <c r="H3" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="226"/>
-      <c r="J3" s="226"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="226"/>
-      <c r="P3" s="240"/>
-      <c r="Q3" s="240"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="240"/>
+      <c r="I3" s="228"/>
+      <c r="J3" s="228"/>
+      <c r="K3" s="228"/>
+      <c r="L3" s="228"/>
+      <c r="P3" s="242"/>
+      <c r="Q3" s="242"/>
+      <c r="R3" s="242"/>
+      <c r="S3" s="242"/>
+      <c r="T3" s="242"/>
+      <c r="U3" s="242"/>
+      <c r="V3" s="242"/>
+      <c r="W3" s="242"/>
+      <c r="X3" s="242"/>
+      <c r="Y3" s="242"/>
+      <c r="Z3" s="242"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="237" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
+      <c r="D5" s="237"/>
+      <c r="E5" s="237"/>
+      <c r="F5" s="237"/>
+      <c r="G5" s="237"/>
+      <c r="H5" s="237"/>
+      <c r="I5" s="237"/>
+      <c r="J5" s="237"/>
+      <c r="K5" s="237"/>
+      <c r="L5" s="237"/>
+      <c r="P5" s="242"/>
+      <c r="Q5" s="242"/>
+      <c r="R5" s="242"/>
+      <c r="S5" s="242"/>
+      <c r="T5" s="242"/>
+      <c r="U5" s="242"/>
+      <c r="V5" s="242"/>
+      <c r="W5" s="242"/>
+      <c r="X5" s="242"/>
+      <c r="Y5" s="242"/>
+      <c r="Z5" s="242"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20663,7 +20666,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-964531.40856467618</v>
+        <v>-964945.54221544415</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20717,23 +20720,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13169.203119622322</v>
+        <v>-13169.786558712953</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19104.137327954715</v>
+        <v>-19105.830117915226</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27713.754562836421</v>
+        <v>-27717.438157958284</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40203.448016742455</v>
+        <v>-40210.573071088947</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58321.842634861219</v>
+        <v>-58334.763028636487</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20752,15 +20755,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-506682.99497121631</v>
+        <v>-507012.84243825806</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="243" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="242"/>
+      <c r="C14" s="244"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -20768,7 +20771,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>112.08499999999999</v>
+        <v>111.285</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -20777,7 +20780,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-134.78658588007033</v>
+        <v>-134.85738825558497</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -20787,20 +20790,20 @@
       <c r="C17" s="158">
         <v>0.65</v>
       </c>
-      <c r="E17" s="243" t="s">
+      <c r="E17" s="245" t="s">
         <v>223</v>
       </c>
-      <c r="F17" s="243"/>
-      <c r="G17" s="243"/>
-      <c r="H17" s="243"/>
-      <c r="I17" s="243"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
+      <c r="I17" s="245"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="241" t="s">
+      <c r="B19" s="243" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="242"/>
+      <c r="C19" s="244"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -20816,7 +20819,7 @@
       </c>
       <c r="C21" s="161">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13740729426085804</v>
+        <v>0.13735690560235675</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -20834,7 +20837,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>563339.21</v>
+        <v>559318.41</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -20861,15 +20864,15 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>575581.21</v>
+        <v>571560.41</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="241" t="s">
+      <c r="B28" s="243" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="242"/>
+      <c r="C28" s="244"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -20877,7 +20880,7 @@
       </c>
       <c r="C29" s="162">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158512.38566201713</v>
+        <v>-158538.3909343119</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -20886,7 +20889,7 @@
       </c>
       <c r="C30" s="162">
         <f ca="1">L11</f>
-        <v>-506682.99497121631</v>
+        <v>-507012.84243825806</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -20895,7 +20898,7 @@
       </c>
       <c r="C31" s="165">
         <f ca="1">C29+C30</f>
-        <v>-665195.38063323346</v>
+        <v>-665551.23337257002</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -20922,7 +20925,7 @@
       </c>
       <c r="C34" s="165">
         <f ca="1">C31+C32-C33</f>
-        <v>-677437.38063323346</v>
+        <v>-677793.23337257002</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -20940,22 +20943,22 @@
       </c>
       <c r="C36" s="168">
         <f ca="1">C34/C35</f>
-        <v>-134.78658588007033</v>
+        <v>-134.85738825558497</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="235" t="s">
+      <c r="C39" s="237" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
-      <c r="I39" s="235"/>
-      <c r="J39" s="235"/>
-      <c r="K39" s="235"/>
-      <c r="L39" s="235"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
+      <c r="I39" s="237"/>
+      <c r="J39" s="237"/>
+      <c r="K39" s="237"/>
+      <c r="L39" s="237"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -21387,17 +21390,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -21407,7 +21410,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0548B83C-60BF-4548-84AB-1D4A73B251A4}">
-  <dimension ref="A1:AE207"/>
+  <dimension ref="A1:AE208"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -28546,426 +28549,428 @@
       <c r="AA129" s="67"/>
       <c r="AC129" s="62">
         <f ca="1">Overview!C5</f>
-        <v>112.08499999999999</v>
-      </c>
-    </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B131" s="1"/>
-    </row>
-    <row r="132" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="14" t="s">
+        <v>111.285</v>
+      </c>
+    </row>
+    <row r="130" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B130" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="C130" s="26"/>
+      <c r="D130" s="26"/>
+      <c r="E130" s="26"/>
+      <c r="F130" s="26"/>
+      <c r="G130" s="26"/>
+      <c r="H130" s="26"/>
+      <c r="I130" s="26"/>
+      <c r="J130" s="26"/>
+      <c r="K130" s="26"/>
+      <c r="L130" s="26"/>
+      <c r="M130" s="64">
+        <f>M129/M84</f>
+        <v>51.31</v>
+      </c>
+      <c r="N130" s="64">
+        <f t="shared" ref="N130:Q130" si="75">N129/N84</f>
+        <v>26.43</v>
+      </c>
+      <c r="O130" s="64">
+        <f t="shared" si="75"/>
+        <v>50.25</v>
+      </c>
+      <c r="P130" s="64">
+        <f t="shared" si="75"/>
+        <v>20.3</v>
+      </c>
+      <c r="Q130" s="64">
+        <f t="shared" si="75"/>
+        <v>36.200000000000003</v>
+      </c>
+      <c r="T130" s="67"/>
+      <c r="U130" s="67"/>
+      <c r="V130" s="67"/>
+      <c r="W130" s="67"/>
+      <c r="X130" s="67"/>
+      <c r="Y130" s="67"/>
+      <c r="Z130" s="67"/>
+      <c r="AA130" s="67"/>
+      <c r="AC130" s="64">
+        <f t="shared" ref="AC130" ca="1" si="76">AC129/AC84</f>
+        <v>111.285</v>
+      </c>
+    </row>
+    <row r="132" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B132" s="1"/>
+    </row>
+    <row r="133" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C132" s="15"/>
-      <c r="D132" s="15"/>
-      <c r="E132" s="15"/>
-      <c r="F132" s="15"/>
-      <c r="G132" s="15"/>
-      <c r="H132" s="15"/>
-      <c r="I132" s="15"/>
-      <c r="J132" s="15"/>
-      <c r="K132" s="15"/>
-      <c r="L132" s="15"/>
-      <c r="M132" s="15"/>
-      <c r="N132" s="15"/>
-      <c r="O132" s="15"/>
-      <c r="P132" s="15"/>
-      <c r="Q132" s="15"/>
-      <c r="T132" s="15"/>
-      <c r="U132" s="15"/>
-      <c r="V132" s="15"/>
-      <c r="W132" s="15"/>
-      <c r="X132" s="15"/>
-      <c r="Y132" s="15"/>
-      <c r="Z132" s="15"/>
-      <c r="AA132" s="15"/>
-      <c r="AC132" s="15"/>
-    </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B133" s="20" t="s">
+      <c r="C133" s="15"/>
+      <c r="D133" s="15"/>
+      <c r="E133" s="15"/>
+      <c r="F133" s="15"/>
+      <c r="G133" s="15"/>
+      <c r="H133" s="15"/>
+      <c r="I133" s="15"/>
+      <c r="J133" s="15"/>
+      <c r="K133" s="15"/>
+      <c r="L133" s="15"/>
+      <c r="M133" s="15"/>
+      <c r="N133" s="15"/>
+      <c r="O133" s="15"/>
+      <c r="P133" s="15"/>
+      <c r="Q133" s="15"/>
+      <c r="T133" s="15"/>
+      <c r="U133" s="15"/>
+      <c r="V133" s="15"/>
+      <c r="W133" s="15"/>
+      <c r="X133" s="15"/>
+      <c r="Y133" s="15"/>
+      <c r="Z133" s="15"/>
+      <c r="AA133" s="15"/>
+      <c r="AC133" s="15"/>
+    </row>
+    <row r="134" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B134" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="M133" s="73">
+      <c r="M134" s="73">
         <f>M124/M5</f>
         <v>0.25141729094958493</v>
       </c>
-      <c r="N133" s="73">
+      <c r="N134" s="73">
         <f>N124/N5</f>
         <v>0.12714498683667966</v>
       </c>
-      <c r="O133" s="73">
+      <c r="O134" s="73">
         <f>O124/O5</f>
         <v>3.088810208748248E-2</v>
       </c>
-      <c r="P133" s="73">
+      <c r="P134" s="73">
         <f>P124/P5</f>
         <v>-0.3621965688028474</v>
       </c>
-      <c r="Q133" s="73">
+      <c r="Q134" s="73">
         <f>Q124/Q5</f>
         <v>4.9193044860272833E-4</v>
       </c>
-      <c r="T133" s="76"/>
-      <c r="U133" s="76"/>
-      <c r="V133" s="76"/>
-      <c r="W133" s="76"/>
-      <c r="X133" s="76"/>
-      <c r="Y133" s="76"/>
-      <c r="Z133" s="76"/>
-      <c r="AA133" s="76"/>
-      <c r="AC133" s="73">
+      <c r="T134" s="76"/>
+      <c r="U134" s="76"/>
+      <c r="V134" s="76"/>
+      <c r="W134" s="76"/>
+      <c r="X134" s="76"/>
+      <c r="Y134" s="76"/>
+      <c r="Z134" s="76"/>
+      <c r="AA134" s="76"/>
+      <c r="AC134" s="73">
         <f>AC124/AC5</f>
         <v>-6.2645313691572266E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B134" s="20" t="s">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B135" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="M134" s="74">
+      <c r="M135" s="74">
         <f>M5/M36</f>
         <v>0.46924693894516822</v>
       </c>
-      <c r="N134" s="74">
+      <c r="N135" s="74">
         <f>N5/N36</f>
         <v>0.34625459218134791</v>
       </c>
-      <c r="O134" s="74">
+      <c r="O135" s="74">
         <f>O5/O36</f>
         <v>0.2830685068799198</v>
       </c>
-      <c r="P134" s="74">
+      <c r="P135" s="74">
         <f>P5/P36</f>
         <v>0.27025472682393059</v>
       </c>
-      <c r="Q134" s="74">
+      <c r="Q135" s="74">
         <f>Q5/Q36</f>
         <v>0.24997989868939455</v>
       </c>
-      <c r="T134" s="77"/>
-      <c r="U134" s="77"/>
-      <c r="V134" s="77"/>
-      <c r="W134" s="77"/>
-      <c r="X134" s="77"/>
-      <c r="Y134" s="77"/>
-      <c r="Z134" s="77"/>
-      <c r="AA134" s="77"/>
-      <c r="AC134" s="74">
+      <c r="T135" s="77"/>
+      <c r="U135" s="77"/>
+      <c r="V135" s="77"/>
+      <c r="W135" s="77"/>
+      <c r="X135" s="77"/>
+      <c r="Y135" s="77"/>
+      <c r="Z135" s="77"/>
+      <c r="AA135" s="77"/>
+      <c r="AC135" s="74">
         <f>AC5/AC36</f>
         <v>0.26183449243176904</v>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B135" s="32" t="s">
+    <row r="136" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B136" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="M135" s="75">
-        <f t="shared" ref="M135:P135" si="75">M133*M134</f>
+      <c r="M136" s="75">
+        <f t="shared" ref="M136:P136" si="77">M134*M135</f>
         <v>0.11797679417597948</v>
       </c>
-      <c r="N135" s="75">
-        <f t="shared" si="75"/>
+      <c r="N136" s="75">
+        <f t="shared" si="77"/>
         <v>4.4024535565037361E-2</v>
       </c>
-      <c r="O135" s="75">
-        <f t="shared" si="75"/>
+      <c r="O136" s="75">
+        <f t="shared" si="77"/>
         <v>8.7434489382581995E-3</v>
       </c>
-      <c r="P135" s="75">
-        <f t="shared" si="75"/>
+      <c r="P136" s="75">
+        <f t="shared" si="77"/>
         <v>-9.7885334758378503E-2</v>
       </c>
-      <c r="Q135" s="75">
-        <f>Q133*Q134</f>
+      <c r="Q136" s="75">
+        <f>Q134*Q135</f>
         <v>1.2297272370393844E-4</v>
       </c>
-      <c r="T135" s="78"/>
-      <c r="U135" s="78"/>
-      <c r="V135" s="78"/>
-      <c r="W135" s="78"/>
-      <c r="X135" s="78"/>
-      <c r="Y135" s="78"/>
-      <c r="Z135" s="78"/>
-      <c r="AA135" s="78"/>
-      <c r="AC135" s="75">
-        <f>AC133*AC134</f>
+      <c r="T136" s="78"/>
+      <c r="U136" s="78"/>
+      <c r="V136" s="78"/>
+      <c r="W136" s="78"/>
+      <c r="X136" s="78"/>
+      <c r="Y136" s="78"/>
+      <c r="Z136" s="78"/>
+      <c r="AA136" s="78"/>
+      <c r="AC136" s="75">
+        <f>AC134*AC135</f>
         <v>-1.6402703913661776E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B136" s="20" t="s">
+    <row r="137" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B137" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="M136" s="74">
+      <c r="M137" s="74">
         <f>M36/M48</f>
         <v>1.7654286043756748</v>
       </c>
-      <c r="N136" s="74">
+      <c r="N137" s="74">
         <f>N36/N48</f>
         <v>1.7954803151159007</v>
       </c>
-      <c r="O136" s="74">
+      <c r="O137" s="74">
         <f>O36/O48</f>
         <v>1.8143005966474097</v>
       </c>
-      <c r="P136" s="74">
+      <c r="P137" s="74">
         <f>P36/P48</f>
         <v>1.9792988818374131</v>
       </c>
-      <c r="Q136" s="74">
+      <c r="Q137" s="74">
         <f>Q36/Q48</f>
         <v>1.8500800658027143</v>
       </c>
-      <c r="T136" s="79"/>
-      <c r="U136" s="79"/>
-      <c r="V136" s="79"/>
-      <c r="W136" s="79"/>
-      <c r="X136" s="79"/>
-      <c r="Y136" s="79"/>
-      <c r="Z136" s="79"/>
-      <c r="AA136" s="79"/>
-      <c r="AC136" s="74">
+      <c r="T137" s="79"/>
+      <c r="U137" s="79"/>
+      <c r="V137" s="79"/>
+      <c r="W137" s="79"/>
+      <c r="X137" s="79"/>
+      <c r="Y137" s="79"/>
+      <c r="Z137" s="79"/>
+      <c r="AA137" s="79"/>
+      <c r="AC137" s="74">
         <f>AC36/AC48</f>
         <v>1.8432949710038242</v>
       </c>
     </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B137" s="32" t="s">
+    <row r="138" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B138" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="M137" s="75">
-        <f t="shared" ref="M137:P137" si="76">M135*M136</f>
+      <c r="M138" s="75">
+        <f t="shared" ref="M138:P138" si="78">M136*M137</f>
         <v>0.20827960709081569</v>
       </c>
-      <c r="N137" s="75">
-        <f t="shared" si="76"/>
+      <c r="N138" s="75">
+        <f t="shared" si="78"/>
         <v>7.904518698914445E-2</v>
       </c>
-      <c r="O137" s="75">
-        <f t="shared" si="76"/>
+      <c r="O138" s="75">
+        <f t="shared" si="78"/>
         <v>1.5863244625438012E-2</v>
       </c>
-      <c r="P137" s="75">
-        <f t="shared" si="76"/>
+      <c r="P138" s="75">
+        <f t="shared" si="78"/>
         <v>-0.19374433363553945</v>
       </c>
-      <c r="Q137" s="75">
-        <f>Q135*Q136</f>
+      <c r="Q138" s="75">
+        <f>Q136*Q137</f>
         <v>2.2750938476212145E-4</v>
       </c>
-      <c r="T137" s="78"/>
-      <c r="U137" s="78"/>
-      <c r="V137" s="78"/>
-      <c r="W137" s="78"/>
-      <c r="X137" s="78"/>
-      <c r="Y137" s="78"/>
-      <c r="Z137" s="78"/>
-      <c r="AA137" s="78"/>
-      <c r="AC137" s="75">
-        <f>AC135*AC136</f>
+      <c r="T138" s="78"/>
+      <c r="U138" s="78"/>
+      <c r="V138" s="78"/>
+      <c r="W138" s="78"/>
+      <c r="X138" s="78"/>
+      <c r="Y138" s="78"/>
+      <c r="Z138" s="78"/>
+      <c r="AA138" s="78"/>
+      <c r="AC138" s="75">
+        <f>AC136*AC137</f>
         <v>-3.0235021634917498E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B139" s="1"/>
-    </row>
-    <row r="140" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="11"/>
-      <c r="B140" s="14" t="s">
+    <row r="140" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B140" s="1"/>
+    </row>
+    <row r="141" spans="1:31" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="11"/>
+      <c r="B141" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="R140" s="1"/>
-      <c r="S140" s="1"/>
-      <c r="AB140" s="1"/>
-      <c r="AD140" s="1"/>
-      <c r="AE140" s="1"/>
-    </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B141" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="M141" s="61">
-        <v>0</v>
-      </c>
-      <c r="N141" s="61">
-        <v>-27005</v>
-      </c>
-      <c r="O141" s="61">
-        <v>-18024</v>
-      </c>
-      <c r="P141" s="61">
-        <v>-17288</v>
-      </c>
-      <c r="Q141" s="61">
-        <v>-17683</v>
-      </c>
-      <c r="T141" s="61">
-        <v>-4278</v>
-      </c>
-      <c r="U141" s="61">
-        <v>-4321</v>
-      </c>
-      <c r="V141" s="61">
-        <v>-4313</v>
-      </c>
-      <c r="W141" s="61">
-        <v>-4698</v>
-      </c>
-      <c r="X141" s="61">
-        <v>-4421</v>
-      </c>
-      <c r="Y141" s="61">
-        <v>-4227</v>
-      </c>
-      <c r="Z141" s="61">
-        <v>-4337</v>
-      </c>
-      <c r="AA141" s="61">
-        <v>-5251</v>
-      </c>
-      <c r="AC141" s="63">
-        <f>SUM(X141:AA141)</f>
-        <v>-18236</v>
-      </c>
+      <c r="R141" s="1"/>
+      <c r="S141" s="1"/>
+      <c r="AB141" s="1"/>
+      <c r="AD141" s="1"/>
+      <c r="AE141" s="1"/>
     </row>
     <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B142" s="20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M142" s="61">
         <v>0</v>
       </c>
       <c r="N142" s="61">
-        <v>0</v>
+        <v>-27005</v>
       </c>
       <c r="O142" s="61">
-        <v>0</v>
+        <v>-18024</v>
       </c>
       <c r="P142" s="61">
-        <f>P108+P141</f>
-        <v>29</v>
+        <v>-17288</v>
       </c>
       <c r="Q142" s="61">
-        <f>Q108+Q141</f>
-        <v>143</v>
+        <v>-17683</v>
       </c>
       <c r="T142" s="61">
-        <f>T108+T141</f>
-        <v>4</v>
+        <v>-4278</v>
       </c>
       <c r="U142" s="61">
-        <f t="shared" ref="U142:AA142" si="77">U108+U141</f>
-        <v>18</v>
+        <v>-4321</v>
       </c>
       <c r="V142" s="61">
-        <f t="shared" si="77"/>
-        <v>27</v>
+        <v>-4313</v>
       </c>
       <c r="W142" s="61">
-        <f t="shared" si="77"/>
-        <v>-31</v>
+        <v>-4698</v>
       </c>
       <c r="X142" s="61">
-        <f t="shared" si="77"/>
-        <v>-4</v>
+        <v>-4421</v>
       </c>
       <c r="Y142" s="61">
-        <f t="shared" si="77"/>
-        <v>8</v>
+        <v>-4227</v>
       </c>
       <c r="Z142" s="61">
-        <f t="shared" si="77"/>
-        <v>170</v>
+        <v>-4337</v>
       </c>
       <c r="AA142" s="61">
-        <f t="shared" si="77"/>
-        <v>170</v>
+        <v>-5251</v>
       </c>
       <c r="AC142" s="63">
         <f>SUM(X142:AA142)</f>
+        <v>-18236</v>
+      </c>
+    </row>
+    <row r="143" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B143" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="M143" s="61">
+        <v>0</v>
+      </c>
+      <c r="N143" s="61">
+        <v>0</v>
+      </c>
+      <c r="O143" s="61">
+        <v>0</v>
+      </c>
+      <c r="P143" s="61">
+        <f>P108+P142</f>
+        <v>29</v>
+      </c>
+      <c r="Q143" s="61">
+        <f>Q108+Q142</f>
+        <v>143</v>
+      </c>
+      <c r="T143" s="61">
+        <f>T108+T142</f>
+        <v>4</v>
+      </c>
+      <c r="U143" s="61">
+        <f t="shared" ref="U143:AA143" si="79">U108+U142</f>
+        <v>18</v>
+      </c>
+      <c r="V143" s="61">
+        <f t="shared" si="79"/>
+        <v>27</v>
+      </c>
+      <c r="W143" s="61">
+        <f t="shared" si="79"/>
+        <v>-31</v>
+      </c>
+      <c r="X143" s="61">
+        <f t="shared" si="79"/>
+        <v>-4</v>
+      </c>
+      <c r="Y143" s="61">
+        <f t="shared" si="79"/>
+        <v>8</v>
+      </c>
+      <c r="Z143" s="61">
+        <f t="shared" si="79"/>
+        <v>170</v>
+      </c>
+      <c r="AA143" s="61">
+        <f t="shared" si="79"/>
+        <v>170</v>
+      </c>
+      <c r="AC143" s="63">
+        <f>SUM(X143:AA143)</f>
         <v>344</v>
       </c>
     </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B144" s="1"/>
-    </row>
-    <row r="145" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="14" t="s">
+    <row r="145" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B145" s="1"/>
+    </row>
+    <row r="146" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B146" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="C145" s="172"/>
-      <c r="D145" s="172"/>
-      <c r="E145" s="172"/>
-      <c r="F145" s="172"/>
-      <c r="G145" s="172"/>
-      <c r="H145" s="172"/>
-      <c r="I145" s="172"/>
-      <c r="J145" s="172"/>
-      <c r="K145" s="172"/>
-      <c r="L145" s="172"/>
-      <c r="M145" s="172"/>
-      <c r="N145" s="172"/>
-      <c r="O145" s="172"/>
-      <c r="P145" s="172"/>
-      <c r="Q145" s="172"/>
-      <c r="T145" s="172"/>
-      <c r="U145" s="172"/>
-      <c r="V145" s="172"/>
-      <c r="W145" s="172"/>
-      <c r="X145" s="172"/>
-      <c r="Y145" s="172"/>
-      <c r="Z145" s="172"/>
-      <c r="AA145" s="172"/>
-      <c r="AC145" s="172"/>
-    </row>
-    <row r="146" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B146" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C146" s="49"/>
-      <c r="D146" s="49"/>
-      <c r="E146" s="49"/>
-      <c r="F146" s="49"/>
-      <c r="G146" s="49"/>
-      <c r="H146" s="49"/>
-      <c r="I146" s="49"/>
-      <c r="J146" s="49"/>
-      <c r="K146" s="49"/>
-      <c r="L146" s="49"/>
-      <c r="M146" s="49"/>
-      <c r="N146" s="49"/>
-      <c r="O146" s="49"/>
-      <c r="P146" s="49"/>
-      <c r="Q146" s="49"/>
-      <c r="T146" s="21">
-        <v>12500</v>
-      </c>
-      <c r="U146" s="21">
-        <v>13300</v>
-      </c>
-      <c r="V146" s="21">
-        <v>11700</v>
-      </c>
-      <c r="W146" s="21">
-        <v>11200</v>
-      </c>
-      <c r="X146" s="21">
-        <v>12600</v>
-      </c>
-      <c r="Y146" s="21">
-        <v>12800</v>
-      </c>
-      <c r="Z146" s="21">
-        <v>11700</v>
-      </c>
-      <c r="AA146" s="21">
-        <v>13800</v>
-      </c>
-      <c r="AC146" s="49"/>
+      <c r="C146" s="172"/>
+      <c r="D146" s="172"/>
+      <c r="E146" s="172"/>
+      <c r="F146" s="172"/>
+      <c r="G146" s="172"/>
+      <c r="H146" s="172"/>
+      <c r="I146" s="172"/>
+      <c r="J146" s="172"/>
+      <c r="K146" s="172"/>
+      <c r="L146" s="172"/>
+      <c r="M146" s="172"/>
+      <c r="N146" s="172"/>
+      <c r="O146" s="172"/>
+      <c r="P146" s="172"/>
+      <c r="Q146" s="172"/>
+      <c r="T146" s="172"/>
+      <c r="U146" s="172"/>
+      <c r="V146" s="172"/>
+      <c r="W146" s="172"/>
+      <c r="X146" s="172"/>
+      <c r="Y146" s="172"/>
+      <c r="Z146" s="172"/>
+      <c r="AA146" s="172"/>
+      <c r="AC146" s="172"/>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B147" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C147" s="49"/>
       <c r="D147" s="49"/>
@@ -28983,34 +28988,34 @@
       <c r="P147" s="49"/>
       <c r="Q147" s="49"/>
       <c r="T147" s="21">
-        <v>13500</v>
+        <v>12500</v>
       </c>
       <c r="U147" s="21">
-        <v>14300</v>
+        <v>13300</v>
       </c>
       <c r="V147" s="21">
-        <v>12700</v>
+        <v>11700</v>
       </c>
       <c r="W147" s="21">
-        <v>12400</v>
+        <v>11200</v>
       </c>
       <c r="X147" s="21">
-        <v>13600</v>
+        <v>12600</v>
       </c>
       <c r="Y147" s="21">
+        <v>12800</v>
+      </c>
+      <c r="Z147" s="21">
+        <v>11700</v>
+      </c>
+      <c r="AA147" s="21">
         <v>13800</v>
-      </c>
-      <c r="Z147" s="21">
-        <v>12700</v>
-      </c>
-      <c r="AA147" s="21">
-        <v>14800</v>
       </c>
       <c r="AC147" s="49"/>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B148" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C148" s="49"/>
       <c r="D148" s="49"/>
@@ -29027,43 +29032,35 @@
       <c r="O148" s="49"/>
       <c r="P148" s="49"/>
       <c r="Q148" s="49"/>
-      <c r="T148" s="25">
-        <f t="shared" ref="T148:AA148" si="78">U5</f>
-        <v>13284</v>
-      </c>
-      <c r="U148" s="25">
-        <f t="shared" si="78"/>
-        <v>14260</v>
-      </c>
-      <c r="V148" s="25">
-        <f t="shared" si="78"/>
-        <v>12667</v>
-      </c>
-      <c r="W148" s="25">
-        <f t="shared" si="78"/>
-        <v>12859</v>
-      </c>
-      <c r="X148" s="25">
-        <f t="shared" si="78"/>
-        <v>13653</v>
-      </c>
-      <c r="Y148" s="25">
-        <f t="shared" si="78"/>
-        <v>13674</v>
-      </c>
-      <c r="Z148" s="25">
-        <f t="shared" si="78"/>
-        <v>13577</v>
-      </c>
-      <c r="AA148" s="25">
-        <f t="shared" si="78"/>
-        <v>0</v>
+      <c r="T148" s="21">
+        <v>13500</v>
+      </c>
+      <c r="U148" s="21">
+        <v>14300</v>
+      </c>
+      <c r="V148" s="21">
+        <v>12700</v>
+      </c>
+      <c r="W148" s="21">
+        <v>12400</v>
+      </c>
+      <c r="X148" s="21">
+        <v>13600</v>
+      </c>
+      <c r="Y148" s="21">
+        <v>13800</v>
+      </c>
+      <c r="Z148" s="21">
+        <v>12700</v>
+      </c>
+      <c r="AA148" s="21">
+        <v>14800</v>
       </c>
       <c r="AC148" s="49"/>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B149" s="20" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="C149" s="49"/>
       <c r="D149" s="49"/>
@@ -29080,43 +29077,43 @@
       <c r="O149" s="49"/>
       <c r="P149" s="49"/>
       <c r="Q149" s="49"/>
-      <c r="T149" s="173" t="str">
-        <f t="shared" ref="T149:AA149" si="79">IF(U5&gt;T147, "BEAT", IF(U5&lt;T146, "MISSED", "MET"))</f>
-        <v>MET</v>
-      </c>
-      <c r="U149" s="173" t="str">
-        <f t="shared" si="79"/>
-        <v>MET</v>
-      </c>
-      <c r="V149" s="173" t="str">
-        <f t="shared" si="79"/>
-        <v>MET</v>
-      </c>
-      <c r="W149" s="173" t="str">
-        <f t="shared" si="79"/>
-        <v>BEAT</v>
-      </c>
-      <c r="X149" s="173" t="str">
-        <f t="shared" si="79"/>
-        <v>BEAT</v>
-      </c>
-      <c r="Y149" s="173" t="str">
-        <f t="shared" si="79"/>
-        <v>MET</v>
-      </c>
-      <c r="Z149" s="173" t="str">
-        <f t="shared" si="79"/>
-        <v>BEAT</v>
-      </c>
-      <c r="AA149" s="173" t="str">
-        <f t="shared" si="79"/>
-        <v>MISSED</v>
+      <c r="T149" s="25">
+        <f t="shared" ref="T149:AA149" si="80">U5</f>
+        <v>13284</v>
+      </c>
+      <c r="U149" s="25">
+        <f t="shared" si="80"/>
+        <v>14260</v>
+      </c>
+      <c r="V149" s="25">
+        <f t="shared" si="80"/>
+        <v>12667</v>
+      </c>
+      <c r="W149" s="25">
+        <f t="shared" si="80"/>
+        <v>12859</v>
+      </c>
+      <c r="X149" s="25">
+        <f t="shared" si="80"/>
+        <v>13653</v>
+      </c>
+      <c r="Y149" s="25">
+        <f t="shared" si="80"/>
+        <v>13674</v>
+      </c>
+      <c r="Z149" s="25">
+        <f t="shared" si="80"/>
+        <v>13577</v>
+      </c>
+      <c r="AA149" s="25">
+        <f t="shared" si="80"/>
+        <v>0</v>
       </c>
       <c r="AC149" s="49"/>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B150" s="20" t="s">
-        <v>367</v>
+        <v>182</v>
       </c>
       <c r="C150" s="49"/>
       <c r="D150" s="49"/>
@@ -29133,35 +29130,43 @@
       <c r="O150" s="49"/>
       <c r="P150" s="49"/>
       <c r="Q150" s="49"/>
-      <c r="T150" s="219">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="U150" s="219">
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="V150" s="219">
-        <v>0.33800000000000002</v>
-      </c>
-      <c r="W150" s="219">
-        <v>0.34300000000000003</v>
-      </c>
-      <c r="X150" s="219">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="Y150" s="219">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="Z150" s="219">
-        <v>0.32300000000000001</v>
-      </c>
-      <c r="AA150" s="219">
-        <v>0.375</v>
+      <c r="T150" s="173" t="str">
+        <f t="shared" ref="T150:AA150" si="81">IF(U5&gt;T148, "BEAT", IF(U5&lt;T147, "MISSED", "MET"))</f>
+        <v>MET</v>
+      </c>
+      <c r="U150" s="173" t="str">
+        <f t="shared" si="81"/>
+        <v>MET</v>
+      </c>
+      <c r="V150" s="173" t="str">
+        <f t="shared" si="81"/>
+        <v>MET</v>
+      </c>
+      <c r="W150" s="173" t="str">
+        <f t="shared" si="81"/>
+        <v>BEAT</v>
+      </c>
+      <c r="X150" s="173" t="str">
+        <f t="shared" si="81"/>
+        <v>BEAT</v>
+      </c>
+      <c r="Y150" s="173" t="str">
+        <f t="shared" si="81"/>
+        <v>MET</v>
+      </c>
+      <c r="Z150" s="173" t="str">
+        <f t="shared" si="81"/>
+        <v>BEAT</v>
+      </c>
+      <c r="AA150" s="173" t="str">
+        <f t="shared" si="81"/>
+        <v>MISSED</v>
       </c>
       <c r="AC150" s="49"/>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B151" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C151" s="49"/>
       <c r="D151" s="49"/>
@@ -29206,7 +29211,7 @@
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B152" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C152" s="49"/>
       <c r="D152" s="49"/>
@@ -29223,43 +29228,35 @@
       <c r="O152" s="49"/>
       <c r="P152" s="49"/>
       <c r="Q152" s="49"/>
-      <c r="T152" s="73">
-        <f t="shared" ref="T152:AA152" si="80">U100</f>
-        <v>0.15033122553447756</v>
-      </c>
-      <c r="U152" s="73">
-        <f t="shared" si="80"/>
-        <v>0.39158485273492288</v>
-      </c>
-      <c r="V152" s="73">
-        <f t="shared" si="80"/>
-        <v>0.36883239914739085</v>
-      </c>
-      <c r="W152" s="73">
-        <f t="shared" si="80"/>
-        <v>0.27544910179640719</v>
-      </c>
-      <c r="X152" s="73">
-        <f t="shared" si="80"/>
-        <v>0.38218706511389439</v>
-      </c>
-      <c r="Y152" s="73">
-        <f t="shared" si="80"/>
-        <v>0.36148895714494661</v>
-      </c>
-      <c r="Z152" s="73">
-        <f t="shared" si="80"/>
-        <v>0.39382779700964865</v>
-      </c>
-      <c r="AA152" s="73">
-        <f t="shared" si="80"/>
-        <v>0</v>
+      <c r="T152" s="219">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="U152" s="219">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="V152" s="219">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="W152" s="219">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="X152" s="219">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="Y152" s="219">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="Z152" s="219">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="AA152" s="219">
+        <v>0.375</v>
       </c>
       <c r="AC152" s="49"/>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B153" s="20" t="s">
-        <v>182</v>
+        <v>369</v>
       </c>
       <c r="C153" s="49"/>
       <c r="D153" s="49"/>
@@ -29276,728 +29273,744 @@
       <c r="O153" s="49"/>
       <c r="P153" s="49"/>
       <c r="Q153" s="49"/>
-      <c r="T153" s="173" t="str">
-        <f t="shared" ref="T153:AA153" si="81">IF(U100&gt;T151, "BEAT", IF(U100&lt;T150, "MISSED", "MET"))</f>
+      <c r="T153" s="73">
+        <f t="shared" ref="T153:AA153" si="82">U100</f>
+        <v>0.15033122553447756</v>
+      </c>
+      <c r="U153" s="73">
+        <f t="shared" si="82"/>
+        <v>0.39158485273492288</v>
+      </c>
+      <c r="V153" s="73">
+        <f t="shared" si="82"/>
+        <v>0.36883239914739085</v>
+      </c>
+      <c r="W153" s="73">
+        <f t="shared" si="82"/>
+        <v>0.27544910179640719</v>
+      </c>
+      <c r="X153" s="73">
+        <f t="shared" si="82"/>
+        <v>0.38218706511389439</v>
+      </c>
+      <c r="Y153" s="73">
+        <f t="shared" si="82"/>
+        <v>0.36148895714494661</v>
+      </c>
+      <c r="Z153" s="73">
+        <f t="shared" si="82"/>
+        <v>0.39382779700964865</v>
+      </c>
+      <c r="AA153" s="73">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="AC153" s="49"/>
+    </row>
+    <row r="154" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B154" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C154" s="49"/>
+      <c r="D154" s="49"/>
+      <c r="E154" s="49"/>
+      <c r="F154" s="49"/>
+      <c r="G154" s="49"/>
+      <c r="H154" s="49"/>
+      <c r="I154" s="49"/>
+      <c r="J154" s="49"/>
+      <c r="K154" s="49"/>
+      <c r="L154" s="49"/>
+      <c r="M154" s="49"/>
+      <c r="N154" s="49"/>
+      <c r="O154" s="49"/>
+      <c r="P154" s="49"/>
+      <c r="Q154" s="49"/>
+      <c r="T154" s="173" t="str">
+        <f t="shared" ref="T154:AA154" si="83">IF(U100&gt;T152, "BEAT", IF(U100&lt;T151, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
-      <c r="U153" s="173" t="str">
-        <f t="shared" si="81"/>
+      <c r="U154" s="173" t="str">
+        <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="V153" s="173" t="str">
-        <f t="shared" si="81"/>
+      <c r="V154" s="173" t="str">
+        <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="W153" s="173" t="str">
-        <f t="shared" si="81"/>
+      <c r="W154" s="173" t="str">
+        <f t="shared" si="83"/>
         <v>MISSED</v>
       </c>
-      <c r="X153" s="173" t="str">
-        <f t="shared" si="81"/>
+      <c r="X154" s="173" t="str">
+        <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="Y153" s="173" t="str">
-        <f t="shared" si="81"/>
+      <c r="Y154" s="173" t="str">
+        <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="Z153" s="173" t="str">
-        <f t="shared" si="81"/>
+      <c r="Z154" s="173" t="str">
+        <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="AA153" s="173" t="str">
-        <f t="shared" si="81"/>
+      <c r="AA154" s="173" t="str">
+        <f t="shared" si="83"/>
         <v>MISSED</v>
       </c>
-      <c r="AC153" s="49"/>
-    </row>
-    <row r="155" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B155" s="1"/>
-    </row>
-    <row r="156" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="14" t="s">
+      <c r="AC154" s="49"/>
+    </row>
+    <row r="156" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B156" s="1"/>
+    </row>
+    <row r="157" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="C156" s="172"/>
-      <c r="D156" s="172"/>
-      <c r="E156" s="172"/>
-      <c r="F156" s="172"/>
-      <c r="G156" s="172"/>
-      <c r="H156" s="172"/>
-      <c r="I156" s="172"/>
-      <c r="J156" s="172"/>
-      <c r="K156" s="172"/>
-      <c r="L156" s="172"/>
-      <c r="M156" s="172"/>
-      <c r="N156" s="172"/>
-      <c r="O156" s="172"/>
-      <c r="P156" s="172"/>
-      <c r="Q156" s="172"/>
-      <c r="T156" s="172"/>
-      <c r="U156" s="172"/>
-      <c r="V156" s="172"/>
-      <c r="W156" s="172"/>
-      <c r="X156" s="172"/>
-      <c r="Y156" s="172"/>
-      <c r="Z156" s="172"/>
-      <c r="AA156" s="172"/>
-      <c r="AC156" s="172"/>
-    </row>
-    <row r="157" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B157" s="20" t="s">
+      <c r="C157" s="172"/>
+      <c r="D157" s="172"/>
+      <c r="E157" s="172"/>
+      <c r="F157" s="172"/>
+      <c r="G157" s="172"/>
+      <c r="H157" s="172"/>
+      <c r="I157" s="172"/>
+      <c r="J157" s="172"/>
+      <c r="K157" s="172"/>
+      <c r="L157" s="172"/>
+      <c r="M157" s="172"/>
+      <c r="N157" s="172"/>
+      <c r="O157" s="172"/>
+      <c r="P157" s="172"/>
+      <c r="Q157" s="172"/>
+      <c r="T157" s="172"/>
+      <c r="U157" s="172"/>
+      <c r="V157" s="172"/>
+      <c r="W157" s="172"/>
+      <c r="X157" s="172"/>
+      <c r="Y157" s="172"/>
+      <c r="Z157" s="172"/>
+      <c r="AA157" s="172"/>
+      <c r="AC157" s="172"/>
+    </row>
+    <row r="158" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B158" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C157" s="80"/>
-      <c r="D157" s="80"/>
-      <c r="E157" s="80"/>
-      <c r="F157" s="80"/>
-      <c r="G157" s="80"/>
-      <c r="H157" s="80"/>
-      <c r="I157" s="80"/>
-      <c r="J157" s="80"/>
-      <c r="K157" s="80"/>
-      <c r="L157" s="80"/>
-      <c r="M157" s="80">
+      <c r="C158" s="80"/>
+      <c r="D158" s="80"/>
+      <c r="E158" s="80"/>
+      <c r="F158" s="80"/>
+      <c r="G158" s="80"/>
+      <c r="H158" s="80"/>
+      <c r="I158" s="80"/>
+      <c r="J158" s="80"/>
+      <c r="K158" s="80"/>
+      <c r="L158" s="80"/>
+      <c r="M158" s="80">
         <f>M122/(M121+M125-M120)</f>
         <v>0.16950089956234582</v>
       </c>
-      <c r="N157" s="80">
+      <c r="N158" s="80">
         <f>N122/(N121+N125-N120)</f>
         <v>1.9948888452038051E-2</v>
       </c>
-      <c r="O157" s="80">
+      <c r="O158" s="80">
         <f>O122/(O121+O125-O120)</f>
         <v>6.9301102111075507E-4</v>
       </c>
-      <c r="P157" s="80">
+      <c r="P158" s="80">
         <f>P122/(P121+P125-P120)</f>
         <v>-8.7817056571991486E-2</v>
       </c>
-      <c r="Q157" s="80">
+      <c r="Q158" s="80">
         <f>Q122/(Q121+Q125-Q120)</f>
         <v>-1.6335987131905347E-2</v>
       </c>
-      <c r="T157" s="49"/>
-      <c r="U157" s="49"/>
-      <c r="V157" s="49"/>
-      <c r="W157" s="49"/>
-      <c r="X157" s="49"/>
-      <c r="Y157" s="49"/>
-      <c r="Z157" s="49"/>
-      <c r="AA157" s="49"/>
-      <c r="AC157" s="80">
+      <c r="T158" s="49"/>
+      <c r="U158" s="49"/>
+      <c r="V158" s="49"/>
+      <c r="W158" s="49"/>
+      <c r="X158" s="49"/>
+      <c r="Y158" s="49"/>
+      <c r="Z158" s="49"/>
+      <c r="AA158" s="49"/>
+      <c r="AC158" s="80">
         <f>AC122/(AC121+AC125-AC120)</f>
         <v>-3.6791978488825414E-2</v>
       </c>
     </row>
-    <row r="158" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B158" s="20" t="s">
+    <row r="159" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B159" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="M158" s="117">
-        <f t="shared" ref="M158:Q159" si="82">M30/M5*365</f>
+      <c r="M159" s="117">
+        <f>M30/M5*365</f>
         <v>43.680464162785988</v>
       </c>
-      <c r="N158" s="117">
-        <f t="shared" si="82"/>
+      <c r="N159" s="117">
+        <f>N30/N5*365</f>
         <v>23.924651885685286</v>
       </c>
-      <c r="O158" s="117">
-        <f t="shared" si="82"/>
+      <c r="O159" s="117">
+        <f>O30/O5*365</f>
         <v>22.898318211993807</v>
       </c>
-      <c r="P158" s="117">
-        <f t="shared" si="82"/>
+      <c r="P159" s="117">
+        <f>P30/P5*365</f>
         <v>23.906706088397584</v>
       </c>
-      <c r="Q158" s="117">
-        <f t="shared" si="82"/>
+      <c r="Q159" s="117">
+        <f>Q30/Q5*365</f>
         <v>26.511929313378616</v>
       </c>
-      <c r="T158" s="117">
-        <f t="shared" ref="T158:AA158" si="83">T30/T5*90</f>
+      <c r="T159" s="117">
+        <f t="shared" ref="T159:AA159" si="84">T30/T5*90</f>
         <v>21.958232681368347</v>
       </c>
-      <c r="U158" s="117">
-        <f t="shared" si="83"/>
+      <c r="U159" s="117">
+        <f t="shared" si="84"/>
         <v>21.144986449864501</v>
       </c>
-      <c r="V158" s="117">
-        <f t="shared" si="83"/>
+      <c r="V159" s="117">
+        <f t="shared" si="84"/>
         <v>21.950911640953716</v>
       </c>
-      <c r="W158" s="117">
-        <f t="shared" si="83"/>
+      <c r="W159" s="117">
+        <f t="shared" si="84"/>
         <v>21.769953422278363</v>
       </c>
-      <c r="X158" s="117">
-        <f t="shared" si="83"/>
+      <c r="X159" s="117">
+        <f t="shared" si="84"/>
         <v>16.517614122404542</v>
       </c>
-      <c r="Y158" s="117">
-        <f t="shared" si="83"/>
+      <c r="Y159" s="117">
+        <f t="shared" si="84"/>
         <v>21.107448912326962</v>
       </c>
-      <c r="Z158" s="117">
-        <f t="shared" si="83"/>
+      <c r="Z159" s="117">
+        <f t="shared" si="84"/>
         <v>25.267661254936375</v>
       </c>
-      <c r="AA158" s="117">
-        <f t="shared" si="83"/>
+      <c r="AA159" s="117">
+        <f t="shared" si="84"/>
         <v>26.952935110849229</v>
       </c>
-      <c r="AC158" s="117">
+      <c r="AC159" s="117">
         <f>AC30/AC5*365</f>
         <v>27.604300355262914</v>
       </c>
     </row>
-    <row r="159" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B159" s="20" t="s">
+    <row r="160" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B160" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="M159" s="117">
-        <f t="shared" si="82"/>
+      <c r="M160" s="117">
+        <f>M31/M6*365</f>
         <v>111.71121020193701</v>
       </c>
-      <c r="N159" s="117">
-        <f t="shared" si="82"/>
+      <c r="N160" s="117">
+        <f>N31/N6*365</f>
         <v>133.38012600862163</v>
       </c>
-      <c r="O159" s="117">
-        <f t="shared" si="82"/>
+      <c r="O160" s="117">
+        <f>O31/O6*365</f>
         <v>124.89943721745549</v>
       </c>
-      <c r="P159" s="117">
-        <f t="shared" si="82"/>
+      <c r="P160" s="117">
+        <f>P31/P6*365</f>
         <v>124.51812283253162</v>
       </c>
-      <c r="Q159" s="117">
-        <f t="shared" si="82"/>
+      <c r="Q160" s="117">
+        <f>Q31/Q6*365</f>
         <v>122.99350310342828</v>
       </c>
-      <c r="T159" s="117">
-        <f t="shared" ref="T159:AA159" si="84">T31/T6*365</f>
+      <c r="T160" s="117">
+        <f t="shared" ref="T160:AA160" si="85">T31/T6*365</f>
         <v>495.30050687907317</v>
       </c>
-      <c r="U159" s="117">
-        <f t="shared" si="84"/>
+      <c r="U160" s="117">
+        <f t="shared" si="85"/>
         <v>390.06201825108536</v>
       </c>
-      <c r="V159" s="117">
-        <f t="shared" si="84"/>
+      <c r="V160" s="117">
+        <f t="shared" si="85"/>
         <v>513.17081604425994</v>
       </c>
-      <c r="W159" s="117">
-        <f t="shared" si="84"/>
+      <c r="W160" s="117">
+        <f t="shared" si="85"/>
         <v>560.6710444027517</v>
       </c>
-      <c r="X159" s="117">
-        <f t="shared" si="84"/>
+      <c r="X160" s="117">
+        <f t="shared" si="85"/>
         <v>445.70194268541377</v>
       </c>
-      <c r="Y159" s="117">
-        <f t="shared" si="84"/>
+      <c r="Y160" s="117">
+        <f t="shared" si="85"/>
         <v>497.15293420272673</v>
       </c>
-      <c r="Z159" s="117">
-        <f t="shared" si="84"/>
+      <c r="Z160" s="117">
+        <f t="shared" si="85"/>
         <v>485.6912152101707</v>
       </c>
-      <c r="AA159" s="117">
-        <f t="shared" si="84"/>
+      <c r="AA160" s="117">
+        <f t="shared" si="85"/>
         <v>551.09234507897929</v>
       </c>
-      <c r="AC159" s="117">
+      <c r="AC160" s="117">
         <f>AC31/AC6*365</f>
         <v>130.6568144499179</v>
       </c>
     </row>
-    <row r="160" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B160" s="20" t="s">
+    <row r="161" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B161" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="M160" s="117">
+      <c r="M161" s="117">
         <f>M37/M6*365</f>
         <v>59.577238774177054</v>
       </c>
-      <c r="N160" s="117">
+      <c r="N161" s="117">
         <f>N37/N6*365</f>
         <v>96.777246601083235</v>
       </c>
-      <c r="O160" s="117">
+      <c r="O161" s="117">
         <f>O37/O6*365</f>
         <v>96.219823476950523</v>
       </c>
-      <c r="P160" s="117">
+      <c r="P161" s="117">
         <f>P37/P6*365</f>
         <v>128.17261438639667</v>
       </c>
-      <c r="Q160" s="117">
+      <c r="Q161" s="117">
         <f>Q37/Q6*365</f>
         <v>104.6154069261558</v>
       </c>
-      <c r="T160" s="117">
-        <f t="shared" ref="T160:AA160" si="85">T37/T6*90</f>
+      <c r="T161" s="117">
+        <f t="shared" ref="T161:AA161" si="86">T37/T6*90</f>
         <v>104.46777697320782</v>
       </c>
-      <c r="U160" s="117">
-        <f t="shared" si="85"/>
+      <c r="U161" s="117">
+        <f t="shared" si="86"/>
         <v>88.301585895277753</v>
       </c>
-      <c r="V160" s="117">
-        <f t="shared" si="85"/>
+      <c r="V161" s="117">
+        <f t="shared" si="86"/>
         <v>130.24896265560164</v>
       </c>
-      <c r="W160" s="117">
-        <f t="shared" si="85"/>
+      <c r="W161" s="117">
+        <f t="shared" si="86"/>
         <v>122.65666041275797</v>
       </c>
-      <c r="X160" s="117">
-        <f t="shared" si="85"/>
+      <c r="X161" s="117">
+        <f t="shared" si="86"/>
         <v>103.03101856820865</v>
       </c>
-      <c r="Y160" s="117">
-        <f t="shared" si="85"/>
+      <c r="Y161" s="117">
+        <f t="shared" si="86"/>
         <v>109.55779490219324</v>
       </c>
-      <c r="Z160" s="117">
-        <f t="shared" si="85"/>
+      <c r="Z161" s="117">
+        <f t="shared" si="86"/>
         <v>101.86462031840568</v>
       </c>
-      <c r="AA160" s="117">
-        <f t="shared" si="85"/>
+      <c r="AA161" s="117">
+        <f t="shared" si="86"/>
         <v>78.287970838396106</v>
       </c>
-      <c r="AC160" s="117">
+      <c r="AC161" s="117">
         <f>AC37/AC6*365</f>
         <v>75.275401146544525</v>
       </c>
     </row>
-    <row r="161" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B161" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="M161" s="117">
-        <f>M158+M159-M160</f>
-        <v>95.814435590545941</v>
-      </c>
-      <c r="N161" s="117">
-        <f t="shared" ref="N161:Q161" si="86">N158+N159-N160</f>
-        <v>60.527531293223674</v>
-      </c>
-      <c r="O161" s="117">
-        <f t="shared" si="86"/>
-        <v>51.577931952498773</v>
-      </c>
-      <c r="P161" s="117">
-        <f t="shared" si="86"/>
-        <v>20.252214534532527</v>
-      </c>
-      <c r="Q161" s="117">
-        <f t="shared" si="86"/>
-        <v>44.890025490651112</v>
-      </c>
-      <c r="T161" s="117">
-        <f t="shared" ref="T161" si="87">T158+T159-T160</f>
-        <v>412.79096258723371</v>
-      </c>
-      <c r="U161" s="117">
-        <f t="shared" ref="U161" si="88">U158+U159-U160</f>
-        <v>322.90541880567213</v>
-      </c>
-      <c r="V161" s="117">
-        <f t="shared" ref="V161" si="89">V158+V159-V160</f>
-        <v>404.87276502961197</v>
-      </c>
-      <c r="W161" s="117">
-        <f t="shared" ref="W161" si="90">W158+W159-W160</f>
-        <v>459.78433741227212</v>
-      </c>
-      <c r="X161" s="117">
-        <f t="shared" ref="X161" si="91">X158+X159-X160</f>
-        <v>359.18853823960967</v>
-      </c>
-      <c r="Y161" s="117">
-        <f t="shared" ref="Y161" si="92">Y158+Y159-Y160</f>
-        <v>408.70258821286052</v>
-      </c>
-      <c r="Z161" s="117">
-        <f t="shared" ref="Z161:AA161" si="93">Z158+Z159-Z160</f>
-        <v>409.09425614670141</v>
-      </c>
-      <c r="AA161" s="117">
-        <f t="shared" si="93"/>
-        <v>499.75730935143241</v>
-      </c>
-      <c r="AC161" s="117">
-        <f t="shared" ref="AC161" si="94">AC158+AC159-AC160</f>
-        <v>82.9857136586363</v>
-      </c>
-    </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B162" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="M162" s="117">
+        <f>M159+M160-M161</f>
+        <v>95.814435590545941</v>
+      </c>
+      <c r="N162" s="117">
+        <f t="shared" ref="N162:Q162" si="87">N159+N160-N161</f>
+        <v>60.527531293223674</v>
+      </c>
+      <c r="O162" s="117">
+        <f t="shared" si="87"/>
+        <v>51.577931952498773</v>
+      </c>
+      <c r="P162" s="117">
+        <f t="shared" si="87"/>
+        <v>20.252214534532527</v>
+      </c>
+      <c r="Q162" s="117">
+        <f t="shared" si="87"/>
+        <v>44.890025490651112</v>
+      </c>
+      <c r="T162" s="117">
+        <f t="shared" ref="T162" si="88">T159+T160-T161</f>
+        <v>412.79096258723371</v>
+      </c>
+      <c r="U162" s="117">
+        <f t="shared" ref="U162" si="89">U159+U160-U161</f>
+        <v>322.90541880567213</v>
+      </c>
+      <c r="V162" s="117">
+        <f t="shared" ref="V162" si="90">V159+V160-V161</f>
+        <v>404.87276502961197</v>
+      </c>
+      <c r="W162" s="117">
+        <f t="shared" ref="W162" si="91">W159+W160-W161</f>
+        <v>459.78433741227212</v>
+      </c>
+      <c r="X162" s="117">
+        <f t="shared" ref="X162" si="92">X159+X160-X161</f>
+        <v>359.18853823960967</v>
+      </c>
+      <c r="Y162" s="117">
+        <f t="shared" ref="Y162" si="93">Y159+Y160-Y161</f>
+        <v>408.70258821286052</v>
+      </c>
+      <c r="Z162" s="117">
+        <f t="shared" ref="Z162:AA162" si="94">Z159+Z160-Z161</f>
+        <v>409.09425614670141</v>
+      </c>
+      <c r="AA162" s="117">
+        <f t="shared" si="94"/>
+        <v>499.75730935143241</v>
+      </c>
+      <c r="AC162" s="117">
+        <f t="shared" ref="AC162" si="95">AC159+AC160-AC161</f>
+        <v>82.9857136586363</v>
+      </c>
+    </row>
+    <row r="163" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B163" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="M162" s="117">
+      <c r="M163" s="117">
         <f>M121/M48</f>
         <v>0.39941923242234595</v>
       </c>
-      <c r="N162" s="117">
+      <c r="N163" s="117">
         <f>N121/N48</f>
         <v>0.41461009830117429</v>
       </c>
-      <c r="O162" s="117">
+      <c r="O163" s="117">
         <f>O121/O48</f>
         <v>0.46657827445780853</v>
       </c>
-      <c r="P162" s="117">
+      <c r="P163" s="117">
         <f>P121/P48</f>
         <v>0.50378764984386015</v>
       </c>
-      <c r="Q162" s="117">
+      <c r="Q163" s="117">
         <f>Q121/Q48</f>
         <v>0.40763556496705489</v>
       </c>
-      <c r="T162" s="117">
-        <f t="shared" ref="T162:AA162" si="95">T121/T48</f>
+      <c r="T163" s="117">
+        <f t="shared" ref="T163:AA163" si="96">T121/T48</f>
         <v>0.46020533025540444</v>
       </c>
-      <c r="U162" s="117">
-        <f t="shared" si="95"/>
+      <c r="U163" s="117">
+        <f t="shared" si="96"/>
         <v>0.50472209942531043</v>
       </c>
-      <c r="V162" s="117">
-        <f t="shared" si="95"/>
+      <c r="V163" s="117">
+        <f t="shared" si="96"/>
         <v>0.50378764984386015</v>
       </c>
-      <c r="W162" s="117">
-        <f t="shared" si="95"/>
+      <c r="W163" s="117">
+        <f t="shared" si="96"/>
         <v>0.50273667749308315</v>
       </c>
-      <c r="X162" s="117">
-        <f t="shared" si="95"/>
+      <c r="X163" s="117">
+        <f t="shared" si="96"/>
         <v>0.51854765383161527</v>
       </c>
-      <c r="Y162" s="117">
-        <f t="shared" si="95"/>
+      <c r="Y163" s="117">
+        <f t="shared" si="96"/>
         <v>0.43762690832518614</v>
       </c>
-      <c r="Z162" s="117">
-        <f t="shared" si="95"/>
+      <c r="Z163" s="117">
+        <f t="shared" si="96"/>
         <v>0.40763556496705489</v>
       </c>
-      <c r="AA162" s="117">
-        <f t="shared" si="95"/>
+      <c r="AA163" s="117">
+        <f t="shared" si="96"/>
         <v>0.40424978005996731</v>
       </c>
-      <c r="AC162" s="117">
+      <c r="AC163" s="117">
         <f>AC121/AC48</f>
         <v>0.40424978005996731</v>
       </c>
     </row>
-    <row r="163" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B163" s="20" t="s">
+    <row r="164" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B164" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="M163" s="181">
+      <c r="M164" s="181">
         <f>(M121-M120)/M48</f>
         <v>0.10156094390456123</v>
       </c>
-      <c r="N163" s="181">
+      <c r="N164" s="181">
         <f>(N121-N120)/N48</f>
         <v>0.13520601835875493</v>
       </c>
-      <c r="O163" s="181">
+      <c r="O164" s="181">
         <f>(O121-O120)/O48</f>
         <v>0.22949142911260537</v>
       </c>
-      <c r="P163" s="181">
+      <c r="P164" s="181">
         <f>(P121-P120)/P48</f>
         <v>0.28154528054800038</v>
       </c>
-      <c r="Q163" s="181">
+      <c r="Q164" s="181">
         <f>(Q121-Q120)/Q48</f>
         <v>8.0232059572457368E-2</v>
       </c>
-      <c r="T163" s="181">
-        <f t="shared" ref="T163:AA163" si="96">(T121-T120)/T48</f>
+      <c r="T164" s="181">
+        <f t="shared" ref="T164:AA164" si="97">(T121-T120)/T48</f>
         <v>0.20616337901049214</v>
       </c>
-      <c r="U163" s="181">
-        <f t="shared" si="96"/>
+      <c r="U164" s="181">
+        <f t="shared" si="97"/>
         <v>0.26272957440823053</v>
       </c>
-      <c r="V163" s="181">
-        <f t="shared" si="96"/>
+      <c r="V164" s="181">
+        <f t="shared" si="97"/>
         <v>0.28154528054800038</v>
       </c>
-      <c r="W163" s="181">
-        <f t="shared" si="96"/>
+      <c r="W164" s="181">
+        <f t="shared" si="97"/>
         <v>0.29174185011427883</v>
       </c>
-      <c r="X163" s="181">
-        <f t="shared" si="96"/>
+      <c r="X164" s="181">
+        <f t="shared" si="97"/>
         <v>0.30190124945087504</v>
       </c>
-      <c r="Y163" s="181">
-        <f t="shared" si="96"/>
+      <c r="Y164" s="181">
+        <f t="shared" si="97"/>
         <v>0.1468188313153343</v>
       </c>
-      <c r="Z163" s="181">
-        <f t="shared" si="96"/>
+      <c r="Z164" s="181">
+        <f t="shared" si="97"/>
         <v>8.0232059572457368E-2</v>
       </c>
-      <c r="AA163" s="181">
-        <f t="shared" si="96"/>
+      <c r="AA164" s="181">
+        <f t="shared" si="97"/>
         <v>0.10989819918487531</v>
       </c>
-      <c r="AC163" s="181">
+      <c r="AC164" s="181">
         <f>(AC121-AC120)/AC48</f>
         <v>0.10989819918487531</v>
       </c>
     </row>
-    <row r="164" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B164" s="20" t="s">
+    <row r="165" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B165" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="M164" s="117">
+      <c r="M165" s="117">
         <f>(M120+M30)/M39</f>
         <v>1.3789964314325249</v>
       </c>
-      <c r="N164" s="117">
+      <c r="N165" s="117">
         <f>(N120+N30)/N39</f>
         <v>1.0098273985383299</v>
       </c>
-      <c r="O164" s="117">
+      <c r="O165" s="117">
         <f>(O120+O30)/O39</f>
         <v>1.0136527287634121</v>
       </c>
-      <c r="P164" s="117">
+      <c r="P165" s="117">
         <f>(P120+P30)/P39</f>
         <v>0.71608815118039593</v>
       </c>
-      <c r="Q164" s="117">
+      <c r="Q165" s="117">
         <f>(Q120+Q30)/Q39</f>
         <v>1.306571654790182</v>
       </c>
-      <c r="T164" s="117">
-        <f t="shared" ref="T164:AA164" si="97">(T120+T30)/T39</f>
+      <c r="T165" s="117">
+        <f t="shared" ref="T165:AA165" si="98">(T120+T30)/T39</f>
         <v>1.0117713179504793</v>
       </c>
-      <c r="U164" s="117">
-        <f t="shared" si="97"/>
+      <c r="U165" s="117">
+        <f t="shared" si="98"/>
         <v>0.77382746949571946</v>
       </c>
-      <c r="V164" s="117">
-        <f t="shared" si="97"/>
+      <c r="V165" s="117">
+        <f t="shared" si="98"/>
         <v>0.71608815118039593</v>
       </c>
-      <c r="W164" s="117">
-        <f t="shared" si="97"/>
+      <c r="W165" s="117">
+        <f t="shared" si="98"/>
         <v>0.7494250015540499</v>
       </c>
-      <c r="X164" s="117">
-        <f t="shared" si="97"/>
+      <c r="X165" s="117">
+        <f t="shared" si="98"/>
         <v>0.67396899845564262</v>
       </c>
-      <c r="Y164" s="117">
-        <f t="shared" si="97"/>
+      <c r="Y165" s="117">
+        <f t="shared" si="98"/>
         <v>1.0569712357184877</v>
       </c>
-      <c r="Z164" s="117">
-        <f t="shared" si="97"/>
+      <c r="Z165" s="117">
+        <f t="shared" si="98"/>
         <v>1.306571654790182</v>
       </c>
-      <c r="AA164" s="117">
-        <f t="shared" si="97"/>
+      <c r="AA165" s="117">
+        <f t="shared" si="98"/>
         <v>1.3708387576715642</v>
       </c>
-      <c r="AC164" s="117">
+      <c r="AC165" s="117">
         <f>(AC120+AC30)/AC39</f>
         <v>1.3708387576715642</v>
       </c>
     </row>
-    <row r="165" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B165" s="20" t="s">
+    <row r="166" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B166" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="M165" s="117">
+      <c r="M166" s="117">
         <f>M32/M39</f>
         <v>2.1017405869929355</v>
       </c>
-      <c r="N165" s="117">
+      <c r="N166" s="117">
         <f>N32/N39</f>
         <v>1.5676255636759446</v>
       </c>
-      <c r="O165" s="117">
+      <c r="O166" s="117">
         <f>O32/O39</f>
         <v>1.5424018821516416</v>
       </c>
-      <c r="P165" s="117">
+      <c r="P166" s="117">
         <f>P32/P39</f>
         <v>1.3268659227275277</v>
       </c>
-      <c r="Q165" s="117">
+      <c r="Q166" s="117">
         <f>Q32/Q39</f>
         <v>2.0170387965162311</v>
       </c>
-      <c r="T165" s="117">
-        <f t="shared" ref="T165:AA165" si="98">T32/T39</f>
+      <c r="T166" s="117">
+        <f t="shared" ref="T166:AA166" si="99">T32/T39</f>
         <v>1.5870671620819934</v>
       </c>
-      <c r="U165" s="117">
-        <f t="shared" si="98"/>
+      <c r="U166" s="117">
+        <f t="shared" si="99"/>
         <v>1.3122386871071419</v>
       </c>
-      <c r="V165" s="117">
-        <f t="shared" si="98"/>
+      <c r="V166" s="117">
+        <f t="shared" si="99"/>
         <v>1.3268659227275277</v>
       </c>
-      <c r="W165" s="117">
-        <f t="shared" si="98"/>
+      <c r="W166" s="117">
+        <f t="shared" si="99"/>
         <v>1.3095667309007273</v>
       </c>
-      <c r="X165" s="117">
-        <f t="shared" si="98"/>
+      <c r="X166" s="117">
+        <f t="shared" si="99"/>
         <v>1.2404907624549562</v>
       </c>
-      <c r="Y165" s="117">
-        <f t="shared" si="98"/>
+      <c r="Y166" s="117">
+        <f t="shared" si="99"/>
         <v>1.6017277146484195</v>
       </c>
-      <c r="Z165" s="117">
-        <f t="shared" si="98"/>
+      <c r="Z166" s="117">
+        <f t="shared" si="99"/>
         <v>2.0170387965162311</v>
       </c>
-      <c r="AA165" s="117">
-        <f t="shared" si="98"/>
+      <c r="AA166" s="117">
+        <f t="shared" si="99"/>
         <v>2.3119583410823878</v>
       </c>
-      <c r="AC165" s="117">
+      <c r="AC166" s="117">
         <f>AC32/AC39</f>
         <v>2.3119583410823878</v>
       </c>
     </row>
-    <row r="166" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B166" s="20" t="s">
+    <row r="167" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B167" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="M166" s="183" t="str">
+      <c r="M167" s="183" t="str">
         <f>IF(M13&gt;=0,"N/A",IF(M12&lt;=0,"N/A",M12/-M13))</f>
         <v>N/A</v>
       </c>
-      <c r="N166" s="183" t="str">
+      <c r="N167" s="183" t="str">
         <f>IF(N13&gt;=0,"N/A",IF(N12&lt;=0,"N/A",N12/-N13))</f>
         <v>N/A</v>
       </c>
-      <c r="O166" s="183" t="str">
+      <c r="O167" s="183" t="str">
         <f>IF(O13&gt;=0,"N/A",IF(O12&lt;=0,"N/A",O12/-O13))</f>
         <v>N/A</v>
       </c>
-      <c r="P166" s="183" t="str">
+      <c r="P167" s="183" t="str">
         <f>IF(P13&gt;=0,"N/A",IF(P12&lt;=0,"N/A",P12/-P13))</f>
         <v>N/A</v>
       </c>
-      <c r="Q166" s="183" t="str">
+      <c r="Q167" s="183" t="str">
         <f>IF(Q13&gt;=0,"N/A",IF(Q12&lt;=0,"N/A",Q12/-Q13))</f>
         <v>N/A</v>
       </c>
-      <c r="T166" s="183" t="str">
-        <f t="shared" ref="T166:AA166" si="99">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+      <c r="T167" s="183" t="str">
+        <f t="shared" ref="T167:AA167" si="100">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
-      <c r="U166" s="183" t="str">
-        <f t="shared" si="99"/>
+      <c r="U167" s="183" t="str">
+        <f t="shared" si="100"/>
         <v>N/A</v>
       </c>
-      <c r="V166" s="183" t="str">
-        <f t="shared" si="99"/>
+      <c r="V167" s="183" t="str">
+        <f t="shared" si="100"/>
         <v>N/A</v>
       </c>
-      <c r="W166" s="183" t="str">
-        <f t="shared" si="99"/>
+      <c r="W167" s="183" t="str">
+        <f t="shared" si="100"/>
         <v>N/A</v>
       </c>
-      <c r="X166" s="183" t="str">
-        <f t="shared" si="99"/>
+      <c r="X167" s="183" t="str">
+        <f t="shared" si="100"/>
         <v>N/A</v>
       </c>
-      <c r="Y166" s="183" t="str">
-        <f t="shared" si="99"/>
+      <c r="Y167" s="183" t="str">
+        <f t="shared" si="100"/>
         <v>N/A</v>
       </c>
-      <c r="Z166" s="183">
-        <f t="shared" si="99"/>
+      <c r="Z167" s="183">
+        <f t="shared" si="100"/>
         <v>5.9793814432989691</v>
       </c>
-      <c r="AA166" s="183" t="str">
-        <f t="shared" si="99"/>
+      <c r="AA167" s="183" t="str">
+        <f t="shared" si="100"/>
         <v>N/A</v>
       </c>
-      <c r="AC166" s="183" t="str">
+      <c r="AC167" s="183" t="str">
         <f>IF(AC13&gt;=0,"N/A",IF(AC12&lt;=0,"N/A",AC12/-AC13))</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="167" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B167" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="M167" s="71">
-        <f>M129/Statement!M26</f>
-        <v>10.557613168724279</v>
-      </c>
-      <c r="N167" s="71">
-        <f>N129/Statement!N26</f>
-        <v>13.623711340206185</v>
-      </c>
-      <c r="O167" s="71">
-        <f>O129/Statement!O26</f>
-        <v>125.625</v>
-      </c>
-      <c r="P167" s="71">
-        <f>P129/Statement!P26</f>
-        <v>-4.634703196347032</v>
-      </c>
-      <c r="Q167" s="71">
-        <f>Q129/Statement!Q26</f>
-        <v>-603.33333333333337</v>
-      </c>
-      <c r="T167" s="49"/>
-      <c r="U167" s="49"/>
-      <c r="V167" s="49"/>
-      <c r="W167" s="49"/>
-      <c r="X167" s="49"/>
-      <c r="Y167" s="49"/>
-      <c r="Z167" s="49"/>
-      <c r="AA167" s="49"/>
-      <c r="AC167" s="71">
-        <f ca="1">AC129/AC26</f>
-        <v>-180.78225806451613</v>
-      </c>
-    </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B168" s="20" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="M168" s="71">
-        <f>M129/(Statement!M5/Statement!M22)</f>
-        <v>2.6556223425794698</v>
+        <f>M130/Statement!M26</f>
+        <v>10.557613168724279</v>
       </c>
       <c r="N168" s="71">
-        <f>N129/(Statement!N5/Statement!N22)</f>
-        <v>1.7282153392330384</v>
+        <f>N130/Statement!N26</f>
+        <v>13.623711340206185</v>
       </c>
       <c r="O168" s="71">
-        <f>O129/(Statement!O5/Statement!O22)</f>
-        <v>3.9030205797742865</v>
+        <f>O130/Statement!O26</f>
+        <v>125.625</v>
       </c>
       <c r="P168" s="71">
-        <f>P129/(Statement!P5/Statement!P22)</f>
-        <v>1.6362027080469295</v>
+        <f>P130/Statement!P26</f>
+        <v>-4.634703196347032</v>
       </c>
       <c r="Q168" s="71">
-        <f>Q129/(Statement!Q5/Statement!Q22)</f>
-        <v>3.102681020944885</v>
+        <f>Q130/Statement!Q26</f>
+        <v>-603.33333333333337</v>
       </c>
       <c r="T168" s="49"/>
       <c r="U168" s="49"/>
@@ -30008,33 +30021,33 @@
       <c r="Z168" s="49"/>
       <c r="AA168" s="49"/>
       <c r="AC168" s="71">
-        <f ca="1">AC129/(Statement!AC5/Statement!AC22)</f>
-        <v>9.8100174376429887</v>
+        <f ca="1">AC130/Statement!AC26</f>
+        <v>-179.49193548387098</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B169" s="20" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="M169" s="71">
-        <f>M129/(Statement!M48/Statement!M74)</f>
-        <v>2.190293843234687</v>
+        <f>M130/(Statement!M5/Statement!M22)</f>
+        <v>2.6556223425794698</v>
       </c>
       <c r="N169" s="71">
-        <f>N129/(Statement!N48/Statement!N74)</f>
-        <v>1.0780681896611222</v>
+        <f>N130/(Statement!N5/Statement!N22)</f>
+        <v>1.7282153392330384</v>
       </c>
       <c r="O169" s="71">
-        <f>O129/(Statement!O48/Statement!O74)</f>
-        <v>2.0120939482905578</v>
+        <f>O130/(Statement!O5/Statement!O22)</f>
+        <v>3.9030205797742865</v>
       </c>
       <c r="P169" s="71">
-        <f>P129/(Statement!P48/Statement!P74)</f>
-        <v>0.88545381283368585</v>
+        <f>P130/(Statement!P5/Statement!P22)</f>
+        <v>1.6362027080469295</v>
       </c>
       <c r="Q169" s="71">
-        <f>Q129/(Statement!Q48/Statement!Q74)</f>
-        <v>1.5822315170500785</v>
+        <f>Q130/(Statement!Q5/Statement!Q22)</f>
+        <v>3.102681020944885</v>
       </c>
       <c r="T169" s="49"/>
       <c r="U169" s="49"/>
@@ -30045,33 +30058,33 @@
       <c r="Z169" s="49"/>
       <c r="AA169" s="49"/>
       <c r="AC169" s="71">
-        <f ca="1">AC129/(Statement!AC48/Statement!AC74)</f>
-        <v>5.0571773165520577</v>
+        <f ca="1">AC130/(Statement!AC5/Statement!AC22)</f>
+        <v>9.7399990234919915</v>
       </c>
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B170" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="M170" s="143">
-        <f>Statement!M129*Statement!M77</f>
-        <v>210524.93000000002</v>
-      </c>
-      <c r="N170" s="143">
-        <f>Statement!N129*Statement!N77</f>
-        <v>109737.36</v>
-      </c>
-      <c r="O170" s="143">
-        <f>Statement!O129*Statement!O77</f>
-        <v>213562.5</v>
-      </c>
-      <c r="P170" s="143">
-        <f>Statement!P129*Statement!P77</f>
-        <v>87899</v>
-      </c>
-      <c r="Q170" s="143">
-        <f>Statement!Q129*Statement!Q77</f>
-        <v>180819</v>
+        <v>241</v>
+      </c>
+      <c r="M170" s="71">
+        <f>M130/(Statement!M48/Statement!M74)</f>
+        <v>2.190293843234687</v>
+      </c>
+      <c r="N170" s="71">
+        <f>N130/(Statement!N48/Statement!N74)</f>
+        <v>1.0780681896611222</v>
+      </c>
+      <c r="O170" s="71">
+        <f>O130/(Statement!O48/Statement!O74)</f>
+        <v>2.0120939482905578</v>
+      </c>
+      <c r="P170" s="71">
+        <f>P130/(Statement!P48/Statement!P74)</f>
+        <v>0.88545381283368585</v>
+      </c>
+      <c r="Q170" s="71">
+        <f>Q130/(Statement!Q48/Statement!Q74)</f>
+        <v>1.5822315170500785</v>
       </c>
       <c r="T170" s="49"/>
       <c r="U170" s="49"/>
@@ -30081,34 +30094,34 @@
       <c r="Y170" s="49"/>
       <c r="Z170" s="49"/>
       <c r="AA170" s="49"/>
-      <c r="AC170" s="143">
-        <f ca="1">Statement!AC129*Statement!AC77</f>
-        <v>563339.21</v>
+      <c r="AC170" s="71">
+        <f ca="1">AC130/(Statement!AC48/Statement!AC74)</f>
+        <v>5.0210820151893278</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B171" s="20" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="M171" s="143">
-        <f>M170+M121-M120+M47+M44</f>
-        <v>220212.93000000002</v>
+        <f>Statement!M130*Statement!M77</f>
+        <v>210524.93000000002</v>
       </c>
       <c r="N171" s="143">
-        <f>N170+N121-N120+N47+N44</f>
-        <v>125313.35999999999</v>
+        <f>Statement!N130*Statement!N77</f>
+        <v>109737.36</v>
       </c>
       <c r="O171" s="143">
-        <f>O170+O121-O120+O47+O44</f>
-        <v>242169.5</v>
+        <f>Statement!O130*Statement!O77</f>
+        <v>213562.5</v>
       </c>
       <c r="P171" s="143">
-        <f>P170+P121-P120+P47+P44</f>
-        <v>121610</v>
+        <f>Statement!P130*Statement!P77</f>
+        <v>87899</v>
       </c>
       <c r="Q171" s="143">
-        <f>Q170+Q121-Q120+Q47+Q44</f>
-        <v>202067</v>
+        <f>Statement!Q130*Statement!Q77</f>
+        <v>180819</v>
       </c>
       <c r="T171" s="49"/>
       <c r="U171" s="49"/>
@@ -30119,33 +30132,33 @@
       <c r="Z171" s="49"/>
       <c r="AA171" s="49"/>
       <c r="AC171" s="143">
-        <f ca="1">AC170+AC121-AC120+AC47+AC44</f>
-        <v>589176.21</v>
+        <f ca="1">Statement!AC130*Statement!AC77</f>
+        <v>559318.41</v>
       </c>
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B172" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="M172" s="185">
-        <f>M171/M5</f>
-        <v>2.7866588631301887</v>
-      </c>
-      <c r="N172" s="185">
-        <f>N171/N5</f>
-        <v>1.9873974688362355</v>
-      </c>
-      <c r="O172" s="185">
-        <f>O171/O5</f>
-        <v>4.4657649184922921</v>
-      </c>
-      <c r="P172" s="185">
-        <f>P171/P5</f>
-        <v>2.2901640270428052</v>
-      </c>
-      <c r="Q172" s="185">
-        <f>Q171/Q5</f>
-        <v>3.823188844531058</v>
+        <v>184</v>
+      </c>
+      <c r="M172" s="143">
+        <f>M171+M121-M120+M47+M44</f>
+        <v>220212.93000000002</v>
+      </c>
+      <c r="N172" s="143">
+        <f>N171+N121-N120+N47+N44</f>
+        <v>125313.35999999999</v>
+      </c>
+      <c r="O172" s="143">
+        <f>O171+O121-O120+O47+O44</f>
+        <v>242169.5</v>
+      </c>
+      <c r="P172" s="143">
+        <f>P171+P121-P120+P47+P44</f>
+        <v>121610</v>
+      </c>
+      <c r="Q172" s="143">
+        <f>Q171+Q121-Q120+Q47+Q44</f>
+        <v>202067</v>
       </c>
       <c r="T172" s="49"/>
       <c r="U172" s="49"/>
@@ -30155,34 +30168,34 @@
       <c r="Y172" s="49"/>
       <c r="Z172" s="49"/>
       <c r="AA172" s="49"/>
-      <c r="AC172" s="185">
-        <f ca="1">AC171/AC5</f>
-        <v>10.958767367892417</v>
+      <c r="AC172" s="143">
+        <f ca="1">AC171+AC121-AC120+AC47+AC44</f>
+        <v>585155.41</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B173" s="20" t="s">
-        <v>200</v>
+        <v>263</v>
       </c>
       <c r="M173" s="185">
-        <f>M171/M12</f>
-        <v>11.318509971217106</v>
+        <f>M172/M5</f>
+        <v>2.7866588631301887</v>
       </c>
       <c r="N173" s="185">
-        <f>N171/N12</f>
-        <v>53.690385604113104</v>
+        <f>N172/N5</f>
+        <v>1.9873974688362355</v>
       </c>
       <c r="O173" s="185">
-        <f>O171/O12</f>
-        <v>2603.9731182795699</v>
+        <f>O172/O5</f>
+        <v>4.4657649184922921</v>
       </c>
       <c r="P173" s="185">
-        <f>P171/P12</f>
-        <v>-10.413598218873094</v>
+        <f>P172/P5</f>
+        <v>2.2901640270428052</v>
       </c>
       <c r="Q173" s="185">
-        <f>Q171/Q12</f>
-        <v>-91.267841011743457</v>
+        <f>Q172/Q5</f>
+        <v>3.823188844531058</v>
       </c>
       <c r="T173" s="49"/>
       <c r="U173" s="49"/>
@@ -30193,131 +30206,131 @@
       <c r="Z173" s="49"/>
       <c r="AA173" s="49"/>
       <c r="AC173" s="185">
-        <f ca="1">AC171/AC12</f>
-        <v>-116.69166369578133</v>
+        <f ca="1">AC172/AC5</f>
+        <v>10.883979874634973</v>
       </c>
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B174" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="M174" s="185">
+        <f>M172/M12</f>
+        <v>11.318509971217106</v>
+      </c>
+      <c r="N174" s="185">
+        <f>N172/N12</f>
+        <v>53.690385604113104</v>
+      </c>
+      <c r="O174" s="185">
+        <f>O172/O12</f>
+        <v>2603.9731182795699</v>
+      </c>
+      <c r="P174" s="185">
+        <f>P172/P12</f>
+        <v>-10.413598218873094</v>
+      </c>
+      <c r="Q174" s="185">
+        <f>Q172/Q12</f>
+        <v>-91.267841011743457</v>
+      </c>
+      <c r="T174" s="49"/>
+      <c r="U174" s="49"/>
+      <c r="V174" s="49"/>
+      <c r="W174" s="49"/>
+      <c r="X174" s="49"/>
+      <c r="Y174" s="49"/>
+      <c r="Z174" s="49"/>
+      <c r="AA174" s="49"/>
+      <c r="AC174" s="185">
+        <f ca="1">AC172/AC12</f>
+        <v>-115.89530798177857</v>
+      </c>
+    </row>
+    <row r="175" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B175" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="M174" s="63">
+      <c r="M175" s="63">
         <f>M58-M53+M123+M64</f>
         <v>8687</v>
       </c>
-      <c r="N174" s="63">
+      <c r="N175" s="63">
         <f>N58-N53+N123+N64</f>
         <v>-12539</v>
       </c>
-      <c r="O174" s="63">
+      <c r="O175" s="63">
         <f>O58-O53+O123+O64</f>
         <v>-17508</v>
       </c>
-      <c r="P174" s="63">
+      <c r="P175" s="63">
         <f>P58-P53+P123+P64</f>
         <v>-19066</v>
       </c>
-      <c r="Q174" s="63">
+      <c r="Q175" s="63">
         <f>Q58-Q53+Q123+Q64</f>
         <v>-7383</v>
       </c>
-      <c r="T174" s="63">
-        <f t="shared" ref="T174:AA174" si="100">T58-T53+T123+T64</f>
-        <v>0</v>
-      </c>
-      <c r="U174" s="63">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="V174" s="63">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="W174" s="63">
-        <f t="shared" si="100"/>
+      <c r="T175" s="63">
+        <f t="shared" ref="T175:AA175" si="101">T58-T53+T123+T64</f>
+        <v>0</v>
+      </c>
+      <c r="U175" s="63">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="V175" s="63">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="W175" s="63">
+        <f t="shared" si="101"/>
         <v>-5054</v>
       </c>
-      <c r="X174" s="63">
-        <f t="shared" si="100"/>
+      <c r="X175" s="63">
+        <f t="shared" si="101"/>
         <v>-2164</v>
       </c>
-      <c r="Y174" s="63">
-        <f t="shared" si="100"/>
+      <c r="Y175" s="63">
+        <f t="shared" si="101"/>
         <v>-427</v>
       </c>
-      <c r="Z174" s="63">
-        <f t="shared" si="100"/>
+      <c r="Z175" s="63">
+        <f t="shared" si="101"/>
         <v>262</v>
       </c>
-      <c r="AA174" s="63">
-        <f t="shared" si="100"/>
+      <c r="AA175" s="63">
+        <f t="shared" si="101"/>
         <v>-3161</v>
       </c>
-      <c r="AC174" s="63">
+      <c r="AC175" s="63">
         <f>AC58-AC53+AC123+AC64</f>
         <v>-5490</v>
       </c>
     </row>
-    <row r="175" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B175" s="20" t="s">
+    <row r="176" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B176" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="M175" s="63">
+      <c r="M176" s="63">
         <f>M122+M52+M123+M54+M56+M57+M55</f>
         <v>5461.985025111735</v>
       </c>
-      <c r="N175" s="63">
-        <f t="shared" ref="N175:Q175" si="101">N122+N52+N123+N54+N56+N57+N55</f>
+      <c r="N176" s="63">
+        <f t="shared" ref="N176:Q176" si="102">N122+N52+N123+N54+N56+N57+N55</f>
         <v>-13983</v>
       </c>
-      <c r="O175" s="63">
-        <f t="shared" si="101"/>
+      <c r="O176" s="63">
+        <f t="shared" si="102"/>
         <v>-16624</v>
       </c>
-      <c r="P175" s="63">
-        <f t="shared" si="101"/>
+      <c r="P176" s="63">
+        <f t="shared" si="102"/>
         <v>-23140</v>
       </c>
-      <c r="Q175" s="63">
-        <f t="shared" si="101"/>
+      <c r="Q176" s="63">
+        <f t="shared" si="102"/>
         <v>-6901</v>
-      </c>
-      <c r="T175" s="49"/>
-      <c r="U175" s="49"/>
-      <c r="V175" s="49"/>
-      <c r="W175" s="49"/>
-      <c r="X175" s="49"/>
-      <c r="Y175" s="49"/>
-      <c r="Z175" s="49"/>
-      <c r="AA175" s="49"/>
-      <c r="AC175" s="63">
-        <f>AC122+AC52+AC123+AC54+AC56+AC57</f>
-        <v>-8573</v>
-      </c>
-    </row>
-    <row r="176" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B176" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="M176" s="71">
-        <f>M170/M174</f>
-        <v>24.234480257856571</v>
-      </c>
-      <c r="N176" s="71">
-        <f t="shared" ref="N176:Q176" si="102">N170/N174</f>
-        <v>-8.7516835473323233</v>
-      </c>
-      <c r="O176" s="71">
-        <f t="shared" si="102"/>
-        <v>-12.197995202193283</v>
-      </c>
-      <c r="P176" s="71">
-        <f t="shared" si="102"/>
-        <v>-4.6102486100912623</v>
-      </c>
-      <c r="Q176" s="71">
-        <f t="shared" si="102"/>
-        <v>-24.491263713937425</v>
       </c>
       <c r="T176" s="49"/>
       <c r="U176" s="49"/>
@@ -30327,34 +30340,34 @@
       <c r="Y176" s="49"/>
       <c r="Z176" s="49"/>
       <c r="AA176" s="49"/>
-      <c r="AC176" s="71">
-        <f t="shared" ref="AC176:AC177" ca="1" si="103">AC170/AC174</f>
-        <v>-102.61187795992713</v>
+      <c r="AC176" s="63">
+        <f>AC122+AC52+AC123+AC54+AC56+AC57</f>
+        <v>-8573</v>
       </c>
     </row>
     <row r="177" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B177" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M177" s="71">
         <f>M171/M175</f>
-        <v>40.317380766801932</v>
+        <v>24.234480257856571</v>
       </c>
       <c r="N177" s="71">
-        <f t="shared" ref="N177:Q177" si="104">N171/N175</f>
-        <v>-8.9618365157691464</v>
+        <f t="shared" ref="N177:Q177" si="103">N171/N175</f>
+        <v>-8.7516835473323233</v>
       </c>
       <c r="O177" s="71">
-        <f t="shared" si="104"/>
-        <v>-14.56746270452358</v>
+        <f t="shared" si="103"/>
+        <v>-12.197995202193283</v>
       </c>
       <c r="P177" s="71">
-        <f t="shared" si="104"/>
-        <v>-5.255401901469317</v>
+        <f t="shared" si="103"/>
+        <v>-4.6102486100912623</v>
       </c>
       <c r="Q177" s="71">
-        <f t="shared" si="104"/>
-        <v>-29.280828865381828</v>
+        <f t="shared" si="103"/>
+        <v>-24.491263713937425</v>
       </c>
       <c r="T177" s="49"/>
       <c r="U177" s="49"/>
@@ -30365,33 +30378,33 @@
       <c r="Z177" s="49"/>
       <c r="AA177" s="49"/>
       <c r="AC177" s="71">
-        <f t="shared" ca="1" si="103"/>
-        <v>-68.724624985419339</v>
+        <f t="shared" ref="AC177:AC178" ca="1" si="104">AC171/AC175</f>
+        <v>-101.8794918032787</v>
       </c>
     </row>
     <row r="178" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B178" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="M178" s="73">
-        <f>M174/M170</f>
-        <v>4.1263521617131038E-2</v>
-      </c>
-      <c r="N178" s="73">
-        <f t="shared" ref="N178:Q178" si="105">N174/N170</f>
-        <v>-0.11426372932609277</v>
-      </c>
-      <c r="O178" s="73">
+        <v>267</v>
+      </c>
+      <c r="M178" s="71">
+        <f>M172/M176</f>
+        <v>40.317380766801932</v>
+      </c>
+      <c r="N178" s="71">
+        <f t="shared" ref="N178:Q178" si="105">N172/N176</f>
+        <v>-8.9618365157691464</v>
+      </c>
+      <c r="O178" s="71">
         <f t="shared" si="105"/>
-        <v>-8.1980684811237922E-2</v>
-      </c>
-      <c r="P178" s="73">
+        <v>-14.56746270452358</v>
+      </c>
+      <c r="P178" s="71">
         <f t="shared" si="105"/>
-        <v>-0.21690804218478027</v>
-      </c>
-      <c r="Q178" s="73">
+        <v>-5.255401901469317</v>
+      </c>
+      <c r="Q178" s="71">
         <f t="shared" si="105"/>
-        <v>-4.0830886134753538E-2</v>
+        <v>-29.280828865381828</v>
       </c>
       <c r="T178" s="49"/>
       <c r="U178" s="49"/>
@@ -30401,34 +30414,34 @@
       <c r="Y178" s="49"/>
       <c r="Z178" s="49"/>
       <c r="AA178" s="49"/>
-      <c r="AC178" s="73">
-        <f t="shared" ref="AC178" ca="1" si="106">AC174/AC170</f>
-        <v>-9.7454604659952572E-3</v>
+      <c r="AC178" s="71">
+        <f t="shared" ca="1" si="104"/>
+        <v>-68.255617636766601</v>
       </c>
     </row>
     <row r="179" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B179" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M179" s="73">
-        <f>M26/M129</f>
-        <v>9.471837848372637E-2</v>
+        <f>M175/M171</f>
+        <v>4.1263521617131038E-2</v>
       </c>
       <c r="N179" s="73">
-        <f>N26/N129</f>
-        <v>7.3401437760121077E-2</v>
+        <f t="shared" ref="N179:Q179" si="106">N175/N171</f>
+        <v>-0.11426372932609277</v>
       </c>
       <c r="O179" s="73">
-        <f>O26/O129</f>
-        <v>7.9601990049751256E-3</v>
+        <f t="shared" si="106"/>
+        <v>-8.1980684811237922E-2</v>
       </c>
       <c r="P179" s="73">
-        <f>P26/P129</f>
-        <v>-0.21576354679802953</v>
+        <f t="shared" si="106"/>
+        <v>-0.21690804218478027</v>
       </c>
       <c r="Q179" s="73">
-        <f>Q26/Q129</f>
-        <v>-1.6574585635359114E-3</v>
+        <f t="shared" si="106"/>
+        <v>-4.0830886134753538E-2</v>
       </c>
       <c r="T179" s="49"/>
       <c r="U179" s="49"/>
@@ -30439,33 +30452,33 @@
       <c r="Z179" s="49"/>
       <c r="AA179" s="49"/>
       <c r="AC179" s="73">
-        <f ca="1">AC26/AC129</f>
-        <v>-5.5315162599812642E-3</v>
+        <f t="shared" ref="AC179" ca="1" si="107">AC175/AC171</f>
+        <v>-9.8155181410889015E-3</v>
       </c>
     </row>
     <row r="180" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="M180" s="154">
-        <f>M81/M129</f>
-        <v>2.7090235821477293E-2</v>
-      </c>
-      <c r="N180" s="154">
-        <f>N81/N129</f>
-        <v>5.5240257283390083E-2</v>
-      </c>
-      <c r="O180" s="154">
-        <f>O81/O129</f>
-        <v>1.472636815920398E-2</v>
-      </c>
-      <c r="P180" s="154">
-        <f>P81/P129</f>
-        <v>1.8719211822660099E-2</v>
-      </c>
-      <c r="Q180" s="154">
-        <f>Q81/Q129</f>
-        <v>0</v>
+        <v>269</v>
+      </c>
+      <c r="M180" s="73">
+        <f>M26/M130</f>
+        <v>9.471837848372637E-2</v>
+      </c>
+      <c r="N180" s="73">
+        <f t="shared" ref="N180:Q180" si="108">N26/N130</f>
+        <v>7.3401437760121077E-2</v>
+      </c>
+      <c r="O180" s="73">
+        <f t="shared" si="108"/>
+        <v>7.9601990049751256E-3</v>
+      </c>
+      <c r="P180" s="73">
+        <f t="shared" si="108"/>
+        <v>-0.21576354679802953</v>
+      </c>
+      <c r="Q180" s="73">
+        <f t="shared" si="108"/>
+        <v>-1.6574585635359114E-3</v>
       </c>
       <c r="T180" s="49"/>
       <c r="U180" s="49"/>
@@ -30475,33 +30488,33 @@
       <c r="Y180" s="49"/>
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
-      <c r="AC180" s="154">
-        <f ca="1">AC81/AC129</f>
-        <v>0</v>
+      <c r="AC180" s="73">
+        <f t="shared" ref="AC180" ca="1" si="109">AC26/AC130</f>
+        <v>-5.5712809453205732E-3</v>
       </c>
     </row>
     <row r="181" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B181" s="20" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="M181" s="154">
-        <f>-M62/M170</f>
-        <v>1.1471325510000168E-2</v>
+        <f>M81/M130</f>
+        <v>2.7090235821477293E-2</v>
       </c>
       <c r="N181" s="154">
-        <f>-N62/N170</f>
-        <v>0</v>
+        <f t="shared" ref="N181:Q181" si="110">N81/N130</f>
+        <v>5.5240257283390083E-2</v>
       </c>
       <c r="O181" s="154">
-        <f>-O62/O170</f>
-        <v>0</v>
+        <f t="shared" si="110"/>
+        <v>1.472636815920398E-2</v>
       </c>
       <c r="P181" s="154">
-        <f>-P62/P170</f>
-        <v>0</v>
+        <f t="shared" si="110"/>
+        <v>1.8719211822660099E-2</v>
       </c>
       <c r="Q181" s="154">
-        <f>-Q62/Q170</f>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="T181" s="49"/>
@@ -30513,32 +30526,32 @@
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
       <c r="AC181" s="154">
-        <f ca="1">-AC62/AC170</f>
+        <f t="shared" ref="AC181" ca="1" si="111">AC81/AC130</f>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B182" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M182" s="154">
-        <f>-(M62+M63)/M170</f>
-        <v>3.8280501981404286E-2</v>
+        <f>-M62/M171</f>
+        <v>1.1471325510000168E-2</v>
       </c>
       <c r="N182" s="154">
-        <f>-(N62+N63)/N170</f>
-        <v>5.4648662953072684E-2</v>
+        <f>-N62/N171</f>
+        <v>0</v>
       </c>
       <c r="O182" s="154">
-        <f>-(O62+O63)/O170</f>
-        <v>1.4459467369037167E-2</v>
+        <f>-O62/O171</f>
+        <v>0</v>
       </c>
       <c r="P182" s="154">
-        <f>-(P62+P63)/P170</f>
-        <v>1.8191333234735322E-2</v>
+        <f>-P62/P171</f>
+        <v>0</v>
       </c>
       <c r="Q182" s="154">
-        <f>-(Q62+Q63)/Q170</f>
+        <f>-Q62/Q171</f>
         <v>0</v>
       </c>
       <c r="T182" s="49"/>
@@ -30550,33 +30563,33 @@
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
       <c r="AC182" s="154">
-        <f ca="1">-(AC62+AC63)/AC170</f>
+        <f ca="1">-AC62/AC171</f>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B183" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="M183" s="71">
-        <f>M175/M5</f>
-        <v>6.9118053061243856E-2</v>
-      </c>
-      <c r="N183" s="71">
-        <f>N175/N5</f>
-        <v>-0.22176229898182509</v>
-      </c>
-      <c r="O183" s="71">
-        <f>O175/O5</f>
-        <v>-0.30655749797152765</v>
-      </c>
-      <c r="P183" s="71">
-        <f>P175/P5</f>
-        <v>-0.43577333760192838</v>
-      </c>
-      <c r="Q183" s="71">
-        <f>Q175/Q5</f>
-        <v>-0.1305696933002857</v>
+        <v>298</v>
+      </c>
+      <c r="M183" s="154">
+        <f>-(M62+M63)/M171</f>
+        <v>3.8280501981404286E-2</v>
+      </c>
+      <c r="N183" s="154">
+        <f>-(N62+N63)/N171</f>
+        <v>5.4648662953072684E-2</v>
+      </c>
+      <c r="O183" s="154">
+        <f>-(O62+O63)/O171</f>
+        <v>1.4459467369037167E-2</v>
+      </c>
+      <c r="P183" s="154">
+        <f>-(P62+P63)/P171</f>
+        <v>1.8191333234735322E-2</v>
+      </c>
+      <c r="Q183" s="154">
+        <f>-(Q62+Q63)/Q171</f>
+        <v>0</v>
       </c>
       <c r="T183" s="49"/>
       <c r="U183" s="49"/>
@@ -30586,34 +30599,34 @@
       <c r="Y183" s="49"/>
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
-      <c r="AC183" s="71">
-        <f>AC175/AC5</f>
-        <v>-0.15945910756468204</v>
+      <c r="AC183" s="154">
+        <f ca="1">-(AC62+AC63)/AC171</f>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B184" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="M184" s="154">
-        <f>-M63/M174</f>
-        <v>0.64970645792563597</v>
-      </c>
-      <c r="N184" s="154">
-        <f>-N63/N174</f>
-        <v>-0.47826780445011563</v>
-      </c>
-      <c r="O184" s="154">
-        <f>-O63/O174</f>
-        <v>-0.1763765135937857</v>
-      </c>
-      <c r="P184" s="154">
-        <f>-P63/P174</f>
-        <v>-8.3866568761145496E-2</v>
-      </c>
-      <c r="Q184" s="154">
-        <f>-Q63/Q174</f>
-        <v>0</v>
+        <v>271</v>
+      </c>
+      <c r="M184" s="71">
+        <f>M176/M5</f>
+        <v>6.9118053061243856E-2</v>
+      </c>
+      <c r="N184" s="71">
+        <f>N176/N5</f>
+        <v>-0.22176229898182509</v>
+      </c>
+      <c r="O184" s="71">
+        <f>O176/O5</f>
+        <v>-0.30655749797152765</v>
+      </c>
+      <c r="P184" s="71">
+        <f>P176/P5</f>
+        <v>-0.43577333760192838</v>
+      </c>
+      <c r="Q184" s="71">
+        <f>Q176/Q5</f>
+        <v>-0.1305696933002857</v>
       </c>
       <c r="T184" s="49"/>
       <c r="U184" s="49"/>
@@ -30623,33 +30636,33 @@
       <c r="Y184" s="49"/>
       <c r="Z184" s="49"/>
       <c r="AA184" s="49"/>
-      <c r="AC184" s="154">
-        <f>-AC63/AC174</f>
-        <v>0</v>
+      <c r="AC184" s="71">
+        <f>AC176/AC5</f>
+        <v>-0.15945910756468204</v>
       </c>
     </row>
     <row r="185" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B185" s="20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M185" s="154">
-        <f>-M62/M174</f>
-        <v>0.27800161160354553</v>
+        <f>-M63/M175</f>
+        <v>0.64970645792563597</v>
       </c>
       <c r="N185" s="154">
-        <f>-N62/N174</f>
-        <v>0</v>
+        <f>-N63/N175</f>
+        <v>-0.47826780445011563</v>
       </c>
       <c r="O185" s="154">
-        <f>-O62/O174</f>
-        <v>0</v>
+        <f>-O63/O175</f>
+        <v>-0.1763765135937857</v>
       </c>
       <c r="P185" s="154">
-        <f>-P62/P174</f>
-        <v>0</v>
+        <f>-P63/P175</f>
+        <v>-8.3866568761145496E-2</v>
       </c>
       <c r="Q185" s="154">
-        <f>-Q62/Q174</f>
+        <f>-Q63/Q175</f>
         <v>0</v>
       </c>
       <c r="T185" s="49"/>
@@ -30661,32 +30674,32 @@
       <c r="Z185" s="49"/>
       <c r="AA185" s="49"/>
       <c r="AC185" s="154">
-        <f>-AC62/AC174</f>
+        <f>-AC63/AC175</f>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="M186" s="154">
-        <f>(-M63-M62)/M174</f>
-        <v>0.9277080695291815</v>
+        <f>-M62/M175</f>
+        <v>0.27800161160354553</v>
       </c>
       <c r="N186" s="154">
-        <f>(-N63-N62)/N174</f>
-        <v>-0.47826780445011563</v>
+        <f>-N62/N175</f>
+        <v>0</v>
       </c>
       <c r="O186" s="154">
-        <f>(-O63-O62)/O174</f>
-        <v>-0.1763765135937857</v>
+        <f>-O62/O175</f>
+        <v>0</v>
       </c>
       <c r="P186" s="154">
-        <f>(-P63-P62)/P174</f>
-        <v>-8.3866568761145496E-2</v>
+        <f>-P62/P175</f>
+        <v>0</v>
       </c>
       <c r="Q186" s="154">
-        <f>(-Q63-Q62)/Q174</f>
+        <f>-Q62/Q175</f>
         <v>0</v>
       </c>
       <c r="T186" s="49"/>
@@ -30698,33 +30711,33 @@
       <c r="Z186" s="49"/>
       <c r="AA186" s="49"/>
       <c r="AC186" s="154">
-        <f>(-AC63-AC62)/AC174</f>
+        <f>-AC62/AC175</f>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B187" s="20" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="M187" s="154">
-        <f>M79/M77</f>
-        <v>4.874482086278333E-4</v>
+        <f>(-M63-M62)/M175</f>
+        <v>0.9277080695291815</v>
       </c>
       <c r="N187" s="154">
-        <f>N79/N77</f>
-        <v>4.8169556840077071E-4</v>
+        <f>(-N63-N62)/N175</f>
+        <v>-0.47826780445011563</v>
       </c>
       <c r="O187" s="154">
-        <f>O79/O77</f>
-        <v>4.7058823529411766E-4</v>
+        <f>(-O63-O62)/O175</f>
+        <v>-0.1763765135937857</v>
       </c>
       <c r="P187" s="154">
-        <f>P79/P77</f>
-        <v>4.6189376443418013E-4</v>
+        <f>(-P63-P62)/P175</f>
+        <v>-8.3866568761145496E-2</v>
       </c>
       <c r="Q187" s="154">
-        <f>Q79/Q77</f>
-        <v>6.0060060060060057E-4</v>
+        <f>(-Q63-Q62)/Q175</f>
+        <v>0</v>
       </c>
       <c r="T187" s="49"/>
       <c r="U187" s="49"/>
@@ -30735,909 +30748,946 @@
       <c r="Z187" s="49"/>
       <c r="AA187" s="49"/>
       <c r="AC187" s="154">
+        <f>(-AC63-AC62)/AC175</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B188" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="M188" s="154">
+        <f>M79/M77</f>
+        <v>4.874482086278333E-4</v>
+      </c>
+      <c r="N188" s="154">
+        <f>N79/N77</f>
+        <v>4.8169556840077071E-4</v>
+      </c>
+      <c r="O188" s="154">
+        <f>O79/O77</f>
+        <v>4.7058823529411766E-4</v>
+      </c>
+      <c r="P188" s="154">
+        <f>P79/P77</f>
+        <v>4.6189376443418013E-4</v>
+      </c>
+      <c r="Q188" s="154">
+        <f>Q79/Q77</f>
+        <v>6.0060060060060057E-4</v>
+      </c>
+      <c r="T188" s="49"/>
+      <c r="U188" s="49"/>
+      <c r="V188" s="49"/>
+      <c r="W188" s="49"/>
+      <c r="X188" s="49"/>
+      <c r="Y188" s="49"/>
+      <c r="Z188" s="49"/>
+      <c r="AA188" s="49"/>
+      <c r="AC188" s="154">
         <f>AC79/AC77</f>
         <v>5.9689614007162755E-4</v>
       </c>
     </row>
-    <row r="188" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B188" s="20" t="s">
+    <row r="189" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B189" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="M188" s="71">
+      <c r="M189" s="71">
         <f>M120/M74</f>
         <v>6.9776522593320234</v>
       </c>
-      <c r="N188" s="71">
+      <c r="N189" s="71">
         <f>N120/N74</f>
         <v>6.8498912255257434</v>
       </c>
-      <c r="O188" s="71">
+      <c r="O189" s="71">
         <f>O120/O74</f>
         <v>5.9210028382213808</v>
       </c>
-      <c r="P188" s="71">
+      <c r="P189" s="71">
         <f>P120/P74</f>
         <v>5.0951501154734409</v>
       </c>
-      <c r="Q188" s="71">
+      <c r="Q189" s="71">
         <f>Q120/Q74</f>
         <v>7.4906906906906903</v>
       </c>
-      <c r="T188" s="71">
-        <f t="shared" ref="T188:AA188" si="107">T120/T74</f>
+      <c r="T189" s="71">
+        <f t="shared" ref="T189:AA189" si="112">T120/T74</f>
         <v>6.8458840037418147</v>
       </c>
-      <c r="U188" s="71">
-        <f t="shared" si="107"/>
+      <c r="U189" s="71">
+        <f t="shared" si="112"/>
         <v>5.5845119406445631</v>
       </c>
-      <c r="V188" s="71">
-        <f t="shared" si="107"/>
+      <c r="V189" s="71">
+        <f t="shared" si="112"/>
         <v>5.0951501154734409</v>
       </c>
-      <c r="W188" s="71">
-        <f t="shared" si="107"/>
+      <c r="W189" s="71">
+        <f t="shared" si="112"/>
         <v>4.825309491059147</v>
       </c>
-      <c r="X188" s="71">
-        <f t="shared" si="107"/>
+      <c r="X189" s="71">
+        <f t="shared" si="112"/>
         <v>4.8448709161526162</v>
       </c>
-      <c r="Y188" s="71">
-        <f t="shared" si="107"/>
+      <c r="Y189" s="71">
+        <f t="shared" si="112"/>
         <v>6.4853249475890982</v>
       </c>
-      <c r="Z188" s="71">
-        <f t="shared" si="107"/>
+      <c r="Z189" s="71">
+        <f t="shared" si="112"/>
         <v>7.4906906906906903</v>
       </c>
-      <c r="AA188" s="71">
-        <f t="shared" si="107"/>
+      <c r="AA189" s="71">
+        <f t="shared" si="112"/>
         <v>6.5238758456028654</v>
       </c>
-      <c r="AC188" s="71">
+      <c r="AC189" s="71">
         <f>AC120/AC74</f>
         <v>6.5238758456028654</v>
       </c>
     </row>
-    <row r="189" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B189" s="20" t="s">
+    <row r="190" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B190" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="M189" s="154">
+      <c r="M190" s="154">
         <f>M53/M58</f>
         <v>6.9120043454644217E-2</v>
       </c>
-      <c r="N189" s="154">
+      <c r="N190" s="154">
         <f>N53/N58</f>
         <v>0.20268256333830104</v>
       </c>
-      <c r="O189" s="154">
+      <c r="O190" s="154">
         <f>O53/O58</f>
         <v>0.28149245924505273</v>
       </c>
-      <c r="P189" s="154">
+      <c r="P190" s="154">
         <f>P53/P58</f>
         <v>0.41143822393822393</v>
       </c>
-      <c r="Q189" s="154">
+      <c r="Q190" s="154">
         <f>Q53/Q58</f>
         <v>0.25100546560791998</v>
       </c>
-      <c r="T189" s="154" t="e">
-        <f t="shared" ref="T189:Y189" si="108">T53/T58</f>
+      <c r="T190" s="154" t="e">
+        <f t="shared" ref="T190:Y190" si="113">T53/T58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U189" s="154" t="e">
-        <f t="shared" si="108"/>
+      <c r="U190" s="154" t="e">
+        <f t="shared" si="113"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V189" s="154" t="e">
-        <f t="shared" si="108"/>
+      <c r="V190" s="154" t="e">
+        <f t="shared" si="113"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W189" s="154">
-        <f t="shared" si="108"/>
+      <c r="W190" s="154">
+        <f t="shared" si="113"/>
         <v>0.84132841328413288</v>
       </c>
-      <c r="X189" s="154">
-        <f t="shared" si="108"/>
+      <c r="X190" s="154">
+        <f t="shared" si="113"/>
         <v>0.32390243902439025</v>
       </c>
-      <c r="Y189" s="154">
-        <f t="shared" si="108"/>
+      <c r="Y190" s="154">
+        <f t="shared" si="113"/>
         <v>0.2152395915161037</v>
       </c>
-      <c r="Z189" s="154">
+      <c r="Z190" s="154">
         <f>W53/W58</f>
         <v>0.84132841328413288</v>
       </c>
-      <c r="AA189" s="154">
+      <c r="AA190" s="154">
         <f>AA53/AA58</f>
         <v>0.56660583941605835</v>
       </c>
-      <c r="AC189" s="154">
+      <c r="AC190" s="154">
         <f>AC53/AC58</f>
         <v>0.2375751503006012</v>
       </c>
     </row>
-    <row r="190" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B190" s="20" t="s">
+    <row r="191" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B191" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="M190" s="154">
+      <c r="M191" s="154">
         <f>M53/M5</f>
         <v>2.5764324762097592E-2</v>
       </c>
-      <c r="N190" s="154">
+      <c r="N191" s="154">
         <f>N53/N5</f>
         <v>4.9608272274558315E-2</v>
       </c>
-      <c r="O190" s="154">
+      <c r="O191" s="154">
         <f>O53/O5</f>
         <v>5.9544884561481153E-2</v>
       </c>
-      <c r="P190" s="154">
+      <c r="P191" s="154">
         <f>P53/P5</f>
         <v>6.4217246379540877E-2</v>
       </c>
-      <c r="Q190" s="154">
+      <c r="Q191" s="154">
         <f>Q53/Q5</f>
         <v>4.6052258149963103E-2</v>
       </c>
-      <c r="T190" s="154">
-        <f t="shared" ref="T190:Y190" si="109">T53/T5</f>
-        <v>0</v>
-      </c>
-      <c r="U190" s="154">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="V190" s="154">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="W190" s="154">
-        <f t="shared" si="109"/>
+      <c r="T191" s="154">
+        <f t="shared" ref="T191:Y191" si="114">T53/T5</f>
+        <v>0</v>
+      </c>
+      <c r="U191" s="154">
+        <f t="shared" si="114"/>
+        <v>0</v>
+      </c>
+      <c r="V191" s="154">
+        <f t="shared" si="114"/>
+        <v>0</v>
+      </c>
+      <c r="W191" s="154">
+        <f t="shared" si="114"/>
         <v>5.3998578984763561E-2</v>
       </c>
-      <c r="X190" s="154">
-        <f t="shared" si="109"/>
+      <c r="X191" s="154">
+        <f t="shared" si="114"/>
         <v>5.1636985768722297E-2</v>
       </c>
-      <c r="Y190" s="154">
-        <f t="shared" si="109"/>
+      <c r="Y191" s="154">
+        <f t="shared" si="114"/>
         <v>4.0137698674284038E-2</v>
       </c>
-      <c r="Z190" s="154">
+      <c r="Z191" s="154">
         <f>W53/Z5</f>
         <v>5.0021939447125935E-2</v>
       </c>
-      <c r="AA190" s="154">
+      <c r="AA191" s="154">
         <f>AA53/AA5</f>
         <v>4.5739117625395891E-2</v>
       </c>
-      <c r="AC190" s="154">
+      <c r="AC191" s="154">
         <f>AC53/AC5</f>
         <v>4.4100961627885349E-2</v>
       </c>
     </row>
-    <row r="191" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B191" s="20" t="s">
+    <row r="192" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B192" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="M191" s="71">
+      <c r="M192" s="71">
         <f>(M120-M121)/M74</f>
         <v>-2.3791748526522594</v>
       </c>
-      <c r="N191" s="71">
+      <c r="N192" s="71">
         <f>(N120-N121)/N74</f>
         <v>-3.3147208121827409</v>
       </c>
-      <c r="O191" s="71">
+      <c r="O192" s="71">
         <f>(O120-O121)/O74</f>
         <v>-5.7313150425733204</v>
       </c>
-      <c r="P191" s="71">
+      <c r="P192" s="71">
         <f>(P120-P121)/P74</f>
         <v>-6.4547344110854503</v>
       </c>
-      <c r="Q191" s="71">
+      <c r="Q192" s="71">
         <f>(Q120-Q121)/Q74</f>
         <v>-1.8356356356356356</v>
       </c>
-      <c r="T191" s="71">
-        <f t="shared" ref="T191:AA191" si="110">(T120-T121)/T74</f>
+      <c r="T192" s="71">
+        <f t="shared" ref="T192:AA192" si="115">(T120-T121)/T74</f>
         <v>-5.5556594948550044</v>
       </c>
-      <c r="U191" s="71">
-        <f t="shared" si="110"/>
+      <c r="U192" s="71">
+        <f t="shared" si="115"/>
         <v>-6.06306515186645</v>
       </c>
-      <c r="V191" s="71">
-        <f t="shared" si="110"/>
+      <c r="V192" s="71">
+        <f t="shared" si="115"/>
         <v>-6.4547344110854503</v>
       </c>
-      <c r="W191" s="71">
-        <f t="shared" si="110"/>
+      <c r="W192" s="71">
+        <f t="shared" si="115"/>
         <v>-6.6719394773039893</v>
       </c>
-      <c r="X191" s="71">
-        <f t="shared" si="110"/>
+      <c r="X192" s="71">
+        <f t="shared" si="115"/>
         <v>-6.7514279186657529</v>
       </c>
-      <c r="Y191" s="71">
-        <f t="shared" si="110"/>
+      <c r="Y192" s="71">
+        <f t="shared" si="115"/>
         <v>-3.2742138364779874</v>
       </c>
-      <c r="Z191" s="71">
-        <f t="shared" si="110"/>
+      <c r="Z192" s="71">
+        <f t="shared" si="115"/>
         <v>-1.8356356356356356</v>
       </c>
-      <c r="AA191" s="71">
-        <f t="shared" si="110"/>
+      <c r="AA192" s="71">
+        <f t="shared" si="115"/>
         <v>-2.435734182252288</v>
       </c>
-      <c r="AC191" s="71">
+      <c r="AC192" s="71">
         <f>(AC120-AC121)/AC74</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
-    <row r="192" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B192" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="M192" s="154">
-        <f>(M120-M121)/M170</f>
-        <v>-4.601830291547894E-2</v>
-      </c>
-      <c r="N192" s="154">
-        <f>(N120-N121)/N170</f>
-        <v>-0.12496200017933728</v>
-      </c>
-      <c r="O192" s="154">
-        <f>(O120-O121)/O170</f>
-        <v>-0.11346561311091601</v>
-      </c>
-      <c r="P192" s="154">
-        <f>(P120-P121)/P170</f>
-        <v>-0.31796721236874137</v>
-      </c>
-      <c r="Q192" s="154">
-        <f>(Q120-Q121)/Q170</f>
-        <v>-5.070816673026618E-2</v>
-      </c>
-      <c r="T192" s="49"/>
-      <c r="U192" s="49"/>
-      <c r="V192" s="49"/>
-      <c r="W192" s="49"/>
-      <c r="X192" s="49"/>
-      <c r="Y192" s="49"/>
-      <c r="Z192" s="49"/>
-      <c r="AA192" s="49"/>
-      <c r="AC192" s="154">
-        <f ca="1">(AC120-AC121)/AC170</f>
-        <v>-2.1731134248581776E-2</v>
-      </c>
-    </row>
     <row r="193" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B193" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="M193" s="154">
+        <f>(M120-M121)/M171</f>
+        <v>-4.601830291547894E-2</v>
+      </c>
+      <c r="N193" s="154">
+        <f>(N120-N121)/N171</f>
+        <v>-0.12496200017933728</v>
+      </c>
+      <c r="O193" s="154">
+        <f>(O120-O121)/O171</f>
+        <v>-0.11346561311091601</v>
+      </c>
+      <c r="P193" s="154">
+        <f>(P120-P121)/P171</f>
+        <v>-0.31796721236874137</v>
+      </c>
+      <c r="Q193" s="154">
+        <f>(Q120-Q121)/Q171</f>
+        <v>-5.070816673026618E-2</v>
+      </c>
+      <c r="T193" s="49"/>
+      <c r="U193" s="49"/>
+      <c r="V193" s="49"/>
+      <c r="W193" s="49"/>
+      <c r="X193" s="49"/>
+      <c r="Y193" s="49"/>
+      <c r="Z193" s="49"/>
+      <c r="AA193" s="49"/>
+      <c r="AC193" s="154">
+        <f ca="1">(AC120-AC121)/AC171</f>
+        <v>-2.1887353931368002E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B194" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="M193" s="154">
+      <c r="M194" s="154">
         <f>-M123/M5</f>
         <v>0.23705456570155903</v>
       </c>
-      <c r="N193" s="154">
+      <c r="N194" s="154">
         <f>-N123/N5</f>
         <v>0.39401148222158783</v>
       </c>
-      <c r="O193" s="154">
+      <c r="O194" s="154">
         <f>-O123/O5</f>
         <v>0.4748469425389098</v>
       </c>
-      <c r="P193" s="154">
+      <c r="P194" s="154">
         <f>-P123/P5</f>
         <v>0.45091429539933336</v>
       </c>
-      <c r="Q193" s="154">
+      <c r="Q194" s="154">
         <f>-Q123/Q5</f>
         <v>0.27710820577829071</v>
       </c>
-      <c r="T193" s="154">
-        <f t="shared" ref="T193:AA193" si="111">-T123/T5</f>
-        <v>0</v>
-      </c>
-      <c r="U193" s="154">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="V193" s="154">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="W193" s="154">
-        <f t="shared" si="111"/>
+      <c r="T194" s="154">
+        <f t="shared" ref="T194:AA194" si="116">-T123/T5</f>
+        <v>0</v>
+      </c>
+      <c r="U194" s="154">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="V194" s="154">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="W194" s="154">
+        <f t="shared" si="116"/>
         <v>0.40917344280413676</v>
       </c>
-      <c r="X193" s="154">
-        <f t="shared" si="111"/>
+      <c r="X194" s="154">
+        <f t="shared" si="116"/>
         <v>0.27607123415506651</v>
       </c>
-      <c r="Y193" s="154">
-        <f t="shared" si="111"/>
+      <c r="Y194" s="154">
+        <f t="shared" si="116"/>
         <v>0.17761664103127517</v>
       </c>
-      <c r="Z193" s="154">
-        <f t="shared" si="111"/>
+      <c r="Z194" s="154">
+        <f t="shared" si="116"/>
         <v>0.25508263858417435</v>
       </c>
-      <c r="AA193" s="154">
-        <f t="shared" si="111"/>
+      <c r="AA194" s="154">
+        <f t="shared" si="116"/>
         <v>0.2678058481255064</v>
       </c>
-      <c r="AC193" s="154">
+      <c r="AC194" s="154">
         <f>-AC123/AC5</f>
         <v>0.24364339787586259</v>
       </c>
     </row>
-    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B194" s="20" t="s">
+    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B195" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="M194" s="154">
+      <c r="M195" s="154">
         <f>-(M123/M58)</f>
         <v>0.63596550787615425</v>
       </c>
-      <c r="N194" s="154">
+      <c r="N195" s="154">
         <f>-(N123/N58)</f>
         <v>1.6097971878442299</v>
       </c>
-      <c r="O194" s="154">
+      <c r="O195" s="154">
         <f>-(O123/O58)</f>
         <v>2.2447912126231366</v>
       </c>
-      <c r="P194" s="154">
+      <c r="P195" s="154">
         <f>-(P123/P58)</f>
         <v>2.8889961389961392</v>
       </c>
-      <c r="Q194" s="154">
+      <c r="Q195" s="154">
         <f>-(Q123/Q58)</f>
         <v>1.5103640301124059</v>
       </c>
-      <c r="T194" s="154" t="e">
-        <f t="shared" ref="T194:Y194" si="112">-(T123/T58)</f>
+      <c r="T195" s="154" t="e">
+        <f t="shared" ref="T195:Y195" si="117">-(T123/T58)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U194" s="154" t="e">
-        <f t="shared" si="112"/>
+      <c r="U195" s="154" t="e">
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V194" s="154" t="e">
-        <f t="shared" si="112"/>
+      <c r="V195" s="154" t="e">
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W194" s="154">
-        <f t="shared" si="112"/>
+      <c r="W195" s="154">
+        <f t="shared" si="117"/>
         <v>6.375153751537515</v>
       </c>
-      <c r="X194" s="154">
-        <f t="shared" si="112"/>
+      <c r="X195" s="154">
+        <f t="shared" si="117"/>
         <v>1.7317073170731707</v>
       </c>
-      <c r="Y194" s="154">
-        <f t="shared" si="112"/>
+      <c r="Y195" s="154">
+        <f t="shared" si="117"/>
         <v>0.95247446975648076</v>
       </c>
-      <c r="Z194" s="154">
+      <c r="Z195" s="154">
         <f>-(Z123/W58)</f>
         <v>4.2902829028290279</v>
       </c>
-      <c r="AA194" s="154">
+      <c r="AA195" s="154">
         <f>-(AA123/AA58)</f>
         <v>3.3175182481751824</v>
       </c>
-      <c r="AC194" s="154">
+      <c r="AC195" s="154">
         <f>-(AC123/AC58)</f>
         <v>1.3125250501002004</v>
       </c>
     </row>
-    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B195" s="20" t="s">
+    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B196" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="M195" s="154">
+      <c r="M196" s="154">
         <f>-M123/M52</f>
         <v>1.5886194029850746</v>
       </c>
-      <c r="N195" s="154">
+      <c r="N196" s="154">
         <f>-N123/N52</f>
         <v>1.9059455312619868</v>
       </c>
-      <c r="O195" s="154">
+      <c r="O196" s="154">
         <f>-O123/O52</f>
         <v>2.6817329722974379</v>
       </c>
-      <c r="P195" s="154">
+      <c r="P196" s="154">
         <f>-P123/P52</f>
         <v>2.1042270849811056</v>
       </c>
-      <c r="Q195" s="154">
+      <c r="Q196" s="154">
         <f>-Q123/Q52</f>
         <v>1.2511532547411583</v>
       </c>
-      <c r="T195" s="154" t="e">
-        <f t="shared" ref="T195:Y195" si="113">-T123/T52</f>
+      <c r="T196" s="154" t="e">
+        <f t="shared" ref="T196:Y196" si="118">-T123/T52</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U195" s="154" t="e">
-        <f t="shared" si="113"/>
+      <c r="U196" s="154" t="e">
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V195" s="154" t="e">
-        <f t="shared" si="113"/>
+      <c r="V196" s="154" t="e">
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W195" s="154">
-        <f t="shared" si="113"/>
+      <c r="W196" s="154">
+        <f t="shared" si="118"/>
         <v>1.9382946896035902</v>
       </c>
-      <c r="X195" s="154">
-        <f t="shared" si="113"/>
+      <c r="X196" s="154">
+        <f t="shared" si="118"/>
         <v>1.1782276800531033</v>
       </c>
-      <c r="Y195" s="154">
-        <f t="shared" si="113"/>
+      <c r="Y196" s="154">
+        <f t="shared" si="118"/>
         <v>0.81049465240641716</v>
       </c>
-      <c r="Z195" s="154">
+      <c r="Z196" s="154">
         <f>-Z123/W52</f>
         <v>1.3044128646222888</v>
       </c>
-      <c r="AA195" s="154">
+      <c r="AA196" s="154">
         <f>-AA123/AA52</f>
         <v>1.159438775510204</v>
       </c>
-      <c r="AC195" s="154">
+      <c r="AC196" s="154">
         <f>-AC123/AC52</f>
         <v>1.0765121630506247</v>
       </c>
     </row>
-    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B197" s="1"/>
-    </row>
-    <row r="198" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B198" s="14" t="s">
+    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B198" s="1"/>
+    </row>
+    <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B199" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="C198" s="172"/>
-      <c r="D198" s="172"/>
-      <c r="E198" s="172"/>
-      <c r="F198" s="172"/>
-      <c r="G198" s="172"/>
-      <c r="H198" s="172"/>
-      <c r="I198" s="172"/>
-      <c r="J198" s="172"/>
-      <c r="K198" s="172"/>
-      <c r="L198" s="172"/>
-      <c r="M198" s="172"/>
-      <c r="N198" s="172"/>
-      <c r="O198" s="172"/>
-      <c r="P198" s="172"/>
-      <c r="Q198" s="172"/>
-      <c r="T198" s="172"/>
-      <c r="U198" s="172"/>
-      <c r="V198" s="172"/>
-      <c r="W198" s="172"/>
-      <c r="X198" s="172"/>
-      <c r="Y198" s="172"/>
-      <c r="Z198" s="172"/>
-      <c r="AA198" s="172"/>
-      <c r="AC198" s="172"/>
-    </row>
-    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B199" s="218" t="s">
+      <c r="C199" s="172"/>
+      <c r="D199" s="172"/>
+      <c r="E199" s="172"/>
+      <c r="F199" s="172"/>
+      <c r="G199" s="172"/>
+      <c r="H199" s="172"/>
+      <c r="I199" s="172"/>
+      <c r="J199" s="172"/>
+      <c r="K199" s="172"/>
+      <c r="L199" s="172"/>
+      <c r="M199" s="172"/>
+      <c r="N199" s="172"/>
+      <c r="O199" s="172"/>
+      <c r="P199" s="172"/>
+      <c r="Q199" s="172"/>
+      <c r="T199" s="172"/>
+      <c r="U199" s="172"/>
+      <c r="V199" s="172"/>
+      <c r="W199" s="172"/>
+      <c r="X199" s="172"/>
+      <c r="Y199" s="172"/>
+      <c r="Z199" s="172"/>
+      <c r="AA199" s="172"/>
+      <c r="AC199" s="172"/>
+    </row>
+    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B200" s="218" t="s">
         <v>362</v>
       </c>
-      <c r="C199" s="80"/>
-      <c r="D199" s="80"/>
-      <c r="E199" s="80"/>
-      <c r="F199" s="80"/>
-      <c r="G199" s="80"/>
-      <c r="H199" s="80"/>
-      <c r="I199" s="80"/>
-      <c r="J199" s="80"/>
-      <c r="K199" s="80"/>
-      <c r="L199" s="80"/>
-      <c r="M199" s="80">
-        <f t="shared" ref="M199:Q203" si="114">IF(L105=0,
+      <c r="C200" s="80"/>
+      <c r="D200" s="80"/>
+      <c r="E200" s="80"/>
+      <c r="F200" s="80"/>
+      <c r="G200" s="80"/>
+      <c r="H200" s="80"/>
+      <c r="I200" s="80"/>
+      <c r="J200" s="80"/>
+      <c r="K200" s="80"/>
+      <c r="L200" s="80"/>
+      <c r="M200" s="80">
+        <f t="shared" ref="M200:Q204" si="119">IF(L105=0,
 IF(M105=0,0,IF(M105&gt;0,1,-1)),
 (M105-L105)/ABS(L105)
 )</f>
         <v>1</v>
       </c>
-      <c r="N199" s="80">
-        <f t="shared" si="114"/>
+      <c r="N200" s="80">
+        <f t="shared" si="119"/>
         <v>-0.22657676298045326</v>
       </c>
-      <c r="O199" s="80">
-        <f t="shared" si="114"/>
+      <c r="O200" s="80">
+        <f t="shared" si="119"/>
         <v>-7.9155257608661447E-2</v>
       </c>
-      <c r="P199" s="80">
-        <f t="shared" si="114"/>
+      <c r="P200" s="80">
+        <f t="shared" si="119"/>
         <v>0.139722469068289</v>
       </c>
-      <c r="Q199" s="80">
-        <f t="shared" si="114"/>
+      <c r="Q200" s="80">
+        <f t="shared" si="119"/>
         <v>-3.3527259641336293E-2</v>
       </c>
-      <c r="T199" s="80">
-        <f t="shared" ref="T199:AA203" si="115">IF(S105=0,
+      <c r="T200" s="80">
+        <f t="shared" ref="T200:AA204" si="120">IF(S105=0,
 IF(T105=0,0,IF(T105&gt;0,1,-1)),
 (T105-S105)/ABS(S105)
 )</f>
         <v>1</v>
       </c>
-      <c r="U199" s="80">
-        <f t="shared" si="115"/>
+      <c r="U200" s="80">
+        <f t="shared" si="120"/>
         <v>2.2104875353063983E-3</v>
       </c>
-      <c r="V199" s="80">
-        <f t="shared" si="115"/>
+      <c r="V200" s="80">
+        <f t="shared" si="120"/>
         <v>7.4500673937017522E-2</v>
       </c>
-      <c r="W199" s="80">
-        <f t="shared" si="115"/>
+      <c r="W200" s="80">
+        <f t="shared" si="120"/>
         <v>-0.13000342114266164</v>
       </c>
-      <c r="X199" s="80">
-        <f t="shared" si="115"/>
+      <c r="X200" s="80">
+        <f t="shared" si="120"/>
         <v>3.1721064359680168E-2</v>
       </c>
-      <c r="Y199" s="80">
-        <f t="shared" si="115"/>
+      <c r="Y200" s="80">
+        <f t="shared" si="120"/>
         <v>8.436030999872951E-2</v>
       </c>
-      <c r="Z199" s="80">
-        <f t="shared" si="115"/>
+      <c r="Z200" s="80">
+        <f t="shared" si="120"/>
         <v>-4.0070298769771528E-2</v>
       </c>
-      <c r="AA199" s="80">
-        <f t="shared" si="115"/>
+      <c r="AA200" s="80">
+        <f t="shared" si="120"/>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="AC199" s="49"/>
-    </row>
-    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B200" s="218" t="s">
+      <c r="AC200" s="49"/>
+    </row>
+    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B201" s="218" t="s">
         <v>363</v>
       </c>
-      <c r="M200" s="80">
-        <f t="shared" si="114"/>
+      <c r="M201" s="80">
+        <f t="shared" si="119"/>
         <v>1</v>
       </c>
-      <c r="N200" s="80">
-        <f t="shared" si="114"/>
+      <c r="N201" s="80">
+        <f t="shared" si="119"/>
         <v>-8.4923946253162061E-2</v>
       </c>
-      <c r="O200" s="80">
-        <f t="shared" si="114"/>
+      <c r="O201" s="80">
+        <f t="shared" si="119"/>
         <v>-0.23547784878293962</v>
       </c>
-      <c r="P200" s="80">
-        <f t="shared" si="114"/>
+      <c r="P201" s="80">
+        <f t="shared" si="119"/>
         <v>-0.242779995304062</v>
       </c>
-      <c r="Q200" s="80">
-        <f t="shared" si="114"/>
+      <c r="Q201" s="80">
+        <f t="shared" si="119"/>
         <v>4.9240310077519382E-2</v>
       </c>
-      <c r="T200" s="80">
-        <f t="shared" si="115"/>
+      <c r="T201" s="80">
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
-      <c r="U200" s="80">
-        <f t="shared" si="115"/>
+      <c r="U201" s="80">
+        <f t="shared" si="120"/>
         <v>8.8304862023653091E-2</v>
       </c>
-      <c r="V200" s="80">
-        <f t="shared" si="115"/>
+      <c r="V201" s="80">
+        <f t="shared" si="120"/>
         <v>5.0712388312001935E-2</v>
       </c>
-      <c r="W200" s="80">
-        <f t="shared" si="115"/>
+      <c r="W201" s="80">
+        <f t="shared" si="120"/>
         <v>-5.1712250057458053E-2</v>
       </c>
-      <c r="X200" s="80">
-        <f t="shared" si="115"/>
+      <c r="X201" s="80">
+        <f t="shared" si="120"/>
         <v>-4.5322346097915654E-2</v>
       </c>
-      <c r="Y200" s="80">
-        <f t="shared" si="115"/>
+      <c r="Y201" s="80">
+        <f t="shared" si="120"/>
         <v>4.5189134298045192E-2</v>
       </c>
-      <c r="Z200" s="80">
-        <f t="shared" si="115"/>
+      <c r="Z201" s="80">
+        <f t="shared" si="120"/>
         <v>0.15059509351469516</v>
       </c>
-      <c r="AA200" s="80">
-        <f t="shared" si="115"/>
+      <c r="AA201" s="80">
+        <f t="shared" si="120"/>
         <v>6.6497783407219763E-2</v>
-      </c>
-      <c r="AC200" s="49"/>
-    </row>
-    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B201" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="M201" s="80">
-        <f t="shared" si="114"/>
-        <v>1</v>
-      </c>
-      <c r="N201" s="80">
-        <f t="shared" si="114"/>
-        <v>-0.16628914988814317</v>
-      </c>
-      <c r="O201" s="80">
-        <f t="shared" si="114"/>
-        <v>-0.1521793818236705</v>
-      </c>
-      <c r="P201" s="80">
-        <f t="shared" si="114"/>
-        <v>-2.1403279726227919E-2</v>
-      </c>
-      <c r="Q201" s="80">
-        <f t="shared" si="114"/>
-        <v>-6.5492915041135214E-3</v>
-      </c>
-      <c r="T201" s="80">
-        <f t="shared" si="115"/>
-        <v>1</v>
-      </c>
-      <c r="U201" s="80">
-        <f t="shared" si="115"/>
-        <v>2.9628389688650822E-2</v>
-      </c>
-      <c r="V201" s="80">
-        <f t="shared" si="115"/>
-        <v>6.6493253129572424E-2</v>
-      </c>
-      <c r="W201" s="80">
-        <f t="shared" si="115"/>
-        <v>-0.10403963414634146</v>
-      </c>
-      <c r="X201" s="80">
-        <f t="shared" si="115"/>
-        <v>4.6788600595491277E-3</v>
-      </c>
-      <c r="Y201" s="80">
-        <f t="shared" si="115"/>
-        <v>7.1295512277730733E-2</v>
-      </c>
-      <c r="Z201" s="80">
-        <f t="shared" si="115"/>
-        <v>2.1972810622826432E-2</v>
-      </c>
-      <c r="AA201" s="80">
-        <f t="shared" si="115"/>
-        <v>-1.1678267594740912E-2</v>
       </c>
       <c r="AC201" s="49"/>
     </row>
     <row r="202" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B202" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M202" s="80">
-        <f t="shared" si="114"/>
+        <f t="shared" si="119"/>
         <v>1</v>
       </c>
       <c r="N202" s="80">
-        <f t="shared" si="114"/>
-        <v>0.35158501440922191</v>
+        <f t="shared" si="119"/>
+        <v>-0.16628914988814317</v>
       </c>
       <c r="O202" s="80">
-        <f t="shared" si="114"/>
-        <v>1.0298507462686568</v>
+        <f t="shared" si="119"/>
+        <v>-0.1521793818236705</v>
       </c>
       <c r="P202" s="80">
-        <f t="shared" si="114"/>
-        <v>17.190126050420169</v>
+        <f t="shared" si="119"/>
+        <v>-2.1403279726227919E-2</v>
       </c>
       <c r="Q202" s="80">
-        <f t="shared" si="114"/>
-        <v>2.9393081942599757E-2</v>
+        <f t="shared" si="119"/>
+        <v>-6.5492915041135214E-3</v>
       </c>
       <c r="T202" s="80">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
       <c r="U202" s="80">
-        <f t="shared" si="115"/>
-        <v>1.3311536665109761E-2</v>
+        <f t="shared" si="120"/>
+        <v>2.9628389688650822E-2</v>
       </c>
       <c r="V202" s="80">
-        <f t="shared" si="115"/>
-        <v>2.3046784973496196E-4</v>
+        <f t="shared" si="120"/>
+        <v>6.6493253129572424E-2</v>
       </c>
       <c r="W202" s="80">
-        <f t="shared" si="115"/>
-        <v>7.5345622119815672E-2</v>
+        <f t="shared" si="120"/>
+        <v>-0.10403963414634146</v>
       </c>
       <c r="X202" s="80">
-        <f t="shared" si="115"/>
-        <v>-5.3567602314120423E-2</v>
+        <f t="shared" si="120"/>
+        <v>4.6788600595491277E-3</v>
       </c>
       <c r="Y202" s="80">
-        <f t="shared" si="115"/>
-        <v>-4.1204437400950873E-2</v>
+        <f t="shared" si="120"/>
+        <v>7.1295512277730733E-2</v>
       </c>
       <c r="Z202" s="80">
-        <f t="shared" si="115"/>
-        <v>6.4226682408500588E-2</v>
+        <f t="shared" si="120"/>
+        <v>2.1972810622826432E-2</v>
       </c>
       <c r="AA202" s="80">
-        <f t="shared" si="115"/>
-        <v>0.2027956512092301</v>
+        <f t="shared" si="120"/>
+        <v>-1.1678267594740912E-2</v>
       </c>
       <c r="AC202" s="49"/>
     </row>
     <row r="203" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B203" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="M203" s="80">
+        <f t="shared" si="119"/>
+        <v>1</v>
+      </c>
+      <c r="N203" s="80">
+        <f t="shared" si="119"/>
+        <v>0.35158501440922191</v>
+      </c>
+      <c r="O203" s="80">
+        <f t="shared" si="119"/>
+        <v>1.0298507462686568</v>
+      </c>
+      <c r="P203" s="80">
+        <f t="shared" si="119"/>
+        <v>17.190126050420169</v>
+      </c>
+      <c r="Q203" s="80">
+        <f t="shared" si="119"/>
+        <v>2.9393081942599757E-2</v>
+      </c>
+      <c r="T203" s="80">
+        <f t="shared" si="120"/>
+        <v>1</v>
+      </c>
+      <c r="U203" s="80">
+        <f t="shared" si="120"/>
+        <v>1.3311536665109761E-2</v>
+      </c>
+      <c r="V203" s="80">
+        <f t="shared" si="120"/>
+        <v>2.3046784973496196E-4</v>
+      </c>
+      <c r="W203" s="80">
+        <f t="shared" si="120"/>
+        <v>7.5345622119815672E-2</v>
+      </c>
+      <c r="X203" s="80">
+        <f t="shared" si="120"/>
+        <v>-5.3567602314120423E-2</v>
+      </c>
+      <c r="Y203" s="80">
+        <f t="shared" si="120"/>
+        <v>-4.1204437400950873E-2</v>
+      </c>
+      <c r="Z203" s="80">
+        <f t="shared" si="120"/>
+        <v>6.4226682408500588E-2</v>
+      </c>
+      <c r="AA203" s="80">
+        <f t="shared" si="120"/>
+        <v>0.2027956512092301</v>
+      </c>
+      <c r="AC203" s="49"/>
+    </row>
+    <row r="204" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B204" s="20" t="s">
         <v>366</v>
       </c>
-      <c r="M203" s="80">
-        <f t="shared" si="114"/>
+      <c r="M204" s="80">
+        <f t="shared" si="119"/>
         <v>1</v>
       </c>
-      <c r="N203" s="80">
-        <f t="shared" si="114"/>
+      <c r="N204" s="80">
+        <f t="shared" si="119"/>
         <v>-0.58669833729216148</v>
       </c>
-      <c r="O203" s="80">
-        <f t="shared" si="114"/>
+      <c r="O204" s="80">
+        <f t="shared" si="119"/>
         <v>-7.9445571331981074E-2</v>
       </c>
-      <c r="P203" s="80">
-        <f t="shared" si="114"/>
+      <c r="P204" s="80">
+        <f t="shared" si="119"/>
         <v>0.32243848696290855</v>
       </c>
-      <c r="Q203" s="80">
-        <f t="shared" si="114"/>
+      <c r="Q204" s="80">
+        <f t="shared" si="119"/>
         <v>-1.0552624271035824E-2</v>
       </c>
-      <c r="T203" s="80">
-        <f t="shared" si="115"/>
+      <c r="T204" s="80">
+        <f t="shared" si="120"/>
         <v>1</v>
       </c>
-      <c r="U203" s="80">
-        <f t="shared" si="115"/>
+      <c r="U204" s="80">
+        <f t="shared" si="120"/>
         <v>9.4211123723041995E-2</v>
       </c>
-      <c r="V203" s="80">
-        <f t="shared" si="115"/>
+      <c r="V204" s="80">
+        <f t="shared" si="120"/>
         <v>0.1545643153526971</v>
       </c>
-      <c r="W203" s="80">
-        <f t="shared" si="115"/>
+      <c r="W204" s="80">
+        <f t="shared" si="120"/>
         <v>-0.1527403414195867</v>
       </c>
-      <c r="X203" s="80">
-        <f t="shared" si="115"/>
+      <c r="X204" s="80">
+        <f t="shared" si="120"/>
         <v>0.11664899257688228</v>
       </c>
-      <c r="Y203" s="80">
-        <f t="shared" si="115"/>
+      <c r="Y204" s="80">
+        <f t="shared" si="120"/>
         <v>-5.6980056980056981E-2</v>
       </c>
-      <c r="Z203" s="80">
-        <f t="shared" si="115"/>
+      <c r="Z204" s="80">
+        <f t="shared" si="120"/>
         <v>-0.42195367573011078</v>
       </c>
-      <c r="AA203" s="80">
-        <f t="shared" si="115"/>
+      <c r="AA204" s="80">
+        <f t="shared" si="120"/>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="AC203" s="49"/>
-    </row>
-    <row r="205" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B205" s="1"/>
-    </row>
-    <row r="206" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B206" s="14" t="s">
+      <c r="AC204" s="49"/>
+    </row>
+    <row r="206" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B206" s="1"/>
+    </row>
+    <row r="207" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B207" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C206" s="172"/>
-      <c r="D206" s="172"/>
-      <c r="E206" s="172"/>
-      <c r="F206" s="172"/>
-      <c r="G206" s="172"/>
-      <c r="H206" s="172"/>
-      <c r="I206" s="172"/>
-      <c r="J206" s="172"/>
-      <c r="K206" s="172"/>
-      <c r="L206" s="172"/>
-      <c r="M206" s="172"/>
-      <c r="N206" s="172"/>
-      <c r="O206" s="172"/>
-      <c r="P206" s="172"/>
-      <c r="Q206" s="172"/>
-      <c r="T206" s="172"/>
-      <c r="U206" s="172"/>
-      <c r="V206" s="172"/>
-      <c r="W206" s="172"/>
-      <c r="X206" s="172"/>
-      <c r="Y206" s="172"/>
-      <c r="Z206" s="172"/>
-      <c r="AA206" s="172"/>
-      <c r="AC206" s="172"/>
-    </row>
-    <row r="207" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B207" s="20" t="s">
+      <c r="C207" s="172"/>
+      <c r="D207" s="172"/>
+      <c r="E207" s="172"/>
+      <c r="F207" s="172"/>
+      <c r="G207" s="172"/>
+      <c r="H207" s="172"/>
+      <c r="I207" s="172"/>
+      <c r="J207" s="172"/>
+      <c r="K207" s="172"/>
+      <c r="L207" s="172"/>
+      <c r="M207" s="172"/>
+      <c r="N207" s="172"/>
+      <c r="O207" s="172"/>
+      <c r="P207" s="172"/>
+      <c r="Q207" s="172"/>
+      <c r="T207" s="172"/>
+      <c r="U207" s="172"/>
+      <c r="V207" s="172"/>
+      <c r="W207" s="172"/>
+      <c r="X207" s="172"/>
+      <c r="Y207" s="172"/>
+      <c r="Z207" s="172"/>
+      <c r="AA207" s="172"/>
+      <c r="AC207" s="172"/>
+    </row>
+    <row r="208" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B208" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="C207" s="80"/>
-      <c r="D207" s="80"/>
-      <c r="E207" s="80"/>
-      <c r="F207" s="80"/>
-      <c r="G207" s="80"/>
-      <c r="H207" s="80"/>
-      <c r="I207" s="80"/>
-      <c r="J207" s="80"/>
-      <c r="K207" s="80"/>
-      <c r="L207" s="80"/>
-      <c r="M207" s="80">
+      <c r="C208" s="80"/>
+      <c r="D208" s="80"/>
+      <c r="E208" s="80"/>
+      <c r="F208" s="80"/>
+      <c r="G208" s="80"/>
+      <c r="H208" s="80"/>
+      <c r="I208" s="80"/>
+      <c r="J208" s="80"/>
+      <c r="K208" s="80"/>
+      <c r="L208" s="80"/>
+      <c r="M208" s="80">
         <f>IF(L63=0,
 IF(M63=0,0,IF(M63&gt;0,1,-1)),
 (M63-L63)/L63
 )</f>
         <v>-1</v>
       </c>
-      <c r="N207" s="80">
+      <c r="N208" s="80">
         <f>IF(M63=0,
 IF(N63=0,0,IF(N63&gt;0,1,-1)),
 (N63-M63)/M63
 )</f>
         <v>6.2544294826364283E-2</v>
       </c>
-      <c r="O207" s="80">
+      <c r="O208" s="80">
         <f>IF(N63=0,
 IF(O63=0,0,IF(O63&gt;0,1,-1)),
 (O63-N63)/N63
 )</f>
         <v>-0.48507587126896784</v>
       </c>
-      <c r="P207" s="80">
+      <c r="P208" s="80">
         <f>IF(O63=0,
 IF(P63=0,0,IF(P63&gt;0,1,-1)),
 (P63-O63)/O63
 )</f>
         <v>-0.48218911917098445</v>
       </c>
-      <c r="Q207" s="80">
+      <c r="Q208" s="80">
         <f>IF(P63=0,
 IF(Q63=0,0,IF(Q63&gt;0,1,-1)),
 (Q63-P63)/P63
 )</f>
         <v>-1</v>
       </c>
-      <c r="T207" s="49"/>
-      <c r="U207" s="49"/>
-      <c r="V207" s="49"/>
-      <c r="W207" s="49"/>
-      <c r="X207" s="49"/>
-      <c r="Y207" s="49"/>
-      <c r="Z207" s="49"/>
-      <c r="AA207" s="49"/>
-      <c r="AC207" s="49"/>
+      <c r="T208" s="49"/>
+      <c r="U208" s="49"/>
+      <c r="V208" s="49"/>
+      <c r="W208" s="49"/>
+      <c r="X208" s="49"/>
+      <c r="Y208" s="49"/>
+      <c r="Z208" s="49"/>
+      <c r="AA208" s="49"/>
+      <c r="AC208" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="AC23 AC80 AC65 AC52:AC56 AC58:AC61 AC5:AC19 AC62:AC64 AC105:AC115 AC141" formulaRange="1"/>
+    <ignoredError sqref="AC23 AC80 AC65 AC52:AC56 AC58:AC61 AC5:AC19 AC62:AC64 AC105:AC115 AC142" formulaRange="1"/>
     <ignoredError sqref="AC20:AC21 AC24:AC25" formula="1" formulaRange="1"/>
-    <ignoredError sqref="M136:Q136 AC136" formula="1"/>
+    <ignoredError sqref="M137:Q137 AC137" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -31683,15 +31733,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="226" t="s">
+      <c r="B4" s="228" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="226"/>
-      <c r="E4" s="226" t="s">
+      <c r="C4" s="228"/>
+      <c r="E4" s="228" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
+      <c r="F4" s="228"/>
+      <c r="G4" s="228"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -31699,7 +31749,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>112.08499999999999</v>
+        <v>111.285</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -31714,8 +31764,8 @@
         <v>242</v>
       </c>
       <c r="C6" s="175">
-        <f ca="1">Statement!AC170</f>
-        <v>563339.21</v>
+        <f ca="1">Statement!AC171</f>
+        <v>559318.41</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -31734,8 +31784,8 @@
         <v>184</v>
       </c>
       <c r="C7" s="175">
-        <f ca="1">Statement!AC171</f>
-        <v>589176.21</v>
+        <f ca="1">Statement!AC172</f>
+        <v>585155.41</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -31754,8 +31804,8 @@
         <v>240</v>
       </c>
       <c r="C8" s="176">
-        <f ca="1">Statement!AC167</f>
-        <v>-180.78225806451613</v>
+        <f ca="1">Statement!AC168</f>
+        <v>-179.49193548387098</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>246</v>
@@ -31774,8 +31824,8 @@
         <v>197</v>
       </c>
       <c r="C9" s="176">
-        <f ca="1">Statement!AC168</f>
-        <v>9.8100174376429887</v>
+        <f ca="1">Statement!AC169</f>
+        <v>9.7399990234919915</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>247</v>
@@ -31794,8 +31844,8 @@
         <v>241</v>
       </c>
       <c r="C10" s="176">
-        <f ca="1">Statement!AC169</f>
-        <v>5.0571773165520577</v>
+        <f ca="1">Statement!AC170</f>
+        <v>5.0210820151893278</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -31814,8 +31864,8 @@
         <v>263</v>
       </c>
       <c r="C11" s="176">
-        <f ca="1">Statement!AC172</f>
-        <v>10.958767367892417</v>
+        <f ca="1">Statement!AC173</f>
+        <v>10.883979874634973</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -31823,19 +31873,19 @@
         <v>200</v>
       </c>
       <c r="C12" s="176">
-        <f ca="1">Statement!AC173</f>
-        <v>-116.69166369578133</v>
+        <f ca="1">Statement!AC174</f>
+        <v>-115.89530798177857</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="226" t="s">
+      <c r="B15" s="228" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="226"/>
-      <c r="E15" s="226" t="s">
+      <c r="C15" s="228"/>
+      <c r="E15" s="228" t="s">
         <v>249</v>
       </c>
-      <c r="F15" s="226"/>
+      <c r="F15" s="228"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -31886,21 +31936,21 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="226" t="s">
+      <c r="B21" s="228" t="s">
         <v>248</v>
       </c>
-      <c r="C21" s="226"/>
-      <c r="E21" s="226" t="s">
+      <c r="C21" s="228"/>
+      <c r="E21" s="228" t="s">
         <v>252</v>
       </c>
-      <c r="F21" s="226"/>
+      <c r="F21" s="228"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
         <v>95</v>
       </c>
       <c r="C22" s="177">
-        <f>Statement!AC133</f>
+        <f>Statement!AC134</f>
         <v>-6.2645313691572266E-2</v>
       </c>
       <c r="E22" s="20" t="s">
@@ -31916,7 +31966,7 @@
         <v>96</v>
       </c>
       <c r="C23" s="176">
-        <f>Statement!AC134</f>
+        <f>Statement!AC135</f>
         <v>0.26183449243176904</v>
       </c>
       <c r="E23" s="20" t="s">
@@ -31932,14 +31982,14 @@
         <v>97</v>
       </c>
       <c r="C24" s="178">
-        <f>Statement!AC135</f>
+        <f>Statement!AC136</f>
         <v>-1.6402703913661776E-2</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>100</v>
       </c>
       <c r="F24" s="177">
-        <f>Statement!AC157</f>
+        <f>Statement!AC158</f>
         <v>-3.6791978488825414E-2</v>
       </c>
     </row>
@@ -31948,7 +31998,7 @@
         <v>98</v>
       </c>
       <c r="C25" s="176">
-        <f>Statement!AC136</f>
+        <f>Statement!AC137</f>
         <v>1.8432949710038242</v>
       </c>
     </row>
@@ -31957,33 +32007,33 @@
         <v>99</v>
       </c>
       <c r="C26" s="178">
-        <f>Statement!AC137</f>
+        <f>Statement!AC138</f>
         <v>-3.0235021634917498E-2</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="226" t="s">
+      <c r="B29" s="228" t="s">
         <v>253</v>
       </c>
-      <c r="C29" s="226"/>
-      <c r="E29" s="226" t="s">
+      <c r="C29" s="228"/>
+      <c r="E29" s="228" t="s">
         <v>259</v>
       </c>
-      <c r="F29" s="226"/>
+      <c r="F29" s="228"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
         <v>134</v>
       </c>
       <c r="C30" s="176">
-        <f>Statement!AC158</f>
+        <f>Statement!AC159</f>
         <v>27.604300355262914</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>260</v>
       </c>
       <c r="F30" s="182">
-        <f>Statement!AC162</f>
+        <f>Statement!AC163</f>
         <v>0.40424978005996731</v>
       </c>
     </row>
@@ -31992,14 +32042,14 @@
         <v>135</v>
       </c>
       <c r="C31" s="176">
-        <f>Statement!AC159</f>
+        <f>Statement!AC160</f>
         <v>130.6568144499179</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>261</v>
       </c>
       <c r="F31" s="182">
-        <f>Statement!AC163</f>
+        <f>Statement!AC164</f>
         <v>0.10989819918487531</v>
       </c>
     </row>
@@ -32008,14 +32058,14 @@
         <v>136</v>
       </c>
       <c r="C32" s="176">
-        <f>Statement!AC160</f>
+        <f>Statement!AC161</f>
         <v>75.275401146544525</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>256</v>
       </c>
       <c r="F32" s="182">
-        <f>Statement!AC165</f>
+        <f>Statement!AC166</f>
         <v>2.3119583410823878</v>
       </c>
     </row>
@@ -32024,14 +32074,14 @@
         <v>137</v>
       </c>
       <c r="C33" s="176">
-        <f>Statement!AC161</f>
+        <f>Statement!AC162</f>
         <v>82.9857136586363</v>
       </c>
       <c r="E33" s="20" t="s">
         <v>255</v>
       </c>
       <c r="F33" s="182">
-        <f>Statement!AC164</f>
+        <f>Statement!AC165</f>
         <v>1.3708387576715642</v>
       </c>
     </row>
@@ -32040,33 +32090,33 @@
         <v>262</v>
       </c>
       <c r="F34" s="184" t="str">
-        <f>Statement!AC166</f>
+        <f>Statement!AC167</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="226" t="s">
+      <c r="B37" s="228" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="226"/>
-      <c r="E37" s="226" t="s">
+      <c r="C37" s="228"/>
+      <c r="E37" s="228" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="226"/>
+      <c r="F37" s="228"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
         <v>269</v>
       </c>
       <c r="C38" s="177">
-        <f ca="1">Statement!AC179</f>
-        <v>-5.5315162599812642E-3</v>
+        <f ca="1">Statement!AC180</f>
+        <v>-5.5712809453205732E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
       </c>
       <c r="F38" s="177">
-        <f>Statement!AC184</f>
+        <f>Statement!AC185</f>
         <v>0</v>
       </c>
     </row>
@@ -32075,14 +32125,14 @@
         <v>273</v>
       </c>
       <c r="C39" s="217">
-        <f ca="1">Statement!AC178</f>
-        <v>-9.7454604659952572E-3</v>
+        <f ca="1">Statement!AC179</f>
+        <v>-9.8155181410889015E-3</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
       </c>
       <c r="F39" s="177">
-        <f>Statement!AC185</f>
+        <f>Statement!AC186</f>
         <v>0</v>
       </c>
     </row>
@@ -32091,14 +32141,14 @@
         <v>270</v>
       </c>
       <c r="C40" s="177">
-        <f ca="1">Statement!AC180</f>
+        <f ca="1">Statement!AC181</f>
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
       </c>
       <c r="F40" s="177">
-        <f>Statement!AC186</f>
+        <f>Statement!AC187</f>
         <v>0</v>
       </c>
     </row>
@@ -32107,7 +32157,7 @@
         <v>296</v>
       </c>
       <c r="C41" s="177">
-        <f ca="1">Statement!AC181</f>
+        <f ca="1">Statement!AC182</f>
         <v>0</v>
       </c>
     </row>
@@ -32116,33 +32166,33 @@
         <v>298</v>
       </c>
       <c r="C42" s="177">
-        <f ca="1">Statement!AC182</f>
+        <f ca="1">Statement!AC183</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="226" t="s">
+      <c r="B45" s="228" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="226"/>
-      <c r="E45" s="226" t="s">
+      <c r="C45" s="228"/>
+      <c r="E45" s="228" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="226"/>
+      <c r="F45" s="228"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
         <v>281</v>
       </c>
       <c r="C46" s="177">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>5.9689614007162755E-4</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>282</v>
       </c>
       <c r="F46" s="176">
-        <f>Statement!AC188</f>
+        <f>Statement!AC189</f>
         <v>6.5238758456028654</v>
       </c>
     </row>
@@ -32151,7 +32201,7 @@
         <v>290</v>
       </c>
       <c r="F47" s="176">
-        <f>Statement!AC191</f>
+        <f>Statement!AC192</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
@@ -32160,33 +32210,33 @@
         <v>295</v>
       </c>
       <c r="F48" s="177">
-        <f ca="1">Statement!AC192</f>
-        <v>-2.1731134248581776E-2</v>
+        <f ca="1">Statement!AC193</f>
+        <v>-2.1887353931368002E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="226" t="s">
+      <c r="B51" s="228" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="226"/>
-      <c r="E51" s="226" t="s">
+      <c r="C51" s="228"/>
+      <c r="E51" s="228" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="226"/>
+      <c r="F51" s="228"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
         <v>284</v>
       </c>
       <c r="C52" s="177">
-        <f>Statement!AC189</f>
+        <f>Statement!AC190</f>
         <v>0.2375751503006012</v>
       </c>
       <c r="E52" s="20" t="s">
         <v>308</v>
       </c>
       <c r="F52" s="177">
-        <f>Statement!AC193</f>
+        <f>Statement!AC194</f>
         <v>0.24364339787586259</v>
       </c>
     </row>
@@ -32195,14 +32245,14 @@
         <v>285</v>
       </c>
       <c r="C53" s="177">
-        <f>Statement!AC190</f>
+        <f>Statement!AC191</f>
         <v>4.4100961627885349E-2</v>
       </c>
       <c r="E53" s="20" t="s">
         <v>305</v>
       </c>
       <c r="F53" s="177">
-        <f>Statement!AC194</f>
+        <f>Statement!AC195</f>
         <v>1.3125250501002004</v>
       </c>
     </row>
@@ -32211,7 +32261,7 @@
         <v>306</v>
       </c>
       <c r="F54" s="177">
-        <f>Statement!AC195</f>
+        <f>Statement!AC196</f>
         <v>1.0765121630506247</v>
       </c>
     </row>
@@ -32340,7 +32390,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC129</f>
-        <v>112.08499999999999</v>
+        <v>111.285</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32348,28 +32398,28 @@
         <v>242</v>
       </c>
       <c r="C7" s="175">
-        <f>Statement!M170</f>
+        <f>Statement!M171</f>
         <v>210524.93000000002</v>
       </c>
       <c r="D7" s="175">
-        <f>Statement!N170</f>
+        <f>Statement!N171</f>
         <v>109737.36</v>
       </c>
       <c r="E7" s="175">
-        <f>Statement!O170</f>
+        <f>Statement!O171</f>
         <v>213562.5</v>
       </c>
       <c r="F7" s="175">
-        <f>Statement!P170</f>
+        <f>Statement!P171</f>
         <v>87899</v>
       </c>
       <c r="G7" s="175">
-        <f>Statement!Q170</f>
+        <f>Statement!Q171</f>
         <v>180819</v>
       </c>
       <c r="I7" s="175">
-        <f ca="1">Statement!AC170</f>
-        <v>563339.21</v>
+        <f ca="1">Statement!AC171</f>
+        <v>559318.41</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32377,28 +32427,28 @@
         <v>184</v>
       </c>
       <c r="C8" s="175">
-        <f>Statement!M171</f>
+        <f>Statement!M172</f>
         <v>220212.93000000002</v>
       </c>
       <c r="D8" s="175">
-        <f>Statement!N171</f>
+        <f>Statement!N172</f>
         <v>125313.35999999999</v>
       </c>
       <c r="E8" s="175">
-        <f>Statement!O171</f>
+        <f>Statement!O172</f>
         <v>242169.5</v>
       </c>
       <c r="F8" s="175">
-        <f>Statement!P171</f>
+        <f>Statement!P172</f>
         <v>121610</v>
       </c>
       <c r="G8" s="175">
-        <f>Statement!Q171</f>
+        <f>Statement!Q172</f>
         <v>202067</v>
       </c>
       <c r="I8" s="175">
-        <f ca="1">Statement!AC171</f>
-        <v>589176.21</v>
+        <f ca="1">Statement!AC172</f>
+        <v>585155.41</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -32406,28 +32456,28 @@
         <v>240</v>
       </c>
       <c r="C9" s="176">
-        <f>Statement!M167</f>
+        <f>Statement!M168</f>
         <v>10.557613168724279</v>
       </c>
       <c r="D9" s="176">
-        <f>Statement!N167</f>
+        <f>Statement!N168</f>
         <v>13.623711340206185</v>
       </c>
       <c r="E9" s="176">
-        <f>Statement!O167</f>
+        <f>Statement!O168</f>
         <v>125.625</v>
       </c>
       <c r="F9" s="176">
-        <f>Statement!P167</f>
+        <f>Statement!P168</f>
         <v>-4.634703196347032</v>
       </c>
       <c r="G9" s="176">
-        <f>Statement!Q167</f>
+        <f>Statement!Q168</f>
         <v>-603.33333333333337</v>
       </c>
       <c r="I9" s="176">
-        <f ca="1">Statement!AC167</f>
-        <v>-180.78225806451613</v>
+        <f ca="1">Statement!AC168</f>
+        <v>-179.49193548387098</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -32435,28 +32485,28 @@
         <v>197</v>
       </c>
       <c r="C10" s="176">
-        <f>Statement!M168</f>
+        <f>Statement!M169</f>
         <v>2.6556223425794698</v>
       </c>
       <c r="D10" s="176">
-        <f>Statement!N168</f>
+        <f>Statement!N169</f>
         <v>1.7282153392330384</v>
       </c>
       <c r="E10" s="176">
-        <f>Statement!O168</f>
+        <f>Statement!O169</f>
         <v>3.9030205797742865</v>
       </c>
       <c r="F10" s="176">
-        <f>Statement!P168</f>
+        <f>Statement!P169</f>
         <v>1.6362027080469295</v>
       </c>
       <c r="G10" s="176">
-        <f>Statement!Q168</f>
+        <f>Statement!Q169</f>
         <v>3.102681020944885</v>
       </c>
       <c r="I10" s="176">
-        <f ca="1">Statement!AC168</f>
-        <v>9.8100174376429887</v>
+        <f ca="1">Statement!AC169</f>
+        <v>9.7399990234919915</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -32464,28 +32514,28 @@
         <v>241</v>
       </c>
       <c r="C11" s="176">
-        <f>Statement!M169</f>
+        <f>Statement!M170</f>
         <v>2.190293843234687</v>
       </c>
       <c r="D11" s="176">
-        <f>Statement!N169</f>
+        <f>Statement!N170</f>
         <v>1.0780681896611222</v>
       </c>
       <c r="E11" s="176">
-        <f>Statement!O169</f>
+        <f>Statement!O170</f>
         <v>2.0120939482905578</v>
       </c>
       <c r="F11" s="176">
-        <f>Statement!P169</f>
+        <f>Statement!P170</f>
         <v>0.88545381283368585</v>
       </c>
       <c r="G11" s="176">
-        <f>Statement!Q169</f>
+        <f>Statement!Q170</f>
         <v>1.5822315170500785</v>
       </c>
       <c r="I11" s="176">
-        <f ca="1">Statement!AC169</f>
-        <v>5.0571773165520577</v>
+        <f ca="1">Statement!AC170</f>
+        <v>5.0210820151893278</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -32493,28 +32543,28 @@
         <v>263</v>
       </c>
       <c r="C12" s="176">
-        <f>Statement!M172</f>
+        <f>Statement!M173</f>
         <v>2.7866588631301887</v>
       </c>
       <c r="D12" s="176">
-        <f>Statement!N172</f>
+        <f>Statement!N173</f>
         <v>1.9873974688362355</v>
       </c>
       <c r="E12" s="176">
-        <f>Statement!O172</f>
+        <f>Statement!O173</f>
         <v>4.4657649184922921</v>
       </c>
       <c r="F12" s="176">
-        <f>Statement!P172</f>
+        <f>Statement!P173</f>
         <v>2.2901640270428052</v>
       </c>
       <c r="G12" s="176">
-        <f>Statement!Q172</f>
+        <f>Statement!Q173</f>
         <v>3.823188844531058</v>
       </c>
       <c r="I12" s="176">
-        <f ca="1">Statement!AC172</f>
-        <v>10.958767367892417</v>
+        <f ca="1">Statement!AC173</f>
+        <v>10.883979874634973</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -32522,28 +32572,28 @@
         <v>200</v>
       </c>
       <c r="C13" s="176">
-        <f>Statement!M173</f>
+        <f>Statement!M174</f>
         <v>11.318509971217106</v>
       </c>
       <c r="D13" s="176">
-        <f>Statement!N173</f>
+        <f>Statement!N174</f>
         <v>53.690385604113104</v>
       </c>
       <c r="E13" s="176">
-        <f>Statement!O173</f>
+        <f>Statement!O174</f>
         <v>2603.9731182795699</v>
       </c>
       <c r="F13" s="176">
-        <f>Statement!P173</f>
+        <f>Statement!P174</f>
         <v>-10.413598218873094</v>
       </c>
       <c r="G13" s="176">
-        <f>Statement!Q173</f>
+        <f>Statement!Q174</f>
         <v>-91.267841011743457</v>
       </c>
       <c r="I13" s="176">
-        <f ca="1">Statement!AC173</f>
-        <v>-116.69166369578133</v>
+        <f ca="1">Statement!AC174</f>
+        <v>-115.89530798177857</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -32758,27 +32808,27 @@
         <v>95</v>
       </c>
       <c r="C26" s="177">
-        <f>Statement!M133</f>
+        <f>Statement!M134</f>
         <v>0.25141729094958493</v>
       </c>
       <c r="D26" s="177">
-        <f>Statement!N133</f>
+        <f>Statement!N134</f>
         <v>0.12714498683667966</v>
       </c>
       <c r="E26" s="177">
-        <f>Statement!O133</f>
+        <f>Statement!O134</f>
         <v>3.088810208748248E-2</v>
       </c>
       <c r="F26" s="177">
-        <f>Statement!P133</f>
+        <f>Statement!P134</f>
         <v>-0.3621965688028474</v>
       </c>
       <c r="G26" s="177">
-        <f>Statement!Q133</f>
+        <f>Statement!Q134</f>
         <v>4.9193044860272833E-4</v>
       </c>
       <c r="I26" s="177">
-        <f>Statement!AC133</f>
+        <f>Statement!AC134</f>
         <v>-6.2645313691572266E-2</v>
       </c>
     </row>
@@ -32787,27 +32837,27 @@
         <v>96</v>
       </c>
       <c r="C27" s="216">
-        <f>Statement!M134</f>
+        <f>Statement!M135</f>
         <v>0.46924693894516822</v>
       </c>
       <c r="D27" s="216">
-        <f>Statement!N134</f>
+        <f>Statement!N135</f>
         <v>0.34625459218134791</v>
       </c>
       <c r="E27" s="216">
-        <f>Statement!O134</f>
+        <f>Statement!O135</f>
         <v>0.2830685068799198</v>
       </c>
       <c r="F27" s="216">
-        <f>Statement!P134</f>
+        <f>Statement!P135</f>
         <v>0.27025472682393059</v>
       </c>
       <c r="G27" s="216">
-        <f>Statement!Q134</f>
+        <f>Statement!Q135</f>
         <v>0.24997989868939455</v>
       </c>
       <c r="I27" s="216">
-        <f>Statement!AC134</f>
+        <f>Statement!AC135</f>
         <v>0.26183449243176904</v>
       </c>
     </row>
@@ -32816,27 +32866,27 @@
         <v>97</v>
       </c>
       <c r="C28" s="178">
-        <f>Statement!M135</f>
+        <f>Statement!M136</f>
         <v>0.11797679417597948</v>
       </c>
       <c r="D28" s="178">
-        <f>Statement!N135</f>
+        <f>Statement!N136</f>
         <v>4.4024535565037361E-2</v>
       </c>
       <c r="E28" s="178">
-        <f>Statement!O135</f>
+        <f>Statement!O136</f>
         <v>8.7434489382581995E-3</v>
       </c>
       <c r="F28" s="178">
-        <f>Statement!P135</f>
+        <f>Statement!P136</f>
         <v>-9.7885334758378503E-2</v>
       </c>
       <c r="G28" s="178">
-        <f>Statement!Q135</f>
+        <f>Statement!Q136</f>
         <v>1.2297272370393844E-4</v>
       </c>
       <c r="I28" s="178">
-        <f>Statement!AC135</f>
+        <f>Statement!AC136</f>
         <v>-1.6402703913661776E-2</v>
       </c>
     </row>
@@ -32845,27 +32895,27 @@
         <v>98</v>
       </c>
       <c r="C29" s="216">
-        <f>Statement!M136</f>
+        <f>Statement!M137</f>
         <v>1.7654286043756748</v>
       </c>
       <c r="D29" s="216">
-        <f>Statement!N136</f>
+        <f>Statement!N137</f>
         <v>1.7954803151159007</v>
       </c>
       <c r="E29" s="216">
-        <f>Statement!O136</f>
+        <f>Statement!O137</f>
         <v>1.8143005966474097</v>
       </c>
       <c r="F29" s="216">
-        <f>Statement!P136</f>
+        <f>Statement!P137</f>
         <v>1.9792988818374131</v>
       </c>
       <c r="G29" s="216">
-        <f>Statement!Q136</f>
+        <f>Statement!Q137</f>
         <v>1.8500800658027143</v>
       </c>
       <c r="I29" s="216">
-        <f>Statement!AC136</f>
+        <f>Statement!AC137</f>
         <v>1.8432949710038242</v>
       </c>
     </row>
@@ -32874,27 +32924,27 @@
         <v>99</v>
       </c>
       <c r="C30" s="178">
-        <f>Statement!M137</f>
+        <f>Statement!M138</f>
         <v>0.20827960709081569</v>
       </c>
       <c r="D30" s="178">
-        <f>Statement!N137</f>
+        <f>Statement!N138</f>
         <v>7.904518698914445E-2</v>
       </c>
       <c r="E30" s="178">
-        <f>Statement!O137</f>
+        <f>Statement!O138</f>
         <v>1.5863244625438012E-2</v>
       </c>
       <c r="F30" s="178">
-        <f>Statement!P137</f>
+        <f>Statement!P138</f>
         <v>-0.19374433363553945</v>
       </c>
       <c r="G30" s="178">
-        <f>Statement!Q137</f>
+        <f>Statement!Q138</f>
         <v>2.2750938476212145E-4</v>
       </c>
       <c r="I30" s="178">
-        <f>Statement!AC137</f>
+        <f>Statement!AC138</f>
         <v>-3.0235021634917498E-2</v>
       </c>
     </row>
@@ -32972,27 +33022,27 @@
         <v>100</v>
       </c>
       <c r="C35" s="177">
-        <f>Statement!M157</f>
+        <f>Statement!M158</f>
         <v>0.16950089956234582</v>
       </c>
       <c r="D35" s="177">
-        <f>Statement!N157</f>
+        <f>Statement!N158</f>
         <v>1.9948888452038051E-2</v>
       </c>
       <c r="E35" s="177">
-        <f>Statement!O157</f>
+        <f>Statement!O158</f>
         <v>6.9301102111075507E-4</v>
       </c>
       <c r="F35" s="177">
-        <f>Statement!P157</f>
+        <f>Statement!P158</f>
         <v>-8.7817056571991486E-2</v>
       </c>
       <c r="G35" s="177">
-        <f>Statement!Q157</f>
+        <f>Statement!Q158</f>
         <v>-1.6335987131905347E-2</v>
       </c>
       <c r="I35" s="177">
-        <f>Statement!AC157</f>
+        <f>Statement!AC158</f>
         <v>-3.6791978488825414E-2</v>
       </c>
     </row>
@@ -33012,27 +33062,27 @@
         <v>134</v>
       </c>
       <c r="C38" s="176">
-        <f>Statement!M158</f>
+        <f>Statement!M159</f>
         <v>43.680464162785988</v>
       </c>
       <c r="D38" s="176">
-        <f>Statement!N158</f>
+        <f>Statement!N159</f>
         <v>23.924651885685286</v>
       </c>
       <c r="E38" s="176">
-        <f>Statement!O158</f>
+        <f>Statement!O159</f>
         <v>22.898318211993807</v>
       </c>
       <c r="F38" s="176">
-        <f>Statement!P158</f>
+        <f>Statement!P159</f>
         <v>23.906706088397584</v>
       </c>
       <c r="G38" s="176">
-        <f>Statement!Q158</f>
+        <f>Statement!Q159</f>
         <v>26.511929313378616</v>
       </c>
       <c r="I38" s="176">
-        <f>Statement!AC158</f>
+        <f>Statement!AC159</f>
         <v>27.604300355262914</v>
       </c>
     </row>
@@ -33041,27 +33091,27 @@
         <v>135</v>
       </c>
       <c r="C39" s="176">
-        <f>Statement!M159</f>
+        <f>Statement!M160</f>
         <v>111.71121020193701</v>
       </c>
       <c r="D39" s="176">
-        <f>Statement!N159</f>
+        <f>Statement!N160</f>
         <v>133.38012600862163</v>
       </c>
       <c r="E39" s="176">
-        <f>Statement!O159</f>
+        <f>Statement!O160</f>
         <v>124.89943721745549</v>
       </c>
       <c r="F39" s="176">
-        <f>Statement!P159</f>
+        <f>Statement!P160</f>
         <v>124.51812283253162</v>
       </c>
       <c r="G39" s="176">
-        <f>Statement!Q159</f>
+        <f>Statement!Q160</f>
         <v>122.99350310342828</v>
       </c>
       <c r="I39" s="176">
-        <f>Statement!AC159</f>
+        <f>Statement!AC160</f>
         <v>130.6568144499179</v>
       </c>
     </row>
@@ -33070,27 +33120,27 @@
         <v>136</v>
       </c>
       <c r="C40" s="176">
-        <f>Statement!M160</f>
+        <f>Statement!M161</f>
         <v>59.577238774177054</v>
       </c>
       <c r="D40" s="176">
-        <f>Statement!N160</f>
+        <f>Statement!N161</f>
         <v>96.777246601083235</v>
       </c>
       <c r="E40" s="176">
-        <f>Statement!O160</f>
+        <f>Statement!O161</f>
         <v>96.219823476950523</v>
       </c>
       <c r="F40" s="176">
-        <f>Statement!P160</f>
+        <f>Statement!P161</f>
         <v>128.17261438639667</v>
       </c>
       <c r="G40" s="176">
-        <f>Statement!Q160</f>
+        <f>Statement!Q161</f>
         <v>104.6154069261558</v>
       </c>
       <c r="I40" s="176">
-        <f>Statement!AC160</f>
+        <f>Statement!AC161</f>
         <v>75.275401146544525</v>
       </c>
     </row>
@@ -33099,27 +33149,27 @@
         <v>137</v>
       </c>
       <c r="C41" s="176">
-        <f>Statement!M161</f>
+        <f>Statement!M162</f>
         <v>95.814435590545941</v>
       </c>
       <c r="D41" s="176">
-        <f>Statement!N161</f>
+        <f>Statement!N162</f>
         <v>60.527531293223674</v>
       </c>
       <c r="E41" s="176">
-        <f>Statement!O161</f>
+        <f>Statement!O162</f>
         <v>51.577931952498773</v>
       </c>
       <c r="F41" s="176">
-        <f>Statement!P161</f>
+        <f>Statement!P162</f>
         <v>20.252214534532527</v>
       </c>
       <c r="G41" s="176">
-        <f>Statement!Q161</f>
+        <f>Statement!Q162</f>
         <v>44.890025490651112</v>
       </c>
       <c r="I41" s="176">
-        <f>Statement!AC161</f>
+        <f>Statement!AC162</f>
         <v>82.9857136586363</v>
       </c>
     </row>
@@ -33139,27 +33189,27 @@
         <v>260</v>
       </c>
       <c r="C44" s="182">
-        <f>Statement!M162</f>
+        <f>Statement!M163</f>
         <v>0.39941923242234595</v>
       </c>
       <c r="D44" s="182">
-        <f>Statement!N162</f>
+        <f>Statement!N163</f>
         <v>0.41461009830117429</v>
       </c>
       <c r="E44" s="182">
-        <f>Statement!O162</f>
+        <f>Statement!O163</f>
         <v>0.46657827445780853</v>
       </c>
       <c r="F44" s="182">
-        <f>Statement!P162</f>
+        <f>Statement!P163</f>
         <v>0.50378764984386015</v>
       </c>
       <c r="G44" s="182">
-        <f>Statement!Q162</f>
+        <f>Statement!Q163</f>
         <v>0.40763556496705489</v>
       </c>
       <c r="I44" s="182">
-        <f>Statement!AC162</f>
+        <f>Statement!AC163</f>
         <v>0.40424978005996731</v>
       </c>
     </row>
@@ -33168,27 +33218,27 @@
         <v>261</v>
       </c>
       <c r="C45" s="182">
-        <f>Statement!M163</f>
+        <f>Statement!M164</f>
         <v>0.10156094390456123</v>
       </c>
       <c r="D45" s="182">
-        <f>Statement!N163</f>
+        <f>Statement!N164</f>
         <v>0.13520601835875493</v>
       </c>
       <c r="E45" s="182">
-        <f>Statement!O163</f>
+        <f>Statement!O164</f>
         <v>0.22949142911260537</v>
       </c>
       <c r="F45" s="182">
-        <f>Statement!P163</f>
+        <f>Statement!P164</f>
         <v>0.28154528054800038</v>
       </c>
       <c r="G45" s="182">
-        <f>Statement!Q163</f>
+        <f>Statement!Q164</f>
         <v>8.0232059572457368E-2</v>
       </c>
       <c r="I45" s="182">
-        <f>Statement!AC163</f>
+        <f>Statement!AC164</f>
         <v>0.10989819918487531</v>
       </c>
     </row>
@@ -33197,27 +33247,27 @@
         <v>255</v>
       </c>
       <c r="C46" s="182">
-        <f>Statement!M164</f>
+        <f>Statement!M165</f>
         <v>1.3789964314325249</v>
       </c>
       <c r="D46" s="182">
-        <f>Statement!N164</f>
+        <f>Statement!N165</f>
         <v>1.0098273985383299</v>
       </c>
       <c r="E46" s="182">
-        <f>Statement!O164</f>
+        <f>Statement!O165</f>
         <v>1.0136527287634121</v>
       </c>
       <c r="F46" s="182">
-        <f>Statement!P164</f>
+        <f>Statement!P165</f>
         <v>0.71608815118039593</v>
       </c>
       <c r="G46" s="182">
-        <f>Statement!Q164</f>
+        <f>Statement!Q165</f>
         <v>1.306571654790182</v>
       </c>
       <c r="I46" s="182">
-        <f>Statement!AC164</f>
+        <f>Statement!AC165</f>
         <v>1.3708387576715642</v>
       </c>
     </row>
@@ -33226,27 +33276,27 @@
         <v>256</v>
       </c>
       <c r="C47" s="182">
-        <f>Statement!M165</f>
+        <f>Statement!M166</f>
         <v>2.1017405869929355</v>
       </c>
       <c r="D47" s="182">
-        <f>Statement!N165</f>
+        <f>Statement!N166</f>
         <v>1.5676255636759446</v>
       </c>
       <c r="E47" s="182">
-        <f>Statement!O165</f>
+        <f>Statement!O166</f>
         <v>1.5424018821516416</v>
       </c>
       <c r="F47" s="182">
-        <f>Statement!P165</f>
+        <f>Statement!P166</f>
         <v>1.3268659227275277</v>
       </c>
       <c r="G47" s="182">
-        <f>Statement!Q165</f>
+        <f>Statement!Q166</f>
         <v>2.0170387965162311</v>
       </c>
       <c r="I47" s="182">
-        <f>Statement!AC165</f>
+        <f>Statement!AC166</f>
         <v>2.3119583410823878</v>
       </c>
     </row>
@@ -33255,27 +33305,27 @@
         <v>262</v>
       </c>
       <c r="C48" s="184" t="str">
-        <f>Statement!M166</f>
+        <f>Statement!M167</f>
         <v>N/A</v>
       </c>
       <c r="D48" s="184" t="str">
-        <f>Statement!N166</f>
+        <f>Statement!N167</f>
         <v>N/A</v>
       </c>
       <c r="E48" s="184" t="str">
-        <f>Statement!O166</f>
+        <f>Statement!O167</f>
         <v>N/A</v>
       </c>
       <c r="F48" s="184" t="str">
-        <f>Statement!P166</f>
+        <f>Statement!P167</f>
         <v>N/A</v>
       </c>
       <c r="G48" s="184" t="str">
-        <f>Statement!Q166</f>
+        <f>Statement!Q167</f>
         <v>N/A</v>
       </c>
       <c r="I48" s="184" t="str">
-        <f>Statement!AC166</f>
+        <f>Statement!AC167</f>
         <v>N/A</v>
       </c>
     </row>
@@ -33295,28 +33345,28 @@
         <v>269</v>
       </c>
       <c r="C51" s="177">
-        <f>Statement!M179</f>
+        <f>Statement!M180</f>
         <v>9.471837848372637E-2</v>
       </c>
       <c r="D51" s="177">
-        <f>Statement!N179</f>
+        <f>Statement!N180</f>
         <v>7.3401437760121077E-2</v>
       </c>
       <c r="E51" s="177">
-        <f>Statement!O179</f>
+        <f>Statement!O180</f>
         <v>7.9601990049751256E-3</v>
       </c>
       <c r="F51" s="177">
-        <f>Statement!P179</f>
+        <f>Statement!P180</f>
         <v>-0.21576354679802953</v>
       </c>
       <c r="G51" s="177">
-        <f>Statement!Q179</f>
+        <f>Statement!Q180</f>
         <v>-1.6574585635359114E-3</v>
       </c>
       <c r="I51" s="177">
-        <f ca="1">Statement!AC179</f>
-        <v>-5.5315162599812642E-3</v>
+        <f ca="1">Statement!AC180</f>
+        <v>-5.5712809453205732E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33324,28 +33374,28 @@
         <v>273</v>
       </c>
       <c r="C52" s="177">
-        <f>Statement!M178</f>
+        <f>Statement!M179</f>
         <v>4.1263521617131038E-2</v>
       </c>
       <c r="D52" s="177">
-        <f>Statement!N178</f>
+        <f>Statement!N179</f>
         <v>-0.11426372932609277</v>
       </c>
       <c r="E52" s="177">
-        <f>Statement!O178</f>
+        <f>Statement!O179</f>
         <v>-8.1980684811237922E-2</v>
       </c>
       <c r="F52" s="177">
-        <f>Statement!P178</f>
+        <f>Statement!P179</f>
         <v>-0.21690804218478027</v>
       </c>
       <c r="G52" s="177">
-        <f>Statement!Q178</f>
+        <f>Statement!Q179</f>
         <v>-4.0830886134753538E-2</v>
       </c>
       <c r="I52" s="177">
-        <f ca="1">Statement!AC178</f>
-        <v>-9.7454604659952572E-3</v>
+        <f ca="1">Statement!AC179</f>
+        <v>-9.8155181410889015E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33353,27 +33403,27 @@
         <v>270</v>
       </c>
       <c r="C53" s="177">
-        <f>Statement!M180</f>
+        <f>Statement!M181</f>
         <v>2.7090235821477293E-2</v>
       </c>
       <c r="D53" s="177">
-        <f>Statement!N180</f>
+        <f>Statement!N181</f>
         <v>5.5240257283390083E-2</v>
       </c>
       <c r="E53" s="177">
-        <f>Statement!O180</f>
+        <f>Statement!O181</f>
         <v>1.472636815920398E-2</v>
       </c>
       <c r="F53" s="177">
-        <f>Statement!P180</f>
+        <f>Statement!P181</f>
         <v>1.8719211822660099E-2</v>
       </c>
       <c r="G53" s="177">
-        <f>Statement!Q180</f>
+        <f>Statement!Q181</f>
         <v>0</v>
       </c>
       <c r="I53" s="177">
-        <f ca="1">Statement!AC180</f>
+        <f ca="1">Statement!AC181</f>
         <v>0</v>
       </c>
     </row>
@@ -33382,27 +33432,27 @@
         <v>296</v>
       </c>
       <c r="C54" s="177">
-        <f>Statement!M181</f>
+        <f>Statement!M182</f>
         <v>1.1471325510000168E-2</v>
       </c>
       <c r="D54" s="177">
-        <f>Statement!N181</f>
+        <f>Statement!N182</f>
         <v>0</v>
       </c>
       <c r="E54" s="177">
-        <f>Statement!O181</f>
+        <f>Statement!O182</f>
         <v>0</v>
       </c>
       <c r="F54" s="177">
-        <f>Statement!P181</f>
+        <f>Statement!P182</f>
         <v>0</v>
       </c>
       <c r="G54" s="177">
-        <f>Statement!Q181</f>
+        <f>Statement!Q182</f>
         <v>0</v>
       </c>
       <c r="I54" s="177">
-        <f ca="1">Statement!AC181</f>
+        <f ca="1">Statement!AC182</f>
         <v>0</v>
       </c>
     </row>
@@ -33411,27 +33461,27 @@
         <v>298</v>
       </c>
       <c r="C55" s="177">
-        <f>Statement!M182</f>
+        <f>Statement!M183</f>
         <v>3.8280501981404286E-2</v>
       </c>
       <c r="D55" s="177">
-        <f>Statement!N182</f>
+        <f>Statement!N183</f>
         <v>5.4648662953072684E-2</v>
       </c>
       <c r="E55" s="177">
-        <f>Statement!O182</f>
+        <f>Statement!O183</f>
         <v>1.4459467369037167E-2</v>
       </c>
       <c r="F55" s="177">
-        <f>Statement!P182</f>
+        <f>Statement!P183</f>
         <v>1.8191333234735322E-2</v>
       </c>
       <c r="G55" s="177">
-        <f>Statement!Q182</f>
+        <f>Statement!Q183</f>
         <v>0</v>
       </c>
       <c r="I55" s="177">
-        <f ca="1">Statement!AC182</f>
+        <f ca="1">Statement!AC183</f>
         <v>0</v>
       </c>
     </row>
@@ -33451,27 +33501,27 @@
         <v>274</v>
       </c>
       <c r="C58" s="177">
-        <f>Statement!M184</f>
+        <f>Statement!M185</f>
         <v>0.64970645792563597</v>
       </c>
       <c r="D58" s="177">
-        <f>Statement!N184</f>
+        <f>Statement!N185</f>
         <v>-0.47826780445011563</v>
       </c>
       <c r="E58" s="177">
-        <f>Statement!O184</f>
+        <f>Statement!O185</f>
         <v>-0.1763765135937857</v>
       </c>
       <c r="F58" s="177">
-        <f>Statement!P184</f>
+        <f>Statement!P185</f>
         <v>-8.3866568761145496E-2</v>
       </c>
       <c r="G58" s="177">
-        <f>Statement!Q184</f>
+        <f>Statement!Q185</f>
         <v>0</v>
       </c>
       <c r="I58" s="177">
-        <f>Statement!AC184</f>
+        <f>Statement!AC185</f>
         <v>0</v>
       </c>
     </row>
@@ -33480,27 +33530,27 @@
         <v>276</v>
       </c>
       <c r="C59" s="177">
-        <f>Statement!M185</f>
+        <f>Statement!M186</f>
         <v>0.27800161160354553</v>
       </c>
       <c r="D59" s="177">
-        <f>Statement!N185</f>
+        <f>Statement!N186</f>
         <v>0</v>
       </c>
       <c r="E59" s="177">
-        <f>Statement!O185</f>
+        <f>Statement!O186</f>
         <v>0</v>
       </c>
       <c r="F59" s="177">
-        <f>Statement!P185</f>
+        <f>Statement!P186</f>
         <v>0</v>
       </c>
       <c r="G59" s="177">
-        <f>Statement!Q185</f>
+        <f>Statement!Q186</f>
         <v>0</v>
       </c>
       <c r="I59" s="177">
-        <f>Statement!AC185</f>
+        <f>Statement!AC186</f>
         <v>0</v>
       </c>
     </row>
@@ -33509,27 +33559,27 @@
         <v>277</v>
       </c>
       <c r="C60" s="177">
-        <f>Statement!M186</f>
+        <f>Statement!M187</f>
         <v>0.9277080695291815</v>
       </c>
       <c r="D60" s="177">
-        <f>Statement!N186</f>
+        <f>Statement!N187</f>
         <v>-0.47826780445011563</v>
       </c>
       <c r="E60" s="177">
-        <f>Statement!O186</f>
+        <f>Statement!O187</f>
         <v>-0.1763765135937857</v>
       </c>
       <c r="F60" s="177">
-        <f>Statement!P186</f>
+        <f>Statement!P187</f>
         <v>-8.3866568761145496E-2</v>
       </c>
       <c r="G60" s="177">
-        <f>Statement!Q186</f>
+        <f>Statement!Q187</f>
         <v>0</v>
       </c>
       <c r="I60" s="177">
-        <f>Statement!AC186</f>
+        <f>Statement!AC187</f>
         <v>0</v>
       </c>
     </row>
@@ -33549,27 +33599,27 @@
         <v>281</v>
       </c>
       <c r="C63" s="177">
-        <f>Statement!M187</f>
+        <f>Statement!M188</f>
         <v>4.874482086278333E-4</v>
       </c>
       <c r="D63" s="177">
-        <f>Statement!N187</f>
+        <f>Statement!N188</f>
         <v>4.8169556840077071E-4</v>
       </c>
       <c r="E63" s="177">
-        <f>Statement!O187</f>
+        <f>Statement!O188</f>
         <v>4.7058823529411766E-4</v>
       </c>
       <c r="F63" s="177">
-        <f>Statement!P187</f>
+        <f>Statement!P188</f>
         <v>4.6189376443418013E-4</v>
       </c>
       <c r="G63" s="177">
-        <f>Statement!Q187</f>
+        <f>Statement!Q188</f>
         <v>6.0060060060060057E-4</v>
       </c>
       <c r="I63" s="177">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>5.9689614007162755E-4</v>
       </c>
     </row>
@@ -33589,27 +33639,27 @@
         <v>282</v>
       </c>
       <c r="C66" s="176">
-        <f>Statement!M188</f>
+        <f>Statement!M189</f>
         <v>6.9776522593320234</v>
       </c>
       <c r="D66" s="176">
-        <f>Statement!N188</f>
+        <f>Statement!N189</f>
         <v>6.8498912255257434</v>
       </c>
       <c r="E66" s="176">
-        <f>Statement!O188</f>
+        <f>Statement!O189</f>
         <v>5.9210028382213808</v>
       </c>
       <c r="F66" s="176">
-        <f>Statement!P188</f>
+        <f>Statement!P189</f>
         <v>5.0951501154734409</v>
       </c>
       <c r="G66" s="176">
-        <f>Statement!Q188</f>
+        <f>Statement!Q189</f>
         <v>7.4906906906906903</v>
       </c>
       <c r="I66" s="176">
-        <f>Statement!AC188</f>
+        <f>Statement!AC189</f>
         <v>6.5238758456028654</v>
       </c>
     </row>
@@ -33618,27 +33668,27 @@
         <v>290</v>
       </c>
       <c r="C67" s="176">
-        <f>Statement!M191</f>
+        <f>Statement!M192</f>
         <v>-2.3791748526522594</v>
       </c>
       <c r="D67" s="176">
-        <f>Statement!N191</f>
+        <f>Statement!N192</f>
         <v>-3.3147208121827409</v>
       </c>
       <c r="E67" s="176">
-        <f>Statement!O191</f>
+        <f>Statement!O192</f>
         <v>-5.7313150425733204</v>
       </c>
       <c r="F67" s="176">
-        <f>Statement!P191</f>
+        <f>Statement!P192</f>
         <v>-6.4547344110854503</v>
       </c>
       <c r="G67" s="176">
-        <f>Statement!Q191</f>
+        <f>Statement!Q192</f>
         <v>-1.8356356356356356</v>
       </c>
       <c r="I67" s="176">
-        <f>Statement!AC191</f>
+        <f>Statement!AC192</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
@@ -33647,28 +33697,28 @@
         <v>295</v>
       </c>
       <c r="C68" s="198">
-        <f>Statement!M192</f>
+        <f>Statement!M193</f>
         <v>-4.601830291547894E-2</v>
       </c>
       <c r="D68" s="198">
-        <f>Statement!N192</f>
+        <f>Statement!N193</f>
         <v>-0.12496200017933728</v>
       </c>
       <c r="E68" s="198">
-        <f>Statement!O192</f>
+        <f>Statement!O193</f>
         <v>-0.11346561311091601</v>
       </c>
       <c r="F68" s="198">
-        <f>Statement!P192</f>
+        <f>Statement!P193</f>
         <v>-0.31796721236874137</v>
       </c>
       <c r="G68" s="198">
-        <f>Statement!Q192</f>
+        <f>Statement!Q193</f>
         <v>-5.070816673026618E-2</v>
       </c>
       <c r="I68" s="198">
-        <f ca="1">Statement!AC192</f>
-        <v>-2.1731134248581776E-2</v>
+        <f ca="1">Statement!AC193</f>
+        <v>-2.1887353931368002E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33687,27 +33737,27 @@
         <v>284</v>
       </c>
       <c r="C71" s="177">
-        <f>Statement!M189</f>
+        <f>Statement!M190</f>
         <v>6.9120043454644217E-2</v>
       </c>
       <c r="D71" s="177">
-        <f>Statement!N189</f>
+        <f>Statement!N190</f>
         <v>0.20268256333830104</v>
       </c>
       <c r="E71" s="177">
-        <f>Statement!O189</f>
+        <f>Statement!O190</f>
         <v>0.28149245924505273</v>
       </c>
       <c r="F71" s="177">
-        <f>Statement!P189</f>
+        <f>Statement!P190</f>
         <v>0.41143822393822393</v>
       </c>
       <c r="G71" s="177">
-        <f>Statement!Q189</f>
+        <f>Statement!Q190</f>
         <v>0.25100546560791998</v>
       </c>
       <c r="I71" s="177">
-        <f>Statement!AC189</f>
+        <f>Statement!AC190</f>
         <v>0.2375751503006012</v>
       </c>
     </row>
@@ -33716,27 +33766,27 @@
         <v>285</v>
       </c>
       <c r="C72" s="177">
-        <f>Statement!M190</f>
+        <f>Statement!M191</f>
         <v>2.5764324762097592E-2</v>
       </c>
       <c r="D72" s="177">
-        <f>Statement!N190</f>
+        <f>Statement!N191</f>
         <v>4.9608272274558315E-2</v>
       </c>
       <c r="E72" s="177">
-        <f>Statement!O190</f>
+        <f>Statement!O191</f>
         <v>5.9544884561481153E-2</v>
       </c>
       <c r="F72" s="177">
-        <f>Statement!P190</f>
+        <f>Statement!P191</f>
         <v>6.4217246379540877E-2</v>
       </c>
       <c r="G72" s="177">
-        <f>Statement!Q190</f>
+        <f>Statement!Q191</f>
         <v>4.6052258149963103E-2</v>
       </c>
       <c r="I72" s="177">
-        <f>Statement!AC190</f>
+        <f>Statement!AC191</f>
         <v>4.4100961627885349E-2</v>
       </c>
     </row>
@@ -33756,27 +33806,27 @@
         <v>308</v>
       </c>
       <c r="C75" s="177">
-        <f>Statement!M193</f>
+        <f>Statement!M194</f>
         <v>0.23705456570155903</v>
       </c>
       <c r="D75" s="177">
-        <f>Statement!N193</f>
+        <f>Statement!N194</f>
         <v>0.39401148222158783</v>
       </c>
       <c r="E75" s="177">
-        <f>Statement!O193</f>
+        <f>Statement!O194</f>
         <v>0.4748469425389098</v>
       </c>
       <c r="F75" s="177">
-        <f>Statement!P193</f>
+        <f>Statement!P194</f>
         <v>0.45091429539933336</v>
       </c>
       <c r="G75" s="177">
-        <f>Statement!Q193</f>
+        <f>Statement!Q194</f>
         <v>0.27710820577829071</v>
       </c>
       <c r="I75" s="177">
-        <f>Statement!AC193</f>
+        <f>Statement!AC194</f>
         <v>0.24364339787586259</v>
       </c>
     </row>
@@ -33785,27 +33835,27 @@
         <v>305</v>
       </c>
       <c r="C76" s="177">
-        <f>Statement!M194</f>
+        <f>Statement!M195</f>
         <v>0.63596550787615425</v>
       </c>
       <c r="D76" s="177">
-        <f>Statement!N194</f>
+        <f>Statement!N195</f>
         <v>1.6097971878442299</v>
       </c>
       <c r="E76" s="177">
-        <f>Statement!O194</f>
+        <f>Statement!O195</f>
         <v>2.2447912126231366</v>
       </c>
       <c r="F76" s="177">
-        <f>Statement!P194</f>
+        <f>Statement!P195</f>
         <v>2.8889961389961392</v>
       </c>
       <c r="G76" s="177">
-        <f>Statement!Q194</f>
+        <f>Statement!Q195</f>
         <v>1.5103640301124059</v>
       </c>
       <c r="I76" s="177">
-        <f>Statement!AC194</f>
+        <f>Statement!AC195</f>
         <v>1.3125250501002004</v>
       </c>
     </row>
@@ -33814,27 +33864,27 @@
         <v>306</v>
       </c>
       <c r="C77" s="177">
-        <f>Statement!M195</f>
+        <f>Statement!M196</f>
         <v>1.5886194029850746</v>
       </c>
       <c r="D77" s="177">
-        <f>Statement!N195</f>
+        <f>Statement!N196</f>
         <v>1.9059455312619868</v>
       </c>
       <c r="E77" s="177">
-        <f>Statement!O195</f>
+        <f>Statement!O196</f>
         <v>2.6817329722974379</v>
       </c>
       <c r="F77" s="177">
-        <f>Statement!P195</f>
+        <f>Statement!P196</f>
         <v>2.1042270849811056</v>
       </c>
       <c r="G77" s="177">
-        <f>Statement!Q195</f>
+        <f>Statement!Q196</f>
         <v>1.2511532547411583</v>
       </c>
       <c r="I77" s="177">
-        <f>Statement!AC195</f>
+        <f>Statement!AC196</f>
         <v>1.0765121630506247</v>
       </c>
     </row>
@@ -34021,23 +34071,23 @@
         <v>362</v>
       </c>
       <c r="C89" s="177">
-        <f>Statement!M199</f>
+        <f>Statement!M200</f>
         <v>1</v>
       </c>
       <c r="D89" s="177">
-        <f>Statement!N199</f>
+        <f>Statement!N200</f>
         <v>-0.22657676298045326</v>
       </c>
       <c r="E89" s="177">
-        <f>Statement!O199</f>
+        <f>Statement!O200</f>
         <v>-7.9155257608661447E-2</v>
       </c>
       <c r="F89" s="177">
-        <f>Statement!P199</f>
+        <f>Statement!P200</f>
         <v>0.139722469068289</v>
       </c>
       <c r="G89" s="177">
-        <f>Statement!Q199</f>
+        <f>Statement!Q200</f>
         <v>-3.3527259641336293E-2</v>
       </c>
       <c r="I89" s="199"/>
@@ -34047,23 +34097,23 @@
         <v>363</v>
       </c>
       <c r="C90" s="177">
-        <f>Statement!M200</f>
+        <f>Statement!M201</f>
         <v>1</v>
       </c>
       <c r="D90" s="177">
-        <f>Statement!N200</f>
+        <f>Statement!N201</f>
         <v>-8.4923946253162061E-2</v>
       </c>
       <c r="E90" s="177">
-        <f>Statement!O200</f>
+        <f>Statement!O201</f>
         <v>-0.23547784878293962</v>
       </c>
       <c r="F90" s="177">
-        <f>Statement!P200</f>
+        <f>Statement!P201</f>
         <v>-0.242779995304062</v>
       </c>
       <c r="G90" s="177">
-        <f>Statement!Q200</f>
+        <f>Statement!Q201</f>
         <v>4.9240310077519382E-2</v>
       </c>
       <c r="I90" s="199"/>
@@ -34073,23 +34123,23 @@
         <v>364</v>
       </c>
       <c r="C91" s="177">
-        <f>Statement!M201</f>
+        <f>Statement!M202</f>
         <v>1</v>
       </c>
       <c r="D91" s="177">
-        <f>Statement!N201</f>
+        <f>Statement!N202</f>
         <v>-0.16628914988814317</v>
       </c>
       <c r="E91" s="177">
-        <f>Statement!O201</f>
+        <f>Statement!O202</f>
         <v>-0.1521793818236705</v>
       </c>
       <c r="F91" s="177">
-        <f>Statement!P201</f>
+        <f>Statement!P202</f>
         <v>-2.1403279726227919E-2</v>
       </c>
       <c r="G91" s="177">
-        <f>Statement!Q201</f>
+        <f>Statement!Q202</f>
         <v>-6.5492915041135214E-3</v>
       </c>
       <c r="I91" s="199"/>
@@ -34099,23 +34149,23 @@
         <v>365</v>
       </c>
       <c r="C92" s="177">
-        <f>Statement!M202</f>
+        <f>Statement!M203</f>
         <v>1</v>
       </c>
       <c r="D92" s="177">
-        <f>Statement!N202</f>
+        <f>Statement!N203</f>
         <v>0.35158501440922191</v>
       </c>
       <c r="E92" s="177">
-        <f>Statement!O202</f>
+        <f>Statement!O203</f>
         <v>1.0298507462686568</v>
       </c>
       <c r="F92" s="177">
-        <f>Statement!P202</f>
+        <f>Statement!P203</f>
         <v>17.190126050420169</v>
       </c>
       <c r="G92" s="177">
-        <f>Statement!Q202</f>
+        <f>Statement!Q203</f>
         <v>2.9393081942599757E-2</v>
       </c>
       <c r="I92" s="199"/>
@@ -34125,23 +34175,23 @@
         <v>366</v>
       </c>
       <c r="C93" s="177">
-        <f>Statement!M203</f>
+        <f>Statement!M204</f>
         <v>1</v>
       </c>
       <c r="D93" s="177">
-        <f>Statement!N203</f>
+        <f>Statement!N204</f>
         <v>-0.58669833729216148</v>
       </c>
       <c r="E93" s="177">
-        <f>Statement!O203</f>
+        <f>Statement!O204</f>
         <v>-7.9445571331981074E-2</v>
       </c>
       <c r="F93" s="177">
-        <f>Statement!P203</f>
+        <f>Statement!P204</f>
         <v>0.32243848696290855</v>
       </c>
       <c r="G93" s="177">
-        <f>Statement!Q203</f>
+        <f>Statement!Q204</f>
         <v>-1.0552624271035824E-2</v>
       </c>
       <c r="I93" s="199"/>
@@ -34162,23 +34212,23 @@
         <v>288</v>
       </c>
       <c r="C96" s="177">
-        <f>Statement!M207</f>
+        <f>Statement!M208</f>
         <v>-1</v>
       </c>
       <c r="D96" s="177">
-        <f>Statement!N207</f>
+        <f>Statement!N208</f>
         <v>6.2544294826364283E-2</v>
       </c>
       <c r="E96" s="177">
-        <f>Statement!O207</f>
+        <f>Statement!O208</f>
         <v>-0.48507587126896784</v>
       </c>
       <c r="F96" s="177">
-        <f>Statement!P207</f>
+        <f>Statement!P208</f>
         <v>-0.48218911917098445</v>
       </c>
       <c r="G96" s="177">
-        <f>Statement!Q207</f>
+        <f>Statement!Q208</f>
         <v>-1</v>
       </c>
       <c r="I96" s="199"/>
@@ -34280,19 +34330,19 @@
       <c r="B7" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="230">
+      <c r="C7" s="235">
         <f>Statement!AA88</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="231"/>
-      <c r="F7" s="230">
+      <c r="D7" s="236"/>
+      <c r="F7" s="235">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="231"/>
+      <c r="G7" s="236"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -34319,19 +34369,19 @@
       <c r="B9" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="230">
+      <c r="C9" s="235">
         <f>Statement!AA89</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="231"/>
-      <c r="F9" s="230">
+      <c r="D9" s="236"/>
+      <c r="F9" s="235">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="231"/>
+      <c r="G9" s="236"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -34358,19 +34408,19 @@
       <c r="B11" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="230">
+      <c r="C11" s="235">
         <f>Statement!AA90</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="231"/>
-      <c r="F11" s="230">
+      <c r="D11" s="236"/>
+      <c r="F11" s="235">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="231"/>
+      <c r="G11" s="236"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -34397,19 +34447,19 @@
       <c r="B13" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="230">
+      <c r="C13" s="235">
         <f>Statement!AA94</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="231"/>
-      <c r="F13" s="230">
+      <c r="D13" s="236"/>
+      <c r="F13" s="235">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="231"/>
+      <c r="G13" s="236"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -34436,19 +34486,19 @@
       <c r="B15" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="230">
+      <c r="C15" s="235">
         <f>Statement!AA95</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="231"/>
-      <c r="F15" s="230">
+      <c r="D15" s="236"/>
+      <c r="F15" s="235">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="231"/>
+      <c r="G15" s="236"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -34475,19 +34525,19 @@
       <c r="B17" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="230">
+      <c r="C17" s="235">
         <f>Statement!AA97</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="231"/>
-      <c r="F17" s="230">
+      <c r="D17" s="236"/>
+      <c r="F17" s="235">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="231"/>
+      <c r="G17" s="236"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -34514,22 +34564,22 @@
       <c r="B19" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="230">
+      <c r="C19" s="235">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="231"/>
-      <c r="F19" s="230">
+      <c r="D19" s="236"/>
+      <c r="F19" s="235">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="231"/>
+      <c r="G19" s="236"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -34556,22 +34606,22 @@
       <c r="B21" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="230">
+      <c r="C21" s="235">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="231"/>
-      <c r="F21" s="230">
+      <c r="D21" s="236"/>
+      <c r="F21" s="235">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="231"/>
+      <c r="G21" s="236"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -34619,22 +34669,22 @@
       <c r="B25" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="230">
+      <c r="C25" s="235">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="231"/>
-      <c r="F25" s="230">
+      <c r="D25" s="236"/>
+      <c r="F25" s="235">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="231"/>
+      <c r="G25" s="236"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -34661,22 +34711,22 @@
       <c r="B27" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="230">
+      <c r="C27" s="235">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="231"/>
-      <c r="F27" s="230">
+      <c r="D27" s="236"/>
+      <c r="F27" s="235">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="231"/>
+      <c r="G27" s="236"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -34703,22 +34753,22 @@
       <c r="B29" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="230">
+      <c r="C29" s="235">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="231"/>
-      <c r="F29" s="230">
+      <c r="D29" s="236"/>
+      <c r="F29" s="235">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="231"/>
+      <c r="G29" s="236"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34745,22 +34795,22 @@
       <c r="B31" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="230">
+      <c r="C31" s="235">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="231"/>
-      <c r="F31" s="230">
+      <c r="D31" s="236"/>
+      <c r="F31" s="235">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="231"/>
+      <c r="G31" s="236"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -34787,37 +34837,25 @@
       <c r="B33" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="230">
+      <c r="C33" s="235">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="231"/>
-      <c r="F33" s="230">
+      <c r="D33" s="236"/>
+      <c r="F33" s="235">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="231"/>
+      <c r="G33" s="236"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -34834,6 +34872,18 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -35078,43 +35128,43 @@
         <v>264</v>
       </c>
       <c r="C60" s="63">
-        <f>Statement!H174</f>
+        <f>Statement!H175</f>
         <v>0</v>
       </c>
       <c r="D60" s="63">
-        <f>Statement!I174</f>
+        <f>Statement!I175</f>
         <v>0</v>
       </c>
       <c r="E60" s="63">
-        <f>Statement!J174</f>
+        <f>Statement!J175</f>
         <v>0</v>
       </c>
       <c r="F60" s="63">
-        <f>Statement!K174</f>
+        <f>Statement!K175</f>
         <v>0</v>
       </c>
       <c r="G60" s="63">
-        <f>Statement!L174</f>
+        <f>Statement!L175</f>
         <v>0</v>
       </c>
       <c r="H60" s="63">
-        <f>Statement!M174</f>
+        <f>Statement!M175</f>
         <v>8687</v>
       </c>
       <c r="I60" s="63">
-        <f>Statement!N174</f>
+        <f>Statement!N175</f>
         <v>-12539</v>
       </c>
       <c r="J60" s="63">
-        <f>Statement!O174</f>
+        <f>Statement!O175</f>
         <v>-17508</v>
       </c>
       <c r="K60" s="63">
-        <f>Statement!P174</f>
+        <f>Statement!P175</f>
         <v>-19066</v>
       </c>
       <c r="L60" s="63">
-        <f>Statement!Q174</f>
+        <f>Statement!Q175</f>
         <v>-7383</v>
       </c>
     </row>
@@ -35123,43 +35173,43 @@
         <v>265</v>
       </c>
       <c r="C61" s="63">
-        <f>Statement!H175</f>
+        <f>Statement!H176</f>
         <v>0</v>
       </c>
       <c r="D61" s="63">
-        <f>Statement!I175</f>
+        <f>Statement!I176</f>
         <v>0</v>
       </c>
       <c r="E61" s="63">
-        <f>Statement!J175</f>
+        <f>Statement!J176</f>
         <v>0</v>
       </c>
       <c r="F61" s="63">
-        <f>Statement!K175</f>
+        <f>Statement!K176</f>
         <v>0</v>
       </c>
       <c r="G61" s="63">
-        <f>Statement!L175</f>
+        <f>Statement!L176</f>
         <v>0</v>
       </c>
       <c r="H61" s="63">
-        <f>Statement!M175</f>
+        <f>Statement!M176</f>
         <v>5461.985025111735</v>
       </c>
       <c r="I61" s="63">
-        <f>Statement!N175</f>
+        <f>Statement!N176</f>
         <v>-13983</v>
       </c>
       <c r="J61" s="63">
-        <f>Statement!O175</f>
+        <f>Statement!O176</f>
         <v>-16624</v>
       </c>
       <c r="K61" s="63">
-        <f>Statement!P175</f>
+        <f>Statement!P176</f>
         <v>-23140</v>
       </c>
       <c r="L61" s="63">
-        <f>Statement!Q175</f>
+        <f>Statement!Q176</f>
         <v>-6901</v>
       </c>
     </row>
@@ -35438,43 +35488,43 @@
         <v>97</v>
       </c>
       <c r="C68" s="225">
-        <f>Statement!H135</f>
+        <f>Statement!H136</f>
         <v>0</v>
       </c>
       <c r="D68" s="225">
-        <f>Statement!I135</f>
+        <f>Statement!I136</f>
         <v>0</v>
       </c>
       <c r="E68" s="225">
-        <f>Statement!J135</f>
+        <f>Statement!J136</f>
         <v>0</v>
       </c>
       <c r="F68" s="225">
-        <f>Statement!K135</f>
+        <f>Statement!K136</f>
         <v>0</v>
       </c>
       <c r="G68" s="225">
-        <f>Statement!L135</f>
+        <f>Statement!L136</f>
         <v>0</v>
       </c>
       <c r="H68" s="225">
-        <f>Statement!M135</f>
+        <f>Statement!M136</f>
         <v>0.11797679417597948</v>
       </c>
       <c r="I68" s="225">
-        <f>Statement!N135</f>
+        <f>Statement!N136</f>
         <v>4.4024535565037361E-2</v>
       </c>
       <c r="J68" s="225">
-        <f>Statement!O135</f>
+        <f>Statement!O136</f>
         <v>8.7434489382581995E-3</v>
       </c>
       <c r="K68" s="225">
-        <f>Statement!P135</f>
+        <f>Statement!P136</f>
         <v>-9.7885334758378503E-2</v>
       </c>
       <c r="L68" s="225">
-        <f>Statement!Q135</f>
+        <f>Statement!Q136</f>
         <v>1.2297272370393844E-4</v>
       </c>
     </row>
@@ -35483,43 +35533,43 @@
         <v>99</v>
       </c>
       <c r="C69" s="225">
-        <f>Statement!H137</f>
+        <f>Statement!H138</f>
         <v>0</v>
       </c>
       <c r="D69" s="225">
-        <f>Statement!I137</f>
+        <f>Statement!I138</f>
         <v>0</v>
       </c>
       <c r="E69" s="225">
-        <f>Statement!J137</f>
+        <f>Statement!J138</f>
         <v>0</v>
       </c>
       <c r="F69" s="225">
-        <f>Statement!K137</f>
+        <f>Statement!K138</f>
         <v>0</v>
       </c>
       <c r="G69" s="225">
-        <f>Statement!L137</f>
+        <f>Statement!L138</f>
         <v>0</v>
       </c>
       <c r="H69" s="225">
-        <f>Statement!M137</f>
+        <f>Statement!M138</f>
         <v>0.20827960709081569</v>
       </c>
       <c r="I69" s="225">
-        <f>Statement!N137</f>
+        <f>Statement!N138</f>
         <v>7.904518698914445E-2</v>
       </c>
       <c r="J69" s="225">
-        <f>Statement!O137</f>
+        <f>Statement!O138</f>
         <v>1.5863244625438012E-2</v>
       </c>
       <c r="K69" s="225">
-        <f>Statement!P137</f>
+        <f>Statement!P138</f>
         <v>-0.19374433363553945</v>
       </c>
       <c r="L69" s="225">
-        <f>Statement!Q137</f>
+        <f>Statement!Q138</f>
         <v>2.2750938476212145E-4</v>
       </c>
     </row>
@@ -35528,43 +35578,43 @@
         <v>100</v>
       </c>
       <c r="C70" s="225">
-        <f>Statement!H157</f>
+        <f>Statement!H158</f>
         <v>0</v>
       </c>
       <c r="D70" s="225">
-        <f>Statement!I157</f>
+        <f>Statement!I158</f>
         <v>0</v>
       </c>
       <c r="E70" s="225">
-        <f>Statement!J157</f>
+        <f>Statement!J158</f>
         <v>0</v>
       </c>
       <c r="F70" s="225">
-        <f>Statement!K157</f>
+        <f>Statement!K158</f>
         <v>0</v>
       </c>
       <c r="G70" s="225">
-        <f>Statement!L157</f>
+        <f>Statement!L158</f>
         <v>0</v>
       </c>
       <c r="H70" s="225">
-        <f>Statement!M157</f>
+        <f>Statement!M158</f>
         <v>0.16950089956234582</v>
       </c>
       <c r="I70" s="225">
-        <f>Statement!N157</f>
+        <f>Statement!N158</f>
         <v>1.9948888452038051E-2</v>
       </c>
       <c r="J70" s="225">
-        <f>Statement!O157</f>
+        <f>Statement!O158</f>
         <v>6.9301102111075507E-4</v>
       </c>
       <c r="K70" s="225">
-        <f>Statement!P157</f>
+        <f>Statement!P158</f>
         <v>-8.7817056571991486E-2</v>
       </c>
       <c r="L70" s="225">
-        <f>Statement!Q157</f>
+        <f>Statement!Q158</f>
         <v>-1.6335987131905347E-2</v>
       </c>
     </row>
@@ -35992,35 +36042,35 @@
         <v>264</v>
       </c>
       <c r="C66" s="63">
-        <f>Statement!T174</f>
+        <f>Statement!T175</f>
         <v>0</v>
       </c>
       <c r="D66" s="63">
-        <f>Statement!U174</f>
+        <f>Statement!U175</f>
         <v>0</v>
       </c>
       <c r="E66" s="63">
-        <f>Statement!V174</f>
+        <f>Statement!V175</f>
         <v>0</v>
       </c>
       <c r="F66" s="63">
-        <f>Statement!W174</f>
+        <f>Statement!W175</f>
         <v>-5054</v>
       </c>
       <c r="G66" s="63">
-        <f>Statement!X174</f>
+        <f>Statement!X175</f>
         <v>-2164</v>
       </c>
       <c r="H66" s="63">
-        <f>Statement!Y174</f>
+        <f>Statement!Y175</f>
         <v>-427</v>
       </c>
       <c r="I66" s="63">
-        <f>Statement!Z174</f>
+        <f>Statement!Z175</f>
         <v>262</v>
       </c>
       <c r="J66" s="63">
-        <f>Statement!AA174</f>
+        <f>Statement!AA175</f>
         <v>-3161</v>
       </c>
     </row>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546458A5-898E-8A44-B4BF-C4B914BEC026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827F1DB6-3DE9-3540-B461-125F6B35ED3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2278,6 +2248,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2285,12 +2261,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11704,7 +11674,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -11724,8 +11694,10 @@
     <v>132.75</v>
     <v>18.965</v>
     <v>2.2317999999999998</v>
-    <v>3.355</v>
-    <v>3.1084999999999998E-2</v>
+    <v>4.78</v>
+    <v>4.4288000000000001E-2</v>
+    <v>-1.89</v>
+    <v>-1.6768999999999999E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -11736,46 +11708,32 @@
     <v>118.29</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46176.724033205472</v>
+    <v>46176.925423043751</v>
     <v>0</v>
     <v>110.86</v>
-    <v>559318410000</v>
+    <v>566480460000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>116.43</v>
+    <v>116.42</v>
     <v>0</v>
     <v>107.93</v>
-    <v>111.285</v>
+    <v>112.71</v>
+    <v>110.82</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>84379814</v>
+    <v>118418472</v>
     <v>145048030</v>
     <v>1989</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -11794,7 +11752,7 @@
     <v>US</v>
     <v>44.63</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>44.28</v>
     <v>10 Y TSY YLD NDX</v>
     <v>44.3</v>
@@ -11804,13 +11762,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -11832,6 +11790,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -11852,6 +11812,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -11861,11 +11822,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -11901,7 +11857,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -11912,13 +11868,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12012,13 +11971,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12090,6 +12055,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12097,6 +12065,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -12610,7 +12581,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC171</f>
-        <v>559318.41</v>
+        <v>566480.46</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -12618,7 +12589,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-8.808241809556387</v>
+        <v>-8.8046952175618021</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -12634,7 +12605,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC172</f>
-        <v>585155.41</v>
+        <v>592317.46</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -12642,7 +12613,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>32.333922448813013</v>
+        <v>32.321232777928991</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -12651,7 +12622,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>111.285</v>
+        <v>112.71</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>246</v>
@@ -12666,23 +12637,23 @@
       </c>
       <c r="I5" s="213">
         <f ca="1">'AVG target price'!C7</f>
-        <v>36.483298773483725</v>
+        <v>36.468980651241303</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="210" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>110.82</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>240</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC168</f>
-        <v>-179.49193548387098</v>
+        <v>-181.79032258064515</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -12690,7 +12661,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-10.988884344918722</v>
+        <v>-10.984571681463171</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -12699,14 +12670,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>3.355</v>
+        <v>4.78</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC169</f>
-        <v>9.7399990234919915</v>
+        <v>9.8647193236984538</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -12714,23 +12685,23 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>12.255023766955407</v>
+        <v>12.25023663253633</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-1.89</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>268</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC179</f>
-        <v>-9.8155181410889015E-3</v>
+        <v>-9.6914198946950452E-3</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -12738,7 +12709,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.88987712839146871</v>
+        <v>-0.8913118921787212</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12747,23 +12718,23 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.1084999999999998E-2</v>
+        <v>4.4288000000000001E-2</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC180</f>
-        <v>-5.5712809453205732E-3</v>
+        <v>-5.5008428710850857E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="72" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-1.6768999999999999E-2</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>297</v>
@@ -12843,7 +12814,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC193</f>
-        <v>-2.1887353931368002E-2</v>
+        <v>-2.1610630665001226E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -12948,7 +12919,7 @@
       <c r="C26" s="171">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="5">
+      <c r="E26" s="187" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="226" cm="1">
@@ -17387,6 +17358,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -17394,12 +17371,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18459,16 +18430,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -18551,7 +18522,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>111.285</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18560,7 +18531,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>559318.41</v>
+        <v>566480.46</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18630,7 +18601,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.4511531334166436E-2</v>
+        <v>7.3638848894180986E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18639,7 +18610,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92548846866583356</v>
+        <v>0.92636115110581896</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18666,7 +18637,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13735690560235675</v>
+        <v>0.13744619934229851</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18925,7 +18896,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23291.932656446141</v>
+        <v>-23274.223920113993</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -18979,23 +18950,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6494.3039834257206</v>
+        <v>-6493.7941565070196</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5057.8691579644583</v>
+        <v>-5057.0750662070459</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3565.1001312306958</v>
+        <v>-3564.2605764441973</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3264.5443554323961</v>
+        <v>-3263.5193608417944</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1408.0891745177687</v>
+        <v>-1407.5365602091188</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -19014,7 +18985,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12238.316532259363</v>
+        <v>-12224.212443256436</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -19037,7 +19008,7 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13735690560235675</v>
+        <v>0.13744619934229851</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -19052,7 +19023,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19789.90680257104</v>
+        <v>-19786.185720209178</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19061,7 +19032,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12238.316532259363</v>
+        <v>-12224.212443256436</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19070,7 +19041,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-32028.223334830403</v>
+        <v>-32010.398163465616</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19097,7 +19068,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-44270.2233348304</v>
+        <v>-44252.398163465616</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19115,7 +19086,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>-8.808241809556387</v>
+        <v>-8.8046952175618021</v>
       </c>
     </row>
   </sheetData>
@@ -20124,7 +20095,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13735690560235675</v>
+        <v>0.13744619934229851</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -20168,7 +20139,7 @@
       </c>
       <c r="C44" s="142">
         <f ca="1">C43/(1+C48)^5</f>
-        <v>32.333922448813013</v>
+        <v>32.321232777928991</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -20192,7 +20163,7 @@
       </c>
       <c r="C48" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13735690560235675</v>
+        <v>0.13744619934229851</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -20227,7 +20198,7 @@
       </c>
       <c r="C52" s="142">
         <f ca="1">C51/(1+C48)^5</f>
-        <v>36.483298773483725</v>
+        <v>36.468980651241303</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -20251,7 +20222,7 @@
       </c>
       <c r="C56" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13735690560235675</v>
+        <v>0.13744619934229851</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -20295,7 +20266,7 @@
       </c>
       <c r="C61" s="142">
         <f ca="1">C60/(1+C56)^5</f>
-        <v>-10.988884344918722</v>
+        <v>-10.984571681463171</v>
       </c>
     </row>
   </sheetData>
@@ -20359,7 +20330,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-8.808241809556387</v>
+        <v>-8.8046952175618021</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -20368,7 +20339,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C44</f>
-        <v>32.333922448813013</v>
+        <v>32.321232777928991</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -20377,7 +20348,7 @@
       </c>
       <c r="C7" s="132">
         <f ca="1">Multiples!C52</f>
-        <v>36.483298773483725</v>
+        <v>36.468980651241303</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -20386,7 +20357,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C61</f>
-        <v>-10.988884344918722</v>
+        <v>-10.984571681463171</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -20395,7 +20366,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>12.255023766955407</v>
+        <v>12.25023663253633</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20404,7 +20375,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>111.285</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20413,7 +20384,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.88987712839146871</v>
+        <v>-0.8913118921787212</v>
       </c>
     </row>
   </sheetData>
@@ -20666,7 +20637,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-964945.54221544415</v>
+        <v>-964211.89909385249</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20720,23 +20691,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13169.786558712953</v>
+        <v>-13168.752681684975</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19105.830117915226</v>
+        <v>-19102.830478790267</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27717.438157958284</v>
+        <v>-27710.910905702134</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40210.573071088947</v>
+        <v>-40197.947842145659</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58334.763028636487</v>
+        <v>-58311.869148529528</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20755,7 +20726,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-507012.84243825806</v>
+        <v>-506428.53378465137</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -20771,7 +20742,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>111.285</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -20780,7 +20751,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-134.85738825558497</v>
+        <v>-134.73196276193872</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -20819,7 +20790,7 @@
       </c>
       <c r="C21" s="161">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13735690560235675</v>
+        <v>0.13744619934229851</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -20837,7 +20808,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>559318.41</v>
+        <v>566480.46</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -20864,7 +20835,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>571560.41</v>
+        <v>578722.46</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -20880,7 +20851,7 @@
       </c>
       <c r="C29" s="162">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158538.3909343119</v>
+        <v>-158492.31105685257</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -20889,7 +20860,7 @@
       </c>
       <c r="C30" s="162">
         <f ca="1">L11</f>
-        <v>-507012.84243825806</v>
+        <v>-506428.53378465137</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -20898,7 +20869,7 @@
       </c>
       <c r="C31" s="165">
         <f ca="1">C29+C30</f>
-        <v>-665551.23337257002</v>
+        <v>-664920.844841504</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -20925,7 +20896,7 @@
       </c>
       <c r="C34" s="165">
         <f ca="1">C31+C32-C33</f>
-        <v>-677793.23337257002</v>
+        <v>-677162.844841504</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -20943,7 +20914,7 @@
       </c>
       <c r="C36" s="168">
         <f ca="1">C34/C35</f>
-        <v>-134.85738825558497</v>
+        <v>-134.73196276193872</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -21390,17 +21361,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28549,7 +28520,7 @@
       <c r="AA129" s="67"/>
       <c r="AC129" s="62">
         <f ca="1">Overview!C5</f>
-        <v>111.285</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="130" spans="1:31" x14ac:dyDescent="0.2">
@@ -28596,7 +28567,7 @@
       <c r="AA130" s="67"/>
       <c r="AC130" s="64">
         <f t="shared" ref="AC130" ca="1" si="76">AC129/AC84</f>
-        <v>111.285</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="132" spans="1:31" x14ac:dyDescent="0.2">
@@ -29444,55 +29415,55 @@
         <v>134</v>
       </c>
       <c r="M159" s="117">
-        <f>M30/M5*365</f>
+        <f t="shared" ref="M159:Q160" si="84">M30/M5*365</f>
         <v>43.680464162785988</v>
       </c>
       <c r="N159" s="117">
-        <f>N30/N5*365</f>
+        <f t="shared" si="84"/>
         <v>23.924651885685286</v>
       </c>
       <c r="O159" s="117">
-        <f>O30/O5*365</f>
+        <f t="shared" si="84"/>
         <v>22.898318211993807</v>
       </c>
       <c r="P159" s="117">
-        <f>P30/P5*365</f>
+        <f t="shared" si="84"/>
         <v>23.906706088397584</v>
       </c>
       <c r="Q159" s="117">
-        <f>Q30/Q5*365</f>
+        <f t="shared" si="84"/>
         <v>26.511929313378616</v>
       </c>
       <c r="T159" s="117">
-        <f t="shared" ref="T159:AA159" si="84">T30/T5*90</f>
+        <f t="shared" ref="T159:AA159" si="85">T30/T5*90</f>
         <v>21.958232681368347</v>
       </c>
       <c r="U159" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>21.144986449864501</v>
       </c>
       <c r="V159" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>21.950911640953716</v>
       </c>
       <c r="W159" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>21.769953422278363</v>
       </c>
       <c r="X159" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>16.517614122404542</v>
       </c>
       <c r="Y159" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>21.107448912326962</v>
       </c>
       <c r="Z159" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>25.267661254936375</v>
       </c>
       <c r="AA159" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>26.952935110849229</v>
       </c>
       <c r="AC159" s="117">
@@ -29505,55 +29476,55 @@
         <v>135</v>
       </c>
       <c r="M160" s="117">
-        <f>M31/M6*365</f>
+        <f t="shared" si="84"/>
         <v>111.71121020193701</v>
       </c>
       <c r="N160" s="117">
-        <f>N31/N6*365</f>
+        <f t="shared" si="84"/>
         <v>133.38012600862163</v>
       </c>
       <c r="O160" s="117">
-        <f>O31/O6*365</f>
+        <f t="shared" si="84"/>
         <v>124.89943721745549</v>
       </c>
       <c r="P160" s="117">
-        <f>P31/P6*365</f>
+        <f t="shared" si="84"/>
         <v>124.51812283253162</v>
       </c>
       <c r="Q160" s="117">
-        <f>Q31/Q6*365</f>
+        <f t="shared" si="84"/>
         <v>122.99350310342828</v>
       </c>
       <c r="T160" s="117">
-        <f t="shared" ref="T160:AA160" si="85">T31/T6*365</f>
+        <f t="shared" ref="T160:AA160" si="86">T31/T6*365</f>
         <v>495.30050687907317</v>
       </c>
       <c r="U160" s="117">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>390.06201825108536</v>
       </c>
       <c r="V160" s="117">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>513.17081604425994</v>
       </c>
       <c r="W160" s="117">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>560.6710444027517</v>
       </c>
       <c r="X160" s="117">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>445.70194268541377</v>
       </c>
       <c r="Y160" s="117">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>497.15293420272673</v>
       </c>
       <c r="Z160" s="117">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>485.6912152101707</v>
       </c>
       <c r="AA160" s="117">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>551.09234507897929</v>
       </c>
       <c r="AC160" s="117">
@@ -29586,35 +29557,35 @@
         <v>104.6154069261558</v>
       </c>
       <c r="T161" s="117">
-        <f t="shared" ref="T161:AA161" si="86">T37/T6*90</f>
+        <f t="shared" ref="T161:AA161" si="87">T37/T6*90</f>
         <v>104.46777697320782</v>
       </c>
       <c r="U161" s="117">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>88.301585895277753</v>
       </c>
       <c r="V161" s="117">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>130.24896265560164</v>
       </c>
       <c r="W161" s="117">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>122.65666041275797</v>
       </c>
       <c r="X161" s="117">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>103.03101856820865</v>
       </c>
       <c r="Y161" s="117">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>109.55779490219324</v>
       </c>
       <c r="Z161" s="117">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>101.86462031840568</v>
       </c>
       <c r="AA161" s="117">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>78.287970838396106</v>
       </c>
       <c r="AC161" s="117">
@@ -29631,55 +29602,55 @@
         <v>95.814435590545941</v>
       </c>
       <c r="N162" s="117">
-        <f t="shared" ref="N162:Q162" si="87">N159+N160-N161</f>
+        <f t="shared" ref="N162:Q162" si="88">N159+N160-N161</f>
         <v>60.527531293223674</v>
       </c>
       <c r="O162" s="117">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>51.577931952498773</v>
       </c>
       <c r="P162" s="117">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>20.252214534532527</v>
       </c>
       <c r="Q162" s="117">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>44.890025490651112</v>
       </c>
       <c r="T162" s="117">
-        <f t="shared" ref="T162" si="88">T159+T160-T161</f>
+        <f t="shared" ref="T162" si="89">T159+T160-T161</f>
         <v>412.79096258723371</v>
       </c>
       <c r="U162" s="117">
-        <f t="shared" ref="U162" si="89">U159+U160-U161</f>
+        <f t="shared" ref="U162" si="90">U159+U160-U161</f>
         <v>322.90541880567213</v>
       </c>
       <c r="V162" s="117">
-        <f t="shared" ref="V162" si="90">V159+V160-V161</f>
+        <f t="shared" ref="V162" si="91">V159+V160-V161</f>
         <v>404.87276502961197</v>
       </c>
       <c r="W162" s="117">
-        <f t="shared" ref="W162" si="91">W159+W160-W161</f>
+        <f t="shared" ref="W162" si="92">W159+W160-W161</f>
         <v>459.78433741227212</v>
       </c>
       <c r="X162" s="117">
-        <f t="shared" ref="X162" si="92">X159+X160-X161</f>
+        <f t="shared" ref="X162" si="93">X159+X160-X161</f>
         <v>359.18853823960967</v>
       </c>
       <c r="Y162" s="117">
-        <f t="shared" ref="Y162" si="93">Y159+Y160-Y161</f>
+        <f t="shared" ref="Y162" si="94">Y159+Y160-Y161</f>
         <v>408.70258821286052</v>
       </c>
       <c r="Z162" s="117">
-        <f t="shared" ref="Z162:AA162" si="94">Z159+Z160-Z161</f>
+        <f t="shared" ref="Z162:AA162" si="95">Z159+Z160-Z161</f>
         <v>409.09425614670141</v>
       </c>
       <c r="AA162" s="117">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>499.75730935143241</v>
       </c>
       <c r="AC162" s="117">
-        <f t="shared" ref="AC162" si="95">AC159+AC160-AC161</f>
+        <f t="shared" ref="AC162" si="96">AC159+AC160-AC161</f>
         <v>82.9857136586363</v>
       </c>
     </row>
@@ -29708,35 +29679,35 @@
         <v>0.40763556496705489</v>
       </c>
       <c r="T163" s="117">
-        <f t="shared" ref="T163:AA163" si="96">T121/T48</f>
+        <f t="shared" ref="T163:AA163" si="97">T121/T48</f>
         <v>0.46020533025540444</v>
       </c>
       <c r="U163" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.50472209942531043</v>
       </c>
       <c r="V163" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.50378764984386015</v>
       </c>
       <c r="W163" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.50273667749308315</v>
       </c>
       <c r="X163" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.51854765383161527</v>
       </c>
       <c r="Y163" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.43762690832518614</v>
       </c>
       <c r="Z163" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.40763556496705489</v>
       </c>
       <c r="AA163" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.40424978005996731</v>
       </c>
       <c r="AC163" s="117">
@@ -29769,35 +29740,35 @@
         <v>8.0232059572457368E-2</v>
       </c>
       <c r="T164" s="181">
-        <f t="shared" ref="T164:AA164" si="97">(T121-T120)/T48</f>
+        <f t="shared" ref="T164:AA164" si="98">(T121-T120)/T48</f>
         <v>0.20616337901049214</v>
       </c>
       <c r="U164" s="181">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.26272957440823053</v>
       </c>
       <c r="V164" s="181">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.28154528054800038</v>
       </c>
       <c r="W164" s="181">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.29174185011427883</v>
       </c>
       <c r="X164" s="181">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.30190124945087504</v>
       </c>
       <c r="Y164" s="181">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.1468188313153343</v>
       </c>
       <c r="Z164" s="181">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>8.0232059572457368E-2</v>
       </c>
       <c r="AA164" s="181">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.10989819918487531</v>
       </c>
       <c r="AC164" s="181">
@@ -29830,35 +29801,35 @@
         <v>1.306571654790182</v>
       </c>
       <c r="T165" s="117">
-        <f t="shared" ref="T165:AA165" si="98">(T120+T30)/T39</f>
+        <f t="shared" ref="T165:AA165" si="99">(T120+T30)/T39</f>
         <v>1.0117713179504793</v>
       </c>
       <c r="U165" s="117">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.77382746949571946</v>
       </c>
       <c r="V165" s="117">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.71608815118039593</v>
       </c>
       <c r="W165" s="117">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.7494250015540499</v>
       </c>
       <c r="X165" s="117">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.67396899845564262</v>
       </c>
       <c r="Y165" s="117">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1.0569712357184877</v>
       </c>
       <c r="Z165" s="117">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1.306571654790182</v>
       </c>
       <c r="AA165" s="117">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1.3708387576715642</v>
       </c>
       <c r="AC165" s="117">
@@ -29891,35 +29862,35 @@
         <v>2.0170387965162311</v>
       </c>
       <c r="T166" s="117">
-        <f t="shared" ref="T166:AA166" si="99">T32/T39</f>
+        <f t="shared" ref="T166:AA166" si="100">T32/T39</f>
         <v>1.5870671620819934</v>
       </c>
       <c r="U166" s="117">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1.3122386871071419</v>
       </c>
       <c r="V166" s="117">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1.3268659227275277</v>
       </c>
       <c r="W166" s="117">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1.3095667309007273</v>
       </c>
       <c r="X166" s="117">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1.2404907624549562</v>
       </c>
       <c r="Y166" s="117">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>1.6017277146484195</v>
       </c>
       <c r="Z166" s="117">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>2.0170387965162311</v>
       </c>
       <c r="AA166" s="117">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>2.3119583410823878</v>
       </c>
       <c r="AC166" s="117">
@@ -29952,35 +29923,35 @@
         <v>N/A</v>
       </c>
       <c r="T167" s="183" t="str">
-        <f t="shared" ref="T167:AA167" si="100">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T167:AA167" si="101">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U167" s="183" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
       <c r="V167" s="183" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
       <c r="W167" s="183" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
       <c r="X167" s="183" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
       <c r="Y167" s="183" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
       <c r="Z167" s="183">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>5.9793814432989691</v>
       </c>
       <c r="AA167" s="183" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
       <c r="AC167" s="183" t="str">
@@ -30022,7 +29993,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="71">
         <f ca="1">AC130/Statement!AC26</f>
-        <v>-179.49193548387098</v>
+        <v>-181.79032258064515</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -30059,7 +30030,7 @@
       <c r="AA169" s="49"/>
       <c r="AC169" s="71">
         <f ca="1">AC130/(Statement!AC5/Statement!AC22)</f>
-        <v>9.7399990234919915</v>
+        <v>9.8647193236984538</v>
       </c>
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
@@ -30096,7 +30067,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="71">
         <f ca="1">AC130/(Statement!AC48/Statement!AC74)</f>
-        <v>5.0210820151893278</v>
+        <v>5.085376770741691</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -30133,7 +30104,7 @@
       <c r="AA171" s="49"/>
       <c r="AC171" s="143">
         <f ca="1">Statement!AC130*Statement!AC77</f>
-        <v>559318.41</v>
+        <v>566480.46</v>
       </c>
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
@@ -30170,7 +30141,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="143">
         <f ca="1">AC171+AC121-AC120+AC47+AC44</f>
-        <v>585155.41</v>
+        <v>592317.46</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -30207,7 +30178,7 @@
       <c r="AA173" s="49"/>
       <c r="AC173" s="185">
         <f ca="1">AC172/AC5</f>
-        <v>10.883979874634973</v>
+        <v>11.017195096999794</v>
       </c>
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
@@ -30244,7 +30215,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="185">
         <f ca="1">AC172/AC12</f>
-        <v>-115.89530798177857</v>
+        <v>-117.313816597346</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -30272,35 +30243,35 @@
         <v>-7383</v>
       </c>
       <c r="T175" s="63">
-        <f t="shared" ref="T175:AA175" si="101">T58-T53+T123+T64</f>
+        <f t="shared" ref="T175:AA175" si="102">T58-T53+T123+T64</f>
         <v>0</v>
       </c>
       <c r="U175" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="V175" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="W175" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-5054</v>
       </c>
       <c r="X175" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-2164</v>
       </c>
       <c r="Y175" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-427</v>
       </c>
       <c r="Z175" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>262</v>
       </c>
       <c r="AA175" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>-3161</v>
       </c>
       <c r="AC175" s="63">
@@ -30317,19 +30288,19 @@
         <v>5461.985025111735</v>
       </c>
       <c r="N176" s="63">
-        <f t="shared" ref="N176:Q176" si="102">N122+N52+N123+N54+N56+N57+N55</f>
+        <f t="shared" ref="N176:Q176" si="103">N122+N52+N123+N54+N56+N57+N55</f>
         <v>-13983</v>
       </c>
       <c r="O176" s="63">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-16624</v>
       </c>
       <c r="P176" s="63">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-23140</v>
       </c>
       <c r="Q176" s="63">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>-6901</v>
       </c>
       <c r="T176" s="49"/>
@@ -30354,19 +30325,19 @@
         <v>24.234480257856571</v>
       </c>
       <c r="N177" s="71">
-        <f t="shared" ref="N177:Q177" si="103">N171/N175</f>
+        <f t="shared" ref="N177:Q177" si="104">N171/N175</f>
         <v>-8.7516835473323233</v>
       </c>
       <c r="O177" s="71">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-12.197995202193283</v>
       </c>
       <c r="P177" s="71">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-4.6102486100912623</v>
       </c>
       <c r="Q177" s="71">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>-24.491263713937425</v>
       </c>
       <c r="T177" s="49"/>
@@ -30378,8 +30349,8 @@
       <c r="Z177" s="49"/>
       <c r="AA177" s="49"/>
       <c r="AC177" s="71">
-        <f t="shared" ref="AC177:AC178" ca="1" si="104">AC171/AC175</f>
-        <v>-101.8794918032787</v>
+        <f t="shared" ref="AC177:AC178" ca="1" si="105">AC171/AC175</f>
+        <v>-103.18405464480874</v>
       </c>
     </row>
     <row r="178" spans="2:29" x14ac:dyDescent="0.2">
@@ -30391,19 +30362,19 @@
         <v>40.317380766801932</v>
       </c>
       <c r="N178" s="71">
-        <f t="shared" ref="N178:Q178" si="105">N172/N176</f>
+        <f t="shared" ref="N178:Q178" si="106">N172/N176</f>
         <v>-8.9618365157691464</v>
       </c>
       <c r="O178" s="71">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>-14.56746270452358</v>
       </c>
       <c r="P178" s="71">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>-5.255401901469317</v>
       </c>
       <c r="Q178" s="71">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>-29.280828865381828</v>
       </c>
       <c r="T178" s="49"/>
@@ -30415,8 +30386,8 @@
       <c r="Z178" s="49"/>
       <c r="AA178" s="49"/>
       <c r="AC178" s="71">
-        <f t="shared" ca="1" si="104"/>
-        <v>-68.255617636766601</v>
+        <f t="shared" ca="1" si="105"/>
+        <v>-69.091036976554292</v>
       </c>
     </row>
     <row r="179" spans="2:29" x14ac:dyDescent="0.2">
@@ -30428,19 +30399,19 @@
         <v>4.1263521617131038E-2</v>
       </c>
       <c r="N179" s="73">
-        <f t="shared" ref="N179:Q179" si="106">N175/N171</f>
+        <f t="shared" ref="N179:Q179" si="107">N175/N171</f>
         <v>-0.11426372932609277</v>
       </c>
       <c r="O179" s="73">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>-8.1980684811237922E-2</v>
       </c>
       <c r="P179" s="73">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>-0.21690804218478027</v>
       </c>
       <c r="Q179" s="73">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>-4.0830886134753538E-2</v>
       </c>
       <c r="T179" s="49"/>
@@ -30452,8 +30423,8 @@
       <c r="Z179" s="49"/>
       <c r="AA179" s="49"/>
       <c r="AC179" s="73">
-        <f t="shared" ref="AC179" ca="1" si="107">AC175/AC171</f>
-        <v>-9.8155181410889015E-3</v>
+        <f t="shared" ref="AC179" ca="1" si="108">AC175/AC171</f>
+        <v>-9.6914198946950452E-3</v>
       </c>
     </row>
     <row r="180" spans="2:29" x14ac:dyDescent="0.2">
@@ -30465,19 +30436,19 @@
         <v>9.471837848372637E-2</v>
       </c>
       <c r="N180" s="73">
-        <f t="shared" ref="N180:Q180" si="108">N26/N130</f>
+        <f t="shared" ref="N180:Q180" si="109">N26/N130</f>
         <v>7.3401437760121077E-2</v>
       </c>
       <c r="O180" s="73">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>7.9601990049751256E-3</v>
       </c>
       <c r="P180" s="73">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>-0.21576354679802953</v>
       </c>
       <c r="Q180" s="73">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>-1.6574585635359114E-3</v>
       </c>
       <c r="T180" s="49"/>
@@ -30489,8 +30460,8 @@
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
       <c r="AC180" s="73">
-        <f t="shared" ref="AC180" ca="1" si="109">AC26/AC130</f>
-        <v>-5.5712809453205732E-3</v>
+        <f t="shared" ref="AC180" ca="1" si="110">AC26/AC130</f>
+        <v>-5.5008428710850857E-3</v>
       </c>
     </row>
     <row r="181" spans="2:29" x14ac:dyDescent="0.2">
@@ -30502,19 +30473,19 @@
         <v>2.7090235821477293E-2</v>
       </c>
       <c r="N181" s="154">
-        <f t="shared" ref="N181:Q181" si="110">N81/N130</f>
+        <f t="shared" ref="N181:Q181" si="111">N81/N130</f>
         <v>5.5240257283390083E-2</v>
       </c>
       <c r="O181" s="154">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>1.472636815920398E-2</v>
       </c>
       <c r="P181" s="154">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>1.8719211822660099E-2</v>
       </c>
       <c r="Q181" s="154">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="T181" s="49"/>
@@ -30526,7 +30497,7 @@
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
       <c r="AC181" s="154">
-        <f t="shared" ref="AC181" ca="1" si="111">AC81/AC130</f>
+        <f t="shared" ref="AC181" ca="1" si="112">AC81/AC130</f>
         <v>0</v>
       </c>
     </row>
@@ -30814,35 +30785,35 @@
         <v>7.4906906906906903</v>
       </c>
       <c r="T189" s="71">
-        <f t="shared" ref="T189:AA189" si="112">T120/T74</f>
+        <f t="shared" ref="T189:AA189" si="113">T120/T74</f>
         <v>6.8458840037418147</v>
       </c>
       <c r="U189" s="71">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>5.5845119406445631</v>
       </c>
       <c r="V189" s="71">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>5.0951501154734409</v>
       </c>
       <c r="W189" s="71">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>4.825309491059147</v>
       </c>
       <c r="X189" s="71">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>4.8448709161526162</v>
       </c>
       <c r="Y189" s="71">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>6.4853249475890982</v>
       </c>
       <c r="Z189" s="71">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>7.4906906906906903</v>
       </c>
       <c r="AA189" s="71">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>6.5238758456028654</v>
       </c>
       <c r="AC189" s="71">
@@ -30875,27 +30846,27 @@
         <v>0.25100546560791998</v>
       </c>
       <c r="T190" s="154" t="e">
-        <f t="shared" ref="T190:Y190" si="113">T53/T58</f>
+        <f t="shared" ref="T190:Y190" si="114">T53/T58</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U190" s="154" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V190" s="154" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W190" s="154">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.84132841328413288</v>
       </c>
       <c r="X190" s="154">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.32390243902439025</v>
       </c>
       <c r="Y190" s="154">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.2152395915161037</v>
       </c>
       <c r="Z190" s="154">
@@ -30936,27 +30907,27 @@
         <v>4.6052258149963103E-2</v>
       </c>
       <c r="T191" s="154">
-        <f t="shared" ref="T191:Y191" si="114">T53/T5</f>
+        <f t="shared" ref="T191:Y191" si="115">T53/T5</f>
         <v>0</v>
       </c>
       <c r="U191" s="154">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="V191" s="154">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="W191" s="154">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>5.3998578984763561E-2</v>
       </c>
       <c r="X191" s="154">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>5.1636985768722297E-2</v>
       </c>
       <c r="Y191" s="154">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>4.0137698674284038E-2</v>
       </c>
       <c r="Z191" s="154">
@@ -30997,35 +30968,35 @@
         <v>-1.8356356356356356</v>
       </c>
       <c r="T192" s="71">
-        <f t="shared" ref="T192:AA192" si="115">(T120-T121)/T74</f>
+        <f t="shared" ref="T192:AA192" si="116">(T120-T121)/T74</f>
         <v>-5.5556594948550044</v>
       </c>
       <c r="U192" s="71">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-6.06306515186645</v>
       </c>
       <c r="V192" s="71">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-6.4547344110854503</v>
       </c>
       <c r="W192" s="71">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-6.6719394773039893</v>
       </c>
       <c r="X192" s="71">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-6.7514279186657529</v>
       </c>
       <c r="Y192" s="71">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-3.2742138364779874</v>
       </c>
       <c r="Z192" s="71">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-1.8356356356356356</v>
       </c>
       <c r="AA192" s="71">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-2.435734182252288</v>
       </c>
       <c r="AC192" s="71">
@@ -31067,7 +31038,7 @@
       <c r="AA193" s="49"/>
       <c r="AC193" s="154">
         <f ca="1">(AC120-AC121)/AC171</f>
-        <v>-2.1887353931368002E-2</v>
+        <v>-2.1610630665001226E-2</v>
       </c>
     </row>
     <row r="194" spans="2:29" x14ac:dyDescent="0.2">
@@ -31095,35 +31066,35 @@
         <v>0.27710820577829071</v>
       </c>
       <c r="T194" s="154">
-        <f t="shared" ref="T194:AA194" si="116">-T123/T5</f>
+        <f t="shared" ref="T194:AA194" si="117">-T123/T5</f>
         <v>0</v>
       </c>
       <c r="U194" s="154">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="V194" s="154">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="W194" s="154">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.40917344280413676</v>
       </c>
       <c r="X194" s="154">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.27607123415506651</v>
       </c>
       <c r="Y194" s="154">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.17761664103127517</v>
       </c>
       <c r="Z194" s="154">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.25508263858417435</v>
       </c>
       <c r="AA194" s="154">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.2678058481255064</v>
       </c>
       <c r="AC194" s="154">
@@ -31156,27 +31127,27 @@
         <v>1.5103640301124059</v>
       </c>
       <c r="T195" s="154" t="e">
-        <f t="shared" ref="T195:Y195" si="117">-(T123/T58)</f>
+        <f t="shared" ref="T195:Y195" si="118">-(T123/T58)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U195" s="154" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V195" s="154" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W195" s="154">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>6.375153751537515</v>
       </c>
       <c r="X195" s="154">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>1.7317073170731707</v>
       </c>
       <c r="Y195" s="154">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.95247446975648076</v>
       </c>
       <c r="Z195" s="154">
@@ -31217,27 +31188,27 @@
         <v>1.2511532547411583</v>
       </c>
       <c r="T196" s="154" t="e">
-        <f t="shared" ref="T196:Y196" si="118">-T123/T52</f>
+        <f t="shared" ref="T196:Y196" si="119">-T123/T52</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U196" s="154" t="e">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V196" s="154" t="e">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W196" s="154">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>1.9382946896035902</v>
       </c>
       <c r="X196" s="154">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>1.1782276800531033</v>
       </c>
       <c r="Y196" s="154">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.81049465240641716</v>
       </c>
       <c r="Z196" s="154">
@@ -31300,61 +31271,61 @@
       <c r="K200" s="80"/>
       <c r="L200" s="80"/>
       <c r="M200" s="80">
-        <f t="shared" ref="M200:Q204" si="119">IF(L105=0,
+        <f t="shared" ref="M200:Q204" si="120">IF(L105=0,
 IF(M105=0,0,IF(M105&gt;0,1,-1)),
 (M105-L105)/ABS(L105)
 )</f>
         <v>1</v>
       </c>
       <c r="N200" s="80">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>-0.22657676298045326</v>
       </c>
       <c r="O200" s="80">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>-7.9155257608661447E-2</v>
       </c>
       <c r="P200" s="80">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.139722469068289</v>
       </c>
       <c r="Q200" s="80">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>-3.3527259641336293E-2</v>
       </c>
       <c r="T200" s="80">
-        <f t="shared" ref="T200:AA204" si="120">IF(S105=0,
+        <f t="shared" ref="T200:AA204" si="121">IF(S105=0,
 IF(T105=0,0,IF(T105&gt;0,1,-1)),
 (T105-S105)/ABS(S105)
 )</f>
         <v>1</v>
       </c>
       <c r="U200" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>2.2104875353063983E-3</v>
       </c>
       <c r="V200" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>7.4500673937017522E-2</v>
       </c>
       <c r="W200" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-0.13000342114266164</v>
       </c>
       <c r="X200" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>3.1721064359680168E-2</v>
       </c>
       <c r="Y200" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>8.436030999872951E-2</v>
       </c>
       <c r="Z200" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-4.0070298769771528E-2</v>
       </c>
       <c r="AA200" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-5.687782253142927E-2</v>
       </c>
       <c r="AC200" s="49"/>
@@ -31364,55 +31335,55 @@
         <v>363</v>
       </c>
       <c r="M201" s="80">
-        <f t="shared" si="119"/>
-        <v>1</v>
-      </c>
-      <c r="N201" s="80">
-        <f t="shared" si="119"/>
-        <v>-8.4923946253162061E-2</v>
-      </c>
-      <c r="O201" s="80">
-        <f t="shared" si="119"/>
-        <v>-0.23547784878293962</v>
-      </c>
-      <c r="P201" s="80">
-        <f t="shared" si="119"/>
-        <v>-0.242779995304062</v>
-      </c>
-      <c r="Q201" s="80">
-        <f t="shared" si="119"/>
-        <v>4.9240310077519382E-2</v>
-      </c>
-      <c r="T201" s="80">
         <f t="shared" si="120"/>
         <v>1</v>
       </c>
+      <c r="N201" s="80">
+        <f t="shared" si="120"/>
+        <v>-8.4923946253162061E-2</v>
+      </c>
+      <c r="O201" s="80">
+        <f t="shared" si="120"/>
+        <v>-0.23547784878293962</v>
+      </c>
+      <c r="P201" s="80">
+        <f t="shared" si="120"/>
+        <v>-0.242779995304062</v>
+      </c>
+      <c r="Q201" s="80">
+        <f t="shared" si="120"/>
+        <v>4.9240310077519382E-2</v>
+      </c>
+      <c r="T201" s="80">
+        <f t="shared" si="121"/>
+        <v>1</v>
+      </c>
       <c r="U201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>8.8304862023653091E-2</v>
       </c>
       <c r="V201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>5.0712388312001935E-2</v>
       </c>
       <c r="W201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-5.1712250057458053E-2</v>
       </c>
       <c r="X201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-4.5322346097915654E-2</v>
       </c>
       <c r="Y201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>4.5189134298045192E-2</v>
       </c>
       <c r="Z201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15059509351469516</v>
       </c>
       <c r="AA201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>6.6497783407219763E-2</v>
       </c>
       <c r="AC201" s="49"/>
@@ -31422,55 +31393,55 @@
         <v>364</v>
       </c>
       <c r="M202" s="80">
-        <f t="shared" si="119"/>
-        <v>1</v>
-      </c>
-      <c r="N202" s="80">
-        <f t="shared" si="119"/>
-        <v>-0.16628914988814317</v>
-      </c>
-      <c r="O202" s="80">
-        <f t="shared" si="119"/>
-        <v>-0.1521793818236705</v>
-      </c>
-      <c r="P202" s="80">
-        <f t="shared" si="119"/>
-        <v>-2.1403279726227919E-2</v>
-      </c>
-      <c r="Q202" s="80">
-        <f t="shared" si="119"/>
-        <v>-6.5492915041135214E-3</v>
-      </c>
-      <c r="T202" s="80">
         <f t="shared" si="120"/>
         <v>1</v>
       </c>
+      <c r="N202" s="80">
+        <f t="shared" si="120"/>
+        <v>-0.16628914988814317</v>
+      </c>
+      <c r="O202" s="80">
+        <f t="shared" si="120"/>
+        <v>-0.1521793818236705</v>
+      </c>
+      <c r="P202" s="80">
+        <f t="shared" si="120"/>
+        <v>-2.1403279726227919E-2</v>
+      </c>
+      <c r="Q202" s="80">
+        <f t="shared" si="120"/>
+        <v>-6.5492915041135214E-3</v>
+      </c>
+      <c r="T202" s="80">
+        <f t="shared" si="121"/>
+        <v>1</v>
+      </c>
       <c r="U202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>2.9628389688650822E-2</v>
       </c>
       <c r="V202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>6.6493253129572424E-2</v>
       </c>
       <c r="W202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-0.10403963414634146</v>
       </c>
       <c r="X202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>4.6788600595491277E-3</v>
       </c>
       <c r="Y202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>7.1295512277730733E-2</v>
       </c>
       <c r="Z202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>2.1972810622826432E-2</v>
       </c>
       <c r="AA202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-1.1678267594740912E-2</v>
       </c>
       <c r="AC202" s="49"/>
@@ -31480,55 +31451,55 @@
         <v>365</v>
       </c>
       <c r="M203" s="80">
-        <f t="shared" si="119"/>
-        <v>1</v>
-      </c>
-      <c r="N203" s="80">
-        <f t="shared" si="119"/>
-        <v>0.35158501440922191</v>
-      </c>
-      <c r="O203" s="80">
-        <f t="shared" si="119"/>
-        <v>1.0298507462686568</v>
-      </c>
-      <c r="P203" s="80">
-        <f t="shared" si="119"/>
-        <v>17.190126050420169</v>
-      </c>
-      <c r="Q203" s="80">
-        <f t="shared" si="119"/>
-        <v>2.9393081942599757E-2</v>
-      </c>
-      <c r="T203" s="80">
         <f t="shared" si="120"/>
         <v>1</v>
       </c>
+      <c r="N203" s="80">
+        <f t="shared" si="120"/>
+        <v>0.35158501440922191</v>
+      </c>
+      <c r="O203" s="80">
+        <f t="shared" si="120"/>
+        <v>1.0298507462686568</v>
+      </c>
+      <c r="P203" s="80">
+        <f t="shared" si="120"/>
+        <v>17.190126050420169</v>
+      </c>
+      <c r="Q203" s="80">
+        <f t="shared" si="120"/>
+        <v>2.9393081942599757E-2</v>
+      </c>
+      <c r="T203" s="80">
+        <f t="shared" si="121"/>
+        <v>1</v>
+      </c>
       <c r="U203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>1.3311536665109761E-2</v>
       </c>
       <c r="V203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>2.3046784973496196E-4</v>
       </c>
       <c r="W203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>7.5345622119815672E-2</v>
       </c>
       <c r="X203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-5.3567602314120423E-2</v>
       </c>
       <c r="Y203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-4.1204437400950873E-2</v>
       </c>
       <c r="Z203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>6.4226682408500588E-2</v>
       </c>
       <c r="AA203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.2027956512092301</v>
       </c>
       <c r="AC203" s="49"/>
@@ -31538,55 +31509,55 @@
         <v>366</v>
       </c>
       <c r="M204" s="80">
-        <f t="shared" si="119"/>
-        <v>1</v>
-      </c>
-      <c r="N204" s="80">
-        <f t="shared" si="119"/>
-        <v>-0.58669833729216148</v>
-      </c>
-      <c r="O204" s="80">
-        <f t="shared" si="119"/>
-        <v>-7.9445571331981074E-2</v>
-      </c>
-      <c r="P204" s="80">
-        <f t="shared" si="119"/>
-        <v>0.32243848696290855</v>
-      </c>
-      <c r="Q204" s="80">
-        <f t="shared" si="119"/>
-        <v>-1.0552624271035824E-2</v>
-      </c>
-      <c r="T204" s="80">
         <f t="shared" si="120"/>
         <v>1</v>
       </c>
+      <c r="N204" s="80">
+        <f t="shared" si="120"/>
+        <v>-0.58669833729216148</v>
+      </c>
+      <c r="O204" s="80">
+        <f t="shared" si="120"/>
+        <v>-7.9445571331981074E-2</v>
+      </c>
+      <c r="P204" s="80">
+        <f t="shared" si="120"/>
+        <v>0.32243848696290855</v>
+      </c>
+      <c r="Q204" s="80">
+        <f t="shared" si="120"/>
+        <v>-1.0552624271035824E-2</v>
+      </c>
+      <c r="T204" s="80">
+        <f t="shared" si="121"/>
+        <v>1</v>
+      </c>
       <c r="U204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>9.4211123723041995E-2</v>
       </c>
       <c r="V204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.1545643153526971</v>
       </c>
       <c r="W204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-0.1527403414195867</v>
       </c>
       <c r="X204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.11664899257688228</v>
       </c>
       <c r="Y204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-5.6980056980056981E-2</v>
       </c>
       <c r="Z204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>-0.42195367573011078</v>
       </c>
       <c r="AA204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>9.4076655052264813E-2</v>
       </c>
       <c r="AC204" s="49"/>
@@ -31749,7 +31720,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>111.285</v>
+        <v>112.71</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -31765,7 +31736,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC171</f>
-        <v>559318.41</v>
+        <v>566480.46</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -31785,7 +31756,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC172</f>
-        <v>585155.41</v>
+        <v>592317.46</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -31805,7 +31776,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC168</f>
-        <v>-179.49193548387098</v>
+        <v>-181.79032258064515</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>246</v>
@@ -31825,7 +31796,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC169</f>
-        <v>9.7399990234919915</v>
+        <v>9.8647193236984538</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>247</v>
@@ -31845,7 +31816,7 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC170</f>
-        <v>5.0210820151893278</v>
+        <v>5.085376770741691</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -31865,7 +31836,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC173</f>
-        <v>10.883979874634973</v>
+        <v>11.017195096999794</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -31874,7 +31845,7 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC174</f>
-        <v>-115.89530798177857</v>
+        <v>-117.313816597346</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -32110,7 +32081,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC180</f>
-        <v>-5.5712809453205732E-3</v>
+        <v>-5.5008428710850857E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -32126,7 +32097,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC179</f>
-        <v>-9.8155181410889015E-3</v>
+        <v>-9.6914198946950452E-3</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -32211,7 +32182,7 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC193</f>
-        <v>-2.1887353931368002E-2</v>
+        <v>-2.1610630665001226E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -32390,7 +32361,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC129</f>
-        <v>111.285</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32419,7 +32390,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC171</f>
-        <v>559318.41</v>
+        <v>566480.46</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32448,7 +32419,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC172</f>
-        <v>585155.41</v>
+        <v>592317.46</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -32477,7 +32448,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC168</f>
-        <v>-179.49193548387098</v>
+        <v>-181.79032258064515</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -32506,7 +32477,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC169</f>
-        <v>9.7399990234919915</v>
+        <v>9.8647193236984538</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -32535,7 +32506,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC170</f>
-        <v>5.0210820151893278</v>
+        <v>5.085376770741691</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -32564,7 +32535,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC173</f>
-        <v>10.883979874634973</v>
+        <v>11.017195096999794</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -32593,7 +32564,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC174</f>
-        <v>-115.89530798177857</v>
+        <v>-117.313816597346</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33366,7 +33337,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC180</f>
-        <v>-5.5712809453205732E-3</v>
+        <v>-5.5008428710850857E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33395,7 +33366,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC179</f>
-        <v>-9.8155181410889015E-3</v>
+        <v>-9.6914198946950452E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33718,7 +33689,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC193</f>
-        <v>-2.1887353931368002E-2</v>
+        <v>-2.1610630665001226E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34256,14 +34227,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="234" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="F3" s="234" t="s">
+      <c r="D3" s="235"/>
+      <c r="F3" s="236" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="233"/>
+      <c r="G3" s="235"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -34330,19 +34301,19 @@
       <c r="B7" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="235">
+      <c r="C7" s="232">
         <f>Statement!AA88</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="236"/>
-      <c r="F7" s="235">
+      <c r="D7" s="233"/>
+      <c r="F7" s="232">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="236"/>
+      <c r="G7" s="233"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -34369,19 +34340,19 @@
       <c r="B9" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="235">
+      <c r="C9" s="232">
         <f>Statement!AA89</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="F9" s="235">
+      <c r="D9" s="233"/>
+      <c r="F9" s="232">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="236"/>
+      <c r="G9" s="233"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -34408,19 +34379,19 @@
       <c r="B11" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="235">
+      <c r="C11" s="232">
         <f>Statement!AA90</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="236"/>
-      <c r="F11" s="235">
+      <c r="D11" s="233"/>
+      <c r="F11" s="232">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="236"/>
+      <c r="G11" s="233"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -34447,19 +34418,19 @@
       <c r="B13" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="235">
+      <c r="C13" s="232">
         <f>Statement!AA94</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="236"/>
-      <c r="F13" s="235">
+      <c r="D13" s="233"/>
+      <c r="F13" s="232">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="236"/>
+      <c r="G13" s="233"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -34486,19 +34457,19 @@
       <c r="B15" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="235">
+      <c r="C15" s="232">
         <f>Statement!AA95</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="236"/>
-      <c r="F15" s="235">
+      <c r="D15" s="233"/>
+      <c r="F15" s="232">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="236"/>
+      <c r="G15" s="233"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -34525,19 +34496,19 @@
       <c r="B17" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="235">
+      <c r="C17" s="232">
         <f>Statement!AA97</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="236"/>
-      <c r="F17" s="235">
+      <c r="D17" s="233"/>
+      <c r="F17" s="232">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="236"/>
+      <c r="G17" s="233"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -34564,22 +34535,22 @@
       <c r="B19" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="235">
+      <c r="C19" s="232">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="236"/>
-      <c r="F19" s="235">
+      <c r="D19" s="233"/>
+      <c r="F19" s="232">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="236"/>
+      <c r="G19" s="233"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -34606,22 +34577,22 @@
       <c r="B21" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="235">
+      <c r="C21" s="232">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="236"/>
-      <c r="F21" s="235">
+      <c r="D21" s="233"/>
+      <c r="F21" s="232">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="236"/>
+      <c r="G21" s="233"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -34669,22 +34640,22 @@
       <c r="B25" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="235">
+      <c r="C25" s="232">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="236"/>
-      <c r="F25" s="235">
+      <c r="D25" s="233"/>
+      <c r="F25" s="232">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="236"/>
+      <c r="G25" s="233"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -34711,22 +34682,22 @@
       <c r="B27" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="235">
+      <c r="C27" s="232">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="236"/>
-      <c r="F27" s="235">
+      <c r="D27" s="233"/>
+      <c r="F27" s="232">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="236"/>
+      <c r="G27" s="233"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -34753,22 +34724,22 @@
       <c r="B29" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="235">
+      <c r="C29" s="232">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="236"/>
-      <c r="F29" s="235">
+      <c r="D29" s="233"/>
+      <c r="F29" s="232">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="236"/>
+      <c r="G29" s="233"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34795,22 +34766,22 @@
       <c r="B31" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="235">
+      <c r="C31" s="232">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="236"/>
-      <c r="F31" s="235">
+      <c r="D31" s="233"/>
+      <c r="F31" s="232">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="236"/>
+      <c r="G31" s="233"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -34837,25 +34808,37 @@
       <c r="B33" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="235">
+      <c r="C33" s="232">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="236"/>
-      <c r="F33" s="235">
+      <c r="D33" s="233"/>
+      <c r="F33" s="232">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="236"/>
+      <c r="G33" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -34872,18 +34855,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827F1DB6-3DE9-3540-B461-125F6B35ED3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD78E10F-6111-134C-8080-3241887127FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2248,12 +2248,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2261,6 +2255,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11693,11 +11693,11 @@
     <v>Powered by Refinitiv</v>
     <v>132.75</v>
     <v>18.965</v>
-    <v>2.2317999999999998</v>
-    <v>4.78</v>
-    <v>4.4288000000000001E-2</v>
-    <v>-1.89</v>
-    <v>-1.6768999999999999E-2</v>
+    <v>2.2513000000000001</v>
+    <v>-12.61</v>
+    <v>-0.11281100000000001</v>
+    <v>-2.2450999999999999</v>
+    <v>-2.2638999999999999E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -11705,25 +11705,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>118.29</v>
+    <v>106.48</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46176.925423043751</v>
+    <v>46178.999997430466</v>
     <v>0</v>
-    <v>110.86</v>
-    <v>566480460000</v>
+    <v>98.33</v>
+    <v>498428420000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>116.42</v>
+    <v>106.48</v>
     <v>0</v>
-    <v>107.93</v>
-    <v>112.71</v>
-    <v>110.82</v>
+    <v>111.78</v>
+    <v>99.17</v>
+    <v>96.924899999999994</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>118418472</v>
-    <v>145048030</v>
+    <v>145209405</v>
+    <v>137584440</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -11747,17 +11747,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.2</v>
-    <v>-4.4689999999999999E-3</v>
+    <v>0.59</v>
+    <v>1.3178E-2</v>
     <v>US</v>
-    <v>44.63</v>
+    <v>45.54</v>
     <v>Index</v>
     <v>3</v>
-    <v>44.28</v>
+    <v>44.65</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.3</v>
-    <v>44.75</v>
-    <v>44.55</v>
+    <v>44.67</v>
+    <v>44.77</v>
+    <v>45.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -11979,9 +11979,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="F3" s="189">
         <f ca="1">Statement!AC171</f>
-        <v>566480.46</v>
+        <v>498428.42</v>
       </c>
       <c r="H3" s="187" t="str">
         <f>'AVG target price'!B5</f>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="I3" s="213">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-8.8046952175618021</v>
+        <v>-8.7808283251417247</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F4" s="190">
         <f ca="1">Statement!AC172</f>
-        <v>592317.46</v>
+        <v>524265.41999999993</v>
       </c>
       <c r="H4" s="187" t="str">
         <f>'AVG target price'!B6</f>
@@ -12613,7 +12613,7 @@
       </c>
       <c r="I4" s="213">
         <f ca="1">'AVG target price'!C6</f>
-        <v>32.321232777928991</v>
+        <v>32.235530728427833</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="C5" s="210" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>112.71</v>
+        <v>99.17</v>
       </c>
       <c r="E5" s="187" t="s">
         <v>246</v>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="I5" s="213">
         <f ca="1">'AVG target price'!C7</f>
-        <v>36.468980651241303</v>
+        <v>36.372280552996166</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -12646,14 +12646,14 @@
       </c>
       <c r="C6" s="210" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>110.82</v>
+        <v>96.924899999999994</v>
       </c>
       <c r="E6" s="187" t="s">
         <v>240</v>
       </c>
       <c r="F6" s="192">
         <f ca="1">Statement!AC168</f>
-        <v>-181.79032258064515</v>
+        <v>-159.95161290322582</v>
       </c>
       <c r="H6" s="187" t="str">
         <f>'AVG target price'!B8</f>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="I6" s="213">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-10.984571681463171</v>
+        <v>-10.955445307711837</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -12670,14 +12670,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>4.78</v>
+        <v>-12.61</v>
       </c>
       <c r="E7" s="188" t="s">
         <v>197</v>
       </c>
       <c r="F7" s="193">
         <f ca="1">Statement!AC169</f>
-        <v>9.8647193236984538</v>
+        <v>8.6796576641928471</v>
       </c>
       <c r="H7" s="186" t="str">
         <f>'AVG target price'!B9</f>
@@ -12685,7 +12685,7 @@
       </c>
       <c r="I7" s="214">
         <f ca="1">'AVG target price'!C9</f>
-        <v>12.25023663253633</v>
+        <v>12.21788441214261</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -12694,14 +12694,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.89</v>
+        <v>-2.2450999999999999</v>
       </c>
       <c r="E8" s="187" t="s">
         <v>268</v>
       </c>
       <c r="F8" s="194">
         <f ca="1">Statement!AC179</f>
-        <v>-9.6914198946950452E-3</v>
+        <v>-1.1014620715247336E-2</v>
       </c>
       <c r="H8" s="186" t="str">
         <f>'AVG target price'!B11</f>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="I8" s="215">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.8913118921787212</v>
+        <v>-0.87679858412682654</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12718,14 +12718,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.4288000000000001E-2</v>
+        <v>-0.11281100000000001</v>
       </c>
       <c r="E9" s="187" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC180</f>
-        <v>-5.5008428710850857E-3</v>
+        <v>-6.2518906927498232E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.6768999999999999E-2</v>
+        <v>-2.2638999999999999E-2</v>
       </c>
       <c r="E10" s="187" t="s">
         <v>297</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C13" s="211" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2317999999999998</v>
+        <v>2.2513000000000001</v>
       </c>
       <c r="E13" s="187" t="s">
         <v>99</v>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="C14" s="212" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>145048030</v>
+        <v>137584440</v>
       </c>
       <c r="E14" s="188" t="s">
         <v>100</v>
@@ -12814,7 +12814,7 @@
       </c>
       <c r="F15" s="194">
         <f ca="1">Statement!AC193</f>
-        <v>-2.1610630665001226E-2</v>
+        <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="F26" s="226" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.55</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="F27" s="227">
         <f ca="1">F26/1000</f>
-        <v>4.4549999999999999E-2</v>
+        <v>4.5359999999999998E-2</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -17358,12 +17358,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -17371,6 +17365,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18430,16 +18430,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>112.71</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>566480.46</v>
+        <v>498428.42</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.4549999999999999E-2</v>
+        <v>4.5359999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.2317999999999998</v>
+        <v>2.2513000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.3638848894180986E-2</v>
+        <v>8.285991252115936E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92636115110581896</v>
+        <v>0.91714008747884079</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.144981</v>
+        <v>0.14666849999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13744619934229851</v>
+        <v>0.13805036478854302</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23274.223920113993</v>
+        <v>-23155.109659807575</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -18950,23 +18950,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6493.7941565070196</v>
+        <v>-6490.3467466508528</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5057.0750662070459</v>
+        <v>-5051.7071157001965</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3564.2605764441973</v>
+        <v>-3558.5870311676535</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3263.5193608417944</v>
+        <v>-3256.594760152715</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1407.5365602091188</v>
+        <v>-1403.8043768240807</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -18985,7 +18985,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12224.212443256436</v>
+        <v>-12129.403131666804</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13744619934229851</v>
+        <v>0.13805036478854302</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19786.185720209178</v>
+        <v>-19761.0400304955</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12224.212443256436</v>
+        <v>-12129.403131666804</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-32010.398163465616</v>
+        <v>-31890.443162162304</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-44252.398163465616</v>
+        <v>-44132.443162162308</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>-8.8046952175618021</v>
+        <v>-8.7808283251417247</v>
       </c>
     </row>
   </sheetData>
@@ -20095,7 +20095,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13744619934229851</v>
+        <v>0.13805036478854302</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C44" s="142">
         <f ca="1">C43/(1+C48)^5</f>
-        <v>32.321232777928991</v>
+        <v>32.235530728427833</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="C48" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13744619934229851</v>
+        <v>0.13805036478854302</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="C52" s="142">
         <f ca="1">C51/(1+C48)^5</f>
-        <v>36.468980651241303</v>
+        <v>36.372280552996166</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C56" s="134">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13744619934229851</v>
+        <v>0.13805036478854302</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="C61" s="142">
         <f ca="1">C60/(1+C56)^5</f>
-        <v>-10.984571681463171</v>
+        <v>-10.955445307711837</v>
       </c>
     </row>
   </sheetData>
@@ -20330,7 +20330,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-8.8046952175618021</v>
+        <v>-8.7808283251417247</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -20339,7 +20339,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C44</f>
-        <v>32.321232777928991</v>
+        <v>32.235530728427833</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="C7" s="132">
         <f ca="1">Multiples!C52</f>
-        <v>36.468980651241303</v>
+        <v>36.372280552996166</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -20357,7 +20357,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C61</f>
-        <v>-10.984571681463171</v>
+        <v>-10.955445307711837</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>12.25023663253633</v>
+        <v>12.21788441214261</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20375,7 +20375,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>112.71</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.8913118921787212</v>
+        <v>-0.87679858412682654</v>
       </c>
     </row>
   </sheetData>
@@ -20637,7 +20637,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-964211.89909385249</v>
+        <v>-959277.1958988749</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20691,23 +20691,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13168.752681684975</v>
+        <v>-13161.76168586741</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19102.830478790267</v>
+        <v>-19082.553332968146</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27710.910905702134</v>
+        <v>-27666.801025319983</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40197.947842145659</v>
+        <v>-40112.65503197661</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58311.869148529528</v>
+        <v>-58157.251076545435</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20726,7 +20726,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-506428.53378465137</v>
+        <v>-502500.74368117063</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>112.71</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-134.73196276193872</v>
+        <v>-133.88853279622924</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -20790,7 +20790,7 @@
       </c>
       <c r="C21" s="161">
         <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13744619934229851</v>
+        <v>0.13805036478854302</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="C23" s="162">
         <f ca="1">C15*C22</f>
-        <v>566480.46</v>
+        <v>498428.42</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="C26" s="163">
         <f ca="1">C23+C25-C24</f>
-        <v>578722.46</v>
+        <v>510670.41999999993</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C29" s="162">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158492.31105685257</v>
+        <v>-158181.02215267759</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="C30" s="162">
         <f ca="1">L11</f>
-        <v>-506428.53378465137</v>
+        <v>-502500.74368117063</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -20869,7 +20869,7 @@
       </c>
       <c r="C31" s="165">
         <f ca="1">C29+C30</f>
-        <v>-664920.844841504</v>
+        <v>-660681.76583384816</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="C34" s="165">
         <f ca="1">C31+C32-C33</f>
-        <v>-677162.844841504</v>
+        <v>-672923.76583384816</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="C36" s="168">
         <f ca="1">C34/C35</f>
-        <v>-134.73196276193872</v>
+        <v>-133.88853279622924</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -21361,17 +21361,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28520,7 +28520,7 @@
       <c r="AA129" s="67"/>
       <c r="AC129" s="62">
         <f ca="1">Overview!C5</f>
-        <v>112.71</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="130" spans="1:31" x14ac:dyDescent="0.2">
@@ -28567,7 +28567,7 @@
       <c r="AA130" s="67"/>
       <c r="AC130" s="64">
         <f t="shared" ref="AC130" ca="1" si="76">AC129/AC84</f>
-        <v>112.71</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="132" spans="1:31" x14ac:dyDescent="0.2">
@@ -29993,7 +29993,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="71">
         <f ca="1">AC130/Statement!AC26</f>
-        <v>-181.79032258064515</v>
+        <v>-159.95161290322582</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -30030,7 +30030,7 @@
       <c r="AA169" s="49"/>
       <c r="AC169" s="71">
         <f ca="1">AC130/(Statement!AC5/Statement!AC22)</f>
-        <v>9.8647193236984538</v>
+        <v>8.6796576641928471</v>
       </c>
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
@@ -30067,7 +30067,7 @@
       <c r="AA170" s="49"/>
       <c r="AC170" s="71">
         <f ca="1">AC130/(Statement!AC48/Statement!AC74)</f>
-        <v>5.085376770741691</v>
+        <v>4.4744637951774777</v>
       </c>
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
@@ -30104,7 +30104,7 @@
       <c r="AA171" s="49"/>
       <c r="AC171" s="143">
         <f ca="1">Statement!AC130*Statement!AC77</f>
-        <v>566480.46</v>
+        <v>498428.42</v>
       </c>
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
@@ -30141,7 +30141,7 @@
       <c r="AA172" s="49"/>
       <c r="AC172" s="143">
         <f ca="1">AC171+AC121-AC120+AC47+AC44</f>
-        <v>592317.46</v>
+        <v>524265.41999999993</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -30178,7 +30178,7 @@
       <c r="AA173" s="49"/>
       <c r="AC173" s="185">
         <f ca="1">AC172/AC5</f>
-        <v>11.017195096999794</v>
+        <v>9.7514167736175423</v>
       </c>
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
@@ -30215,7 +30215,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="185">
         <f ca="1">AC172/AC12</f>
-        <v>-117.313816597346</v>
+        <v>-103.83549613784906</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -30350,7 +30350,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="71">
         <f t="shared" ref="AC177:AC178" ca="1" si="105">AC171/AC175</f>
-        <v>-103.18405464480874</v>
+        <v>-90.788418943533699</v>
       </c>
     </row>
     <row r="178" spans="2:29" x14ac:dyDescent="0.2">
@@ -30387,7 +30387,7 @@
       <c r="AA178" s="49"/>
       <c r="AC178" s="71">
         <f t="shared" ca="1" si="105"/>
-        <v>-69.091036976554292</v>
+        <v>-61.153087600606547</v>
       </c>
     </row>
     <row r="179" spans="2:29" x14ac:dyDescent="0.2">
@@ -30424,7 +30424,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="73">
         <f t="shared" ref="AC179" ca="1" si="108">AC175/AC171</f>
-        <v>-9.6914198946950452E-3</v>
+        <v>-1.1014620715247336E-2</v>
       </c>
     </row>
     <row r="180" spans="2:29" x14ac:dyDescent="0.2">
@@ -30461,7 +30461,7 @@
       <c r="AA180" s="49"/>
       <c r="AC180" s="73">
         <f t="shared" ref="AC180" ca="1" si="110">AC26/AC130</f>
-        <v>-5.5008428710850857E-3</v>
+        <v>-6.2518906927498232E-3</v>
       </c>
     </row>
     <row r="181" spans="2:29" x14ac:dyDescent="0.2">
@@ -31038,7 +31038,7 @@
       <c r="AA193" s="49"/>
       <c r="AC193" s="154">
         <f ca="1">(AC120-AC121)/AC171</f>
-        <v>-2.1610630665001226E-2</v>
+        <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="194" spans="2:29" x14ac:dyDescent="0.2">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="C5" s="174">
         <f ca="1">Overview!C5</f>
-        <v>112.71</v>
+        <v>99.17</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="C6" s="175">
         <f ca="1">Statement!AC171</f>
-        <v>566480.46</v>
+        <v>498428.42</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="C7" s="175">
         <f ca="1">Statement!AC172</f>
-        <v>592317.46</v>
+        <v>524265.41999999993</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -31776,7 +31776,7 @@
       </c>
       <c r="C8" s="176">
         <f ca="1">Statement!AC168</f>
-        <v>-181.79032258064515</v>
+        <v>-159.95161290322582</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>246</v>
@@ -31796,7 +31796,7 @@
       </c>
       <c r="C9" s="176">
         <f ca="1">Statement!AC169</f>
-        <v>9.8647193236984538</v>
+        <v>8.6796576641928471</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>247</v>
@@ -31816,17 +31816,17 @@
       </c>
       <c r="C10" s="176">
         <f ca="1">Statement!AC170</f>
-        <v>5.085376770741691</v>
+        <v>4.4744637951774777</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="180">
-        <f>IF(Statement!M129&lt;=0,"N/A",_xlfn.RRI(4,Statement!M129,Statement!Q129))</f>
+        <f>IF(Statement!M130&lt;=0,"N/A",_xlfn.RRI(4,Statement!M130,Statement!Q130))</f>
         <v>-8.3512303772420138E-2</v>
       </c>
       <c r="G10" s="180" t="str">
-        <f>IF(Statement!H129&lt;=0,"N/A",_xlfn.RRI(9,Statement!H129,Statement!Q129))</f>
+        <f>IF(Statement!H130&lt;=0,"N/A",_xlfn.RRI(9,Statement!H130,Statement!Q130))</f>
         <v>N/A</v>
       </c>
     </row>
@@ -31836,7 +31836,7 @@
       </c>
       <c r="C11" s="176">
         <f ca="1">Statement!AC173</f>
-        <v>11.017195096999794</v>
+        <v>9.7514167736175423</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -31845,7 +31845,7 @@
       </c>
       <c r="C12" s="176">
         <f ca="1">Statement!AC174</f>
-        <v>-117.313816597346</v>
+        <v>-103.83549613784906</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -32081,7 +32081,7 @@
       </c>
       <c r="C38" s="177">
         <f ca="1">Statement!AC180</f>
-        <v>-5.5008428710850857E-3</v>
+        <v>-6.2518906927498232E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -32097,7 +32097,7 @@
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC179</f>
-        <v>-9.6914198946950452E-3</v>
+        <v>-1.1014620715247336E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -32182,7 +32182,7 @@
       </c>
       <c r="F48" s="177">
         <f ca="1">Statement!AC193</f>
-        <v>-2.1610630665001226E-2</v>
+        <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="I6" s="174">
         <f ca="1">Statement!AC129</f>
-        <v>112.71</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32390,7 +32390,7 @@
       </c>
       <c r="I7" s="175">
         <f ca="1">Statement!AC171</f>
-        <v>566480.46</v>
+        <v>498428.42</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32419,7 +32419,7 @@
       </c>
       <c r="I8" s="175">
         <f ca="1">Statement!AC172</f>
-        <v>592317.46</v>
+        <v>524265.41999999993</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -32448,7 +32448,7 @@
       </c>
       <c r="I9" s="176">
         <f ca="1">Statement!AC168</f>
-        <v>-181.79032258064515</v>
+        <v>-159.95161290322582</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -32477,7 +32477,7 @@
       </c>
       <c r="I10" s="176">
         <f ca="1">Statement!AC169</f>
-        <v>9.8647193236984538</v>
+        <v>8.6796576641928471</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -32506,7 +32506,7 @@
       </c>
       <c r="I11" s="176">
         <f ca="1">Statement!AC170</f>
-        <v>5.085376770741691</v>
+        <v>4.4744637951774777</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -32535,7 +32535,7 @@
       </c>
       <c r="I12" s="176">
         <f ca="1">Statement!AC173</f>
-        <v>11.017195096999794</v>
+        <v>9.7514167736175423</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="I13" s="176">
         <f ca="1">Statement!AC174</f>
-        <v>-117.313816597346</v>
+        <v>-103.83549613784906</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33337,7 +33337,7 @@
       </c>
       <c r="I51" s="177">
         <f ca="1">Statement!AC180</f>
-        <v>-5.5008428710850857E-3</v>
+        <v>-6.2518906927498232E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33366,7 +33366,7 @@
       </c>
       <c r="I52" s="177">
         <f ca="1">Statement!AC179</f>
-        <v>-9.6914198946950452E-3</v>
+        <v>-1.1014620715247336E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -33689,7 +33689,7 @@
       </c>
       <c r="I68" s="198">
         <f ca="1">Statement!AC193</f>
-        <v>-2.1610630665001226E-2</v>
+        <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34227,14 +34227,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="232" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="F3" s="236" t="s">
+      <c r="D3" s="233"/>
+      <c r="F3" s="234" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="235"/>
+      <c r="G3" s="233"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -34301,19 +34301,19 @@
       <c r="B7" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="232">
+      <c r="C7" s="235">
         <f>Statement!AA88</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="233"/>
-      <c r="F7" s="232">
+      <c r="D7" s="236"/>
+      <c r="F7" s="235">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="233"/>
+      <c r="G7" s="236"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="209" t="s">
@@ -34340,19 +34340,19 @@
       <c r="B9" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="232">
+      <c r="C9" s="235">
         <f>Statement!AA89</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="233"/>
-      <c r="F9" s="232">
+      <c r="D9" s="236"/>
+      <c r="F9" s="235">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="233"/>
+      <c r="G9" s="236"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="209" t="s">
@@ -34379,19 +34379,19 @@
       <c r="B11" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="232">
+      <c r="C11" s="235">
         <f>Statement!AA90</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="233"/>
-      <c r="F11" s="232">
+      <c r="D11" s="236"/>
+      <c r="F11" s="235">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="233"/>
+      <c r="G11" s="236"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="209" t="s">
@@ -34418,19 +34418,19 @@
       <c r="B13" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="232">
+      <c r="C13" s="235">
         <f>Statement!AA94</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="233"/>
-      <c r="F13" s="232">
+      <c r="D13" s="236"/>
+      <c r="F13" s="235">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="233"/>
+      <c r="G13" s="236"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
@@ -34457,19 +34457,19 @@
       <c r="B15" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="232">
+      <c r="C15" s="235">
         <f>Statement!AA95</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="233"/>
-      <c r="F15" s="232">
+      <c r="D15" s="236"/>
+      <c r="F15" s="235">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="233"/>
+      <c r="G15" s="236"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="209" t="s">
@@ -34496,19 +34496,19 @@
       <c r="B17" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="232">
+      <c r="C17" s="235">
         <f>Statement!AA97</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="233"/>
-      <c r="F17" s="232">
+      <c r="D17" s="236"/>
+      <c r="F17" s="235">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="233"/>
+      <c r="G17" s="236"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
@@ -34535,22 +34535,22 @@
       <c r="B19" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="232">
+      <c r="C19" s="235">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="233"/>
-      <c r="F19" s="232">
+      <c r="D19" s="236"/>
+      <c r="F19" s="235">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="233"/>
+      <c r="G19" s="236"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="209" t="s">
@@ -34577,22 +34577,22 @@
       <c r="B21" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="232">
+      <c r="C21" s="235">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="233"/>
-      <c r="F21" s="232">
+      <c r="D21" s="236"/>
+      <c r="F21" s="235">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="233"/>
+      <c r="G21" s="236"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -34640,22 +34640,22 @@
       <c r="B25" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="232">
+      <c r="C25" s="235">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="233"/>
-      <c r="F25" s="232">
+      <c r="D25" s="236"/>
+      <c r="F25" s="235">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="233"/>
+      <c r="G25" s="236"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -34682,22 +34682,22 @@
       <c r="B27" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="232">
+      <c r="C27" s="235">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="233"/>
-      <c r="F27" s="232">
+      <c r="D27" s="236"/>
+      <c r="F27" s="235">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="233"/>
+      <c r="G27" s="236"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -34724,22 +34724,22 @@
       <c r="B29" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="232">
+      <c r="C29" s="235">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="233"/>
-      <c r="F29" s="232">
+      <c r="D29" s="236"/>
+      <c r="F29" s="235">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="233"/>
+      <c r="G29" s="236"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34766,22 +34766,22 @@
       <c r="B31" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="232">
+      <c r="C31" s="235">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="233"/>
-      <c r="F31" s="232">
+      <c r="D31" s="236"/>
+      <c r="F31" s="235">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="233"/>
+      <c r="G31" s="236"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -34808,37 +34808,25 @@
       <c r="B33" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="232">
+      <c r="C33" s="235">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="233"/>
-      <c r="F33" s="232">
+      <c r="D33" s="236"/>
+      <c r="F33" s="235">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="233"/>
+      <c r="G33" s="236"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -34855,6 +34843,18 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD78E10F-6111-134C-8080-3241887127FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81E3354-E6F3-8E44-8BA9-0AB58DD17B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="4" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="393">
   <si>
     <t>Ticker</t>
   </si>
@@ -967,9 +967,6 @@
     <t>Dividend yield</t>
   </si>
   <si>
-    <t>FCF/Sales</t>
-  </si>
-  <si>
     <t>Earnings yields</t>
   </si>
   <si>
@@ -1328,6 +1325,12 @@
   </si>
   <si>
     <t>Last market price for period adjusted</t>
+  </si>
+  <si>
+    <t>FCFF/Sales (FCFF Margin)</t>
+  </si>
+  <si>
+    <t>FCFE/Sales (FCFE Margin)</t>
   </si>
 </sst>
 </file>
@@ -12560,11 +12563,11 @@
       </c>
       <c r="C2" s="230"/>
       <c r="E2" s="229" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F2" s="230"/>
       <c r="H2" s="229" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I2" s="230"/>
     </row>
@@ -12721,7 +12724,7 @@
         <v>-0.11281100000000001</v>
       </c>
       <c r="E9" s="187" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F9" s="194">
         <f ca="1">Statement!AC180</f>
@@ -12737,7 +12740,7 @@
         <v>-2.2638999999999999E-2</v>
       </c>
       <c r="E10" s="187" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F10" s="194">
         <f ca="1">Statement!AC182</f>
@@ -12753,7 +12756,7 @@
         <v>132.75</v>
       </c>
       <c r="E11" s="188" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F11" s="195">
         <f ca="1">Statement!AC181</f>
@@ -12810,19 +12813,19 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E15" s="187" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F15" s="194">
-        <f ca="1">Statement!AC193</f>
+        <f ca="1">Statement!AC194</f>
         <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E16" s="188" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F16" s="193">
-        <f>Statement!AC192</f>
+        <f>Statement!AC193</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
@@ -12832,10 +12835,10 @@
       </c>
       <c r="C17" s="231"/>
       <c r="E17" s="186" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F17" s="196">
-        <f>Statement!AC188</f>
+        <f>Statement!AC189</f>
         <v>5.9689614007162755E-4</v>
       </c>
     </row>
@@ -12844,10 +12847,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E18" s="187" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F18" s="192">
         <f>Statement!AC162</f>
@@ -12875,10 +12878,10 @@
         <v>88</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E20" s="188" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F20" s="193">
         <f>Statement!AC165</f>
@@ -12890,7 +12893,7 @@
         <v>89</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I21" s="50"/>
     </row>
@@ -12899,7 +12902,7 @@
         <v>90</v>
       </c>
       <c r="C22" s="68" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
@@ -12908,7 +12911,7 @@
       </c>
       <c r="C25" s="231"/>
       <c r="E25" s="229" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F25" s="230"/>
     </row>
@@ -12935,7 +12938,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="E27" s="188" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F27" s="227">
         <f ca="1">F26/1000</f>
@@ -12944,7 +12947,7 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B31" s="228" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C31" s="228"/>
       <c r="D31" s="228"/>
@@ -12955,18 +12958,18 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
@@ -12980,7 +12983,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="228" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C40" s="228"/>
       <c r="D40" s="228"/>
@@ -12991,10 +12994,10 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="41" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C42" s="41" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D42" s="41" t="s">
         <v>86</v>
@@ -13003,12 +13006,12 @@
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
@@ -13309,11 +13312,11 @@
         <v>38452.690209023996</v>
       </c>
       <c r="N6" s="89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R6" s="1" t="str">
         <f>B6</f>
@@ -13408,11 +13411,11 @@
         <v>27957.189758960001</v>
       </c>
       <c r="N7" s="89" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="89" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R7" s="1" t="str">
         <f t="shared" ref="R7:R10" si="3">B7</f>
@@ -13507,11 +13510,11 @@
         <v>66409.879967984001</v>
       </c>
       <c r="N8" s="89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O8" s="5"/>
       <c r="Q8" s="89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R8" s="1" t="str">
         <f t="shared" si="3"/>
@@ -13606,11 +13609,11 @@
         <v>6177.5999999999995</v>
       </c>
       <c r="N9" s="89" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O9" s="5"/>
       <c r="Q9" s="89" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R9" s="1" t="str">
         <f t="shared" si="3"/>
@@ -13702,11 +13705,11 @@
         <v>4678.557983820001</v>
       </c>
       <c r="N10" s="89" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O10" s="5"/>
       <c r="Q10" s="89" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R10" s="1" t="str">
         <f t="shared" si="3"/>
@@ -13797,11 +13800,11 @@
         <v>77266.037951804014</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O11" s="5"/>
       <c r="Q11" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="R11" s="16" t="s">
         <v>116</v>
@@ -18295,7 +18298,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -18941,7 +18944,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C10" s="137"/>
       <c r="D10" s="137"/>
@@ -20038,7 +20041,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C34" s="149">
         <f>C32/C8</f>
@@ -20203,7 +20206,7 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="228" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C54" s="228"/>
     </row>
@@ -20353,7 +20356,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C61</f>
@@ -20682,7 +20685,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C10" s="137"/>
       <c r="D10" s="137"/>
@@ -20756,7 +20759,7 @@
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="157" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C17" s="158">
         <v>0.65</v>
@@ -21065,7 +21068,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="121" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C43" s="94">
         <f>C41/C42</f>
@@ -21150,7 +21153,7 @@
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="121" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C45" s="94">
         <f>C41/C44</f>
@@ -21190,7 +21193,7 @@
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="121" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C46" s="137"/>
       <c r="D46" s="94">
@@ -21381,7 +21384,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0548B83C-60BF-4548-84AB-1D4A73B251A4}">
-  <dimension ref="A1:AE208"/>
+  <dimension ref="A1:AE209"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -21418,45 +21421,45 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="M2" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="U2" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="V2" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="W2" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="X2" s="10" t="s">
-        <v>351</v>
-      </c>
       <c r="Y2" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -21485,16 +21488,16 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="X3" s="10" t="s">
         <v>85</v>
@@ -21815,7 +21818,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -22334,7 +22337,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -24023,7 +24026,7 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
@@ -24136,7 +24139,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -24194,7 +24197,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -25003,7 +25006,7 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C63" s="61"/>
       <c r="D63" s="61"/>
@@ -25056,7 +25059,7 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C64" s="61"/>
       <c r="D64" s="61"/>
@@ -25847,7 +25850,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -25889,7 +25892,7 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B79" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -26569,7 +26572,7 @@
     </row>
     <row r="92" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C92" s="49"/>
       <c r="D92" s="50"/>
@@ -27278,7 +27281,7 @@
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B105" s="218" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C105" s="61"/>
       <c r="D105" s="61"/>
@@ -27336,7 +27339,7 @@
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B106" s="218" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C106" s="61"/>
       <c r="D106" s="61"/>
@@ -27397,7 +27400,7 @@
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B107" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C107" s="61"/>
       <c r="D107" s="61"/>
@@ -27458,7 +27461,7 @@
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B108" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C108" s="21"/>
       <c r="D108" s="21"/>
@@ -27516,7 +27519,7 @@
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B109" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C109" s="61"/>
       <c r="D109" s="61"/>
@@ -27603,7 +27606,7 @@
     </row>
     <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B111" s="218" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C111" s="61"/>
       <c r="D111" s="61"/>
@@ -27664,7 +27667,7 @@
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B112" s="218" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C112" s="61"/>
       <c r="D112" s="61"/>
@@ -27725,7 +27728,7 @@
     </row>
     <row r="113" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B113" s="20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C113" s="61"/>
       <c r="D113" s="61"/>
@@ -27786,7 +27789,7 @@
     </row>
     <row r="114" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B114" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C114" s="61"/>
       <c r="D114" s="61"/>
@@ -27847,7 +27850,7 @@
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B115" s="20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C115" s="61"/>
       <c r="D115" s="61"/>
@@ -28245,7 +28248,7 @@
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B123" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C123" s="25"/>
       <c r="D123" s="25"/>
@@ -28316,7 +28319,7 @@
     </row>
     <row r="124" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B124" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C124" s="25"/>
       <c r="D124" s="25"/>
@@ -28387,7 +28390,7 @@
     </row>
     <row r="125" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B125" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C125" s="25"/>
       <c r="D125" s="25"/>
@@ -28525,7 +28528,7 @@
     </row>
     <row r="130" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B130" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C130" s="26"/>
       <c r="D130" s="26"/>
@@ -28803,7 +28806,7 @@
     </row>
     <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B142" s="20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M142" s="61">
         <v>0</v>
@@ -28851,7 +28854,7 @@
     </row>
     <row r="143" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B143" s="20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M143" s="61">
         <v>0</v>
@@ -29102,7 +29105,7 @@
       <c r="P150" s="49"/>
       <c r="Q150" s="49"/>
       <c r="T150" s="173" t="str">
-        <f t="shared" ref="T150:AA150" si="81">IF(U5&gt;T148, "BEAT", IF(U5&lt;T147, "MISSED", "MET"))</f>
+        <f t="shared" ref="T150:Z150" si="81">IF(T149&gt;T148, "BEAT", IF(T149&lt;T147, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U150" s="173" t="str">
@@ -29130,14 +29133,14 @@
         <v>BEAT</v>
       </c>
       <c r="AA150" s="173" t="str">
-        <f t="shared" si="81"/>
+        <f>IF(AA149&gt;AA148, "BEAT", IF(AA149&lt;AA147, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="AC150" s="49"/>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B151" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C151" s="49"/>
       <c r="D151" s="49"/>
@@ -29182,7 +29185,7 @@
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B152" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C152" s="49"/>
       <c r="D152" s="49"/>
@@ -29227,7 +29230,7 @@
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B153" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C153" s="49"/>
       <c r="D153" s="49"/>
@@ -29298,7 +29301,7 @@
       <c r="P154" s="49"/>
       <c r="Q154" s="49"/>
       <c r="T154" s="173" t="str">
-        <f t="shared" ref="T154:AA154" si="83">IF(U100&gt;T152, "BEAT", IF(U100&lt;T151, "MISSED", "MET"))</f>
+        <f t="shared" ref="T154:Z154" si="83">IF(T153&gt;T152, "BEAT", IF(T153&lt;T151, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U154" s="173" t="str">
@@ -29326,7 +29329,7 @@
         <v>BEAT</v>
       </c>
       <c r="AA154" s="173" t="str">
-        <f t="shared" si="83"/>
+        <f>IF(AA153&gt;AA152, "BEAT", IF(AA153&lt;AA151, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="AC154" s="49"/>
@@ -30503,7 +30506,7 @@
     </row>
     <row r="182" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B182" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M182" s="154">
         <f>-M62/M171</f>
@@ -30540,7 +30543,7 @@
     </row>
     <row r="183" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B183" s="20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M183" s="154">
         <f>-(M62+M63)/M171</f>
@@ -30577,25 +30580,25 @@
     </row>
     <row r="184" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B184" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="M184" s="71">
+        <v>391</v>
+      </c>
+      <c r="M184" s="154">
         <f>M176/M5</f>
         <v>6.9118053061243856E-2</v>
       </c>
-      <c r="N184" s="71">
+      <c r="N184" s="154">
         <f>N176/N5</f>
         <v>-0.22176229898182509</v>
       </c>
-      <c r="O184" s="71">
+      <c r="O184" s="154">
         <f>O176/O5</f>
         <v>-0.30655749797152765</v>
       </c>
-      <c r="P184" s="71">
+      <c r="P184" s="154">
         <f>P176/P5</f>
         <v>-0.43577333760192838</v>
       </c>
-      <c r="Q184" s="71">
+      <c r="Q184" s="154">
         <f>Q176/Q5</f>
         <v>-0.1305696933002857</v>
       </c>
@@ -30607,34 +30610,34 @@
       <c r="Y184" s="49"/>
       <c r="Z184" s="49"/>
       <c r="AA184" s="49"/>
-      <c r="AC184" s="71">
+      <c r="AC184" s="154">
         <f>AC176/AC5</f>
         <v>-0.15945910756468204</v>
       </c>
     </row>
     <row r="185" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B185" s="20" t="s">
-        <v>274</v>
+        <v>392</v>
       </c>
       <c r="M185" s="154">
-        <f>-M63/M175</f>
-        <v>0.64970645792563597</v>
+        <f>M175/M5</f>
+        <v>0.10992862927718161</v>
       </c>
       <c r="N185" s="154">
-        <f>-N63/N175</f>
-        <v>-0.47826780445011563</v>
+        <f t="shared" ref="N185:Q185" si="113">N175/N5</f>
+        <v>-0.19886129349446507</v>
       </c>
       <c r="O185" s="154">
-        <f>-O63/O175</f>
-        <v>-0.1763765135937857</v>
+        <f t="shared" si="113"/>
+        <v>-0.3228590396105333</v>
       </c>
       <c r="P185" s="154">
-        <f>-P63/P175</f>
-        <v>-8.3866568761145496E-2</v>
+        <f t="shared" si="113"/>
+        <v>-0.35905161861358542</v>
       </c>
       <c r="Q185" s="154">
-        <f>-Q63/Q175</f>
-        <v>0</v>
+        <f t="shared" si="113"/>
+        <v>-0.13968932700130551</v>
       </c>
       <c r="T185" s="49"/>
       <c r="U185" s="49"/>
@@ -30645,32 +30648,32 @@
       <c r="Z185" s="49"/>
       <c r="AA185" s="49"/>
       <c r="AC185" s="154">
-        <f>-AC63/AC175</f>
-        <v>0</v>
+        <f t="shared" ref="AC184:AC185" si="114">AC175/AC5</f>
+        <v>-0.1021148373416662</v>
       </c>
     </row>
     <row r="186" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M186" s="154">
-        <f>-M62/M175</f>
-        <v>0.27800161160354553</v>
+        <f>-M63/M175</f>
+        <v>0.64970645792563597</v>
       </c>
       <c r="N186" s="154">
-        <f>-N62/N175</f>
-        <v>0</v>
+        <f>-N63/N175</f>
+        <v>-0.47826780445011563</v>
       </c>
       <c r="O186" s="154">
-        <f>-O62/O175</f>
-        <v>0</v>
+        <f>-O63/O175</f>
+        <v>-0.1763765135937857</v>
       </c>
       <c r="P186" s="154">
-        <f>-P62/P175</f>
-        <v>0</v>
+        <f>-P63/P175</f>
+        <v>-8.3866568761145496E-2</v>
       </c>
       <c r="Q186" s="154">
-        <f>-Q62/Q175</f>
+        <f>-Q63/Q175</f>
         <v>0</v>
       </c>
       <c r="T186" s="49"/>
@@ -30682,32 +30685,32 @@
       <c r="Z186" s="49"/>
       <c r="AA186" s="49"/>
       <c r="AC186" s="154">
-        <f>-AC62/AC175</f>
+        <f>-AC63/AC175</f>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B187" s="20" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="M187" s="154">
-        <f>(-M63-M62)/M175</f>
-        <v>0.9277080695291815</v>
+        <f>-M62/M175</f>
+        <v>0.27800161160354553</v>
       </c>
       <c r="N187" s="154">
-        <f>(-N63-N62)/N175</f>
-        <v>-0.47826780445011563</v>
+        <f>-N62/N175</f>
+        <v>0</v>
       </c>
       <c r="O187" s="154">
-        <f>(-O63-O62)/O175</f>
-        <v>-0.1763765135937857</v>
+        <f>-O62/O175</f>
+        <v>0</v>
       </c>
       <c r="P187" s="154">
-        <f>(-P63-P62)/P175</f>
-        <v>-8.3866568761145496E-2</v>
+        <f>-P62/P175</f>
+        <v>0</v>
       </c>
       <c r="Q187" s="154">
-        <f>(-Q63-Q62)/Q175</f>
+        <f>-Q62/Q175</f>
         <v>0</v>
       </c>
       <c r="T187" s="49"/>
@@ -30719,33 +30722,33 @@
       <c r="Z187" s="49"/>
       <c r="AA187" s="49"/>
       <c r="AC187" s="154">
-        <f>(-AC63-AC62)/AC175</f>
+        <f>-AC62/AC175</f>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B188" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="M188" s="154">
-        <f>M79/M77</f>
-        <v>4.874482086278333E-4</v>
+        <f>(-M63-M62)/M175</f>
+        <v>0.9277080695291815</v>
       </c>
       <c r="N188" s="154">
-        <f>N79/N77</f>
-        <v>4.8169556840077071E-4</v>
+        <f>(-N63-N62)/N175</f>
+        <v>-0.47826780445011563</v>
       </c>
       <c r="O188" s="154">
-        <f>O79/O77</f>
-        <v>4.7058823529411766E-4</v>
+        <f>(-O63-O62)/O175</f>
+        <v>-0.1763765135937857</v>
       </c>
       <c r="P188" s="154">
-        <f>P79/P77</f>
-        <v>4.6189376443418013E-4</v>
+        <f>(-P63-P62)/P175</f>
+        <v>-8.3866568761145496E-2</v>
       </c>
       <c r="Q188" s="154">
-        <f>Q79/Q77</f>
-        <v>6.0060060060060057E-4</v>
+        <f>(-Q63-Q62)/Q175</f>
+        <v>0</v>
       </c>
       <c r="T188" s="49"/>
       <c r="U188" s="49"/>
@@ -30756,902 +30759,939 @@
       <c r="Z188" s="49"/>
       <c r="AA188" s="49"/>
       <c r="AC188" s="154">
+        <f>(-AC63-AC62)/AC175</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B189" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="M189" s="154">
+        <f>M79/M77</f>
+        <v>4.874482086278333E-4</v>
+      </c>
+      <c r="N189" s="154">
+        <f>N79/N77</f>
+        <v>4.8169556840077071E-4</v>
+      </c>
+      <c r="O189" s="154">
+        <f>O79/O77</f>
+        <v>4.7058823529411766E-4</v>
+      </c>
+      <c r="P189" s="154">
+        <f>P79/P77</f>
+        <v>4.6189376443418013E-4</v>
+      </c>
+      <c r="Q189" s="154">
+        <f>Q79/Q77</f>
+        <v>6.0060060060060057E-4</v>
+      </c>
+      <c r="T189" s="49"/>
+      <c r="U189" s="49"/>
+      <c r="V189" s="49"/>
+      <c r="W189" s="49"/>
+      <c r="X189" s="49"/>
+      <c r="Y189" s="49"/>
+      <c r="Z189" s="49"/>
+      <c r="AA189" s="49"/>
+      <c r="AC189" s="154">
         <f>AC79/AC77</f>
         <v>5.9689614007162755E-4</v>
       </c>
     </row>
-    <row r="189" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B189" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="M189" s="71">
+    <row r="190" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B190" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="M190" s="71">
         <f>M120/M74</f>
         <v>6.9776522593320234</v>
       </c>
-      <c r="N189" s="71">
+      <c r="N190" s="71">
         <f>N120/N74</f>
         <v>6.8498912255257434</v>
       </c>
-      <c r="O189" s="71">
+      <c r="O190" s="71">
         <f>O120/O74</f>
         <v>5.9210028382213808</v>
       </c>
-      <c r="P189" s="71">
+      <c r="P190" s="71">
         <f>P120/P74</f>
         <v>5.0951501154734409</v>
       </c>
-      <c r="Q189" s="71">
+      <c r="Q190" s="71">
         <f>Q120/Q74</f>
         <v>7.4906906906906903</v>
       </c>
-      <c r="T189" s="71">
-        <f t="shared" ref="T189:AA189" si="113">T120/T74</f>
+      <c r="T190" s="71">
+        <f t="shared" ref="T190:AA190" si="115">T120/T74</f>
         <v>6.8458840037418147</v>
       </c>
-      <c r="U189" s="71">
-        <f t="shared" si="113"/>
+      <c r="U190" s="71">
+        <f t="shared" si="115"/>
         <v>5.5845119406445631</v>
       </c>
-      <c r="V189" s="71">
-        <f t="shared" si="113"/>
+      <c r="V190" s="71">
+        <f t="shared" si="115"/>
         <v>5.0951501154734409</v>
       </c>
-      <c r="W189" s="71">
-        <f t="shared" si="113"/>
+      <c r="W190" s="71">
+        <f t="shared" si="115"/>
         <v>4.825309491059147</v>
       </c>
-      <c r="X189" s="71">
-        <f t="shared" si="113"/>
+      <c r="X190" s="71">
+        <f t="shared" si="115"/>
         <v>4.8448709161526162</v>
       </c>
-      <c r="Y189" s="71">
-        <f t="shared" si="113"/>
+      <c r="Y190" s="71">
+        <f t="shared" si="115"/>
         <v>6.4853249475890982</v>
       </c>
-      <c r="Z189" s="71">
-        <f t="shared" si="113"/>
+      <c r="Z190" s="71">
+        <f t="shared" si="115"/>
         <v>7.4906906906906903</v>
       </c>
-      <c r="AA189" s="71">
-        <f t="shared" si="113"/>
+      <c r="AA190" s="71">
+        <f t="shared" si="115"/>
         <v>6.5238758456028654</v>
       </c>
-      <c r="AC189" s="71">
+      <c r="AC190" s="71">
         <f>AC120/AC74</f>
         <v>6.5238758456028654</v>
       </c>
     </row>
-    <row r="190" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B190" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="M190" s="154">
+    <row r="191" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B191" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="M191" s="154">
         <f>M53/M58</f>
         <v>6.9120043454644217E-2</v>
       </c>
-      <c r="N190" s="154">
+      <c r="N191" s="154">
         <f>N53/N58</f>
         <v>0.20268256333830104</v>
       </c>
-      <c r="O190" s="154">
+      <c r="O191" s="154">
         <f>O53/O58</f>
         <v>0.28149245924505273</v>
       </c>
-      <c r="P190" s="154">
+      <c r="P191" s="154">
         <f>P53/P58</f>
         <v>0.41143822393822393</v>
       </c>
-      <c r="Q190" s="154">
+      <c r="Q191" s="154">
         <f>Q53/Q58</f>
         <v>0.25100546560791998</v>
       </c>
-      <c r="T190" s="154" t="e">
-        <f t="shared" ref="T190:Y190" si="114">T53/T58</f>
+      <c r="T191" s="154" t="e">
+        <f t="shared" ref="T191:Y191" si="116">T53/T58</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U190" s="154" t="e">
-        <f t="shared" si="114"/>
+      <c r="U191" s="154" t="e">
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V190" s="154" t="e">
-        <f t="shared" si="114"/>
+      <c r="V191" s="154" t="e">
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W190" s="154">
-        <f t="shared" si="114"/>
+      <c r="W191" s="154">
+        <f t="shared" si="116"/>
         <v>0.84132841328413288</v>
       </c>
-      <c r="X190" s="154">
-        <f t="shared" si="114"/>
+      <c r="X191" s="154">
+        <f t="shared" si="116"/>
         <v>0.32390243902439025</v>
       </c>
-      <c r="Y190" s="154">
-        <f t="shared" si="114"/>
+      <c r="Y191" s="154">
+        <f t="shared" si="116"/>
         <v>0.2152395915161037</v>
       </c>
-      <c r="Z190" s="154">
+      <c r="Z191" s="154">
         <f>W53/W58</f>
         <v>0.84132841328413288</v>
       </c>
-      <c r="AA190" s="154">
+      <c r="AA191" s="154">
         <f>AA53/AA58</f>
         <v>0.56660583941605835</v>
       </c>
-      <c r="AC190" s="154">
+      <c r="AC191" s="154">
         <f>AC53/AC58</f>
         <v>0.2375751503006012</v>
       </c>
     </row>
-    <row r="191" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B191" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="M191" s="154">
+    <row r="192" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B192" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="M192" s="154">
         <f>M53/M5</f>
         <v>2.5764324762097592E-2</v>
       </c>
-      <c r="N191" s="154">
+      <c r="N192" s="154">
         <f>N53/N5</f>
         <v>4.9608272274558315E-2</v>
       </c>
-      <c r="O191" s="154">
+      <c r="O192" s="154">
         <f>O53/O5</f>
         <v>5.9544884561481153E-2</v>
       </c>
-      <c r="P191" s="154">
+      <c r="P192" s="154">
         <f>P53/P5</f>
         <v>6.4217246379540877E-2</v>
       </c>
-      <c r="Q191" s="154">
+      <c r="Q192" s="154">
         <f>Q53/Q5</f>
         <v>4.6052258149963103E-2</v>
       </c>
-      <c r="T191" s="154">
-        <f t="shared" ref="T191:Y191" si="115">T53/T5</f>
-        <v>0</v>
-      </c>
-      <c r="U191" s="154">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="V191" s="154">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="W191" s="154">
-        <f t="shared" si="115"/>
+      <c r="T192" s="154">
+        <f t="shared" ref="T192:Y192" si="117">T53/T5</f>
+        <v>0</v>
+      </c>
+      <c r="U192" s="154">
+        <f t="shared" si="117"/>
+        <v>0</v>
+      </c>
+      <c r="V192" s="154">
+        <f t="shared" si="117"/>
+        <v>0</v>
+      </c>
+      <c r="W192" s="154">
+        <f t="shared" si="117"/>
         <v>5.3998578984763561E-2</v>
       </c>
-      <c r="X191" s="154">
-        <f t="shared" si="115"/>
+      <c r="X192" s="154">
+        <f t="shared" si="117"/>
         <v>5.1636985768722297E-2</v>
       </c>
-      <c r="Y191" s="154">
-        <f t="shared" si="115"/>
+      <c r="Y192" s="154">
+        <f t="shared" si="117"/>
         <v>4.0137698674284038E-2</v>
       </c>
-      <c r="Z191" s="154">
+      <c r="Z192" s="154">
         <f>W53/Z5</f>
         <v>5.0021939447125935E-2</v>
       </c>
-      <c r="AA191" s="154">
+      <c r="AA192" s="154">
         <f>AA53/AA5</f>
         <v>4.5739117625395891E-2</v>
       </c>
-      <c r="AC191" s="154">
+      <c r="AC192" s="154">
         <f>AC53/AC5</f>
         <v>4.4100961627885349E-2</v>
       </c>
     </row>
-    <row r="192" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B192" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="M192" s="71">
+    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B193" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="M193" s="71">
         <f>(M120-M121)/M74</f>
         <v>-2.3791748526522594</v>
       </c>
-      <c r="N192" s="71">
+      <c r="N193" s="71">
         <f>(N120-N121)/N74</f>
         <v>-3.3147208121827409</v>
       </c>
-      <c r="O192" s="71">
+      <c r="O193" s="71">
         <f>(O120-O121)/O74</f>
         <v>-5.7313150425733204</v>
       </c>
-      <c r="P192" s="71">
+      <c r="P193" s="71">
         <f>(P120-P121)/P74</f>
         <v>-6.4547344110854503</v>
       </c>
-      <c r="Q192" s="71">
+      <c r="Q193" s="71">
         <f>(Q120-Q121)/Q74</f>
         <v>-1.8356356356356356</v>
       </c>
-      <c r="T192" s="71">
-        <f t="shared" ref="T192:AA192" si="116">(T120-T121)/T74</f>
+      <c r="T193" s="71">
+        <f t="shared" ref="T193:AA193" si="118">(T120-T121)/T74</f>
         <v>-5.5556594948550044</v>
       </c>
-      <c r="U192" s="71">
-        <f t="shared" si="116"/>
+      <c r="U193" s="71">
+        <f t="shared" si="118"/>
         <v>-6.06306515186645</v>
       </c>
-      <c r="V192" s="71">
-        <f t="shared" si="116"/>
+      <c r="V193" s="71">
+        <f t="shared" si="118"/>
         <v>-6.4547344110854503</v>
       </c>
-      <c r="W192" s="71">
-        <f t="shared" si="116"/>
+      <c r="W193" s="71">
+        <f t="shared" si="118"/>
         <v>-6.6719394773039893</v>
       </c>
-      <c r="X192" s="71">
-        <f t="shared" si="116"/>
+      <c r="X193" s="71">
+        <f t="shared" si="118"/>
         <v>-6.7514279186657529</v>
       </c>
-      <c r="Y192" s="71">
-        <f t="shared" si="116"/>
+      <c r="Y193" s="71">
+        <f t="shared" si="118"/>
         <v>-3.2742138364779874</v>
       </c>
-      <c r="Z192" s="71">
-        <f t="shared" si="116"/>
+      <c r="Z193" s="71">
+        <f t="shared" si="118"/>
         <v>-1.8356356356356356</v>
       </c>
-      <c r="AA192" s="71">
-        <f t="shared" si="116"/>
+      <c r="AA193" s="71">
+        <f t="shared" si="118"/>
         <v>-2.435734182252288</v>
       </c>
-      <c r="AC192" s="71">
+      <c r="AC193" s="71">
         <f>(AC120-AC121)/AC74</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
-    <row r="193" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B193" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="M193" s="154">
+    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B194" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="M194" s="154">
         <f>(M120-M121)/M171</f>
         <v>-4.601830291547894E-2</v>
       </c>
-      <c r="N193" s="154">
+      <c r="N194" s="154">
         <f>(N120-N121)/N171</f>
         <v>-0.12496200017933728</v>
       </c>
-      <c r="O193" s="154">
+      <c r="O194" s="154">
         <f>(O120-O121)/O171</f>
         <v>-0.11346561311091601</v>
       </c>
-      <c r="P193" s="154">
+      <c r="P194" s="154">
         <f>(P120-P121)/P171</f>
         <v>-0.31796721236874137</v>
       </c>
-      <c r="Q193" s="154">
+      <c r="Q194" s="154">
         <f>(Q120-Q121)/Q171</f>
         <v>-5.070816673026618E-2</v>
       </c>
-      <c r="T193" s="49"/>
-      <c r="U193" s="49"/>
-      <c r="V193" s="49"/>
-      <c r="W193" s="49"/>
-      <c r="X193" s="49"/>
-      <c r="Y193" s="49"/>
-      <c r="Z193" s="49"/>
-      <c r="AA193" s="49"/>
-      <c r="AC193" s="154">
+      <c r="T194" s="49"/>
+      <c r="U194" s="49"/>
+      <c r="V194" s="49"/>
+      <c r="W194" s="49"/>
+      <c r="X194" s="49"/>
+      <c r="Y194" s="49"/>
+      <c r="Z194" s="49"/>
+      <c r="AA194" s="49"/>
+      <c r="AC194" s="154">
         <f ca="1">(AC120-AC121)/AC171</f>
         <v>-2.4561199780702713E-2</v>
       </c>
     </row>
-    <row r="194" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B194" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="M194" s="154">
+    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B195" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="M195" s="154">
         <f>-M123/M5</f>
         <v>0.23705456570155903</v>
       </c>
-      <c r="N194" s="154">
+      <c r="N195" s="154">
         <f>-N123/N5</f>
         <v>0.39401148222158783</v>
       </c>
-      <c r="O194" s="154">
+      <c r="O195" s="154">
         <f>-O123/O5</f>
         <v>0.4748469425389098</v>
       </c>
-      <c r="P194" s="154">
+      <c r="P195" s="154">
         <f>-P123/P5</f>
         <v>0.45091429539933336</v>
       </c>
-      <c r="Q194" s="154">
+      <c r="Q195" s="154">
         <f>-Q123/Q5</f>
         <v>0.27710820577829071</v>
       </c>
-      <c r="T194" s="154">
-        <f t="shared" ref="T194:AA194" si="117">-T123/T5</f>
-        <v>0</v>
-      </c>
-      <c r="U194" s="154">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="V194" s="154">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-      <c r="W194" s="154">
-        <f t="shared" si="117"/>
+      <c r="T195" s="154">
+        <f t="shared" ref="T195:AA195" si="119">-T123/T5</f>
+        <v>0</v>
+      </c>
+      <c r="U195" s="154">
+        <f t="shared" si="119"/>
+        <v>0</v>
+      </c>
+      <c r="V195" s="154">
+        <f t="shared" si="119"/>
+        <v>0</v>
+      </c>
+      <c r="W195" s="154">
+        <f t="shared" si="119"/>
         <v>0.40917344280413676</v>
       </c>
-      <c r="X194" s="154">
-        <f t="shared" si="117"/>
+      <c r="X195" s="154">
+        <f t="shared" si="119"/>
         <v>0.27607123415506651</v>
       </c>
-      <c r="Y194" s="154">
-        <f t="shared" si="117"/>
+      <c r="Y195" s="154">
+        <f t="shared" si="119"/>
         <v>0.17761664103127517</v>
       </c>
-      <c r="Z194" s="154">
-        <f t="shared" si="117"/>
+      <c r="Z195" s="154">
+        <f t="shared" si="119"/>
         <v>0.25508263858417435</v>
       </c>
-      <c r="AA194" s="154">
-        <f t="shared" si="117"/>
+      <c r="AA195" s="154">
+        <f t="shared" si="119"/>
         <v>0.2678058481255064</v>
       </c>
-      <c r="AC194" s="154">
+      <c r="AC195" s="154">
         <f>-AC123/AC5</f>
         <v>0.24364339787586259</v>
       </c>
     </row>
-    <row r="195" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B195" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="M195" s="154">
+    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B196" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="M196" s="154">
         <f>-(M123/M58)</f>
         <v>0.63596550787615425</v>
       </c>
-      <c r="N195" s="154">
+      <c r="N196" s="154">
         <f>-(N123/N58)</f>
         <v>1.6097971878442299</v>
       </c>
-      <c r="O195" s="154">
+      <c r="O196" s="154">
         <f>-(O123/O58)</f>
         <v>2.2447912126231366</v>
       </c>
-      <c r="P195" s="154">
+      <c r="P196" s="154">
         <f>-(P123/P58)</f>
         <v>2.8889961389961392</v>
       </c>
-      <c r="Q195" s="154">
+      <c r="Q196" s="154">
         <f>-(Q123/Q58)</f>
         <v>1.5103640301124059</v>
       </c>
-      <c r="T195" s="154" t="e">
-        <f t="shared" ref="T195:Y195" si="118">-(T123/T58)</f>
+      <c r="T196" s="154" t="e">
+        <f t="shared" ref="T196:Y196" si="120">-(T123/T58)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U195" s="154" t="e">
-        <f t="shared" si="118"/>
+      <c r="U196" s="154" t="e">
+        <f t="shared" si="120"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V195" s="154" t="e">
-        <f t="shared" si="118"/>
+      <c r="V196" s="154" t="e">
+        <f t="shared" si="120"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W195" s="154">
-        <f t="shared" si="118"/>
+      <c r="W196" s="154">
+        <f t="shared" si="120"/>
         <v>6.375153751537515</v>
       </c>
-      <c r="X195" s="154">
-        <f t="shared" si="118"/>
+      <c r="X196" s="154">
+        <f t="shared" si="120"/>
         <v>1.7317073170731707</v>
       </c>
-      <c r="Y195" s="154">
-        <f t="shared" si="118"/>
+      <c r="Y196" s="154">
+        <f t="shared" si="120"/>
         <v>0.95247446975648076</v>
       </c>
-      <c r="Z195" s="154">
+      <c r="Z196" s="154">
         <f>-(Z123/W58)</f>
         <v>4.2902829028290279</v>
       </c>
-      <c r="AA195" s="154">
+      <c r="AA196" s="154">
         <f>-(AA123/AA58)</f>
         <v>3.3175182481751824</v>
       </c>
-      <c r="AC195" s="154">
+      <c r="AC196" s="154">
         <f>-(AC123/AC58)</f>
         <v>1.3125250501002004</v>
       </c>
     </row>
-    <row r="196" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B196" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="M196" s="154">
+    <row r="197" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B197" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="M197" s="154">
         <f>-M123/M52</f>
         <v>1.5886194029850746</v>
       </c>
-      <c r="N196" s="154">
+      <c r="N197" s="154">
         <f>-N123/N52</f>
         <v>1.9059455312619868</v>
       </c>
-      <c r="O196" s="154">
+      <c r="O197" s="154">
         <f>-O123/O52</f>
         <v>2.6817329722974379</v>
       </c>
-      <c r="P196" s="154">
+      <c r="P197" s="154">
         <f>-P123/P52</f>
         <v>2.1042270849811056</v>
       </c>
-      <c r="Q196" s="154">
+      <c r="Q197" s="154">
         <f>-Q123/Q52</f>
         <v>1.2511532547411583</v>
       </c>
-      <c r="T196" s="154" t="e">
-        <f t="shared" ref="T196:Y196" si="119">-T123/T52</f>
+      <c r="T197" s="154" t="e">
+        <f t="shared" ref="T197:Y197" si="121">-T123/T52</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U196" s="154" t="e">
-        <f t="shared" si="119"/>
+      <c r="U197" s="154" t="e">
+        <f t="shared" si="121"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V196" s="154" t="e">
-        <f t="shared" si="119"/>
+      <c r="V197" s="154" t="e">
+        <f t="shared" si="121"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W196" s="154">
-        <f t="shared" si="119"/>
+      <c r="W197" s="154">
+        <f t="shared" si="121"/>
         <v>1.9382946896035902</v>
       </c>
-      <c r="X196" s="154">
-        <f t="shared" si="119"/>
+      <c r="X197" s="154">
+        <f t="shared" si="121"/>
         <v>1.1782276800531033</v>
       </c>
-      <c r="Y196" s="154">
-        <f t="shared" si="119"/>
+      <c r="Y197" s="154">
+        <f t="shared" si="121"/>
         <v>0.81049465240641716</v>
       </c>
-      <c r="Z196" s="154">
+      <c r="Z197" s="154">
         <f>-Z123/W52</f>
         <v>1.3044128646222888</v>
       </c>
-      <c r="AA196" s="154">
+      <c r="AA197" s="154">
         <f>-AA123/AA52</f>
         <v>1.159438775510204</v>
       </c>
-      <c r="AC196" s="154">
+      <c r="AC197" s="154">
         <f>-AC123/AC52</f>
         <v>1.0765121630506247</v>
       </c>
     </row>
-    <row r="198" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B198" s="1"/>
-    </row>
-    <row r="199" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="C199" s="172"/>
-      <c r="D199" s="172"/>
-      <c r="E199" s="172"/>
-      <c r="F199" s="172"/>
-      <c r="G199" s="172"/>
-      <c r="H199" s="172"/>
-      <c r="I199" s="172"/>
-      <c r="J199" s="172"/>
-      <c r="K199" s="172"/>
-      <c r="L199" s="172"/>
-      <c r="M199" s="172"/>
-      <c r="N199" s="172"/>
-      <c r="O199" s="172"/>
-      <c r="P199" s="172"/>
-      <c r="Q199" s="172"/>
-      <c r="T199" s="172"/>
-      <c r="U199" s="172"/>
-      <c r="V199" s="172"/>
-      <c r="W199" s="172"/>
-      <c r="X199" s="172"/>
-      <c r="Y199" s="172"/>
-      <c r="Z199" s="172"/>
-      <c r="AA199" s="172"/>
-      <c r="AC199" s="172"/>
-    </row>
-    <row r="200" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B200" s="218" t="s">
-        <v>362</v>
-      </c>
-      <c r="C200" s="80"/>
-      <c r="D200" s="80"/>
-      <c r="E200" s="80"/>
-      <c r="F200" s="80"/>
-      <c r="G200" s="80"/>
-      <c r="H200" s="80"/>
-      <c r="I200" s="80"/>
-      <c r="J200" s="80"/>
-      <c r="K200" s="80"/>
-      <c r="L200" s="80"/>
-      <c r="M200" s="80">
-        <f t="shared" ref="M200:Q204" si="120">IF(L105=0,
+    <row r="199" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B199" s="1"/>
+    </row>
+    <row r="200" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B200" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="C200" s="172"/>
+      <c r="D200" s="172"/>
+      <c r="E200" s="172"/>
+      <c r="F200" s="172"/>
+      <c r="G200" s="172"/>
+      <c r="H200" s="172"/>
+      <c r="I200" s="172"/>
+      <c r="J200" s="172"/>
+      <c r="K200" s="172"/>
+      <c r="L200" s="172"/>
+      <c r="M200" s="172"/>
+      <c r="N200" s="172"/>
+      <c r="O200" s="172"/>
+      <c r="P200" s="172"/>
+      <c r="Q200" s="172"/>
+      <c r="T200" s="172"/>
+      <c r="U200" s="172"/>
+      <c r="V200" s="172"/>
+      <c r="W200" s="172"/>
+      <c r="X200" s="172"/>
+      <c r="Y200" s="172"/>
+      <c r="Z200" s="172"/>
+      <c r="AA200" s="172"/>
+      <c r="AC200" s="172"/>
+    </row>
+    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B201" s="218" t="s">
+        <v>361</v>
+      </c>
+      <c r="C201" s="80"/>
+      <c r="D201" s="80"/>
+      <c r="E201" s="80"/>
+      <c r="F201" s="80"/>
+      <c r="G201" s="80"/>
+      <c r="H201" s="80"/>
+      <c r="I201" s="80"/>
+      <c r="J201" s="80"/>
+      <c r="K201" s="80"/>
+      <c r="L201" s="80"/>
+      <c r="M201" s="80">
+        <f t="shared" ref="M201:Q205" si="122">IF(L105=0,
 IF(M105=0,0,IF(M105&gt;0,1,-1)),
 (M105-L105)/ABS(L105)
 )</f>
         <v>1</v>
       </c>
-      <c r="N200" s="80">
-        <f t="shared" si="120"/>
+      <c r="N201" s="80">
+        <f t="shared" si="122"/>
         <v>-0.22657676298045326</v>
       </c>
-      <c r="O200" s="80">
-        <f t="shared" si="120"/>
+      <c r="O201" s="80">
+        <f t="shared" si="122"/>
         <v>-7.9155257608661447E-2</v>
       </c>
-      <c r="P200" s="80">
-        <f t="shared" si="120"/>
+      <c r="P201" s="80">
+        <f t="shared" si="122"/>
         <v>0.139722469068289</v>
       </c>
-      <c r="Q200" s="80">
-        <f t="shared" si="120"/>
+      <c r="Q201" s="80">
+        <f t="shared" si="122"/>
         <v>-3.3527259641336293E-2</v>
       </c>
-      <c r="T200" s="80">
-        <f t="shared" ref="T200:AA204" si="121">IF(S105=0,
+      <c r="T201" s="80">
+        <f t="shared" ref="T201:AA205" si="123">IF(S105=0,
 IF(T105=0,0,IF(T105&gt;0,1,-1)),
 (T105-S105)/ABS(S105)
 )</f>
         <v>1</v>
       </c>
-      <c r="U200" s="80">
-        <f t="shared" si="121"/>
+      <c r="U201" s="80">
+        <f t="shared" si="123"/>
         <v>2.2104875353063983E-3</v>
       </c>
-      <c r="V200" s="80">
-        <f t="shared" si="121"/>
+      <c r="V201" s="80">
+        <f t="shared" si="123"/>
         <v>7.4500673937017522E-2</v>
       </c>
-      <c r="W200" s="80">
-        <f t="shared" si="121"/>
+      <c r="W201" s="80">
+        <f t="shared" si="123"/>
         <v>-0.13000342114266164</v>
       </c>
-      <c r="X200" s="80">
-        <f t="shared" si="121"/>
+      <c r="X201" s="80">
+        <f t="shared" si="123"/>
         <v>3.1721064359680168E-2</v>
       </c>
-      <c r="Y200" s="80">
-        <f t="shared" si="121"/>
+      <c r="Y201" s="80">
+        <f t="shared" si="123"/>
         <v>8.436030999872951E-2</v>
       </c>
-      <c r="Z200" s="80">
-        <f t="shared" si="121"/>
+      <c r="Z201" s="80">
+        <f t="shared" si="123"/>
         <v>-4.0070298769771528E-2</v>
       </c>
-      <c r="AA200" s="80">
-        <f t="shared" si="121"/>
+      <c r="AA201" s="80">
+        <f t="shared" si="123"/>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="AC200" s="49"/>
-    </row>
-    <row r="201" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B201" s="218" t="s">
-        <v>363</v>
-      </c>
-      <c r="M201" s="80">
-        <f t="shared" si="120"/>
+      <c r="AC201" s="49"/>
+    </row>
+    <row r="202" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B202" s="218" t="s">
+        <v>362</v>
+      </c>
+      <c r="M202" s="80">
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
-      <c r="N201" s="80">
-        <f t="shared" si="120"/>
+      <c r="N202" s="80">
+        <f t="shared" si="122"/>
         <v>-8.4923946253162061E-2</v>
       </c>
-      <c r="O201" s="80">
-        <f t="shared" si="120"/>
+      <c r="O202" s="80">
+        <f t="shared" si="122"/>
         <v>-0.23547784878293962</v>
       </c>
-      <c r="P201" s="80">
-        <f t="shared" si="120"/>
+      <c r="P202" s="80">
+        <f t="shared" si="122"/>
         <v>-0.242779995304062</v>
       </c>
-      <c r="Q201" s="80">
-        <f t="shared" si="120"/>
+      <c r="Q202" s="80">
+        <f t="shared" si="122"/>
         <v>4.9240310077519382E-2</v>
       </c>
-      <c r="T201" s="80">
-        <f t="shared" si="121"/>
+      <c r="T202" s="80">
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
-      <c r="U201" s="80">
-        <f t="shared" si="121"/>
+      <c r="U202" s="80">
+        <f t="shared" si="123"/>
         <v>8.8304862023653091E-2</v>
       </c>
-      <c r="V201" s="80">
-        <f t="shared" si="121"/>
+      <c r="V202" s="80">
+        <f t="shared" si="123"/>
         <v>5.0712388312001935E-2</v>
       </c>
-      <c r="W201" s="80">
-        <f t="shared" si="121"/>
+      <c r="W202" s="80">
+        <f t="shared" si="123"/>
         <v>-5.1712250057458053E-2</v>
       </c>
-      <c r="X201" s="80">
-        <f t="shared" si="121"/>
+      <c r="X202" s="80">
+        <f t="shared" si="123"/>
         <v>-4.5322346097915654E-2</v>
       </c>
-      <c r="Y201" s="80">
-        <f t="shared" si="121"/>
+      <c r="Y202" s="80">
+        <f t="shared" si="123"/>
         <v>4.5189134298045192E-2</v>
       </c>
-      <c r="Z201" s="80">
-        <f t="shared" si="121"/>
+      <c r="Z202" s="80">
+        <f t="shared" si="123"/>
         <v>0.15059509351469516</v>
       </c>
-      <c r="AA201" s="80">
-        <f t="shared" si="121"/>
+      <c r="AA202" s="80">
+        <f t="shared" si="123"/>
         <v>6.6497783407219763E-2</v>
-      </c>
-      <c r="AC201" s="49"/>
-    </row>
-    <row r="202" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B202" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="M202" s="80">
-        <f t="shared" si="120"/>
-        <v>1</v>
-      </c>
-      <c r="N202" s="80">
-        <f t="shared" si="120"/>
-        <v>-0.16628914988814317</v>
-      </c>
-      <c r="O202" s="80">
-        <f t="shared" si="120"/>
-        <v>-0.1521793818236705</v>
-      </c>
-      <c r="P202" s="80">
-        <f t="shared" si="120"/>
-        <v>-2.1403279726227919E-2</v>
-      </c>
-      <c r="Q202" s="80">
-        <f t="shared" si="120"/>
-        <v>-6.5492915041135214E-3</v>
-      </c>
-      <c r="T202" s="80">
-        <f t="shared" si="121"/>
-        <v>1</v>
-      </c>
-      <c r="U202" s="80">
-        <f t="shared" si="121"/>
-        <v>2.9628389688650822E-2</v>
-      </c>
-      <c r="V202" s="80">
-        <f t="shared" si="121"/>
-        <v>6.6493253129572424E-2</v>
-      </c>
-      <c r="W202" s="80">
-        <f t="shared" si="121"/>
-        <v>-0.10403963414634146</v>
-      </c>
-      <c r="X202" s="80">
-        <f t="shared" si="121"/>
-        <v>4.6788600595491277E-3</v>
-      </c>
-      <c r="Y202" s="80">
-        <f t="shared" si="121"/>
-        <v>7.1295512277730733E-2</v>
-      </c>
-      <c r="Z202" s="80">
-        <f t="shared" si="121"/>
-        <v>2.1972810622826432E-2</v>
-      </c>
-      <c r="AA202" s="80">
-        <f t="shared" si="121"/>
-        <v>-1.1678267594740912E-2</v>
       </c>
       <c r="AC202" s="49"/>
     </row>
     <row r="203" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B203" s="20" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
       <c r="N203" s="80">
-        <f t="shared" si="120"/>
-        <v>0.35158501440922191</v>
+        <f t="shared" si="122"/>
+        <v>-0.16628914988814317</v>
       </c>
       <c r="O203" s="80">
-        <f t="shared" si="120"/>
-        <v>1.0298507462686568</v>
+        <f t="shared" si="122"/>
+        <v>-0.1521793818236705</v>
       </c>
       <c r="P203" s="80">
-        <f t="shared" si="120"/>
-        <v>17.190126050420169</v>
+        <f t="shared" si="122"/>
+        <v>-2.1403279726227919E-2</v>
       </c>
       <c r="Q203" s="80">
-        <f t="shared" si="120"/>
-        <v>2.9393081942599757E-2</v>
+        <f t="shared" si="122"/>
+        <v>-6.5492915041135214E-3</v>
       </c>
       <c r="T203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U203" s="80">
-        <f t="shared" si="121"/>
-        <v>1.3311536665109761E-2</v>
+        <f t="shared" si="123"/>
+        <v>2.9628389688650822E-2</v>
       </c>
       <c r="V203" s="80">
-        <f t="shared" si="121"/>
-        <v>2.3046784973496196E-4</v>
+        <f t="shared" si="123"/>
+        <v>6.6493253129572424E-2</v>
       </c>
       <c r="W203" s="80">
-        <f t="shared" si="121"/>
-        <v>7.5345622119815672E-2</v>
+        <f t="shared" si="123"/>
+        <v>-0.10403963414634146</v>
       </c>
       <c r="X203" s="80">
-        <f t="shared" si="121"/>
-        <v>-5.3567602314120423E-2</v>
+        <f t="shared" si="123"/>
+        <v>4.6788600595491277E-3</v>
       </c>
       <c r="Y203" s="80">
-        <f t="shared" si="121"/>
-        <v>-4.1204437400950873E-2</v>
+        <f t="shared" si="123"/>
+        <v>7.1295512277730733E-2</v>
       </c>
       <c r="Z203" s="80">
-        <f t="shared" si="121"/>
-        <v>6.4226682408500588E-2</v>
+        <f t="shared" si="123"/>
+        <v>2.1972810622826432E-2</v>
       </c>
       <c r="AA203" s="80">
-        <f t="shared" si="121"/>
-        <v>0.2027956512092301</v>
+        <f t="shared" si="123"/>
+        <v>-1.1678267594740912E-2</v>
       </c>
       <c r="AC203" s="49"/>
     </row>
     <row r="204" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B204" s="20" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
       <c r="N204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
+        <v>0.35158501440922191</v>
+      </c>
+      <c r="O204" s="80">
+        <f t="shared" si="122"/>
+        <v>1.0298507462686568</v>
+      </c>
+      <c r="P204" s="80">
+        <f t="shared" si="122"/>
+        <v>17.190126050420169</v>
+      </c>
+      <c r="Q204" s="80">
+        <f t="shared" si="122"/>
+        <v>2.9393081942599757E-2</v>
+      </c>
+      <c r="T204" s="80">
+        <f t="shared" si="123"/>
+        <v>1</v>
+      </c>
+      <c r="U204" s="80">
+        <f t="shared" si="123"/>
+        <v>1.3311536665109761E-2</v>
+      </c>
+      <c r="V204" s="80">
+        <f t="shared" si="123"/>
+        <v>2.3046784973496196E-4</v>
+      </c>
+      <c r="W204" s="80">
+        <f t="shared" si="123"/>
+        <v>7.5345622119815672E-2</v>
+      </c>
+      <c r="X204" s="80">
+        <f t="shared" si="123"/>
+        <v>-5.3567602314120423E-2</v>
+      </c>
+      <c r="Y204" s="80">
+        <f t="shared" si="123"/>
+        <v>-4.1204437400950873E-2</v>
+      </c>
+      <c r="Z204" s="80">
+        <f t="shared" si="123"/>
+        <v>6.4226682408500588E-2</v>
+      </c>
+      <c r="AA204" s="80">
+        <f t="shared" si="123"/>
+        <v>0.2027956512092301</v>
+      </c>
+      <c r="AC204" s="49"/>
+    </row>
+    <row r="205" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B205" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="M205" s="80">
+        <f t="shared" si="122"/>
+        <v>1</v>
+      </c>
+      <c r="N205" s="80">
+        <f t="shared" si="122"/>
         <v>-0.58669833729216148</v>
       </c>
-      <c r="O204" s="80">
-        <f t="shared" si="120"/>
+      <c r="O205" s="80">
+        <f t="shared" si="122"/>
         <v>-7.9445571331981074E-2</v>
       </c>
-      <c r="P204" s="80">
-        <f t="shared" si="120"/>
+      <c r="P205" s="80">
+        <f t="shared" si="122"/>
         <v>0.32243848696290855</v>
       </c>
-      <c r="Q204" s="80">
-        <f t="shared" si="120"/>
+      <c r="Q205" s="80">
+        <f t="shared" si="122"/>
         <v>-1.0552624271035824E-2</v>
       </c>
-      <c r="T204" s="80">
-        <f t="shared" si="121"/>
+      <c r="T205" s="80">
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
-      <c r="U204" s="80">
-        <f t="shared" si="121"/>
+      <c r="U205" s="80">
+        <f t="shared" si="123"/>
         <v>9.4211123723041995E-2</v>
       </c>
-      <c r="V204" s="80">
-        <f t="shared" si="121"/>
+      <c r="V205" s="80">
+        <f t="shared" si="123"/>
         <v>0.1545643153526971</v>
       </c>
-      <c r="W204" s="80">
-        <f t="shared" si="121"/>
+      <c r="W205" s="80">
+        <f t="shared" si="123"/>
         <v>-0.1527403414195867</v>
       </c>
-      <c r="X204" s="80">
-        <f t="shared" si="121"/>
+      <c r="X205" s="80">
+        <f t="shared" si="123"/>
         <v>0.11664899257688228</v>
       </c>
-      <c r="Y204" s="80">
-        <f t="shared" si="121"/>
+      <c r="Y205" s="80">
+        <f t="shared" si="123"/>
         <v>-5.6980056980056981E-2</v>
       </c>
-      <c r="Z204" s="80">
-        <f t="shared" si="121"/>
+      <c r="Z205" s="80">
+        <f t="shared" si="123"/>
         <v>-0.42195367573011078</v>
       </c>
-      <c r="AA204" s="80">
-        <f t="shared" si="121"/>
+      <c r="AA205" s="80">
+        <f t="shared" si="123"/>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="AC204" s="49"/>
-    </row>
-    <row r="206" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B206" s="1"/>
-    </row>
-    <row r="207" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B207" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="C207" s="172"/>
-      <c r="D207" s="172"/>
-      <c r="E207" s="172"/>
-      <c r="F207" s="172"/>
-      <c r="G207" s="172"/>
-      <c r="H207" s="172"/>
-      <c r="I207" s="172"/>
-      <c r="J207" s="172"/>
-      <c r="K207" s="172"/>
-      <c r="L207" s="172"/>
-      <c r="M207" s="172"/>
-      <c r="N207" s="172"/>
-      <c r="O207" s="172"/>
-      <c r="P207" s="172"/>
-      <c r="Q207" s="172"/>
-      <c r="T207" s="172"/>
-      <c r="U207" s="172"/>
-      <c r="V207" s="172"/>
-      <c r="W207" s="172"/>
-      <c r="X207" s="172"/>
-      <c r="Y207" s="172"/>
-      <c r="Z207" s="172"/>
-      <c r="AA207" s="172"/>
-      <c r="AC207" s="172"/>
-    </row>
-    <row r="208" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B208" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="C208" s="80"/>
-      <c r="D208" s="80"/>
-      <c r="E208" s="80"/>
-      <c r="F208" s="80"/>
-      <c r="G208" s="80"/>
-      <c r="H208" s="80"/>
-      <c r="I208" s="80"/>
-      <c r="J208" s="80"/>
-      <c r="K208" s="80"/>
-      <c r="L208" s="80"/>
-      <c r="M208" s="80">
+      <c r="AC205" s="49"/>
+    </row>
+    <row r="207" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B207" s="1"/>
+    </row>
+    <row r="208" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B208" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C208" s="172"/>
+      <c r="D208" s="172"/>
+      <c r="E208" s="172"/>
+      <c r="F208" s="172"/>
+      <c r="G208" s="172"/>
+      <c r="H208" s="172"/>
+      <c r="I208" s="172"/>
+      <c r="J208" s="172"/>
+      <c r="K208" s="172"/>
+      <c r="L208" s="172"/>
+      <c r="M208" s="172"/>
+      <c r="N208" s="172"/>
+      <c r="O208" s="172"/>
+      <c r="P208" s="172"/>
+      <c r="Q208" s="172"/>
+      <c r="T208" s="172"/>
+      <c r="U208" s="172"/>
+      <c r="V208" s="172"/>
+      <c r="W208" s="172"/>
+      <c r="X208" s="172"/>
+      <c r="Y208" s="172"/>
+      <c r="Z208" s="172"/>
+      <c r="AA208" s="172"/>
+      <c r="AC208" s="172"/>
+    </row>
+    <row r="209" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B209" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C209" s="80"/>
+      <c r="D209" s="80"/>
+      <c r="E209" s="80"/>
+      <c r="F209" s="80"/>
+      <c r="G209" s="80"/>
+      <c r="H209" s="80"/>
+      <c r="I209" s="80"/>
+      <c r="J209" s="80"/>
+      <c r="K209" s="80"/>
+      <c r="L209" s="80"/>
+      <c r="M209" s="80">
         <f>IF(L63=0,
 IF(M63=0,0,IF(M63&gt;0,1,-1)),
 (M63-L63)/L63
 )</f>
         <v>-1</v>
       </c>
-      <c r="N208" s="80">
+      <c r="N209" s="80">
         <f>IF(M63=0,
 IF(N63=0,0,IF(N63&gt;0,1,-1)),
 (N63-M63)/M63
 )</f>
         <v>6.2544294826364283E-2</v>
       </c>
-      <c r="O208" s="80">
+      <c r="O209" s="80">
         <f>IF(N63=0,
 IF(O63=0,0,IF(O63&gt;0,1,-1)),
 (O63-N63)/N63
 )</f>
         <v>-0.48507587126896784</v>
       </c>
-      <c r="P208" s="80">
+      <c r="P209" s="80">
         <f>IF(O63=0,
 IF(P63=0,0,IF(P63&gt;0,1,-1)),
 (P63-O63)/O63
 )</f>
         <v>-0.48218911917098445</v>
       </c>
-      <c r="Q208" s="80">
+      <c r="Q209" s="80">
         <f>IF(P63=0,
 IF(Q63=0,0,IF(Q63&gt;0,1,-1)),
 (Q63-P63)/P63
 )</f>
         <v>-1</v>
       </c>
-      <c r="T208" s="49"/>
-      <c r="U208" s="49"/>
-      <c r="V208" s="49"/>
-      <c r="W208" s="49"/>
-      <c r="X208" s="49"/>
-      <c r="Y208" s="49"/>
-      <c r="Z208" s="49"/>
-      <c r="AA208" s="49"/>
-      <c r="AC208" s="49"/>
+      <c r="T209" s="49"/>
+      <c r="U209" s="49"/>
+      <c r="V209" s="49"/>
+      <c r="W209" s="49"/>
+      <c r="X209" s="49"/>
+      <c r="Y209" s="49"/>
+      <c r="Z209" s="49"/>
+      <c r="AA209" s="49"/>
+      <c r="AC209" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31700,7 +31740,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
@@ -32067,11 +32107,11 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="228" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C37" s="228"/>
       <c r="E37" s="228" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F37" s="228"/>
     </row>
@@ -32084,26 +32124,26 @@
         <v>-6.2518906927498232E-3</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F38" s="177">
-        <f>Statement!AC185</f>
+        <f>Statement!AC186</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="217">
         <f ca="1">Statement!AC179</f>
         <v>-1.1014620715247336E-2</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F39" s="177">
-        <f>Statement!AC186</f>
+        <f>Statement!AC187</f>
         <v>0</v>
       </c>
     </row>
@@ -32116,16 +32156,16 @@
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F40" s="177">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C41" s="177">
         <f ca="1">Statement!AC182</f>
@@ -32134,7 +32174,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C42" s="177">
         <f ca="1">Statement!AC183</f>
@@ -32143,96 +32183,96 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="228" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C45" s="228"/>
       <c r="E45" s="228" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F45" s="228"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="C46" s="177">
+        <f>Statement!AC189</f>
+        <v>5.9689614007162755E-4</v>
+      </c>
+      <c r="E46" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="C46" s="177">
-        <f>Statement!AC188</f>
-        <v>5.9689614007162755E-4</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>282</v>
-      </c>
       <c r="F46" s="176">
-        <f>Statement!AC189</f>
+        <f>Statement!AC190</f>
         <v>6.5238758456028654</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F47" s="176">
-        <f>Statement!AC192</f>
+        <f>Statement!AC193</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F48" s="177">
-        <f ca="1">Statement!AC193</f>
+        <f ca="1">Statement!AC194</f>
         <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="228" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C51" s="228"/>
       <c r="E51" s="228" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F51" s="228"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C52" s="177">
-        <f>Statement!AC190</f>
+        <f>Statement!AC191</f>
         <v>0.2375751503006012</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F52" s="177">
-        <f>Statement!AC194</f>
+        <f>Statement!AC195</f>
         <v>0.24364339787586259</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C53" s="177">
-        <f>Statement!AC191</f>
+        <f>Statement!AC192</f>
         <v>4.4100961627885349E-2</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F53" s="177">
-        <f>Statement!AC195</f>
+        <f>Statement!AC196</f>
         <v>1.3125250501002004</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F54" s="177">
-        <f>Statement!AC196</f>
+        <f>Statement!AC197</f>
         <v>1.0765121630506247</v>
       </c>
     </row>
@@ -32921,7 +32961,7 @@
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -33302,7 +33342,7 @@
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -33342,7 +33382,7 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C52" s="177">
         <f>Statement!M179</f>
@@ -33400,7 +33440,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C54" s="177">
         <f>Statement!M182</f>
@@ -33429,7 +33469,7 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C55" s="177">
         <f>Statement!M183</f>
@@ -33458,7 +33498,7 @@
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -33469,94 +33509,94 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C58" s="177">
-        <f>Statement!M185</f>
+        <f>Statement!M186</f>
         <v>0.64970645792563597</v>
       </c>
       <c r="D58" s="177">
-        <f>Statement!N185</f>
+        <f>Statement!N186</f>
         <v>-0.47826780445011563</v>
       </c>
       <c r="E58" s="177">
-        <f>Statement!O185</f>
+        <f>Statement!O186</f>
         <v>-0.1763765135937857</v>
       </c>
       <c r="F58" s="177">
-        <f>Statement!P185</f>
+        <f>Statement!P186</f>
         <v>-8.3866568761145496E-2</v>
       </c>
       <c r="G58" s="177">
-        <f>Statement!Q185</f>
+        <f>Statement!Q186</f>
         <v>0</v>
       </c>
       <c r="I58" s="177">
-        <f>Statement!AC185</f>
+        <f>Statement!AC186</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C59" s="177">
-        <f>Statement!M186</f>
+        <f>Statement!M187</f>
         <v>0.27800161160354553</v>
       </c>
       <c r="D59" s="177">
-        <f>Statement!N186</f>
+        <f>Statement!N187</f>
         <v>0</v>
       </c>
       <c r="E59" s="177">
-        <f>Statement!O186</f>
+        <f>Statement!O187</f>
         <v>0</v>
       </c>
       <c r="F59" s="177">
-        <f>Statement!P186</f>
+        <f>Statement!P187</f>
         <v>0</v>
       </c>
       <c r="G59" s="177">
-        <f>Statement!Q186</f>
+        <f>Statement!Q187</f>
         <v>0</v>
       </c>
       <c r="I59" s="177">
-        <f>Statement!AC186</f>
+        <f>Statement!AC187</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C60" s="177">
-        <f>Statement!M187</f>
+        <f>Statement!M188</f>
         <v>0.9277080695291815</v>
       </c>
       <c r="D60" s="177">
-        <f>Statement!N187</f>
+        <f>Statement!N188</f>
         <v>-0.47826780445011563</v>
       </c>
       <c r="E60" s="177">
-        <f>Statement!O187</f>
+        <f>Statement!O188</f>
         <v>-0.1763765135937857</v>
       </c>
       <c r="F60" s="177">
-        <f>Statement!P187</f>
+        <f>Statement!P188</f>
         <v>-8.3866568761145496E-2</v>
       </c>
       <c r="G60" s="177">
-        <f>Statement!Q187</f>
+        <f>Statement!Q188</f>
         <v>0</v>
       </c>
       <c r="I60" s="177">
-        <f>Statement!AC187</f>
+        <f>Statement!AC188</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -33567,36 +33607,36 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C63" s="177">
-        <f>Statement!M188</f>
+        <f>Statement!M189</f>
         <v>4.874482086278333E-4</v>
       </c>
       <c r="D63" s="177">
-        <f>Statement!N188</f>
+        <f>Statement!N189</f>
         <v>4.8169556840077071E-4</v>
       </c>
       <c r="E63" s="177">
-        <f>Statement!O188</f>
+        <f>Statement!O189</f>
         <v>4.7058823529411766E-4</v>
       </c>
       <c r="F63" s="177">
-        <f>Statement!P188</f>
+        <f>Statement!P189</f>
         <v>4.6189376443418013E-4</v>
       </c>
       <c r="G63" s="177">
-        <f>Statement!Q188</f>
+        <f>Statement!Q189</f>
         <v>6.0060060060060057E-4</v>
       </c>
       <c r="I63" s="177">
-        <f>Statement!AC188</f>
+        <f>Statement!AC189</f>
         <v>5.9689614007162755E-4</v>
       </c>
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -33607,94 +33647,94 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C66" s="176">
-        <f>Statement!M189</f>
+        <f>Statement!M190</f>
         <v>6.9776522593320234</v>
       </c>
       <c r="D66" s="176">
-        <f>Statement!N189</f>
+        <f>Statement!N190</f>
         <v>6.8498912255257434</v>
       </c>
       <c r="E66" s="176">
-        <f>Statement!O189</f>
+        <f>Statement!O190</f>
         <v>5.9210028382213808</v>
       </c>
       <c r="F66" s="176">
-        <f>Statement!P189</f>
+        <f>Statement!P190</f>
         <v>5.0951501154734409</v>
       </c>
       <c r="G66" s="176">
-        <f>Statement!Q189</f>
+        <f>Statement!Q190</f>
         <v>7.4906906906906903</v>
       </c>
       <c r="I66" s="176">
-        <f>Statement!AC189</f>
+        <f>Statement!AC190</f>
         <v>6.5238758456028654</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C67" s="176">
-        <f>Statement!M192</f>
+        <f>Statement!M193</f>
         <v>-2.3791748526522594</v>
       </c>
       <c r="D67" s="176">
-        <f>Statement!N192</f>
+        <f>Statement!N193</f>
         <v>-3.3147208121827409</v>
       </c>
       <c r="E67" s="176">
-        <f>Statement!O192</f>
+        <f>Statement!O193</f>
         <v>-5.7313150425733204</v>
       </c>
       <c r="F67" s="176">
-        <f>Statement!P192</f>
+        <f>Statement!P193</f>
         <v>-6.4547344110854503</v>
       </c>
       <c r="G67" s="176">
-        <f>Statement!Q192</f>
+        <f>Statement!Q193</f>
         <v>-1.8356356356356356</v>
       </c>
       <c r="I67" s="176">
-        <f>Statement!AC192</f>
+        <f>Statement!AC193</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C68" s="198">
-        <f>Statement!M193</f>
+        <f>Statement!M194</f>
         <v>-4.601830291547894E-2</v>
       </c>
       <c r="D68" s="198">
-        <f>Statement!N193</f>
+        <f>Statement!N194</f>
         <v>-0.12496200017933728</v>
       </c>
       <c r="E68" s="198">
-        <f>Statement!O193</f>
+        <f>Statement!O194</f>
         <v>-0.11346561311091601</v>
       </c>
       <c r="F68" s="198">
-        <f>Statement!P193</f>
+        <f>Statement!P194</f>
         <v>-0.31796721236874137</v>
       </c>
       <c r="G68" s="198">
-        <f>Statement!Q193</f>
+        <f>Statement!Q194</f>
         <v>-5.070816673026618E-2</v>
       </c>
       <c r="I68" s="198">
-        <f ca="1">Statement!AC193</f>
+        <f ca="1">Statement!AC194</f>
         <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -33705,65 +33745,65 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C71" s="177">
-        <f>Statement!M190</f>
+        <f>Statement!M191</f>
         <v>6.9120043454644217E-2</v>
       </c>
       <c r="D71" s="177">
-        <f>Statement!N190</f>
+        <f>Statement!N191</f>
         <v>0.20268256333830104</v>
       </c>
       <c r="E71" s="177">
-        <f>Statement!O190</f>
+        <f>Statement!O191</f>
         <v>0.28149245924505273</v>
       </c>
       <c r="F71" s="177">
-        <f>Statement!P190</f>
+        <f>Statement!P191</f>
         <v>0.41143822393822393</v>
       </c>
       <c r="G71" s="177">
-        <f>Statement!Q190</f>
+        <f>Statement!Q191</f>
         <v>0.25100546560791998</v>
       </c>
       <c r="I71" s="177">
-        <f>Statement!AC190</f>
+        <f>Statement!AC191</f>
         <v>0.2375751503006012</v>
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C72" s="177">
-        <f>Statement!M191</f>
+        <f>Statement!M192</f>
         <v>2.5764324762097592E-2</v>
       </c>
       <c r="D72" s="177">
-        <f>Statement!N191</f>
+        <f>Statement!N192</f>
         <v>4.9608272274558315E-2</v>
       </c>
       <c r="E72" s="177">
-        <f>Statement!O191</f>
+        <f>Statement!O192</f>
         <v>5.9544884561481153E-2</v>
       </c>
       <c r="F72" s="177">
-        <f>Statement!P191</f>
+        <f>Statement!P192</f>
         <v>6.4217246379540877E-2</v>
       </c>
       <c r="G72" s="177">
-        <f>Statement!Q191</f>
+        <f>Statement!Q192</f>
         <v>4.6052258149963103E-2</v>
       </c>
       <c r="I72" s="177">
-        <f>Statement!AC191</f>
+        <f>Statement!AC192</f>
         <v>4.4100961627885349E-2</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -33774,88 +33814,88 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C75" s="177">
-        <f>Statement!M194</f>
+        <f>Statement!M195</f>
         <v>0.23705456570155903</v>
       </c>
       <c r="D75" s="177">
-        <f>Statement!N194</f>
+        <f>Statement!N195</f>
         <v>0.39401148222158783</v>
       </c>
       <c r="E75" s="177">
-        <f>Statement!O194</f>
+        <f>Statement!O195</f>
         <v>0.4748469425389098</v>
       </c>
       <c r="F75" s="177">
-        <f>Statement!P194</f>
+        <f>Statement!P195</f>
         <v>0.45091429539933336</v>
       </c>
       <c r="G75" s="177">
-        <f>Statement!Q194</f>
+        <f>Statement!Q195</f>
         <v>0.27710820577829071</v>
       </c>
       <c r="I75" s="177">
-        <f>Statement!AC194</f>
+        <f>Statement!AC195</f>
         <v>0.24364339787586259</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="177">
-        <f>Statement!M195</f>
+        <f>Statement!M196</f>
         <v>0.63596550787615425</v>
       </c>
       <c r="D76" s="177">
-        <f>Statement!N195</f>
+        <f>Statement!N196</f>
         <v>1.6097971878442299</v>
       </c>
       <c r="E76" s="177">
-        <f>Statement!O195</f>
+        <f>Statement!O196</f>
         <v>2.2447912126231366</v>
       </c>
       <c r="F76" s="177">
-        <f>Statement!P195</f>
+        <f>Statement!P196</f>
         <v>2.8889961389961392</v>
       </c>
       <c r="G76" s="177">
-        <f>Statement!Q195</f>
+        <f>Statement!Q196</f>
         <v>1.5103640301124059</v>
       </c>
       <c r="I76" s="177">
-        <f>Statement!AC195</f>
+        <f>Statement!AC196</f>
         <v>1.3125250501002004</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C77" s="177">
-        <f>Statement!M196</f>
+        <f>Statement!M197</f>
         <v>1.5886194029850746</v>
       </c>
       <c r="D77" s="177">
-        <f>Statement!N196</f>
+        <f>Statement!N197</f>
         <v>1.9059455312619868</v>
       </c>
       <c r="E77" s="177">
-        <f>Statement!O196</f>
+        <f>Statement!O197</f>
         <v>2.6817329722974379</v>
       </c>
       <c r="F77" s="177">
-        <f>Statement!P196</f>
+        <f>Statement!P197</f>
         <v>2.1042270849811056</v>
       </c>
       <c r="G77" s="177">
-        <f>Statement!Q196</f>
+        <f>Statement!Q197</f>
         <v>1.2511532547411583</v>
       </c>
       <c r="I77" s="177">
-        <f>Statement!AC196</f>
+        <f>Statement!AC197</f>
         <v>1.0765121630506247</v>
       </c>
     </row>
@@ -33976,7 +34016,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C84" s="177">
         <f>Statement!M95</f>
@@ -34002,7 +34042,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C85" s="177">
         <f>Statement!M97</f>
@@ -34028,7 +34068,7 @@
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -34039,137 +34079,137 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="218" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C89" s="177">
-        <f>Statement!M200</f>
+        <f>Statement!M201</f>
         <v>1</v>
       </c>
       <c r="D89" s="177">
-        <f>Statement!N200</f>
+        <f>Statement!N201</f>
         <v>-0.22657676298045326</v>
       </c>
       <c r="E89" s="177">
-        <f>Statement!O200</f>
+        <f>Statement!O201</f>
         <v>-7.9155257608661447E-2</v>
       </c>
       <c r="F89" s="177">
-        <f>Statement!P200</f>
+        <f>Statement!P201</f>
         <v>0.139722469068289</v>
       </c>
       <c r="G89" s="177">
-        <f>Statement!Q200</f>
+        <f>Statement!Q201</f>
         <v>-3.3527259641336293E-2</v>
       </c>
       <c r="I89" s="199"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="218" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C90" s="177">
-        <f>Statement!M201</f>
+        <f>Statement!M202</f>
         <v>1</v>
       </c>
       <c r="D90" s="177">
-        <f>Statement!N201</f>
+        <f>Statement!N202</f>
         <v>-8.4923946253162061E-2</v>
       </c>
       <c r="E90" s="177">
-        <f>Statement!O201</f>
+        <f>Statement!O202</f>
         <v>-0.23547784878293962</v>
       </c>
       <c r="F90" s="177">
-        <f>Statement!P201</f>
+        <f>Statement!P202</f>
         <v>-0.242779995304062</v>
       </c>
       <c r="G90" s="177">
-        <f>Statement!Q201</f>
+        <f>Statement!Q202</f>
         <v>4.9240310077519382E-2</v>
       </c>
       <c r="I90" s="199"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C91" s="177">
-        <f>Statement!M202</f>
+        <f>Statement!M203</f>
         <v>1</v>
       </c>
       <c r="D91" s="177">
-        <f>Statement!N202</f>
+        <f>Statement!N203</f>
         <v>-0.16628914988814317</v>
       </c>
       <c r="E91" s="177">
-        <f>Statement!O202</f>
+        <f>Statement!O203</f>
         <v>-0.1521793818236705</v>
       </c>
       <c r="F91" s="177">
-        <f>Statement!P202</f>
+        <f>Statement!P203</f>
         <v>-2.1403279726227919E-2</v>
       </c>
       <c r="G91" s="177">
-        <f>Statement!Q202</f>
+        <f>Statement!Q203</f>
         <v>-6.5492915041135214E-3</v>
       </c>
       <c r="I91" s="199"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C92" s="177">
-        <f>Statement!M203</f>
+        <f>Statement!M204</f>
         <v>1</v>
       </c>
       <c r="D92" s="177">
-        <f>Statement!N203</f>
+        <f>Statement!N204</f>
         <v>0.35158501440922191</v>
       </c>
       <c r="E92" s="177">
-        <f>Statement!O203</f>
+        <f>Statement!O204</f>
         <v>1.0298507462686568</v>
       </c>
       <c r="F92" s="177">
-        <f>Statement!P203</f>
+        <f>Statement!P204</f>
         <v>17.190126050420169</v>
       </c>
       <c r="G92" s="177">
-        <f>Statement!Q203</f>
+        <f>Statement!Q204</f>
         <v>2.9393081942599757E-2</v>
       </c>
       <c r="I92" s="199"/>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B93" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C93" s="177">
-        <f>Statement!M204</f>
+        <f>Statement!M205</f>
         <v>1</v>
       </c>
       <c r="D93" s="177">
-        <f>Statement!N204</f>
+        <f>Statement!N205</f>
         <v>-0.58669833729216148</v>
       </c>
       <c r="E93" s="177">
-        <f>Statement!O204</f>
+        <f>Statement!O205</f>
         <v>-7.9445571331981074E-2</v>
       </c>
       <c r="F93" s="177">
-        <f>Statement!P204</f>
+        <f>Statement!P205</f>
         <v>0.32243848696290855</v>
       </c>
       <c r="G93" s="177">
-        <f>Statement!Q204</f>
+        <f>Statement!Q205</f>
         <v>-1.0552624271035824E-2</v>
       </c>
       <c r="I93" s="199"/>
     </row>
     <row r="95" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B95" s="14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -34180,26 +34220,26 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B96" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C96" s="177">
-        <f>Statement!M208</f>
+        <f>Statement!M209</f>
         <v>-1</v>
       </c>
       <c r="D96" s="177">
-        <f>Statement!N208</f>
+        <f>Statement!N209</f>
         <v>6.2544294826364283E-2</v>
       </c>
       <c r="E96" s="177">
-        <f>Statement!O208</f>
+        <f>Statement!O209</f>
         <v>-0.48507587126896784</v>
       </c>
       <c r="F96" s="177">
-        <f>Statement!P208</f>
+        <f>Statement!P209</f>
         <v>-0.48218911917098445</v>
       </c>
       <c r="G96" s="177">
-        <f>Statement!Q208</f>
+        <f>Statement!Q209</f>
         <v>-1</v>
       </c>
       <c r="I96" s="199"/>
@@ -34228,11 +34268,11 @@
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
       <c r="C3" s="232" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D3" s="233"/>
       <c r="F3" s="234" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G3" s="233"/>
     </row>
@@ -34257,7 +34297,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
@@ -34299,7 +34339,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C7" s="235">
         <f>Statement!AA88</f>
@@ -34338,7 +34378,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C9" s="235">
         <f>Statement!AA89</f>
@@ -34377,7 +34417,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C11" s="235">
         <f>Statement!AA90</f>
@@ -34416,7 +34456,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C13" s="235">
         <f>Statement!AA94</f>
@@ -34434,7 +34474,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="209" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C14" s="202">
         <f>Statement!Z12</f>
@@ -34455,7 +34495,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C15" s="235">
         <f>Statement!AA95</f>
@@ -34494,7 +34534,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C17" s="235">
         <f>Statement!AA97</f>
@@ -34512,7 +34552,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="209" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C18" s="202">
         <f>Statement!Z22</f>
@@ -34533,7 +34573,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C19" s="235">
         <f>IF(C18=0,
@@ -34575,7 +34615,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C21" s="235">
         <f>IF(C20=0,
@@ -34596,7 +34636,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
@@ -34617,7 +34657,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C24" s="202">
         <f>Statement!Z105</f>
@@ -34638,7 +34678,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C25" s="235">
         <f>IF(C24=0,
@@ -34659,7 +34699,7 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C26" s="202">
         <f>Statement!Z106</f>
@@ -34680,7 +34720,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C27" s="235">
         <f>IF(C26=0,
@@ -34701,7 +34741,7 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C28" s="202">
         <f>Statement!Z107</f>
@@ -34722,7 +34762,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C29" s="235">
         <f>IF(C28=0,
@@ -34743,7 +34783,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C30" s="202">
         <f>Statement!Z108</f>
@@ -34764,7 +34804,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C31" s="235">
         <f>IF(C30=0,
@@ -34785,7 +34825,7 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C32" s="202">
         <f>Statement!Z109</f>
@@ -34806,7 +34846,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C33" s="235">
         <f>IF(C32=0,
@@ -35321,7 +35361,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C65" s="63">
         <f>Statement!H107</f>
@@ -35366,7 +35406,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C66" s="63">
         <f>Statement!H108</f>
@@ -35411,7 +35451,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C67" s="63">
         <f>Statement!H109</f>
@@ -35899,7 +35939,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C63" s="63">
         <f>Statement!T107</f>
@@ -35936,7 +35976,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C64" s="63">
         <f>Statement!T108</f>
@@ -35973,7 +36013,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C65" s="63">
         <f>Statement!T109</f>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81E3354-E6F3-8E44-8BA9-0AB58DD17B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F7BE80-9DA7-7642-B327-BAA527741F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="9" activeTab="16" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="397">
   <si>
     <t>Ticker</t>
   </si>
@@ -1331,6 +1331,18 @@
   </si>
   <si>
     <t>FCFE/Sales (FCFE Margin)</t>
+  </si>
+  <si>
+    <t>Manual WACC</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PV of EV</t>
   </si>
 </sst>
 </file>
@@ -1934,7 +1946,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2140,7 +2152,6 @@
     <xf numFmtId="10" fontId="10" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="10" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2251,6 +2262,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2258,12 +2275,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2293,6 +2304,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="12" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="16" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12541,7 +12555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I47"/>
+  <dimension ref="B1:I49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -12558,338 +12572,338 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="229" t="s">
+      <c r="B2" s="228" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="230"/>
-      <c r="E2" s="229" t="s">
+      <c r="C2" s="229"/>
+      <c r="E2" s="228" t="s">
         <v>290</v>
       </c>
-      <c r="F2" s="230"/>
-      <c r="H2" s="229" t="s">
+      <c r="F2" s="229"/>
+      <c r="H2" s="228" t="s">
         <v>331</v>
       </c>
-      <c r="I2" s="230"/>
+      <c r="I2" s="229"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="186" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="223" t="e" vm="1">
+      <c r="C3" s="222" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="187" t="s">
+      <c r="E3" s="186" t="s">
         <v>242</v>
       </c>
-      <c r="F3" s="189">
+      <c r="F3" s="188">
         <f ca="1">Statement!AC171</f>
         <v>498428.42</v>
       </c>
-      <c r="H3" s="187" t="str">
+      <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
         <v>DCF price</v>
       </c>
-      <c r="I3" s="213">
+      <c r="I3" s="212">
         <f ca="1">'AVG target price'!C5</f>
         <v>-8.7808283251417247</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="187" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="191" t="str" cm="1">
+      <c r="B4" s="186" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="190" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">_FV(C3,"Ticker symbol",TRUE)</f>
         <v>INTC</v>
       </c>
-      <c r="E4" s="188" t="s">
+      <c r="E4" s="187" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="190">
+      <c r="F4" s="189">
         <f ca="1">Statement!AC172</f>
         <v>524265.41999999993</v>
       </c>
-      <c r="H4" s="187" t="str">
+      <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
         <v>EV/EBIT price</v>
       </c>
-      <c r="I4" s="213">
+      <c r="I4" s="212">
         <f ca="1">'AVG target price'!C6</f>
-        <v>32.235530728427833</v>
+        <v>34.816924856030617</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="187" t="s">
+      <c r="B5" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="210" cm="1">
+      <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
         <v>99.17</v>
       </c>
-      <c r="E5" s="187" t="s">
+      <c r="E5" s="186" t="s">
         <v>246</v>
       </c>
-      <c r="F5" s="191">
+      <c r="F5" s="190">
         <f>Statement!AC26</f>
         <v>-0.62</v>
       </c>
-      <c r="H5" s="187" t="str">
+      <c r="H5" s="186" t="str">
         <f>'AVG target price'!B7</f>
         <v>PS price</v>
       </c>
-      <c r="I5" s="213">
-        <f ca="1">'AVG target price'!C7</f>
-        <v>36.372280552996166</v>
+      <c r="I5" s="212">
+        <f>'AVG target price'!C7</f>
+        <v>39.399238739054248</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="187" t="s">
+      <c r="B6" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="210" cm="1">
+      <c r="C6" s="209" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
         <v>96.924899999999994</v>
       </c>
-      <c r="E6" s="187" t="s">
+      <c r="E6" s="186" t="s">
         <v>240</v>
       </c>
-      <c r="F6" s="192">
+      <c r="F6" s="191">
         <f ca="1">Statement!AC168</f>
         <v>-159.95161290322582</v>
       </c>
-      <c r="H6" s="187" t="str">
+      <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
         <v>EV/FCFF price</v>
       </c>
-      <c r="I6" s="213">
+      <c r="I6" s="212">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-10.955445307711837</v>
+        <v>-13.952287486888657</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="187" t="s">
+      <c r="B7" s="186" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
         <v>-12.61</v>
       </c>
-      <c r="E7" s="188" t="s">
+      <c r="E7" s="187" t="s">
         <v>197</v>
       </c>
-      <c r="F7" s="193">
+      <c r="F7" s="192">
         <f ca="1">Statement!AC169</f>
         <v>8.6796576641928471</v>
       </c>
-      <c r="H7" s="186" t="str">
+      <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
         <v>AVG price</v>
       </c>
-      <c r="I7" s="214">
+      <c r="I7" s="213">
         <f ca="1">'AVG target price'!C9</f>
-        <v>12.21788441214261</v>
+        <v>12.87076194576362</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="187" t="s">
+      <c r="B8" s="186" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
         <v>-2.2450999999999999</v>
       </c>
-      <c r="E8" s="187" t="s">
+      <c r="E8" s="186" t="s">
         <v>268</v>
       </c>
-      <c r="F8" s="194">
+      <c r="F8" s="193">
         <f ca="1">Statement!AC179</f>
         <v>-1.1014620715247336E-2</v>
       </c>
-      <c r="H8" s="186" t="str">
+      <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
         <v>Upside/Downside</v>
       </c>
-      <c r="I8" s="215">
+      <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.87679858412682654</v>
+        <v>-0.87021516642368035</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="187" t="s">
+      <c r="B9" s="186" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
         <v>-0.11281100000000001</v>
       </c>
-      <c r="E9" s="187" t="s">
+      <c r="E9" s="186" t="s">
         <v>291</v>
       </c>
-      <c r="F9" s="194">
+      <c r="F9" s="193">
         <f ca="1">Statement!AC180</f>
         <v>-6.2518906927498232E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="187" t="s">
+      <c r="B10" s="186" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
         <v>-2.2638999999999999E-2</v>
       </c>
-      <c r="E10" s="187" t="s">
+      <c r="E10" s="186" t="s">
         <v>296</v>
       </c>
-      <c r="F10" s="194">
+      <c r="F10" s="193">
         <f ca="1">Statement!AC182</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="187" t="s">
+      <c r="B11" s="186" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="211" cm="1">
+      <c r="C11" s="210" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
         <v>132.75</v>
       </c>
-      <c r="E11" s="188" t="s">
+      <c r="E11" s="187" t="s">
         <v>292</v>
       </c>
-      <c r="F11" s="195">
+      <c r="F11" s="194">
         <f ca="1">Statement!AC181</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="187" t="s">
+      <c r="B12" s="186" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="211" cm="1">
+      <c r="C12" s="210" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
         <v>18.965</v>
       </c>
-      <c r="E12" s="187" t="s">
+      <c r="E12" s="186" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="194">
+      <c r="F12" s="193">
         <f>Statement!AC136</f>
         <v>-1.6402703913661776E-2</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="187" t="s">
+      <c r="B13" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="211" cm="1">
+      <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
         <v>2.2513000000000001</v>
       </c>
-      <c r="E13" s="187" t="s">
+      <c r="E13" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="194">
+      <c r="F13" s="193">
         <f>Statement!AC138</f>
         <v>-3.0235021634917498E-2</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="188" t="s">
+      <c r="B14" s="187" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="212" cm="1">
+      <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
         <v>137584440</v>
       </c>
-      <c r="E14" s="188" t="s">
+      <c r="E14" s="187" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="195">
+      <c r="F14" s="194">
         <f>Statement!AC158</f>
         <v>-3.6791978488825414E-2</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E15" s="187" t="s">
+      <c r="E15" s="186" t="s">
         <v>293</v>
       </c>
-      <c r="F15" s="194">
+      <c r="F15" s="193">
         <f ca="1">Statement!AC194</f>
         <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="E16" s="188" t="s">
+      <c r="E16" s="187" t="s">
         <v>298</v>
       </c>
-      <c r="F16" s="193">
+      <c r="F16" s="192">
         <f>Statement!AC193</f>
         <v>-2.435734182252288</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="231" t="s">
+      <c r="B17" s="230" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="231"/>
-      <c r="E17" s="186" t="s">
+      <c r="C17" s="230"/>
+      <c r="E17" s="185" t="s">
         <v>299</v>
       </c>
-      <c r="F17" s="196">
+      <c r="F17" s="195">
         <f>Statement!AC189</f>
         <v>5.9689614007162755E-4</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" s="186" t="s">
+      <c r="B18" s="185" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="68" t="s">
         <v>336</v>
       </c>
-      <c r="E18" s="187" t="s">
+      <c r="E18" s="186" t="s">
         <v>300</v>
       </c>
-      <c r="F18" s="192">
+      <c r="F18" s="191">
         <f>Statement!AC162</f>
         <v>82.9857136586363</v>
       </c>
       <c r="I18" s="50"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="186" t="s">
+      <c r="B19" s="185" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="69">
         <v>1000000</v>
       </c>
-      <c r="E19" s="187" t="s">
+      <c r="E19" s="186" t="s">
         <v>261</v>
       </c>
-      <c r="F19" s="192">
+      <c r="F19" s="191">
         <f>Statement!AC164</f>
         <v>0.10989819918487531</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="186" t="s">
+      <c r="B20" s="185" t="s">
         <v>88</v>
       </c>
       <c r="C20" s="68" t="s">
         <v>377</v>
       </c>
-      <c r="E20" s="188" t="s">
+      <c r="E20" s="187" t="s">
         <v>301</v>
       </c>
-      <c r="F20" s="193">
+      <c r="F20" s="192">
         <f>Statement!AC165</f>
         <v>1.3708387576715642</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="186" t="s">
+      <c r="B21" s="185" t="s">
         <v>89</v>
       </c>
       <c r="C21" s="68" t="s">
@@ -12898,7 +12912,7 @@
       <c r="I21" s="50"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="186" t="s">
+      <c r="B22" s="185" t="s">
         <v>90</v>
       </c>
       <c r="C22" s="68" t="s">
@@ -12906,129 +12920,151 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="231" t="s">
+      <c r="B25" s="230" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="231"/>
-      <c r="E25" s="229" t="s">
+      <c r="C25" s="230"/>
+      <c r="E25" s="228" t="s">
         <v>388</v>
       </c>
-      <c r="F25" s="230"/>
+      <c r="F25" s="229"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="186" t="s">
+      <c r="B26" s="185" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="171">
+      <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="187" t="e" vm="2">
+      <c r="E26" s="186" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="F26" s="226" cm="1">
+      <c r="F26" s="225" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
         <v>45.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="186" t="s">
+      <c r="B27" s="185" t="s">
         <v>168</v>
       </c>
-      <c r="C27" s="221">
+      <c r="C27" s="220">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E27" s="188" t="s">
+      <c r="E27" s="187" t="s">
         <v>389</v>
       </c>
-      <c r="F27" s="227">
+      <c r="F27" s="226">
         <f ca="1">F26/1000</f>
         <v>4.5359999999999998E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="228" t="s">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="185" t="s">
+        <v>393</v>
+      </c>
+      <c r="C28" s="220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="185" t="s">
+        <v>394</v>
+      </c>
+      <c r="C29" s="220">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" s="227" t="s">
         <v>356</v>
       </c>
-      <c r="C31" s="228"/>
-      <c r="D31" s="228"/>
-      <c r="E31" s="228"/>
-      <c r="F31" s="228"/>
-      <c r="G31" s="228"/>
-      <c r="H31" s="228"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="16" t="s">
+      <c r="C33" s="227"/>
+      <c r="D33" s="227"/>
+      <c r="E33" s="227"/>
+      <c r="F33" s="227"/>
+      <c r="G33" s="227"/>
+      <c r="H33" s="227"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="16" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="228"/>
-      <c r="C37" s="228"/>
-      <c r="D37" s="228"/>
-      <c r="E37" s="228"/>
-      <c r="F37" s="228"/>
-      <c r="G37" s="228"/>
-      <c r="H37" s="228"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="228" t="s">
+    <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="227"/>
+      <c r="C39" s="227"/>
+      <c r="D39" s="227"/>
+      <c r="E39" s="227"/>
+      <c r="F39" s="227"/>
+      <c r="G39" s="227"/>
+      <c r="H39" s="227"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="227" t="s">
         <v>359</v>
       </c>
-      <c r="C40" s="228"/>
-      <c r="D40" s="228"/>
-      <c r="E40" s="228"/>
-      <c r="F40" s="228"/>
-      <c r="G40" s="228"/>
-      <c r="H40" s="228"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="41" t="s">
+      <c r="C42" s="227"/>
+      <c r="D42" s="227"/>
+      <c r="E42" s="227"/>
+      <c r="F42" s="227"/>
+      <c r="G42" s="227"/>
+      <c r="H42" s="227"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="41" t="s">
         <v>360</v>
       </c>
-      <c r="C42" s="41" t="s">
+      <c r="C44" s="41" t="s">
         <v>343</v>
       </c>
-      <c r="D42" s="41" t="s">
+      <c r="D44" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="E42" s="220"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B43" s="1" t="s">
+      <c r="E44" s="219"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="245" t="s">
+        <v>395</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="245" t="s">
+        <v>395</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="228"/>
-      <c r="C47" s="228"/>
-      <c r="D47" s="228"/>
-      <c r="E47" s="228"/>
-      <c r="F47" s="228"/>
-      <c r="G47" s="228"/>
-      <c r="H47" s="228"/>
+    <row r="49" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="227"/>
+      <c r="C49" s="227"/>
+      <c r="D49" s="227"/>
+      <c r="E49" s="227"/>
+      <c r="F49" s="227"/>
+      <c r="G49" s="227"/>
+      <c r="H49" s="227"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
@@ -13104,36 +13140,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="228" t="s">
+      <c r="C2" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="228"/>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="241" t="s">
+      <c r="D2" s="227"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="228"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="227"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="228" t="s">
+      <c r="S2" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="228"/>
-      <c r="U2" s="228"/>
-      <c r="V2" s="228"/>
-      <c r="W2" s="228"/>
-      <c r="X2" s="228"/>
-      <c r="Y2" s="228"/>
-      <c r="Z2" s="228"/>
-      <c r="AA2" s="228" t="s">
+      <c r="T2" s="227"/>
+      <c r="U2" s="227"/>
+      <c r="V2" s="227"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="227"/>
+      <c r="Y2" s="227"/>
+      <c r="Z2" s="227"/>
+      <c r="AA2" s="227" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="228"/>
-      <c r="AC2" s="228"/>
+      <c r="AB2" s="227"/>
+      <c r="AC2" s="227"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -13144,32 +13180,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="237" t="s">
+      <c r="C4" s="236" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="237"/>
-      <c r="E4" s="237"/>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
-      <c r="H4" s="237"/>
-      <c r="I4" s="237"/>
-      <c r="J4" s="237"/>
-      <c r="K4" s="237"/>
-      <c r="L4" s="237"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="238" t="s">
+      <c r="S4" s="237" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="239"/>
-      <c r="U4" s="239"/>
-      <c r="V4" s="239"/>
-      <c r="W4" s="239"/>
-      <c r="X4" s="239"/>
-      <c r="Y4" s="239"/>
-      <c r="Z4" s="239"/>
-      <c r="AA4" s="239"/>
-      <c r="AB4" s="239"/>
-      <c r="AC4" s="239"/>
+      <c r="T4" s="238"/>
+      <c r="U4" s="238"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="238"/>
+      <c r="X4" s="238"/>
+      <c r="Y4" s="238"/>
+      <c r="Z4" s="238"/>
+      <c r="AA4" s="238"/>
+      <c r="AB4" s="238"/>
+      <c r="AC4" s="238"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13857,33 +13893,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="237" t="s">
+      <c r="C13" s="236" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="E13" s="237"/>
-      <c r="F13" s="237"/>
-      <c r="G13" s="237"/>
-      <c r="H13" s="237"/>
-      <c r="I13" s="237"/>
-      <c r="J13" s="237"/>
-      <c r="K13" s="237"/>
-      <c r="L13" s="237"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="236"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="236"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="238" t="s">
+      <c r="S13" s="237" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="239"/>
-      <c r="U13" s="239"/>
-      <c r="V13" s="239"/>
-      <c r="W13" s="239"/>
-      <c r="X13" s="239"/>
-      <c r="Y13" s="239"/>
-      <c r="Z13" s="239"/>
-      <c r="AA13" s="239"/>
-      <c r="AB13" s="239"/>
-      <c r="AC13" s="239"/>
+      <c r="T13" s="238"/>
+      <c r="U13" s="238"/>
+      <c r="V13" s="238"/>
+      <c r="W13" s="238"/>
+      <c r="X13" s="238"/>
+      <c r="Y13" s="238"/>
+      <c r="Z13" s="238"/>
+      <c r="AA13" s="238"/>
+      <c r="AB13" s="238"/>
+      <c r="AC13" s="238"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -14520,35 +14556,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="228" t="s">
+      <c r="C2" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="228"/>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="241" t="s">
+      <c r="D2" s="227"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="228"/>
-      <c r="P2" s="228" t="s">
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="227"/>
+      <c r="P2" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="228"/>
-      <c r="R2" s="228"/>
-      <c r="S2" s="228"/>
-      <c r="T2" s="228"/>
-      <c r="U2" s="228"/>
-      <c r="V2" s="228"/>
-      <c r="W2" s="228"/>
-      <c r="X2" s="228" t="s">
+      <c r="Q2" s="227"/>
+      <c r="R2" s="227"/>
+      <c r="S2" s="227"/>
+      <c r="T2" s="227"/>
+      <c r="U2" s="227"/>
+      <c r="V2" s="227"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="227" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="228"/>
-      <c r="Z2" s="228"/>
+      <c r="Y2" s="227"/>
+      <c r="Z2" s="227"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14557,31 +14593,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="237" t="s">
+      <c r="C4" s="236" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="237"/>
-      <c r="E4" s="237"/>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
-      <c r="H4" s="237"/>
-      <c r="I4" s="237"/>
-      <c r="J4" s="237"/>
-      <c r="K4" s="237"/>
-      <c r="L4" s="237"/>
-      <c r="P4" s="239" t="s">
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
+      <c r="P4" s="238" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="239"/>
-      <c r="R4" s="239"/>
-      <c r="S4" s="239"/>
-      <c r="T4" s="239"/>
-      <c r="U4" s="239"/>
-      <c r="V4" s="239"/>
-      <c r="W4" s="239"/>
-      <c r="X4" s="239"/>
-      <c r="Y4" s="239"/>
-      <c r="Z4" s="239"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="238"/>
+      <c r="T4" s="238"/>
+      <c r="U4" s="238"/>
+      <c r="V4" s="238"/>
+      <c r="W4" s="238"/>
+      <c r="X4" s="238"/>
+      <c r="Y4" s="238"/>
+      <c r="Z4" s="238"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -14776,32 +14812,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="237" t="s">
+      <c r="C9" s="236" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="E9" s="237"/>
-      <c r="F9" s="237"/>
-      <c r="G9" s="237"/>
-      <c r="H9" s="237"/>
-      <c r="I9" s="237"/>
-      <c r="J9" s="237"/>
-      <c r="K9" s="237"/>
-      <c r="L9" s="237"/>
+      <c r="D9" s="236"/>
+      <c r="E9" s="236"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="239" t="s">
+      <c r="P9" s="238" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="239"/>
-      <c r="R9" s="239"/>
-      <c r="S9" s="239"/>
-      <c r="T9" s="239"/>
-      <c r="U9" s="239"/>
-      <c r="V9" s="239"/>
-      <c r="W9" s="239"/>
-      <c r="X9" s="239"/>
-      <c r="Y9" s="239"/>
-      <c r="Z9" s="239"/>
+      <c r="Q9" s="238"/>
+      <c r="R9" s="238"/>
+      <c r="S9" s="238"/>
+      <c r="T9" s="238"/>
+      <c r="U9" s="238"/>
+      <c r="V9" s="238"/>
+      <c r="W9" s="238"/>
+      <c r="X9" s="238"/>
+      <c r="Y9" s="238"/>
+      <c r="Z9" s="238"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -15371,31 +15407,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="237" t="s">
+      <c r="C18" s="236" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="237"/>
-      <c r="E18" s="237"/>
-      <c r="F18" s="237"/>
-      <c r="G18" s="237"/>
-      <c r="H18" s="237"/>
-      <c r="I18" s="237"/>
-      <c r="J18" s="237"/>
-      <c r="K18" s="237"/>
-      <c r="L18" s="237"/>
-      <c r="P18" s="239" t="s">
+      <c r="D18" s="236"/>
+      <c r="E18" s="236"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="236"/>
+      <c r="P18" s="238" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="239"/>
-      <c r="R18" s="239"/>
-      <c r="S18" s="239"/>
-      <c r="T18" s="239"/>
-      <c r="U18" s="239"/>
-      <c r="V18" s="239"/>
-      <c r="W18" s="239"/>
-      <c r="X18" s="239"/>
-      <c r="Y18" s="239"/>
-      <c r="Z18" s="239"/>
+      <c r="Q18" s="238"/>
+      <c r="R18" s="238"/>
+      <c r="S18" s="238"/>
+      <c r="T18" s="238"/>
+      <c r="U18" s="238"/>
+      <c r="V18" s="238"/>
+      <c r="W18" s="238"/>
+      <c r="X18" s="238"/>
+      <c r="Y18" s="238"/>
+      <c r="Z18" s="238"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -15955,60 +15991,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="228" t="s">
+      <c r="C3" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="228"/>
-      <c r="E3" s="228"/>
-      <c r="F3" s="228"/>
-      <c r="G3" s="240"/>
-      <c r="H3" s="241" t="s">
+      <c r="D3" s="227"/>
+      <c r="E3" s="227"/>
+      <c r="F3" s="227"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="228"/>
-      <c r="J3" s="228"/>
-      <c r="K3" s="228"/>
-      <c r="L3" s="228"/>
-      <c r="P3" s="242"/>
-      <c r="Q3" s="242"/>
-      <c r="R3" s="242"/>
-      <c r="S3" s="242"/>
-      <c r="T3" s="242"/>
-      <c r="U3" s="242"/>
-      <c r="V3" s="242"/>
-      <c r="W3" s="242"/>
-      <c r="X3" s="242"/>
-      <c r="Y3" s="242"/>
-      <c r="Z3" s="242"/>
+      <c r="I3" s="227"/>
+      <c r="J3" s="227"/>
+      <c r="K3" s="227"/>
+      <c r="L3" s="227"/>
+      <c r="P3" s="241"/>
+      <c r="Q3" s="241"/>
+      <c r="R3" s="241"/>
+      <c r="S3" s="241"/>
+      <c r="T3" s="241"/>
+      <c r="U3" s="241"/>
+      <c r="V3" s="241"/>
+      <c r="W3" s="241"/>
+      <c r="X3" s="241"/>
+      <c r="Y3" s="241"/>
+      <c r="Z3" s="241"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="237" t="s">
+      <c r="C5" s="236" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="237"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="237"/>
-      <c r="G5" s="237"/>
-      <c r="H5" s="237"/>
-      <c r="I5" s="237"/>
-      <c r="J5" s="237"/>
-      <c r="K5" s="237"/>
-      <c r="L5" s="237"/>
-      <c r="P5" s="242"/>
-      <c r="Q5" s="242"/>
-      <c r="R5" s="242"/>
-      <c r="S5" s="242"/>
-      <c r="T5" s="242"/>
-      <c r="U5" s="242"/>
-      <c r="V5" s="242"/>
-      <c r="W5" s="242"/>
-      <c r="X5" s="242"/>
-      <c r="Y5" s="242"/>
-      <c r="Z5" s="242"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="236"/>
+      <c r="P5" s="241"/>
+      <c r="Q5" s="241"/>
+      <c r="R5" s="241"/>
+      <c r="S5" s="241"/>
+      <c r="T5" s="241"/>
+      <c r="U5" s="241"/>
+      <c r="V5" s="241"/>
+      <c r="W5" s="241"/>
+      <c r="X5" s="241"/>
+      <c r="Y5" s="241"/>
+      <c r="Z5" s="241"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -16194,30 +16230,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="237" t="s">
+      <c r="C11" s="236" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="E11" s="237"/>
-      <c r="F11" s="237"/>
-      <c r="G11" s="237"/>
-      <c r="H11" s="237"/>
-      <c r="I11" s="237"/>
-      <c r="J11" s="237"/>
-      <c r="K11" s="237"/>
-      <c r="L11" s="237"/>
+      <c r="D11" s="236"/>
+      <c r="E11" s="236"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="242"/>
-      <c r="Q11" s="242"/>
-      <c r="R11" s="242"/>
-      <c r="S11" s="242"/>
-      <c r="T11" s="242"/>
-      <c r="U11" s="242"/>
-      <c r="V11" s="242"/>
-      <c r="W11" s="242"/>
-      <c r="X11" s="242"/>
-      <c r="Y11" s="242"/>
-      <c r="Z11" s="242"/>
+      <c r="P11" s="241"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="241"/>
+      <c r="S11" s="241"/>
+      <c r="T11" s="241"/>
+      <c r="U11" s="241"/>
+      <c r="V11" s="241"/>
+      <c r="W11" s="241"/>
+      <c r="X11" s="241"/>
+      <c r="Y11" s="241"/>
+      <c r="Z11" s="241"/>
       <c r="AB11" s="109"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -16459,18 +16495,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="237" t="s">
+      <c r="C18" s="236" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="237"/>
-      <c r="E18" s="237"/>
-      <c r="F18" s="237"/>
-      <c r="G18" s="237"/>
-      <c r="H18" s="237"/>
-      <c r="I18" s="237"/>
-      <c r="J18" s="237"/>
-      <c r="K18" s="237"/>
-      <c r="L18" s="237"/>
+      <c r="D18" s="236"/>
+      <c r="E18" s="236"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="236"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -16683,23 +16719,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="242"/>
-      <c r="C25" s="242"/>
+      <c r="B25" s="241"/>
+      <c r="C25" s="241"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="237" t="s">
+      <c r="C26" s="236" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="237"/>
-      <c r="E26" s="237"/>
-      <c r="F26" s="237"/>
-      <c r="G26" s="237"/>
-      <c r="H26" s="237"/>
-      <c r="I26" s="237"/>
-      <c r="J26" s="237"/>
-      <c r="K26" s="237"/>
-      <c r="L26" s="237"/>
+      <c r="D26" s="236"/>
+      <c r="E26" s="236"/>
+      <c r="F26" s="236"/>
+      <c r="G26" s="236"/>
+      <c r="H26" s="236"/>
+      <c r="I26" s="236"/>
+      <c r="J26" s="236"/>
+      <c r="K26" s="236"/>
+      <c r="L26" s="236"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -16891,18 +16927,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="237" t="s">
+      <c r="C33" s="236" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
-      <c r="I33" s="237"/>
-      <c r="J33" s="237"/>
-      <c r="K33" s="237"/>
-      <c r="L33" s="237"/>
+      <c r="D33" s="236"/>
+      <c r="E33" s="236"/>
+      <c r="F33" s="236"/>
+      <c r="G33" s="236"/>
+      <c r="H33" s="236"/>
+      <c r="I33" s="236"/>
+      <c r="J33" s="236"/>
+      <c r="K33" s="236"/>
+      <c r="L33" s="236"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17086,18 +17122,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="237" t="s">
+      <c r="C40" s="236" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="237"/>
-      <c r="E40" s="237"/>
-      <c r="F40" s="237"/>
-      <c r="G40" s="237"/>
-      <c r="H40" s="237"/>
-      <c r="I40" s="237"/>
-      <c r="J40" s="237"/>
-      <c r="K40" s="237"/>
-      <c r="L40" s="237"/>
+      <c r="D40" s="236"/>
+      <c r="E40" s="236"/>
+      <c r="F40" s="236"/>
+      <c r="G40" s="236"/>
+      <c r="H40" s="236"/>
+      <c r="I40" s="236"/>
+      <c r="J40" s="236"/>
+      <c r="K40" s="236"/>
+      <c r="L40" s="236"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -17361,6 +17397,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -17368,12 +17410,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17411,60 +17447,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="228" t="s">
+      <c r="C2" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="228"/>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="241" t="s">
+      <c r="D2" s="227"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="228"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242"/>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="227"/>
+      <c r="S2" s="241"/>
+      <c r="T2" s="241"/>
+      <c r="U2" s="241"/>
+      <c r="V2" s="241"/>
+      <c r="W2" s="241"/>
+      <c r="X2" s="241"/>
+      <c r="Y2" s="241"/>
+      <c r="Z2" s="241"/>
+      <c r="AA2" s="241"/>
+      <c r="AB2" s="241"/>
+      <c r="AC2" s="241"/>
       <c r="AE2" s="108"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="237" t="s">
+      <c r="C4" s="236" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="237"/>
-      <c r="E4" s="237"/>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
-      <c r="H4" s="237"/>
-      <c r="I4" s="237"/>
-      <c r="J4" s="237"/>
-      <c r="K4" s="237"/>
-      <c r="L4" s="237"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
-      <c r="AA4" s="242"/>
-      <c r="AB4" s="242"/>
-      <c r="AC4" s="242"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
+      <c r="S4" s="241"/>
+      <c r="T4" s="241"/>
+      <c r="U4" s="241"/>
+      <c r="V4" s="241"/>
+      <c r="W4" s="241"/>
+      <c r="X4" s="241"/>
+      <c r="Y4" s="241"/>
+      <c r="Z4" s="241"/>
+      <c r="AA4" s="241"/>
+      <c r="AB4" s="241"/>
+      <c r="AC4" s="241"/>
       <c r="AE4" s="109"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17827,18 +17863,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="237" t="s">
+      <c r="C13" s="236" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="E13" s="237"/>
-      <c r="F13" s="237"/>
-      <c r="G13" s="237"/>
-      <c r="H13" s="237"/>
-      <c r="I13" s="237"/>
-      <c r="J13" s="237"/>
-      <c r="K13" s="237"/>
-      <c r="L13" s="237"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="236"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="236"/>
+      <c r="L13" s="236"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -17931,18 +17967,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="237" t="s">
+      <c r="C18" s="236" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="237"/>
-      <c r="E18" s="237"/>
-      <c r="F18" s="237"/>
-      <c r="G18" s="237"/>
-      <c r="H18" s="237"/>
-      <c r="I18" s="237"/>
-      <c r="J18" s="237"/>
-      <c r="K18" s="237"/>
-      <c r="L18" s="237"/>
+      <c r="D18" s="236"/>
+      <c r="E18" s="236"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="236"/>
+      <c r="H18" s="236"/>
+      <c r="I18" s="236"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="236"/>
+      <c r="L18" s="236"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18134,18 +18170,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="237" t="s">
+      <c r="C25" s="236" t="s">
         <v>157</v>
       </c>
-      <c r="D25" s="237"/>
-      <c r="E25" s="237"/>
-      <c r="F25" s="237"/>
-      <c r="G25" s="237"/>
-      <c r="H25" s="237"/>
-      <c r="I25" s="237"/>
-      <c r="J25" s="237"/>
-      <c r="K25" s="237"/>
-      <c r="L25" s="237"/>
+      <c r="D25" s="236"/>
+      <c r="E25" s="236"/>
+      <c r="F25" s="236"/>
+      <c r="G25" s="236"/>
+      <c r="H25" s="236"/>
+      <c r="I25" s="236"/>
+      <c r="J25" s="236"/>
+      <c r="K25" s="236"/>
+      <c r="L25" s="236"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -18283,18 +18319,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="237" t="s">
+      <c r="C31" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="237"/>
-      <c r="E31" s="237"/>
-      <c r="F31" s="237"/>
-      <c r="G31" s="237"/>
-      <c r="H31" s="237"/>
-      <c r="I31" s="237"/>
-      <c r="J31" s="237"/>
-      <c r="K31" s="237"/>
-      <c r="L31" s="237"/>
+      <c r="D31" s="236"/>
+      <c r="E31" s="236"/>
+      <c r="F31" s="236"/>
+      <c r="G31" s="236"/>
+      <c r="H31" s="236"/>
+      <c r="I31" s="236"/>
+      <c r="J31" s="236"/>
+      <c r="K31" s="236"/>
+      <c r="L31" s="236"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -18365,23 +18401,23 @@
         <f>Statement!Q100</f>
         <v>0.34766238434904356</v>
       </c>
-      <c r="H33" s="222">
+      <c r="H33" s="221">
         <f>H8/H6</f>
         <v>0.36</v>
       </c>
-      <c r="I33" s="222">
+      <c r="I33" s="221">
         <f t="shared" ref="I33:L33" si="9">I8/I6</f>
         <v>0.38</v>
       </c>
-      <c r="J33" s="222">
+      <c r="J33" s="221">
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
-      <c r="K33" s="222">
+      <c r="K33" s="221">
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
-      <c r="L33" s="222">
+      <c r="L33" s="221">
         <f t="shared" si="9"/>
         <v>0.43000000000000005</v>
       </c>
@@ -18410,39 +18446,39 @@
         <f>Statement!Q101</f>
         <v>-4.1889769738709247E-2</v>
       </c>
-      <c r="H34" s="222">
+      <c r="H34" s="221">
         <f>H10/H6</f>
         <v>1.0000000000000004E-2</v>
       </c>
-      <c r="I34" s="222">
+      <c r="I34" s="221">
         <f t="shared" ref="I34:L34" si="10">I10/I6</f>
         <v>3.0000000000000013E-2</v>
       </c>
-      <c r="J34" s="222">
+      <c r="J34" s="221">
         <f t="shared" si="10"/>
         <v>6.9999999999999951E-2</v>
       </c>
-      <c r="K34" s="222">
+      <c r="K34" s="221">
         <f t="shared" si="10"/>
         <v>7.9999999999999974E-2</v>
       </c>
-      <c r="L34" s="222">
+      <c r="L34" s="221">
         <f t="shared" si="10"/>
         <v>0.13000000000000003</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -18505,10 +18541,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="228" t="s">
+      <c r="B4" s="227" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="228"/>
+      <c r="C4" s="227"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -18593,10 +18629,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="228" t="s">
+      <c r="B15" s="227" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="228"/>
+      <c r="C15" s="227"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -18693,60 +18729,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="228" t="s">
+      <c r="C3" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="228"/>
-      <c r="E3" s="228"/>
-      <c r="F3" s="228"/>
-      <c r="G3" s="240"/>
-      <c r="H3" s="241" t="s">
+      <c r="D3" s="227"/>
+      <c r="E3" s="227"/>
+      <c r="F3" s="227"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="228"/>
-      <c r="J3" s="228"/>
-      <c r="K3" s="228"/>
-      <c r="L3" s="228"/>
-      <c r="P3" s="242"/>
-      <c r="Q3" s="242"/>
-      <c r="R3" s="242"/>
-      <c r="S3" s="242"/>
-      <c r="T3" s="242"/>
-      <c r="U3" s="242"/>
-      <c r="V3" s="242"/>
-      <c r="W3" s="242"/>
-      <c r="X3" s="242"/>
-      <c r="Y3" s="242"/>
-      <c r="Z3" s="242"/>
+      <c r="I3" s="227"/>
+      <c r="J3" s="227"/>
+      <c r="K3" s="227"/>
+      <c r="L3" s="227"/>
+      <c r="P3" s="241"/>
+      <c r="Q3" s="241"/>
+      <c r="R3" s="241"/>
+      <c r="S3" s="241"/>
+      <c r="T3" s="241"/>
+      <c r="U3" s="241"/>
+      <c r="V3" s="241"/>
+      <c r="W3" s="241"/>
+      <c r="X3" s="241"/>
+      <c r="Y3" s="241"/>
+      <c r="Z3" s="241"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="237" t="s">
+      <c r="C5" s="236" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="237"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="237"/>
-      <c r="G5" s="237"/>
-      <c r="H5" s="237"/>
-      <c r="I5" s="237"/>
-      <c r="J5" s="237"/>
-      <c r="K5" s="237"/>
-      <c r="L5" s="237"/>
-      <c r="P5" s="242"/>
-      <c r="Q5" s="242"/>
-      <c r="R5" s="242"/>
-      <c r="S5" s="242"/>
-      <c r="T5" s="242"/>
-      <c r="U5" s="242"/>
-      <c r="V5" s="242"/>
-      <c r="W5" s="242"/>
-      <c r="X5" s="242"/>
-      <c r="Y5" s="242"/>
-      <c r="Z5" s="242"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="236"/>
+      <c r="P5" s="241"/>
+      <c r="Q5" s="241"/>
+      <c r="R5" s="241"/>
+      <c r="S5" s="241"/>
+      <c r="T5" s="241"/>
+      <c r="U5" s="241"/>
+      <c r="V5" s="241"/>
+      <c r="W5" s="241"/>
+      <c r="X5" s="241"/>
+      <c r="Y5" s="241"/>
+      <c r="Z5" s="241"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18992,10 +19028,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="228" t="s">
+      <c r="B13" s="227" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="228"/>
+      <c r="C13" s="227"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19010,15 +19046,15 @@
         <v>161</v>
       </c>
       <c r="C15" s="134">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.13805036478854302</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="228" t="s">
+      <c r="B18" s="227" t="s">
         <v>182</v>
       </c>
-      <c r="C18" s="228"/>
+      <c r="C18" s="227"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19051,7 +19087,7 @@
       <c r="B22" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="87">
         <f>Statement!AC120</f>
         <v>32789</v>
       </c>
@@ -19060,7 +19096,7 @@
       <c r="B23" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="87">
         <f>Statement!AC121</f>
         <v>45031</v>
       </c>
@@ -19078,7 +19114,7 @@
       <c r="B25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="63">
+      <c r="C25" s="87">
         <f>Statement!AC77</f>
         <v>5026</v>
       </c>
@@ -19110,7 +19146,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="82" customWidth="1"/>
@@ -19132,37 +19168,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="228" t="s">
+      <c r="C2" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="228"/>
-      <c r="E2" s="228"/>
-      <c r="F2" s="228"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="241" t="s">
+      <c r="D2" s="227"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
-      <c r="K2" s="228"/>
-      <c r="L2" s="228"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="227"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="237" t="s">
+      <c r="C4" s="236" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="237"/>
-      <c r="E4" s="237"/>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
-      <c r="H4" s="237"/>
-      <c r="I4" s="237"/>
-      <c r="J4" s="237"/>
-      <c r="K4" s="237"/>
-      <c r="L4" s="237"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -19351,18 +19387,18 @@
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="237" t="s">
+      <c r="C10" s="236" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="237"/>
-      <c r="E10" s="237"/>
-      <c r="F10" s="237"/>
-      <c r="G10" s="237"/>
-      <c r="H10" s="237"/>
-      <c r="I10" s="237"/>
-      <c r="J10" s="237"/>
-      <c r="K10" s="237"/>
-      <c r="L10" s="237"/>
+      <c r="D10" s="236"/>
+      <c r="E10" s="236"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -19556,18 +19592,18 @@
       <c r="N15" s="90"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="237" t="s">
+      <c r="C16" s="236" t="s">
         <v>192</v>
       </c>
-      <c r="D16" s="237"/>
-      <c r="E16" s="237"/>
-      <c r="F16" s="237"/>
-      <c r="G16" s="237"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="237"/>
-      <c r="J16" s="237"/>
-      <c r="K16" s="237"/>
-      <c r="L16" s="237"/>
+      <c r="D16" s="236"/>
+      <c r="E16" s="236"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="236"/>
+      <c r="H16" s="236"/>
+      <c r="I16" s="236"/>
+      <c r="J16" s="236"/>
+      <c r="K16" s="236"/>
+      <c r="L16" s="236"/>
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -19701,18 +19737,18 @@
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="237" t="s">
+      <c r="C21" s="236" t="s">
         <v>195</v>
       </c>
-      <c r="D21" s="237"/>
-      <c r="E21" s="237"/>
-      <c r="F21" s="237"/>
-      <c r="G21" s="237"/>
-      <c r="H21" s="237"/>
-      <c r="I21" s="237"/>
-      <c r="J21" s="237"/>
-      <c r="K21" s="237"/>
-      <c r="L21" s="237"/>
+      <c r="D21" s="236"/>
+      <c r="E21" s="236"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="236"/>
+      <c r="H21" s="236"/>
+      <c r="I21" s="236"/>
+      <c r="J21" s="236"/>
+      <c r="K21" s="236"/>
+      <c r="L21" s="236"/>
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -19796,18 +19832,18 @@
       <c r="N25" s="90"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="237" t="s">
+      <c r="C26" s="236" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="237"/>
-      <c r="E26" s="237"/>
-      <c r="F26" s="237"/>
-      <c r="G26" s="237"/>
-      <c r="H26" s="237"/>
-      <c r="I26" s="237"/>
-      <c r="J26" s="237"/>
-      <c r="K26" s="237"/>
-      <c r="L26" s="237"/>
+      <c r="D26" s="236"/>
+      <c r="E26" s="236"/>
+      <c r="F26" s="236"/>
+      <c r="G26" s="236"/>
+      <c r="H26" s="236"/>
+      <c r="I26" s="236"/>
+      <c r="J26" s="236"/>
+      <c r="K26" s="236"/>
+      <c r="L26" s="236"/>
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -20077,10 +20113,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="228" t="s">
+      <c r="B37" s="227" t="s">
         <v>201</v>
       </c>
-      <c r="C37" s="228"/>
+      <c r="C37" s="227"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20097,7 +20133,7 @@
         <v>161</v>
       </c>
       <c r="C39" s="134">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.13805036478854302</v>
       </c>
     </row>
@@ -20111,29 +20147,29 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C41" s="24">
-        <f>L18</f>
-        <v>5563.9177776000006</v>
+        <f>(C38*C40)</f>
+        <v>351560.47268070834</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>199</v>
+        <v>396</v>
       </c>
       <c r="C42" s="24">
-        <f>(C38*C40)-G30+G31</f>
-        <v>342391.47268070834</v>
+        <f ca="1">C41/(1+C39)^5-G30+G31</f>
+        <v>174989.86432640988</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C43" s="24">
-        <f>C42/C41</f>
-        <v>61.537838330242025</v>
+        <v>67</v>
+      </c>
+      <c r="C43" s="87">
+        <f>Statement!AC77</f>
+        <v>5026</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -20141,15 +20177,15 @@
         <v>205</v>
       </c>
       <c r="C44" s="142">
-        <f ca="1">C43/(1+C48)^5</f>
-        <v>32.235530728427833</v>
+        <f ca="1">C42/C43</f>
+        <v>34.816924856030617</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="228" t="s">
+      <c r="B46" s="227" t="s">
         <v>206</v>
       </c>
-      <c r="C46" s="228"/>
+      <c r="C46" s="227"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -20162,11 +20198,11 @@
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>161</v>
+        <v>394</v>
       </c>
       <c r="C48" s="134">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
-        <v>0.13805036478854302</v>
+        <f>Overview!C29</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -20200,15 +20236,15 @@
         <v>205</v>
       </c>
       <c r="C52" s="142">
-        <f ca="1">C51/(1+C48)^5</f>
-        <v>36.372280552996166</v>
+        <f>C51/(1+C48)^5</f>
+        <v>39.399238739054248</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="228" t="s">
+      <c r="B54" s="227" t="s">
         <v>325</v>
       </c>
-      <c r="C54" s="228"/>
+      <c r="C54" s="227"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -20224,7 +20260,7 @@
         <v>161</v>
       </c>
       <c r="C56" s="134">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.13805036478854302</v>
       </c>
     </row>
@@ -20256,20 +20292,29 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>188</v>
+        <v>396</v>
       </c>
       <c r="C60" s="24">
-        <f>C59/C58</f>
-        <v>-20.914016519890566</v>
+        <f ca="1">C59/(1+C56)^5-G30+G31</f>
+        <v>-70124.196909102393</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="141" t="s">
+      <c r="B61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="87">
+        <f>Statement!AC77</f>
+        <v>5026</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="141" t="s">
         <v>205</v>
       </c>
-      <c r="C61" s="142">
-        <f ca="1">C60/(1+C56)^5</f>
-        <v>-10.955445307711837</v>
+      <c r="C62" s="142">
+        <f ca="1">C60/C61</f>
+        <v>-13.952287486888657</v>
       </c>
     </row>
   </sheetData>
@@ -20321,10 +20366,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="228" t="s">
+      <c r="B4" s="227" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="228"/>
+      <c r="C4" s="227"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20342,7 +20387,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C44</f>
-        <v>32.235530728427833</v>
+        <v>34.816924856030617</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -20350,8 +20395,8 @@
         <v>215</v>
       </c>
       <c r="C7" s="132">
-        <f ca="1">Multiples!C52</f>
-        <v>36.372280552996166</v>
+        <f>Multiples!C52</f>
+        <v>39.399238739054248</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -20359,8 +20404,8 @@
         <v>326</v>
       </c>
       <c r="C8" s="132">
-        <f ca="1">Multiples!C61</f>
-        <v>-10.955445307711837</v>
+        <f ca="1">Multiples!C62</f>
+        <v>-13.952287486888657</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -20369,7 +20414,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>12.21788441214261</v>
+        <v>12.87076194576362</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20387,7 +20432,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.87679858412682654</v>
+        <v>-0.87021516642368035</v>
       </c>
     </row>
   </sheetData>
@@ -20452,60 +20497,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="228" t="s">
+      <c r="C3" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="228"/>
-      <c r="E3" s="228"/>
-      <c r="F3" s="228"/>
-      <c r="G3" s="240"/>
-      <c r="H3" s="241" t="s">
+      <c r="D3" s="227"/>
+      <c r="E3" s="227"/>
+      <c r="F3" s="227"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="228"/>
-      <c r="J3" s="228"/>
-      <c r="K3" s="228"/>
-      <c r="L3" s="228"/>
-      <c r="P3" s="242"/>
-      <c r="Q3" s="242"/>
-      <c r="R3" s="242"/>
-      <c r="S3" s="242"/>
-      <c r="T3" s="242"/>
-      <c r="U3" s="242"/>
-      <c r="V3" s="242"/>
-      <c r="W3" s="242"/>
-      <c r="X3" s="242"/>
-      <c r="Y3" s="242"/>
-      <c r="Z3" s="242"/>
+      <c r="I3" s="227"/>
+      <c r="J3" s="227"/>
+      <c r="K3" s="227"/>
+      <c r="L3" s="227"/>
+      <c r="P3" s="241"/>
+      <c r="Q3" s="241"/>
+      <c r="R3" s="241"/>
+      <c r="S3" s="241"/>
+      <c r="T3" s="241"/>
+      <c r="U3" s="241"/>
+      <c r="V3" s="241"/>
+      <c r="W3" s="241"/>
+      <c r="X3" s="241"/>
+      <c r="Y3" s="241"/>
+      <c r="Z3" s="241"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="237" t="s">
+      <c r="C5" s="236" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="237"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="237"/>
-      <c r="G5" s="237"/>
-      <c r="H5" s="237"/>
-      <c r="I5" s="237"/>
-      <c r="J5" s="237"/>
-      <c r="K5" s="237"/>
-      <c r="L5" s="237"/>
-      <c r="P5" s="242"/>
-      <c r="Q5" s="242"/>
-      <c r="R5" s="242"/>
-      <c r="S5" s="242"/>
-      <c r="T5" s="242"/>
-      <c r="U5" s="242"/>
-      <c r="V5" s="242"/>
-      <c r="W5" s="242"/>
-      <c r="X5" s="242"/>
-      <c r="Y5" s="242"/>
-      <c r="Z5" s="242"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="236"/>
+      <c r="P5" s="241"/>
+      <c r="Q5" s="241"/>
+      <c r="R5" s="241"/>
+      <c r="S5" s="241"/>
+      <c r="T5" s="241"/>
+      <c r="U5" s="241"/>
+      <c r="V5" s="241"/>
+      <c r="W5" s="241"/>
+      <c r="X5" s="241"/>
+      <c r="Y5" s="241"/>
+      <c r="Z5" s="241"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20734,10 +20779,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="243" t="s">
+      <c r="B14" s="242" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="244"/>
+      <c r="C14" s="243"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -20764,20 +20809,20 @@
       <c r="C17" s="158">
         <v>0.65</v>
       </c>
-      <c r="E17" s="245" t="s">
+      <c r="E17" s="244" t="s">
         <v>223</v>
       </c>
-      <c r="F17" s="245"/>
-      <c r="G17" s="245"/>
-      <c r="H17" s="245"/>
-      <c r="I17" s="245"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="243" t="s">
+      <c r="B19" s="242" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="244"/>
+      <c r="C19" s="243"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -20791,8 +20836,8 @@
       <c r="B21" s="159" t="s">
         <v>161</v>
       </c>
-      <c r="C21" s="161">
-        <f ca="1">IF(WACC!C21&gt;0,WACC!C21,WACC!C20)</f>
+      <c r="C21" s="246">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.13805036478854302</v>
       </c>
     </row>
@@ -20800,7 +20845,7 @@
       <c r="B22" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="162">
+      <c r="C22" s="247">
         <f>Statement!AC74</f>
         <v>5026</v>
       </c>
@@ -20809,7 +20854,7 @@
       <c r="B23" s="159" t="s">
         <v>224</v>
       </c>
-      <c r="C23" s="162">
+      <c r="C23" s="161">
         <f ca="1">C15*C22</f>
         <v>498428.42</v>
       </c>
@@ -20818,7 +20863,7 @@
       <c r="B24" s="159" t="s">
         <v>174</v>
       </c>
-      <c r="C24" s="162">
+      <c r="C24" s="247">
         <f>Statement!AC120</f>
         <v>32789</v>
       </c>
@@ -20827,7 +20872,7 @@
       <c r="B25" s="159" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="162">
+      <c r="C25" s="247">
         <f>Statement!AC121</f>
         <v>45031</v>
       </c>
@@ -20836,23 +20881,23 @@
       <c r="B26" s="157" t="s">
         <v>225</v>
       </c>
-      <c r="C26" s="163">
+      <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
         <v>510670.41999999993</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="243" t="s">
+      <c r="B28" s="242" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="244"/>
+      <c r="C28" s="243"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="162">
+      <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
         <v>-158181.02215267759</v>
       </c>
@@ -20861,16 +20906,16 @@
       <c r="B30" s="159" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="162">
+      <c r="C30" s="161">
         <f ca="1">L11</f>
         <v>-502500.74368117063</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="164" t="s">
+      <c r="B31" s="163" t="s">
         <v>184</v>
       </c>
-      <c r="C31" s="165">
+      <c r="C31" s="164">
         <f ca="1">C29+C30</f>
         <v>-660681.76583384816</v>
       </c>
@@ -20879,7 +20924,7 @@
       <c r="B32" s="159" t="s">
         <v>185</v>
       </c>
-      <c r="C32" s="166">
+      <c r="C32" s="165">
         <f>C24</f>
         <v>32789</v>
       </c>
@@ -20888,16 +20933,16 @@
       <c r="B33" s="159" t="s">
         <v>186</v>
       </c>
-      <c r="C33" s="166">
+      <c r="C33" s="165">
         <f>C25</f>
         <v>45031</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="164" t="s">
+      <c r="B34" s="163" t="s">
         <v>187</v>
       </c>
-      <c r="C34" s="165">
+      <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
         <v>-672923.76583384816</v>
       </c>
@@ -20906,33 +20951,33 @@
       <c r="B35" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="162">
+      <c r="C35" s="161">
         <f>C22</f>
         <v>5026</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="167" t="s">
+      <c r="B36" s="166" t="s">
         <v>188</v>
       </c>
-      <c r="C36" s="168">
+      <c r="C36" s="167">
         <f ca="1">C34/C35</f>
         <v>-133.88853279622924</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="237" t="s">
+      <c r="C39" s="236" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="237"/>
-      <c r="E39" s="237"/>
-      <c r="F39" s="237"/>
-      <c r="G39" s="237"/>
-      <c r="H39" s="237"/>
-      <c r="I39" s="237"/>
-      <c r="J39" s="237"/>
-      <c r="K39" s="237"/>
-      <c r="L39" s="237"/>
+      <c r="D39" s="236"/>
+      <c r="E39" s="236"/>
+      <c r="F39" s="236"/>
+      <c r="G39" s="236"/>
+      <c r="H39" s="236"/>
+      <c r="I39" s="236"/>
+      <c r="J39" s="236"/>
+      <c r="K39" s="236"/>
+      <c r="L39" s="236"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -21090,19 +21135,19 @@
         <f t="shared" si="4"/>
         <v>4.1002840567904721</v>
       </c>
-      <c r="H43" s="169">
+      <c r="H43" s="168">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I43" s="169">
+      <c r="I43" s="168">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J43" s="169">
+      <c r="J43" s="168">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K43" s="169">
+      <c r="K43" s="168">
         <v>1.1000000000000001</v>
       </c>
-      <c r="L43" s="169">
+      <c r="L43" s="168">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -21175,19 +21220,19 @@
         <f t="shared" si="6"/>
         <v>-0.17175995500225352</v>
       </c>
-      <c r="H45" s="169">
+      <c r="H45" s="168">
         <v>0.01</v>
       </c>
-      <c r="I45" s="169">
+      <c r="I45" s="168">
         <v>0.02</v>
       </c>
-      <c r="J45" s="169">
+      <c r="J45" s="168">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="K45" s="169">
+      <c r="K45" s="168">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L45" s="169">
+      <c r="L45" s="168">
         <v>0.15</v>
       </c>
     </row>
@@ -21212,23 +21257,23 @@
         <f t="shared" si="7"/>
         <v>-0.6076910586977482</v>
       </c>
-      <c r="H46" s="170">
+      <c r="H46" s="169">
         <f t="shared" si="7"/>
         <v>0.64999999999999991</v>
       </c>
-      <c r="I46" s="170">
+      <c r="I46" s="169">
         <f t="shared" si="7"/>
         <v>0.64999999999999991</v>
       </c>
-      <c r="J46" s="170">
+      <c r="J46" s="169">
         <f t="shared" si="7"/>
         <v>0.64999999999999991</v>
       </c>
-      <c r="K46" s="170">
+      <c r="K46" s="169">
         <f t="shared" si="7"/>
         <v>0.65000000000000013</v>
       </c>
-      <c r="L46" s="170">
+      <c r="L46" s="169">
         <f t="shared" si="7"/>
         <v>0.64999999999999991</v>
       </c>
@@ -21254,23 +21299,23 @@
         <f t="shared" si="7"/>
         <v>-0.81041274190786095</v>
       </c>
-      <c r="H47" s="170">
+      <c r="H47" s="169">
         <f t="shared" si="7"/>
         <v>5.1504260851857078</v>
       </c>
-      <c r="I47" s="170">
+      <c r="I47" s="169">
         <f t="shared" si="7"/>
         <v>0.64999999999999991</v>
       </c>
-      <c r="J47" s="170">
+      <c r="J47" s="169">
         <f t="shared" si="7"/>
         <v>0.64999999999999969</v>
       </c>
-      <c r="K47" s="170">
+      <c r="K47" s="169">
         <f t="shared" si="7"/>
         <v>0.65000000000000013</v>
       </c>
-      <c r="L47" s="170">
+      <c r="L47" s="169">
         <f t="shared" si="7"/>
         <v>0.64999999999999991</v>
       </c>
@@ -21296,23 +21341,23 @@
         <f t="shared" si="8"/>
         <v>-4.6703451912393223E-3</v>
       </c>
-      <c r="H48" s="170">
+      <c r="H48" s="169">
         <f t="shared" si="8"/>
         <v>-29.340392575371833</v>
       </c>
-      <c r="I48" s="170">
+      <c r="I48" s="169">
         <f t="shared" si="8"/>
         <v>-0.17500000000000016</v>
       </c>
-      <c r="J48" s="170">
+      <c r="J48" s="169">
         <f t="shared" si="8"/>
         <v>-0.2142857142857143</v>
       </c>
-      <c r="K48" s="170">
+      <c r="K48" s="169">
         <f t="shared" si="8"/>
         <v>-1.0000000000000009E-2</v>
       </c>
-      <c r="L48" s="170">
+      <c r="L48" s="169">
         <f t="shared" si="8"/>
         <v>-0.22999999999999987</v>
       </c>
@@ -21341,40 +21386,40 @@
         <f t="shared" si="9"/>
         <v>-4.1889769738709247E-2</v>
       </c>
-      <c r="H49" s="170">
+      <c r="H49" s="169">
         <f t="shared" si="9"/>
         <v>9.0909090909090887E-3</v>
       </c>
-      <c r="I49" s="170">
+      <c r="I49" s="169">
         <f t="shared" si="9"/>
         <v>1.8181818181818181E-2</v>
       </c>
-      <c r="J49" s="170">
+      <c r="J49" s="169">
         <f t="shared" si="9"/>
         <v>3.8181818181818178E-2</v>
       </c>
-      <c r="K49" s="170">
+      <c r="K49" s="169">
         <f t="shared" si="9"/>
         <v>6.363636363636363E-2</v>
       </c>
-      <c r="L49" s="170">
+      <c r="L49" s="169">
         <f t="shared" si="9"/>
         <v>0.13636363636363633</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -27280,7 +27325,7 @@
       <c r="AE104" s="1"/>
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B105" s="218" t="s">
+      <c r="B105" s="217" t="s">
         <v>361</v>
       </c>
       <c r="C105" s="61"/>
@@ -27338,7 +27383,7 @@
       </c>
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B106" s="218" t="s">
+      <c r="B106" s="217" t="s">
         <v>362</v>
       </c>
       <c r="C106" s="61"/>
@@ -27605,7 +27650,7 @@
       <c r="AC110" s="61"/>
     </row>
     <row r="111" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B111" s="218" t="s">
+      <c r="B111" s="217" t="s">
         <v>372</v>
       </c>
       <c r="C111" s="61"/>
@@ -27666,7 +27711,7 @@
       </c>
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B112" s="218" t="s">
+      <c r="B112" s="217" t="s">
         <v>373</v>
       </c>
       <c r="C112" s="61"/>
@@ -28917,30 +28962,30 @@
       <c r="B146" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="C146" s="172"/>
-      <c r="D146" s="172"/>
-      <c r="E146" s="172"/>
-      <c r="F146" s="172"/>
-      <c r="G146" s="172"/>
-      <c r="H146" s="172"/>
-      <c r="I146" s="172"/>
-      <c r="J146" s="172"/>
-      <c r="K146" s="172"/>
-      <c r="L146" s="172"/>
-      <c r="M146" s="172"/>
-      <c r="N146" s="172"/>
-      <c r="O146" s="172"/>
-      <c r="P146" s="172"/>
-      <c r="Q146" s="172"/>
-      <c r="T146" s="172"/>
-      <c r="U146" s="172"/>
-      <c r="V146" s="172"/>
-      <c r="W146" s="172"/>
-      <c r="X146" s="172"/>
-      <c r="Y146" s="172"/>
-      <c r="Z146" s="172"/>
-      <c r="AA146" s="172"/>
-      <c r="AC146" s="172"/>
+      <c r="C146" s="171"/>
+      <c r="D146" s="171"/>
+      <c r="E146" s="171"/>
+      <c r="F146" s="171"/>
+      <c r="G146" s="171"/>
+      <c r="H146" s="171"/>
+      <c r="I146" s="171"/>
+      <c r="J146" s="171"/>
+      <c r="K146" s="171"/>
+      <c r="L146" s="171"/>
+      <c r="M146" s="171"/>
+      <c r="N146" s="171"/>
+      <c r="O146" s="171"/>
+      <c r="P146" s="171"/>
+      <c r="Q146" s="171"/>
+      <c r="T146" s="171"/>
+      <c r="U146" s="171"/>
+      <c r="V146" s="171"/>
+      <c r="W146" s="171"/>
+      <c r="X146" s="171"/>
+      <c r="Y146" s="171"/>
+      <c r="Z146" s="171"/>
+      <c r="AA146" s="171"/>
+      <c r="AC146" s="171"/>
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B147" s="20" t="s">
@@ -29104,35 +29149,35 @@
       <c r="O150" s="49"/>
       <c r="P150" s="49"/>
       <c r="Q150" s="49"/>
-      <c r="T150" s="173" t="str">
+      <c r="T150" s="172" t="str">
         <f t="shared" ref="T150:Z150" si="81">IF(T149&gt;T148, "BEAT", IF(T149&lt;T147, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
-      <c r="U150" s="173" t="str">
+      <c r="U150" s="172" t="str">
         <f t="shared" si="81"/>
         <v>MET</v>
       </c>
-      <c r="V150" s="173" t="str">
+      <c r="V150" s="172" t="str">
         <f t="shared" si="81"/>
         <v>MET</v>
       </c>
-      <c r="W150" s="173" t="str">
+      <c r="W150" s="172" t="str">
         <f t="shared" si="81"/>
         <v>BEAT</v>
       </c>
-      <c r="X150" s="173" t="str">
+      <c r="X150" s="172" t="str">
         <f t="shared" si="81"/>
         <v>BEAT</v>
       </c>
-      <c r="Y150" s="173" t="str">
+      <c r="Y150" s="172" t="str">
         <f t="shared" si="81"/>
         <v>MET</v>
       </c>
-      <c r="Z150" s="173" t="str">
+      <c r="Z150" s="172" t="str">
         <f t="shared" si="81"/>
         <v>BEAT</v>
       </c>
-      <c r="AA150" s="173" t="str">
+      <c r="AA150" s="172" t="str">
         <f>IF(AA149&gt;AA148, "BEAT", IF(AA149&lt;AA147, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
@@ -29157,28 +29202,28 @@
       <c r="O151" s="49"/>
       <c r="P151" s="49"/>
       <c r="Q151" s="49"/>
-      <c r="T151" s="219">
+      <c r="T151" s="218">
         <v>0.34499999999999997</v>
       </c>
-      <c r="U151" s="219">
+      <c r="U151" s="218">
         <v>0.36499999999999999</v>
       </c>
-      <c r="V151" s="219">
+      <c r="V151" s="218">
         <v>0.33800000000000002</v>
       </c>
-      <c r="W151" s="219">
+      <c r="W151" s="218">
         <v>0.34300000000000003</v>
       </c>
-      <c r="X151" s="219">
+      <c r="X151" s="218">
         <v>0.34100000000000003</v>
       </c>
-      <c r="Y151" s="219">
+      <c r="Y151" s="218">
         <v>0.34499999999999997</v>
       </c>
-      <c r="Z151" s="219">
+      <c r="Z151" s="218">
         <v>0.32300000000000001</v>
       </c>
-      <c r="AA151" s="219">
+      <c r="AA151" s="218">
         <v>0.375</v>
       </c>
       <c r="AC151" s="49"/>
@@ -29202,28 +29247,28 @@
       <c r="O152" s="49"/>
       <c r="P152" s="49"/>
       <c r="Q152" s="49"/>
-      <c r="T152" s="219">
+      <c r="T152" s="218">
         <v>0.34499999999999997</v>
       </c>
-      <c r="U152" s="219">
+      <c r="U152" s="218">
         <v>0.36499999999999999</v>
       </c>
-      <c r="V152" s="219">
+      <c r="V152" s="218">
         <v>0.33800000000000002</v>
       </c>
-      <c r="W152" s="219">
+      <c r="W152" s="218">
         <v>0.34300000000000003</v>
       </c>
-      <c r="X152" s="219">
+      <c r="X152" s="218">
         <v>0.34100000000000003</v>
       </c>
-      <c r="Y152" s="219">
+      <c r="Y152" s="218">
         <v>0.34499999999999997</v>
       </c>
-      <c r="Z152" s="219">
+      <c r="Z152" s="218">
         <v>0.32300000000000001</v>
       </c>
-      <c r="AA152" s="219">
+      <c r="AA152" s="218">
         <v>0.375</v>
       </c>
       <c r="AC152" s="49"/>
@@ -29300,35 +29345,35 @@
       <c r="O154" s="49"/>
       <c r="P154" s="49"/>
       <c r="Q154" s="49"/>
-      <c r="T154" s="173" t="str">
+      <c r="T154" s="172" t="str">
         <f t="shared" ref="T154:Z154" si="83">IF(T153&gt;T152, "BEAT", IF(T153&lt;T151, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
-      <c r="U154" s="173" t="str">
+      <c r="U154" s="172" t="str">
         <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="V154" s="173" t="str">
+      <c r="V154" s="172" t="str">
         <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="W154" s="173" t="str">
+      <c r="W154" s="172" t="str">
         <f t="shared" si="83"/>
         <v>MISSED</v>
       </c>
-      <c r="X154" s="173" t="str">
+      <c r="X154" s="172" t="str">
         <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="Y154" s="173" t="str">
+      <c r="Y154" s="172" t="str">
         <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="Z154" s="173" t="str">
+      <c r="Z154" s="172" t="str">
         <f t="shared" si="83"/>
         <v>BEAT</v>
       </c>
-      <c r="AA154" s="173" t="str">
+      <c r="AA154" s="172" t="str">
         <f>IF(AA153&gt;AA152, "BEAT", IF(AA153&lt;AA151, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
@@ -29341,30 +29386,30 @@
       <c r="B157" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="C157" s="172"/>
-      <c r="D157" s="172"/>
-      <c r="E157" s="172"/>
-      <c r="F157" s="172"/>
-      <c r="G157" s="172"/>
-      <c r="H157" s="172"/>
-      <c r="I157" s="172"/>
-      <c r="J157" s="172"/>
-      <c r="K157" s="172"/>
-      <c r="L157" s="172"/>
-      <c r="M157" s="172"/>
-      <c r="N157" s="172"/>
-      <c r="O157" s="172"/>
-      <c r="P157" s="172"/>
-      <c r="Q157" s="172"/>
-      <c r="T157" s="172"/>
-      <c r="U157" s="172"/>
-      <c r="V157" s="172"/>
-      <c r="W157" s="172"/>
-      <c r="X157" s="172"/>
-      <c r="Y157" s="172"/>
-      <c r="Z157" s="172"/>
-      <c r="AA157" s="172"/>
-      <c r="AC157" s="172"/>
+      <c r="C157" s="171"/>
+      <c r="D157" s="171"/>
+      <c r="E157" s="171"/>
+      <c r="F157" s="171"/>
+      <c r="G157" s="171"/>
+      <c r="H157" s="171"/>
+      <c r="I157" s="171"/>
+      <c r="J157" s="171"/>
+      <c r="K157" s="171"/>
+      <c r="L157" s="171"/>
+      <c r="M157" s="171"/>
+      <c r="N157" s="171"/>
+      <c r="O157" s="171"/>
+      <c r="P157" s="171"/>
+      <c r="Q157" s="171"/>
+      <c r="T157" s="171"/>
+      <c r="U157" s="171"/>
+      <c r="V157" s="171"/>
+      <c r="W157" s="171"/>
+      <c r="X157" s="171"/>
+      <c r="Y157" s="171"/>
+      <c r="Z157" s="171"/>
+      <c r="AA157" s="171"/>
+      <c r="AC157" s="171"/>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B158" s="20" t="s">
@@ -29722,59 +29767,59 @@
       <c r="B164" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="M164" s="181">
+      <c r="M164" s="180">
         <f>(M121-M120)/M48</f>
         <v>0.10156094390456123</v>
       </c>
-      <c r="N164" s="181">
+      <c r="N164" s="180">
         <f>(N121-N120)/N48</f>
         <v>0.13520601835875493</v>
       </c>
-      <c r="O164" s="181">
+      <c r="O164" s="180">
         <f>(O121-O120)/O48</f>
         <v>0.22949142911260537</v>
       </c>
-      <c r="P164" s="181">
+      <c r="P164" s="180">
         <f>(P121-P120)/P48</f>
         <v>0.28154528054800038</v>
       </c>
-      <c r="Q164" s="181">
+      <c r="Q164" s="180">
         <f>(Q121-Q120)/Q48</f>
         <v>8.0232059572457368E-2</v>
       </c>
-      <c r="T164" s="181">
+      <c r="T164" s="180">
         <f t="shared" ref="T164:AA164" si="98">(T121-T120)/T48</f>
         <v>0.20616337901049214</v>
       </c>
-      <c r="U164" s="181">
+      <c r="U164" s="180">
         <f t="shared" si="98"/>
         <v>0.26272957440823053</v>
       </c>
-      <c r="V164" s="181">
+      <c r="V164" s="180">
         <f t="shared" si="98"/>
         <v>0.28154528054800038</v>
       </c>
-      <c r="W164" s="181">
+      <c r="W164" s="180">
         <f t="shared" si="98"/>
         <v>0.29174185011427883</v>
       </c>
-      <c r="X164" s="181">
+      <c r="X164" s="180">
         <f t="shared" si="98"/>
         <v>0.30190124945087504</v>
       </c>
-      <c r="Y164" s="181">
+      <c r="Y164" s="180">
         <f t="shared" si="98"/>
         <v>0.1468188313153343</v>
       </c>
-      <c r="Z164" s="181">
+      <c r="Z164" s="180">
         <f t="shared" si="98"/>
         <v>8.0232059572457368E-2</v>
       </c>
-      <c r="AA164" s="181">
+      <c r="AA164" s="180">
         <f t="shared" si="98"/>
         <v>0.10989819918487531</v>
       </c>
-      <c r="AC164" s="181">
+      <c r="AC164" s="180">
         <f>(AC121-AC120)/AC48</f>
         <v>0.10989819918487531</v>
       </c>
@@ -29905,59 +29950,59 @@
       <c r="B167" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="M167" s="183" t="str">
+      <c r="M167" s="182" t="str">
         <f>IF(M13&gt;=0,"N/A",IF(M12&lt;=0,"N/A",M12/-M13))</f>
         <v>N/A</v>
       </c>
-      <c r="N167" s="183" t="str">
+      <c r="N167" s="182" t="str">
         <f>IF(N13&gt;=0,"N/A",IF(N12&lt;=0,"N/A",N12/-N13))</f>
         <v>N/A</v>
       </c>
-      <c r="O167" s="183" t="str">
+      <c r="O167" s="182" t="str">
         <f>IF(O13&gt;=0,"N/A",IF(O12&lt;=0,"N/A",O12/-O13))</f>
         <v>N/A</v>
       </c>
-      <c r="P167" s="183" t="str">
+      <c r="P167" s="182" t="str">
         <f>IF(P13&gt;=0,"N/A",IF(P12&lt;=0,"N/A",P12/-P13))</f>
         <v>N/A</v>
       </c>
-      <c r="Q167" s="183" t="str">
+      <c r="Q167" s="182" t="str">
         <f>IF(Q13&gt;=0,"N/A",IF(Q12&lt;=0,"N/A",Q12/-Q13))</f>
         <v>N/A</v>
       </c>
-      <c r="T167" s="183" t="str">
+      <c r="T167" s="182" t="str">
         <f t="shared" ref="T167:AA167" si="101">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
-      <c r="U167" s="183" t="str">
+      <c r="U167" s="182" t="str">
         <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
-      <c r="V167" s="183" t="str">
+      <c r="V167" s="182" t="str">
         <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
-      <c r="W167" s="183" t="str">
+      <c r="W167" s="182" t="str">
         <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
-      <c r="X167" s="183" t="str">
+      <c r="X167" s="182" t="str">
         <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
-      <c r="Y167" s="183" t="str">
+      <c r="Y167" s="182" t="str">
         <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
-      <c r="Z167" s="183">
+      <c r="Z167" s="182">
         <f t="shared" si="101"/>
         <v>5.9793814432989691</v>
       </c>
-      <c r="AA167" s="183" t="str">
+      <c r="AA167" s="182" t="str">
         <f t="shared" si="101"/>
         <v>N/A</v>
       </c>
-      <c r="AC167" s="183" t="str">
+      <c r="AC167" s="182" t="str">
         <f>IF(AC13&gt;=0,"N/A",IF(AC12&lt;=0,"N/A",AC12/-AC13))</f>
         <v>N/A</v>
       </c>
@@ -30151,23 +30196,23 @@
       <c r="B173" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="M173" s="185">
+      <c r="M173" s="184">
         <f>M172/M5</f>
         <v>2.7866588631301887</v>
       </c>
-      <c r="N173" s="185">
+      <c r="N173" s="184">
         <f>N172/N5</f>
         <v>1.9873974688362355</v>
       </c>
-      <c r="O173" s="185">
+      <c r="O173" s="184">
         <f>O172/O5</f>
         <v>4.4657649184922921</v>
       </c>
-      <c r="P173" s="185">
+      <c r="P173" s="184">
         <f>P172/P5</f>
         <v>2.2901640270428052</v>
       </c>
-      <c r="Q173" s="185">
+      <c r="Q173" s="184">
         <f>Q172/Q5</f>
         <v>3.823188844531058</v>
       </c>
@@ -30179,7 +30224,7 @@
       <c r="Y173" s="49"/>
       <c r="Z173" s="49"/>
       <c r="AA173" s="49"/>
-      <c r="AC173" s="185">
+      <c r="AC173" s="184">
         <f ca="1">AC172/AC5</f>
         <v>9.7514167736175423</v>
       </c>
@@ -30188,23 +30233,23 @@
       <c r="B174" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="M174" s="185">
+      <c r="M174" s="184">
         <f>M172/M12</f>
         <v>11.318509971217106</v>
       </c>
-      <c r="N174" s="185">
+      <c r="N174" s="184">
         <f>N172/N12</f>
         <v>53.690385604113104</v>
       </c>
-      <c r="O174" s="185">
+      <c r="O174" s="184">
         <f>O172/O12</f>
         <v>2603.9731182795699</v>
       </c>
-      <c r="P174" s="185">
+      <c r="P174" s="184">
         <f>P172/P12</f>
         <v>-10.413598218873094</v>
       </c>
-      <c r="Q174" s="185">
+      <c r="Q174" s="184">
         <f>Q172/Q12</f>
         <v>-91.267841011743457</v>
       </c>
@@ -30216,7 +30261,7 @@
       <c r="Y174" s="49"/>
       <c r="Z174" s="49"/>
       <c r="AA174" s="49"/>
-      <c r="AC174" s="185">
+      <c r="AC174" s="184">
         <f ca="1">AC172/AC12</f>
         <v>-103.83549613784906</v>
       </c>
@@ -30648,7 +30693,7 @@
       <c r="Z185" s="49"/>
       <c r="AA185" s="49"/>
       <c r="AC185" s="154">
-        <f t="shared" ref="AC184:AC185" si="114">AC175/AC5</f>
+        <f t="shared" ref="AC185" si="114">AC175/AC5</f>
         <v>-0.1021148373416662</v>
       </c>
     </row>
@@ -31271,33 +31316,33 @@
       <c r="B200" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C200" s="172"/>
-      <c r="D200" s="172"/>
-      <c r="E200" s="172"/>
-      <c r="F200" s="172"/>
-      <c r="G200" s="172"/>
-      <c r="H200" s="172"/>
-      <c r="I200" s="172"/>
-      <c r="J200" s="172"/>
-      <c r="K200" s="172"/>
-      <c r="L200" s="172"/>
-      <c r="M200" s="172"/>
-      <c r="N200" s="172"/>
-      <c r="O200" s="172"/>
-      <c r="P200" s="172"/>
-      <c r="Q200" s="172"/>
-      <c r="T200" s="172"/>
-      <c r="U200" s="172"/>
-      <c r="V200" s="172"/>
-      <c r="W200" s="172"/>
-      <c r="X200" s="172"/>
-      <c r="Y200" s="172"/>
-      <c r="Z200" s="172"/>
-      <c r="AA200" s="172"/>
-      <c r="AC200" s="172"/>
+      <c r="C200" s="171"/>
+      <c r="D200" s="171"/>
+      <c r="E200" s="171"/>
+      <c r="F200" s="171"/>
+      <c r="G200" s="171"/>
+      <c r="H200" s="171"/>
+      <c r="I200" s="171"/>
+      <c r="J200" s="171"/>
+      <c r="K200" s="171"/>
+      <c r="L200" s="171"/>
+      <c r="M200" s="171"/>
+      <c r="N200" s="171"/>
+      <c r="O200" s="171"/>
+      <c r="P200" s="171"/>
+      <c r="Q200" s="171"/>
+      <c r="T200" s="171"/>
+      <c r="U200" s="171"/>
+      <c r="V200" s="171"/>
+      <c r="W200" s="171"/>
+      <c r="X200" s="171"/>
+      <c r="Y200" s="171"/>
+      <c r="Z200" s="171"/>
+      <c r="AA200" s="171"/>
+      <c r="AC200" s="171"/>
     </row>
     <row r="201" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B201" s="218" t="s">
+      <c r="B201" s="217" t="s">
         <v>361</v>
       </c>
       <c r="C201" s="80"/>
@@ -31371,7 +31416,7 @@
       <c r="AC201" s="49"/>
     </row>
     <row r="202" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B202" s="218" t="s">
+      <c r="B202" s="217" t="s">
         <v>362</v>
       </c>
       <c r="M202" s="80">
@@ -31609,30 +31654,30 @@
       <c r="B208" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="C208" s="172"/>
-      <c r="D208" s="172"/>
-      <c r="E208" s="172"/>
-      <c r="F208" s="172"/>
-      <c r="G208" s="172"/>
-      <c r="H208" s="172"/>
-      <c r="I208" s="172"/>
-      <c r="J208" s="172"/>
-      <c r="K208" s="172"/>
-      <c r="L208" s="172"/>
-      <c r="M208" s="172"/>
-      <c r="N208" s="172"/>
-      <c r="O208" s="172"/>
-      <c r="P208" s="172"/>
-      <c r="Q208" s="172"/>
-      <c r="T208" s="172"/>
-      <c r="U208" s="172"/>
-      <c r="V208" s="172"/>
-      <c r="W208" s="172"/>
-      <c r="X208" s="172"/>
-      <c r="Y208" s="172"/>
-      <c r="Z208" s="172"/>
-      <c r="AA208" s="172"/>
-      <c r="AC208" s="172"/>
+      <c r="C208" s="171"/>
+      <c r="D208" s="171"/>
+      <c r="E208" s="171"/>
+      <c r="F208" s="171"/>
+      <c r="G208" s="171"/>
+      <c r="H208" s="171"/>
+      <c r="I208" s="171"/>
+      <c r="J208" s="171"/>
+      <c r="K208" s="171"/>
+      <c r="L208" s="171"/>
+      <c r="M208" s="171"/>
+      <c r="N208" s="171"/>
+      <c r="O208" s="171"/>
+      <c r="P208" s="171"/>
+      <c r="Q208" s="171"/>
+      <c r="T208" s="171"/>
+      <c r="U208" s="171"/>
+      <c r="V208" s="171"/>
+      <c r="W208" s="171"/>
+      <c r="X208" s="171"/>
+      <c r="Y208" s="171"/>
+      <c r="Z208" s="171"/>
+      <c r="AA208" s="171"/>
+      <c r="AC208" s="171"/>
     </row>
     <row r="209" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B209" s="20" t="s">
@@ -31744,21 +31789,21 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="228" t="s">
+      <c r="B4" s="227" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="228"/>
-      <c r="E4" s="228" t="s">
+      <c r="C4" s="227"/>
+      <c r="E4" s="227" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="228"/>
-      <c r="G4" s="228"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="174">
+      <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
         <v>99.17</v>
       </c>
@@ -31774,18 +31819,18 @@
       <c r="B6" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="C6" s="175">
+      <c r="C6" s="174">
         <f ca="1">Statement!AC171</f>
         <v>498428.42</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="180">
+      <c r="F6" s="179">
         <f>IF(Statement!M5&lt;=0,"N/A",_xlfn.RRI(4,Statement!M5,Statement!Q5))</f>
         <v>-9.5668499906773397E-2</v>
       </c>
-      <c r="G6" s="180" t="str">
+      <c r="G6" s="179" t="str">
         <f>IF(Statement!H5&lt;=0,"N/A",_xlfn.RRI(9,Statement!H5,Statement!Q5))</f>
         <v>N/A</v>
       </c>
@@ -31794,18 +31839,18 @@
       <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="175">
+      <c r="C7" s="174">
         <f ca="1">Statement!AC172</f>
         <v>524265.41999999993</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="180" t="str">
+      <c r="F7" s="179" t="str">
         <f>IF(OR(Statement!M18&lt;=0, Statement!Q18&lt;=0), "N/A", _xlfn.RRI(4, Statement!M18, Statement!Q18))</f>
         <v>N/A</v>
       </c>
-      <c r="G7" s="180" t="str">
+      <c r="G7" s="179" t="str">
         <f>IF(OR(Statement!H18&lt;=0, Statement!Q18&lt;=0), "N/A", _xlfn.RRI(9, Statement!H18, Statement!Q18))</f>
         <v>N/A</v>
       </c>
@@ -31814,18 +31859,18 @@
       <c r="B8" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="C8" s="176">
+      <c r="C8" s="175">
         <f ca="1">Statement!AC168</f>
         <v>-159.95161290322582</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="F8" s="180" t="str">
+      <c r="F8" s="179" t="str">
         <f>IF(OR(Statement!M26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(4, Statement!M26, Statement!Q26))</f>
         <v>N/A</v>
       </c>
-      <c r="G8" s="180" t="str">
+      <c r="G8" s="179" t="str">
         <f>IF(OR(Statement!H26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(9, Statement!H26, Statement!Q26))</f>
         <v>N/A</v>
       </c>
@@ -31834,18 +31879,18 @@
       <c r="B9" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="176">
+      <c r="C9" s="175">
         <f ca="1">Statement!AC169</f>
         <v>8.6796576641928471</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="F9" s="180">
+      <c r="F9" s="179">
         <f>IF(Statement!M81&lt;=0,"N/A",_xlfn.RRI(4,Statement!M81,Statement!Q81))</f>
         <v>-1</v>
       </c>
-      <c r="G9" s="180" t="str">
+      <c r="G9" s="179" t="str">
         <f>IF(Statement!H81&lt;=0,"N/A",_xlfn.RRI(9,Statement!H81,Statement!Q81))</f>
         <v>N/A</v>
       </c>
@@ -31854,18 +31899,18 @@
       <c r="B10" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="176">
+      <c r="C10" s="175">
         <f ca="1">Statement!AC170</f>
         <v>4.4744637951774777</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="180">
+      <c r="F10" s="179">
         <f>IF(Statement!M130&lt;=0,"N/A",_xlfn.RRI(4,Statement!M130,Statement!Q130))</f>
         <v>-8.3512303772420138E-2</v>
       </c>
-      <c r="G10" s="180" t="str">
+      <c r="G10" s="179" t="str">
         <f>IF(Statement!H130&lt;=0,"N/A",_xlfn.RRI(9,Statement!H130,Statement!Q130))</f>
         <v>N/A</v>
       </c>
@@ -31874,7 +31919,7 @@
       <c r="B11" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="C11" s="176">
+      <c r="C11" s="175">
         <f ca="1">Statement!AC173</f>
         <v>9.7514167736175423</v>
       </c>
@@ -31883,33 +31928,33 @@
       <c r="B12" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="C12" s="176">
+      <c r="C12" s="175">
         <f ca="1">Statement!AC174</f>
         <v>-103.83549613784906</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="228" t="s">
+      <c r="B15" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="228"/>
-      <c r="E15" s="228" t="s">
+      <c r="C15" s="227"/>
+      <c r="E15" s="227" t="s">
         <v>249</v>
       </c>
-      <c r="F15" s="228"/>
+      <c r="F15" s="227"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="177">
+      <c r="C16" s="176">
         <f>Statement!AC100</f>
         <v>0.35433290552982533</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="175">
+      <c r="F16" s="174">
         <f>Statement!AC18</f>
         <v>-3174</v>
       </c>
@@ -31918,14 +31963,14 @@
       <c r="B17" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="177">
+      <c r="C17" s="176">
         <f>Statement!AC101</f>
         <v>-9.391217007979466E-2</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="F17" s="175">
+      <c r="F17" s="174">
         <f>Statement!AC58</f>
         <v>9980</v>
       </c>
@@ -31934,40 +31979,40 @@
       <c r="B18" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="177">
+      <c r="C18" s="176">
         <f>Statement!AC102</f>
         <v>-6.2645313691572266E-2</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="F18" s="179" t="str">
+      <c r="F18" s="178" t="str">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="228" t="s">
+      <c r="B21" s="227" t="s">
         <v>248</v>
       </c>
-      <c r="C21" s="228"/>
-      <c r="E21" s="228" t="s">
+      <c r="C21" s="227"/>
+      <c r="E21" s="227" t="s">
         <v>252</v>
       </c>
-      <c r="F21" s="228"/>
+      <c r="F21" s="227"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="177">
+      <c r="C22" s="176">
         <f>Statement!AC134</f>
         <v>-6.2645313691572266E-2</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="177">
+      <c r="F22" s="176">
         <f>C24</f>
         <v>-1.6402703913661776E-2</v>
       </c>
@@ -31976,14 +32021,14 @@
       <c r="B23" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="176">
+      <c r="C23" s="175">
         <f>Statement!AC135</f>
         <v>0.26183449243176904</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="177">
+      <c r="F23" s="176">
         <f>C26</f>
         <v>-3.0235021634917498E-2</v>
       </c>
@@ -31992,14 +32037,14 @@
       <c r="B24" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="178">
+      <c r="C24" s="177">
         <f>Statement!AC136</f>
         <v>-1.6402703913661776E-2</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="177">
+      <c r="F24" s="176">
         <f>Statement!AC158</f>
         <v>-3.6791978488825414E-2</v>
       </c>
@@ -32008,7 +32053,7 @@
       <c r="B25" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="176">
+      <c r="C25" s="175">
         <f>Statement!AC137</f>
         <v>1.8432949710038242</v>
       </c>
@@ -32017,33 +32062,33 @@
       <c r="B26" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="178">
+      <c r="C26" s="177">
         <f>Statement!AC138</f>
         <v>-3.0235021634917498E-2</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="228" t="s">
+      <c r="B29" s="227" t="s">
         <v>253</v>
       </c>
-      <c r="C29" s="228"/>
-      <c r="E29" s="228" t="s">
+      <c r="C29" s="227"/>
+      <c r="E29" s="227" t="s">
         <v>259</v>
       </c>
-      <c r="F29" s="228"/>
+      <c r="F29" s="227"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="176">
+      <c r="C30" s="175">
         <f>Statement!AC159</f>
         <v>27.604300355262914</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="F30" s="182">
+      <c r="F30" s="181">
         <f>Statement!AC163</f>
         <v>0.40424978005996731</v>
       </c>
@@ -32052,14 +32097,14 @@
       <c r="B31" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C31" s="176">
+      <c r="C31" s="175">
         <f>Statement!AC160</f>
         <v>130.6568144499179</v>
       </c>
       <c r="E31" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="F31" s="182">
+      <c r="F31" s="181">
         <f>Statement!AC164</f>
         <v>0.10989819918487531</v>
       </c>
@@ -32068,14 +32113,14 @@
       <c r="B32" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="176">
+      <c r="C32" s="175">
         <f>Statement!AC161</f>
         <v>75.275401146544525</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="F32" s="182">
+      <c r="F32" s="181">
         <f>Statement!AC166</f>
         <v>2.3119583410823878</v>
       </c>
@@ -32084,14 +32129,14 @@
       <c r="B33" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C33" s="176">
+      <c r="C33" s="175">
         <f>Statement!AC162</f>
         <v>82.9857136586363</v>
       </c>
       <c r="E33" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="F33" s="182">
+      <c r="F33" s="181">
         <f>Statement!AC165</f>
         <v>1.3708387576715642</v>
       </c>
@@ -32100,33 +32145,33 @@
       <c r="E34" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="F34" s="184" t="str">
+      <c r="F34" s="183" t="str">
         <f>Statement!AC167</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="228" t="s">
+      <c r="B37" s="227" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="228"/>
-      <c r="E37" s="228" t="s">
+      <c r="C37" s="227"/>
+      <c r="E37" s="227" t="s">
         <v>274</v>
       </c>
-      <c r="F37" s="228"/>
+      <c r="F37" s="227"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="C38" s="177">
+      <c r="C38" s="176">
         <f ca="1">Statement!AC180</f>
         <v>-6.2518906927498232E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="F38" s="177">
+      <c r="F38" s="176">
         <f>Statement!AC186</f>
         <v>0</v>
       </c>
@@ -32135,14 +32180,14 @@
       <c r="B39" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="C39" s="217">
+      <c r="C39" s="216">
         <f ca="1">Statement!AC179</f>
         <v>-1.1014620715247336E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="F39" s="177">
+      <c r="F39" s="176">
         <f>Statement!AC187</f>
         <v>0</v>
       </c>
@@ -32151,14 +32196,14 @@
       <c r="B40" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="C40" s="177">
+      <c r="C40" s="176">
         <f ca="1">Statement!AC181</f>
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="F40" s="177">
+      <c r="F40" s="176">
         <f>Statement!AC188</f>
         <v>0</v>
       </c>
@@ -32167,7 +32212,7 @@
       <c r="B41" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="C41" s="177">
+      <c r="C41" s="176">
         <f ca="1">Statement!AC182</f>
         <v>0</v>
       </c>
@@ -32176,33 +32221,33 @@
       <c r="B42" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="C42" s="177">
+      <c r="C42" s="176">
         <f ca="1">Statement!AC183</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="228" t="s">
+      <c r="B45" s="227" t="s">
         <v>282</v>
       </c>
-      <c r="C45" s="228"/>
-      <c r="E45" s="228" t="s">
+      <c r="C45" s="227"/>
+      <c r="E45" s="227" t="s">
         <v>288</v>
       </c>
-      <c r="F45" s="228"/>
+      <c r="F45" s="227"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="C46" s="177">
+      <c r="C46" s="176">
         <f>Statement!AC189</f>
         <v>5.9689614007162755E-4</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="F46" s="176">
+      <c r="F46" s="175">
         <f>Statement!AC190</f>
         <v>6.5238758456028654</v>
       </c>
@@ -32211,7 +32256,7 @@
       <c r="E47" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="F47" s="176">
+      <c r="F47" s="175">
         <f>Statement!AC193</f>
         <v>-2.435734182252288</v>
       </c>
@@ -32220,33 +32265,33 @@
       <c r="E48" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="F48" s="177">
+      <c r="F48" s="176">
         <f ca="1">Statement!AC194</f>
         <v>-2.4561199780702713E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="228" t="s">
+      <c r="B51" s="227" t="s">
         <v>285</v>
       </c>
-      <c r="C51" s="228"/>
-      <c r="E51" s="228" t="s">
+      <c r="C51" s="227"/>
+      <c r="E51" s="227" t="s">
         <v>306</v>
       </c>
-      <c r="F51" s="228"/>
+      <c r="F51" s="227"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="C52" s="177">
+      <c r="C52" s="176">
         <f>Statement!AC191</f>
         <v>0.2375751503006012</v>
       </c>
       <c r="E52" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="F52" s="177">
+      <c r="F52" s="176">
         <f>Statement!AC195</f>
         <v>0.24364339787586259</v>
       </c>
@@ -32255,14 +32300,14 @@
       <c r="B53" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="C53" s="177">
+      <c r="C53" s="176">
         <f>Statement!AC192</f>
         <v>4.4100961627885349E-2</v>
       </c>
       <c r="E53" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="F53" s="177">
+      <c r="F53" s="176">
         <f>Statement!AC196</f>
         <v>1.3125250501002004</v>
       </c>
@@ -32271,7 +32316,7 @@
       <c r="E54" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="F54" s="177">
+      <c r="F54" s="176">
         <f>Statement!AC197</f>
         <v>1.0765121630506247</v>
       </c>
@@ -32379,27 +32424,27 @@
       <c r="B6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="174">
+      <c r="C6" s="173">
         <f>Statement!M129</f>
         <v>51.31</v>
       </c>
-      <c r="D6" s="174">
+      <c r="D6" s="173">
         <f>Statement!N129</f>
         <v>26.43</v>
       </c>
-      <c r="E6" s="174">
+      <c r="E6" s="173">
         <f>Statement!O129</f>
         <v>50.25</v>
       </c>
-      <c r="F6" s="174">
+      <c r="F6" s="173">
         <f>Statement!P129</f>
         <v>20.3</v>
       </c>
-      <c r="G6" s="174">
+      <c r="G6" s="173">
         <f>Statement!Q129</f>
         <v>36.200000000000003</v>
       </c>
-      <c r="I6" s="174">
+      <c r="I6" s="173">
         <f ca="1">Statement!AC129</f>
         <v>99.17</v>
       </c>
@@ -32408,27 +32453,27 @@
       <c r="B7" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="C7" s="175">
+      <c r="C7" s="174">
         <f>Statement!M171</f>
         <v>210524.93000000002</v>
       </c>
-      <c r="D7" s="175">
+      <c r="D7" s="174">
         <f>Statement!N171</f>
         <v>109737.36</v>
       </c>
-      <c r="E7" s="175">
+      <c r="E7" s="174">
         <f>Statement!O171</f>
         <v>213562.5</v>
       </c>
-      <c r="F7" s="175">
+      <c r="F7" s="174">
         <f>Statement!P171</f>
         <v>87899</v>
       </c>
-      <c r="G7" s="175">
+      <c r="G7" s="174">
         <f>Statement!Q171</f>
         <v>180819</v>
       </c>
-      <c r="I7" s="175">
+      <c r="I7" s="174">
         <f ca="1">Statement!AC171</f>
         <v>498428.42</v>
       </c>
@@ -32437,27 +32482,27 @@
       <c r="B8" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="175">
+      <c r="C8" s="174">
         <f>Statement!M172</f>
         <v>220212.93000000002</v>
       </c>
-      <c r="D8" s="175">
+      <c r="D8" s="174">
         <f>Statement!N172</f>
         <v>125313.35999999999</v>
       </c>
-      <c r="E8" s="175">
+      <c r="E8" s="174">
         <f>Statement!O172</f>
         <v>242169.5</v>
       </c>
-      <c r="F8" s="175">
+      <c r="F8" s="174">
         <f>Statement!P172</f>
         <v>121610</v>
       </c>
-      <c r="G8" s="175">
+      <c r="G8" s="174">
         <f>Statement!Q172</f>
         <v>202067</v>
       </c>
-      <c r="I8" s="175">
+      <c r="I8" s="174">
         <f ca="1">Statement!AC172</f>
         <v>524265.41999999993</v>
       </c>
@@ -32466,27 +32511,27 @@
       <c r="B9" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="176">
+      <c r="C9" s="175">
         <f>Statement!M168</f>
         <v>10.557613168724279</v>
       </c>
-      <c r="D9" s="176">
+      <c r="D9" s="175">
         <f>Statement!N168</f>
         <v>13.623711340206185</v>
       </c>
-      <c r="E9" s="176">
+      <c r="E9" s="175">
         <f>Statement!O168</f>
         <v>125.625</v>
       </c>
-      <c r="F9" s="176">
+      <c r="F9" s="175">
         <f>Statement!P168</f>
         <v>-4.634703196347032</v>
       </c>
-      <c r="G9" s="176">
+      <c r="G9" s="175">
         <f>Statement!Q168</f>
         <v>-603.33333333333337</v>
       </c>
-      <c r="I9" s="176">
+      <c r="I9" s="175">
         <f ca="1">Statement!AC168</f>
         <v>-159.95161290322582</v>
       </c>
@@ -32495,27 +32540,27 @@
       <c r="B10" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="C10" s="176">
+      <c r="C10" s="175">
         <f>Statement!M169</f>
         <v>2.6556223425794698</v>
       </c>
-      <c r="D10" s="176">
+      <c r="D10" s="175">
         <f>Statement!N169</f>
         <v>1.7282153392330384</v>
       </c>
-      <c r="E10" s="176">
+      <c r="E10" s="175">
         <f>Statement!O169</f>
         <v>3.9030205797742865</v>
       </c>
-      <c r="F10" s="176">
+      <c r="F10" s="175">
         <f>Statement!P169</f>
         <v>1.6362027080469295</v>
       </c>
-      <c r="G10" s="176">
+      <c r="G10" s="175">
         <f>Statement!Q169</f>
         <v>3.102681020944885</v>
       </c>
-      <c r="I10" s="176">
+      <c r="I10" s="175">
         <f ca="1">Statement!AC169</f>
         <v>8.6796576641928471</v>
       </c>
@@ -32524,27 +32569,27 @@
       <c r="B11" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="176">
+      <c r="C11" s="175">
         <f>Statement!M170</f>
         <v>2.190293843234687</v>
       </c>
-      <c r="D11" s="176">
+      <c r="D11" s="175">
         <f>Statement!N170</f>
         <v>1.0780681896611222</v>
       </c>
-      <c r="E11" s="176">
+      <c r="E11" s="175">
         <f>Statement!O170</f>
         <v>2.0120939482905578</v>
       </c>
-      <c r="F11" s="176">
+      <c r="F11" s="175">
         <f>Statement!P170</f>
         <v>0.88545381283368585</v>
       </c>
-      <c r="G11" s="176">
+      <c r="G11" s="175">
         <f>Statement!Q170</f>
         <v>1.5822315170500785</v>
       </c>
-      <c r="I11" s="176">
+      <c r="I11" s="175">
         <f ca="1">Statement!AC170</f>
         <v>4.4744637951774777</v>
       </c>
@@ -32553,27 +32598,27 @@
       <c r="B12" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="C12" s="176">
+      <c r="C12" s="175">
         <f>Statement!M173</f>
         <v>2.7866588631301887</v>
       </c>
-      <c r="D12" s="176">
+      <c r="D12" s="175">
         <f>Statement!N173</f>
         <v>1.9873974688362355</v>
       </c>
-      <c r="E12" s="176">
+      <c r="E12" s="175">
         <f>Statement!O173</f>
         <v>4.4657649184922921</v>
       </c>
-      <c r="F12" s="176">
+      <c r="F12" s="175">
         <f>Statement!P173</f>
         <v>2.2901640270428052</v>
       </c>
-      <c r="G12" s="176">
+      <c r="G12" s="175">
         <f>Statement!Q173</f>
         <v>3.823188844531058</v>
       </c>
-      <c r="I12" s="176">
+      <c r="I12" s="175">
         <f ca="1">Statement!AC173</f>
         <v>9.7514167736175423</v>
       </c>
@@ -32582,27 +32627,27 @@
       <c r="B13" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="176">
+      <c r="C13" s="175">
         <f>Statement!M174</f>
         <v>11.318509971217106</v>
       </c>
-      <c r="D13" s="176">
+      <c r="D13" s="175">
         <f>Statement!N174</f>
         <v>53.690385604113104</v>
       </c>
-      <c r="E13" s="176">
+      <c r="E13" s="175">
         <f>Statement!O174</f>
         <v>2603.9731182795699</v>
       </c>
-      <c r="F13" s="176">
+      <c r="F13" s="175">
         <f>Statement!P174</f>
         <v>-10.413598218873094</v>
       </c>
-      <c r="G13" s="176">
+      <c r="G13" s="175">
         <f>Statement!Q174</f>
         <v>-91.267841011743457</v>
       </c>
-      <c r="I13" s="176">
+      <c r="I13" s="175">
         <f ca="1">Statement!AC174</f>
         <v>-103.83549613784906</v>
       </c>
@@ -32622,27 +32667,27 @@
       <c r="B16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="177">
+      <c r="C16" s="176">
         <f>Statement!M100</f>
         <v>0.5544518121077141</v>
       </c>
-      <c r="D16" s="177">
+      <c r="D16" s="176">
         <f>Statement!N100</f>
         <v>0.42607923367272499</v>
       </c>
-      <c r="E16" s="177">
+      <c r="E16" s="176">
         <f>Statement!O100</f>
         <v>0.40036512502766097</v>
       </c>
-      <c r="F16" s="177">
+      <c r="F16" s="176">
         <f>Statement!P100</f>
         <v>0.32664168283083184</v>
       </c>
-      <c r="G16" s="177">
+      <c r="G16" s="176">
         <f>Statement!Q100</f>
         <v>0.34766238434904356</v>
       </c>
-      <c r="I16" s="177">
+      <c r="I16" s="176">
         <f>Statement!AC100</f>
         <v>0.35433290552982533</v>
       </c>
@@ -32651,27 +32696,27 @@
       <c r="B17" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="177">
+      <c r="C17" s="176">
         <f>Statement!M101</f>
         <v>0.24620368495646891</v>
       </c>
-      <c r="D17" s="177">
+      <c r="D17" s="176">
         <f>Statement!N101</f>
         <v>3.7015891140926828E-2</v>
       </c>
-      <c r="E17" s="177">
+      <c r="E17" s="176">
         <f>Statement!O101</f>
         <v>1.714981190528878E-3</v>
       </c>
-      <c r="F17" s="177">
+      <c r="F17" s="176">
         <f>Statement!P101</f>
         <v>-0.21992052880360069</v>
       </c>
-      <c r="G17" s="177">
+      <c r="G17" s="176">
         <f>Statement!Q101</f>
         <v>-4.1889769738709247E-2</v>
       </c>
-      <c r="I17" s="177">
+      <c r="I17" s="176">
         <f>Statement!AC101</f>
         <v>-9.391217007979466E-2</v>
       </c>
@@ -32680,27 +32725,27 @@
       <c r="B18" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="177">
+      <c r="C18" s="176">
         <f>Statement!M102</f>
         <v>0.25141729094958493</v>
       </c>
-      <c r="D18" s="177">
+      <c r="D18" s="176">
         <f>Statement!N102</f>
         <v>0.12714498683667966</v>
       </c>
-      <c r="E18" s="177">
+      <c r="E18" s="176">
         <f>Statement!O102</f>
         <v>3.088810208748248E-2</v>
       </c>
-      <c r="F18" s="177">
+      <c r="F18" s="176">
         <f>Statement!P102</f>
         <v>-0.3621965688028474</v>
       </c>
-      <c r="G18" s="177">
+      <c r="G18" s="176">
         <f>Statement!Q102</f>
         <v>4.9193044860272833E-4</v>
       </c>
-      <c r="I18" s="177">
+      <c r="I18" s="176">
         <f>Statement!AC102</f>
         <v>-6.2645313691572266E-2</v>
       </c>
@@ -32720,27 +32765,27 @@
       <c r="B21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="179">
+      <c r="C21" s="178">
         <f>Statement!M18</f>
         <v>19868</v>
       </c>
-      <c r="D21" s="179">
+      <c r="D21" s="178">
         <f>Statement!N18</f>
         <v>8014</v>
       </c>
-      <c r="E21" s="179">
+      <c r="E21" s="178">
         <f>Statement!O18</f>
         <v>1689</v>
       </c>
-      <c r="F21" s="179">
+      <c r="F21" s="178">
         <f>Statement!P18</f>
         <v>-18756</v>
       </c>
-      <c r="G21" s="179">
+      <c r="G21" s="178">
         <f>Statement!Q18</f>
         <v>-267</v>
       </c>
-      <c r="I21" s="179">
+      <c r="I21" s="178">
         <f>Statement!AC18</f>
         <v>-3174</v>
       </c>
@@ -32749,27 +32794,27 @@
       <c r="B22" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C22" s="179">
+      <c r="C22" s="178">
         <f>Statement!M58</f>
         <v>29456</v>
       </c>
-      <c r="D22" s="179">
+      <c r="D22" s="178">
         <f>Statement!N58</f>
         <v>15433</v>
       </c>
-      <c r="E22" s="179">
+      <c r="E22" s="178">
         <f>Statement!O58</f>
         <v>11471</v>
       </c>
-      <c r="F22" s="179">
+      <c r="F22" s="178">
         <f>Statement!P58</f>
         <v>8288</v>
       </c>
-      <c r="G22" s="179">
+      <c r="G22" s="178">
         <f>Statement!Q58</f>
         <v>9697</v>
       </c>
-      <c r="I22" s="179">
+      <c r="I22" s="178">
         <f>Statement!AC58</f>
         <v>9980</v>
       </c>
@@ -32778,27 +32823,27 @@
       <c r="B23" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="C23" s="197">
+      <c r="C23" s="196">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
         <v>-9588</v>
       </c>
-      <c r="D23" s="197">
+      <c r="D23" s="196">
         <f t="shared" ref="D23:I23" si="0">IF(OR(D21&lt;=0, D22&lt;=0),"N/A",D21-D22)</f>
         <v>-7419</v>
       </c>
-      <c r="E23" s="197">
+      <c r="E23" s="196">
         <f t="shared" si="0"/>
         <v>-9782</v>
       </c>
-      <c r="F23" s="197" t="str">
+      <c r="F23" s="196" t="str">
         <f t="shared" si="0"/>
         <v>N/A</v>
       </c>
-      <c r="G23" s="197" t="str">
+      <c r="G23" s="196" t="str">
         <f t="shared" si="0"/>
         <v>N/A</v>
       </c>
-      <c r="I23" s="197" t="str">
+      <c r="I23" s="196" t="str">
         <f t="shared" si="0"/>
         <v>N/A</v>
       </c>
@@ -32818,27 +32863,27 @@
       <c r="B26" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="177">
+      <c r="C26" s="176">
         <f>Statement!M134</f>
         <v>0.25141729094958493</v>
       </c>
-      <c r="D26" s="177">
+      <c r="D26" s="176">
         <f>Statement!N134</f>
         <v>0.12714498683667966</v>
       </c>
-      <c r="E26" s="177">
+      <c r="E26" s="176">
         <f>Statement!O134</f>
         <v>3.088810208748248E-2</v>
       </c>
-      <c r="F26" s="177">
+      <c r="F26" s="176">
         <f>Statement!P134</f>
         <v>-0.3621965688028474</v>
       </c>
-      <c r="G26" s="177">
+      <c r="G26" s="176">
         <f>Statement!Q134</f>
         <v>4.9193044860272833E-4</v>
       </c>
-      <c r="I26" s="177">
+      <c r="I26" s="176">
         <f>Statement!AC134</f>
         <v>-6.2645313691572266E-2</v>
       </c>
@@ -32847,27 +32892,27 @@
       <c r="B27" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="216">
+      <c r="C27" s="215">
         <f>Statement!M135</f>
         <v>0.46924693894516822</v>
       </c>
-      <c r="D27" s="216">
+      <c r="D27" s="215">
         <f>Statement!N135</f>
         <v>0.34625459218134791</v>
       </c>
-      <c r="E27" s="216">
+      <c r="E27" s="215">
         <f>Statement!O135</f>
         <v>0.2830685068799198</v>
       </c>
-      <c r="F27" s="216">
+      <c r="F27" s="215">
         <f>Statement!P135</f>
         <v>0.27025472682393059</v>
       </c>
-      <c r="G27" s="216">
+      <c r="G27" s="215">
         <f>Statement!Q135</f>
         <v>0.24997989868939455</v>
       </c>
-      <c r="I27" s="216">
+      <c r="I27" s="215">
         <f>Statement!AC135</f>
         <v>0.26183449243176904</v>
       </c>
@@ -32876,27 +32921,27 @@
       <c r="B28" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="178">
+      <c r="C28" s="177">
         <f>Statement!M136</f>
         <v>0.11797679417597948</v>
       </c>
-      <c r="D28" s="178">
+      <c r="D28" s="177">
         <f>Statement!N136</f>
         <v>4.4024535565037361E-2</v>
       </c>
-      <c r="E28" s="178">
+      <c r="E28" s="177">
         <f>Statement!O136</f>
         <v>8.7434489382581995E-3</v>
       </c>
-      <c r="F28" s="178">
+      <c r="F28" s="177">
         <f>Statement!P136</f>
         <v>-9.7885334758378503E-2</v>
       </c>
-      <c r="G28" s="178">
+      <c r="G28" s="177">
         <f>Statement!Q136</f>
         <v>1.2297272370393844E-4</v>
       </c>
-      <c r="I28" s="178">
+      <c r="I28" s="177">
         <f>Statement!AC136</f>
         <v>-1.6402703913661776E-2</v>
       </c>
@@ -32905,27 +32950,27 @@
       <c r="B29" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="216">
+      <c r="C29" s="215">
         <f>Statement!M137</f>
         <v>1.7654286043756748</v>
       </c>
-      <c r="D29" s="216">
+      <c r="D29" s="215">
         <f>Statement!N137</f>
         <v>1.7954803151159007</v>
       </c>
-      <c r="E29" s="216">
+      <c r="E29" s="215">
         <f>Statement!O137</f>
         <v>1.8143005966474097</v>
       </c>
-      <c r="F29" s="216">
+      <c r="F29" s="215">
         <f>Statement!P137</f>
         <v>1.9792988818374131</v>
       </c>
-      <c r="G29" s="216">
+      <c r="G29" s="215">
         <f>Statement!Q137</f>
         <v>1.8500800658027143</v>
       </c>
-      <c r="I29" s="216">
+      <c r="I29" s="215">
         <f>Statement!AC137</f>
         <v>1.8432949710038242</v>
       </c>
@@ -32934,27 +32979,27 @@
       <c r="B30" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="178">
+      <c r="C30" s="177">
         <f>Statement!M138</f>
         <v>0.20827960709081569</v>
       </c>
-      <c r="D30" s="178">
+      <c r="D30" s="177">
         <f>Statement!N138</f>
         <v>7.904518698914445E-2</v>
       </c>
-      <c r="E30" s="178">
+      <c r="E30" s="177">
         <f>Statement!O138</f>
         <v>1.5863244625438012E-2</v>
       </c>
-      <c r="F30" s="178">
+      <c r="F30" s="177">
         <f>Statement!P138</f>
         <v>-0.19374433363553945</v>
       </c>
-      <c r="G30" s="178">
+      <c r="G30" s="177">
         <f>Statement!Q138</f>
         <v>2.2750938476212145E-4</v>
       </c>
-      <c r="I30" s="178">
+      <c r="I30" s="177">
         <f>Statement!AC138</f>
         <v>-3.0235021634917498E-2</v>
       </c>
@@ -32974,27 +33019,27 @@
       <c r="B33" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="177">
+      <c r="C33" s="176">
         <f>C28</f>
         <v>0.11797679417597948</v>
       </c>
-      <c r="D33" s="177">
+      <c r="D33" s="176">
         <f t="shared" ref="D33:G33" si="1">D28</f>
         <v>4.4024535565037361E-2</v>
       </c>
-      <c r="E33" s="177">
+      <c r="E33" s="176">
         <f t="shared" si="1"/>
         <v>8.7434489382581995E-3</v>
       </c>
-      <c r="F33" s="177">
+      <c r="F33" s="176">
         <f t="shared" si="1"/>
         <v>-9.7885334758378503E-2</v>
       </c>
-      <c r="G33" s="177">
+      <c r="G33" s="176">
         <f t="shared" si="1"/>
         <v>1.2297272370393844E-4</v>
       </c>
-      <c r="I33" s="177">
+      <c r="I33" s="176">
         <f>I28</f>
         <v>-1.6402703913661776E-2</v>
       </c>
@@ -33003,27 +33048,27 @@
       <c r="B34" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="177">
+      <c r="C34" s="176">
         <f>C30</f>
         <v>0.20827960709081569</v>
       </c>
-      <c r="D34" s="177">
+      <c r="D34" s="176">
         <f t="shared" ref="D34:G34" si="2">D30</f>
         <v>7.904518698914445E-2</v>
       </c>
-      <c r="E34" s="177">
+      <c r="E34" s="176">
         <f t="shared" si="2"/>
         <v>1.5863244625438012E-2</v>
       </c>
-      <c r="F34" s="177">
+      <c r="F34" s="176">
         <f t="shared" si="2"/>
         <v>-0.19374433363553945</v>
       </c>
-      <c r="G34" s="177">
+      <c r="G34" s="176">
         <f t="shared" si="2"/>
         <v>2.2750938476212145E-4</v>
       </c>
-      <c r="I34" s="177">
+      <c r="I34" s="176">
         <f>I30</f>
         <v>-3.0235021634917498E-2</v>
       </c>
@@ -33032,27 +33077,27 @@
       <c r="B35" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="177">
+      <c r="C35" s="176">
         <f>Statement!M158</f>
         <v>0.16950089956234582</v>
       </c>
-      <c r="D35" s="177">
+      <c r="D35" s="176">
         <f>Statement!N158</f>
         <v>1.9948888452038051E-2</v>
       </c>
-      <c r="E35" s="177">
+      <c r="E35" s="176">
         <f>Statement!O158</f>
         <v>6.9301102111075507E-4</v>
       </c>
-      <c r="F35" s="177">
+      <c r="F35" s="176">
         <f>Statement!P158</f>
         <v>-8.7817056571991486E-2</v>
       </c>
-      <c r="G35" s="177">
+      <c r="G35" s="176">
         <f>Statement!Q158</f>
         <v>-1.6335987131905347E-2</v>
       </c>
-      <c r="I35" s="177">
+      <c r="I35" s="176">
         <f>Statement!AC158</f>
         <v>-3.6791978488825414E-2</v>
       </c>
@@ -33072,27 +33117,27 @@
       <c r="B38" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="176">
+      <c r="C38" s="175">
         <f>Statement!M159</f>
         <v>43.680464162785988</v>
       </c>
-      <c r="D38" s="176">
+      <c r="D38" s="175">
         <f>Statement!N159</f>
         <v>23.924651885685286</v>
       </c>
-      <c r="E38" s="176">
+      <c r="E38" s="175">
         <f>Statement!O159</f>
         <v>22.898318211993807</v>
       </c>
-      <c r="F38" s="176">
+      <c r="F38" s="175">
         <f>Statement!P159</f>
         <v>23.906706088397584</v>
       </c>
-      <c r="G38" s="176">
+      <c r="G38" s="175">
         <f>Statement!Q159</f>
         <v>26.511929313378616</v>
       </c>
-      <c r="I38" s="176">
+      <c r="I38" s="175">
         <f>Statement!AC159</f>
         <v>27.604300355262914</v>
       </c>
@@ -33101,27 +33146,27 @@
       <c r="B39" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="176">
+      <c r="C39" s="175">
         <f>Statement!M160</f>
         <v>111.71121020193701</v>
       </c>
-      <c r="D39" s="176">
+      <c r="D39" s="175">
         <f>Statement!N160</f>
         <v>133.38012600862163</v>
       </c>
-      <c r="E39" s="176">
+      <c r="E39" s="175">
         <f>Statement!O160</f>
         <v>124.89943721745549</v>
       </c>
-      <c r="F39" s="176">
+      <c r="F39" s="175">
         <f>Statement!P160</f>
         <v>124.51812283253162</v>
       </c>
-      <c r="G39" s="176">
+      <c r="G39" s="175">
         <f>Statement!Q160</f>
         <v>122.99350310342828</v>
       </c>
-      <c r="I39" s="176">
+      <c r="I39" s="175">
         <f>Statement!AC160</f>
         <v>130.6568144499179</v>
       </c>
@@ -33130,27 +33175,27 @@
       <c r="B40" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C40" s="176">
+      <c r="C40" s="175">
         <f>Statement!M161</f>
         <v>59.577238774177054</v>
       </c>
-      <c r="D40" s="176">
+      <c r="D40" s="175">
         <f>Statement!N161</f>
         <v>96.777246601083235</v>
       </c>
-      <c r="E40" s="176">
+      <c r="E40" s="175">
         <f>Statement!O161</f>
         <v>96.219823476950523</v>
       </c>
-      <c r="F40" s="176">
+      <c r="F40" s="175">
         <f>Statement!P161</f>
         <v>128.17261438639667</v>
       </c>
-      <c r="G40" s="176">
+      <c r="G40" s="175">
         <f>Statement!Q161</f>
         <v>104.6154069261558</v>
       </c>
-      <c r="I40" s="176">
+      <c r="I40" s="175">
         <f>Statement!AC161</f>
         <v>75.275401146544525</v>
       </c>
@@ -33159,27 +33204,27 @@
       <c r="B41" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="176">
+      <c r="C41" s="175">
         <f>Statement!M162</f>
         <v>95.814435590545941</v>
       </c>
-      <c r="D41" s="176">
+      <c r="D41" s="175">
         <f>Statement!N162</f>
         <v>60.527531293223674</v>
       </c>
-      <c r="E41" s="176">
+      <c r="E41" s="175">
         <f>Statement!O162</f>
         <v>51.577931952498773</v>
       </c>
-      <c r="F41" s="176">
+      <c r="F41" s="175">
         <f>Statement!P162</f>
         <v>20.252214534532527</v>
       </c>
-      <c r="G41" s="176">
+      <c r="G41" s="175">
         <f>Statement!Q162</f>
         <v>44.890025490651112</v>
       </c>
-      <c r="I41" s="176">
+      <c r="I41" s="175">
         <f>Statement!AC162</f>
         <v>82.9857136586363</v>
       </c>
@@ -33199,27 +33244,27 @@
       <c r="B44" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="C44" s="182">
+      <c r="C44" s="181">
         <f>Statement!M163</f>
         <v>0.39941923242234595</v>
       </c>
-      <c r="D44" s="182">
+      <c r="D44" s="181">
         <f>Statement!N163</f>
         <v>0.41461009830117429</v>
       </c>
-      <c r="E44" s="182">
+      <c r="E44" s="181">
         <f>Statement!O163</f>
         <v>0.46657827445780853</v>
       </c>
-      <c r="F44" s="182">
+      <c r="F44" s="181">
         <f>Statement!P163</f>
         <v>0.50378764984386015</v>
       </c>
-      <c r="G44" s="182">
+      <c r="G44" s="181">
         <f>Statement!Q163</f>
         <v>0.40763556496705489</v>
       </c>
-      <c r="I44" s="182">
+      <c r="I44" s="181">
         <f>Statement!AC163</f>
         <v>0.40424978005996731</v>
       </c>
@@ -33228,27 +33273,27 @@
       <c r="B45" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="C45" s="182">
+      <c r="C45" s="181">
         <f>Statement!M164</f>
         <v>0.10156094390456123</v>
       </c>
-      <c r="D45" s="182">
+      <c r="D45" s="181">
         <f>Statement!N164</f>
         <v>0.13520601835875493</v>
       </c>
-      <c r="E45" s="182">
+      <c r="E45" s="181">
         <f>Statement!O164</f>
         <v>0.22949142911260537</v>
       </c>
-      <c r="F45" s="182">
+      <c r="F45" s="181">
         <f>Statement!P164</f>
         <v>0.28154528054800038</v>
       </c>
-      <c r="G45" s="182">
+      <c r="G45" s="181">
         <f>Statement!Q164</f>
         <v>8.0232059572457368E-2</v>
       </c>
-      <c r="I45" s="182">
+      <c r="I45" s="181">
         <f>Statement!AC164</f>
         <v>0.10989819918487531</v>
       </c>
@@ -33257,27 +33302,27 @@
       <c r="B46" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="C46" s="182">
+      <c r="C46" s="181">
         <f>Statement!M165</f>
         <v>1.3789964314325249</v>
       </c>
-      <c r="D46" s="182">
+      <c r="D46" s="181">
         <f>Statement!N165</f>
         <v>1.0098273985383299</v>
       </c>
-      <c r="E46" s="182">
+      <c r="E46" s="181">
         <f>Statement!O165</f>
         <v>1.0136527287634121</v>
       </c>
-      <c r="F46" s="182">
+      <c r="F46" s="181">
         <f>Statement!P165</f>
         <v>0.71608815118039593</v>
       </c>
-      <c r="G46" s="182">
+      <c r="G46" s="181">
         <f>Statement!Q165</f>
         <v>1.306571654790182</v>
       </c>
-      <c r="I46" s="182">
+      <c r="I46" s="181">
         <f>Statement!AC165</f>
         <v>1.3708387576715642</v>
       </c>
@@ -33286,27 +33331,27 @@
       <c r="B47" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="C47" s="182">
+      <c r="C47" s="181">
         <f>Statement!M166</f>
         <v>2.1017405869929355</v>
       </c>
-      <c r="D47" s="182">
+      <c r="D47" s="181">
         <f>Statement!N166</f>
         <v>1.5676255636759446</v>
       </c>
-      <c r="E47" s="182">
+      <c r="E47" s="181">
         <f>Statement!O166</f>
         <v>1.5424018821516416</v>
       </c>
-      <c r="F47" s="182">
+      <c r="F47" s="181">
         <f>Statement!P166</f>
         <v>1.3268659227275277</v>
       </c>
-      <c r="G47" s="182">
+      <c r="G47" s="181">
         <f>Statement!Q166</f>
         <v>2.0170387965162311</v>
       </c>
-      <c r="I47" s="182">
+      <c r="I47" s="181">
         <f>Statement!AC166</f>
         <v>2.3119583410823878</v>
       </c>
@@ -33315,27 +33360,27 @@
       <c r="B48" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="C48" s="184" t="str">
+      <c r="C48" s="183" t="str">
         <f>Statement!M167</f>
         <v>N/A</v>
       </c>
-      <c r="D48" s="184" t="str">
+      <c r="D48" s="183" t="str">
         <f>Statement!N167</f>
         <v>N/A</v>
       </c>
-      <c r="E48" s="184" t="str">
+      <c r="E48" s="183" t="str">
         <f>Statement!O167</f>
         <v>N/A</v>
       </c>
-      <c r="F48" s="184" t="str">
+      <c r="F48" s="183" t="str">
         <f>Statement!P167</f>
         <v>N/A</v>
       </c>
-      <c r="G48" s="184" t="str">
+      <c r="G48" s="183" t="str">
         <f>Statement!Q167</f>
         <v>N/A</v>
       </c>
-      <c r="I48" s="184" t="str">
+      <c r="I48" s="183" t="str">
         <f>Statement!AC167</f>
         <v>N/A</v>
       </c>
@@ -33355,27 +33400,27 @@
       <c r="B51" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="C51" s="177">
+      <c r="C51" s="176">
         <f>Statement!M180</f>
         <v>9.471837848372637E-2</v>
       </c>
-      <c r="D51" s="177">
+      <c r="D51" s="176">
         <f>Statement!N180</f>
         <v>7.3401437760121077E-2</v>
       </c>
-      <c r="E51" s="177">
+      <c r="E51" s="176">
         <f>Statement!O180</f>
         <v>7.9601990049751256E-3</v>
       </c>
-      <c r="F51" s="177">
+      <c r="F51" s="176">
         <f>Statement!P180</f>
         <v>-0.21576354679802953</v>
       </c>
-      <c r="G51" s="177">
+      <c r="G51" s="176">
         <f>Statement!Q180</f>
         <v>-1.6574585635359114E-3</v>
       </c>
-      <c r="I51" s="177">
+      <c r="I51" s="176">
         <f ca="1">Statement!AC180</f>
         <v>-6.2518906927498232E-3</v>
       </c>
@@ -33384,27 +33429,27 @@
       <c r="B52" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="177">
+      <c r="C52" s="176">
         <f>Statement!M179</f>
         <v>4.1263521617131038E-2</v>
       </c>
-      <c r="D52" s="177">
+      <c r="D52" s="176">
         <f>Statement!N179</f>
         <v>-0.11426372932609277</v>
       </c>
-      <c r="E52" s="177">
+      <c r="E52" s="176">
         <f>Statement!O179</f>
         <v>-8.1980684811237922E-2</v>
       </c>
-      <c r="F52" s="177">
+      <c r="F52" s="176">
         <f>Statement!P179</f>
         <v>-0.21690804218478027</v>
       </c>
-      <c r="G52" s="177">
+      <c r="G52" s="176">
         <f>Statement!Q179</f>
         <v>-4.0830886134753538E-2</v>
       </c>
-      <c r="I52" s="177">
+      <c r="I52" s="176">
         <f ca="1">Statement!AC179</f>
         <v>-1.1014620715247336E-2</v>
       </c>
@@ -33413,27 +33458,27 @@
       <c r="B53" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="C53" s="177">
+      <c r="C53" s="176">
         <f>Statement!M181</f>
         <v>2.7090235821477293E-2</v>
       </c>
-      <c r="D53" s="177">
+      <c r="D53" s="176">
         <f>Statement!N181</f>
         <v>5.5240257283390083E-2</v>
       </c>
-      <c r="E53" s="177">
+      <c r="E53" s="176">
         <f>Statement!O181</f>
         <v>1.472636815920398E-2</v>
       </c>
-      <c r="F53" s="177">
+      <c r="F53" s="176">
         <f>Statement!P181</f>
         <v>1.8719211822660099E-2</v>
       </c>
-      <c r="G53" s="177">
+      <c r="G53" s="176">
         <f>Statement!Q181</f>
         <v>0</v>
       </c>
-      <c r="I53" s="177">
+      <c r="I53" s="176">
         <f ca="1">Statement!AC181</f>
         <v>0</v>
       </c>
@@ -33442,27 +33487,27 @@
       <c r="B54" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="C54" s="177">
+      <c r="C54" s="176">
         <f>Statement!M182</f>
         <v>1.1471325510000168E-2</v>
       </c>
-      <c r="D54" s="177">
+      <c r="D54" s="176">
         <f>Statement!N182</f>
         <v>0</v>
       </c>
-      <c r="E54" s="177">
+      <c r="E54" s="176">
         <f>Statement!O182</f>
         <v>0</v>
       </c>
-      <c r="F54" s="177">
+      <c r="F54" s="176">
         <f>Statement!P182</f>
         <v>0</v>
       </c>
-      <c r="G54" s="177">
+      <c r="G54" s="176">
         <f>Statement!Q182</f>
         <v>0</v>
       </c>
-      <c r="I54" s="177">
+      <c r="I54" s="176">
         <f ca="1">Statement!AC182</f>
         <v>0</v>
       </c>
@@ -33471,27 +33516,27 @@
       <c r="B55" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="C55" s="177">
+      <c r="C55" s="176">
         <f>Statement!M183</f>
         <v>3.8280501981404286E-2</v>
       </c>
-      <c r="D55" s="177">
+      <c r="D55" s="176">
         <f>Statement!N183</f>
         <v>5.4648662953072684E-2</v>
       </c>
-      <c r="E55" s="177">
+      <c r="E55" s="176">
         <f>Statement!O183</f>
         <v>1.4459467369037167E-2</v>
       </c>
-      <c r="F55" s="177">
+      <c r="F55" s="176">
         <f>Statement!P183</f>
         <v>1.8191333234735322E-2</v>
       </c>
-      <c r="G55" s="177">
+      <c r="G55" s="176">
         <f>Statement!Q183</f>
         <v>0</v>
       </c>
-      <c r="I55" s="177">
+      <c r="I55" s="176">
         <f ca="1">Statement!AC183</f>
         <v>0</v>
       </c>
@@ -33511,27 +33556,27 @@
       <c r="B58" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="C58" s="177">
+      <c r="C58" s="176">
         <f>Statement!M186</f>
         <v>0.64970645792563597</v>
       </c>
-      <c r="D58" s="177">
+      <c r="D58" s="176">
         <f>Statement!N186</f>
         <v>-0.47826780445011563</v>
       </c>
-      <c r="E58" s="177">
+      <c r="E58" s="176">
         <f>Statement!O186</f>
         <v>-0.1763765135937857</v>
       </c>
-      <c r="F58" s="177">
+      <c r="F58" s="176">
         <f>Statement!P186</f>
         <v>-8.3866568761145496E-2</v>
       </c>
-      <c r="G58" s="177">
+      <c r="G58" s="176">
         <f>Statement!Q186</f>
         <v>0</v>
       </c>
-      <c r="I58" s="177">
+      <c r="I58" s="176">
         <f>Statement!AC186</f>
         <v>0</v>
       </c>
@@ -33540,27 +33585,27 @@
       <c r="B59" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="C59" s="177">
+      <c r="C59" s="176">
         <f>Statement!M187</f>
         <v>0.27800161160354553</v>
       </c>
-      <c r="D59" s="177">
+      <c r="D59" s="176">
         <f>Statement!N187</f>
         <v>0</v>
       </c>
-      <c r="E59" s="177">
+      <c r="E59" s="176">
         <f>Statement!O187</f>
         <v>0</v>
       </c>
-      <c r="F59" s="177">
+      <c r="F59" s="176">
         <f>Statement!P187</f>
         <v>0</v>
       </c>
-      <c r="G59" s="177">
+      <c r="G59" s="176">
         <f>Statement!Q187</f>
         <v>0</v>
       </c>
-      <c r="I59" s="177">
+      <c r="I59" s="176">
         <f>Statement!AC187</f>
         <v>0</v>
       </c>
@@ -33569,27 +33614,27 @@
       <c r="B60" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="C60" s="177">
+      <c r="C60" s="176">
         <f>Statement!M188</f>
         <v>0.9277080695291815</v>
       </c>
-      <c r="D60" s="177">
+      <c r="D60" s="176">
         <f>Statement!N188</f>
         <v>-0.47826780445011563</v>
       </c>
-      <c r="E60" s="177">
+      <c r="E60" s="176">
         <f>Statement!O188</f>
         <v>-0.1763765135937857</v>
       </c>
-      <c r="F60" s="177">
+      <c r="F60" s="176">
         <f>Statement!P188</f>
         <v>-8.3866568761145496E-2</v>
       </c>
-      <c r="G60" s="177">
+      <c r="G60" s="176">
         <f>Statement!Q188</f>
         <v>0</v>
       </c>
-      <c r="I60" s="177">
+      <c r="I60" s="176">
         <f>Statement!AC188</f>
         <v>0</v>
       </c>
@@ -33609,27 +33654,27 @@
       <c r="B63" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="C63" s="177">
+      <c r="C63" s="176">
         <f>Statement!M189</f>
         <v>4.874482086278333E-4</v>
       </c>
-      <c r="D63" s="177">
+      <c r="D63" s="176">
         <f>Statement!N189</f>
         <v>4.8169556840077071E-4</v>
       </c>
-      <c r="E63" s="177">
+      <c r="E63" s="176">
         <f>Statement!O189</f>
         <v>4.7058823529411766E-4</v>
       </c>
-      <c r="F63" s="177">
+      <c r="F63" s="176">
         <f>Statement!P189</f>
         <v>4.6189376443418013E-4</v>
       </c>
-      <c r="G63" s="177">
+      <c r="G63" s="176">
         <f>Statement!Q189</f>
         <v>6.0060060060060057E-4</v>
       </c>
-      <c r="I63" s="177">
+      <c r="I63" s="176">
         <f>Statement!AC189</f>
         <v>5.9689614007162755E-4</v>
       </c>
@@ -33649,27 +33694,27 @@
       <c r="B66" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="C66" s="176">
+      <c r="C66" s="175">
         <f>Statement!M190</f>
         <v>6.9776522593320234</v>
       </c>
-      <c r="D66" s="176">
+      <c r="D66" s="175">
         <f>Statement!N190</f>
         <v>6.8498912255257434</v>
       </c>
-      <c r="E66" s="176">
+      <c r="E66" s="175">
         <f>Statement!O190</f>
         <v>5.9210028382213808</v>
       </c>
-      <c r="F66" s="176">
+      <c r="F66" s="175">
         <f>Statement!P190</f>
         <v>5.0951501154734409</v>
       </c>
-      <c r="G66" s="176">
+      <c r="G66" s="175">
         <f>Statement!Q190</f>
         <v>7.4906906906906903</v>
       </c>
-      <c r="I66" s="176">
+      <c r="I66" s="175">
         <f>Statement!AC190</f>
         <v>6.5238758456028654</v>
       </c>
@@ -33678,27 +33723,27 @@
       <c r="B67" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="C67" s="176">
+      <c r="C67" s="175">
         <f>Statement!M193</f>
         <v>-2.3791748526522594</v>
       </c>
-      <c r="D67" s="176">
+      <c r="D67" s="175">
         <f>Statement!N193</f>
         <v>-3.3147208121827409</v>
       </c>
-      <c r="E67" s="176">
+      <c r="E67" s="175">
         <f>Statement!O193</f>
         <v>-5.7313150425733204</v>
       </c>
-      <c r="F67" s="176">
+      <c r="F67" s="175">
         <f>Statement!P193</f>
         <v>-6.4547344110854503</v>
       </c>
-      <c r="G67" s="176">
+      <c r="G67" s="175">
         <f>Statement!Q193</f>
         <v>-1.8356356356356356</v>
       </c>
-      <c r="I67" s="176">
+      <c r="I67" s="175">
         <f>Statement!AC193</f>
         <v>-2.435734182252288</v>
       </c>
@@ -33707,27 +33752,27 @@
       <c r="B68" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C68" s="198">
+      <c r="C68" s="197">
         <f>Statement!M194</f>
         <v>-4.601830291547894E-2</v>
       </c>
-      <c r="D68" s="198">
+      <c r="D68" s="197">
         <f>Statement!N194</f>
         <v>-0.12496200017933728</v>
       </c>
-      <c r="E68" s="198">
+      <c r="E68" s="197">
         <f>Statement!O194</f>
         <v>-0.11346561311091601</v>
       </c>
-      <c r="F68" s="198">
+      <c r="F68" s="197">
         <f>Statement!P194</f>
         <v>-0.31796721236874137</v>
       </c>
-      <c r="G68" s="198">
+      <c r="G68" s="197">
         <f>Statement!Q194</f>
         <v>-5.070816673026618E-2</v>
       </c>
-      <c r="I68" s="198">
+      <c r="I68" s="197">
         <f ca="1">Statement!AC194</f>
         <v>-2.4561199780702713E-2</v>
       </c>
@@ -33747,27 +33792,27 @@
       <c r="B71" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="C71" s="177">
+      <c r="C71" s="176">
         <f>Statement!M191</f>
         <v>6.9120043454644217E-2</v>
       </c>
-      <c r="D71" s="177">
+      <c r="D71" s="176">
         <f>Statement!N191</f>
         <v>0.20268256333830104</v>
       </c>
-      <c r="E71" s="177">
+      <c r="E71" s="176">
         <f>Statement!O191</f>
         <v>0.28149245924505273</v>
       </c>
-      <c r="F71" s="177">
+      <c r="F71" s="176">
         <f>Statement!P191</f>
         <v>0.41143822393822393</v>
       </c>
-      <c r="G71" s="177">
+      <c r="G71" s="176">
         <f>Statement!Q191</f>
         <v>0.25100546560791998</v>
       </c>
-      <c r="I71" s="177">
+      <c r="I71" s="176">
         <f>Statement!AC191</f>
         <v>0.2375751503006012</v>
       </c>
@@ -33776,27 +33821,27 @@
       <c r="B72" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="C72" s="177">
+      <c r="C72" s="176">
         <f>Statement!M192</f>
         <v>2.5764324762097592E-2</v>
       </c>
-      <c r="D72" s="177">
+      <c r="D72" s="176">
         <f>Statement!N192</f>
         <v>4.9608272274558315E-2</v>
       </c>
-      <c r="E72" s="177">
+      <c r="E72" s="176">
         <f>Statement!O192</f>
         <v>5.9544884561481153E-2</v>
       </c>
-      <c r="F72" s="177">
+      <c r="F72" s="176">
         <f>Statement!P192</f>
         <v>6.4217246379540877E-2</v>
       </c>
-      <c r="G72" s="177">
+      <c r="G72" s="176">
         <f>Statement!Q192</f>
         <v>4.6052258149963103E-2</v>
       </c>
-      <c r="I72" s="177">
+      <c r="I72" s="176">
         <f>Statement!AC192</f>
         <v>4.4100961627885349E-2</v>
       </c>
@@ -33816,27 +33861,27 @@
       <c r="B75" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="C75" s="177">
+      <c r="C75" s="176">
         <f>Statement!M195</f>
         <v>0.23705456570155903</v>
       </c>
-      <c r="D75" s="177">
+      <c r="D75" s="176">
         <f>Statement!N195</f>
         <v>0.39401148222158783</v>
       </c>
-      <c r="E75" s="177">
+      <c r="E75" s="176">
         <f>Statement!O195</f>
         <v>0.4748469425389098</v>
       </c>
-      <c r="F75" s="177">
+      <c r="F75" s="176">
         <f>Statement!P195</f>
         <v>0.45091429539933336</v>
       </c>
-      <c r="G75" s="177">
+      <c r="G75" s="176">
         <f>Statement!Q195</f>
         <v>0.27710820577829071</v>
       </c>
-      <c r="I75" s="177">
+      <c r="I75" s="176">
         <f>Statement!AC195</f>
         <v>0.24364339787586259</v>
       </c>
@@ -33845,27 +33890,27 @@
       <c r="B76" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="C76" s="177">
+      <c r="C76" s="176">
         <f>Statement!M196</f>
         <v>0.63596550787615425</v>
       </c>
-      <c r="D76" s="177">
+      <c r="D76" s="176">
         <f>Statement!N196</f>
         <v>1.6097971878442299</v>
       </c>
-      <c r="E76" s="177">
+      <c r="E76" s="176">
         <f>Statement!O196</f>
         <v>2.2447912126231366</v>
       </c>
-      <c r="F76" s="177">
+      <c r="F76" s="176">
         <f>Statement!P196</f>
         <v>2.8889961389961392</v>
       </c>
-      <c r="G76" s="177">
+      <c r="G76" s="176">
         <f>Statement!Q196</f>
         <v>1.5103640301124059</v>
       </c>
-      <c r="I76" s="177">
+      <c r="I76" s="176">
         <f>Statement!AC196</f>
         <v>1.3125250501002004</v>
       </c>
@@ -33874,27 +33919,27 @@
       <c r="B77" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="C77" s="177">
+      <c r="C77" s="176">
         <f>Statement!M197</f>
         <v>1.5886194029850746</v>
       </c>
-      <c r="D77" s="177">
+      <c r="D77" s="176">
         <f>Statement!N197</f>
         <v>1.9059455312619868</v>
       </c>
-      <c r="E77" s="177">
+      <c r="E77" s="176">
         <f>Statement!O197</f>
         <v>2.6817329722974379</v>
       </c>
-      <c r="F77" s="177">
+      <c r="F77" s="176">
         <f>Statement!P197</f>
         <v>2.1042270849811056</v>
       </c>
-      <c r="G77" s="177">
+      <c r="G77" s="176">
         <f>Statement!Q197</f>
         <v>1.2511532547411583</v>
       </c>
-      <c r="I77" s="177">
+      <c r="I77" s="176">
         <f>Statement!AC197</f>
         <v>1.0765121630506247</v>
       </c>
@@ -33914,157 +33959,157 @@
       <c r="B80" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="177">
+      <c r="C80" s="176">
         <f>Statement!M88</f>
         <v>1</v>
       </c>
-      <c r="D80" s="177">
+      <c r="D80" s="176">
         <f>Statement!N88</f>
         <v>-0.20209050415063778</v>
       </c>
-      <c r="E80" s="177">
+      <c r="E80" s="176">
         <f>Statement!O88</f>
         <v>-0.13997525930155105</v>
       </c>
-      <c r="F80" s="177">
+      <c r="F80" s="176">
         <f>Statement!P88</f>
         <v>-2.0782621523935976E-2</v>
       </c>
-      <c r="G80" s="177">
+      <c r="G80" s="176">
         <f>Statement!Q88</f>
         <v>-4.6703451912393362E-3</v>
       </c>
-      <c r="I80" s="199"/>
+      <c r="I80" s="198"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B81" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C81" s="177">
+      <c r="C81" s="176">
         <f>Statement!M89</f>
         <v>1</v>
       </c>
-      <c r="D81" s="177">
+      <c r="D81" s="176">
         <f>Statement!N89</f>
         <v>2.7805390667158966E-2</v>
       </c>
-      <c r="E81" s="177">
+      <c r="E81" s="176">
         <f>Statement!O89</f>
         <v>-0.10144246711617111</v>
       </c>
-      <c r="F81" s="177">
+      <c r="F81" s="176">
         <f>Statement!P89</f>
         <v>9.9609435064735366E-2</v>
       </c>
-      <c r="G81" s="177">
+      <c r="G81" s="176">
         <f>Statement!Q89</f>
         <v>-3.5742253048439421E-2</v>
       </c>
-      <c r="I81" s="199"/>
+      <c r="I81" s="198"/>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B82" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="177">
+      <c r="C82" s="176">
         <f>Statement!M90</f>
         <v>1</v>
       </c>
-      <c r="D82" s="177">
+      <c r="D82" s="176">
         <f>Statement!N90</f>
         <v>-0.38683099395184295</v>
       </c>
-      <c r="E82" s="177">
+      <c r="E82" s="176">
         <f>Statement!O90</f>
         <v>-0.19187821037742872</v>
       </c>
-      <c r="F82" s="177">
+      <c r="F82" s="176">
         <f>Statement!P90</f>
         <v>-0.20109621850674772</v>
       </c>
-      <c r="G82" s="177">
+      <c r="G82" s="176">
         <f>Statement!Q90</f>
         <v>5.9383107523782071E-2</v>
       </c>
-      <c r="I82" s="199"/>
+      <c r="I82" s="198"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B83" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="177">
+      <c r="C83" s="176">
         <f>Statement!M94</f>
         <v>1</v>
       </c>
-      <c r="D83" s="177">
+      <c r="D83" s="176">
         <f>Statement!N94</f>
         <v>7.1020977872654871E-3</v>
       </c>
-      <c r="E83" s="177">
+      <c r="E83" s="176">
         <f>Statement!O94</f>
         <v>-0.11878362954508397</v>
       </c>
-      <c r="F83" s="177">
+      <c r="F83" s="176">
         <f>Statement!P94</f>
         <v>0.34253862521972428</v>
       </c>
-      <c r="G83" s="177">
+      <c r="G83" s="176">
         <f>Statement!Q94</f>
         <v>-0.29059711263480686</v>
       </c>
-      <c r="I83" s="199"/>
+      <c r="I83" s="198"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="C84" s="177">
+      <c r="C84" s="176">
         <f>Statement!M95</f>
         <v>1</v>
       </c>
-      <c r="D84" s="177">
+      <c r="D84" s="176">
         <f>Statement!N95</f>
         <v>-0.88003700657894735</v>
       </c>
-      <c r="E84" s="177">
+      <c r="E84" s="176">
         <f>Statement!O95</f>
         <v>-0.96015424164524421</v>
       </c>
-      <c r="F84" s="177">
+      <c r="F84" s="176">
         <f>Statement!P95</f>
         <v>-126.56989247311827</v>
       </c>
-      <c r="G84" s="177">
+      <c r="G84" s="176">
         <f>Statement!Q95</f>
         <v>0.81041274190786095</v>
       </c>
-      <c r="I84" s="199"/>
+      <c r="I84" s="198"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="C85" s="177">
+      <c r="C85" s="176">
         <f>Statement!M97</f>
         <v>1</v>
       </c>
-      <c r="D85" s="177">
+      <c r="D85" s="176">
         <f>Statement!N97</f>
         <v>-0.59663780954298373</v>
       </c>
-      <c r="E85" s="177">
+      <c r="E85" s="176">
         <f>Statement!O97</f>
         <v>-0.78924382330920884</v>
       </c>
-      <c r="F85" s="177">
+      <c r="F85" s="176">
         <f>Statement!P97</f>
         <v>-12.104795737122558</v>
       </c>
-      <c r="G85" s="177">
+      <c r="G85" s="176">
         <f>Statement!Q97</f>
         <v>0.98576455534229046</v>
       </c>
-      <c r="I85" s="199"/>
+      <c r="I85" s="198"/>
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
@@ -34078,134 +34123,134 @@
       <c r="I88" s="14"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="218" t="s">
+      <c r="B89" s="217" t="s">
         <v>361</v>
       </c>
-      <c r="C89" s="177">
+      <c r="C89" s="176">
         <f>Statement!M201</f>
         <v>1</v>
       </c>
-      <c r="D89" s="177">
+      <c r="D89" s="176">
         <f>Statement!N201</f>
         <v>-0.22657676298045326</v>
       </c>
-      <c r="E89" s="177">
+      <c r="E89" s="176">
         <f>Statement!O201</f>
         <v>-7.9155257608661447E-2</v>
       </c>
-      <c r="F89" s="177">
+      <c r="F89" s="176">
         <f>Statement!P201</f>
         <v>0.139722469068289</v>
       </c>
-      <c r="G89" s="177">
+      <c r="G89" s="176">
         <f>Statement!Q201</f>
         <v>-3.3527259641336293E-2</v>
       </c>
-      <c r="I89" s="199"/>
+      <c r="I89" s="198"/>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="218" t="s">
+      <c r="B90" s="217" t="s">
         <v>362</v>
       </c>
-      <c r="C90" s="177">
+      <c r="C90" s="176">
         <f>Statement!M202</f>
         <v>1</v>
       </c>
-      <c r="D90" s="177">
+      <c r="D90" s="176">
         <f>Statement!N202</f>
         <v>-8.4923946253162061E-2</v>
       </c>
-      <c r="E90" s="177">
+      <c r="E90" s="176">
         <f>Statement!O202</f>
         <v>-0.23547784878293962</v>
       </c>
-      <c r="F90" s="177">
+      <c r="F90" s="176">
         <f>Statement!P202</f>
         <v>-0.242779995304062</v>
       </c>
-      <c r="G90" s="177">
+      <c r="G90" s="176">
         <f>Statement!Q202</f>
         <v>4.9240310077519382E-2</v>
       </c>
-      <c r="I90" s="199"/>
+      <c r="I90" s="198"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="C91" s="177">
+      <c r="C91" s="176">
         <f>Statement!M203</f>
         <v>1</v>
       </c>
-      <c r="D91" s="177">
+      <c r="D91" s="176">
         <f>Statement!N203</f>
         <v>-0.16628914988814317</v>
       </c>
-      <c r="E91" s="177">
+      <c r="E91" s="176">
         <f>Statement!O203</f>
         <v>-0.1521793818236705</v>
       </c>
-      <c r="F91" s="177">
+      <c r="F91" s="176">
         <f>Statement!P203</f>
         <v>-2.1403279726227919E-2</v>
       </c>
-      <c r="G91" s="177">
+      <c r="G91" s="176">
         <f>Statement!Q203</f>
         <v>-6.5492915041135214E-3</v>
       </c>
-      <c r="I91" s="199"/>
+      <c r="I91" s="198"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="C92" s="177">
+      <c r="C92" s="176">
         <f>Statement!M204</f>
         <v>1</v>
       </c>
-      <c r="D92" s="177">
+      <c r="D92" s="176">
         <f>Statement!N204</f>
         <v>0.35158501440922191</v>
       </c>
-      <c r="E92" s="177">
+      <c r="E92" s="176">
         <f>Statement!O204</f>
         <v>1.0298507462686568</v>
       </c>
-      <c r="F92" s="177">
+      <c r="F92" s="176">
         <f>Statement!P204</f>
         <v>17.190126050420169</v>
       </c>
-      <c r="G92" s="177">
+      <c r="G92" s="176">
         <f>Statement!Q204</f>
         <v>2.9393081942599757E-2</v>
       </c>
-      <c r="I92" s="199"/>
+      <c r="I92" s="198"/>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B93" s="20" t="s">
         <v>365</v>
       </c>
-      <c r="C93" s="177">
+      <c r="C93" s="176">
         <f>Statement!M205</f>
         <v>1</v>
       </c>
-      <c r="D93" s="177">
+      <c r="D93" s="176">
         <f>Statement!N205</f>
         <v>-0.58669833729216148</v>
       </c>
-      <c r="E93" s="177">
+      <c r="E93" s="176">
         <f>Statement!O205</f>
         <v>-7.9445571331981074E-2</v>
       </c>
-      <c r="F93" s="177">
+      <c r="F93" s="176">
         <f>Statement!P205</f>
         <v>0.32243848696290855</v>
       </c>
-      <c r="G93" s="177">
+      <c r="G93" s="176">
         <f>Statement!Q205</f>
         <v>-1.0552624271035824E-2</v>
       </c>
-      <c r="I93" s="199"/>
+      <c r="I93" s="198"/>
     </row>
     <row r="95" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B95" s="14" t="s">
@@ -34222,27 +34267,27 @@
       <c r="B96" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="C96" s="177">
+      <c r="C96" s="176">
         <f>Statement!M209</f>
         <v>-1</v>
       </c>
-      <c r="D96" s="177">
+      <c r="D96" s="176">
         <f>Statement!N209</f>
         <v>6.2544294826364283E-2</v>
       </c>
-      <c r="E96" s="177">
+      <c r="E96" s="176">
         <f>Statement!O209</f>
         <v>-0.48507587126896784</v>
       </c>
-      <c r="F96" s="177">
+      <c r="F96" s="176">
         <f>Statement!P209</f>
         <v>-0.48218911917098445</v>
       </c>
-      <c r="G96" s="177">
+      <c r="G96" s="176">
         <f>Statement!Q209</f>
         <v>-1</v>
       </c>
-      <c r="I96" s="199"/>
+      <c r="I96" s="198"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34267,14 +34312,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="233" t="s">
         <v>316</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="F3" s="234" t="s">
+      <c r="D3" s="234"/>
+      <c r="F3" s="235" t="s">
         <v>317</v>
       </c>
-      <c r="G3" s="233"/>
+      <c r="G3" s="234"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -34282,15 +34327,15 @@
         <f>Statement!Z2</f>
         <v>27.12.2025</v>
       </c>
-      <c r="D4" s="205" t="str">
+      <c r="D4" s="204" t="str">
         <f>Statement!AA2</f>
         <v>28.03.2026</v>
       </c>
-      <c r="F4" s="206" t="str">
+      <c r="F4" s="205" t="str">
         <f>Statement!W2</f>
         <v>29.03.2025</v>
       </c>
-      <c r="G4" s="205" t="str">
+      <c r="G4" s="204" t="str">
         <f>Statement!AA2</f>
         <v>28.03.2026</v>
       </c>
@@ -34303,336 +34348,336 @@
         <f>Statement!Z3</f>
         <v>Q4 2025</v>
       </c>
-      <c r="D5" s="205" t="str">
+      <c r="D5" s="204" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2026</v>
       </c>
-      <c r="F5" s="206" t="str">
+      <c r="F5" s="205" t="str">
         <f>Statement!W3</f>
         <v>Q1 2025</v>
       </c>
-      <c r="G5" s="205" t="str">
+      <c r="G5" s="204" t="str">
         <f>Statement!AA3</f>
         <v>Q1 2026</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="207" t="s">
+      <c r="B6" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="201">
+      <c r="C6" s="200">
         <f>Statement!Z5</f>
         <v>13674</v>
       </c>
-      <c r="D6" s="200">
+      <c r="D6" s="199">
         <f>Statement!AA5</f>
         <v>13577</v>
       </c>
-      <c r="F6" s="201">
+      <c r="F6" s="200">
         <f>Statement!W5</f>
         <v>12667</v>
       </c>
-      <c r="G6" s="200">
+      <c r="G6" s="199">
         <f>Statement!AA5</f>
         <v>13577</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="208" t="s">
+      <c r="B7" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C7" s="235">
+      <c r="C7" s="231">
         <f>Statement!AA88</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="236"/>
-      <c r="F7" s="235">
+      <c r="D7" s="232"/>
+      <c r="F7" s="231">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="236"/>
+      <c r="G7" s="232"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="209" t="s">
+      <c r="B8" s="208" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="202">
+      <c r="C8" s="201">
         <f>Statement!Z6</f>
         <v>8731</v>
       </c>
-      <c r="D8" s="200">
+      <c r="D8" s="199">
         <f>Statement!AA6</f>
         <v>8230</v>
       </c>
-      <c r="F8" s="202">
+      <c r="F8" s="201">
         <f>Statement!W6</f>
         <v>7995</v>
       </c>
-      <c r="G8" s="200">
+      <c r="G8" s="199">
         <f>Statement!AA6</f>
         <v>8230</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="208" t="s">
+      <c r="B9" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="235">
+      <c r="C9" s="231">
         <f>Statement!AA89</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="F9" s="235">
+      <c r="D9" s="232"/>
+      <c r="F9" s="231">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="236"/>
+      <c r="G9" s="232"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="209" t="s">
+      <c r="B10" s="208" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="202">
+      <c r="C10" s="201">
         <f>Statement!Z7</f>
         <v>4943</v>
       </c>
-      <c r="D10" s="200">
+      <c r="D10" s="199">
         <f>Statement!AA7</f>
         <v>5347</v>
       </c>
-      <c r="F10" s="202">
+      <c r="F10" s="201">
         <f>Statement!W7</f>
         <v>4672</v>
       </c>
-      <c r="G10" s="200">
+      <c r="G10" s="199">
         <f>Statement!AA7</f>
         <v>5347</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C11" s="235">
+      <c r="C11" s="231">
         <f>Statement!AA90</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="236"/>
-      <c r="F11" s="235">
+      <c r="D11" s="232"/>
+      <c r="F11" s="231">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="236"/>
+      <c r="G11" s="232"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="209" t="s">
+      <c r="B12" s="208" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="202">
+      <c r="C12" s="201">
         <f>Statement!Z11</f>
         <v>4363</v>
       </c>
-      <c r="D12" s="200">
+      <c r="D12" s="199">
         <f>Statement!AA11</f>
         <v>8483</v>
       </c>
-      <c r="F12" s="202">
+      <c r="F12" s="201">
         <f>Statement!W11</f>
         <v>4973</v>
       </c>
-      <c r="G12" s="200">
+      <c r="G12" s="199">
         <f>Statement!AA11</f>
         <v>8483</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="208" t="s">
+      <c r="B13" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C13" s="235">
+      <c r="C13" s="231">
         <f>Statement!AA94</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="236"/>
-      <c r="F13" s="235">
+      <c r="D13" s="232"/>
+      <c r="F13" s="231">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="236"/>
+      <c r="G13" s="232"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="209" t="s">
+      <c r="B14" s="208" t="s">
         <v>319</v>
       </c>
-      <c r="C14" s="202">
+      <c r="C14" s="201">
         <f>Statement!Z12</f>
         <v>580</v>
       </c>
-      <c r="D14" s="200">
+      <c r="D14" s="199">
         <f>Statement!AA12</f>
         <v>-3136</v>
       </c>
-      <c r="F14" s="202">
+      <c r="F14" s="201">
         <f>Statement!W12</f>
         <v>-301</v>
       </c>
-      <c r="G14" s="200">
+      <c r="G14" s="199">
         <f>Statement!AA12</f>
         <v>-3136</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="208" t="s">
+      <c r="B15" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C15" s="235">
+      <c r="C15" s="231">
         <f>Statement!AA95</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="236"/>
-      <c r="F15" s="235">
+      <c r="D15" s="232"/>
+      <c r="F15" s="231">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="236"/>
+      <c r="G15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="209" t="s">
+      <c r="B16" s="208" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="202">
+      <c r="C16" s="201">
         <f>Statement!Z18</f>
         <v>-591</v>
       </c>
-      <c r="D16" s="200">
+      <c r="D16" s="199">
         <f>Statement!AA18</f>
         <v>-3728</v>
       </c>
-      <c r="F16" s="202">
+      <c r="F16" s="201">
         <f>Statement!W18</f>
         <v>-821</v>
       </c>
-      <c r="G16" s="200">
+      <c r="G16" s="199">
         <f>Statement!AA18</f>
         <v>-3728</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="208" t="s">
+      <c r="B17" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C17" s="235">
+      <c r="C17" s="231">
         <f>Statement!AA97</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="236"/>
-      <c r="F17" s="235">
+      <c r="D17" s="232"/>
+      <c r="F17" s="231">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="236"/>
+      <c r="G17" s="232"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="209" t="s">
+      <c r="B18" s="208" t="s">
         <v>320</v>
       </c>
-      <c r="C18" s="202">
+      <c r="C18" s="201">
         <f>Statement!Z22</f>
         <v>4856</v>
       </c>
-      <c r="D18" s="200">
+      <c r="D18" s="199">
         <f>Statement!AA22</f>
         <v>5083</v>
       </c>
-      <c r="F18" s="202">
+      <c r="F18" s="201">
         <f>Statement!W22</f>
         <v>4343</v>
       </c>
-      <c r="G18" s="200">
+      <c r="G18" s="199">
         <f>Statement!AA22</f>
         <v>5083</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="208" t="s">
+      <c r="B19" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C19" s="235">
+      <c r="C19" s="231">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="236"/>
-      <c r="F19" s="235">
+      <c r="D19" s="232"/>
+      <c r="F19" s="231">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="236"/>
+      <c r="G19" s="232"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="209" t="s">
+      <c r="B20" s="208" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="203">
+      <c r="C20" s="202">
         <f>Statement!Z26</f>
         <v>-0.12</v>
       </c>
-      <c r="D20" s="204">
+      <c r="D20" s="203">
         <f>Statement!AA26</f>
         <v>-0.73</v>
       </c>
-      <c r="F20" s="203">
+      <c r="F20" s="202">
         <f>Statement!W26</f>
         <v>-0.19</v>
       </c>
-      <c r="G20" s="204">
+      <c r="G20" s="203">
         <f>Statement!AA26</f>
         <v>-0.73</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="208" t="s">
+      <c r="B21" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C21" s="235">
+      <c r="C21" s="231">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="236"/>
-      <c r="F21" s="235">
+      <c r="D21" s="232"/>
+      <c r="F21" s="231">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="236"/>
+      <c r="G21" s="232"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -34642,15 +34687,15 @@
         <f>C5</f>
         <v>Q4 2025</v>
       </c>
-      <c r="D23" s="205" t="str">
+      <c r="D23" s="204" t="str">
         <f>D5</f>
         <v>Q1 2026</v>
       </c>
-      <c r="F23" s="206" t="str">
+      <c r="F23" s="205" t="str">
         <f>F5</f>
         <v>Q1 2025</v>
       </c>
-      <c r="G23" s="205" t="str">
+      <c r="G23" s="204" t="str">
         <f>G5</f>
         <v>Q1 2026</v>
       </c>
@@ -34659,214 +34704,226 @@
       <c r="B24" s="20" t="s">
         <v>361</v>
       </c>
-      <c r="C24" s="202">
+      <c r="C24" s="201">
         <f>Statement!Z105</f>
         <v>8193</v>
       </c>
-      <c r="D24" s="200">
+      <c r="D24" s="199">
         <f>Statement!AA105</f>
         <v>7727</v>
       </c>
-      <c r="F24" s="202">
+      <c r="F24" s="201">
         <f>Statement!W105</f>
         <v>7629</v>
       </c>
-      <c r="G24" s="200">
+      <c r="G24" s="199">
         <f>Statement!AA105</f>
         <v>7727</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="208" t="s">
+      <c r="B25" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C25" s="235">
+      <c r="C25" s="231">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="236"/>
-      <c r="F25" s="235">
+      <c r="D25" s="232"/>
+      <c r="F25" s="231">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="236"/>
+      <c r="G25" s="232"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
         <v>362</v>
       </c>
-      <c r="C26" s="202">
+      <c r="C26" s="201">
         <f>Statement!Z106</f>
         <v>4737</v>
       </c>
-      <c r="D26" s="200">
+      <c r="D26" s="199">
         <f>Statement!AA106</f>
         <v>5052</v>
       </c>
-      <c r="F26" s="202">
+      <c r="F26" s="201">
         <f>Statement!W106</f>
         <v>4126</v>
       </c>
-      <c r="G26" s="200">
+      <c r="G26" s="199">
         <f>Statement!AA106</f>
         <v>5052</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="208" t="s">
+      <c r="B27" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C27" s="235">
+      <c r="C27" s="231">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="236"/>
-      <c r="F27" s="235">
+      <c r="D27" s="232"/>
+      <c r="F27" s="231">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="236"/>
+      <c r="G27" s="232"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="C28" s="202">
+      <c r="C28" s="201">
         <f>Statement!Z107</f>
         <v>12930</v>
       </c>
-      <c r="D28" s="200">
+      <c r="D28" s="199">
         <f>Statement!AA107</f>
         <v>12779</v>
       </c>
-      <c r="F28" s="202">
+      <c r="F28" s="201">
         <f>Statement!W107</f>
         <v>11755</v>
       </c>
-      <c r="G28" s="200">
+      <c r="G28" s="199">
         <f>Statement!AA107</f>
         <v>12779</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="208" t="s">
+      <c r="B29" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C29" s="235">
+      <c r="C29" s="231">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="236"/>
-      <c r="F29" s="235">
+      <c r="D29" s="232"/>
+      <c r="F29" s="231">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="236"/>
+      <c r="G29" s="232"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="C30" s="202">
+      <c r="C30" s="201">
         <f>Statement!Z108</f>
         <v>4507</v>
       </c>
-      <c r="D30" s="202">
+      <c r="D30" s="201">
         <f>Statement!AA108</f>
         <v>5421</v>
       </c>
-      <c r="F30" s="202">
+      <c r="F30" s="201">
         <f>Statement!W108</f>
         <v>4667</v>
       </c>
-      <c r="G30" s="200">
+      <c r="G30" s="199">
         <f>Statement!AA108</f>
         <v>5421</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="208" t="s">
+      <c r="B31" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C31" s="235">
+      <c r="C31" s="231">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="236"/>
-      <c r="F31" s="235">
+      <c r="D31" s="232"/>
+      <c r="F31" s="231">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="236"/>
+      <c r="G31" s="232"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
         <v>365</v>
       </c>
-      <c r="C32" s="202">
+      <c r="C32" s="201">
         <f>Statement!Z109</f>
         <v>574</v>
       </c>
-      <c r="D32" s="200">
+      <c r="D32" s="199">
         <f>Statement!AA109</f>
         <v>628</v>
       </c>
-      <c r="F32" s="202">
+      <c r="F32" s="201">
         <f>Statement!W109</f>
         <v>943</v>
       </c>
-      <c r="G32" s="200">
+      <c r="G32" s="199">
         <f>Statement!AA109</f>
         <v>628</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B33" s="208" t="s">
+      <c r="B33" s="207" t="s">
         <v>318</v>
       </c>
-      <c r="C33" s="235">
+      <c r="C33" s="231">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="236"/>
-      <c r="F33" s="235">
+      <c r="D33" s="232"/>
+      <c r="F33" s="231">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="236"/>
+      <c r="G33" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -34883,18 +34940,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -35228,43 +35273,43 @@
       <c r="B62" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="224">
+      <c r="C62" s="223">
         <f>Statement!H100</f>
         <v>0</v>
       </c>
-      <c r="D62" s="224">
+      <c r="D62" s="223">
         <f>Statement!I100</f>
         <v>0</v>
       </c>
-      <c r="E62" s="224">
+      <c r="E62" s="223">
         <f>Statement!J100</f>
         <v>0</v>
       </c>
-      <c r="F62" s="224">
+      <c r="F62" s="223">
         <f>Statement!K100</f>
         <v>0</v>
       </c>
-      <c r="G62" s="224">
+      <c r="G62" s="223">
         <f>Statement!L100</f>
         <v>0</v>
       </c>
-      <c r="H62" s="224">
+      <c r="H62" s="223">
         <f>Statement!M100</f>
         <v>0.5544518121077141</v>
       </c>
-      <c r="I62" s="224">
+      <c r="I62" s="223">
         <f>Statement!N100</f>
         <v>0.42607923367272499</v>
       </c>
-      <c r="J62" s="224">
+      <c r="J62" s="223">
         <f>Statement!O100</f>
         <v>0.40036512502766097</v>
       </c>
-      <c r="K62" s="224">
+      <c r="K62" s="223">
         <f>Statement!P100</f>
         <v>0.32664168283083184</v>
       </c>
-      <c r="L62" s="224">
+      <c r="L62" s="223">
         <f>Statement!Q100</f>
         <v>0.34766238434904356</v>
       </c>
@@ -35273,43 +35318,43 @@
       <c r="B63" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="224">
+      <c r="C63" s="223">
         <f>Statement!H101</f>
         <v>0</v>
       </c>
-      <c r="D63" s="224">
+      <c r="D63" s="223">
         <f>Statement!I101</f>
         <v>0</v>
       </c>
-      <c r="E63" s="224">
+      <c r="E63" s="223">
         <f>Statement!J101</f>
         <v>0</v>
       </c>
-      <c r="F63" s="224">
+      <c r="F63" s="223">
         <f>Statement!K101</f>
         <v>0</v>
       </c>
-      <c r="G63" s="224">
+      <c r="G63" s="223">
         <f>Statement!L101</f>
         <v>0</v>
       </c>
-      <c r="H63" s="224">
+      <c r="H63" s="223">
         <f>Statement!M101</f>
         <v>0.24620368495646891</v>
       </c>
-      <c r="I63" s="224">
+      <c r="I63" s="223">
         <f>Statement!N101</f>
         <v>3.7015891140926828E-2</v>
       </c>
-      <c r="J63" s="224">
+      <c r="J63" s="223">
         <f>Statement!O101</f>
         <v>1.714981190528878E-3</v>
       </c>
-      <c r="K63" s="224">
+      <c r="K63" s="223">
         <f>Statement!P101</f>
         <v>-0.21992052880360069</v>
       </c>
-      <c r="L63" s="224">
+      <c r="L63" s="223">
         <f>Statement!Q101</f>
         <v>-4.1889769738709247E-2</v>
       </c>
@@ -35318,43 +35363,43 @@
       <c r="B64" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="224">
+      <c r="C64" s="223">
         <f>Statement!H102</f>
         <v>0</v>
       </c>
-      <c r="D64" s="224">
+      <c r="D64" s="223">
         <f>Statement!I102</f>
         <v>0</v>
       </c>
-      <c r="E64" s="224">
+      <c r="E64" s="223">
         <f>Statement!J102</f>
         <v>0</v>
       </c>
-      <c r="F64" s="224">
+      <c r="F64" s="223">
         <f>Statement!K102</f>
         <v>0</v>
       </c>
-      <c r="G64" s="224">
+      <c r="G64" s="223">
         <f>Statement!L102</f>
         <v>0</v>
       </c>
-      <c r="H64" s="224">
+      <c r="H64" s="223">
         <f>Statement!M102</f>
         <v>0.25141729094958493</v>
       </c>
-      <c r="I64" s="224">
+      <c r="I64" s="223">
         <f>Statement!N102</f>
         <v>0.12714498683667966</v>
       </c>
-      <c r="J64" s="224">
+      <c r="J64" s="223">
         <f>Statement!O102</f>
         <v>3.088810208748248E-2</v>
       </c>
-      <c r="K64" s="224">
+      <c r="K64" s="223">
         <f>Statement!P102</f>
         <v>-0.3621965688028474</v>
       </c>
-      <c r="L64" s="224">
+      <c r="L64" s="223">
         <f>Statement!Q102</f>
         <v>4.9193044860272833E-4</v>
       </c>
@@ -35498,43 +35543,43 @@
       <c r="B68" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C68" s="225">
+      <c r="C68" s="224">
         <f>Statement!H136</f>
         <v>0</v>
       </c>
-      <c r="D68" s="225">
+      <c r="D68" s="224">
         <f>Statement!I136</f>
         <v>0</v>
       </c>
-      <c r="E68" s="225">
+      <c r="E68" s="224">
         <f>Statement!J136</f>
         <v>0</v>
       </c>
-      <c r="F68" s="225">
+      <c r="F68" s="224">
         <f>Statement!K136</f>
         <v>0</v>
       </c>
-      <c r="G68" s="225">
+      <c r="G68" s="224">
         <f>Statement!L136</f>
         <v>0</v>
       </c>
-      <c r="H68" s="225">
+      <c r="H68" s="224">
         <f>Statement!M136</f>
         <v>0.11797679417597948</v>
       </c>
-      <c r="I68" s="225">
+      <c r="I68" s="224">
         <f>Statement!N136</f>
         <v>4.4024535565037361E-2</v>
       </c>
-      <c r="J68" s="225">
+      <c r="J68" s="224">
         <f>Statement!O136</f>
         <v>8.7434489382581995E-3</v>
       </c>
-      <c r="K68" s="225">
+      <c r="K68" s="224">
         <f>Statement!P136</f>
         <v>-9.7885334758378503E-2</v>
       </c>
-      <c r="L68" s="225">
+      <c r="L68" s="224">
         <f>Statement!Q136</f>
         <v>1.2297272370393844E-4</v>
       </c>
@@ -35543,43 +35588,43 @@
       <c r="B69" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C69" s="225">
+      <c r="C69" s="224">
         <f>Statement!H138</f>
         <v>0</v>
       </c>
-      <c r="D69" s="225">
+      <c r="D69" s="224">
         <f>Statement!I138</f>
         <v>0</v>
       </c>
-      <c r="E69" s="225">
+      <c r="E69" s="224">
         <f>Statement!J138</f>
         <v>0</v>
       </c>
-      <c r="F69" s="225">
+      <c r="F69" s="224">
         <f>Statement!K138</f>
         <v>0</v>
       </c>
-      <c r="G69" s="225">
+      <c r="G69" s="224">
         <f>Statement!L138</f>
         <v>0</v>
       </c>
-      <c r="H69" s="225">
+      <c r="H69" s="224">
         <f>Statement!M138</f>
         <v>0.20827960709081569</v>
       </c>
-      <c r="I69" s="225">
+      <c r="I69" s="224">
         <f>Statement!N138</f>
         <v>7.904518698914445E-2</v>
       </c>
-      <c r="J69" s="225">
+      <c r="J69" s="224">
         <f>Statement!O138</f>
         <v>1.5863244625438012E-2</v>
       </c>
-      <c r="K69" s="225">
+      <c r="K69" s="224">
         <f>Statement!P138</f>
         <v>-0.19374433363553945</v>
       </c>
-      <c r="L69" s="225">
+      <c r="L69" s="224">
         <f>Statement!Q138</f>
         <v>2.2750938476212145E-4</v>
       </c>
@@ -35588,43 +35633,43 @@
       <c r="B70" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C70" s="225">
+      <c r="C70" s="224">
         <f>Statement!H158</f>
         <v>0</v>
       </c>
-      <c r="D70" s="225">
+      <c r="D70" s="224">
         <f>Statement!I158</f>
         <v>0</v>
       </c>
-      <c r="E70" s="225">
+      <c r="E70" s="224">
         <f>Statement!J158</f>
         <v>0</v>
       </c>
-      <c r="F70" s="225">
+      <c r="F70" s="224">
         <f>Statement!K158</f>
         <v>0</v>
       </c>
-      <c r="G70" s="225">
+      <c r="G70" s="224">
         <f>Statement!L158</f>
         <v>0</v>
       </c>
-      <c r="H70" s="225">
+      <c r="H70" s="224">
         <f>Statement!M158</f>
         <v>0.16950089956234582</v>
       </c>
-      <c r="I70" s="225">
+      <c r="I70" s="224">
         <f>Statement!N158</f>
         <v>1.9948888452038051E-2</v>
       </c>
-      <c r="J70" s="225">
+      <c r="J70" s="224">
         <f>Statement!O158</f>
         <v>6.9301102111075507E-4</v>
       </c>
-      <c r="K70" s="225">
+      <c r="K70" s="224">
         <f>Statement!P158</f>
         <v>-8.7817056571991486E-2</v>
       </c>
-      <c r="L70" s="225">
+      <c r="L70" s="224">
         <f>Statement!Q158</f>
         <v>-1.6335987131905347E-2</v>
       </c>
@@ -35830,35 +35875,35 @@
       <c r="B60" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C60" s="224">
+      <c r="C60" s="223">
         <f>Statement!T100</f>
         <v>0.35432089145172602</v>
       </c>
-      <c r="D60" s="224">
+      <c r="D60" s="223">
         <f>Statement!U100</f>
         <v>0.15033122553447756</v>
       </c>
-      <c r="E60" s="224">
+      <c r="E60" s="223">
         <f>Statement!V100</f>
         <v>0.39158485273492288</v>
       </c>
-      <c r="F60" s="224">
+      <c r="F60" s="223">
         <f>Statement!W100</f>
         <v>0.36883239914739085</v>
       </c>
-      <c r="G60" s="224">
+      <c r="G60" s="223">
         <f>Statement!X100</f>
         <v>0.27544910179640719</v>
       </c>
-      <c r="H60" s="224">
+      <c r="H60" s="223">
         <f>Statement!Y100</f>
         <v>0.38218706511389439</v>
       </c>
-      <c r="I60" s="224">
+      <c r="I60" s="223">
         <f>Statement!Z100</f>
         <v>0.36148895714494661</v>
       </c>
-      <c r="J60" s="224">
+      <c r="J60" s="223">
         <f>Statement!AA100</f>
         <v>0.39382779700964865</v>
       </c>
@@ -35867,35 +35912,35 @@
       <c r="B61" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C61" s="224">
+      <c r="C61" s="223">
         <f>Statement!T101</f>
         <v>-0.15304293618016052</v>
       </c>
-      <c r="D61" s="224">
+      <c r="D61" s="223">
         <f>Statement!U101</f>
         <v>-0.68179765130984649</v>
       </c>
-      <c r="E61" s="224">
+      <c r="E61" s="223">
         <f>Statement!V101</f>
         <v>2.8892005610098175E-2</v>
       </c>
-      <c r="F61" s="224">
+      <c r="F61" s="223">
         <f>Statement!W101</f>
         <v>-2.3762532564932503E-2</v>
       </c>
-      <c r="G61" s="224">
+      <c r="G61" s="223">
         <f>Statement!X101</f>
         <v>-0.246986546387744</v>
       </c>
-      <c r="H61" s="224">
+      <c r="H61" s="223">
         <f>Statement!Y101</f>
         <v>5.0025635391489048E-2</v>
       </c>
-      <c r="I61" s="224">
+      <c r="I61" s="223">
         <f>Statement!Z101</f>
         <v>4.2416264443469361E-2</v>
       </c>
-      <c r="J61" s="224">
+      <c r="J61" s="223">
         <f>Statement!AA101</f>
         <v>-0.23097886130956766</v>
       </c>
@@ -35904,35 +35949,35 @@
       <c r="B62" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C62" s="224">
+      <c r="C62" s="223">
         <f>Statement!T102</f>
         <v>-0.12888646458349567</v>
       </c>
-      <c r="D62" s="224">
+      <c r="D62" s="223">
         <f>Statement!U102</f>
         <v>-1.278906955736224</v>
       </c>
-      <c r="E62" s="224">
+      <c r="E62" s="223">
         <f>Statement!V102</f>
         <v>-1.0729312762973352E-2</v>
       </c>
-      <c r="F62" s="224">
+      <c r="F62" s="223">
         <f>Statement!W102</f>
         <v>-7.0024473040183152E-2</v>
       </c>
-      <c r="G62" s="224">
+      <c r="G62" s="223">
         <f>Statement!X102</f>
         <v>-0.23516603157321719</v>
       </c>
-      <c r="H62" s="224">
+      <c r="H62" s="223">
         <f>Statement!Y102</f>
         <v>0.31275177616641031</v>
       </c>
-      <c r="I62" s="224">
+      <c r="I62" s="223">
         <f>Statement!Z102</f>
         <v>-2.4352786309784994E-2</v>
       </c>
-      <c r="J62" s="224">
+      <c r="J62" s="223">
         <f>Statement!AA102</f>
         <v>-0.31531266111806733</v>
       </c>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2274D35-42D3-4D4E-851F-07F5EDF29207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2199889-51F8-BF4B-A517-47B3D778F183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,19 +161,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="402">
   <si>
     <t>Ticker</t>
   </si>
@@ -623,9 +653,6 @@
   </si>
   <si>
     <t>Change in NWC</t>
-  </si>
-  <si>
-    <t>UFCF</t>
   </si>
   <si>
     <t>NOPAT</t>
@@ -11709,7 +11736,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -11728,11 +11755,9 @@
     <v>Powered by Refinitiv</v>
     <v>132.75</v>
     <v>18.965</v>
-    <v>2.2294999999999998</v>
-    <v>-0.88</v>
-    <v>-8.1539999999999998E-3</v>
-    <v>-1.17</v>
-    <v>-1.093E-2</v>
+    <v>2.2189000000000001</v>
+    <v>5.875</v>
+    <v>5.4885999999999997E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -11740,35 +11765,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>111.5</v>
+    <v>119.44</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46183.915457499999</v>
+    <v>46184.658226770312</v>
     <v>0</v>
-    <v>104.92</v>
-    <v>537983040000</v>
+    <v>111.6</v>
+    <v>567510790000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>106.03</v>
+    <v>113.85</v>
     <v>0</v>
-    <v>107.92</v>
     <v>107.04</v>
-    <v>105.87</v>
+    <v>112.91500000000001</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>121969629</v>
-    <v>137320931</v>
+    <v>89416502</v>
+    <v>134287791</v>
     <v>1989</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -11782,28 +11821,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.24</v>
-    <v>-5.2719999999999998E-3</v>
+    <v>0.14000000000000001</v>
+    <v>3.0919999999999997E-3</v>
     <v>US</v>
-    <v>45.56</v>
+    <v>45.6</v>
     <v>Index</v>
-    <v>3</v>
-    <v>45.2</v>
+    <v>6</v>
+    <v>45.13</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.46</v>
-    <v>45.52</v>
+    <v>45.34</v>
     <v>45.28</v>
+    <v>45.42</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -11825,8 +11864,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -11847,7 +11884,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -11857,6 +11893,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -11892,7 +11933,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -11903,16 +11944,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12006,19 +12044,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -12090,9 +12122,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -12100,9 +12129,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -12595,11 +12621,11 @@
       </c>
       <c r="C2" s="232"/>
       <c r="E2" s="231" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F2" s="232"/>
       <c r="H2" s="231" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I2" s="232"/>
     </row>
@@ -12612,11 +12638,11 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="186" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="188">
         <f ca="1">Statement!AC153</f>
-        <v>537983.04</v>
+        <v>567510.79</v>
       </c>
       <c r="H3" s="186" t="str">
         <f>'AVG target price'!B5</f>
@@ -12624,7 +12650,7 @@
       </c>
       <c r="I3" s="212">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-7.1089558803142063</v>
+        <v>-7.1061455419777575</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -12636,11 +12662,11 @@
         <v>INTC</v>
       </c>
       <c r="E4" s="187" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F4" s="189">
         <f ca="1">Statement!AC154</f>
-        <v>555339.04</v>
+        <v>584866.79</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>'AVG target price'!B6</f>
@@ -12648,7 +12674,7 @@
       </c>
       <c r="I4" s="212">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.574068041485262</v>
+        <v>36.562604017004602</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -12657,10 +12683,10 @@
       </c>
       <c r="C5" s="209" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>107.04</v>
+        <v>112.91500000000001</v>
       </c>
       <c r="E5" s="186" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F5" s="190">
         <f>Statement!AC26</f>
@@ -12679,16 +12705,16 @@
       <c r="B6" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="209" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>105.87</v>
+      <c r="C6" s="209" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="186" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F6" s="191">
         <f ca="1">Statement!AC150</f>
-        <v>-172.64516129032259</v>
+        <v>-182.12096774193549</v>
       </c>
       <c r="H6" s="186" t="str">
         <f>'AVG target price'!B8</f>
@@ -12696,7 +12722,7 @@
       </c>
       <c r="I6" s="212">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-11.391030504289473</v>
+        <v>-11.387513566081854</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -12705,14 +12731,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.88</v>
+        <v>5.875</v>
       </c>
       <c r="E7" s="187" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F7" s="192">
         <f ca="1">Statement!AC151</f>
-        <v>9.3684638134032703</v>
+        <v>9.882661542324648</v>
       </c>
       <c r="H7" s="185" t="str">
         <f>'AVG target price'!B9</f>
@@ -12720,23 +12746,23 @@
       </c>
       <c r="I7" s="213">
         <f ca="1">'AVG target price'!C9</f>
-        <v>14.368330098983957</v>
+        <v>14.36704591199981</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.17</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="186" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F8" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>-1.0204782663780627E-2</v>
+        <v>-9.67382488005206E-3</v>
       </c>
       <c r="H8" s="185" t="str">
         <f>'AVG target price'!B11</f>
@@ -12744,7 +12770,7 @@
       </c>
       <c r="I8" s="214">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.86576672179574032</v>
+        <v>-0.87276229099765479</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12753,26 +12779,26 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-8.1539999999999998E-3</v>
+        <v>5.4885999999999997E-2</v>
       </c>
       <c r="E9" s="186" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9" s="193">
         <f ca="1">Statement!AC162</f>
-        <v>-5.7922272047832585E-3</v>
+        <v>-5.490855953593411E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.093E-2</v>
+      <c r="C10" s="72" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="186" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F10" s="193">
         <f ca="1">Statement!AC164</f>
@@ -12788,7 +12814,7 @@
         <v>132.75</v>
       </c>
       <c r="E11" s="187" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F11" s="194">
         <f ca="1">Statement!AC163</f>
@@ -12817,7 +12843,7 @@
       </c>
       <c r="C13" s="210" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2294999999999998</v>
+        <v>2.2189000000000001</v>
       </c>
       <c r="E13" s="186" t="s">
         <v>99</v>
@@ -12833,7 +12859,7 @@
       </c>
       <c r="C14" s="211" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>137320931</v>
+        <v>134287791</v>
       </c>
       <c r="E14" s="187" t="s">
         <v>100</v>
@@ -12845,16 +12871,16 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E15" s="186" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F15" s="193">
         <f ca="1">Statement!AC176</f>
-        <v>-6.9909267028194786E-3</v>
+        <v>-6.6271867711977768E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E16" s="187" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F16" s="192">
         <f>Statement!AC175</f>
@@ -12867,7 +12893,7 @@
       </c>
       <c r="C17" s="233"/>
       <c r="E17" s="185" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F17" s="195">
         <f>Statement!AC171</f>
@@ -12879,10 +12905,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E18" s="186" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F18" s="191">
         <f>Statement!AC144</f>
@@ -12898,7 +12924,7 @@
         <v>1000000</v>
       </c>
       <c r="E19" s="186" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F19" s="191">
         <f>Statement!AC146</f>
@@ -12910,10 +12936,10 @@
         <v>88</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E20" s="187" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F20" s="192">
         <f>Statement!AC147</f>
@@ -12925,7 +12951,7 @@
         <v>89</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I21" s="50"/>
     </row>
@@ -12934,7 +12960,7 @@
         <v>90</v>
       </c>
       <c r="C22" s="68" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
@@ -12943,7 +12969,7 @@
       </c>
       <c r="C25" s="233"/>
       <c r="E25" s="231" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F25" s="232"/>
     </row>
@@ -12954,32 +12980,32 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="186" t="e" vm="2">
+      <c r="E26" s="186" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="225" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.28</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B27" s="185" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C27" s="220">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="E27" s="187" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F27" s="226">
         <f ca="1">F26/1000</f>
-        <v>4.5280000000000001E-2</v>
+        <v>4.5420000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="185" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C28" s="220">
         <v>0</v>
@@ -12987,7 +13013,7 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="185" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C29" s="220">
         <v>0.12</v>
@@ -12995,7 +13021,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="230" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C33" s="230"/>
       <c r="D33" s="230"/>
@@ -13006,18 +13032,18 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
@@ -13031,7 +13057,7 @@
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="230" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C42" s="230"/>
       <c r="D42" s="230"/>
@@ -13042,10 +13068,10 @@
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D44" s="41" t="s">
         <v>86</v>
@@ -13054,18 +13080,18 @@
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="227" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="227" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
@@ -13366,11 +13392,11 @@
         <v>38452.690209023996</v>
       </c>
       <c r="N6" s="89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R6" s="1" t="str">
         <f>B6</f>
@@ -13465,11 +13491,11 @@
         <v>27957.189758960001</v>
       </c>
       <c r="N7" s="89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R7" s="1" t="str">
         <f t="shared" ref="R7:R10" si="3">B7</f>
@@ -13564,11 +13590,11 @@
         <v>66409.879967984001</v>
       </c>
       <c r="N8" s="89" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O8" s="5"/>
       <c r="Q8" s="89" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R8" s="1" t="str">
         <f t="shared" si="3"/>
@@ -13663,11 +13689,11 @@
         <v>6177.5999999999995</v>
       </c>
       <c r="N9" s="89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O9" s="5"/>
       <c r="Q9" s="89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R9" s="1" t="str">
         <f t="shared" si="3"/>
@@ -13759,11 +13785,11 @@
         <v>4678.557983820001</v>
       </c>
       <c r="N10" s="89" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O10" s="5"/>
       <c r="Q10" s="89" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R10" s="1" t="str">
         <f t="shared" si="3"/>
@@ -13854,11 +13880,11 @@
         <v>77266.037951804014</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O11" s="5"/>
       <c r="Q11" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R11" s="16" t="s">
         <v>116</v>
@@ -17981,7 +18007,7 @@
         <v>0.21</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -18189,7 +18215,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C25" s="239" t="s">
-        <v>157</v>
+        <v>264</v>
       </c>
       <c r="D25" s="239"/>
       <c r="E25" s="239"/>
@@ -18248,7 +18274,7 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C27" s="125">
         <f>C10*(1-C15)</f>
@@ -18293,7 +18319,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" s="93">
         <f>C27+C20-C21+C22</f>
@@ -18352,7 +18378,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -18518,7 +18544,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -18550,7 +18576,7 @@
     <row r="1" spans="1:3" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -18560,13 +18586,13 @@
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="230" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C4" s="230"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" s="136">
         <f>Statement!AC78</f>
@@ -18579,21 +18605,21 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>107.04</v>
+        <v>112.91500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>537983.04</v>
+        <v>567510.79</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C8" s="111">
         <f>Statement!AC108</f>
@@ -18602,11 +18628,11 @@
     </row>
     <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.5280000000000001E-2</v>
+        <v>4.5420000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18615,12 +18641,12 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.2294999999999998</v>
+        <v>2.2189000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C11" s="134">
         <f>[1]Sheet1!$C$12</f>
@@ -18638,7 +18664,7 @@
     </row>
     <row r="13" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C13" s="134">
         <f>Overview!C27</f>
@@ -18648,31 +18674,31 @@
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="230" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C15" s="230"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.7238277143377193E-2</v>
+        <v>7.3514984177650955E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92276172285662283</v>
+        <v>0.92648501582234899</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C18" s="46">
         <f>C13*(1-C12)</f>
@@ -18681,25 +18707,25 @@
     </row>
     <row r="19" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1456075</v>
+        <v>0.1452705</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13765601246378217</v>
+        <v>0.13772709071603914</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C21" s="135">
         <v>0</v>
@@ -18738,7 +18764,7 @@
     <row r="1" spans="1:28" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="81" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -18779,7 +18805,7 @@
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
       <c r="C5" s="239" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" s="239"/>
       <c r="E5" s="239"/>
@@ -18863,7 +18889,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C7" s="111">
         <f>'FCF &amp; Other'!C28</f>
@@ -18922,7 +18948,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B8" s="39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C8" s="125">
         <v>0</v>
@@ -18953,7 +18979,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23232.719559490757</v>
+        <v>-23218.692702193755</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -18972,7 +18998,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C9" s="137"/>
       <c r="D9" s="137"/>
@@ -18998,7 +19024,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C10" s="137"/>
       <c r="D10" s="137"/>
@@ -19007,29 +19033,29 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6492.5965333174763</v>
+        <v>-6492.1909154694331</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5055.2099279720178</v>
+        <v>-5054.5783103099566</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3562.2889152775961</v>
+        <v>-3561.6213067076965</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3261.1125180797726</v>
+        <v>-3260.2976567325713</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1406.2391085759746</v>
+        <v>-1405.799897227409</v>
       </c>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" s="137"/>
       <c r="D11" s="137"/>
@@ -19042,18 +19068,18 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12191.165251236367</v>
+        <v>-12179.999407533141</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B13" s="230" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C13" s="230"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C14" s="140">
         <v>0.02</v>
@@ -19061,49 +19087,49 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13765601246378217</v>
+        <v>0.13772709071603914</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="230" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C18" s="230"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19777.447003222835</v>
+        <v>-19774.488086447069</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12191.165251236367</v>
+        <v>-12179.999407533141</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-31968.6122544592</v>
+        <v>-31954.48749398021</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C22" s="87">
         <f>Statement!AC107</f>
@@ -19112,7 +19138,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C23" s="87">
         <f>Statement!AC108</f>
@@ -19121,11 +19147,11 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-35729.6122544592</v>
+        <v>-35715.48749398021</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19139,11 +19165,11 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="141" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>-7.1089558803142063</v>
+        <v>-7.1061455419777575</v>
       </c>
     </row>
   </sheetData>
@@ -19181,7 +19207,7 @@
     <row r="1" spans="1:14" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="81" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -19206,7 +19232,7 @@
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
       <c r="C4" s="239" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D4" s="239"/>
       <c r="E4" s="239"/>
@@ -19357,7 +19383,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C8" s="91">
         <f>'FCF &amp; Other'!C28</f>
@@ -19421,7 +19447,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C11" s="12">
         <f>C5</f>
@@ -19559,7 +19585,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C14" s="137"/>
       <c r="D14" s="94">
@@ -19611,7 +19637,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C16" s="239" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D16" s="239"/>
       <c r="E16" s="239"/>
@@ -19669,7 +19695,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C18" s="99">
         <f>Statement!M22</f>
@@ -19715,7 +19741,7 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C19" s="137"/>
       <c r="D19" s="144">
@@ -19756,7 +19782,7 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C21" s="239" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D21" s="239"/>
       <c r="E21" s="239"/>
@@ -19851,7 +19877,7 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C26" s="239" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D26" s="239"/>
       <c r="E26" s="239"/>
@@ -19909,7 +19935,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C28" s="149">
         <f>C23/(C6/C18)</f>
@@ -19940,7 +19966,7 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C29" s="143">
         <f>C23*C18</f>
@@ -19971,7 +19997,7 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C30" s="87">
         <f>Statement!M108</f>
@@ -20002,7 +20028,7 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C31" s="152">
         <f>Statement!M107</f>
@@ -20033,7 +20059,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C32" s="143">
         <f>C29+C30-C31</f>
@@ -20064,7 +20090,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C33" s="149">
         <f>C32/C7</f>
@@ -20095,7 +20121,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C34" s="149">
         <f>C32/C8</f>
@@ -20132,14 +20158,14 @@
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="230" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C37" s="230"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C38" s="63">
         <f>L7</f>
@@ -20148,16 +20174,16 @@
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13765601246378217</v>
+        <v>0.13772709071603914</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B40" s="39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C40" s="104">
         <v>35</v>
@@ -20165,7 +20191,7 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C41" s="24">
         <f>(C38*C40)</f>
@@ -20174,11 +20200,11 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>183821.26597650492</v>
+        <v>183763.64778946512</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -20192,22 +20218,22 @@
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B44" s="141" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C44" s="142">
         <f ca="1">C42/C43</f>
-        <v>36.574068041485262</v>
+        <v>36.562604017004602</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B46" s="230" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C46" s="230"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C47" s="63">
         <f>L6</f>
@@ -20216,7 +20242,7 @@
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C48" s="134">
         <f>Overview!C29</f>
@@ -20225,7 +20251,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" s="39" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C49" s="104">
         <v>5</v>
@@ -20233,7 +20259,7 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C50" s="24">
         <f>L18</f>
@@ -20242,7 +20268,7 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C51" s="24">
         <f>(C47*C49)/C50</f>
@@ -20251,7 +20277,7 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="141" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C52" s="142">
         <f>C51/(1+C48)^5</f>
@@ -20260,13 +20286,13 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="230" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C54" s="230"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C55" s="63">
         <f>L8</f>
@@ -20275,16 +20301,16 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C56" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13765601246378217</v>
+        <v>0.13772709071603914</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C57" s="104">
         <v>40</v>
@@ -20292,7 +20318,7 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C58" s="24">
         <f>L18</f>
@@ -20301,7 +20327,7 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C59" s="24">
         <f>(C55*C57)-G30+G31</f>
@@ -20310,11 +20336,11 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C56)^5-G30+G31</f>
-        <v>-57251.319314558888</v>
+        <v>-57233.643183127395</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -20328,11 +20354,11 @@
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" s="141" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C62" s="142">
         <f ca="1">C60/C61</f>
-        <v>-11.391030504289473</v>
+        <v>-11.387513566081854</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20400,7 @@
     <row r="1" spans="1:14" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -20385,32 +20411,32 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B4" s="230" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C4" s="230"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-7.1089558803142063</v>
+        <v>-7.1061455419777575</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C44</f>
-        <v>36.574068041485262</v>
+        <v>36.562604017004602</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C7" s="132">
         <f>Multiples!C52</f>
@@ -20419,38 +20445,38 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C62</f>
-        <v>-11.391030504289473</v>
+        <v>-11.387513566081854</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="141" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>14.368330098983957</v>
+        <v>14.36704591199981</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>107.04</v>
+        <v>112.91500000000001</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.86576672179574032</v>
+        <v>-0.87276229099765479</v>
       </c>
     </row>
   </sheetData>
@@ -20506,7 +20532,7 @@
     <row r="1" spans="1:28" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="81" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -20547,7 +20573,7 @@
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
       <c r="C5" s="239" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" s="239"/>
       <c r="E5" s="239"/>
@@ -20631,7 +20657,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C7" s="111">
         <f>'FCF &amp; Other'!C28</f>
@@ -20690,7 +20716,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B8" s="39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C8" s="137"/>
       <c r="D8" s="137"/>
@@ -20703,7 +20729,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-962492.44333392824</v>
+        <v>-961911.33425982634</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20722,7 +20748,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C9" s="137"/>
       <c r="D9" s="137"/>
@@ -20748,7 +20774,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C10" s="137"/>
       <c r="D10" s="137"/>
@@ -20757,29 +20783,29 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13166.324023922063</v>
+        <v>-13165.501472268064</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19095.785018903516</v>
+        <v>-19093.399116980407</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27695.581912282007</v>
+        <v>-27690.391483242496</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40168.301889689283</v>
+        <v>-40158.264947875359</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58258.117912506779</v>
+        <v>-58239.922126045429</v>
       </c>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" s="137"/>
       <c r="D11" s="137"/>
@@ -20792,43 +20818,43 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-505059.44427658612</v>
+        <v>-504596.86217722058</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="245" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C14" s="246"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>107.04</v>
+        <v>112.91500000000001</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B16" s="155" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-132.75060784597886</v>
+        <v>-132.65128160040436</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="157" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C17" s="158">
         <v>0.65</v>
       </c>
       <c r="E17" s="247" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F17" s="247"/>
       <c r="G17" s="247"/>
@@ -20838,13 +20864,13 @@
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="245" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" s="246"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C20" s="160">
         <v>0.02</v>
@@ -20852,11 +20878,11 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B21" s="159" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="228">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13765601246378217</v>
+        <v>0.13772709071603914</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -20870,16 +20896,16 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="159" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>537983.04</v>
+        <v>567510.79</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B24" s="159" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="229">
         <f>Statement!AC107</f>
@@ -20888,7 +20914,7 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B25" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C25" s="229">
         <f>Statement!AC108</f>
@@ -20897,50 +20923,50 @@
     </row>
     <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="157" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>541744.04</v>
+        <v>571271.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="245" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C28" s="246"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158384.11075730363</v>
+        <v>-158347.47914641176</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B30" s="159" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>-505059.44427658612</v>
+        <v>-504596.86217722058</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B31" s="163" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>-663443.55503388972</v>
+        <v>-662944.34132363228</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B32" s="159" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C32" s="165">
         <f>C24</f>
@@ -20949,7 +20975,7 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="159" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" s="165">
         <f>C25</f>
@@ -20958,11 +20984,11 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="163" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>-667204.55503388972</v>
+        <v>-666705.34132363228</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -20976,16 +21002,16 @@
     </row>
     <row r="36" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="166" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>-132.75060784597886</v>
+        <v>-132.65128160040436</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="239" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D39" s="239"/>
       <c r="E39" s="239"/>
@@ -21041,7 +21067,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C41" s="111">
         <f>C7</f>
@@ -21131,7 +21157,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="121" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C43" s="94">
         <f>C41/C42</f>
@@ -21216,7 +21242,7 @@
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="121" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C45" s="94">
         <f>C41/C44</f>
@@ -21256,7 +21282,7 @@
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="121" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C46" s="137"/>
       <c r="D46" s="94">
@@ -21298,7 +21324,7 @@
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="121" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C47" s="137"/>
       <c r="D47" s="94">
@@ -21340,7 +21366,7 @@
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C48" s="137"/>
       <c r="D48" s="94">
@@ -21382,7 +21408,7 @@
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="121" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C49" s="94">
         <f>C42/C44</f>
@@ -21484,45 +21510,45 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="M2" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="U2" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="V2" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="W2" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="X2" s="10" t="s">
-        <v>350</v>
-      </c>
       <c r="Y2" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -21551,16 +21577,16 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="X3" s="10" t="s">
         <v>85</v>
@@ -21881,7 +21907,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -22400,7 +22426,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -23440,7 +23466,7 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -23755,7 +23781,7 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B39" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
@@ -23877,7 +23903,7 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
@@ -24147,7 +24173,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -24260,7 +24286,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -24318,7 +24344,7 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
@@ -25127,7 +25153,7 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C64" s="61"/>
       <c r="D64" s="61"/>
@@ -25180,7 +25206,7 @@
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C65" s="61"/>
       <c r="D65" s="61"/>
@@ -25771,7 +25797,7 @@
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -25829,7 +25855,7 @@
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -25900,7 +25926,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -25971,7 +25997,7 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B79" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -26013,7 +26039,7 @@
     </row>
     <row r="80" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B80" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -26417,96 +26443,63 @@
       <c r="K89" s="48"/>
       <c r="L89" s="48"/>
       <c r="M89" s="48">
-        <f>IF(L5=0,
+        <f t="shared" ref="M89:Q96" si="59">IF(L5=0,
 IF(M5=0,0,IF(M5&gt;0,1,-1)),
 (M5-L5)/ABS(L5)
 )</f>
         <v>1</v>
       </c>
       <c r="N89" s="48">
-        <f>IF(M5=0,
-IF(N5=0,0,IF(N5&gt;0,1,-1)),
-(N5-M5)/ABS(M5)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.20209050415063778</v>
       </c>
       <c r="O89" s="48">
-        <f>IF(N5=0,
-IF(O5=0,0,IF(O5&gt;0,1,-1)),
-(O5-N5)/ABS(N5)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.13997525930155105</v>
       </c>
       <c r="P89" s="48">
-        <f>IF(O5=0,
-IF(P5=0,0,IF(P5&gt;0,1,-1)),
-(P5-O5)/ABS(O5)
-)</f>
+        <f t="shared" si="59"/>
         <v>-2.0782621523935976E-2</v>
       </c>
       <c r="Q89" s="48">
-        <f>IF(P5=0,
-IF(Q5=0,0,IF(Q5&gt;0,1,-1)),
-(Q5-P5)/ABS(P5)
-)</f>
+        <f t="shared" si="59"/>
         <v>-4.6703451912393362E-3</v>
       </c>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
       <c r="T89" s="48">
-        <f>IF(S5=0,
+        <f t="shared" ref="T89:AA96" si="60">IF(S5=0,
 IF(T5=0,0,IF(T5&gt;0,1,-1)),
 (T5-S5)/ABS(S5)
 )</f>
         <v>1</v>
       </c>
       <c r="U89" s="48">
-        <f>IF(T5=0,
-IF(U5=0,0,IF(U5&gt;0,1,-1)),
-(U5-T5)/ABS(T5)
-)</f>
+        <f t="shared" si="60"/>
         <v>3.5143769968051117E-2</v>
       </c>
       <c r="V89" s="48">
-        <f>IF(U5=0,
-IF(V5=0,0,IF(V5&gt;0,1,-1)),
-(V5-U5)/ABS(U5)
-)</f>
+        <f t="shared" si="60"/>
         <v>7.3471845829569407E-2</v>
       </c>
       <c r="W89" s="48">
-        <f>IF(V5=0,
-IF(W5=0,0,IF(W5&gt;0,1,-1)),
-(W5-V5)/ABS(V5)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.11171107994389902</v>
       </c>
       <c r="X89" s="48">
-        <f>IF(W5=0,
-IF(X5=0,0,IF(X5&gt;0,1,-1)),
-(X5-W5)/ABS(W5)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.5157495855372228E-2</v>
       </c>
       <c r="Y89" s="48">
-        <f>IF(X5=0,
-IF(Y5=0,0,IF(Y5&gt;0,1,-1)),
-(Y5-X5)/ABS(X5)
-)</f>
+        <f t="shared" si="60"/>
         <v>6.1746636596936001E-2</v>
       </c>
       <c r="Z89" s="48">
-        <f>IF(Y5=0,
-IF(Z5=0,0,IF(Z5&gt;0,1,-1)),
-(Z5-Y5)/ABS(Y5)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.5381234893430016E-3</v>
       </c>
       <c r="AA89" s="48">
-        <f>IF(Z5=0,
-IF(AA5=0,0,IF(AA5&gt;0,1,-1)),
-(AA5-Z5)/ABS(Z5)
-)</f>
+        <f t="shared" si="60"/>
         <v>-7.0937545707181514E-3</v>
       </c>
       <c r="AB89" s="1"/>
@@ -26529,94 +26522,55 @@
       <c r="K90" s="50"/>
       <c r="L90" s="50"/>
       <c r="M90" s="50">
-        <f>IF(L6=0,
-IF(M6=0,0,IF(M6&gt;0,1,-1)),
-(M6-L6)/ABS(L6)
-)</f>
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="N90" s="50">
-        <f>IF(M6=0,
-IF(N6=0,0,IF(N6&gt;0,1,-1)),
-(N6-M6)/ABS(M6)
-)</f>
+        <f t="shared" si="59"/>
         <v>2.7805390667158966E-2</v>
       </c>
       <c r="O90" s="50">
-        <f>IF(N6=0,
-IF(O6=0,0,IF(O6&gt;0,1,-1)),
-(O6-N6)/ABS(N6)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.10144246711617111</v>
       </c>
       <c r="P90" s="50">
-        <f>IF(O6=0,
-IF(P6=0,0,IF(P6&gt;0,1,-1)),
-(P6-O6)/ABS(O6)
-)</f>
+        <f t="shared" si="59"/>
         <v>9.9609435064735366E-2</v>
       </c>
       <c r="Q90" s="50">
-        <f>IF(P6=0,
-IF(Q6=0,0,IF(Q6&gt;0,1,-1)),
-(Q6-P6)/ABS(P6)
-)</f>
+        <f t="shared" si="59"/>
         <v>-3.5742253048439421E-2</v>
       </c>
       <c r="T90" s="50">
-        <f>IF(S6=0,
-IF(T6=0,0,IF(T6&gt;0,1,-1)),
-(T6-S6)/ABS(S6)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="U90" s="50">
-        <f>IF(T6=0,
-IF(U6=0,0,IF(U6&gt;0,1,-1)),
-(U6-T6)/ABS(T6)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.36217716630461017</v>
       </c>
       <c r="V90" s="50">
-        <f>IF(U6=0,
-IF(V6=0,0,IF(V6&gt;0,1,-1)),
-(V6-U6)/ABS(U6)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.23132807654824133</v>
       </c>
       <c r="W90" s="50">
-        <f>IF(V6=0,
-IF(W6=0,0,IF(W6&gt;0,1,-1)),
-(W6-V6)/ABS(V6)
-)</f>
+        <f t="shared" si="60"/>
         <v>-7.8492392807745504E-2</v>
       </c>
       <c r="X90" s="50">
-        <f>IF(W6=0,
-IF(X6=0,0,IF(X6&gt;0,1,-1)),
-(X6-W6)/ABS(W6)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.16535334584115072</v>
       </c>
       <c r="Y90" s="50">
-        <f>IF(X6=0,
-IF(Y6=0,0,IF(Y6&gt;0,1,-1)),
-(Y6-X6)/ABS(X6)
-)</f>
+        <f t="shared" si="60"/>
         <v>-9.4665664913598804E-2</v>
       </c>
       <c r="Z90" s="50">
-        <f>IF(Y6=0,
-IF(Z6=0,0,IF(Z6&gt;0,1,-1)),
-(Z6-Y6)/ABS(Y6)
-)</f>
+        <f t="shared" si="60"/>
         <v>3.5091879075281565E-2</v>
       </c>
       <c r="AA90" s="50">
-        <f>IF(Z6=0,
-IF(AA6=0,0,IF(AA6&gt;0,1,-1)),
-(AA6-Z6)/ABS(Z6)
-)</f>
+        <f t="shared" si="60"/>
         <v>-5.7381743213835761E-2</v>
       </c>
       <c r="AC90" s="67"/>
@@ -26637,96 +26591,57 @@
       <c r="K91" s="48"/>
       <c r="L91" s="48"/>
       <c r="M91" s="48">
-        <f>IF(L7=0,
-IF(M7=0,0,IF(M7&gt;0,1,-1)),
-(M7-L7)/ABS(L7)
-)</f>
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="N91" s="48">
-        <f>IF(M7=0,
-IF(N7=0,0,IF(N7&gt;0,1,-1)),
-(N7-M7)/ABS(M7)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.38683099395184295</v>
       </c>
       <c r="O91" s="48">
-        <f>IF(N7=0,
-IF(O7=0,0,IF(O7&gt;0,1,-1)),
-(O7-N7)/ABS(N7)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.19187821037742872</v>
       </c>
       <c r="P91" s="48">
-        <f>IF(O7=0,
-IF(P7=0,0,IF(P7&gt;0,1,-1)),
-(P7-O7)/ABS(O7)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.20109621850674772</v>
       </c>
       <c r="Q91" s="48">
-        <f>IF(P7=0,
-IF(Q7=0,0,IF(Q7&gt;0,1,-1)),
-(Q7-P7)/ABS(P7)
-)</f>
+        <f t="shared" si="59"/>
         <v>5.9383107523782071E-2</v>
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
       <c r="T91" s="48">
-        <f>IF(S7=0,
-IF(T7=0,0,IF(T7&gt;0,1,-1)),
-(T7-S7)/ABS(S7)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="U91" s="48">
-        <f>IF(T7=0,
-IF(U7=0,0,IF(U7&gt;0,1,-1)),
-(U7-T7)/ABS(T7)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.56080932482955792</v>
       </c>
       <c r="V91" s="48">
-        <f>IF(U7=0,
-IF(V7=0,0,IF(V7&gt;0,1,-1)),
-(V7-U7)/ABS(U7)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.7961942914371558</v>
       </c>
       <c r="W91" s="48">
-        <f>IF(V7=0,
-IF(W7=0,0,IF(W7&gt;0,1,-1)),
-(W7-V7)/ABS(V7)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.16332378223495703</v>
       </c>
       <c r="X91" s="48">
-        <f>IF(W7=0,
-IF(X7=0,0,IF(X7&gt;0,1,-1)),
-(X7-W7)/ABS(W7)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.24186643835616439</v>
       </c>
       <c r="Y91" s="48">
-        <f>IF(X7=0,
-IF(Y7=0,0,IF(Y7&gt;0,1,-1)),
-(Y7-X7)/ABS(X7)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.47317899491812537</v>
       </c>
       <c r="Z91" s="48">
-        <f>IF(Y7=0,
-IF(Z7=0,0,IF(Z7&gt;0,1,-1)),
-(Z7-Y7)/ABS(Y7)
-)</f>
+        <f t="shared" si="60"/>
         <v>-5.2702184745113068E-2</v>
       </c>
       <c r="AA91" s="48">
-        <f>IF(Z7=0,
-IF(AA7=0,0,IF(AA7&gt;0,1,-1)),
-(AA7-Z7)/ABS(Z7)
-)</f>
+        <f t="shared" si="60"/>
         <v>8.1731741857171761E-2</v>
       </c>
       <c r="AB91" s="1"/>
@@ -26749,101 +26664,62 @@
       <c r="K92" s="50"/>
       <c r="L92" s="50"/>
       <c r="M92" s="50">
-        <f>IF(L8=0,
-IF(M8=0,0,IF(M8&gt;0,1,-1)),
-(M8-L8)/ABS(L8)
-)</f>
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="N92" s="50">
-        <f>IF(M8=0,
-IF(N8=0,0,IF(N8&gt;0,1,-1)),
-(N8-M8)/ABS(M8)
-)</f>
+        <f t="shared" si="59"/>
         <v>0.15391705069124423</v>
       </c>
       <c r="O92" s="50">
-        <f>IF(N8=0,
-IF(O8=0,0,IF(O8&gt;0,1,-1)),
-(O8-N8)/ABS(N8)
-)</f>
+        <f t="shared" si="59"/>
         <v>-8.4550433591967136E-2</v>
       </c>
       <c r="P92" s="50">
-        <f>IF(O8=0,
-IF(P8=0,0,IF(P8&gt;0,1,-1)),
-(P8-O8)/ABS(O8)
-)</f>
+        <f t="shared" si="59"/>
         <v>3.1160413810295402E-2</v>
       </c>
       <c r="Q92" s="50">
-        <f>IF(P8=0,
-IF(Q8=0,0,IF(Q8&gt;0,1,-1)),
-(Q8-P8)/ABS(P8)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.16753293847455578</v>
       </c>
       <c r="T92" s="50">
-        <f>IF(S8=0,
-IF(T8=0,0,IF(T8&gt;0,1,-1)),
-(T8-S8)/ABS(S8)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="U92" s="50">
-        <f>IF(T8=0,
-IF(U8=0,0,IF(U8&gt;0,1,-1)),
-(U8-T8)/ABS(T8)
-)</f>
+        <f t="shared" si="60"/>
         <v>-4.4821891955649916E-2</v>
       </c>
       <c r="V92" s="50">
-        <f>IF(U8=0,
-IF(V8=0,0,IF(V8&gt;0,1,-1)),
-(V8-U8)/ABS(U8)
-)</f>
+        <f t="shared" si="60"/>
         <v>-4.2726599160286489E-2</v>
       </c>
       <c r="W92" s="50">
-        <f>IF(V8=0,
-IF(W8=0,0,IF(W8&gt;0,1,-1)),
-(W8-V8)/ABS(V8)
-)</f>
+        <f t="shared" si="60"/>
         <v>-6.0887512899896801E-2</v>
       </c>
       <c r="X92" s="50">
-        <f>IF(W8=0,
-IF(X8=0,0,IF(X8&gt;0,1,-1)),
-(X8-W8)/ABS(W8)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.2087912087912088E-2</v>
       </c>
       <c r="Y92" s="50">
-        <f>IF(X8=0,
-IF(Y8=0,0,IF(Y8&gt;0,1,-1)),
-(Y8-X8)/ABS(X8)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.12296416938110749</v>
       </c>
       <c r="Z92" s="50">
-        <f>IF(Y8=0,
-IF(Z8=0,0,IF(Z8&gt;0,1,-1)),
-(Z8-Y8)/ABS(Y8)
-)</f>
+        <f t="shared" si="60"/>
         <v>-3.7140204271123491E-3</v>
       </c>
       <c r="AA92" s="50">
-        <f>IF(Z8=0,
-IF(AA8=0,0,IF(AA8&gt;0,1,-1)),
-(AA8-Z8)/ABS(Z8)
-)</f>
+        <f t="shared" si="60"/>
         <v>4.8462255358807084E-2</v>
       </c>
       <c r="AC92" s="67"/>
     </row>
     <row r="93" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B93" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C93" s="49"/>
       <c r="D93" s="50"/>
@@ -26856,94 +26732,55 @@
       <c r="K93" s="50"/>
       <c r="L93" s="50"/>
       <c r="M93" s="50">
-        <f>IF(L9=0,
-IF(M9=0,0,IF(M9&gt;0,1,-1)),
-(M9-L9)/ABS(L9)
-)</f>
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="N93" s="50">
-        <f>IF(M9=0,
-IF(N9=0,0,IF(N9&gt;0,1,-1)),
-(N9-M9)/ABS(M9)
-)</f>
+        <f t="shared" si="59"/>
         <v>7.0151306740027508E-2</v>
       </c>
       <c r="O93" s="50">
-        <f>IF(N9=0,
-IF(O9=0,0,IF(O9&gt;0,1,-1)),
-(O9-N9)/ABS(N9)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.19537275064267351</v>
       </c>
       <c r="P93" s="50">
-        <f>IF(O9=0,
-IF(P9=0,0,IF(P9&gt;0,1,-1)),
-(P9-O9)/ABS(O9)
-)</f>
+        <f t="shared" si="59"/>
         <v>-2.2541711040113595E-2</v>
       </c>
       <c r="Q93" s="50">
-        <f>IF(P9=0,
-IF(Q9=0,0,IF(Q9&gt;0,1,-1)),
-(Q9-P9)/ABS(P9)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.16034138369348103</v>
       </c>
       <c r="T93" s="50">
-        <f>IF(S9=0,
-IF(T9=0,0,IF(T9&gt;0,1,-1)),
-(T9-S9)/ABS(S9)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="U93" s="50">
-        <f>IF(T9=0,
-IF(U9=0,0,IF(U9&gt;0,1,-1)),
-(U9-T9)/ABS(T9)
-)</f>
+        <f t="shared" si="60"/>
         <v>4.0632054176072234E-2</v>
       </c>
       <c r="V93" s="50">
-        <f>IF(U9=0,
-IF(V9=0,0,IF(V9&gt;0,1,-1)),
-(V9-U9)/ABS(U9)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.10412147505422993</v>
       </c>
       <c r="W93" s="50">
-        <f>IF(V9=0,
-IF(W9=0,0,IF(W9&gt;0,1,-1)),
-(W9-V9)/ABS(V9)
-)</f>
+        <f t="shared" si="60"/>
         <v>-5.004035512510089E-2</v>
       </c>
       <c r="X93" s="50">
-        <f>IF(W9=0,
-IF(X9=0,0,IF(X9&gt;0,1,-1)),
-(X9-W9)/ABS(W9)
-)</f>
+        <f t="shared" si="60"/>
         <v>-2.8037383177570093E-2</v>
       </c>
       <c r="Y93" s="50">
-        <f>IF(X9=0,
-IF(Y9=0,0,IF(Y9&gt;0,1,-1)),
-(Y9-X9)/ABS(X9)
-)</f>
+        <f t="shared" si="60"/>
         <v>-1.3111888111888112E-2</v>
       </c>
       <c r="Z93" s="50">
-        <f>IF(Y9=0,
-IF(Z9=0,0,IF(Z9&gt;0,1,-1)),
-(Z9-Y9)/ABS(Y9)
-)</f>
+        <f t="shared" si="60"/>
         <v>3.9858281665190433E-2</v>
       </c>
       <c r="AA93" s="50">
-        <f>IF(Z9=0,
-IF(AA9=0,0,IF(AA9&gt;0,1,-1)),
-(AA9-Z9)/ABS(Z9)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.11584327086882454</v>
       </c>
       <c r="AC93" s="67"/>
@@ -26963,94 +26800,55 @@
       <c r="K94" s="50"/>
       <c r="L94" s="50"/>
       <c r="M94" s="50">
-        <f>IF(L10=0,
-IF(M10=0,0,IF(M10&gt;0,1,-1)),
-(M10-L10)/ABS(L10)
-)</f>
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="N94" s="50">
-        <f>IF(M10=0,
-IF(N10=0,0,IF(N10&gt;0,1,-1)),
-(N10-M10)/ABS(M10)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.99923838537699927</v>
       </c>
       <c r="O94" s="50">
-        <f>IF(N10=0,
-IF(O10=0,0,IF(O10&gt;0,1,-1)),
-(O10-N10)/ABS(N10)
-)</f>
+        <f t="shared" si="59"/>
         <v>-32</v>
       </c>
       <c r="P94" s="50">
-        <f>IF(O10=0,
-IF(P10=0,0,IF(P10&gt;0,1,-1)),
-(P10-O10)/ABS(O10)
-)</f>
+        <f t="shared" si="59"/>
         <v>113.41935483870968</v>
       </c>
       <c r="Q94" s="50">
-        <f>IF(P10=0,
-IF(Q10=0,0,IF(Q10&gt;0,1,-1)),
-(Q10-P10)/ABS(P10)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.68565279770444765</v>
       </c>
       <c r="T94" s="50">
-        <f>IF(S10=0,
-IF(T10=0,0,IF(T10&gt;0,1,-1)),
-(T10-S10)/ABS(S10)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="U94" s="50">
-        <f>IF(T10=0,
-IF(U10=0,0,IF(U10&gt;0,1,-1)),
-(U10-T10)/ABS(T10)
-)</f>
+        <f t="shared" si="60"/>
         <v>4.9618239660657473</v>
       </c>
       <c r="V94" s="50">
-        <f>IF(U10=0,
-IF(V10=0,0,IF(V10&gt;0,1,-1)),
-(V10-U10)/ABS(U10)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.98986125933831381</v>
       </c>
       <c r="W94" s="50">
-        <f>IF(V10=0,
-IF(W10=0,0,IF(W10&gt;0,1,-1)),
-(W10-V10)/ABS(V10)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.736842105263158</v>
       </c>
       <c r="X94" s="50">
-        <f>IF(W10=0,
-IF(X10=0,0,IF(X10&gt;0,1,-1)),
-(X10-W10)/ABS(W10)
-)</f>
+        <f t="shared" si="60"/>
         <v>11.115384615384615</v>
       </c>
       <c r="Y94" s="50">
-        <f>IF(X10=0,
-IF(Y10=0,0,IF(Y10&gt;0,1,-1)),
-(Y10-X10)/ABS(X10)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.90740740740740744</v>
       </c>
       <c r="Z94" s="50">
-        <f>IF(Y10=0,
-IF(Z10=0,0,IF(Z10&gt;0,1,-1)),
-(Z10-Y10)/ABS(Y10)
-)</f>
+        <f t="shared" si="60"/>
         <v>-1.1714285714285715</v>
       </c>
       <c r="AA94" s="50">
-        <f>IF(Z10=0,
-IF(AA10=0,0,IF(AA10&gt;0,1,-1)),
-(AA10-Z10)/ABS(Z10)
-)</f>
+        <f t="shared" si="60"/>
         <v>136.66666666666666</v>
       </c>
       <c r="AC94" s="67"/>
@@ -27070,94 +26868,55 @@
       <c r="K95" s="50"/>
       <c r="L95" s="50"/>
       <c r="M95" s="50">
-        <f>IF(L11=0,
-IF(M11=0,0,IF(M11&gt;0,1,-1)),
-(M11-L11)/ABS(L11)
-)</f>
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="N95" s="50">
-        <f>IF(M11=0,
-IF(N11=0,0,IF(N11&gt;0,1,-1)),
-(N11-M11)/ABS(M11)
-)</f>
+        <f t="shared" si="59"/>
         <v>7.1020977872654871E-3</v>
       </c>
       <c r="O95" s="50">
-        <f>IF(N11=0,
-IF(O11=0,0,IF(O11&gt;0,1,-1)),
-(O11-N11)/ABS(N11)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.11878362954508397</v>
       </c>
       <c r="P95" s="50">
-        <f>IF(O11=0,
-IF(P11=0,0,IF(P11&gt;0,1,-1)),
-(P11-O11)/ABS(O11)
-)</f>
+        <f t="shared" si="59"/>
         <v>0.34253862521972428</v>
       </c>
       <c r="Q95" s="50">
-        <f>IF(P11=0,
-IF(Q11=0,0,IF(Q11&gt;0,1,-1)),
-(Q11-P11)/ABS(P11)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.29059711263480686</v>
       </c>
       <c r="T95" s="50">
-        <f>IF(S11=0,
-IF(T11=0,0,IF(T11&gt;0,1,-1)),
-(T11-S11)/ABS(S11)
-)</f>
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="U95" s="50">
-        <f>IF(T11=0,
-IF(U11=0,0,IF(U11&gt;0,1,-1)),
-(U11-T11)/ABS(T11)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.6977422822915067</v>
       </c>
       <c r="V95" s="50">
-        <f>IF(U11=0,
-IF(V11=0,0,IF(V11&gt;0,1,-1)),
-(V11-U11)/ABS(U11)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.53211507146734216</v>
       </c>
       <c r="W95" s="50">
-        <f>IF(V11=0,
-IF(W11=0,0,IF(W11&gt;0,1,-1)),
-(W11-V11)/ABS(V11)
-)</f>
+        <f t="shared" si="60"/>
         <v>-3.8476411446249033E-2</v>
       </c>
       <c r="X95" s="50">
-        <f>IF(W11=0,
-IF(X11=0,0,IF(X11&gt;0,1,-1)),
-(X11-W11)/ABS(W11)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.35089483209330385</v>
       </c>
       <c r="Y95" s="50">
-        <f>IF(X11=0,
-IF(Y11=0,0,IF(Y11&gt;0,1,-1)),
-(Y11-X11)/ABS(X11)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.32494790116105982</v>
       </c>
       <c r="Z95" s="50">
-        <f>IF(Y11=0,
-IF(Z11=0,0,IF(Z11&gt;0,1,-1)),
-(Z11-Y11)/ABS(Y11)
-)</f>
+        <f t="shared" si="60"/>
         <v>-3.7927232635060641E-2</v>
       </c>
       <c r="AA95" s="50">
-        <f>IF(Z11=0,
-IF(AA11=0,0,IF(AA11&gt;0,1,-1)),
-(AA11-Z11)/ABS(Z11)
-)</f>
+        <f t="shared" si="60"/>
         <v>0.94430437772175113</v>
       </c>
       <c r="AC95" s="67"/>
@@ -27178,96 +26937,57 @@
       <c r="K96" s="48"/>
       <c r="L96" s="48"/>
       <c r="M96" s="48">
-        <f>IF(L12=0,
-IF(M12=0,0,IF(M12&gt;0,1,-1)),
-(M12-L12)/ABS(L12)
-)</f>
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
       <c r="N96" s="48">
-        <f>IF(M12=0,
-IF(N12=0,0,IF(N12&gt;0,1,-1)),
-(N12-M12)/ABS(M12)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.88003700657894735</v>
       </c>
       <c r="O96" s="48">
-        <f>IF(N12=0,
-IF(O12=0,0,IF(O12&gt;0,1,-1)),
-(O12-N12)/ABS(N12)
-)</f>
+        <f t="shared" si="59"/>
         <v>-0.96015424164524421</v>
       </c>
       <c r="P96" s="48">
-        <f>IF(O12=0,
-IF(P12=0,0,IF(P12&gt;0,1,-1)),
-(P12-O12)/ABS(O12)
-)</f>
+        <f t="shared" si="59"/>
         <v>-126.56989247311827</v>
       </c>
       <c r="Q96" s="48">
-        <f>IF(P12=0,
-IF(Q12=0,0,IF(Q12&gt;0,1,-1)),
-(Q12-P12)/ABS(P12)
-)</f>
+        <f t="shared" si="59"/>
         <v>0.81041274190786095</v>
       </c>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
       <c r="T96" s="48">
-        <f>IF(S12=0,
-IF(T12=0,0,IF(T12&gt;0,1,-1)),
-(T12-S12)/ABS(S12)
-)</f>
+        <f t="shared" si="60"/>
         <v>-1</v>
       </c>
       <c r="U96" s="48">
-        <f>IF(T12=0,
-IF(U12=0,0,IF(U12&gt;0,1,-1)),
-(U12-T12)/ABS(T12)
-)</f>
+        <f t="shared" si="60"/>
         <v>-3.6115071283095723</v>
       </c>
       <c r="V96" s="48">
-        <f>IF(U12=0,
-IF(V12=0,0,IF(V12&gt;0,1,-1)),
-(V12-U12)/ABS(U12)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.0454896764933201</v>
       </c>
       <c r="W96" s="48">
-        <f>IF(V12=0,
-IF(W12=0,0,IF(W12&gt;0,1,-1)),
-(W12-V12)/ABS(V12)
-)</f>
+        <f t="shared" si="60"/>
         <v>-1.7305825242718447</v>
       </c>
       <c r="X96" s="48">
-        <f>IF(W12=0,
-IF(X12=0,0,IF(X12&gt;0,1,-1)),
-(X12-W12)/ABS(W12)
-)</f>
+        <f t="shared" si="60"/>
         <v>-9.5514950166112964</v>
       </c>
       <c r="Y96" s="48">
-        <f>IF(X12=0,
-IF(Y12=0,0,IF(Y12&gt;0,1,-1)),
-(Y12-X12)/ABS(X12)
-)</f>
+        <f t="shared" si="60"/>
         <v>1.2150503778337531</v>
       </c>
       <c r="Z96" s="48">
-        <f>IF(Y12=0,
-IF(Z12=0,0,IF(Z12&gt;0,1,-1)),
-(Z12-Y12)/ABS(Y12)
-)</f>
+        <f t="shared" si="60"/>
         <v>-0.15080527086383602</v>
       </c>
       <c r="AA96" s="48">
-        <f>IF(Z12=0,
-IF(AA12=0,0,IF(AA12&gt;0,1,-1)),
-(AA12-Z12)/ABS(Z12)
-)</f>
+        <f t="shared" si="60"/>
         <v>-6.4068965517241381</v>
       </c>
       <c r="AB96" s="1"/>
@@ -27328,38 +27048,38 @@
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
       <c r="T97" s="52">
-        <f t="shared" ref="T97:AA97" si="59">IF(S15=0,
+        <f t="shared" ref="T97:AA97" si="61">IF(S15=0,
 IF(T15=0,0,IF(T15&gt;0,1,-1)),
 (T15-S15)/ABS(S15)
 )</f>
         <v>-1</v>
       </c>
       <c r="U97" s="52">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-3.5339321357285427</v>
       </c>
       <c r="V97" s="52">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>1.065925599823905</v>
       </c>
       <c r="W97" s="52">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-1.978297161936561</v>
       </c>
       <c r="X97" s="52">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-3.7252559726962455</v>
       </c>
       <c r="Y97" s="52">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>2.6518598772119897</v>
       </c>
       <c r="Z97" s="52">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-0.92610406646261478</v>
       </c>
       <c r="AA97" s="52">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-12.674556213017752</v>
       </c>
       <c r="AB97" s="1"/>
@@ -27420,38 +27140,38 @@
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
       <c r="T98" s="52">
-        <f t="shared" ref="T98:AA98" si="60">IF(S18=0,
+        <f t="shared" ref="T98:AA98" si="62">IF(S18=0,
 IF(T18=0,0,IF(T18&gt;0,1,-1)),
 (T18-S18)/ABS(S18)
 )</f>
         <v>-1</v>
       </c>
       <c r="U98" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-9.3347826086956527</v>
       </c>
       <c r="V98" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.99242742953302487</v>
       </c>
       <c r="W98" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-5.5158730158730158</v>
       </c>
       <c r="X98" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-2.5542021924482339</v>
       </c>
       <c r="Y98" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>2.3923920493488691</v>
       </c>
       <c r="Z98" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-1.1454590204282551</v>
       </c>
       <c r="AA98" s="52">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-5.3079526226734348</v>
       </c>
       <c r="AB98" s="1"/>
@@ -27508,35 +27228,35 @@
         <v>0.34766238434904356</v>
       </c>
       <c r="T101" s="50">
-        <f t="shared" ref="T101:AA101" si="61">T7/T5</f>
+        <f t="shared" ref="T101:AA101" si="63">T7/T5</f>
         <v>0.35432089145172602</v>
       </c>
       <c r="U101" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.15033122553447756</v>
       </c>
       <c r="V101" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.39158485273492288</v>
       </c>
       <c r="W101" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.36883239914739085</v>
       </c>
       <c r="X101" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.27544910179640719</v>
       </c>
       <c r="Y101" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.38218706511389439</v>
       </c>
       <c r="Z101" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.36148895714494661</v>
       </c>
       <c r="AA101" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.39382779700964865</v>
       </c>
       <c r="AC101" s="50">
@@ -27579,35 +27299,35 @@
         <v>-4.1889769738709247E-2</v>
       </c>
       <c r="T102" s="50">
-        <f t="shared" ref="T102:AA102" si="62">T12/T5</f>
+        <f t="shared" ref="T102:AA102" si="64">T12/T5</f>
         <v>-0.15304293618016052</v>
       </c>
       <c r="U102" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-0.68179765130984649</v>
       </c>
       <c r="V102" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>2.8892005610098175E-2</v>
       </c>
       <c r="W102" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-2.3762532564932503E-2</v>
       </c>
       <c r="X102" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-0.246986546387744</v>
       </c>
       <c r="Y102" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>5.0025635391489048E-2</v>
       </c>
       <c r="Z102" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>4.2416264443469361E-2</v>
       </c>
       <c r="AA102" s="50">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-0.23097886130956766</v>
       </c>
       <c r="AC102" s="50">
@@ -27653,35 +27373,35 @@
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
       <c r="T103" s="55">
-        <f t="shared" ref="T103:AA103" si="63">T111/T5</f>
+        <f t="shared" ref="T103:AA103" si="65">T111/T5</f>
         <v>-0.12888646458349567</v>
       </c>
       <c r="U103" s="55">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-1.278906955736224</v>
       </c>
       <c r="V103" s="55">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-1.0729312762973352E-2</v>
       </c>
       <c r="W103" s="55">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-7.0024473040183152E-2</v>
       </c>
       <c r="X103" s="55">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-0.23516603157321719</v>
       </c>
       <c r="Y103" s="55">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.31275177616641031</v>
       </c>
       <c r="Z103" s="55">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-2.4352786309784994E-2</v>
       </c>
       <c r="AA103" s="55">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-0.31531266111806733</v>
       </c>
       <c r="AB103" s="1"/>
@@ -27711,95 +27431,95 @@
         <v>71</v>
       </c>
       <c r="C106" s="80">
-        <f t="shared" ref="C106:Q106" si="64">IF(AND(C83&gt;=0,C12&gt;=0),C83,0)</f>
+        <f t="shared" ref="C106:Q106" si="66">IF(AND(C83&gt;=0,C12&gt;=0),C83,0)</f>
         <v>0</v>
       </c>
       <c r="D106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="E106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="F106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="G106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="H106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="I106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="J106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="K106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="L106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="M106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>8.4550522969174771E-2</v>
       </c>
       <c r="N106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="P106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="Q106" s="80">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="T106" s="80">
-        <f t="shared" ref="T106:AA106" si="65">IF(AND(T83&gt;=0,T12&gt;=0),T83,0)</f>
+        <f t="shared" ref="T106:AA106" si="67">IF(AND(T83&gt;=0,T12&gt;=0),T83,0)</f>
         <v>0</v>
       </c>
       <c r="U106" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="V106" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1.2554257095158599</v>
       </c>
       <c r="W106" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="X106" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="Y106" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>6.6462614779186704E-2</v>
       </c>
       <c r="Z106" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1.985207100591716</v>
       </c>
       <c r="AA106" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AC106" s="80">
@@ -27809,7 +27529,7 @@
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B107" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C107" s="25"/>
       <c r="D107" s="25"/>
@@ -27826,51 +27546,51 @@
         <v>34711</v>
       </c>
       <c r="N107" s="25">
-        <f t="shared" ref="N107:Q107" si="66">N29+N34</f>
+        <f t="shared" ref="N107:Q107" si="68">N29+N34</f>
         <v>34250</v>
       </c>
       <c r="O107" s="25">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>30863</v>
       </c>
       <c r="P107" s="25">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>27445</v>
       </c>
       <c r="Q107" s="25">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>45928</v>
       </c>
       <c r="T107" s="25">
-        <f t="shared" ref="T107:AA107" si="67">T29+T34</f>
+        <f t="shared" ref="T107:AA107" si="69">T29+T34</f>
         <v>35097</v>
       </c>
       <c r="U107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>29582</v>
       </c>
       <c r="V107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>27445</v>
       </c>
       <c r="W107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>26075</v>
       </c>
       <c r="X107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>26589</v>
       </c>
       <c r="Y107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>39602</v>
       </c>
       <c r="Z107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>45928</v>
       </c>
       <c r="AA107" s="25">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>41270</v>
       </c>
       <c r="AC107" s="25">
@@ -27880,7 +27600,7 @@
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B108" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C108" s="25">
         <v>0</v>
@@ -27933,35 +27653,35 @@
         <v>46585</v>
       </c>
       <c r="T108" s="25">
-        <f t="shared" ref="T108:AA108" si="68">T39+T41</f>
+        <f t="shared" ref="T108:AA108" si="70">T39+T41</f>
         <v>53029</v>
       </c>
       <c r="U108" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>50236</v>
       </c>
       <c r="V108" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>50011</v>
       </c>
       <c r="W108" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>50151</v>
       </c>
       <c r="X108" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>50757</v>
       </c>
       <c r="Y108" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>46553</v>
       </c>
       <c r="Z108" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>46585</v>
       </c>
       <c r="AA108" s="25">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>45031</v>
       </c>
       <c r="AC108" s="25">
@@ -27971,7 +27691,7 @@
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B109" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C109" s="25"/>
       <c r="D109" s="25"/>
@@ -28018,7 +27738,7 @@
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B110" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C110" s="25"/>
       <c r="D110" s="25"/>
@@ -28051,35 +27771,35 @@
         <v>-14646</v>
       </c>
       <c r="T110" s="125">
-        <f t="shared" ref="T110:AA110" si="69">T60+T61</f>
+        <f t="shared" ref="T110:AA110" si="71">T60+T61</f>
         <v>0</v>
       </c>
       <c r="U110" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="V110" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="W110" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-5183</v>
       </c>
       <c r="X110" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-3550</v>
       </c>
       <c r="Y110" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-2425</v>
       </c>
       <c r="Z110" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-3488</v>
       </c>
       <c r="AA110" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-3636</v>
       </c>
       <c r="AC110" s="125">
@@ -28089,7 +27809,7 @@
     </row>
     <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B111" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C111" s="25"/>
       <c r="D111" s="25"/>
@@ -28122,35 +27842,35 @@
         <v>26</v>
       </c>
       <c r="T111" s="125">
-        <f t="shared" ref="T111:AA111" si="70">T17+T18</f>
+        <f t="shared" ref="T111:AA111" si="72">T17+T18</f>
         <v>-1654</v>
       </c>
       <c r="U111" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-16989</v>
       </c>
       <c r="V111" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-153</v>
       </c>
       <c r="W111" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-887</v>
       </c>
       <c r="X111" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-3024</v>
       </c>
       <c r="Y111" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>4270</v>
       </c>
       <c r="Z111" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-333</v>
       </c>
       <c r="AA111" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-4281</v>
       </c>
       <c r="AC111" s="125">
@@ -28160,7 +27880,7 @@
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B112" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C112" s="25"/>
       <c r="D112" s="25"/>
@@ -28193,35 +27913,35 @@
         <v>126360</v>
       </c>
       <c r="T112" s="125">
-        <f t="shared" ref="T112:AA112" si="71">T49+T48</f>
+        <f t="shared" ref="T112:AA112" si="73">T49+T48</f>
         <v>120434</v>
       </c>
       <c r="U112" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>104864</v>
       </c>
       <c r="V112" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>105032</v>
       </c>
       <c r="W112" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>106413</v>
       </c>
       <c r="X112" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>105751</v>
       </c>
       <c r="Y112" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>116730</v>
       </c>
       <c r="Z112" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>126360</v>
       </c>
       <c r="AA112" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>124989</v>
       </c>
       <c r="AC112" s="125">
@@ -28293,12 +28013,12 @@
       <c r="AA116" s="67"/>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>107.04</v>
+        <v>112.91500000000001</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B117" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C117" s="26"/>
       <c r="D117" s="26"/>
@@ -28340,7 +28060,7 @@
       <c r="AA117" s="67"/>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>107.04</v>
+        <v>112.91500000000001</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -28454,19 +28174,19 @@
         <v>97</v>
       </c>
       <c r="M123" s="75">
-        <f t="shared" ref="M123:P123" si="72">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="74">M121*M122</f>
         <v>0.11797679417597948</v>
       </c>
       <c r="N123" s="75">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>4.4024535565037361E-2</v>
       </c>
       <c r="O123" s="75">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>8.7434489382581995E-3</v>
       </c>
       <c r="P123" s="75">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>-9.7885334758378503E-2</v>
       </c>
       <c r="Q123" s="75">
@@ -28528,19 +28248,19 @@
         <v>99</v>
       </c>
       <c r="M125" s="75">
-        <f t="shared" ref="M125:P125" si="73">M123*M124</f>
+        <f t="shared" ref="M125:P125" si="75">M123*M124</f>
         <v>0.20827960709081569</v>
       </c>
       <c r="N125" s="75">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>7.904518698914445E-2</v>
       </c>
       <c r="O125" s="75">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>1.5863244625438012E-2</v>
       </c>
       <c r="P125" s="75">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>-0.19374433363553945</v>
       </c>
       <c r="Q125" s="75">
@@ -28565,7 +28285,7 @@
     </row>
     <row r="128" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B128" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C128" s="171"/>
       <c r="D128" s="171"/>
@@ -28594,7 +28314,7 @@
     </row>
     <row r="129" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B129" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C129" s="49"/>
       <c r="D129" s="49"/>
@@ -28639,7 +28359,7 @@
     </row>
     <row r="130" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B130" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C130" s="49"/>
       <c r="D130" s="49"/>
@@ -28684,7 +28404,7 @@
     </row>
     <row r="131" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B131" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C131" s="49"/>
       <c r="D131" s="49"/>
@@ -28702,42 +28422,42 @@
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
       <c r="T131" s="25">
-        <f t="shared" ref="T131:AA131" si="74">U5</f>
+        <f t="shared" ref="T131:AA131" si="76">U5</f>
         <v>13284</v>
       </c>
       <c r="U131" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>14260</v>
       </c>
       <c r="V131" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>12667</v>
       </c>
       <c r="W131" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>12859</v>
       </c>
       <c r="X131" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>13653</v>
       </c>
       <c r="Y131" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>13674</v>
       </c>
       <c r="Z131" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>13577</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
     </row>
     <row r="132" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B132" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C132" s="49"/>
       <c r="D132" s="49"/>
@@ -28755,31 +28475,31 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="172" t="str">
-        <f t="shared" ref="T132:Z132" si="75">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Z132" si="77">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U132" s="172" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>MET</v>
       </c>
       <c r="V132" s="172" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>MET</v>
       </c>
       <c r="W132" s="172" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>BEAT</v>
       </c>
       <c r="X132" s="172" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>BEAT</v>
       </c>
       <c r="Y132" s="172" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>MET</v>
       </c>
       <c r="Z132" s="172" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>BEAT</v>
       </c>
       <c r="AA132" s="172" t="str">
@@ -28790,7 +28510,7 @@
     </row>
     <row r="133" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B133" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C133" s="49"/>
       <c r="D133" s="49"/>
@@ -28835,7 +28555,7 @@
     </row>
     <row r="134" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B134" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C134" s="49"/>
       <c r="D134" s="49"/>
@@ -28880,7 +28600,7 @@
     </row>
     <row r="135" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B135" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C135" s="49"/>
       <c r="D135" s="49"/>
@@ -28898,42 +28618,42 @@
       <c r="P135" s="49"/>
       <c r="Q135" s="49"/>
       <c r="T135" s="73">
-        <f t="shared" ref="T135:AA135" si="76">U101</f>
+        <f t="shared" ref="T135:AA135" si="78">U101</f>
         <v>0.15033122553447756</v>
       </c>
       <c r="U135" s="73">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.39158485273492288</v>
       </c>
       <c r="V135" s="73">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.36883239914739085</v>
       </c>
       <c r="W135" s="73">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.27544910179640719</v>
       </c>
       <c r="X135" s="73">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.38218706511389439</v>
       </c>
       <c r="Y135" s="73">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.36148895714494661</v>
       </c>
       <c r="Z135" s="73">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0.39382779700964865</v>
       </c>
       <c r="AA135" s="73">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
     </row>
     <row r="136" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B136" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C136" s="49"/>
       <c r="D136" s="49"/>
@@ -28951,31 +28671,31 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="172" t="str">
-        <f t="shared" ref="T136:Z136" si="77">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Z136" si="79">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U136" s="172" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="V136" s="172" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="W136" s="172" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>MISSED</v>
       </c>
       <c r="X136" s="172" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="Y136" s="172" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="Z136" s="172" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>BEAT</v>
       </c>
       <c r="AA136" s="172" t="str">
@@ -28989,7 +28709,7 @@
     </row>
     <row r="139" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B139" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C139" s="171"/>
       <c r="D139" s="171"/>
@@ -29068,55 +28788,55 @@
         <v>134</v>
       </c>
       <c r="M141" s="117">
-        <f>M30/M5*365</f>
+        <f t="shared" ref="M141:Q142" si="80">M30/M5*365</f>
         <v>43.680464162785988</v>
       </c>
       <c r="N141" s="117">
-        <f>N30/N5*365</f>
+        <f t="shared" si="80"/>
         <v>23.924651885685286</v>
       </c>
       <c r="O141" s="117">
-        <f>O30/O5*365</f>
+        <f t="shared" si="80"/>
         <v>22.898318211993807</v>
       </c>
       <c r="P141" s="117">
-        <f>P30/P5*365</f>
+        <f t="shared" si="80"/>
         <v>23.906706088397584</v>
       </c>
       <c r="Q141" s="117">
-        <f>Q30/Q5*365</f>
+        <f t="shared" si="80"/>
         <v>26.511929313378616</v>
       </c>
       <c r="T141" s="117">
-        <f t="shared" ref="T141:AA141" si="78">T30/T5*90</f>
+        <f t="shared" ref="T141:AA141" si="81">T30/T5*90</f>
         <v>21.958232681368347</v>
       </c>
       <c r="U141" s="117">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>21.144986449864501</v>
       </c>
       <c r="V141" s="117">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>21.950911640953716</v>
       </c>
       <c r="W141" s="117">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>21.769953422278363</v>
       </c>
       <c r="X141" s="117">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>16.517614122404542</v>
       </c>
       <c r="Y141" s="117">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>21.107448912326962</v>
       </c>
       <c r="Z141" s="117">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>25.267661254936375</v>
       </c>
       <c r="AA141" s="117">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>26.952935110849229</v>
       </c>
       <c r="AC141" s="117">
@@ -29129,55 +28849,55 @@
         <v>135</v>
       </c>
       <c r="M142" s="117">
-        <f>M31/M6*365</f>
+        <f t="shared" si="80"/>
         <v>111.71121020193701</v>
       </c>
       <c r="N142" s="117">
-        <f>N31/N6*365</f>
+        <f t="shared" si="80"/>
         <v>133.38012600862163</v>
       </c>
       <c r="O142" s="117">
-        <f>O31/O6*365</f>
+        <f t="shared" si="80"/>
         <v>124.89943721745549</v>
       </c>
       <c r="P142" s="117">
-        <f>P31/P6*365</f>
+        <f t="shared" si="80"/>
         <v>124.51812283253162</v>
       </c>
       <c r="Q142" s="117">
-        <f>Q31/Q6*365</f>
+        <f t="shared" si="80"/>
         <v>122.99350310342828</v>
       </c>
       <c r="T142" s="117">
-        <f t="shared" ref="T142:AA142" si="79">T31/T6*365</f>
+        <f t="shared" ref="T142:AA142" si="82">T31/T6*365</f>
         <v>495.30050687907317</v>
       </c>
       <c r="U142" s="117">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>390.06201825108536</v>
       </c>
       <c r="V142" s="117">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>513.17081604425994</v>
       </c>
       <c r="W142" s="117">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>560.6710444027517</v>
       </c>
       <c r="X142" s="117">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>445.70194268541377</v>
       </c>
       <c r="Y142" s="117">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>497.15293420272673</v>
       </c>
       <c r="Z142" s="117">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>485.6912152101707</v>
       </c>
       <c r="AA142" s="117">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>551.09234507897929</v>
       </c>
       <c r="AC142" s="117">
@@ -29210,35 +28930,35 @@
         <v>104.6154069261558</v>
       </c>
       <c r="T143" s="117">
-        <f t="shared" ref="T143:AA143" si="80">T38/T6*90</f>
+        <f t="shared" ref="T143:AA143" si="83">T38/T6*90</f>
         <v>104.46777697320782</v>
       </c>
       <c r="U143" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>88.301585895277753</v>
       </c>
       <c r="V143" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>130.24896265560164</v>
       </c>
       <c r="W143" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>122.65666041275797</v>
       </c>
       <c r="X143" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>103.03101856820865</v>
       </c>
       <c r="Y143" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>109.55779490219324</v>
       </c>
       <c r="Z143" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>101.86462031840568</v>
       </c>
       <c r="AA143" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>78.287970838396106</v>
       </c>
       <c r="AC143" s="117">
@@ -29255,61 +28975,61 @@
         <v>95.814435590545941</v>
       </c>
       <c r="N144" s="117">
-        <f t="shared" ref="N144:Q144" si="81">N141+N142-N143</f>
+        <f t="shared" ref="N144:Q144" si="84">N141+N142-N143</f>
         <v>60.527531293223674</v>
       </c>
       <c r="O144" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>51.577931952498773</v>
       </c>
       <c r="P144" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>20.252214534532527</v>
       </c>
       <c r="Q144" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>44.890025490651112</v>
       </c>
       <c r="T144" s="117">
-        <f t="shared" ref="T144" si="82">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="85">T141+T142-T143</f>
         <v>412.79096258723371</v>
       </c>
       <c r="U144" s="117">
-        <f t="shared" ref="U144" si="83">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="86">U141+U142-U143</f>
         <v>322.90541880567213</v>
       </c>
       <c r="V144" s="117">
-        <f t="shared" ref="V144" si="84">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="87">V141+V142-V143</f>
         <v>404.87276502961197</v>
       </c>
       <c r="W144" s="117">
-        <f t="shared" ref="W144" si="85">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="88">W141+W142-W143</f>
         <v>459.78433741227212</v>
       </c>
       <c r="X144" s="117">
-        <f t="shared" ref="X144" si="86">X141+X142-X143</f>
+        <f t="shared" ref="X144" si="89">X141+X142-X143</f>
         <v>359.18853823960967</v>
       </c>
       <c r="Y144" s="117">
-        <f t="shared" ref="Y144" si="87">Y141+Y142-Y143</f>
+        <f t="shared" ref="Y144" si="90">Y141+Y142-Y143</f>
         <v>408.70258821286052</v>
       </c>
       <c r="Z144" s="117">
-        <f t="shared" ref="Z144:AA144" si="88">Z141+Z142-Z143</f>
+        <f t="shared" ref="Z144:AA144" si="91">Z141+Z142-Z143</f>
         <v>409.09425614670141</v>
       </c>
       <c r="AA144" s="117">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>499.75730935143241</v>
       </c>
       <c r="AC144" s="117">
-        <f t="shared" ref="AC144" si="89">AC141+AC142-AC143</f>
+        <f t="shared" ref="AC144" si="92">AC141+AC142-AC143</f>
         <v>82.9857136586363</v>
       </c>
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B145" s="20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M145" s="117">
         <f>M108/M49</f>
@@ -29332,35 +29052,35 @@
         <v>0.40763556496705489</v>
       </c>
       <c r="T145" s="117">
-        <f t="shared" ref="T145:AA145" si="90">T108/T49</f>
+        <f t="shared" ref="T145:AA145" si="93">T108/T49</f>
         <v>0.46020533025540444</v>
       </c>
       <c r="U145" s="117">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>0.50472209942531043</v>
       </c>
       <c r="V145" s="117">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>0.50378764984386015</v>
       </c>
       <c r="W145" s="117">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>0.50273667749308315</v>
       </c>
       <c r="X145" s="117">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>0.51854765383161527</v>
       </c>
       <c r="Y145" s="117">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>0.43762690832518614</v>
       </c>
       <c r="Z145" s="117">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>0.40763556496705489</v>
       </c>
       <c r="AA145" s="117">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>0.40424978005996731</v>
       </c>
       <c r="AC145" s="117">
@@ -29370,7 +29090,7 @@
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B146" s="20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M146" s="180">
         <f>(M108-M107)/M49</f>
@@ -29393,35 +29113,35 @@
         <v>5.7489871457197606E-3</v>
       </c>
       <c r="T146" s="180">
-        <f t="shared" ref="T146:AA146" si="91">(T108-T107)/T49</f>
+        <f t="shared" ref="T146:AA146" si="94">(T108-T107)/T49</f>
         <v>0.15562054691093388</v>
       </c>
       <c r="U146" s="180">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.20751115219225977</v>
       </c>
       <c r="V146" s="180">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.22731943185252343</v>
       </c>
       <c r="W146" s="180">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.2413488912947592</v>
       </c>
       <c r="X146" s="180">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.24690702164829439</v>
       </c>
       <c r="Y146" s="180">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>6.5343686545837401E-2</v>
       </c>
       <c r="Z146" s="180">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>5.7489871457197606E-3</v>
       </c>
       <c r="AA146" s="180">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>3.3763039301937268E-2</v>
       </c>
       <c r="AC146" s="180">
@@ -29431,7 +29151,7 @@
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B147" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M147" s="117">
         <f>(M107+M30)/M40</f>
@@ -29454,35 +29174,35 @@
         <v>1.5761520190023752</v>
       </c>
       <c r="T147" s="117">
-        <f t="shared" ref="T147:AA147" si="92">(T107+T30)/T40</f>
+        <f t="shared" ref="T147:AA147" si="95">(T107+T30)/T40</f>
         <v>1.1936178849096075</v>
       </c>
       <c r="U147" s="117">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>0.93014590858670609</v>
       </c>
       <c r="V147" s="117">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>0.86701620591039086</v>
       </c>
       <c r="W147" s="117">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>0.90566917386709767</v>
       </c>
       <c r="X147" s="117">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>0.82791854944803522</v>
       </c>
       <c r="Y147" s="117">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>1.32532433352943</v>
       </c>
       <c r="Z147" s="117">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>1.5761520190023752</v>
       </c>
       <c r="AA147" s="117">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>1.686293472196392</v>
       </c>
       <c r="AC147" s="117">
@@ -29492,7 +29212,7 @@
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B148" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M148" s="117">
         <f>M32/M40</f>
@@ -29515,35 +29235,35 @@
         <v>2.0170387965162311</v>
       </c>
       <c r="T148" s="117">
-        <f t="shared" ref="T148:AA148" si="93">T32/T40</f>
+        <f t="shared" ref="T148:AA148" si="96">T32/T40</f>
         <v>1.5870671620819934</v>
       </c>
       <c r="U148" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1.3122386871071419</v>
       </c>
       <c r="V148" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1.3268659227275277</v>
       </c>
       <c r="W148" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1.3095667309007273</v>
       </c>
       <c r="X148" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1.2404907624549562</v>
       </c>
       <c r="Y148" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1.6017277146484195</v>
       </c>
       <c r="Z148" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.0170387965162311</v>
       </c>
       <c r="AA148" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2.3119583410823878</v>
       </c>
       <c r="AC148" s="117">
@@ -29553,7 +29273,7 @@
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B149" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M149" s="182" t="str">
         <f>IF(M13&gt;=0,"N/A",IF(M12&lt;=0,"N/A",M12/-M13))</f>
@@ -29576,35 +29296,35 @@
         <v>N/A</v>
       </c>
       <c r="T149" s="182" t="str">
-        <f t="shared" ref="T149:AA149" si="94">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T149:AA149" si="97">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U149" s="182" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>N/A</v>
       </c>
       <c r="V149" s="182" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>N/A</v>
       </c>
       <c r="W149" s="182" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>N/A</v>
       </c>
       <c r="X149" s="182" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>N/A</v>
       </c>
       <c r="Y149" s="182" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>N/A</v>
       </c>
       <c r="Z149" s="182">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>5.9793814432989691</v>
       </c>
       <c r="AA149" s="182" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>N/A</v>
       </c>
       <c r="AC149" s="182" t="str">
@@ -29614,7 +29334,7 @@
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B150" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M150" s="71">
         <f>M117/Statement!M26</f>
@@ -29646,12 +29366,12 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-172.64516129032259</v>
+        <v>-182.12096774193549</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B151" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M151" s="71">
         <f>M117/(Statement!M5/Statement!M22)</f>
@@ -29683,12 +29403,12 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>9.3684638134032703</v>
+        <v>9.882661542324648</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B152" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M152" s="71">
         <f>M117/(Statement!M49/Statement!M75)</f>
@@ -29720,12 +29440,12 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.8295513223333391</v>
+        <v>5.094626191715891</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B153" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M153" s="143">
         <f>Statement!M117*Statement!M78</f>
@@ -29757,12 +29477,12 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>537983.04</v>
+        <v>567510.79</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B154" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M154" s="143">
         <f>M153+M108-M107+M48+M45</f>
@@ -29794,12 +29514,12 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>555339.04</v>
+        <v>584866.79</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B155" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M155" s="184">
         <f>M154/M5</f>
@@ -29831,12 +29551,12 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="184">
         <f ca="1">AC154/AC5</f>
-        <v>10.32939084500493</v>
+        <v>10.878611498614289</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B156" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M156" s="184">
         <f>M154/M12</f>
@@ -29868,12 +29588,12 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="184">
         <f ca="1">AC154/AC12</f>
-        <v>-109.98990691225985</v>
+        <v>-115.83814418696772</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B157" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M157" s="63">
         <f>M59-M54+M110+M65</f>
@@ -29896,35 +29616,35 @@
         <v>-7383</v>
       </c>
       <c r="T157" s="63">
-        <f t="shared" ref="T157:AA157" si="95">T59-T54+T110+T65</f>
+        <f t="shared" ref="T157:AA157" si="98">T59-T54+T110+T65</f>
         <v>0</v>
       </c>
       <c r="U157" s="63">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="V157" s="63">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="W157" s="63">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>-5054</v>
       </c>
       <c r="X157" s="63">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>-2164</v>
       </c>
       <c r="Y157" s="63">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>-427</v>
       </c>
       <c r="Z157" s="63">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>262</v>
       </c>
       <c r="AA157" s="63">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>-3161</v>
       </c>
       <c r="AC157" s="63">
@@ -29934,7 +29654,7 @@
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B158" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M158" s="63">
         <f>M109+M53+M110+M55+M57+M58+M56</f>
@@ -29971,26 +29691,26 @@
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B159" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M159" s="71">
         <f>M153/M157</f>
         <v>24.234480257856571</v>
       </c>
       <c r="N159" s="71">
-        <f t="shared" ref="N159:Q159" si="96">N153/N157</f>
+        <f t="shared" ref="N159:Q159" si="99">N153/N157</f>
         <v>-8.7516835473323233</v>
       </c>
       <c r="O159" s="71">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-12.197995202193283</v>
       </c>
       <c r="P159" s="71">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-4.6102486100912623</v>
       </c>
       <c r="Q159" s="71">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>-24.491263713937425</v>
       </c>
       <c r="T159" s="49"/>
@@ -30002,32 +29722,32 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
-        <f t="shared" ref="AC159:AC160" ca="1" si="97">AC153/AC157</f>
-        <v>-97.993267759562855</v>
+        <f t="shared" ref="AC159:AC160" ca="1" si="100">AC153/AC157</f>
+        <v>-103.37172859744992</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B160" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M160" s="71">
         <f>M154/M158</f>
         <v>39.164320117414455</v>
       </c>
       <c r="N160" s="71">
-        <f t="shared" ref="N160:Q160" si="98">N154/N158</f>
+        <f t="shared" ref="N160:Q160" si="101">N154/N158</f>
         <v>-8.5390374025602505</v>
       </c>
       <c r="O160" s="71">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>-14.216825072184793</v>
       </c>
       <c r="P160" s="71">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>-5.0227744165946415</v>
       </c>
       <c r="Q160" s="71">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>-28.047384437038112</v>
       </c>
       <c r="T160" s="49"/>
@@ -30039,32 +29759,32 @@
       <c r="Z160" s="49"/>
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
-        <f t="shared" ca="1" si="97"/>
-        <v>-64.777678758894211</v>
+        <f t="shared" ca="1" si="100"/>
+        <v>-68.221951475562818</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B161" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M161" s="73">
         <f>M157/M153</f>
         <v>4.1263521617131038E-2</v>
       </c>
       <c r="N161" s="73">
-        <f t="shared" ref="N161:Q161" si="99">N157/N153</f>
+        <f t="shared" ref="N161:Q161" si="102">N157/N153</f>
         <v>-0.11426372932609277</v>
       </c>
       <c r="O161" s="73">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>-8.1980684811237922E-2</v>
       </c>
       <c r="P161" s="73">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>-0.21690804218478027</v>
       </c>
       <c r="Q161" s="73">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>-4.0830886134753538E-2</v>
       </c>
       <c r="T161" s="49"/>
@@ -30076,13 +29796,13 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
-        <f t="shared" ref="AC161" ca="1" si="100">AC157/AC153</f>
-        <v>-1.0204782663780627E-2</v>
+        <f t="shared" ref="AC161" ca="1" si="103">AC157/AC153</f>
+        <v>-9.67382488005206E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B162" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M162" s="73">
         <f>M26/M117</f>
@@ -30114,12 +29834,12 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-5.7922272047832585E-3</v>
+        <v>-5.490855953593411E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B163" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M163" s="154">
         <f>M82/M117</f>
@@ -30156,7 +29876,7 @@
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B164" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M164" s="154">
         <f>-M63/M153</f>
@@ -30193,7 +29913,7 @@
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B165" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M165" s="154">
         <f>-(M63+M64)/M153</f>
@@ -30230,7 +29950,7 @@
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B166" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M166" s="154">
         <f>M158/M5</f>
@@ -30267,7 +29987,7 @@
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B167" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M167" s="154">
         <f>M157/M5</f>
@@ -30304,7 +30024,7 @@
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B168" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M168" s="154">
         <f>-M64/M157</f>
@@ -30341,7 +30061,7 @@
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B169" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M169" s="154">
         <f>-M63/M157</f>
@@ -30378,7 +30098,7 @@
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B170" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M170" s="154">
         <f>(-M64-M63)/M157</f>
@@ -30415,7 +30135,7 @@
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B171" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M171" s="154">
         <f>M80/M78</f>
@@ -30452,7 +30172,7 @@
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B172" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M172" s="71">
         <f>M107/M75</f>
@@ -30475,35 +30195,35 @@
         <v>9.1947947947947952</v>
       </c>
       <c r="T172" s="71">
-        <f t="shared" ref="T172:AA172" si="101">T107/T75</f>
+        <f t="shared" ref="T172:AA172" si="104">T107/T75</f>
         <v>8.2079045837231064</v>
       </c>
       <c r="U172" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>6.8587989798284257</v>
       </c>
       <c r="V172" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>6.3383371824480372</v>
       </c>
       <c r="W172" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>5.977762494268684</v>
       </c>
       <c r="X172" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>6.0747087045921866</v>
       </c>
       <c r="Y172" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>8.3023060796645698</v>
       </c>
       <c r="Z172" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>9.1947947947947952</v>
       </c>
       <c r="AA172" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>8.2113012335853561</v>
       </c>
       <c r="AC172" s="71">
@@ -30513,7 +30233,7 @@
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B173" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M173" s="154">
         <f>M54/M59</f>
@@ -30536,27 +30256,27 @@
         <v>0.25100546560791998</v>
       </c>
       <c r="T173" s="154" t="e">
-        <f t="shared" ref="T173:Y173" si="102">T54/T59</f>
+        <f t="shared" ref="T173:Y173" si="105">T54/T59</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U173" s="154" t="e">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V173" s="154" t="e">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W173" s="154">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>0.84132841328413288</v>
       </c>
       <c r="X173" s="154">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>0.32390243902439025</v>
       </c>
       <c r="Y173" s="154">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>0.2152395915161037</v>
       </c>
       <c r="Z173" s="154">
@@ -30574,7 +30294,7 @@
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B174" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M174" s="154">
         <f>M54/M5</f>
@@ -30597,27 +30317,27 @@
         <v>4.6052258149963103E-2</v>
       </c>
       <c r="T174" s="154">
-        <f t="shared" ref="T174:Y174" si="103">T54/T5</f>
+        <f t="shared" ref="T174:Y174" si="106">T54/T5</f>
         <v>0</v>
       </c>
       <c r="U174" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="V174" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="W174" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>5.3998578984763561E-2</v>
       </c>
       <c r="X174" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>5.1636985768722297E-2</v>
       </c>
       <c r="Y174" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>4.0137698674284038E-2</v>
       </c>
       <c r="Z174" s="154">
@@ -30635,7 +30355,7 @@
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B175" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M175" s="71">
         <f>(M107-M108)/M75</f>
@@ -30658,35 +30378,35 @@
         <v>-0.13153153153153152</v>
       </c>
       <c r="T175" s="71">
-        <f t="shared" ref="T175:AA175" si="104">(T107-T108)/T75</f>
+        <f t="shared" ref="T175:AA175" si="107">(T107-T108)/T75</f>
         <v>-4.1936389148737137</v>
       </c>
       <c r="U175" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>-4.7887781126825875</v>
       </c>
       <c r="V175" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>-5.2115473441108549</v>
       </c>
       <c r="W175" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>-5.5194864740944523</v>
       </c>
       <c r="X175" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>-5.5215901302261825</v>
       </c>
       <c r="Y175" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>-1.4572327044025157</v>
       </c>
       <c r="Z175" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>-0.13153153153153152</v>
       </c>
       <c r="AA175" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>-0.74830879426979702</v>
       </c>
       <c r="AC175" s="71">
@@ -30696,7 +30416,7 @@
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B176" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M176" s="154">
         <f>(M107-M108)/M153</f>
@@ -30728,12 +30448,12 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-6.9909267028194786E-3</v>
+        <v>-6.6271867711977768E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B177" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M177" s="154">
         <f>-M110/M5</f>
@@ -30756,35 +30476,35 @@
         <v>0.27710820577829071</v>
       </c>
       <c r="T177" s="154">
-        <f t="shared" ref="T177:AA177" si="105">-T110/T5</f>
+        <f t="shared" ref="T177:AA177" si="108">-T110/T5</f>
         <v>0</v>
       </c>
       <c r="U177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="V177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="W177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.40917344280413676</v>
       </c>
       <c r="X177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.27607123415506651</v>
       </c>
       <c r="Y177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.17761664103127517</v>
       </c>
       <c r="Z177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.25508263858417435</v>
       </c>
       <c r="AA177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.2678058481255064</v>
       </c>
       <c r="AC177" s="154">
@@ -30794,7 +30514,7 @@
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B178" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M178" s="154">
         <f>-(M110/M59)</f>
@@ -30817,27 +30537,27 @@
         <v>1.5103640301124059</v>
       </c>
       <c r="T178" s="154" t="e">
-        <f t="shared" ref="T178:Y178" si="106">-(T110/T59)</f>
+        <f t="shared" ref="T178:Y178" si="109">-(T110/T59)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U178" s="154" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V178" s="154" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W178" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>6.375153751537515</v>
       </c>
       <c r="X178" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>1.7317073170731707</v>
       </c>
       <c r="Y178" s="154">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>0.95247446975648076</v>
       </c>
       <c r="Z178" s="154">
@@ -30855,7 +30575,7 @@
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B179" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M179" s="154">
         <f>-M110/M53</f>
@@ -30878,27 +30598,27 @@
         <v>1.2511532547411583</v>
       </c>
       <c r="T179" s="154" t="e">
-        <f t="shared" ref="T179:Y179" si="107">-T110/T53</f>
+        <f t="shared" ref="T179:Y179" si="110">-T110/T53</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U179" s="154" t="e">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V179" s="154" t="e">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W179" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>1.9382946896035902</v>
       </c>
       <c r="X179" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>1.1782276800531033</v>
       </c>
       <c r="Y179" s="154">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.81049465240641716</v>
       </c>
       <c r="Z179" s="154">
@@ -30916,7 +30636,7 @@
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M180" s="71">
         <f>M37/M5</f>
@@ -30967,7 +30687,7 @@
     </row>
     <row r="184" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B184" s="217" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C184" s="61"/>
       <c r="D184" s="61"/>
@@ -31025,7 +30745,7 @@
     </row>
     <row r="185" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B185" s="217" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C185" s="61"/>
       <c r="D185" s="61"/>
@@ -31080,13 +30800,13 @@
         <v>5052</v>
       </c>
       <c r="AC185" s="61">
-        <f t="shared" ref="AC185:AC194" si="108">SUM(X185:AA185)</f>
+        <f t="shared" ref="AC185:AC194" si="111">SUM(X185:AA185)</f>
         <v>17845</v>
       </c>
     </row>
     <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C186" s="61"/>
       <c r="D186" s="61"/>
@@ -31141,13 +30861,13 @@
         <v>12779</v>
       </c>
       <c r="AC186" s="61">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>50171</v>
       </c>
     </row>
     <row r="187" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B187" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C187" s="21"/>
       <c r="D187" s="21"/>
@@ -31199,13 +30919,13 @@
         <v>5421</v>
       </c>
       <c r="AC187" s="61">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>18580</v>
       </c>
     </row>
     <row r="188" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B188" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C188" s="61"/>
       <c r="D188" s="61"/>
@@ -31260,7 +30980,7 @@
         <v>628</v>
       </c>
       <c r="AC188" s="61">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>3248</v>
       </c>
     </row>
@@ -31292,7 +31012,7 @@
     </row>
     <row r="190" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B190" s="217" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C190" s="61"/>
       <c r="D190" s="61"/>
@@ -31347,13 +31067,13 @@
         <v>2516</v>
       </c>
       <c r="AC190" s="61">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>20159</v>
       </c>
     </row>
     <row r="191" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B191" s="217" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C191" s="61"/>
       <c r="D191" s="61"/>
@@ -31408,13 +31128,13 @@
         <v>3510</v>
       </c>
       <c r="AC191" s="61">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>13456</v>
       </c>
     </row>
     <row r="192" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B192" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C192" s="61"/>
       <c r="D192" s="61"/>
@@ -31469,13 +31189,13 @@
         <v>8721</v>
       </c>
       <c r="AC192" s="61">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>36310</v>
       </c>
     </row>
     <row r="193" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B193" s="20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C193" s="61"/>
       <c r="D193" s="61"/>
@@ -31530,13 +31250,13 @@
         <v>7858</v>
       </c>
       <c r="AC193" s="61">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>29015</v>
       </c>
     </row>
     <row r="194" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B194" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C194" s="61"/>
       <c r="D194" s="61"/>
@@ -31591,7 +31311,7 @@
         <v>526</v>
       </c>
       <c r="AC194" s="61">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>2985</v>
       </c>
     </row>
@@ -31613,7 +31333,7 @@
     </row>
     <row r="197" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B197" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C197" s="171"/>
       <c r="D197" s="171"/>
@@ -31642,7 +31362,7 @@
     </row>
     <row r="198" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B198" s="217" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C198" s="80"/>
       <c r="D198" s="80"/>
@@ -31655,293 +31375,293 @@
       <c r="K198" s="80"/>
       <c r="L198" s="80"/>
       <c r="M198" s="80">
-        <f t="shared" ref="M198:Q202" si="109">IF(L184=0,
+        <f t="shared" ref="M198:Q202" si="112">IF(L184=0,
 IF(M184=0,0,IF(M184&gt;0,1,-1)),
 (M184-L184)/ABS(L184)
 )</f>
         <v>1</v>
       </c>
       <c r="N198" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-0.22657676298045326</v>
       </c>
       <c r="O198" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-7.9155257608661447E-2</v>
       </c>
       <c r="P198" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>0.139722469068289</v>
       </c>
       <c r="Q198" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-3.3527259641336293E-2</v>
       </c>
       <c r="T198" s="80">
-        <f t="shared" ref="T198:AA202" si="110">IF(S184=0,
+        <f t="shared" ref="T198:AA202" si="113">IF(S184=0,
 IF(T184=0,0,IF(T184&gt;0,1,-1)),
 (T184-S184)/ABS(S184)
 )</f>
         <v>1</v>
       </c>
       <c r="U198" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>2.2104875353063983E-3</v>
       </c>
       <c r="V198" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>7.4500673937017522E-2</v>
       </c>
       <c r="W198" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-0.13000342114266164</v>
       </c>
       <c r="X198" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>3.1721064359680168E-2</v>
       </c>
       <c r="Y198" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>8.436030999872951E-2</v>
       </c>
       <c r="Z198" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-4.0070298769771528E-2</v>
       </c>
       <c r="AA198" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-5.687782253142927E-2</v>
       </c>
       <c r="AC198" s="49"/>
     </row>
     <row r="199" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B199" s="217" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M199" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
       <c r="N199" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-8.4923946253162061E-2</v>
       </c>
       <c r="O199" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-0.23547784878293962</v>
       </c>
       <c r="P199" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-0.242779995304062</v>
       </c>
       <c r="Q199" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>4.9240310077519382E-2</v>
       </c>
       <c r="T199" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1</v>
       </c>
       <c r="U199" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>8.8304862023653091E-2</v>
       </c>
       <c r="V199" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>5.0712388312001935E-2</v>
       </c>
       <c r="W199" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-5.1712250057458053E-2</v>
       </c>
       <c r="X199" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-4.5322346097915654E-2</v>
       </c>
       <c r="Y199" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>4.5189134298045192E-2</v>
       </c>
       <c r="Z199" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.15059509351469516</v>
       </c>
       <c r="AA199" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>6.6497783407219763E-2</v>
       </c>
       <c r="AC199" s="49"/>
     </row>
     <row r="200" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B200" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M200" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
       <c r="N200" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-0.16628914988814317</v>
       </c>
       <c r="O200" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-0.1521793818236705</v>
       </c>
       <c r="P200" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-2.1403279726227919E-2</v>
       </c>
       <c r="Q200" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-6.5492915041135214E-3</v>
       </c>
       <c r="T200" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1</v>
       </c>
       <c r="U200" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>2.9628389688650822E-2</v>
       </c>
       <c r="V200" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>6.6493253129572424E-2</v>
       </c>
       <c r="W200" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-0.10403963414634146</v>
       </c>
       <c r="X200" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>4.6788600595491277E-3</v>
       </c>
       <c r="Y200" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>7.1295512277730733E-2</v>
       </c>
       <c r="Z200" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>2.1972810622826432E-2</v>
       </c>
       <c r="AA200" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-1.1678267594740912E-2</v>
       </c>
       <c r="AC200" s="49"/>
     </row>
     <row r="201" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B201" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M201" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
       <c r="N201" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>0.35158501440922191</v>
       </c>
       <c r="O201" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>1.0298507462686568</v>
       </c>
       <c r="P201" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>17.190126050420169</v>
       </c>
       <c r="Q201" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>2.9393081942599757E-2</v>
       </c>
       <c r="T201" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1</v>
       </c>
       <c r="U201" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1.3311536665109761E-2</v>
       </c>
       <c r="V201" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>2.3046784973496196E-4</v>
       </c>
       <c r="W201" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>7.5345622119815672E-2</v>
       </c>
       <c r="X201" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-5.3567602314120423E-2</v>
       </c>
       <c r="Y201" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-4.1204437400950873E-2</v>
       </c>
       <c r="Z201" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>6.4226682408500588E-2</v>
       </c>
       <c r="AA201" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.2027956512092301</v>
       </c>
       <c r="AC201" s="49"/>
     </row>
     <row r="202" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B202" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M202" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>1</v>
       </c>
       <c r="N202" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-0.58669833729216148</v>
       </c>
       <c r="O202" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-7.9445571331981074E-2</v>
       </c>
       <c r="P202" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>0.32243848696290855</v>
       </c>
       <c r="Q202" s="80">
-        <f t="shared" si="109"/>
+        <f t="shared" si="112"/>
         <v>-1.0552624271035824E-2</v>
       </c>
       <c r="T202" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>1</v>
       </c>
       <c r="U202" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>9.4211123723041995E-2</v>
       </c>
       <c r="V202" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.1545643153526971</v>
       </c>
       <c r="W202" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-0.1527403414195867</v>
       </c>
       <c r="X202" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>0.11664899257688228</v>
       </c>
       <c r="Y202" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-5.6980056980056981E-2</v>
       </c>
       <c r="Z202" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>-0.42195367573011078</v>
       </c>
       <c r="AA202" s="80">
-        <f t="shared" si="110"/>
+        <f t="shared" si="113"/>
         <v>9.4076655052264813E-2</v>
       </c>
       <c r="AC202" s="49"/>
@@ -31951,7 +31671,7 @@
     </row>
     <row r="205" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B205" s="14" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C205" s="171"/>
       <c r="D205" s="171"/>
@@ -31980,7 +31700,7 @@
     </row>
     <row r="206" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B206" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C206" s="80"/>
       <c r="D206" s="80"/>
@@ -32042,7 +31762,7 @@
     </row>
     <row r="209" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B209" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C209" s="171"/>
       <c r="D209" s="171"/>
@@ -32071,7 +31791,7 @@
     </row>
     <row r="210" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B210" s="20" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M210" s="143">
         <v>100</v>
@@ -32081,15 +31801,15 @@
         <v>51.510426817384527</v>
       </c>
       <c r="O210" s="143">
-        <f t="shared" ref="O210:Q210" si="111">100*(1+((O117-$M117)/ABS($M117)))</f>
+        <f t="shared" ref="O210:Q210" si="114">100*(1+((O117-$M117)/ABS($M117)))</f>
         <v>97.934125901383737</v>
       </c>
       <c r="P210" s="143">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>39.563437926330145</v>
       </c>
       <c r="Q210" s="143">
-        <f t="shared" si="111"/>
+        <f t="shared" si="114"/>
         <v>70.551549405573965</v>
       </c>
       <c r="T210" s="49"/>
@@ -32104,7 +31824,7 @@
     </row>
     <row r="211" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B211" s="20" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M211" s="143">
         <v>100</v>
@@ -32114,15 +31834,15 @@
         <v>79.790949584936214</v>
       </c>
       <c r="O211" s="143">
-        <f t="shared" ref="O211:Q211" si="112">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O211:Q211" si="115">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>68.6221907268678</v>
       </c>
       <c r="P211" s="143">
-        <f t="shared" si="112"/>
+        <f t="shared" si="115"/>
         <v>67.196041708847943</v>
       </c>
       <c r="Q211" s="143">
-        <f t="shared" si="112"/>
+        <f t="shared" si="115"/>
         <v>66.882212998582702</v>
       </c>
       <c r="T211" s="49"/>
@@ -32137,7 +31857,7 @@
     </row>
     <row r="212" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B212" s="20" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M212" s="143">
         <v>100</v>
@@ -32147,15 +31867,15 @@
         <v>39.917695473251023</v>
       </c>
       <c r="O212" s="143">
-        <f t="shared" ref="O212:Q212" si="113">100*(1+((O26-$M26)/ABS($M26)))</f>
+        <f t="shared" ref="O212:Q212" si="116">100*(1+((O26-$M26)/ABS($M26)))</f>
         <v>8.2304526748971263</v>
       </c>
       <c r="P212" s="143">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>-90.123456790123456</v>
       </c>
       <c r="Q212" s="143">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>-1.2345679012345512</v>
       </c>
       <c r="T212" s="49"/>
@@ -32184,7 +31904,7 @@
     </row>
     <row r="216" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B216" s="20" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M216" s="61">
         <v>0</v>
@@ -32232,7 +31952,7 @@
     </row>
     <row r="217" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B217" s="20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M217" s="61">
         <v>0</v>
@@ -32252,35 +31972,35 @@
         <v>143</v>
       </c>
       <c r="T217" s="61">
-        <f t="shared" ref="T217:AA217" si="114">T187+T216</f>
+        <f t="shared" ref="T217:AA217" si="117">T187+T216</f>
         <v>4</v>
       </c>
       <c r="U217" s="61">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>18</v>
       </c>
       <c r="V217" s="61">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>27</v>
       </c>
       <c r="W217" s="61">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>-31</v>
       </c>
       <c r="X217" s="61">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>-4</v>
       </c>
       <c r="Y217" s="61">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>8</v>
       </c>
       <c r="Z217" s="61">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>170</v>
       </c>
       <c r="AA217" s="61">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>170</v>
       </c>
       <c r="AC217" s="63">
@@ -32315,7 +32035,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -32338,16 +32058,16 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="81" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="230" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="230"/>
       <c r="E4" s="230" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F4" s="230"/>
       <c r="G4" s="230"/>
@@ -32358,23 +32078,23 @@
       </c>
       <c r="C5" s="173">
         <f ca="1">Overview!C5</f>
-        <v>107.04</v>
+        <v>112.91500000000001</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
+        <v>243</v>
+      </c>
+      <c r="G5" s="131" t="s">
         <v>244</v>
-      </c>
-      <c r="G5" s="131" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C6" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>537983.04</v>
+        <v>567510.79</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32390,11 +32110,11 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C7" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>555339.04</v>
+        <v>584866.79</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32410,14 +32130,14 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C8" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>-172.64516129032259</v>
+        <v>-182.12096774193549</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F8" s="179" t="str">
         <f>IF(OR(Statement!M26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(4, Statement!M26, Statement!Q26))</f>
@@ -32430,14 +32150,14 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C9" s="175">
         <f ca="1">Statement!AC151</f>
-        <v>9.3684638134032703</v>
+        <v>9.882661542324648</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F9" s="179">
         <f>IF(Statement!M82&lt;=0,"N/A",_xlfn.RRI(4,Statement!M82,Statement!Q82))</f>
@@ -32450,11 +32170,11 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C10" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>4.8295513223333391</v>
+        <v>5.094626191715891</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32470,20 +32190,20 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C11" s="175">
         <f ca="1">Statement!AC155</f>
-        <v>10.32939084500493</v>
+        <v>10.878611498614289</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C12" s="175">
         <f ca="1">Statement!AC156</f>
-        <v>-109.98990691225985</v>
+        <v>-115.83814418696772</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -32492,7 +32212,7 @@
       </c>
       <c r="C15" s="230"/>
       <c r="E15" s="230" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F15" s="230"/>
     </row>
@@ -32521,7 +32241,7 @@
         <v>-9.391217007979466E-2</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F17" s="174">
         <f>Statement!AC59</f>
@@ -32537,7 +32257,7 @@
         <v>-6.2645313691572266E-2</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F18" s="178" t="str">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
@@ -32546,11 +32266,11 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="230" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C21" s="230"/>
       <c r="E21" s="230" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F21" s="230"/>
     </row>
@@ -32622,11 +32342,11 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="230" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C29" s="230"/>
       <c r="E29" s="230" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F29" s="230"/>
     </row>
@@ -32639,7 +32359,7 @@
         <v>27.604300355262914</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F30" s="181">
         <f>Statement!AC145</f>
@@ -32655,7 +32375,7 @@
         <v>130.6568144499179</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F31" s="181">
         <f>Statement!AC146</f>
@@ -32671,7 +32391,7 @@
         <v>75.275401146544525</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F32" s="181">
         <f>Statement!AC148</f>
@@ -32687,7 +32407,7 @@
         <v>82.9857136586363</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F33" s="181">
         <f>Statement!AC147</f>
@@ -32696,7 +32416,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E34" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F34" s="183" t="str">
         <f>Statement!AC149</f>
@@ -32705,24 +32425,24 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="230" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C37" s="230"/>
       <c r="E37" s="230" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F37" s="230"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C38" s="176">
         <f ca="1">Statement!AC162</f>
-        <v>-5.7922272047832585E-3</v>
+        <v>-5.490855953593411E-3</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F38" s="176">
         <f>Statement!AC168</f>
@@ -32731,14 +32451,14 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C39" s="216">
         <f ca="1">Statement!AC161</f>
-        <v>-1.0204782663780627E-2</v>
+        <v>-9.67382488005206E-3</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F39" s="176">
         <f>Statement!AC169</f>
@@ -32747,14 +32467,14 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C40" s="176">
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F40" s="176">
         <f>Statement!AC170</f>
@@ -32763,7 +32483,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C41" s="176">
         <f ca="1">Statement!AC164</f>
@@ -32772,7 +32492,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C42" s="176">
         <f ca="1">Statement!AC165</f>
@@ -32781,24 +32501,24 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="230" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C45" s="230"/>
       <c r="E45" s="230" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F45" s="230"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C46" s="176">
         <f>Statement!AC171</f>
         <v>5.9689614007162755E-4</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F46" s="175">
         <f>Statement!AC172</f>
@@ -32807,7 +32527,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F47" s="175">
         <f>Statement!AC175</f>
@@ -32816,33 +32536,33 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F48" s="176">
         <f ca="1">Statement!AC176</f>
-        <v>-6.9909267028194786E-3</v>
+        <v>-6.6271867711977768E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="230" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C51" s="230"/>
       <c r="E51" s="230" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F51" s="230"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C52" s="176">
         <f>Statement!AC173</f>
         <v>0.2375751503006012</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F52" s="176">
         <f>Statement!AC177</f>
@@ -32851,14 +32571,14 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C53" s="176">
         <f>Statement!AC174</f>
         <v>4.4100961627885349E-2</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F53" s="176">
         <f>Statement!AC178</f>
@@ -32867,7 +32587,7 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F54" s="176">
         <f>Statement!AC179</f>
@@ -32964,7 +32684,7 @@
     </row>
     <row r="5" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -32999,12 +32719,12 @@
       </c>
       <c r="I6" s="173">
         <f ca="1">Statement!AC116</f>
-        <v>107.04</v>
+        <v>112.91500000000001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C7" s="174">
         <f>Statement!M153</f>
@@ -33028,12 +32748,12 @@
       </c>
       <c r="I7" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>537983.04</v>
+        <v>567510.79</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C8" s="174">
         <f>Statement!M154</f>
@@ -33057,12 +32777,12 @@
       </c>
       <c r="I8" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>555339.04</v>
+        <v>584866.79</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C9" s="175">
         <f>Statement!M150</f>
@@ -33086,12 +32806,12 @@
       </c>
       <c r="I9" s="175">
         <f ca="1">Statement!AC150</f>
-        <v>-172.64516129032259</v>
+        <v>-182.12096774193549</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="175">
         <f>Statement!M151</f>
@@ -33115,12 +32835,12 @@
       </c>
       <c r="I10" s="175">
         <f ca="1">Statement!AC151</f>
-        <v>9.3684638134032703</v>
+        <v>9.882661542324648</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C11" s="175">
         <f>Statement!M152</f>
@@ -33144,12 +32864,12 @@
       </c>
       <c r="I11" s="175">
         <f ca="1">Statement!AC152</f>
-        <v>4.8295513223333391</v>
+        <v>5.094626191715891</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C12" s="175">
         <f>Statement!M155</f>
@@ -33173,12 +32893,12 @@
       </c>
       <c r="I12" s="175">
         <f ca="1">Statement!AC155</f>
-        <v>10.32939084500493</v>
+        <v>10.878611498614289</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C13" s="175">
         <f>Statement!M156</f>
@@ -33202,7 +32922,7 @@
       </c>
       <c r="I13" s="175">
         <f ca="1">Statement!AC156</f>
-        <v>-109.98990691225985</v>
+        <v>-115.83814418696772</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33305,7 +33025,7 @@
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -33345,7 +33065,7 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C22" s="178">
         <f>Statement!M59</f>
@@ -33374,7 +33094,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C23" s="196">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
@@ -33403,7 +33123,7 @@
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -33559,7 +33279,7 @@
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -33657,7 +33377,7 @@
     </row>
     <row r="37" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -33784,7 +33504,7 @@
     </row>
     <row r="43" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -33795,7 +33515,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C44" s="181">
         <f>Statement!M145</f>
@@ -33824,7 +33544,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C45" s="181">
         <f>Statement!M146</f>
@@ -33853,7 +33573,7 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C46" s="181">
         <f>Statement!M147</f>
@@ -33882,7 +33602,7 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C47" s="181">
         <f>Statement!M148</f>
@@ -33911,7 +33631,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C48" s="183" t="str">
         <f>Statement!M149</f>
@@ -33940,7 +33660,7 @@
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -33951,7 +33671,7 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C51" s="176">
         <f>Statement!M162</f>
@@ -33975,12 +33695,12 @@
       </c>
       <c r="I51" s="176">
         <f ca="1">Statement!AC162</f>
-        <v>-5.7922272047832585E-3</v>
+        <v>-5.490855953593411E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C52" s="176">
         <f>Statement!M161</f>
@@ -34004,12 +33724,12 @@
       </c>
       <c r="I52" s="176">
         <f ca="1">Statement!AC161</f>
-        <v>-1.0204782663780627E-2</v>
+        <v>-9.67382488005206E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C53" s="176">
         <f>Statement!M163</f>
@@ -34038,7 +33758,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C54" s="176">
         <f>Statement!M164</f>
@@ -34067,7 +33787,7 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C55" s="176">
         <f>Statement!M165</f>
@@ -34096,7 +33816,7 @@
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -34107,7 +33827,7 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C58" s="176">
         <f>Statement!M168</f>
@@ -34136,7 +33856,7 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C59" s="176">
         <f>Statement!M169</f>
@@ -34165,7 +33885,7 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C60" s="176">
         <f>Statement!M170</f>
@@ -34194,7 +33914,7 @@
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -34205,7 +33925,7 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C63" s="176">
         <f>Statement!M171</f>
@@ -34234,7 +33954,7 @@
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -34245,7 +33965,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C66" s="175">
         <f>Statement!M172</f>
@@ -34274,7 +33994,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C67" s="175">
         <f>Statement!M175</f>
@@ -34303,7 +34023,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="197">
         <f>Statement!M176</f>
@@ -34327,12 +34047,12 @@
       </c>
       <c r="I68" s="197">
         <f ca="1">Statement!AC176</f>
-        <v>-6.9909267028194786E-3</v>
+        <v>-6.6271867711977768E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -34343,7 +34063,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C71" s="176">
         <f>Statement!M173</f>
@@ -34372,7 +34092,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="176">
         <f>Statement!M174</f>
@@ -34401,7 +34121,7 @@
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -34412,7 +34132,7 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C75" s="176">
         <f>Statement!M177</f>
@@ -34441,7 +34161,7 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C76" s="176">
         <f>Statement!M178</f>
@@ -34470,7 +34190,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C77" s="176">
         <f>Statement!M179</f>
@@ -34614,7 +34334,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C84" s="176">
         <f>Statement!M96</f>
@@ -34640,7 +34360,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C85" s="176">
         <f>Statement!M98</f>
@@ -34666,7 +34386,7 @@
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -34677,7 +34397,7 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="217" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C89" s="176">
         <f>Statement!M198</f>
@@ -34703,7 +34423,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="217" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C90" s="176">
         <f>Statement!M199</f>
@@ -34729,7 +34449,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C91" s="176">
         <f>Statement!M200</f>
@@ -34755,7 +34475,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C92" s="176">
         <f>Statement!M201</f>
@@ -34781,7 +34501,7 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B93" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C93" s="176">
         <f>Statement!M202</f>
@@ -34807,7 +34527,7 @@
     </row>
     <row r="95" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B95" s="14" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -34818,7 +34538,7 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B96" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C96" s="176">
         <f>Statement!M206</f>
@@ -34866,11 +34586,11 @@
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
       <c r="C3" s="236" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D3" s="237"/>
       <c r="F3" s="238" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G3" s="237"/>
     </row>
@@ -34895,7 +34615,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
@@ -34937,7 +34657,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C7" s="234">
         <f>Statement!AA89</f>
@@ -34976,7 +34696,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C9" s="234">
         <f>Statement!AA90</f>
@@ -35015,7 +34735,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C11" s="234">
         <f>Statement!AA91</f>
@@ -35054,7 +34774,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C13" s="234">
         <f>Statement!AA95</f>
@@ -35072,7 +34792,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C14" s="201">
         <f>Statement!Z12</f>
@@ -35093,7 +34813,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C15" s="234">
         <f>Statement!AA96</f>
@@ -35132,7 +34852,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C17" s="234">
         <f>Statement!AA98</f>
@@ -35150,7 +34870,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="208" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C18" s="201">
         <f>Statement!Z22</f>
@@ -35171,7 +34891,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C19" s="234">
         <f>IF(C18=0,
@@ -35213,7 +34933,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C21" s="234">
         <f>IF(C20=0,
@@ -35234,7 +34954,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
@@ -35255,7 +34975,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C24" s="201">
         <f>Statement!Z184</f>
@@ -35276,7 +34996,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C25" s="234">
         <f>IF(C24=0,
@@ -35297,7 +35017,7 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C26" s="201">
         <f>Statement!Z185</f>
@@ -35318,7 +35038,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C27" s="234">
         <f>IF(C26=0,
@@ -35339,7 +35059,7 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C28" s="201">
         <f>Statement!Z186</f>
@@ -35360,7 +35080,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C29" s="234">
         <f>IF(C28=0,
@@ -35381,7 +35101,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C30" s="201">
         <f>Statement!Z187</f>
@@ -35402,7 +35122,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C31" s="234">
         <f>IF(C30=0,
@@ -35423,7 +35143,7 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C32" s="201">
         <f>Statement!Z188</f>
@@ -35444,7 +35164,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C33" s="234">
         <f>IF(C32=0,
@@ -35734,7 +35454,7 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C60" s="63">
         <f>Statement!H157</f>
@@ -35779,7 +35499,7 @@
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C61" s="63">
         <f>Statement!H158</f>
@@ -35959,7 +35679,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C65" s="63">
         <f>Statement!H186</f>
@@ -36004,7 +35724,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C66" s="63">
         <f>Statement!H187</f>
@@ -36049,7 +35769,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C67" s="63">
         <f>Statement!H188</f>
@@ -36537,7 +36257,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C63" s="63">
         <f>Statement!T186</f>
@@ -36574,7 +36294,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C64" s="63">
         <f>Statement!T187</f>
@@ -36611,7 +36331,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C65" s="63">
         <f>Statement!T188</f>
@@ -36648,7 +36368,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C66" s="63">
         <f>Statement!T157</f>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF9D38-C0C9-8E40-B2A0-D4BAAEE199CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DE51EC-5746-BE4A-8984-D2E34527EEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="405">
   <si>
     <t>Ticker</t>
   </si>
@@ -1970,7 +1970,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2276,6 +2276,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2809,6 +2810,301 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>FCFE</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Quarter'!$C$66:$J$66</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_);\(#,##0\)</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5054</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2164</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-427</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-3161</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C6C3-9E46-BD59-26236BD1964D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1163393471"/>
+        <c:axId val="1163381375"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1163393471"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1163381375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1163381375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);\(#,##0\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1163393471"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -4611,6 +4907,368 @@
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Price 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$71:$L$71</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51.510426817384527</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>97.934125901383737</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39.563437926330145</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70.551549405573965</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1CDB-5840-BA36-D267E632E511}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Revenue 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$72:$L$72</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79.790949584936214</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68.6221907268678</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67.196041708847943</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>66.882212998582702</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1CDB-5840-BA36-D267E632E511}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>EPS 5y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graphs Year'!$H$73:$L$73</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39.917695473251023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2304526748971263</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-90.123456790123456</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.2345679012345512</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1CDB-5840-BA36-D267E632E511}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1848432767"/>
+        <c:axId val="1848427391"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1848432767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1848427391"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1848427391"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1848432767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -5045,7 +5703,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5496,7 +6154,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6046,302 +6704,47 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>FCFE</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="34925" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>'Graphs Quarter'!$C$66:$J$66</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0_);\(#,##0\)</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-5054</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-2164</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-427</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>262</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-3161</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C6C3-9E46-BD59-26236BD1964D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1163393471"/>
-        <c:axId val="1163381375"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1163393471"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1163381375"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1163381375"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="#,##0_);\(#,##0\)" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1163393471"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7192,6 +7595,502 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -9182,7 +10081,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9204,11 +10103,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
             <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9285,7 +10184,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
@@ -9295,7 +10194,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -9305,7 +10204,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="34925" cap="rnd">
@@ -9325,7 +10224,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9344,7 +10243,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -9381,7 +10280,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9405,7 +10304,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9424,7 +10323,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -9442,7 +10341,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -9450,7 +10349,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -9469,7 +10368,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
@@ -9487,7 +10386,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9506,7 +10405,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -9535,7 +10434,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -9543,7 +10442,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -9613,7 +10512,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -9639,7 +10538,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9671,7 +10570,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -10670,7 +11569,7 @@
 </file>
 
 <file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10692,11 +11591,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
             <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10773,7 +11672,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
@@ -10783,7 +11682,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -10793,7 +11692,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="34925" cap="rnd">
@@ -10813,7 +11712,7 @@
     </cs:fillRef>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10832,7 +11731,7 @@
     <cs:fillRef idx="3"/>
     <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -10869,7 +11768,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -10893,7 +11792,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10912,7 +11811,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -10930,7 +11829,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -10938,7 +11837,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -10957,7 +11856,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
@@ -10975,7 +11874,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -10994,7 +11893,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -11023,7 +11922,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -11031,7 +11930,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -11101,7 +12000,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -11127,7 +12026,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -11159,7 +12058,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -11352,6 +12251,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>725258</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>62141</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>361032</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>9744</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81C4FBD6-4E35-86BB-8164-4BD0873A9CD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11731,13 +12666,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>132.75</v>
+    <v>135.47999999999999</v>
     <v>18.965</v>
-    <v>2.222</v>
-    <v>4.05</v>
-    <v>3.4601E-2</v>
-    <v>0.66449999999999998</v>
-    <v>5.4869999999999997E-3</v>
+    <v>2.1960999999999999</v>
+    <v>12.89</v>
+    <v>0.10644099999999999</v>
+    <v>0.19</v>
+    <v>1.418E-3</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -11745,25 +12680,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>125.2</v>
+    <v>135.47999999999999</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46190.87187977969</v>
+    <v>46191.999985810158</v>
     <v>0</v>
-    <v>118.06</v>
-    <v>608648600000</v>
+    <v>127.9</v>
+    <v>673433740000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>121.85</v>
+    <v>131.80500000000001</v>
     <v>0</v>
-    <v>117.05</v>
     <v>121.1</v>
-    <v>121.7645</v>
+    <v>133.99</v>
+    <v>134.18</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>113757648</v>
-    <v>131097366</v>
+    <v>233906555</v>
+    <v>128809703</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -11787,17 +12722,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.41</v>
-    <v>-9.1739999999999999E-3</v>
+    <v>-0.12</v>
+    <v>-2.6889999999999996E-3</v>
     <v>US</v>
-    <v>44.59</v>
+    <v>44.53</v>
     <v>Index</v>
     <v>3</v>
     <v>44.2</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.43</v>
-    <v>44.69</v>
-    <v>44.28</v>
+    <v>44.53</v>
+    <v>44.63</v>
+    <v>44.51</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12019,9 +12954,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -12595,18 +13530,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="230" t="s">
+      <c r="B2" s="231" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="231"/>
-      <c r="E2" s="230" t="s">
+      <c r="C2" s="232"/>
+      <c r="E2" s="231" t="s">
         <v>289</v>
       </c>
-      <c r="F2" s="231"/>
-      <c r="H2" s="230" t="s">
+      <c r="F2" s="232"/>
+      <c r="H2" s="231" t="s">
         <v>330</v>
       </c>
-      <c r="I2" s="231"/>
+      <c r="I2" s="232"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -12621,7 +13556,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>608648.6</v>
+        <v>673433.74</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -12629,7 +13564,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-7.1242633484471662</v>
+        <v>-7.1340605230057248</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -12645,7 +13580,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>626004.6</v>
+        <v>690789.74</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -12653,7 +13588,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.636363187726744</v>
+        <v>36.676103181034087</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -12662,7 +13597,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>121.1</v>
+        <v>133.99</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>245</v>
@@ -12686,14 +13621,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>121.7645</v>
+        <v>134.18</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>239</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-195.32258064516128</v>
+        <v>-216.11290322580646</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -12701,7 +13636,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-11.410141435213914</v>
+        <v>-11.42233288692173</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -12710,14 +13645,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>4.05</v>
+        <v>12.89</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>10.599037442107024</v>
+        <v>11.727209140114949</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -12725,7 +13660,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>14.375299285779978</v>
+        <v>14.379737127540219</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -12734,14 +13669,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.66449999999999998</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>267</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>-9.0199829589684422E-3</v>
+        <v>-8.152249692746312E-3</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -12749,7 +13684,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.88129397782180041</v>
+        <v>-0.89268051998253439</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -12758,14 +13693,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.4601E-2</v>
+        <v>0.10644099999999999</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-5.1197357555739058E-3</v>
+        <v>-4.627210985894469E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -12774,7 +13709,7 @@
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>5.4869999999999997E-3</v>
+        <v>1.418E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>295</v>
@@ -12790,7 +13725,7 @@
       </c>
       <c r="C11" s="209" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>132.75</v>
+        <v>135.47999999999999</v>
       </c>
       <c r="E11" s="186" t="s">
         <v>291</v>
@@ -12822,7 +13757,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.222</v>
+        <v>2.1960999999999999</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>99</v>
@@ -12838,7 +13773,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>131097366</v>
+        <v>128809703</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>100</v>
@@ -12854,7 +13789,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>-6.1792633713443198E-3</v>
+        <v>-5.5848107640107253E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -12867,10 +13802,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="232" t="s">
+      <c r="B17" s="233" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="232"/>
+      <c r="C17" s="233"/>
       <c r="E17" s="184" t="s">
         <v>298</v>
       </c>
@@ -12943,14 +13878,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="232" t="s">
+      <c r="B25" s="233" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="232"/>
-      <c r="E25" s="230" t="s">
+      <c r="C25" s="233"/>
+      <c r="E25" s="231" t="s">
         <v>387</v>
       </c>
-      <c r="F25" s="231"/>
+      <c r="F25" s="232"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -12964,7 +13899,7 @@
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.28</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -12979,7 +13914,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.428E-2</v>
+        <v>4.4510000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -12999,15 +13934,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="229" t="s">
+      <c r="B33" s="230" t="s">
         <v>355</v>
       </c>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230"/>
+      <c r="E33" s="230"/>
+      <c r="F33" s="230"/>
+      <c r="G33" s="230"/>
+      <c r="H33" s="230"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13026,24 +13961,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="229"/>
-      <c r="C39" s="229"/>
-      <c r="D39" s="229"/>
-      <c r="E39" s="229"/>
-      <c r="F39" s="229"/>
-      <c r="G39" s="229"/>
-      <c r="H39" s="229"/>
+      <c r="B39" s="230"/>
+      <c r="C39" s="230"/>
+      <c r="D39" s="230"/>
+      <c r="E39" s="230"/>
+      <c r="F39" s="230"/>
+      <c r="G39" s="230"/>
+      <c r="H39" s="230"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="229" t="s">
+      <c r="B42" s="230" t="s">
         <v>358</v>
       </c>
-      <c r="C42" s="229"/>
-      <c r="D42" s="229"/>
-      <c r="E42" s="229"/>
-      <c r="F42" s="229"/>
-      <c r="G42" s="229"/>
-      <c r="H42" s="229"/>
+      <c r="C42" s="230"/>
+      <c r="D42" s="230"/>
+      <c r="E42" s="230"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="230"/>
+      <c r="H42" s="230"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -13074,24 +14009,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="229"/>
-      <c r="C49" s="229"/>
-      <c r="D49" s="229"/>
-      <c r="E49" s="229"/>
-      <c r="F49" s="229"/>
-      <c r="G49" s="229"/>
-      <c r="H49" s="229"/>
+      <c r="B49" s="230"/>
+      <c r="C49" s="230"/>
+      <c r="D49" s="230"/>
+      <c r="E49" s="230"/>
+      <c r="F49" s="230"/>
+      <c r="G49" s="230"/>
+      <c r="H49" s="230"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="229" t="s">
+      <c r="B52" s="230" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="229"/>
-      <c r="D52" s="229"/>
-      <c r="E52" s="229"/>
-      <c r="F52" s="229"/>
-      <c r="G52" s="229"/>
-      <c r="H52" s="229"/>
+      <c r="C52" s="230"/>
+      <c r="D52" s="230"/>
+      <c r="E52" s="230"/>
+      <c r="F52" s="230"/>
+      <c r="G52" s="230"/>
+      <c r="H52" s="230"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -13106,13 +14041,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="229"/>
-      <c r="C59" s="229"/>
-      <c r="D59" s="229"/>
-      <c r="E59" s="229"/>
-      <c r="F59" s="229"/>
-      <c r="G59" s="229"/>
-      <c r="H59" s="229"/>
+      <c r="B59" s="230"/>
+      <c r="C59" s="230"/>
+      <c r="D59" s="230"/>
+      <c r="E59" s="230"/>
+      <c r="F59" s="230"/>
+      <c r="G59" s="230"/>
+      <c r="H59" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -13197,36 +14132,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="229" t="s">
+      <c r="C2" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="229"/>
-      <c r="E2" s="229"/>
-      <c r="F2" s="229"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="229"/>
-      <c r="J2" s="229"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="229"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="229" t="s">
+      <c r="S2" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="229"/>
-      <c r="U2" s="229"/>
-      <c r="V2" s="229"/>
-      <c r="W2" s="229"/>
-      <c r="X2" s="229"/>
-      <c r="Y2" s="229"/>
-      <c r="Z2" s="229"/>
-      <c r="AA2" s="229" t="s">
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="230"/>
+      <c r="Y2" s="230"/>
+      <c r="Z2" s="230"/>
+      <c r="AA2" s="230" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="229"/>
-      <c r="AC2" s="229"/>
+      <c r="AB2" s="230"/>
+      <c r="AC2" s="230"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -13237,32 +14172,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="239" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="239" t="s">
+      <c r="S4" s="240" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
-      <c r="AA4" s="240"/>
-      <c r="AB4" s="240"/>
-      <c r="AC4" s="240"/>
+      <c r="T4" s="241"/>
+      <c r="U4" s="241"/>
+      <c r="V4" s="241"/>
+      <c r="W4" s="241"/>
+      <c r="X4" s="241"/>
+      <c r="Y4" s="241"/>
+      <c r="Z4" s="241"/>
+      <c r="AA4" s="241"/>
+      <c r="AB4" s="241"/>
+      <c r="AC4" s="241"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -13950,33 +14885,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="238" t="s">
+      <c r="C13" s="239" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="E13" s="238"/>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="238"/>
-      <c r="L13" s="238"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239"/>
+      <c r="F13" s="239"/>
+      <c r="G13" s="239"/>
+      <c r="H13" s="239"/>
+      <c r="I13" s="239"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="239" t="s">
+      <c r="S13" s="240" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="240"/>
-      <c r="U13" s="240"/>
-      <c r="V13" s="240"/>
-      <c r="W13" s="240"/>
-      <c r="X13" s="240"/>
-      <c r="Y13" s="240"/>
-      <c r="Z13" s="240"/>
-      <c r="AA13" s="240"/>
-      <c r="AB13" s="240"/>
-      <c r="AC13" s="240"/>
+      <c r="T13" s="241"/>
+      <c r="U13" s="241"/>
+      <c r="V13" s="241"/>
+      <c r="W13" s="241"/>
+      <c r="X13" s="241"/>
+      <c r="Y13" s="241"/>
+      <c r="Z13" s="241"/>
+      <c r="AA13" s="241"/>
+      <c r="AB13" s="241"/>
+      <c r="AC13" s="241"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -14613,35 +15548,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="229" t="s">
+      <c r="C2" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="229"/>
-      <c r="E2" s="229"/>
-      <c r="F2" s="229"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="229"/>
-      <c r="J2" s="229"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="229"/>
-      <c r="P2" s="229" t="s">
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
+      <c r="P2" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="229"/>
-      <c r="S2" s="229"/>
-      <c r="T2" s="229"/>
-      <c r="U2" s="229"/>
-      <c r="V2" s="229"/>
-      <c r="W2" s="229"/>
-      <c r="X2" s="229" t="s">
+      <c r="Q2" s="230"/>
+      <c r="R2" s="230"/>
+      <c r="S2" s="230"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="230" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="229"/>
-      <c r="Z2" s="229"/>
+      <c r="Y2" s="230"/>
+      <c r="Z2" s="230"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14650,31 +15585,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="239" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="P4" s="240" t="s">
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
+      <c r="P4" s="241" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="240"/>
-      <c r="R4" s="240"/>
-      <c r="S4" s="240"/>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
+      <c r="Q4" s="241"/>
+      <c r="R4" s="241"/>
+      <c r="S4" s="241"/>
+      <c r="T4" s="241"/>
+      <c r="U4" s="241"/>
+      <c r="V4" s="241"/>
+      <c r="W4" s="241"/>
+      <c r="X4" s="241"/>
+      <c r="Y4" s="241"/>
+      <c r="Z4" s="241"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -14869,32 +15804,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="238" t="s">
+      <c r="C9" s="239" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="E9" s="238"/>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
-      <c r="K9" s="238"/>
-      <c r="L9" s="238"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="239"/>
+      <c r="F9" s="239"/>
+      <c r="G9" s="239"/>
+      <c r="H9" s="239"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="239"/>
+      <c r="L9" s="239"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="240" t="s">
+      <c r="P9" s="241" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="240"/>
-      <c r="R9" s="240"/>
-      <c r="S9" s="240"/>
-      <c r="T9" s="240"/>
-      <c r="U9" s="240"/>
-      <c r="V9" s="240"/>
-      <c r="W9" s="240"/>
-      <c r="X9" s="240"/>
-      <c r="Y9" s="240"/>
-      <c r="Z9" s="240"/>
+      <c r="Q9" s="241"/>
+      <c r="R9" s="241"/>
+      <c r="S9" s="241"/>
+      <c r="T9" s="241"/>
+      <c r="U9" s="241"/>
+      <c r="V9" s="241"/>
+      <c r="W9" s="241"/>
+      <c r="X9" s="241"/>
+      <c r="Y9" s="241"/>
+      <c r="Z9" s="241"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -15464,31 +16399,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="239" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
-      <c r="P18" s="240" t="s">
+      <c r="D18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
+      <c r="P18" s="241" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="240"/>
-      <c r="R18" s="240"/>
-      <c r="S18" s="240"/>
-      <c r="T18" s="240"/>
-      <c r="U18" s="240"/>
-      <c r="V18" s="240"/>
-      <c r="W18" s="240"/>
-      <c r="X18" s="240"/>
-      <c r="Y18" s="240"/>
-      <c r="Z18" s="240"/>
+      <c r="Q18" s="241"/>
+      <c r="R18" s="241"/>
+      <c r="S18" s="241"/>
+      <c r="T18" s="241"/>
+      <c r="U18" s="241"/>
+      <c r="V18" s="241"/>
+      <c r="W18" s="241"/>
+      <c r="X18" s="241"/>
+      <c r="Y18" s="241"/>
+      <c r="Z18" s="241"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -16048,60 +16983,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="229" t="s">
+      <c r="C3" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="229"/>
-      <c r="E3" s="229"/>
-      <c r="F3" s="229"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="229"/>
-      <c r="J3" s="229"/>
-      <c r="K3" s="229"/>
-      <c r="L3" s="229"/>
-      <c r="P3" s="243"/>
-      <c r="Q3" s="243"/>
-      <c r="R3" s="243"/>
-      <c r="S3" s="243"/>
-      <c r="T3" s="243"/>
-      <c r="U3" s="243"/>
-      <c r="V3" s="243"/>
-      <c r="W3" s="243"/>
-      <c r="X3" s="243"/>
-      <c r="Y3" s="243"/>
-      <c r="Z3" s="243"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="239" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="243"/>
-      <c r="R5" s="243"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="243"/>
-      <c r="U5" s="243"/>
-      <c r="V5" s="243"/>
-      <c r="W5" s="243"/>
-      <c r="X5" s="243"/>
-      <c r="Y5" s="243"/>
-      <c r="Z5" s="243"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -16287,30 +17222,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="238" t="s">
+      <c r="C11" s="239" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="E11" s="238"/>
-      <c r="F11" s="238"/>
-      <c r="G11" s="238"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="238"/>
-      <c r="L11" s="238"/>
+      <c r="D11" s="239"/>
+      <c r="E11" s="239"/>
+      <c r="F11" s="239"/>
+      <c r="G11" s="239"/>
+      <c r="H11" s="239"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="239"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="243"/>
-      <c r="Q11" s="243"/>
-      <c r="R11" s="243"/>
-      <c r="S11" s="243"/>
-      <c r="T11" s="243"/>
-      <c r="U11" s="243"/>
-      <c r="V11" s="243"/>
-      <c r="W11" s="243"/>
-      <c r="X11" s="243"/>
-      <c r="Y11" s="243"/>
-      <c r="Z11" s="243"/>
+      <c r="P11" s="244"/>
+      <c r="Q11" s="244"/>
+      <c r="R11" s="244"/>
+      <c r="S11" s="244"/>
+      <c r="T11" s="244"/>
+      <c r="U11" s="244"/>
+      <c r="V11" s="244"/>
+      <c r="W11" s="244"/>
+      <c r="X11" s="244"/>
+      <c r="Y11" s="244"/>
+      <c r="Z11" s="244"/>
       <c r="AB11" s="109"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -16552,18 +17487,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="239" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
+      <c r="D18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -16776,23 +17711,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="243"/>
-      <c r="C25" s="243"/>
+      <c r="B25" s="244"/>
+      <c r="C25" s="244"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="238" t="s">
+      <c r="C26" s="239" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238"/>
-      <c r="L26" s="238"/>
+      <c r="D26" s="239"/>
+      <c r="E26" s="239"/>
+      <c r="F26" s="239"/>
+      <c r="G26" s="239"/>
+      <c r="H26" s="239"/>
+      <c r="I26" s="239"/>
+      <c r="J26" s="239"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -16984,18 +17919,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="238" t="s">
+      <c r="C33" s="239" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="E33" s="238"/>
-      <c r="F33" s="238"/>
-      <c r="G33" s="238"/>
-      <c r="H33" s="238"/>
-      <c r="I33" s="238"/>
-      <c r="J33" s="238"/>
-      <c r="K33" s="238"/>
-      <c r="L33" s="238"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="239"/>
+      <c r="F33" s="239"/>
+      <c r="G33" s="239"/>
+      <c r="H33" s="239"/>
+      <c r="I33" s="239"/>
+      <c r="J33" s="239"/>
+      <c r="K33" s="239"/>
+      <c r="L33" s="239"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -17179,18 +18114,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="238" t="s">
+      <c r="C40" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="238"/>
-      <c r="E40" s="238"/>
-      <c r="F40" s="238"/>
-      <c r="G40" s="238"/>
-      <c r="H40" s="238"/>
-      <c r="I40" s="238"/>
-      <c r="J40" s="238"/>
-      <c r="K40" s="238"/>
-      <c r="L40" s="238"/>
+      <c r="D40" s="239"/>
+      <c r="E40" s="239"/>
+      <c r="F40" s="239"/>
+      <c r="G40" s="239"/>
+      <c r="H40" s="239"/>
+      <c r="I40" s="239"/>
+      <c r="J40" s="239"/>
+      <c r="K40" s="239"/>
+      <c r="L40" s="239"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -17504,60 +18439,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="229" t="s">
+      <c r="C2" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="229"/>
-      <c r="E2" s="229"/>
-      <c r="F2" s="229"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="229"/>
-      <c r="J2" s="229"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="229"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243"/>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
+      <c r="S2" s="244"/>
+      <c r="T2" s="244"/>
+      <c r="U2" s="244"/>
+      <c r="V2" s="244"/>
+      <c r="W2" s="244"/>
+      <c r="X2" s="244"/>
+      <c r="Y2" s="244"/>
+      <c r="Z2" s="244"/>
+      <c r="AA2" s="244"/>
+      <c r="AB2" s="244"/>
+      <c r="AC2" s="244"/>
       <c r="AE2" s="108"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
-      <c r="AA4" s="243"/>
-      <c r="AB4" s="243"/>
-      <c r="AC4" s="243"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
+      <c r="S4" s="244"/>
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="244"/>
+      <c r="Y4" s="244"/>
+      <c r="Z4" s="244"/>
+      <c r="AA4" s="244"/>
+      <c r="AB4" s="244"/>
+      <c r="AC4" s="244"/>
       <c r="AE4" s="109"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17920,18 +18855,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="238" t="s">
+      <c r="C13" s="239" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="E13" s="238"/>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="238"/>
-      <c r="L13" s="238"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239"/>
+      <c r="F13" s="239"/>
+      <c r="G13" s="239"/>
+      <c r="H13" s="239"/>
+      <c r="I13" s="239"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18024,18 +18959,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="239" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
+      <c r="D18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18227,18 +19162,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="238" t="s">
+      <c r="C25" s="239" t="s">
         <v>264</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="E25" s="238"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="238"/>
-      <c r="H25" s="238"/>
-      <c r="I25" s="238"/>
-      <c r="J25" s="238"/>
-      <c r="K25" s="238"/>
-      <c r="L25" s="238"/>
+      <c r="D25" s="239"/>
+      <c r="E25" s="239"/>
+      <c r="F25" s="239"/>
+      <c r="G25" s="239"/>
+      <c r="H25" s="239"/>
+      <c r="I25" s="239"/>
+      <c r="J25" s="239"/>
+      <c r="K25" s="239"/>
+      <c r="L25" s="239"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -18376,18 +19311,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="238" t="s">
+      <c r="C31" s="239" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="E31" s="238"/>
-      <c r="F31" s="238"/>
-      <c r="G31" s="238"/>
-      <c r="H31" s="238"/>
-      <c r="I31" s="238"/>
-      <c r="J31" s="238"/>
-      <c r="K31" s="238"/>
-      <c r="L31" s="238"/>
+      <c r="D31" s="239"/>
+      <c r="E31" s="239"/>
+      <c r="F31" s="239"/>
+      <c r="G31" s="239"/>
+      <c r="H31" s="239"/>
+      <c r="I31" s="239"/>
+      <c r="J31" s="239"/>
+      <c r="K31" s="239"/>
+      <c r="L31" s="239"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -18598,10 +19533,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="229" t="s">
+      <c r="B4" s="230" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="229"/>
+      <c r="C4" s="230"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -18618,7 +19553,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>121.1</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18627,7 +19562,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>608648.6</v>
+        <v>673433.74</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18645,7 +19580,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.428E-2</v>
+        <v>4.4510000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18654,7 +19589,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.222</v>
+        <v>2.1960999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18686,10 +19621,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="229" t="s">
+      <c r="B15" s="230" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="229"/>
+      <c r="C15" s="230"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -18697,7 +19632,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.8888489100776593E-2</v>
+        <v>6.2676701434227655E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18706,7 +19641,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93111151089922339</v>
+        <v>0.93732329856577234</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18724,7 +19659,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14427000000000001</v>
+        <v>0.1433345</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18733,7 +19668,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13727024062247009</v>
+        <v>0.13702455442145986</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -18786,60 +19721,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="229" t="s">
+      <c r="C3" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="229"/>
-      <c r="E3" s="229"/>
-      <c r="F3" s="229"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="229"/>
-      <c r="J3" s="229"/>
-      <c r="K3" s="229"/>
-      <c r="L3" s="229"/>
-      <c r="P3" s="243"/>
-      <c r="Q3" s="243"/>
-      <c r="R3" s="243"/>
-      <c r="S3" s="243"/>
-      <c r="T3" s="243"/>
-      <c r="U3" s="243"/>
-      <c r="V3" s="243"/>
-      <c r="W3" s="243"/>
-      <c r="X3" s="243"/>
-      <c r="Y3" s="243"/>
-      <c r="Z3" s="243"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="239" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="243"/>
-      <c r="R5" s="243"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="243"/>
-      <c r="U5" s="243"/>
-      <c r="V5" s="243"/>
-      <c r="W5" s="243"/>
-      <c r="X5" s="243"/>
-      <c r="Y5" s="243"/>
-      <c r="Z5" s="243"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18992,7 +19927,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23309.145845951658</v>
+        <v>-23358.082033062106</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -19046,23 +19981,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6494.7988778703266</v>
+        <v>-6496.2022622180302</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5058.6400509587629</v>
+        <v>-5060.8264106581382</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3565.915222135774</v>
+        <v>-3568.2272711048495</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3265.5395595703262</v>
+        <v>-3268.3629219387994</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1408.6257691449555</v>
+        <v>-1410.1482934628298</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -19081,14 +20016,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12252.028109615308</v>
+        <v>-12291.021029244122</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="229" t="s">
+      <c r="B13" s="230" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="229"/>
+      <c r="C13" s="230"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -19104,14 +20039,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13727024062247009</v>
+        <v>0.13702455442145986</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="229" t="s">
+      <c r="B18" s="230" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="229"/>
+      <c r="C18" s="230"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -19119,7 +20054,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19793.519479680144</v>
+        <v>-19803.767159382645</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -19128,7 +20063,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12252.028109615308</v>
+        <v>-12291.021029244122</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -19137,7 +20072,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-32045.547589295453</v>
+        <v>-32094.788188626768</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -19164,7 +20099,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-35806.547589295456</v>
+        <v>-35855.788188626771</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -19182,7 +20117,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>-7.1242633484471662</v>
+        <v>-7.1340605230057248</v>
       </c>
     </row>
   </sheetData>
@@ -19225,37 +20160,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="229" t="s">
+      <c r="C2" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="229"/>
-      <c r="E2" s="229"/>
-      <c r="F2" s="229"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="229"/>
-      <c r="J2" s="229"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="229"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="239" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -19444,18 +20379,18 @@
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="238" t="s">
+      <c r="C10" s="239" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="238"/>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239"/>
+      <c r="H10" s="239"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -19649,18 +20584,18 @@
       <c r="N15" s="90"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="238" t="s">
+      <c r="C16" s="239" t="s">
         <v>191</v>
       </c>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="238"/>
-      <c r="L16" s="238"/>
+      <c r="D16" s="239"/>
+      <c r="E16" s="239"/>
+      <c r="F16" s="239"/>
+      <c r="G16" s="239"/>
+      <c r="H16" s="239"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="239"/>
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -19794,18 +20729,18 @@
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="238" t="s">
+      <c r="C21" s="239" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="E21" s="238"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
-      <c r="H21" s="238"/>
-      <c r="I21" s="238"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="238"/>
-      <c r="L21" s="238"/>
+      <c r="D21" s="239"/>
+      <c r="E21" s="239"/>
+      <c r="F21" s="239"/>
+      <c r="G21" s="239"/>
+      <c r="H21" s="239"/>
+      <c r="I21" s="239"/>
+      <c r="J21" s="239"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="239"/>
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -19889,18 +20824,18 @@
       <c r="N25" s="90"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="238" t="s">
+      <c r="C26" s="239" t="s">
         <v>195</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238"/>
-      <c r="L26" s="238"/>
+      <c r="D26" s="239"/>
+      <c r="E26" s="239"/>
+      <c r="F26" s="239"/>
+      <c r="G26" s="239"/>
+      <c r="H26" s="239"/>
+      <c r="I26" s="239"/>
+      <c r="J26" s="239"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -20170,10 +21105,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="229" t="s">
+      <c r="B37" s="230" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="229"/>
+      <c r="C37" s="230"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -20191,7 +21126,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13727024062247009</v>
+        <v>0.13702455442145986</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -20217,7 +21152,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>184134.36138151461</v>
+        <v>184334.09458787731</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -20235,14 +21170,14 @@
       </c>
       <c r="C44" s="142">
         <f ca="1">C42/C43</f>
-        <v>36.636363187726744</v>
+        <v>36.676103181034087</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="229" t="s">
+      <c r="B46" s="230" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="229"/>
+      <c r="C46" s="230"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -20298,10 +21233,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="229" t="s">
+      <c r="B54" s="230" t="s">
         <v>324</v>
       </c>
-      <c r="C54" s="229"/>
+      <c r="C54" s="230"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -20318,7 +21253,7 @@
       </c>
       <c r="C56" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13727024062247009</v>
+        <v>0.13702455442145986</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -20353,7 +21288,7 @@
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C56)^5-G30+G31</f>
-        <v>-57347.370853385131</v>
+        <v>-57408.645089668615</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -20371,7 +21306,7 @@
       </c>
       <c r="C62" s="142">
         <f ca="1">C60/C61</f>
-        <v>-11.410141435213914</v>
+        <v>-11.42233288692173</v>
       </c>
     </row>
   </sheetData>
@@ -20423,10 +21358,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="229" t="s">
+      <c r="B4" s="230" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="229"/>
+      <c r="C4" s="230"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -20435,7 +21370,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-7.1242633484471662</v>
+        <v>-7.1340605230057248</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -20444,7 +21379,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C44</f>
-        <v>36.636363187726744</v>
+        <v>36.676103181034087</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -20462,7 +21397,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C62</f>
-        <v>-11.410141435213914</v>
+        <v>-11.42233288692173</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -20471,7 +21406,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>14.375299285779978</v>
+        <v>14.379737127540219</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -20480,7 +21415,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>121.1</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20489,7 +21424,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.88129397782180041</v>
+        <v>-0.89268051998253439</v>
       </c>
     </row>
   </sheetData>
@@ -20554,60 +21489,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="229" t="s">
+      <c r="C3" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="229"/>
-      <c r="E3" s="229"/>
-      <c r="F3" s="229"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="229"/>
-      <c r="J3" s="229"/>
-      <c r="K3" s="229"/>
-      <c r="L3" s="229"/>
-      <c r="P3" s="243"/>
-      <c r="Q3" s="243"/>
-      <c r="R3" s="243"/>
-      <c r="S3" s="243"/>
-      <c r="T3" s="243"/>
-      <c r="U3" s="243"/>
-      <c r="V3" s="243"/>
-      <c r="W3" s="243"/>
-      <c r="X3" s="243"/>
-      <c r="Y3" s="243"/>
-      <c r="Z3" s="243"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="244"/>
+      <c r="T3" s="244"/>
+      <c r="U3" s="244"/>
+      <c r="V3" s="244"/>
+      <c r="W3" s="244"/>
+      <c r="X3" s="244"/>
+      <c r="Y3" s="244"/>
+      <c r="Z3" s="244"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="239" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="243"/>
-      <c r="R5" s="243"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="243"/>
-      <c r="U5" s="243"/>
-      <c r="V5" s="243"/>
-      <c r="W5" s="243"/>
-      <c r="X5" s="243"/>
-      <c r="Y5" s="243"/>
-      <c r="Z5" s="243"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="244"/>
+      <c r="T5" s="244"/>
+      <c r="U5" s="244"/>
+      <c r="V5" s="244"/>
+      <c r="W5" s="244"/>
+      <c r="X5" s="244"/>
+      <c r="Y5" s="244"/>
+      <c r="Z5" s="244"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20742,7 +21677,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-965658.65566659707</v>
+        <v>-967685.99948137393</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20796,23 +21731,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13170.790154205433</v>
+        <v>-13173.636074625276</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19108.74212495382</v>
+        <v>-19117.000981734869</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27723.775211876273</v>
+        <v>-27741.750604420544</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40222.831360256409</v>
+        <v>-40257.60773529164</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58356.993240320422</v>
+        <v>-58420.068858609258</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20831,15 +21766,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-507580.88999538944</v>
+        <v>-509196.30098462629</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="244" t="s">
+      <c r="B14" s="245" t="s">
         <v>219</v>
       </c>
-      <c r="C14" s="245"/>
+      <c r="C14" s="246"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -20847,7 +21782,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>121.1</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -20856,7 +21791,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-133.29188660704375</v>
+        <v>-133.63855257447432</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -20866,20 +21801,20 @@
       <c r="C17" s="158">
         <v>0.65</v>
       </c>
-      <c r="E17" s="246" t="s">
+      <c r="E17" s="247" t="s">
         <v>222</v>
       </c>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
+      <c r="F17" s="247"/>
+      <c r="G17" s="247"/>
+      <c r="H17" s="247"/>
+      <c r="I17" s="247"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="244" t="s">
+      <c r="B19" s="245" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="245"/>
+      <c r="C19" s="246"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -20895,7 +21830,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13727024062247009</v>
+        <v>0.13702455442145986</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -20913,7 +21848,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>608648.6</v>
+        <v>673433.74</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -20940,15 +21875,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>612409.59999999998</v>
+        <v>677194.74</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="244" t="s">
+      <c r="B28" s="245" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="245"/>
+      <c r="C28" s="246"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -20956,7 +21891,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158583.13209161235</v>
+        <v>-158710.06425468158</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -20965,7 +21900,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>-507580.88999538944</v>
+        <v>-509196.30098462629</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -20974,7 +21909,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>-666164.02208700182</v>
+        <v>-667906.36523930787</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21001,7 +21936,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>-669925.02208700182</v>
+        <v>-671667.36523930787</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21019,22 +21954,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>-133.29188660704375</v>
+        <v>-133.63855257447432</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="238" t="s">
+      <c r="C39" s="239" t="s">
         <v>225</v>
       </c>
-      <c r="D39" s="238"/>
-      <c r="E39" s="238"/>
-      <c r="F39" s="238"/>
-      <c r="G39" s="238"/>
-      <c r="H39" s="238"/>
-      <c r="I39" s="238"/>
-      <c r="J39" s="238"/>
-      <c r="K39" s="238"/>
-      <c r="L39" s="238"/>
+      <c r="D39" s="239"/>
+      <c r="E39" s="239"/>
+      <c r="F39" s="239"/>
+      <c r="G39" s="239"/>
+      <c r="H39" s="239"/>
+      <c r="I39" s="239"/>
+      <c r="J39" s="239"/>
+      <c r="K39" s="239"/>
+      <c r="L39" s="239"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23101,6 +24036,8 @@
         <f>Q25/Q$85</f>
         <v>-0.06</v>
       </c>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
       <c r="T26" s="65">
         <f t="shared" ref="T26:AA26" si="17">T25/T$85</f>
         <v>-0.38</v>
@@ -28026,7 +28963,7 @@
       <c r="AA116" s="67"/>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>121.1</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -28073,7 +29010,7 @@
       <c r="AA117" s="67"/>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>121.1</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -29379,7 +30316,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-195.32258064516128</v>
+        <v>-216.11290322580646</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -29416,7 +30353,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>10.599037442107024</v>
+        <v>11.727209140114949</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -29453,7 +30390,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>5.4639262437833267</v>
+        <v>6.045511786990323</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -29490,7 +30427,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>608648.6</v>
+        <v>673433.74</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -29527,7 +30464,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>626004.6</v>
+        <v>690789.74</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -29564,7 +30501,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>11.643781039004519</v>
+        <v>12.848794524115098</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -29601,7 +30538,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>-123.98585858585858</v>
+        <v>-136.81714002772827</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -29736,7 +30673,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="100">AC153/AC157</f>
-        <v>-110.86495446265937</v>
+        <v>-122.66552641165755</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -29773,7 +30710,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="100"/>
-        <v>-73.020482911466232</v>
+        <v>-80.577363816633621</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -29810,7 +30747,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="103">AC157/AC153</f>
-        <v>-9.0199829589684422E-3</v>
+        <v>-8.152249692746312E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -29847,7 +30784,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-5.1197357555739058E-3</v>
+        <v>-4.627210985894469E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -30461,7 +31398,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-6.1792633713443198E-3</v>
+        <v>-5.5848107640107253E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32186,15 +33123,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="229" t="s">
+      <c r="B4" s="230" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="229"/>
-      <c r="E4" s="229" t="s">
+      <c r="C4" s="230"/>
+      <c r="E4" s="230" t="s">
         <v>242</v>
       </c>
-      <c r="F4" s="229"/>
-      <c r="G4" s="229"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -32202,7 +33139,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>121.1</v>
+        <v>133.99</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -32218,7 +33155,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>608648.6</v>
+        <v>673433.74</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -32238,7 +33175,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>626004.6</v>
+        <v>690789.74</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -32258,7 +33195,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-195.32258064516128</v>
+        <v>-216.11290322580646</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>245</v>
@@ -32278,7 +33215,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>10.599037442107024</v>
+        <v>11.727209140114949</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>246</v>
@@ -32298,7 +33235,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>5.4639262437833267</v>
+        <v>6.045511786990323</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -32318,7 +33255,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>11.643781039004519</v>
+        <v>12.848794524115098</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -32327,18 +33264,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>-123.98585858585858</v>
+        <v>-136.81714002772827</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="229" t="s">
+      <c r="B15" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="229"/>
-      <c r="E15" s="229" t="s">
+      <c r="C15" s="230"/>
+      <c r="E15" s="230" t="s">
         <v>248</v>
       </c>
-      <c r="F15" s="229"/>
+      <c r="F15" s="230"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -32389,14 +33326,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="229" t="s">
+      <c r="B21" s="230" t="s">
         <v>247</v>
       </c>
-      <c r="C21" s="229"/>
-      <c r="E21" s="229" t="s">
+      <c r="C21" s="230"/>
+      <c r="E21" s="230" t="s">
         <v>251</v>
       </c>
-      <c r="F21" s="229"/>
+      <c r="F21" s="230"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -32465,14 +33402,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="229" t="s">
+      <c r="B29" s="230" t="s">
         <v>252</v>
       </c>
-      <c r="C29" s="229"/>
-      <c r="E29" s="229" t="s">
+      <c r="C29" s="230"/>
+      <c r="E29" s="230" t="s">
         <v>258</v>
       </c>
-      <c r="F29" s="229"/>
+      <c r="F29" s="230"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -32548,14 +33485,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="229" t="s">
+      <c r="B37" s="230" t="s">
         <v>270</v>
       </c>
-      <c r="C37" s="229"/>
-      <c r="E37" s="229" t="s">
+      <c r="C37" s="230"/>
+      <c r="E37" s="230" t="s">
         <v>273</v>
       </c>
-      <c r="F37" s="229"/>
+      <c r="F37" s="230"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -32563,7 +33500,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-5.1197357555739058E-3</v>
+        <v>-4.627210985894469E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>272</v>
@@ -32579,7 +33516,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>-9.0199829589684422E-3</v>
+        <v>-8.152249692746312E-3</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>274</v>
@@ -32624,14 +33561,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="229" t="s">
+      <c r="B45" s="230" t="s">
         <v>281</v>
       </c>
-      <c r="C45" s="229"/>
-      <c r="E45" s="229" t="s">
+      <c r="C45" s="230"/>
+      <c r="E45" s="230" t="s">
         <v>287</v>
       </c>
-      <c r="F45" s="229"/>
+      <c r="F45" s="230"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -32664,18 +33601,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>-6.1792633713443198E-3</v>
+        <v>-5.5848107640107253E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="229" t="s">
+      <c r="B51" s="230" t="s">
         <v>284</v>
       </c>
-      <c r="C51" s="229"/>
-      <c r="E51" s="229" t="s">
+      <c r="C51" s="230"/>
+      <c r="E51" s="230" t="s">
         <v>305</v>
       </c>
-      <c r="F51" s="229"/>
+      <c r="F51" s="230"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -32843,7 +33780,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>121.1</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -32872,7 +33809,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>608648.6</v>
+        <v>673433.74</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -32901,7 +33838,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>626004.6</v>
+        <v>690789.74</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -32930,7 +33867,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-195.32258064516128</v>
+        <v>-216.11290322580646</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -32959,7 +33896,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>10.599037442107024</v>
+        <v>11.727209140114949</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -32988,7 +33925,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>5.4639262437833267</v>
+        <v>6.045511786990323</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33017,7 +33954,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>11.643781039004519</v>
+        <v>12.848794524115098</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33046,7 +33983,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>-123.98585858585858</v>
+        <v>-136.81714002772827</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33819,7 +34756,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-5.1197357555739058E-3</v>
+        <v>-4.627210985894469E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -33848,7 +34785,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>-9.0199829589684422E-3</v>
+        <v>-8.152249692746312E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -34171,7 +35108,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>-6.1792633713443198E-3</v>
+        <v>-5.5848107640107253E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34709,14 +35646,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="234" t="s">
         <v>315</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="F3" s="235" t="s">
+      <c r="D3" s="235"/>
+      <c r="F3" s="236" t="s">
         <v>316</v>
       </c>
-      <c r="G3" s="234"/>
+      <c r="G3" s="235"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -34783,19 +35720,19 @@
       <c r="B7" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C7" s="236">
+      <c r="C7" s="237">
         <f>Statement!AA89</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="F7" s="236">
+      <c r="D7" s="238"/>
+      <c r="F7" s="237">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="237"/>
+      <c r="G7" s="238"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -34822,19 +35759,19 @@
       <c r="B9" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="237">
         <f>Statement!AA90</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="F9" s="236">
+      <c r="D9" s="238"/>
+      <c r="F9" s="237">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="237"/>
+      <c r="G9" s="238"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -34861,19 +35798,19 @@
       <c r="B11" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C11" s="236">
+      <c r="C11" s="237">
         <f>Statement!AA91</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="F11" s="236">
+      <c r="D11" s="238"/>
+      <c r="F11" s="237">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="237"/>
+      <c r="G11" s="238"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -34900,19 +35837,19 @@
       <c r="B13" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C13" s="236">
+      <c r="C13" s="237">
         <f>Statement!AA95</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="F13" s="236">
+      <c r="D13" s="238"/>
+      <c r="F13" s="237">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="237"/>
+      <c r="G13" s="238"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -34939,19 +35876,19 @@
       <c r="B15" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C15" s="236">
+      <c r="C15" s="237">
         <f>Statement!AA96</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="237"/>
-      <c r="F15" s="236">
+      <c r="D15" s="238"/>
+      <c r="F15" s="237">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="237"/>
+      <c r="G15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -34978,19 +35915,19 @@
       <c r="B17" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C17" s="236">
+      <c r="C17" s="237">
         <f>Statement!AA98</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="237"/>
-      <c r="F17" s="236">
+      <c r="D17" s="238"/>
+      <c r="F17" s="237">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="237"/>
+      <c r="G17" s="238"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35017,22 +35954,22 @@
       <c r="B19" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C19" s="236">
+      <c r="C19" s="237">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="237"/>
-      <c r="F19" s="236">
+      <c r="D19" s="238"/>
+      <c r="F19" s="237">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="237"/>
+      <c r="G19" s="238"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35059,22 +35996,22 @@
       <c r="B21" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C21" s="236">
+      <c r="C21" s="237">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="237"/>
-      <c r="F21" s="236">
+      <c r="D21" s="238"/>
+      <c r="F21" s="237">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="237"/>
+      <c r="G21" s="238"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -35122,22 +36059,22 @@
       <c r="B25" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C25" s="236">
+      <c r="C25" s="237">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="237"/>
-      <c r="F25" s="236">
+      <c r="D25" s="238"/>
+      <c r="F25" s="237">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="237"/>
+      <c r="G25" s="238"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -35164,22 +36101,22 @@
       <c r="B27" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C27" s="236">
+      <c r="C27" s="237">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="237"/>
-      <c r="F27" s="236">
+      <c r="D27" s="238"/>
+      <c r="F27" s="237">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="237"/>
+      <c r="G27" s="238"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -35206,22 +36143,22 @@
       <c r="B29" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C29" s="236">
+      <c r="C29" s="237">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="237"/>
-      <c r="F29" s="236">
+      <c r="D29" s="238"/>
+      <c r="F29" s="237">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="237"/>
+      <c r="G29" s="238"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35248,22 +36185,22 @@
       <c r="B31" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C31" s="236">
+      <c r="C31" s="237">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="237"/>
-      <c r="F31" s="236">
+      <c r="D31" s="238"/>
+      <c r="F31" s="237">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="237"/>
+      <c r="G31" s="238"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -35290,22 +36227,22 @@
       <c r="B33" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C33" s="236">
+      <c r="C33" s="237">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="237"/>
-      <c r="F33" s="236">
+      <c r="D33" s="238"/>
+      <c r="F33" s="237">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="237"/>
+      <c r="G33" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -35347,7 +36284,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493C1714-C888-F946-B58E-37A028776C2A}">
-  <dimension ref="B55:L70"/>
+  <dimension ref="B55:L73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -36069,6 +37006,141 @@
       <c r="L70" s="222">
         <f>Statement!Q140</f>
         <v>-1.7430737617799192E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B71" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="C71" s="229">
+        <f>Statement!H213</f>
+        <v>0</v>
+      </c>
+      <c r="D71" s="229">
+        <f>Statement!I213</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="229">
+        <f>Statement!J213</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="229">
+        <f>Statement!K213</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="229">
+        <f>Statement!L213</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="229">
+        <f>Statement!M213</f>
+        <v>100</v>
+      </c>
+      <c r="I71" s="229">
+        <f>Statement!N213</f>
+        <v>51.510426817384527</v>
+      </c>
+      <c r="J71" s="229">
+        <f>Statement!O213</f>
+        <v>97.934125901383737</v>
+      </c>
+      <c r="K71" s="229">
+        <f>Statement!P213</f>
+        <v>39.563437926330145</v>
+      </c>
+      <c r="L71" s="229">
+        <f>Statement!Q213</f>
+        <v>70.551549405573965</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B72" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="C72" s="229">
+        <f>Statement!H214</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="229">
+        <f>Statement!I214</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="229">
+        <f>Statement!J214</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="229">
+        <f>Statement!K214</f>
+        <v>0</v>
+      </c>
+      <c r="G72" s="229">
+        <f>Statement!L214</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="229">
+        <f>Statement!M214</f>
+        <v>100</v>
+      </c>
+      <c r="I72" s="229">
+        <f>Statement!N214</f>
+        <v>79.790949584936214</v>
+      </c>
+      <c r="J72" s="229">
+        <f>Statement!O214</f>
+        <v>68.6221907268678</v>
+      </c>
+      <c r="K72" s="229">
+        <f>Statement!P214</f>
+        <v>67.196041708847943</v>
+      </c>
+      <c r="L72" s="229">
+        <f>Statement!Q214</f>
+        <v>66.882212998582702</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B73" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="C73" s="229">
+        <f>Statement!H215</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="229">
+        <f>Statement!I215</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="229">
+        <f>Statement!J215</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="229">
+        <f>Statement!K215</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="229">
+        <f>Statement!L215</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="229">
+        <f>Statement!M215</f>
+        <v>100</v>
+      </c>
+      <c r="I73" s="229">
+        <f>Statement!N215</f>
+        <v>39.917695473251023</v>
+      </c>
+      <c r="J73" s="229">
+        <f>Statement!O215</f>
+        <v>8.2304526748971263</v>
+      </c>
+      <c r="K73" s="229">
+        <f>Statement!P215</f>
+        <v>-90.123456790123456</v>
+      </c>
+      <c r="L73" s="229">
+        <f>Statement!Q215</f>
+        <v>-1.2345679012345512</v>
       </c>
     </row>
   </sheetData>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DE51EC-5746-BE4A-8984-D2E34527EEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95736EB-C546-C24A-B1CF-75218DE151D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2277,9 +2277,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2289,6 +2286,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2296,12 +2302,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12666,13 +12666,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>135.47999999999999</v>
+    <v>142.35</v>
     <v>18.965</v>
-    <v>2.1960999999999999</v>
-    <v>12.89</v>
-    <v>0.10644099999999999</v>
-    <v>0.19</v>
-    <v>1.418E-3</v>
+    <v>2.2117</v>
+    <v>-6.67</v>
+    <v>-5.2511000000000002E-2</v>
+    <v>0.66</v>
+    <v>5.4840000000000002E-3</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -12680,25 +12680,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>135.47999999999999</v>
+    <v>130.74</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46191.999985810158</v>
+    <v>46205.999999293752</v>
     <v>0</v>
-    <v>127.9</v>
-    <v>673433740000</v>
+    <v>117.63</v>
+    <v>604879100000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>131.80500000000001</v>
+    <v>128.91499999999999</v>
     <v>0</v>
-    <v>121.1</v>
-    <v>133.99</v>
-    <v>134.18</v>
+    <v>127.02</v>
+    <v>120.35</v>
+    <v>121.01</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>233906555</v>
-    <v>128809703</v>
+    <v>125021717</v>
+    <v>130207762</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -12722,17 +12722,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.12</v>
-    <v>-2.6889999999999996E-3</v>
+    <v>0.1</v>
+    <v>2.235E-3</v>
     <v>US</v>
-    <v>44.53</v>
+    <v>45.05</v>
     <v>Index</v>
     <v>3</v>
-    <v>44.2</v>
+    <v>44.53</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.53</v>
-    <v>44.63</v>
-    <v>44.51</v>
+    <v>45.03</v>
+    <v>44.75</v>
+    <v>44.85</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13530,18 +13530,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="231" t="s">
+      <c r="B2" s="230" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="232"/>
-      <c r="E2" s="231" t="s">
+      <c r="C2" s="231"/>
+      <c r="E2" s="230" t="s">
         <v>289</v>
       </c>
-      <c r="F2" s="232"/>
-      <c r="H2" s="231" t="s">
+      <c r="F2" s="231"/>
+      <c r="H2" s="230" t="s">
         <v>330</v>
       </c>
-      <c r="I2" s="232"/>
+      <c r="I2" s="231"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>673433.74</v>
+        <v>604879.1</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-7.1340605230057248</v>
+        <v>-7.1219352400478764</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>690789.74</v>
+        <v>622235.1</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.676103181034087</v>
+        <v>36.626904790684932</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>133.99</v>
+        <v>120.35</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>245</v>
@@ -13621,14 +13621,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>134.18</v>
+        <v>121.01</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>239</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-216.11290322580646</v>
+        <v>-194.11290322580643</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-11.42233288692173</v>
+        <v>-11.407239784227796</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13645,14 +13645,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>12.89</v>
+        <v>-6.67</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>11.727209140114949</v>
+        <v>10.533395178840466</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>14.379737127540219</v>
+        <v>14.374242126365875</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13669,14 +13669,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.19</v>
+        <v>0.66</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>267</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>-8.152249692746312E-3</v>
+        <v>-9.0761939038726917E-3</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.89268051998253439</v>
+        <v>-0.88056300684365707</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13693,14 +13693,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>0.10644099999999999</v>
+        <v>-5.2511000000000002E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-4.627210985894469E-3</v>
+        <v>-5.1516410469464062E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.418E-3</v>
+        <v>5.4840000000000002E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>295</v>
@@ -13725,7 +13725,7 @@
       </c>
       <c r="C11" s="209" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>135.47999999999999</v>
+        <v>142.35</v>
       </c>
       <c r="E11" s="186" t="s">
         <v>291</v>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1960999999999999</v>
+        <v>2.2117</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>99</v>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>128809703</v>
+        <v>130207762</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>100</v>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>-5.5848107640107253E-3</v>
+        <v>-6.2177714521794523E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13802,10 +13802,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="233" t="s">
+      <c r="B17" s="232" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="233"/>
+      <c r="C17" s="232"/>
       <c r="E17" s="184" t="s">
         <v>298</v>
       </c>
@@ -13878,14 +13878,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="233" t="s">
+      <c r="B25" s="232" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="233"/>
-      <c r="E25" s="231" t="s">
+      <c r="C25" s="232"/>
+      <c r="E25" s="230" t="s">
         <v>387</v>
       </c>
-      <c r="F25" s="232"/>
+      <c r="F25" s="231"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.51</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -13934,15 +13934,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="230" t="s">
+      <c r="B33" s="233" t="s">
         <v>355</v>
       </c>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="233"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="233"/>
+      <c r="H33" s="233"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -13961,24 +13961,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="230"/>
-      <c r="C39" s="230"/>
-      <c r="D39" s="230"/>
-      <c r="E39" s="230"/>
-      <c r="F39" s="230"/>
-      <c r="G39" s="230"/>
-      <c r="H39" s="230"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="230" t="s">
+      <c r="B42" s="233" t="s">
         <v>358</v>
       </c>
-      <c r="C42" s="230"/>
-      <c r="D42" s="230"/>
-      <c r="E42" s="230"/>
-      <c r="F42" s="230"/>
-      <c r="G42" s="230"/>
-      <c r="H42" s="230"/>
+      <c r="C42" s="233"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="233"/>
+      <c r="H42" s="233"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14009,24 +14009,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="230"/>
-      <c r="C49" s="230"/>
-      <c r="D49" s="230"/>
-      <c r="E49" s="230"/>
-      <c r="F49" s="230"/>
-      <c r="G49" s="230"/>
-      <c r="H49" s="230"/>
+      <c r="B49" s="233"/>
+      <c r="C49" s="233"/>
+      <c r="D49" s="233"/>
+      <c r="E49" s="233"/>
+      <c r="F49" s="233"/>
+      <c r="G49" s="233"/>
+      <c r="H49" s="233"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="230" t="s">
+      <c r="B52" s="233" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="230"/>
-      <c r="D52" s="230"/>
-      <c r="E52" s="230"/>
-      <c r="F52" s="230"/>
-      <c r="G52" s="230"/>
-      <c r="H52" s="230"/>
+      <c r="C52" s="233"/>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="233"/>
+      <c r="H52" s="233"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14041,28 +14041,28 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="230"/>
-      <c r="C59" s="230"/>
-      <c r="D59" s="230"/>
-      <c r="E59" s="230"/>
-      <c r="F59" s="230"/>
-      <c r="G59" s="230"/>
-      <c r="H59" s="230"/>
+      <c r="B59" s="233"/>
+      <c r="C59" s="233"/>
+      <c r="D59" s="233"/>
+      <c r="E59" s="233"/>
+      <c r="F59" s="233"/>
+      <c r="G59" s="233"/>
+      <c r="H59" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14132,36 +14132,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="230" t="s">
+      <c r="S2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230"/>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
-      <c r="AA2" s="230" t="s">
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="230"/>
-      <c r="AC2" s="230"/>
+      <c r="AB2" s="233"/>
+      <c r="AC2" s="233"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15548,35 +15548,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
-      <c r="P2" s="230" t="s">
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="P2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="230"/>
-      <c r="R2" s="230"/>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="230"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="230" t="s">
+      <c r="Q2" s="233"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="230"/>
-      <c r="Z2" s="230"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -16983,20 +16983,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -18307,23 +18307,23 @@
         <v>58</v>
       </c>
       <c r="C45" s="113">
-        <f>-Statement!M60</f>
+        <f>-Statement!M110</f>
         <v>18733</v>
       </c>
       <c r="D45" s="113">
-        <f>-Statement!N60</f>
+        <f>-Statement!N110</f>
         <v>24844</v>
       </c>
       <c r="E45" s="113">
-        <f>-Statement!O60</f>
+        <f>-Statement!O110</f>
         <v>25750</v>
       </c>
       <c r="F45" s="113">
-        <f>-Statement!P60</f>
+        <f>-Statement!P110</f>
         <v>23944</v>
       </c>
       <c r="G45" s="114">
-        <f>-Statement!Q60</f>
+        <f>-Statement!Q110</f>
         <v>14646</v>
       </c>
       <c r="H45" s="25">
@@ -18389,6 +18389,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18396,12 +18402,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18439,20 +18439,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="S2" s="244"/>
       <c r="T2" s="244"/>
       <c r="U2" s="244"/>
@@ -19461,16 +19461,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19533,10 +19533,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="233"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19553,7 +19553,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>133.99</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>673433.74</v>
+        <v>604879.1</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.4510000000000001E-2</v>
+        <v>4.4850000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.1960999999999999</v>
+        <v>2.2117</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19621,10 +19621,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="233" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="230"/>
+      <c r="C15" s="233"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19632,7 +19632,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.2676701434227655E-2</v>
+        <v>6.9288044608015784E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93732329856577234</v>
+        <v>0.93071195539198426</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1433345</v>
+        <v>0.14437649999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13702455442145986</v>
+        <v>0.13732876261062876</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19721,20 +19721,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23358.082033062106</v>
+        <v>-23297.5195615962</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -19981,23 +19981,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6496.2022622180302</v>
+        <v>-6494.4646837872097</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5060.8264106581382</v>
+        <v>-5058.1194731515634</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3568.2272711048495</v>
+        <v>-3565.3647910270524</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3268.3629219387994</v>
+        <v>-3264.8674896323796</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1410.1482934628298</v>
+        <v>-1408.2633976822103</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20016,14 +20016,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12291.021029244122</v>
+        <v>-12242.76668120021</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="230" t="s">
+      <c r="B13" s="233" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="230"/>
+      <c r="C13" s="233"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20039,14 +20039,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13702455442145986</v>
+        <v>0.13732876261062876</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="233" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="230"/>
+      <c r="C18" s="233"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19803.767159382645</v>
+        <v>-19791.079835280416</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12291.021029244122</v>
+        <v>-12242.76668120021</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-32094.788188626768</v>
+        <v>-32033.846516480626</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-35855.788188626771</v>
+        <v>-35794.846516480626</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>-7.1340605230057248</v>
+        <v>-7.1219352400478764</v>
       </c>
     </row>
   </sheetData>
@@ -20160,20 +20160,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="230" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
       <c r="G2" s="242"/>
       <c r="H2" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21105,10 +21105,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="233" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="230"/>
+      <c r="C37" s="233"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13702455442145986</v>
+        <v>0.13732876261062876</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>184334.09458787731</v>
+        <v>184086.82347798249</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21170,14 +21170,14 @@
       </c>
       <c r="C44" s="142">
         <f ca="1">C42/C43</f>
-        <v>36.676103181034087</v>
+        <v>36.626904790684932</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="230" t="s">
+      <c r="B46" s="233" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="230"/>
+      <c r="C46" s="233"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -21233,10 +21233,10 @@
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="230" t="s">
+      <c r="B54" s="233" t="s">
         <v>324</v>
       </c>
-      <c r="C54" s="230"/>
+      <c r="C54" s="233"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -21253,7 +21253,7 @@
       </c>
       <c r="C56" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13702455442145986</v>
+        <v>0.13732876261062876</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="C60" s="24">
         <f ca="1">C59/(1+C56)^5-G30+G31</f>
-        <v>-57408.645089668615</v>
+        <v>-57332.787155528902</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="C62" s="142">
         <f ca="1">C60/C61</f>
-        <v>-11.42233288692173</v>
+        <v>-11.407239784227796</v>
       </c>
     </row>
   </sheetData>
@@ -21358,10 +21358,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="230"/>
+      <c r="C4" s="233"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21370,7 +21370,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-7.1340605230057248</v>
+        <v>-7.1219352400478764</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21379,7 +21379,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C44</f>
-        <v>36.676103181034087</v>
+        <v>36.626904790684932</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21397,7 +21397,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C62</f>
-        <v>-11.42233288692173</v>
+        <v>-11.407239784227796</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>14.379737127540219</v>
+        <v>14.374242126365875</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>133.99</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.89268051998253439</v>
+        <v>-0.88056300684365707</v>
       </c>
     </row>
   </sheetData>
@@ -21489,20 +21489,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="230" t="s">
+      <c r="C3" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="230"/>
-      <c r="E3" s="230"/>
-      <c r="F3" s="230"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
       <c r="G3" s="242"/>
       <c r="H3" s="243" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="230"/>
-      <c r="L3" s="230"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -21677,7 +21677,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-967685.99948137393</v>
+        <v>-965176.99828647287</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -21731,23 +21731,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13173.636074625276</v>
+        <v>-13170.112442666974</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19117.000981734869</v>
+        <v>-19106.775670141153</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27741.750604420544</v>
+        <v>-27719.495797650969</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40257.60773529164</v>
+        <v>-40214.55323185429</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58420.068858609258</v>
+        <v>-58341.980800916637</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -21766,7 +21766,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-509196.30098462629</v>
+        <v>-507197.20461403806</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>133.99</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-133.63855257447432</v>
+        <v>-133.20953492981855</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13702455442145986</v>
+        <v>0.13732876261062876</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>673433.74</v>
+        <v>604879.1</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>677194.74</v>
+        <v>608640.1</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21891,7 +21891,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158710.06425468158</v>
+        <v>-158552.91794323002</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>-509196.30098462629</v>
+        <v>-507197.20461403806</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>-667906.36523930787</v>
+        <v>-665750.12255726801</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21936,7 +21936,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>-671667.36523930787</v>
+        <v>-669511.12255726801</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>-133.63855257447432</v>
+        <v>-133.20953492981855</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22401,17 +22401,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28963,7 +28963,7 @@
       <c r="AA116" s="67"/>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>133.99</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29010,7 +29010,7 @@
       <c r="AA117" s="67"/>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>133.99</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30316,7 +30316,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-216.11290322580646</v>
+        <v>-194.11290322580643</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30353,7 +30353,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>11.727209140114949</v>
+        <v>10.533395178840466</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30390,7 +30390,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>6.045511786990323</v>
+        <v>5.4300868987557669</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30427,7 +30427,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>673433.74</v>
+        <v>604879.1</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30464,7 +30464,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>690789.74</v>
+        <v>622235.1</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30501,7 +30501,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>12.848794524115098</v>
+        <v>11.573667764075665</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30538,7 +30538,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>-136.81714002772827</v>
+        <v>-123.23927510398099</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30673,7 +30673,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="100">AC153/AC157</f>
-        <v>-122.66552641165755</v>
+        <v>-110.17834244080146</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30710,7 +30710,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="100"/>
-        <v>-80.577363816633621</v>
+        <v>-72.580788522104285</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -30747,7 +30747,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="103">AC157/AC153</f>
-        <v>-8.152249692746312E-3</v>
+        <v>-9.0761939038726917E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30784,7 +30784,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-4.627210985894469E-3</v>
+        <v>-5.1516410469464062E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31398,7 +31398,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-5.5848107640107253E-3</v>
+        <v>-6.2177714521794523E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33123,15 +33123,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="230" t="s">
+      <c r="B4" s="233" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="230"/>
-      <c r="E4" s="230" t="s">
+      <c r="C4" s="233"/>
+      <c r="E4" s="233" t="s">
         <v>242</v>
       </c>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33139,7 +33139,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>133.99</v>
+        <v>120.35</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -33155,7 +33155,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>673433.74</v>
+        <v>604879.1</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>690789.74</v>
+        <v>622235.1</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33195,7 +33195,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-216.11290322580646</v>
+        <v>-194.11290322580643</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>245</v>
@@ -33215,7 +33215,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>11.727209140114949</v>
+        <v>10.533395178840466</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>246</v>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>6.045511786990323</v>
+        <v>5.4300868987557669</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>12.848794524115098</v>
+        <v>11.573667764075665</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33264,18 +33264,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>-136.81714002772827</v>
+        <v>-123.23927510398099</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="230" t="s">
+      <c r="B15" s="233" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="230"/>
-      <c r="E15" s="230" t="s">
+      <c r="C15" s="233"/>
+      <c r="E15" s="233" t="s">
         <v>248</v>
       </c>
-      <c r="F15" s="230"/>
+      <c r="F15" s="233"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33326,14 +33326,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="230" t="s">
+      <c r="B21" s="233" t="s">
         <v>247</v>
       </c>
-      <c r="C21" s="230"/>
-      <c r="E21" s="230" t="s">
+      <c r="C21" s="233"/>
+      <c r="E21" s="233" t="s">
         <v>251</v>
       </c>
-      <c r="F21" s="230"/>
+      <c r="F21" s="233"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33402,14 +33402,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="230" t="s">
+      <c r="B29" s="233" t="s">
         <v>252</v>
       </c>
-      <c r="C29" s="230"/>
-      <c r="E29" s="230" t="s">
+      <c r="C29" s="233"/>
+      <c r="E29" s="233" t="s">
         <v>258</v>
       </c>
-      <c r="F29" s="230"/>
+      <c r="F29" s="233"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33485,14 +33485,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="230" t="s">
+      <c r="B37" s="233" t="s">
         <v>270</v>
       </c>
-      <c r="C37" s="230"/>
-      <c r="E37" s="230" t="s">
+      <c r="C37" s="233"/>
+      <c r="E37" s="233" t="s">
         <v>273</v>
       </c>
-      <c r="F37" s="230"/>
+      <c r="F37" s="233"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33500,7 +33500,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-4.627210985894469E-3</v>
+        <v>-5.1516410469464062E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>272</v>
@@ -33516,7 +33516,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>-8.152249692746312E-3</v>
+        <v>-9.0761939038726917E-3</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>274</v>
@@ -33561,14 +33561,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="230" t="s">
+      <c r="B45" s="233" t="s">
         <v>281</v>
       </c>
-      <c r="C45" s="230"/>
-      <c r="E45" s="230" t="s">
+      <c r="C45" s="233"/>
+      <c r="E45" s="233" t="s">
         <v>287</v>
       </c>
-      <c r="F45" s="230"/>
+      <c r="F45" s="233"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33601,18 +33601,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>-5.5848107640107253E-3</v>
+        <v>-6.2177714521794523E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="230" t="s">
+      <c r="B51" s="233" t="s">
         <v>284</v>
       </c>
-      <c r="C51" s="230"/>
-      <c r="E51" s="230" t="s">
+      <c r="C51" s="233"/>
+      <c r="E51" s="233" t="s">
         <v>305</v>
       </c>
-      <c r="F51" s="230"/>
+      <c r="F51" s="233"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -33780,7 +33780,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>133.99</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33809,7 +33809,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>673433.74</v>
+        <v>604879.1</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33838,7 +33838,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>690789.74</v>
+        <v>622235.1</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-216.11290322580646</v>
+        <v>-194.11290322580643</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>11.727209140114949</v>
+        <v>10.533395178840466</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33925,7 +33925,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>6.045511786990323</v>
+        <v>5.4300868987557669</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>12.848794524115098</v>
+        <v>11.573667764075665</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33983,7 +33983,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>-136.81714002772827</v>
+        <v>-123.23927510398099</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34756,7 +34756,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-4.627210985894469E-3</v>
+        <v>-5.1516410469464062E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34785,7 +34785,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>-8.152249692746312E-3</v>
+        <v>-9.0761939038726917E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35108,7 +35108,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>-5.5848107640107253E-3</v>
+        <v>-6.2177714521794523E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35646,14 +35646,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="236" t="s">
         <v>315</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="F3" s="236" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>316</v>
       </c>
-      <c r="G3" s="235"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35720,19 +35720,19 @@
       <c r="B7" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C7" s="237">
+      <c r="C7" s="234">
         <f>Statement!AA89</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="F7" s="237">
+      <c r="D7" s="235"/>
+      <c r="F7" s="234">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="238"/>
+      <c r="G7" s="235"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35759,19 +35759,19 @@
       <c r="B9" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C9" s="237">
+      <c r="C9" s="234">
         <f>Statement!AA90</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="F9" s="237">
+      <c r="D9" s="235"/>
+      <c r="F9" s="234">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="238"/>
+      <c r="G9" s="235"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35798,19 +35798,19 @@
       <c r="B11" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="234">
         <f>Statement!AA91</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="F11" s="237">
+      <c r="D11" s="235"/>
+      <c r="F11" s="234">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="238"/>
+      <c r="G11" s="235"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35837,19 +35837,19 @@
       <c r="B13" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C13" s="237">
+      <c r="C13" s="234">
         <f>Statement!AA95</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="F13" s="237">
+      <c r="D13" s="235"/>
+      <c r="F13" s="234">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="238"/>
+      <c r="G13" s="235"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35876,19 +35876,19 @@
       <c r="B15" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C15" s="237">
+      <c r="C15" s="234">
         <f>Statement!AA96</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="F15" s="237">
+      <c r="D15" s="235"/>
+      <c r="F15" s="234">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="238"/>
+      <c r="G15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35915,19 +35915,19 @@
       <c r="B17" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C17" s="237">
+      <c r="C17" s="234">
         <f>Statement!AA98</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="F17" s="237">
+      <c r="D17" s="235"/>
+      <c r="F17" s="234">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="238"/>
+      <c r="G17" s="235"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -35954,22 +35954,22 @@
       <c r="B19" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="234">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="238"/>
-      <c r="F19" s="237">
+      <c r="D19" s="235"/>
+      <c r="F19" s="234">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="238"/>
+      <c r="G19" s="235"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35996,22 +35996,22 @@
       <c r="B21" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C21" s="237">
+      <c r="C21" s="234">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="F21" s="237">
+      <c r="D21" s="235"/>
+      <c r="F21" s="234">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="238"/>
+      <c r="G21" s="235"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36059,22 +36059,22 @@
       <c r="B25" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C25" s="237">
+      <c r="C25" s="234">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="F25" s="237">
+      <c r="D25" s="235"/>
+      <c r="F25" s="234">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="238"/>
+      <c r="G25" s="235"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36101,22 +36101,22 @@
       <c r="B27" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C27" s="237">
+      <c r="C27" s="234">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="238"/>
-      <c r="F27" s="237">
+      <c r="D27" s="235"/>
+      <c r="F27" s="234">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="238"/>
+      <c r="G27" s="235"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36143,22 +36143,22 @@
       <c r="B29" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C29" s="237">
+      <c r="C29" s="234">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="238"/>
-      <c r="F29" s="237">
+      <c r="D29" s="235"/>
+      <c r="F29" s="234">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="238"/>
+      <c r="G29" s="235"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36185,22 +36185,22 @@
       <c r="B31" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C31" s="237">
+      <c r="C31" s="234">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="F31" s="237">
+      <c r="D31" s="235"/>
+      <c r="F31" s="234">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="238"/>
+      <c r="G31" s="235"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36227,25 +36227,37 @@
       <c r="B33" s="206" t="s">
         <v>317</v>
       </c>
-      <c r="C33" s="237">
+      <c r="C33" s="234">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="F33" s="237">
+      <c r="D33" s="235"/>
+      <c r="F33" s="234">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="238"/>
+      <c r="G33" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -36262,18 +36274,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95736EB-C546-C24A-B1CF-75218DE151D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB90BB29-CB5A-8B4A-9D2A-B1E187576F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="3" activeTab="12" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,7 +130,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -140,19 +161,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="405">
   <si>
     <t>Ticker</t>
   </si>
@@ -781,9 +811,6 @@
     <t>Year 5 UFCF</t>
   </si>
   <si>
-    <t>Applied EV/UFCF ratio</t>
-  </si>
-  <si>
     <t>AVG target price</t>
   </si>
   <si>
@@ -1367,6 +1394,9 @@
   </si>
   <si>
     <t>Sales/Assets</t>
+  </si>
+  <si>
+    <t>Applied EV/FCFF ratio</t>
   </si>
 </sst>
 </file>
@@ -2277,6 +2307,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2284,9 +2326,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2304,19 +2343,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12649,7 +12679,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12668,11 +12698,9 @@
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
     <v>18.965</v>
-    <v>2.2117</v>
-    <v>-6.67</v>
-    <v>-5.2511000000000002E-2</v>
-    <v>0.66</v>
-    <v>5.4840000000000002E-3</v>
+    <v>2.2035999999999998</v>
+    <v>-11.25</v>
+    <v>-9.2062000000000005E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -12680,35 +12708,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>130.74</v>
+    <v>116.4699</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46205.999999293752</v>
+    <v>46210.767058205471</v>
     <v>0</v>
-    <v>117.63</v>
-    <v>604879100000</v>
+    <v>108.36</v>
+    <v>557634700000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>128.91499999999999</v>
+    <v>116.31</v>
     <v>0</v>
-    <v>127.02</v>
-    <v>120.35</v>
-    <v>121.01</v>
+    <v>122.2</v>
+    <v>110.95</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>125021717</v>
-    <v>130207762</v>
+    <v>99608122</v>
+    <v>131060866</v>
     <v>1989</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12722,28 +12764,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.1</v>
-    <v>2.235E-3</v>
+    <v>-0.06</v>
+    <v>-1.338E-3</v>
     <v>US</v>
-    <v>45.05</v>
+    <v>44.91</v>
     <v>Index</v>
-    <v>3</v>
-    <v>44.53</v>
+    <v>6</v>
+    <v>44.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.03</v>
-    <v>44.75</v>
+    <v>44.57</v>
     <v>44.85</v>
+    <v>44.79</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12765,8 +12807,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12787,7 +12827,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12797,6 +12836,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12832,7 +12876,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12843,16 +12887,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12946,19 +12987,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13030,9 +13065,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13040,9 +13072,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13530,18 +13559,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="230" t="s">
+      <c r="B2" s="234" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="231"/>
-      <c r="E2" s="230" t="s">
-        <v>289</v>
-      </c>
-      <c r="F2" s="231"/>
-      <c r="H2" s="230" t="s">
-        <v>330</v>
-      </c>
-      <c r="I2" s="231"/>
+      <c r="C2" s="235"/>
+      <c r="E2" s="234" t="s">
+        <v>288</v>
+      </c>
+      <c r="F2" s="235"/>
+      <c r="H2" s="234" t="s">
+        <v>329</v>
+      </c>
+      <c r="I2" s="235"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13552,11 +13581,11 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="185" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>604879.1</v>
+        <v>557634.70000000007</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13564,7 +13593,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-7.1219352400478764</v>
+        <v>-7.1598029745542915</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13580,7 +13609,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>622235.1</v>
+        <v>574990.70000000007</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13588,7 +13617,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.626904790684932</v>
+        <v>36.031729813513621</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13597,10 +13626,10 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>120.35</v>
+        <v>110.95</v>
       </c>
       <c r="E5" s="185" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F5" s="189">
         <f>Statement!AC26</f>
@@ -13619,16 +13648,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>121.01</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-194.11290322580643</v>
+        <v>-178.95161290322582</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13636,7 +13665,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-11.407239784227796</v>
+        <v>-12.202527034723067</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13645,14 +13674,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-6.67</v>
+        <v>-11.25</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>10.533395178840466</v>
+        <v>9.7106788125662629</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13660,23 +13689,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>14.374242126365875</v>
+        <v>14.017159635822628</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.66</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>-9.0761939038726917E-3</v>
+        <v>-9.8451549015870048E-3</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13684,7 +13713,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.88056300684365707</v>
+        <v>-0.87366237371948963</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13693,26 +13722,26 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-5.2511000000000002E-2</v>
+        <v>-9.2062000000000005E-2</v>
       </c>
       <c r="E9" s="185" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-5.1516410469464062E-3</v>
+        <v>-5.5881027489860296E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>5.4840000000000002E-3</v>
+      <c r="C10" s="72" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC164</f>
@@ -13728,7 +13757,7 @@
         <v>142.35</v>
       </c>
       <c r="E11" s="186" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC163</f>
@@ -13757,7 +13786,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2117</v>
+        <v>2.2035999999999998</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>99</v>
@@ -13773,7 +13802,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>130207762</v>
+        <v>131060866</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>100</v>
@@ -13785,16 +13814,16 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E15" s="185" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>-6.2177714521794523E-3</v>
+        <v>-6.7445587586281832E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="E16" s="186" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F16" s="191">
         <f>Statement!AC175</f>
@@ -13802,12 +13831,12 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="232" t="s">
+      <c r="B17" s="236" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="232"/>
+      <c r="C17" s="236"/>
       <c r="E17" s="184" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F17" s="194">
         <f>Statement!AC171</f>
@@ -13819,10 +13848,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E18" s="185" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F18" s="190">
         <f>Statement!AC144</f>
@@ -13838,7 +13867,7 @@
         <v>1000000</v>
       </c>
       <c r="E19" s="185" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F19" s="190">
         <f>Statement!AC146</f>
@@ -13850,10 +13879,10 @@
         <v>88</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E20" s="186" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F20" s="191">
         <f>Statement!AC147</f>
@@ -13865,7 +13894,7 @@
         <v>89</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I21" s="50"/>
     </row>
@@ -13874,18 +13903,18 @@
         <v>90</v>
       </c>
       <c r="C22" s="68" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="232" t="s">
+      <c r="B25" s="236" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="232"/>
-      <c r="E25" s="230" t="s">
-        <v>387</v>
-      </c>
-      <c r="F25" s="231"/>
+      <c r="C25" s="236"/>
+      <c r="E25" s="234" t="s">
+        <v>386</v>
+      </c>
+      <c r="F25" s="235"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -13894,12 +13923,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.85</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13910,16 +13939,16 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="E27" s="186" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="184" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C28" s="218">
         <v>0</v>
@@ -13927,65 +13956,65 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="184" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C29" s="218">
         <v>0.12</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="233" t="s">
-        <v>355</v>
-      </c>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
+      <c r="B33" s="231" t="s">
+        <v>354</v>
+      </c>
+      <c r="C33" s="231"/>
+      <c r="D33" s="231"/>
+      <c r="E33" s="231"/>
+      <c r="F33" s="231"/>
+      <c r="G33" s="231"/>
+      <c r="H33" s="231"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="231"/>
+      <c r="C39" s="231"/>
+      <c r="D39" s="231"/>
+      <c r="E39" s="231"/>
+      <c r="F39" s="231"/>
+      <c r="G39" s="231"/>
+      <c r="H39" s="231"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="231" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="233" t="s">
-        <v>358</v>
-      </c>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="233"/>
+      <c r="C42" s="231"/>
+      <c r="D42" s="231"/>
+      <c r="E42" s="231"/>
+      <c r="F42" s="231"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="231"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D44" s="41"/>
       <c r="E44" s="41" t="s">
@@ -13994,46 +14023,46 @@
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="225" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="225" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="233"/>
-      <c r="C49" s="233"/>
-      <c r="D49" s="233"/>
-      <c r="E49" s="233"/>
-      <c r="F49" s="233"/>
-      <c r="G49" s="233"/>
-      <c r="H49" s="233"/>
+      <c r="B49" s="231"/>
+      <c r="C49" s="231"/>
+      <c r="D49" s="231"/>
+      <c r="E49" s="231"/>
+      <c r="F49" s="231"/>
+      <c r="G49" s="231"/>
+      <c r="H49" s="231"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="233" t="s">
+      <c r="B52" s="231" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="233"/>
+      <c r="C52" s="231"/>
+      <c r="D52" s="231"/>
+      <c r="E52" s="231"/>
+      <c r="F52" s="231"/>
+      <c r="G52" s="231"/>
+      <c r="H52" s="231"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D54" s="41"/>
       <c r="E54" s="41" t="s">
@@ -14041,13 +14070,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="233"/>
-      <c r="C59" s="233"/>
-      <c r="D59" s="233"/>
-      <c r="E59" s="233"/>
-      <c r="F59" s="233"/>
-      <c r="G59" s="233"/>
-      <c r="H59" s="233"/>
+      <c r="B59" s="231"/>
+      <c r="C59" s="231"/>
+      <c r="D59" s="231"/>
+      <c r="E59" s="231"/>
+      <c r="F59" s="231"/>
+      <c r="G59" s="231"/>
+      <c r="H59" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14132,36 +14161,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="232"/>
+      <c r="H2" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="233" t="s">
+      <c r="S2" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233" t="s">
+      <c r="T2" s="231"/>
+      <c r="U2" s="231"/>
+      <c r="V2" s="231"/>
+      <c r="W2" s="231"/>
+      <c r="X2" s="231"/>
+      <c r="Y2" s="231"/>
+      <c r="Z2" s="231"/>
+      <c r="AA2" s="231" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="AB2" s="231"/>
+      <c r="AC2" s="231"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14172,32 +14201,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="230" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="230"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
+      <c r="H4" s="230"/>
+      <c r="I4" s="230"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="240" t="s">
+      <c r="S4" s="242" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
-      <c r="AA4" s="241"/>
-      <c r="AB4" s="241"/>
-      <c r="AC4" s="241"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
+      <c r="AA4" s="243"/>
+      <c r="AB4" s="243"/>
+      <c r="AC4" s="243"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14340,11 +14369,11 @@
         <v>38452.690209023996</v>
       </c>
       <c r="N6" s="89" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="89" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R6" s="1" t="str">
         <f>B6</f>
@@ -14439,11 +14468,11 @@
         <v>27957.189758960001</v>
       </c>
       <c r="N7" s="89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R7" s="1" t="str">
         <f t="shared" ref="R7:R10" si="3">B7</f>
@@ -14538,11 +14567,11 @@
         <v>66409.879967984001</v>
       </c>
       <c r="N8" s="89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O8" s="5"/>
       <c r="Q8" s="89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R8" s="1" t="str">
         <f t="shared" si="3"/>
@@ -14637,11 +14666,11 @@
         <v>6177.5999999999995</v>
       </c>
       <c r="N9" s="89" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O9" s="5"/>
       <c r="Q9" s="89" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R9" s="1" t="str">
         <f t="shared" si="3"/>
@@ -14733,11 +14762,11 @@
         <v>4678.557983820001</v>
       </c>
       <c r="N10" s="89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O10" s="5"/>
       <c r="Q10" s="89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R10" s="1" t="str">
         <f t="shared" si="3"/>
@@ -14828,11 +14857,11 @@
         <v>77266.037951804014</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O11" s="5"/>
       <c r="Q11" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R11" s="16" t="s">
         <v>116</v>
@@ -14885,33 +14914,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="230" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="230"/>
+      <c r="E13" s="230"/>
+      <c r="F13" s="230"/>
+      <c r="G13" s="230"/>
+      <c r="H13" s="230"/>
+      <c r="I13" s="230"/>
+      <c r="J13" s="230"/>
+      <c r="K13" s="230"/>
+      <c r="L13" s="230"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="240" t="s">
+      <c r="S13" s="242" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="241"/>
-      <c r="U13" s="241"/>
-      <c r="V13" s="241"/>
-      <c r="W13" s="241"/>
-      <c r="X13" s="241"/>
-      <c r="Y13" s="241"/>
-      <c r="Z13" s="241"/>
-      <c r="AA13" s="241"/>
-      <c r="AB13" s="241"/>
-      <c r="AC13" s="241"/>
+      <c r="T13" s="243"/>
+      <c r="U13" s="243"/>
+      <c r="V13" s="243"/>
+      <c r="W13" s="243"/>
+      <c r="X13" s="243"/>
+      <c r="Y13" s="243"/>
+      <c r="Z13" s="243"/>
+      <c r="AA13" s="243"/>
+      <c r="AB13" s="243"/>
+      <c r="AC13" s="243"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15548,35 +15577,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="232"/>
+      <c r="H2" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="P2" s="233" t="s">
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="P2" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233" t="s">
+      <c r="Q2" s="231"/>
+      <c r="R2" s="231"/>
+      <c r="S2" s="231"/>
+      <c r="T2" s="231"/>
+      <c r="U2" s="231"/>
+      <c r="V2" s="231"/>
+      <c r="W2" s="231"/>
+      <c r="X2" s="231" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
+      <c r="Y2" s="231"/>
+      <c r="Z2" s="231"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15585,31 +15614,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="230" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="P4" s="241" t="s">
+      <c r="D4" s="230"/>
+      <c r="E4" s="230"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
+      <c r="H4" s="230"/>
+      <c r="I4" s="230"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
+      <c r="P4" s="243" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="241"/>
-      <c r="R4" s="241"/>
-      <c r="S4" s="241"/>
-      <c r="T4" s="241"/>
-      <c r="U4" s="241"/>
-      <c r="V4" s="241"/>
-      <c r="W4" s="241"/>
-      <c r="X4" s="241"/>
-      <c r="Y4" s="241"/>
-      <c r="Z4" s="241"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="243"/>
+      <c r="S4" s="243"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15804,32 +15833,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="230" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
+      <c r="D9" s="230"/>
+      <c r="E9" s="230"/>
+      <c r="F9" s="230"/>
+      <c r="G9" s="230"/>
+      <c r="H9" s="230"/>
+      <c r="I9" s="230"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="230"/>
+      <c r="L9" s="230"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="241" t="s">
+      <c r="P9" s="243" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="241"/>
-      <c r="R9" s="241"/>
-      <c r="S9" s="241"/>
-      <c r="T9" s="241"/>
-      <c r="U9" s="241"/>
-      <c r="V9" s="241"/>
-      <c r="W9" s="241"/>
-      <c r="X9" s="241"/>
-      <c r="Y9" s="241"/>
-      <c r="Z9" s="241"/>
+      <c r="Q9" s="243"/>
+      <c r="R9" s="243"/>
+      <c r="S9" s="243"/>
+      <c r="T9" s="243"/>
+      <c r="U9" s="243"/>
+      <c r="V9" s="243"/>
+      <c r="W9" s="243"/>
+      <c r="X9" s="243"/>
+      <c r="Y9" s="243"/>
+      <c r="Z9" s="243"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -16399,31 +16428,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="230" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
-      <c r="P18" s="241" t="s">
+      <c r="D18" s="230"/>
+      <c r="E18" s="230"/>
+      <c r="F18" s="230"/>
+      <c r="G18" s="230"/>
+      <c r="H18" s="230"/>
+      <c r="I18" s="230"/>
+      <c r="J18" s="230"/>
+      <c r="K18" s="230"/>
+      <c r="L18" s="230"/>
+      <c r="P18" s="243" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="241"/>
-      <c r="R18" s="241"/>
-      <c r="S18" s="241"/>
-      <c r="T18" s="241"/>
-      <c r="U18" s="241"/>
-      <c r="V18" s="241"/>
-      <c r="W18" s="241"/>
-      <c r="X18" s="241"/>
-      <c r="Y18" s="241"/>
-      <c r="Z18" s="241"/>
+      <c r="Q18" s="243"/>
+      <c r="R18" s="243"/>
+      <c r="S18" s="243"/>
+      <c r="T18" s="243"/>
+      <c r="U18" s="243"/>
+      <c r="V18" s="243"/>
+      <c r="W18" s="243"/>
+      <c r="X18" s="243"/>
+      <c r="Y18" s="243"/>
+      <c r="Z18" s="243"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -16983,20 +17012,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -17014,18 +17043,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="230" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
+      <c r="D5" s="230"/>
+      <c r="E5" s="230"/>
+      <c r="F5" s="230"/>
+      <c r="G5" s="230"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="230"/>
+      <c r="L5" s="230"/>
       <c r="P5" s="244"/>
       <c r="Q5" s="244"/>
       <c r="R5" s="244"/>
@@ -17222,18 +17251,18 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="239" t="s">
+      <c r="C11" s="230" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
+      <c r="D11" s="230"/>
+      <c r="E11" s="230"/>
+      <c r="F11" s="230"/>
+      <c r="G11" s="230"/>
+      <c r="H11" s="230"/>
+      <c r="I11" s="230"/>
+      <c r="J11" s="230"/>
+      <c r="K11" s="230"/>
+      <c r="L11" s="230"/>
       <c r="N11" s="90"/>
       <c r="P11" s="244"/>
       <c r="Q11" s="244"/>
@@ -17487,18 +17516,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="230" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="230"/>
+      <c r="E18" s="230"/>
+      <c r="F18" s="230"/>
+      <c r="G18" s="230"/>
+      <c r="H18" s="230"/>
+      <c r="I18" s="230"/>
+      <c r="J18" s="230"/>
+      <c r="K18" s="230"/>
+      <c r="L18" s="230"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17716,18 +17745,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="230" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="230"/>
+      <c r="E26" s="230"/>
+      <c r="F26" s="230"/>
+      <c r="G26" s="230"/>
+      <c r="H26" s="230"/>
+      <c r="I26" s="230"/>
+      <c r="J26" s="230"/>
+      <c r="K26" s="230"/>
+      <c r="L26" s="230"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -17919,18 +17948,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="239" t="s">
+      <c r="C33" s="230" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="239"/>
-      <c r="E33" s="239"/>
-      <c r="F33" s="239"/>
-      <c r="G33" s="239"/>
-      <c r="H33" s="239"/>
-      <c r="I33" s="239"/>
-      <c r="J33" s="239"/>
-      <c r="K33" s="239"/>
-      <c r="L33" s="239"/>
+      <c r="D33" s="230"/>
+      <c r="E33" s="230"/>
+      <c r="F33" s="230"/>
+      <c r="G33" s="230"/>
+      <c r="H33" s="230"/>
+      <c r="I33" s="230"/>
+      <c r="J33" s="230"/>
+      <c r="K33" s="230"/>
+      <c r="L33" s="230"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18114,18 +18143,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="239" t="s">
+      <c r="C40" s="230" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="230"/>
+      <c r="J40" s="230"/>
+      <c r="K40" s="230"/>
+      <c r="L40" s="230"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18439,20 +18468,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="232"/>
+      <c r="H2" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
       <c r="S2" s="244"/>
       <c r="T2" s="244"/>
       <c r="U2" s="244"/>
@@ -18470,18 +18499,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="230" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="230"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
+      <c r="H4" s="230"/>
+      <c r="I4" s="230"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
       <c r="S4" s="244"/>
       <c r="T4" s="244"/>
       <c r="U4" s="244"/>
@@ -18855,18 +18884,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="239" t="s">
+      <c r="C13" s="230" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
+      <c r="D13" s="230"/>
+      <c r="E13" s="230"/>
+      <c r="F13" s="230"/>
+      <c r="G13" s="230"/>
+      <c r="H13" s="230"/>
+      <c r="I13" s="230"/>
+      <c r="J13" s="230"/>
+      <c r="K13" s="230"/>
+      <c r="L13" s="230"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -18959,18 +18988,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="239" t="s">
+      <c r="C18" s="230" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="239"/>
-      <c r="F18" s="239"/>
-      <c r="G18" s="239"/>
-      <c r="H18" s="239"/>
-      <c r="I18" s="239"/>
-      <c r="J18" s="239"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
+      <c r="D18" s="230"/>
+      <c r="E18" s="230"/>
+      <c r="F18" s="230"/>
+      <c r="G18" s="230"/>
+      <c r="H18" s="230"/>
+      <c r="I18" s="230"/>
+      <c r="J18" s="230"/>
+      <c r="K18" s="230"/>
+      <c r="L18" s="230"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19162,18 +19191,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="239" t="s">
-        <v>264</v>
-      </c>
-      <c r="D25" s="239"/>
-      <c r="E25" s="239"/>
-      <c r="F25" s="239"/>
-      <c r="G25" s="239"/>
-      <c r="H25" s="239"/>
-      <c r="I25" s="239"/>
-      <c r="J25" s="239"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="239"/>
+      <c r="C25" s="230" t="s">
+        <v>263</v>
+      </c>
+      <c r="D25" s="230"/>
+      <c r="E25" s="230"/>
+      <c r="F25" s="230"/>
+      <c r="G25" s="230"/>
+      <c r="H25" s="230"/>
+      <c r="I25" s="230"/>
+      <c r="J25" s="230"/>
+      <c r="K25" s="230"/>
+      <c r="L25" s="230"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19267,7 +19296,7 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C28" s="93">
         <f>C27+C20-C21+C22</f>
@@ -19311,22 +19340,22 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="239" t="s">
+      <c r="C31" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="239"/>
-      <c r="E31" s="239"/>
-      <c r="F31" s="239"/>
-      <c r="G31" s="239"/>
-      <c r="H31" s="239"/>
-      <c r="I31" s="239"/>
-      <c r="J31" s="239"/>
-      <c r="K31" s="239"/>
-      <c r="L31" s="239"/>
+      <c r="D31" s="230"/>
+      <c r="E31" s="230"/>
+      <c r="F31" s="230"/>
+      <c r="G31" s="230"/>
+      <c r="H31" s="230"/>
+      <c r="I31" s="230"/>
+      <c r="J31" s="230"/>
+      <c r="K31" s="230"/>
+      <c r="L31" s="230"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C32" s="12">
         <f>C5</f>
@@ -19533,10 +19562,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="231" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="231"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19553,7 +19582,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>120.35</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19562,7 +19591,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>604879.1</v>
+        <v>557634.70000000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19580,7 +19609,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19589,7 +19618,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.2117</v>
+        <v>2.2035999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19621,10 +19650,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="231" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="233"/>
+      <c r="C15" s="231"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19632,7 +19661,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.9288044608015784E-2</v>
+        <v>7.4719699495093203E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19641,7 +19670,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93071195539198426</v>
+        <v>0.92528030050490684</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19659,7 +19688,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14437649999999999</v>
+        <v>0.14395199999999997</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19668,12 +19697,12 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13732876261062876</v>
+        <v>0.13638349219874299</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C21" s="135">
         <v>0</v>
@@ -19721,20 +19750,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -19752,18 +19781,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="230" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
+      <c r="D5" s="230"/>
+      <c r="E5" s="230"/>
+      <c r="F5" s="230"/>
+      <c r="G5" s="230"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="230"/>
+      <c r="L5" s="230"/>
       <c r="P5" s="244"/>
       <c r="Q5" s="244"/>
       <c r="R5" s="244"/>
@@ -19837,7 +19866,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C7" s="111">
         <f>'FCF &amp; Other'!C28</f>
@@ -19927,7 +19956,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23297.5195615962</v>
+        <v>-23486.742753784831</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -19972,7 +20001,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C10" s="137"/>
       <c r="D10" s="137"/>
@@ -19981,23 +20010,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6494.4646837872097</v>
+        <v>-6499.8669316628302</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5058.1194731515634</v>
+        <v>-5066.5378975749927</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3565.3647910270524</v>
+        <v>-3574.2694559165493</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3264.8674896323796</v>
+        <v>-3275.7442245807038</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1408.2633976822103</v>
+        <v>-1414.1302824251998</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20016,14 +20045,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12242.76668120021</v>
+        <v>-12393.620957949592</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="233" t="s">
+      <c r="B13" s="231" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="233"/>
+      <c r="C13" s="231"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20039,14 +20068,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13732876261062876</v>
+        <v>0.13638349219874299</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="231" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="233"/>
+      <c r="C18" s="231"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20054,7 +20083,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19791.079835280416</v>
+        <v>-19830.548792160276</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20063,7 +20092,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12242.76668120021</v>
+        <v>-12393.620957949592</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20072,7 +20101,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-32033.846516480626</v>
+        <v>-32224.169750109868</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20099,7 +20128,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-35794.846516480626</v>
+        <v>-35985.169750109868</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20117,7 +20146,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>-7.1219352400478764</v>
+        <v>-7.1598029745542915</v>
       </c>
     </row>
   </sheetData>
@@ -20138,7 +20167,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="82" customWidth="1"/>
@@ -20160,37 +20189,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="232"/>
+      <c r="H2" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="239" t="s">
+      <c r="C4" s="230" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="230"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
+      <c r="H4" s="230"/>
+      <c r="I4" s="230"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20331,7 +20360,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C8" s="91">
         <f>'FCF &amp; Other'!C28</f>
@@ -20379,18 +20408,18 @@
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="239" t="s">
+      <c r="C10" s="230" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
+      <c r="D10" s="230"/>
+      <c r="E10" s="230"/>
+      <c r="F10" s="230"/>
+      <c r="G10" s="230"/>
+      <c r="H10" s="230"/>
+      <c r="I10" s="230"/>
+      <c r="J10" s="230"/>
+      <c r="K10" s="230"/>
+      <c r="L10" s="230"/>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20533,7 +20562,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C14" s="137"/>
       <c r="D14" s="94">
@@ -20584,18 +20613,18 @@
       <c r="N15" s="90"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="239" t="s">
+      <c r="C16" s="230" t="s">
         <v>191</v>
       </c>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239"/>
-      <c r="F16" s="239"/>
-      <c r="G16" s="239"/>
-      <c r="H16" s="239"/>
-      <c r="I16" s="239"/>
-      <c r="J16" s="239"/>
-      <c r="K16" s="239"/>
-      <c r="L16" s="239"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="230"/>
+      <c r="F16" s="230"/>
+      <c r="G16" s="230"/>
+      <c r="H16" s="230"/>
+      <c r="I16" s="230"/>
+      <c r="J16" s="230"/>
+      <c r="K16" s="230"/>
+      <c r="L16" s="230"/>
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20729,18 +20758,18 @@
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="239" t="s">
+      <c r="C21" s="230" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="239"/>
-      <c r="E21" s="239"/>
-      <c r="F21" s="239"/>
-      <c r="G21" s="239"/>
-      <c r="H21" s="239"/>
-      <c r="I21" s="239"/>
-      <c r="J21" s="239"/>
-      <c r="K21" s="239"/>
-      <c r="L21" s="239"/>
+      <c r="D21" s="230"/>
+      <c r="E21" s="230"/>
+      <c r="F21" s="230"/>
+      <c r="G21" s="230"/>
+      <c r="H21" s="230"/>
+      <c r="I21" s="230"/>
+      <c r="J21" s="230"/>
+      <c r="K21" s="230"/>
+      <c r="L21" s="230"/>
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -20824,18 +20853,18 @@
       <c r="N25" s="90"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="239" t="s">
+      <c r="C26" s="230" t="s">
         <v>195</v>
       </c>
-      <c r="D26" s="239"/>
-      <c r="E26" s="239"/>
-      <c r="F26" s="239"/>
-      <c r="G26" s="239"/>
-      <c r="H26" s="239"/>
-      <c r="I26" s="239"/>
-      <c r="J26" s="239"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
+      <c r="D26" s="230"/>
+      <c r="E26" s="230"/>
+      <c r="F26" s="230"/>
+      <c r="G26" s="230"/>
+      <c r="H26" s="230"/>
+      <c r="I26" s="230"/>
+      <c r="J26" s="230"/>
+      <c r="K26" s="230"/>
+      <c r="L26" s="230"/>
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21069,7 +21098,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C34" s="149">
         <f>C32/C8</f>
@@ -21105,10 +21134,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="231" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="233"/>
+      <c r="C37" s="231"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21126,7 +21155,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13732876261062876</v>
+        <v>0.13638349219874299</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21148,173 +21177,218 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>184086.82347798249</v>
+        <v>184856.47404271946</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C43" s="87">
+        <f>Statement!AC107</f>
+        <v>41270</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C44" s="87">
+        <f>Statement!AC108</f>
+        <v>45031</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C45" s="24">
+        <f ca="1">C42+C43-C44</f>
+        <v>181095.47404271946</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="87">
+      <c r="C46" s="87">
         <f>Statement!AC78</f>
         <v>5026</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="141" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="141" t="s">
         <v>204</v>
       </c>
-      <c r="C44" s="142">
-        <f ca="1">C42/C43</f>
-        <v>36.626904790684932</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="233" t="s">
+      <c r="C47" s="142">
+        <f ca="1">C45/C46</f>
+        <v>36.031729813513621</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="231" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="233"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="1" t="s">
+      <c r="C49" s="231"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C47" s="63">
+      <c r="C50" s="63">
         <f>L6</f>
         <v>77266.037951804014</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C48" s="134">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C51" s="134">
         <f>Overview!C29</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="39" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="C49" s="104">
+      <c r="C52" s="104">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="1" t="s">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="24">
+      <c r="C53" s="24">
         <f>L18</f>
         <v>5563.9177776000006</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C51" s="24">
-        <f>(C47*C49)/C50</f>
+      <c r="C54" s="24">
+        <f>(C50*C52)/C53</f>
         <v>69.434920716183527</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="141" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="141" t="s">
         <v>204</v>
       </c>
-      <c r="C52" s="142">
-        <f>C51/(1+C48)^5</f>
+      <c r="C55" s="142">
+        <f>C54/(1+C51)^5</f>
         <v>39.399238739054248</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="233" t="s">
-        <v>324</v>
-      </c>
-      <c r="C54" s="233"/>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="231" t="s">
+        <v>323</v>
+      </c>
+      <c r="C57" s="231"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C55" s="63">
+      <c r="C58" s="63">
         <f>L8</f>
         <v>-2679.8717079009807</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C56" s="134">
-        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13732876261062876</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="C57" s="104">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C58" s="24">
-        <f>L18</f>
-        <v>5563.9177776000006</v>
-      </c>
-    </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C59" s="24">
-        <f>(C55*C57)-G30+G31</f>
-        <v>-107851.86831603921</v>
+        <v>160</v>
+      </c>
+      <c r="C59" s="134">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.13638349219874299</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C60" s="24">
-        <f ca="1">C59/(1+C56)^5-G30+G31</f>
-        <v>-57332.787155528902</v>
+      <c r="B60" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="C60" s="104">
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="63">
+        <f>(C58*C60)-G30+G31</f>
+        <v>-107851.86831603921</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C62" s="63">
+        <f ca="1">C61/(1+C59)^5-G30+G31</f>
+        <v>-57568.900876518135</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C63" s="87">
+        <f>Statement!AC107</f>
+        <v>41270</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C64" s="87">
+        <f>Statement!AC108</f>
+        <v>45031</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C65" s="24">
+        <f ca="1">C62+C63-C64</f>
+        <v>-61329.900876518135</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C61" s="87">
+      <c r="C66" s="87">
         <f>Statement!AC78</f>
         <v>5026</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="141" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="141" t="s">
         <v>204</v>
       </c>
-      <c r="C62" s="142">
-        <f ca="1">C60/C61</f>
-        <v>-11.407239784227796</v>
+      <c r="C67" s="142">
+        <f ca="1">C65/C66</f>
+        <v>-12.202527034723067</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -21348,7 +21422,7 @@
     <row r="1" spans="1:14" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="81" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -21358,73 +21432,73 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" s="233"/>
+      <c r="B4" s="231" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="231"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-7.1219352400478764</v>
+        <v>-7.1598029745542915</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C6" s="132">
-        <f ca="1">Multiples!C44</f>
-        <v>36.626904790684932</v>
+        <f ca="1">Multiples!C47</f>
+        <v>36.031729813513621</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C7" s="132">
-        <f>Multiples!C52</f>
+        <f>Multiples!C55</f>
         <v>39.399238739054248</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C8" s="132">
-        <f ca="1">Multiples!C62</f>
-        <v>-11.407239784227796</v>
+        <f ca="1">Multiples!C67</f>
+        <v>-12.202527034723067</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="141" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>14.374242126365875</v>
+        <v>14.017159635822628</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>120.35</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.88056300684365707</v>
+        <v>-0.87366237371948963</v>
       </c>
     </row>
   </sheetData>
@@ -21480,7 +21554,7 @@
     <row r="1" spans="1:28" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="81" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="82" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -21489,20 +21563,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
       <c r="P3" s="244"/>
       <c r="Q3" s="244"/>
       <c r="R3" s="244"/>
@@ -21520,18 +21594,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="239" t="s">
+      <c r="C5" s="230" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
+      <c r="D5" s="230"/>
+      <c r="E5" s="230"/>
+      <c r="F5" s="230"/>
+      <c r="G5" s="230"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="230"/>
+      <c r="L5" s="230"/>
       <c r="P5" s="244"/>
       <c r="Q5" s="244"/>
       <c r="R5" s="244"/>
@@ -21605,7 +21679,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C7" s="111">
         <f>'FCF &amp; Other'!C28</f>
@@ -21677,7 +21751,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-965176.99828647287</v>
+        <v>-973016.19645346852</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -21722,7 +21796,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C10" s="137"/>
       <c r="D10" s="137"/>
@@ -21731,23 +21805,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13170.112442666974</v>
+        <v>-13181.067650744815</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19106.775670141153</v>
+        <v>-19138.575817964527</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27719.495797650969</v>
+        <v>-27788.726531517277</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40214.55323185429</v>
+        <v>-40348.525908527117</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58341.980800916637</v>
+        <v>-58585.035954945371</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -21766,43 +21840,43 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-507197.20461403806</v>
+        <v>-513446.84323443676</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="245" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C14" s="246"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>120.35</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B16" s="155" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-133.20953492981855</v>
+        <v>-134.5502934934612</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="157" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C17" s="158">
         <v>0.65</v>
       </c>
       <c r="E17" s="247" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F17" s="247"/>
       <c r="G17" s="247"/>
@@ -21830,7 +21904,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13732876261062876</v>
+        <v>0.13638349219874299</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21844,11 +21918,11 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="159" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>604879.1</v>
+        <v>557634.70000000007</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21871,11 +21945,11 @@
     </row>
     <row r="26" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="157" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>608640.1</v>
+        <v>561395.70000000007</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21891,7 +21965,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158552.91794323002</v>
+        <v>-159041.93186369911</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21900,7 +21974,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>-507197.20461403806</v>
+        <v>-513446.84323443676</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21909,7 +21983,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>-665750.12255726801</v>
+        <v>-672488.77509813593</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -21936,7 +22010,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>-669511.12255726801</v>
+        <v>-676249.77509813593</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -21954,22 +22028,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>-133.20953492981855</v>
+        <v>-134.5502934934612</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="239" t="s">
-        <v>225</v>
-      </c>
-      <c r="D39" s="239"/>
-      <c r="E39" s="239"/>
-      <c r="F39" s="239"/>
-      <c r="G39" s="239"/>
-      <c r="H39" s="239"/>
-      <c r="I39" s="239"/>
-      <c r="J39" s="239"/>
-      <c r="K39" s="239"/>
-      <c r="L39" s="239"/>
+      <c r="C39" s="230" t="s">
+        <v>224</v>
+      </c>
+      <c r="D39" s="230"/>
+      <c r="E39" s="230"/>
+      <c r="F39" s="230"/>
+      <c r="G39" s="230"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="230"/>
+      <c r="J39" s="230"/>
+      <c r="K39" s="230"/>
+      <c r="L39" s="230"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -22015,7 +22089,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C41" s="111">
         <f>C7</f>
@@ -22105,7 +22179,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B43" s="121" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C43" s="94">
         <f>C41/C42</f>
@@ -22190,7 +22264,7 @@
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="121" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C45" s="94">
         <f>C41/C44</f>
@@ -22230,7 +22304,7 @@
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="121" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C46" s="137"/>
       <c r="D46" s="94">
@@ -22272,7 +22346,7 @@
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B47" s="121" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C47" s="137"/>
       <c r="D47" s="94">
@@ -22314,7 +22388,7 @@
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" s="121" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C48" s="137"/>
       <c r="D48" s="94">
@@ -22356,7 +22430,7 @@
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C49" s="94">
         <f>C42/C44</f>
@@ -22458,45 +22532,45 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="M2" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="U2" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="V2" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="W2" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="X2" s="10" t="s">
-        <v>349</v>
-      </c>
       <c r="Y2" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -22525,16 +22599,16 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="X3" s="10" t="s">
         <v>85</v>
@@ -22855,7 +22929,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -23374,7 +23448,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -24416,7 +24490,7 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B34" s="20" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -25123,7 +25197,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -25236,7 +25310,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -25294,7 +25368,7 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
@@ -26103,7 +26177,7 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C64" s="61"/>
       <c r="D64" s="61"/>
@@ -26156,7 +26230,7 @@
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C65" s="61"/>
       <c r="D65" s="61"/>
@@ -26747,7 +26821,7 @@
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
@@ -26805,7 +26879,7 @@
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
@@ -26876,7 +26950,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B78" s="20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
@@ -26947,7 +27021,7 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B79" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
@@ -26989,7 +27063,7 @@
     </row>
     <row r="80" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B80" s="20" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
@@ -27669,7 +27743,7 @@
     </row>
     <row r="93" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B93" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C93" s="49"/>
       <c r="D93" s="50"/>
@@ -28688,7 +28762,7 @@
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B110" s="20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C110" s="25"/>
       <c r="D110" s="25"/>
@@ -28759,7 +28833,7 @@
     </row>
     <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B111" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C111" s="25"/>
       <c r="D111" s="25"/>
@@ -28830,7 +28904,7 @@
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B112" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C112" s="25"/>
       <c r="D112" s="25"/>
@@ -28963,12 +29037,12 @@
       <c r="AA116" s="67"/>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>120.35</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B117" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C117" s="26"/>
       <c r="D117" s="26"/>
@@ -29010,7 +29084,7 @@
       <c r="AA117" s="67"/>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>120.35</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -29235,7 +29309,7 @@
     </row>
     <row r="128" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B128" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C128" s="171"/>
       <c r="D128" s="171"/>
@@ -29264,7 +29338,7 @@
     </row>
     <row r="129" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B129" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C129" s="49"/>
       <c r="D129" s="49"/>
@@ -29309,7 +29383,7 @@
     </row>
     <row r="130" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B130" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C130" s="49"/>
       <c r="D130" s="49"/>
@@ -29354,7 +29428,7 @@
     </row>
     <row r="131" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B131" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C131" s="49"/>
       <c r="D131" s="49"/>
@@ -29460,7 +29534,7 @@
     </row>
     <row r="133" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B133" s="20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C133" s="49"/>
       <c r="D133" s="49"/>
@@ -29505,7 +29579,7 @@
     </row>
     <row r="134" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B134" s="20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C134" s="49"/>
       <c r="D134" s="49"/>
@@ -29550,7 +29624,7 @@
     </row>
     <row r="135" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B135" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C135" s="49"/>
       <c r="D135" s="49"/>
@@ -29659,7 +29733,7 @@
     </row>
     <row r="139" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B139" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C139" s="171"/>
       <c r="D139" s="171"/>
@@ -29979,7 +30053,7 @@
     </row>
     <row r="145" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B145" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M145" s="117">
         <f>M108/M49</f>
@@ -30040,7 +30114,7 @@
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B146" s="20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M146" s="179">
         <f>(M108-M107)/M49</f>
@@ -30101,7 +30175,7 @@
     </row>
     <row r="147" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B147" s="20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M147" s="117">
         <f>(M107+M30)/M40</f>
@@ -30162,7 +30236,7 @@
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B148" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M148" s="117">
         <f>M32/M40</f>
@@ -30223,7 +30297,7 @@
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B149" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M149" s="181" t="str">
         <f>IF(M13&gt;=0,"N/A",IF(M12&lt;=0,"N/A",M12/-M13))</f>
@@ -30284,7 +30358,7 @@
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B150" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M150" s="71">
         <f>M117/Statement!M26</f>
@@ -30316,7 +30390,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-194.11290322580643</v>
+        <v>-178.95161290322582</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30353,12 +30427,12 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>10.533395178840466</v>
+        <v>9.7106788125662629</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B152" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M152" s="71">
         <f>M117/(Statement!M49/Statement!M75)</f>
@@ -30390,12 +30464,12 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>5.4300868987557669</v>
+        <v>5.0059671077436843</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B153" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M153" s="143">
         <f>Statement!M117*Statement!M78</f>
@@ -30427,7 +30501,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>604879.1</v>
+        <v>557634.70000000007</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30464,12 +30538,12 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>622235.1</v>
+        <v>574990.70000000007</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B155" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M155" s="183">
         <f>M154/M5</f>
@@ -30501,7 +30575,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>11.573667764075665</v>
+        <v>10.694914718300691</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30538,12 +30612,12 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>-123.23927510398099</v>
+        <v>-113.88209546444843</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B157" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M157" s="63">
         <f>M59-M54+M110+M65</f>
@@ -30604,7 +30678,7 @@
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B158" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M158" s="63">
         <f>M109+M53+M110+M55+M57+M58+M56</f>
@@ -30641,7 +30715,7 @@
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B159" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M159" s="71">
         <f>M153/M157</f>
@@ -30673,12 +30747,12 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="100">AC153/AC157</f>
-        <v>-110.17834244080146</v>
+        <v>-101.57280510018217</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B160" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M160" s="71">
         <f>M154/M158</f>
@@ -30710,12 +30784,12 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="100"/>
-        <v>-72.580788522104285</v>
+        <v>-67.069952175434508</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B161" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M161" s="73">
         <f>M157/M153</f>
@@ -30747,12 +30821,12 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="103">AC157/AC153</f>
-        <v>-9.0761939038726917E-3</v>
+        <v>-9.8451549015870048E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B162" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M162" s="73">
         <f>M26/M117</f>
@@ -30784,12 +30858,12 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-5.1516410469464062E-3</v>
+        <v>-5.5881027489860296E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B163" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M163" s="154">
         <f>M82/M117</f>
@@ -30826,7 +30900,7 @@
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B164" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M164" s="154">
         <f>-M63/M153</f>
@@ -30863,7 +30937,7 @@
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B165" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M165" s="154">
         <f>-(M63+M64)/M153</f>
@@ -30900,7 +30974,7 @@
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B166" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M166" s="154">
         <f>M158/M5</f>
@@ -30937,7 +31011,7 @@
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B167" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M167" s="154">
         <f>M157/M5</f>
@@ -30974,7 +31048,7 @@
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B168" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M168" s="154">
         <f>-M64/M157</f>
@@ -31011,7 +31085,7 @@
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B169" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M169" s="154">
         <f>-M63/M157</f>
@@ -31048,7 +31122,7 @@
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B170" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M170" s="154">
         <f>(-M64-M63)/M157</f>
@@ -31085,7 +31159,7 @@
     </row>
     <row r="171" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B171" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M171" s="154">
         <f>M80/M78</f>
@@ -31122,7 +31196,7 @@
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B172" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M172" s="71">
         <f>M107/M75</f>
@@ -31183,7 +31257,7 @@
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B173" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M173" s="154">
         <f>M54/M59</f>
@@ -31244,7 +31318,7 @@
     </row>
     <row r="174" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B174" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M174" s="154">
         <f>M54/M5</f>
@@ -31305,7 +31379,7 @@
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B175" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M175" s="71">
         <f>(M107-M108)/M75</f>
@@ -31366,7 +31440,7 @@
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B176" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M176" s="154">
         <f>(M107-M108)/M153</f>
@@ -31398,12 +31472,12 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-6.2177714521794523E-3</v>
+        <v>-6.7445587586281832E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B177" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M177" s="154">
         <f>-M110/M5</f>
@@ -31464,7 +31538,7 @@
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B178" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M178" s="154">
         <f>-(M110/M59)</f>
@@ -31525,7 +31599,7 @@
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B179" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M179" s="154">
         <f>-M110/M53</f>
@@ -31586,7 +31660,7 @@
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B180" s="20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M180" s="71">
         <f>M5/M37</f>
@@ -31623,7 +31697,7 @@
     </row>
     <row r="181" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B181" s="20" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M181" s="71">
         <f>IF(AND(M12&gt;0,M108&gt;0),M108/M12,"N/A")</f>
@@ -31660,7 +31734,7 @@
     </row>
     <row r="182" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B182" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M182" s="71">
         <f>IF(AND(M12&gt;0,M108&gt;0),(M108-M107)/M12,"N/A")</f>
@@ -31697,7 +31771,7 @@
     </row>
     <row r="183" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B183" s="20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M183" s="71">
         <f>M5/(M108+M112-M107)</f>
@@ -31748,7 +31822,7 @@
     </row>
     <row r="187" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B187" s="216" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C187" s="61"/>
       <c r="D187" s="61"/>
@@ -31806,7 +31880,7 @@
     </row>
     <row r="188" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B188" s="216" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C188" s="61"/>
       <c r="D188" s="61"/>
@@ -31867,7 +31941,7 @@
     </row>
     <row r="189" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B189" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C189" s="61"/>
       <c r="D189" s="61"/>
@@ -31928,7 +32002,7 @@
     </row>
     <row r="190" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B190" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C190" s="21"/>
       <c r="D190" s="21"/>
@@ -31986,7 +32060,7 @@
     </row>
     <row r="191" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B191" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C191" s="61"/>
       <c r="D191" s="61"/>
@@ -32073,7 +32147,7 @@
     </row>
     <row r="193" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B193" s="216" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C193" s="61"/>
       <c r="D193" s="61"/>
@@ -32134,7 +32208,7 @@
     </row>
     <row r="194" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B194" s="216" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C194" s="61"/>
       <c r="D194" s="61"/>
@@ -32195,7 +32269,7 @@
     </row>
     <row r="195" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B195" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C195" s="61"/>
       <c r="D195" s="61"/>
@@ -32256,7 +32330,7 @@
     </row>
     <row r="196" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B196" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C196" s="61"/>
       <c r="D196" s="61"/>
@@ -32317,7 +32391,7 @@
     </row>
     <row r="197" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B197" s="20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C197" s="61"/>
       <c r="D197" s="61"/>
@@ -32394,7 +32468,7 @@
     </row>
     <row r="200" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B200" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C200" s="171"/>
       <c r="D200" s="171"/>
@@ -32423,7 +32497,7 @@
     </row>
     <row r="201" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B201" s="216" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C201" s="80"/>
       <c r="D201" s="80"/>
@@ -32497,7 +32571,7 @@
     </row>
     <row r="202" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B202" s="216" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M202" s="80">
         <f t="shared" si="120"/>
@@ -32555,7 +32629,7 @@
     </row>
     <row r="203" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B203" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M203" s="80">
         <f t="shared" si="120"/>
@@ -32613,7 +32687,7 @@
     </row>
     <row r="204" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B204" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M204" s="80">
         <f t="shared" si="120"/>
@@ -32671,7 +32745,7 @@
     </row>
     <row r="205" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B205" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M205" s="80">
         <f t="shared" si="120"/>
@@ -32732,7 +32806,7 @@
     </row>
     <row r="208" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B208" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C208" s="171"/>
       <c r="D208" s="171"/>
@@ -32761,7 +32835,7 @@
     </row>
     <row r="209" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B209" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C209" s="80"/>
       <c r="D209" s="80"/>
@@ -32823,7 +32897,7 @@
     </row>
     <row r="212" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B212" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C212" s="171"/>
       <c r="D212" s="171"/>
@@ -32852,7 +32926,7 @@
     </row>
     <row r="213" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B213" s="20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M213" s="143">
         <v>100</v>
@@ -32885,7 +32959,7 @@
     </row>
     <row r="214" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B214" s="20" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M214" s="143">
         <v>100</v>
@@ -32918,7 +32992,7 @@
     </row>
     <row r="215" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B215" s="20" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M215" s="143">
         <v>100</v>
@@ -32965,7 +33039,7 @@
     </row>
     <row r="219" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B219" s="20" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M219" s="61">
         <v>0</v>
@@ -33013,7 +33087,7 @@
     </row>
     <row r="220" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B220" s="20" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M220" s="61">
         <v>0</v>
@@ -33096,7 +33170,7 @@
   <sheetData>
     <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -33119,19 +33193,19 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" s="81" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
-        <v>235</v>
-      </c>
-      <c r="C4" s="233"/>
-      <c r="E4" s="233" t="s">
-        <v>242</v>
-      </c>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
+      <c r="B4" s="231" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="231"/>
+      <c r="E4" s="231" t="s">
+        <v>241</v>
+      </c>
+      <c r="F4" s="231"/>
+      <c r="G4" s="231"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33139,23 +33213,23 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>120.35</v>
+        <v>110.95</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
+        <v>242</v>
+      </c>
+      <c r="G5" s="131" t="s">
         <v>243</v>
-      </c>
-      <c r="G5" s="131" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>604879.1</v>
+        <v>557634.70000000007</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33175,7 +33249,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>622235.1</v>
+        <v>574990.70000000007</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33191,14 +33265,14 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-194.11290322580643</v>
+        <v>-178.95161290322582</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F8" s="178" t="str">
         <f>IF(OR(Statement!M26&lt;=0, Statement!Q26&lt;=0), "N/A", _xlfn.RRI(4, Statement!M26, Statement!Q26))</f>
@@ -33215,10 +33289,10 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>10.533395178840466</v>
+        <v>9.7106788125662629</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F9" s="178">
         <f>IF(Statement!M82&lt;=0,"N/A",_xlfn.RRI(4,Statement!M82,Statement!Q82))</f>
@@ -33231,11 +33305,11 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>5.4300868987557669</v>
+        <v>5.0059671077436843</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33251,11 +33325,11 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>11.573667764075665</v>
+        <v>10.694914718300691</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33264,18 +33338,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>-123.23927510398099</v>
+        <v>-113.88209546444843</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="231" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="233"/>
-      <c r="E15" s="233" t="s">
-        <v>248</v>
-      </c>
-      <c r="F15" s="233"/>
+      <c r="C15" s="231"/>
+      <c r="E15" s="231" t="s">
+        <v>247</v>
+      </c>
+      <c r="F15" s="231"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33302,7 +33376,7 @@
         <v>-9.391217007979466E-2</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F17" s="173">
         <f>Statement!AC59</f>
@@ -33318,7 +33392,7 @@
         <v>-6.2645313691572266E-2</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F18" s="177" t="str">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
@@ -33326,14 +33400,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="233" t="s">
-        <v>247</v>
-      </c>
-      <c r="C21" s="233"/>
-      <c r="E21" s="233" t="s">
-        <v>251</v>
-      </c>
-      <c r="F21" s="233"/>
+      <c r="B21" s="231" t="s">
+        <v>246</v>
+      </c>
+      <c r="C21" s="231"/>
+      <c r="E21" s="231" t="s">
+        <v>250</v>
+      </c>
+      <c r="F21" s="231"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33402,14 +33476,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="233" t="s">
-        <v>252</v>
-      </c>
-      <c r="C29" s="233"/>
-      <c r="E29" s="233" t="s">
-        <v>258</v>
-      </c>
-      <c r="F29" s="233"/>
+      <c r="B29" s="231" t="s">
+        <v>251</v>
+      </c>
+      <c r="C29" s="231"/>
+      <c r="E29" s="231" t="s">
+        <v>257</v>
+      </c>
+      <c r="F29" s="231"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33420,7 +33494,7 @@
         <v>27.604300355262914</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F30" s="180">
         <f>Statement!AC145</f>
@@ -33436,7 +33510,7 @@
         <v>130.6568144499179</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F31" s="180">
         <f>Statement!AC146</f>
@@ -33452,7 +33526,7 @@
         <v>75.275401146544525</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F32" s="180">
         <f>Statement!AC148</f>
@@ -33468,7 +33542,7 @@
         <v>82.9857136586363</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F33" s="180">
         <f>Statement!AC147</f>
@@ -33477,7 +33551,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E34" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F34" s="182" t="str">
         <f>Statement!AC149</f>
@@ -33485,25 +33559,25 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
-        <v>270</v>
-      </c>
-      <c r="C37" s="233"/>
-      <c r="E37" s="233" t="s">
-        <v>273</v>
-      </c>
-      <c r="F37" s="233"/>
+      <c r="B37" s="231" t="s">
+        <v>269</v>
+      </c>
+      <c r="C37" s="231"/>
+      <c r="E37" s="231" t="s">
+        <v>272</v>
+      </c>
+      <c r="F37" s="231"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-5.1516410469464062E-3</v>
+        <v>-5.5881027489860296E-3</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F38" s="175">
         <f>Statement!AC168</f>
@@ -33512,14 +33586,14 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" s="54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>-9.0761939038726917E-3</v>
+        <v>-9.8451549015870048E-3</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F39" s="175">
         <f>Statement!AC169</f>
@@ -33528,14 +33602,14 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F40" s="175">
         <f>Statement!AC170</f>
@@ -33544,7 +33618,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC164</f>
@@ -33553,7 +33627,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC165</f>
@@ -33561,25 +33635,25 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="233" t="s">
-        <v>281</v>
-      </c>
-      <c r="C45" s="233"/>
-      <c r="E45" s="233" t="s">
-        <v>287</v>
-      </c>
-      <c r="F45" s="233"/>
+      <c r="B45" s="231" t="s">
+        <v>280</v>
+      </c>
+      <c r="C45" s="231"/>
+      <c r="E45" s="231" t="s">
+        <v>286</v>
+      </c>
+      <c r="F45" s="231"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C46" s="175">
         <f>Statement!AC171</f>
         <v>5.9689614007162755E-4</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F46" s="174">
         <f>Statement!AC172</f>
@@ -33588,7 +33662,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E47" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F47" s="174">
         <f>Statement!AC175</f>
@@ -33597,33 +33671,33 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E48" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>-6.2177714521794523E-3</v>
+        <v>-6.7445587586281832E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="233" t="s">
-        <v>284</v>
-      </c>
-      <c r="C51" s="233"/>
-      <c r="E51" s="233" t="s">
-        <v>305</v>
-      </c>
-      <c r="F51" s="233"/>
+      <c r="B51" s="231" t="s">
+        <v>283</v>
+      </c>
+      <c r="C51" s="231"/>
+      <c r="E51" s="231" t="s">
+        <v>304</v>
+      </c>
+      <c r="F51" s="231"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C52" s="175">
         <f>Statement!AC173</f>
         <v>0.2375751503006012</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F52" s="175">
         <f>Statement!AC177</f>
@@ -33632,14 +33706,14 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C53" s="175">
         <f>Statement!AC174</f>
         <v>4.4100961627885349E-2</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F53" s="175">
         <f>Statement!AC178</f>
@@ -33648,7 +33722,7 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E54" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F54" s="175">
         <f>Statement!AC179</f>
@@ -33745,7 +33819,7 @@
     </row>
     <row r="5" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -33780,12 +33854,12 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>120.35</v>
+        <v>110.95</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C7" s="173">
         <f>Statement!M153</f>
@@ -33809,7 +33883,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>604879.1</v>
+        <v>557634.70000000007</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33838,12 +33912,12 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>622235.1</v>
+        <v>574990.70000000007</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C9" s="174">
         <f>Statement!M150</f>
@@ -33867,7 +33941,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-194.11290322580643</v>
+        <v>-178.95161290322582</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33896,12 +33970,12 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>10.533395178840466</v>
+        <v>9.7106788125662629</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C11" s="174">
         <f>Statement!M152</f>
@@ -33925,12 +33999,12 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>5.4300868987557669</v>
+        <v>5.0059671077436843</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C12" s="174">
         <f>Statement!M155</f>
@@ -33954,7 +34028,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>11.573667764075665</v>
+        <v>10.694914718300691</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -33983,7 +34057,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>-123.23927510398099</v>
+        <v>-113.88209546444843</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34086,7 +34160,7 @@
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -34126,7 +34200,7 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C22" s="177">
         <f>Statement!M59</f>
@@ -34155,7 +34229,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B23" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C23" s="195">
         <f>IF(OR(C21&lt;=0, C22&lt;=0),"N/A",C21-C22)</f>
@@ -34184,7 +34258,7 @@
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -34340,7 +34414,7 @@
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -34438,7 +34512,7 @@
     </row>
     <row r="37" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -34565,7 +34639,7 @@
     </row>
     <row r="43" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -34576,7 +34650,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C44" s="180">
         <f>Statement!M145</f>
@@ -34605,7 +34679,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C45" s="180">
         <f>Statement!M146</f>
@@ -34634,7 +34708,7 @@
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C46" s="180">
         <f>Statement!M147</f>
@@ -34663,7 +34737,7 @@
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C47" s="180">
         <f>Statement!M148</f>
@@ -34692,7 +34766,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C48" s="182" t="str">
         <f>Statement!M149</f>
@@ -34721,7 +34795,7 @@
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -34732,7 +34806,7 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C51" s="175">
         <f>Statement!M162</f>
@@ -34756,12 +34830,12 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-5.1516410469464062E-3</v>
+        <v>-5.5881027489860296E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C52" s="175">
         <f>Statement!M161</f>
@@ -34785,12 +34859,12 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>-9.0761939038726917E-3</v>
+        <v>-9.8451549015870048E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C53" s="175">
         <f>Statement!M163</f>
@@ -34819,7 +34893,7 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C54" s="175">
         <f>Statement!M164</f>
@@ -34848,7 +34922,7 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C55" s="175">
         <f>Statement!M165</f>
@@ -34877,7 +34951,7 @@
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -34888,7 +34962,7 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C58" s="175">
         <f>Statement!M168</f>
@@ -34917,7 +34991,7 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C59" s="175">
         <f>Statement!M169</f>
@@ -34946,7 +35020,7 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C60" s="175">
         <f>Statement!M170</f>
@@ -34975,7 +35049,7 @@
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -34986,7 +35060,7 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C63" s="175">
         <f>Statement!M171</f>
@@ -35015,7 +35089,7 @@
     </row>
     <row r="65" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -35026,7 +35100,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C66" s="174">
         <f>Statement!M172</f>
@@ -35055,7 +35129,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C67" s="174">
         <f>Statement!M175</f>
@@ -35084,7 +35158,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="196">
         <f>Statement!M176</f>
@@ -35108,12 +35182,12 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>-6.2177714521794523E-3</v>
+        <v>-6.7445587586281832E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -35124,7 +35198,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C71" s="175">
         <f>Statement!M173</f>
@@ -35153,7 +35227,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C72" s="175">
         <f>Statement!M174</f>
@@ -35182,7 +35256,7 @@
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -35193,7 +35267,7 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C75" s="175">
         <f>Statement!M177</f>
@@ -35222,7 +35296,7 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C76" s="175">
         <f>Statement!M178</f>
@@ -35251,7 +35325,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C77" s="175">
         <f>Statement!M179</f>
@@ -35395,7 +35469,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B84" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C84" s="175">
         <f>Statement!M96</f>
@@ -35421,7 +35495,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B85" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C85" s="175">
         <f>Statement!M98</f>
@@ -35447,7 +35521,7 @@
     </row>
     <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -35458,7 +35532,7 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B89" s="216" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C89" s="175">
         <f>Statement!M201</f>
@@ -35484,7 +35558,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="216" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C90" s="175">
         <f>Statement!M202</f>
@@ -35510,7 +35584,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C91" s="175">
         <f>Statement!M203</f>
@@ -35536,7 +35610,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B92" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C92" s="175">
         <f>Statement!M204</f>
@@ -35562,7 +35636,7 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B93" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C93" s="175">
         <f>Statement!M205</f>
@@ -35588,7 +35662,7 @@
     </row>
     <row r="95" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B95" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -35599,7 +35673,7 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B96" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C96" s="175">
         <f>Statement!M209</f>
@@ -35646,14 +35720,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="239" t="s">
+        <v>314</v>
+      </c>
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>315</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
-        <v>316</v>
-      </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35676,7 +35750,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C5" s="10" t="str">
         <f>Statement!Z3</f>
@@ -35718,21 +35792,21 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C7" s="234">
+        <v>316</v>
+      </c>
+      <c r="C7" s="237">
         <f>Statement!AA89</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="235"/>
-      <c r="F7" s="234">
+      <c r="D7" s="238"/>
+      <c r="F7" s="237">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="235"/>
+      <c r="G7" s="238"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35757,21 +35831,21 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C9" s="234">
+        <v>316</v>
+      </c>
+      <c r="C9" s="237">
         <f>Statement!AA90</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="235"/>
-      <c r="F9" s="234">
+      <c r="D9" s="238"/>
+      <c r="F9" s="237">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="235"/>
+      <c r="G9" s="238"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35796,21 +35870,21 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C11" s="234">
+        <v>316</v>
+      </c>
+      <c r="C11" s="237">
         <f>Statement!AA91</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="235"/>
-      <c r="F11" s="234">
+      <c r="D11" s="238"/>
+      <c r="F11" s="237">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="235"/>
+      <c r="G11" s="238"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35835,25 +35909,25 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C13" s="234">
+        <v>316</v>
+      </c>
+      <c r="C13" s="237">
         <f>Statement!AA95</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="F13" s="234">
+      <c r="D13" s="238"/>
+      <c r="F13" s="237">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="235"/>
+      <c r="G13" s="238"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C14" s="200">
         <f>Statement!Z12</f>
@@ -35874,21 +35948,21 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C15" s="234">
+        <v>316</v>
+      </c>
+      <c r="C15" s="237">
         <f>Statement!AA96</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="235"/>
-      <c r="F15" s="234">
+      <c r="D15" s="238"/>
+      <c r="F15" s="237">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="235"/>
+      <c r="G15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35913,25 +35987,25 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C17" s="234">
+        <v>316</v>
+      </c>
+      <c r="C17" s="237">
         <f>Statement!AA98</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="235"/>
-      <c r="F17" s="234">
+      <c r="D17" s="238"/>
+      <c r="F17" s="237">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="235"/>
+      <c r="G17" s="238"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C18" s="200">
         <f>Statement!Z22</f>
@@ -35952,24 +36026,24 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C19" s="234">
+        <v>316</v>
+      </c>
+      <c r="C19" s="237">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="235"/>
-      <c r="F19" s="234">
+      <c r="D19" s="238"/>
+      <c r="F19" s="237">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="235"/>
+      <c r="G19" s="238"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -35994,28 +36068,28 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C21" s="234">
+        <v>316</v>
+      </c>
+      <c r="C21" s="237">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="235"/>
-      <c r="F21" s="234">
+      <c r="D21" s="238"/>
+      <c r="F21" s="237">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="235"/>
+      <c r="G21" s="238"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C23" s="10" t="str">
         <f>C5</f>
@@ -36036,7 +36110,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="20" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C24" s="200">
         <f>Statement!Z187</f>
@@ -36057,28 +36131,28 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C25" s="234">
+        <v>316</v>
+      </c>
+      <c r="C25" s="237">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="235"/>
-      <c r="F25" s="234">
+      <c r="D25" s="238"/>
+      <c r="F25" s="237">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="235"/>
+      <c r="G25" s="238"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C26" s="200">
         <f>Statement!Z188</f>
@@ -36099,28 +36173,28 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C27" s="234">
+        <v>316</v>
+      </c>
+      <c r="C27" s="237">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="235"/>
-      <c r="F27" s="234">
+      <c r="D27" s="238"/>
+      <c r="F27" s="237">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="235"/>
+      <c r="G27" s="238"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C28" s="200">
         <f>Statement!Z189</f>
@@ -36141,28 +36215,28 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C29" s="234">
+        <v>316</v>
+      </c>
+      <c r="C29" s="237">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="235"/>
-      <c r="F29" s="234">
+      <c r="D29" s="238"/>
+      <c r="F29" s="237">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="235"/>
+      <c r="G29" s="238"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C30" s="200">
         <f>Statement!Z190</f>
@@ -36183,28 +36257,28 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C31" s="234">
+        <v>316</v>
+      </c>
+      <c r="C31" s="237">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="235"/>
-      <c r="F31" s="234">
+      <c r="D31" s="238"/>
+      <c r="F31" s="237">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="235"/>
+      <c r="G31" s="238"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C32" s="200">
         <f>Statement!Z191</f>
@@ -36225,24 +36299,24 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="206" t="s">
-        <v>317</v>
-      </c>
-      <c r="C33" s="234">
+        <v>316</v>
+      </c>
+      <c r="C33" s="237">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="235"/>
-      <c r="F33" s="234">
+      <c r="D33" s="238"/>
+      <c r="F33" s="237">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="235"/>
+      <c r="G33" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -36515,7 +36589,7 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C60" s="63">
         <f>Statement!H157</f>
@@ -36560,7 +36634,7 @@
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C61" s="63">
         <f>Statement!H158</f>
@@ -36740,7 +36814,7 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C65" s="63">
         <f>Statement!H189</f>
@@ -36785,7 +36859,7 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C66" s="63">
         <f>Statement!H190</f>
@@ -36830,7 +36904,7 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C67" s="63">
         <f>Statement!H191</f>
@@ -37010,7 +37084,7 @@
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C71" s="229">
         <f>Statement!H213</f>
@@ -37055,7 +37129,7 @@
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C72" s="229">
         <f>Statement!H214</f>
@@ -37100,7 +37174,7 @@
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B73" s="20" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C73" s="229">
         <f>Statement!H215</f>
@@ -37453,7 +37527,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="20" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C63" s="63">
         <f>Statement!T189</f>
@@ -37490,7 +37564,7 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C64" s="63">
         <f>Statement!T190</f>
@@ -37527,7 +37601,7 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="20" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C65" s="63">
         <f>Statement!T191</f>
@@ -37564,7 +37638,7 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C66" s="63">
         <f>Statement!T157</f>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB90BB29-CB5A-8B4A-9D2A-B1E187576F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D1989F-371E-784A-A87D-DE05EDD3C830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -130,28 +130,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -161,21 +140,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2328,12 +2298,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2341,6 +2305,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12679,7 +12649,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12698,9 +12668,11 @@
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
     <v>18.965</v>
-    <v>2.2035999999999998</v>
-    <v>-11.25</v>
-    <v>-9.2062000000000005E-2</v>
+    <v>2.2189000000000001</v>
+    <v>2.2999999999999998</v>
+    <v>2.0863999999999997E-2</v>
+    <v>0.20499999999999999</v>
+    <v>1.8220000000000001E-3</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>83200</v>
@@ -12708,49 +12680,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>116.4699</v>
+    <v>116.76990000000001</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46210.767058205471</v>
+    <v>46212.91806523125</v>
     <v>0</v>
-    <v>108.36</v>
-    <v>557634700000</v>
+    <v>111.51</v>
+    <v>565626040000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>116.31</v>
+    <v>114.87</v>
     <v>0</v>
-    <v>122.2</v>
-    <v>110.95</v>
+    <v>110.24</v>
+    <v>112.54</v>
+    <v>112.745</v>
     <v>5026000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>99608122</v>
-    <v>131060866</v>
+    <v>98989684</v>
+    <v>127833564</v>
     <v>1989</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12764,28 +12722,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.06</v>
-    <v>-1.338E-3</v>
+    <v>0.4</v>
+    <v>8.8319999999999996E-3</v>
     <v>US</v>
-    <v>44.91</v>
+    <v>45.97</v>
     <v>Index</v>
-    <v>6</v>
-    <v>44.57</v>
+    <v>3</v>
+    <v>45.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.57</v>
-    <v>44.85</v>
-    <v>44.79</v>
+    <v>45.61</v>
+    <v>45.29</v>
+    <v>45.69</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12807,6 +12765,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12827,6 +12787,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12836,11 +12797,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12876,7 +12832,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12887,13 +12843,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -12987,13 +12946,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13065,6 +13030,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13072,6 +13040,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13585,7 +13556,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC153</f>
-        <v>557634.70000000007</v>
+        <v>565626.04</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13593,7 +13564,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-7.1598029745542915</v>
+        <v>-7.0971986796984128</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13609,7 +13580,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC154</f>
-        <v>574990.70000000007</v>
+        <v>582982.04</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13617,7 +13588,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.031729813513621</v>
+        <v>35.777742757998219</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13626,7 +13597,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>110.95</v>
+        <v>112.54</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>244</v>
@@ -13648,16 +13619,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>112.745</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>238</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC150</f>
-        <v>-178.95161290322582</v>
+        <v>-181.51612903225808</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13665,7 +13636,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-12.202527034723067</v>
+        <v>-12.124608779987122</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13674,14 +13645,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-11.25</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC151</f>
-        <v>9.7106788125662629</v>
+        <v>9.8498404106913675</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13689,23 +13660,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>14.017159635822628</v>
+        <v>13.988793509341734</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0.20499999999999999</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>266</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC161</f>
-        <v>-9.8451549015870048E-3</v>
+        <v>-9.706059501786728E-3</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13713,7 +13684,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.87366237371948963</v>
+        <v>-0.87569936458733133</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13722,23 +13693,23 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-9.2062000000000005E-2</v>
+        <v>2.0863999999999997E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>289</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>-5.5881027489860296E-3</v>
+        <v>-5.509152301403945E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="72" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>1.8220000000000001E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>294</v>
@@ -13786,7 +13757,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2035999999999998</v>
+        <v>2.2189000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>99</v>
@@ -13802,7 +13773,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>131060866</v>
+        <v>127833564</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>100</v>
@@ -13818,7 +13789,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC176</f>
-        <v>-6.7445587586281832E-3</v>
+        <v>-6.6492695421165541E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13923,12 +13894,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.79</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -13943,7 +13914,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14080,18 +14051,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -18418,12 +18389,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18431,6 +18396,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19490,16 +19461,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19582,7 +19553,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>110.95</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19591,7 +19562,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>557634.70000000007</v>
+        <v>565626.04</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19609,7 +19580,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19618,7 +19589,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.2035999999999998</v>
+        <v>2.2189000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19661,7 +19632,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.4719699495093203E-2</v>
+        <v>7.3741883005229908E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19670,7 +19641,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92528030050490684</v>
+        <v>0.92625811699477012</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19688,7 +19659,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14395199999999997</v>
+        <v>0.14554049999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19697,7 +19668,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13638349219874299</v>
+        <v>0.13795389820548043</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19956,7 +19927,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23486.742753784831</v>
+        <v>-23174.0466711595</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20010,23 +19981,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6499.8669316628302</v>
+        <v>-6490.8969460697635</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5066.5378975749927</v>
+        <v>-5052.5636382367029</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3574.2694559165493</v>
+        <v>-3559.492113088048</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3275.7442245807038</v>
+        <v>-3257.6991722688063</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1414.1302824251998</v>
+        <v>-1404.3994939608738</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20045,7 +20016,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12393.620957949592</v>
+        <v>-12144.469200540032</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20068,7 +20039,7 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13638349219874299</v>
+        <v>0.13795389820548043</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20083,7 +20054,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19830.548792160276</v>
+        <v>-19765.051363624196</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20092,7 +20063,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12393.620957949592</v>
+        <v>-12144.469200540032</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20101,7 +20072,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-32224.169750109868</v>
+        <v>-31909.520564164228</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20128,7 +20099,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-35985.169750109868</v>
+        <v>-35670.520564164224</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20146,7 +20117,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>-7.1598029745542915</v>
+        <v>-7.0971986796984128</v>
       </c>
     </row>
   </sheetData>
@@ -21155,7 +21126,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13638349219874299</v>
+        <v>0.13795389820548043</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21181,7 +21152,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>184856.47404271946</v>
+        <v>183579.93510169905</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21208,7 +21179,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>181095.47404271946</v>
+        <v>179818.93510169905</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21226,7 +21197,7 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>36.031729813513621</v>
+        <v>35.777742757998219</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21309,7 +21280,7 @@
       </c>
       <c r="C59" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13638349219874299</v>
+        <v>0.13795389820548043</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21335,7 +21306,7 @@
       </c>
       <c r="C62" s="63">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>-57568.900876518135</v>
+        <v>-57177.283728215276</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21362,7 +21333,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>-61329.900876518135</v>
+        <v>-60938.283728215276</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21380,7 +21351,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>-12.202527034723067</v>
+        <v>-12.124608779987122</v>
       </c>
     </row>
   </sheetData>
@@ -21444,7 +21415,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-7.1598029745542915</v>
+        <v>-7.0971986796984128</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21453,7 +21424,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C47</f>
-        <v>36.031729813513621</v>
+        <v>35.777742757998219</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21471,7 +21442,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C67</f>
-        <v>-12.202527034723067</v>
+        <v>-12.124608779987122</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21480,7 +21451,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>14.017159635822628</v>
+        <v>13.988793509341734</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21489,7 +21460,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>110.95</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21498,7 +21469,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.87366237371948963</v>
+        <v>-0.87569936458733133</v>
       </c>
     </row>
   </sheetData>
@@ -21751,7 +21722,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-973016.19645346852</v>
+        <v>-960061.7243859031</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -21805,23 +21776,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13181.067650744815</v>
+        <v>-13162.877434210925</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19138.575817964527</v>
+        <v>-19085.788801020713</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27788.726531517277</v>
+        <v>-27673.837728703613</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40348.525908527117</v>
+        <v>-40126.258475293522</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58585.035954945371</v>
+        <v>-58181.905777240077</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -21840,7 +21811,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-513446.84323443676</v>
+        <v>-503124.90554065933</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21856,7 +21827,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>110.95</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -21865,7 +21836,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>-134.5502934934612</v>
+        <v>-132.33517185776526</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -21904,7 +21875,7 @@
       </c>
       <c r="C21" s="226">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13638349219874299</v>
+        <v>0.13795389820548043</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -21922,7 +21893,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>557634.70000000007</v>
+        <v>565626.04</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -21949,7 +21920,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>561395.70000000007</v>
+        <v>569387.04</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -21965,7 +21936,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-159041.93186369911</v>
+        <v>-158230.66821646885</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -21974,7 +21945,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>-513446.84323443676</v>
+        <v>-503124.90554065933</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -21983,7 +21954,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>-672488.77509813593</v>
+        <v>-661355.57375712821</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22010,7 +21981,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>-676249.77509813593</v>
+        <v>-665116.57375712821</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22028,7 +21999,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>-134.5502934934612</v>
+        <v>-132.33517185776526</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22475,17 +22446,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29037,7 +29008,7 @@
       <c r="AA116" s="67"/>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>110.95</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29084,7 +29055,7 @@
       <c r="AA117" s="67"/>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>110.95</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30390,7 +30361,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-178.95161290322582</v>
+        <v>-181.51612903225808</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30427,7 +30398,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>9.7106788125662629</v>
+        <v>9.8498404106913675</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30464,7 +30435,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>5.0059671077436843</v>
+        <v>5.0777065192021116</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30501,7 +30472,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="143">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>557634.70000000007</v>
+        <v>565626.04</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30538,7 +30509,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="143">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>574990.70000000007</v>
+        <v>582982.04</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30575,7 +30546,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="183">
         <f ca="1">AC154/AC5</f>
-        <v>10.694914718300691</v>
+        <v>10.843554861149862</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -30612,7 +30583,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="183">
         <f ca="1">AC154/AC12</f>
-        <v>-113.88209546444843</v>
+        <v>-115.46485244602893</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -30747,7 +30718,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="100">AC153/AC157</f>
-        <v>-101.57280510018217</v>
+        <v>-103.02842258652096</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -30784,7 +30755,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="100"/>
-        <v>-67.069952175434508</v>
+        <v>-68.002104280881838</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -30821,7 +30792,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="103">AC157/AC153</f>
-        <v>-9.8451549015870048E-3</v>
+        <v>-9.706059501786728E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -30858,7 +30829,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-5.5881027489860296E-3</v>
+        <v>-5.509152301403945E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31472,7 +31443,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="154">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-6.7445587586281832E-3</v>
+        <v>-6.6492695421165541E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33213,7 +33184,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>110.95</v>
+        <v>112.54</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -33229,7 +33200,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>557634.70000000007</v>
+        <v>565626.04</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33249,7 +33220,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>574990.70000000007</v>
+        <v>582982.04</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33269,7 +33240,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-178.95161290322582</v>
+        <v>-181.51612903225808</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>244</v>
@@ -33289,7 +33260,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>9.7106788125662629</v>
+        <v>9.8498404106913675</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>245</v>
@@ -33309,7 +33280,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>5.0059671077436843</v>
+        <v>5.0777065192021116</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33329,7 +33300,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>10.694914718300691</v>
+        <v>10.843554861149862</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33338,7 +33309,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>-113.88209546444843</v>
+        <v>-115.46485244602893</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33574,7 +33545,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-5.5881027489860296E-3</v>
+        <v>-5.509152301403945E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>271</v>
@@ -33590,7 +33561,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC161</f>
-        <v>-9.8451549015870048E-3</v>
+        <v>-9.706059501786728E-3</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>273</v>
@@ -33675,7 +33646,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC176</f>
-        <v>-6.7445587586281832E-3</v>
+        <v>-6.6492695421165541E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -33854,7 +33825,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC116</f>
-        <v>110.95</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -33883,7 +33854,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC153</f>
-        <v>557634.70000000007</v>
+        <v>565626.04</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -33912,7 +33883,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC154</f>
-        <v>574990.70000000007</v>
+        <v>582982.04</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -33941,7 +33912,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>-178.95161290322582</v>
+        <v>-181.51612903225808</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -33970,7 +33941,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC151</f>
-        <v>9.7106788125662629</v>
+        <v>9.8498404106913675</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -33999,7 +33970,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC152</f>
-        <v>5.0059671077436843</v>
+        <v>5.0777065192021116</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34028,7 +33999,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>10.694914718300691</v>
+        <v>10.843554861149862</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34057,7 +34028,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC156</f>
-        <v>-113.88209546444843</v>
+        <v>-115.46485244602893</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34830,7 +34801,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>-5.5881027489860296E-3</v>
+        <v>-5.509152301403945E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -34859,7 +34830,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>-9.8451549015870048E-3</v>
+        <v>-9.706059501786728E-3</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35182,7 +35153,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>-6.7445587586281832E-3</v>
+        <v>-6.6492695421165541E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35720,14 +35691,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="237" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="238"/>
+      <c r="F3" s="239" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="238"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35794,19 +35765,19 @@
       <c r="B7" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="237">
+      <c r="C7" s="240">
         <f>Statement!AA89</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="F7" s="237">
+      <c r="D7" s="241"/>
+      <c r="F7" s="240">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="238"/>
+      <c r="G7" s="241"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -35833,19 +35804,19 @@
       <c r="B9" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="237">
+      <c r="C9" s="240">
         <f>Statement!AA90</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="F9" s="237">
+      <c r="D9" s="241"/>
+      <c r="F9" s="240">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="238"/>
+      <c r="G9" s="241"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -35872,19 +35843,19 @@
       <c r="B11" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="240">
         <f>Statement!AA91</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="F11" s="237">
+      <c r="D11" s="241"/>
+      <c r="F11" s="240">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="238"/>
+      <c r="G11" s="241"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -35911,19 +35882,19 @@
       <c r="B13" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="237">
+      <c r="C13" s="240">
         <f>Statement!AA95</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="F13" s="237">
+      <c r="D13" s="241"/>
+      <c r="F13" s="240">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="238"/>
+      <c r="G13" s="241"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -35950,19 +35921,19 @@
       <c r="B15" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="237">
+      <c r="C15" s="240">
         <f>Statement!AA96</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="F15" s="237">
+      <c r="D15" s="241"/>
+      <c r="F15" s="240">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="238"/>
+      <c r="G15" s="241"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -35989,19 +35960,19 @@
       <c r="B17" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C17" s="237">
+      <c r="C17" s="240">
         <f>Statement!AA98</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="F17" s="237">
+      <c r="D17" s="241"/>
+      <c r="F17" s="240">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="238"/>
+      <c r="G17" s="241"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36028,22 +35999,22 @@
       <c r="B19" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="240">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="238"/>
-      <c r="F19" s="237">
+      <c r="D19" s="241"/>
+      <c r="F19" s="240">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="238"/>
+      <c r="G19" s="241"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36070,22 +36041,22 @@
       <c r="B21" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="237">
+      <c r="C21" s="240">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="F21" s="237">
+      <c r="D21" s="241"/>
+      <c r="F21" s="240">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="238"/>
+      <c r="G21" s="241"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36133,22 +36104,22 @@
       <c r="B25" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="237">
+      <c r="C25" s="240">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="F25" s="237">
+      <c r="D25" s="241"/>
+      <c r="F25" s="240">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="238"/>
+      <c r="G25" s="241"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36175,22 +36146,22 @@
       <c r="B27" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C27" s="237">
+      <c r="C27" s="240">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="238"/>
-      <c r="F27" s="237">
+      <c r="D27" s="241"/>
+      <c r="F27" s="240">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="238"/>
+      <c r="G27" s="241"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36217,22 +36188,22 @@
       <c r="B29" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C29" s="237">
+      <c r="C29" s="240">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="238"/>
-      <c r="F29" s="237">
+      <c r="D29" s="241"/>
+      <c r="F29" s="240">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="238"/>
+      <c r="G29" s="241"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36259,22 +36230,22 @@
       <c r="B31" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C31" s="237">
+      <c r="C31" s="240">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="F31" s="237">
+      <c r="D31" s="241"/>
+      <c r="F31" s="240">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="238"/>
+      <c r="G31" s="241"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36301,37 +36272,25 @@
       <c r="B33" s="206" t="s">
         <v>316</v>
       </c>
-      <c r="C33" s="237">
+      <c r="C33" s="240">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="F33" s="237">
+      <c r="D33" s="241"/>
+      <c r="F33" s="240">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="238"/>
+      <c r="G33" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -36348,6 +36307,18 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13334882-53AE-6243-B5F8-C5DF70F611FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0640C68-658C-E548-A5AD-096610FFA2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2308,6 +2308,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2362,11 +2367,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12793,37 +12793,37 @@
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
     <v>18.965</v>
-    <v>2.1977000000000002</v>
-    <v>-2.7</v>
-    <v>-2.3990999999999998E-2</v>
-    <v>-0.22500000000000001</v>
-    <v>-2.0479999999999999E-3</v>
+    <v>2.2986</v>
+    <v>-0.93</v>
+    <v>-1.0204999999999999E-2</v>
+    <v>-0.5</v>
+    <v>-5.5430000000000002E-3</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
-    <v>83200</v>
+    <v>82300</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>110.85</v>
+    <v>97.9</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999984073438</v>
+    <v>46234.91275688594</v>
     <v>0</v>
-    <v>107.45</v>
-    <v>552055840000</v>
+    <v>90.13</v>
+    <v>454968800000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>109.575</v>
+    <v>96.72</v>
     <v>0</v>
-    <v>112.54</v>
-    <v>109.84</v>
-    <v>109.61499999999999</v>
-    <v>5026000000</v>
+    <v>91.13</v>
+    <v>90.2</v>
+    <v>89.7</v>
+    <v>5044000000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>70846601</v>
-    <v>127554214</v>
+    <v>108528738</v>
+    <v>116427519</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -12845,19 +12845,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>0.3</v>
-    <v>6.6090000000000003E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.71</v>
+    <v>46.86</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.39</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.41</v>
-    <v>45.39</v>
-    <v>45.69</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13079,9 +13079,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13655,18 +13655,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="229" t="s">
+      <c r="B2" s="234" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="230"/>
-      <c r="E2" s="229" t="s">
+      <c r="C2" s="235"/>
+      <c r="E2" s="234" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="230"/>
-      <c r="H2" s="229" t="s">
+      <c r="F2" s="235"/>
+      <c r="H2" s="234" t="s">
         <v>328</v>
       </c>
-      <c r="I2" s="230"/>
+      <c r="I2" s="235"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="184" t="s">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>552055.84</v>
+        <v>453345.2</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-7.1390648853624414</v>
+        <v>-7.0041093681778079</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>569411.83999999997</v>
+        <v>470701.2</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>35.948054252788353</v>
+        <v>35.392302750768145</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>109.84</v>
+        <v>90.2</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>243</v>
@@ -13746,14 +13746,14 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>109.61499999999999</v>
+        <v>89.7</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC150</f>
-        <v>-177.16129032258064</v>
+        <v>-145.48387096774195</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -13761,7 +13761,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-12.176857011333356</v>
+        <v>-12.006363333943286</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13770,14 +13770,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.7</v>
+        <v>-0.93</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC151</f>
-        <v>9.6135282629317569</v>
+        <v>7.8945761955248033</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13785,7 +13785,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>14.007842773786702</v>
+        <v>13.945267196925325</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13794,14 +13794,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.22500000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC161</f>
-        <v>-9.9446461792705616E-3</v>
+        <v>-1.2109977121187122E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B11</f>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.8724704772961881</v>
+        <v>-0.84539615081014052</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13818,14 +13818,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.3990999999999998E-2</v>
+        <v>-1.0204999999999999E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC162</f>
-        <v>-5.644573925710124E-3</v>
+        <v>-6.873614190687361E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.0479999999999999E-3</v>
+        <v>-5.5430000000000002E-3</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>293</v>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1977000000000002</v>
+        <v>2.2986</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>99</v>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>127554214</v>
+        <v>116427519</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>100</v>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-6.8127166266369003E-3</v>
+        <v>-8.296106366627462E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13934,10 +13934,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="231" t="s">
+      <c r="B17" s="236" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="231"/>
+      <c r="C17" s="236"/>
       <c r="E17" s="183" t="s">
         <v>296</v>
       </c>
@@ -14010,14 +14010,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="231" t="s">
+      <c r="B25" s="236" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="231"/>
-      <c r="E25" s="229" t="s">
+      <c r="C25" s="236"/>
+      <c r="E25" s="234" t="s">
         <v>385</v>
       </c>
-      <c r="F25" s="230"/>
+      <c r="F25" s="235"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="183" t="s">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="F26" s="222" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.69</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="F27" s="223">
         <f ca="1">F26/1000</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14066,15 +14066,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="237" t="s">
         <v>353</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14093,24 +14093,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="237"/>
+      <c r="C39" s="237"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="237" t="s">
         <v>356</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14141,24 +14141,24 @@
       </c>
     </row>
     <row r="49" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
-      <c r="D49" s="232"/>
-      <c r="E49" s="232"/>
-      <c r="F49" s="232"/>
-      <c r="G49" s="232"/>
-      <c r="H49" s="232"/>
+      <c r="B49" s="237"/>
+      <c r="C49" s="237"/>
+      <c r="D49" s="237"/>
+      <c r="E49" s="237"/>
+      <c r="F49" s="237"/>
+      <c r="G49" s="237"/>
+      <c r="H49" s="237"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="237" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="C52" s="237"/>
+      <c r="D52" s="237"/>
+      <c r="E52" s="237"/>
+      <c r="F52" s="237"/>
+      <c r="G52" s="237"/>
+      <c r="H52" s="237"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="41" t="s">
@@ -14173,13 +14173,13 @@
       </c>
     </row>
     <row r="59" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-      <c r="H59" s="232"/>
+      <c r="B59" s="237"/>
+      <c r="C59" s="237"/>
+      <c r="D59" s="237"/>
+      <c r="E59" s="237"/>
+      <c r="F59" s="237"/>
+      <c r="G59" s="237"/>
+      <c r="H59" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14264,36 +14264,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
+      <c r="AA2" s="237" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14304,32 +14304,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="243" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="243"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="239" t="s">
+      <c r="S4" s="244" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
-      <c r="AA4" s="240"/>
-      <c r="AB4" s="240"/>
-      <c r="AC4" s="240"/>
+      <c r="T4" s="245"/>
+      <c r="U4" s="245"/>
+      <c r="V4" s="245"/>
+      <c r="W4" s="245"/>
+      <c r="X4" s="245"/>
+      <c r="Y4" s="245"/>
+      <c r="Z4" s="245"/>
+      <c r="AA4" s="245"/>
+      <c r="AB4" s="245"/>
+      <c r="AC4" s="245"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15017,33 +15017,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="238" t="s">
+      <c r="C13" s="243" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="E13" s="238"/>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="238"/>
-      <c r="L13" s="238"/>
+      <c r="D13" s="243"/>
+      <c r="E13" s="243"/>
+      <c r="F13" s="243"/>
+      <c r="G13" s="243"/>
+      <c r="H13" s="243"/>
+      <c r="I13" s="243"/>
+      <c r="J13" s="243"/>
+      <c r="K13" s="243"/>
+      <c r="L13" s="243"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="239" t="s">
+      <c r="S13" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="240"/>
-      <c r="U13" s="240"/>
-      <c r="V13" s="240"/>
-      <c r="W13" s="240"/>
-      <c r="X13" s="240"/>
-      <c r="Y13" s="240"/>
-      <c r="Z13" s="240"/>
-      <c r="AA13" s="240"/>
-      <c r="AB13" s="240"/>
-      <c r="AC13" s="240"/>
+      <c r="T13" s="245"/>
+      <c r="U13" s="245"/>
+      <c r="V13" s="245"/>
+      <c r="W13" s="245"/>
+      <c r="X13" s="245"/>
+      <c r="Y13" s="245"/>
+      <c r="Z13" s="245"/>
+      <c r="AA13" s="245"/>
+      <c r="AB13" s="245"/>
+      <c r="AC13" s="245"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15680,35 +15680,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
+      <c r="P2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="237"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="237"/>
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15717,31 +15717,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="243" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="P4" s="240" t="s">
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="243"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
+      <c r="P4" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="240"/>
-      <c r="R4" s="240"/>
-      <c r="S4" s="240"/>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
+      <c r="Q4" s="245"/>
+      <c r="R4" s="245"/>
+      <c r="S4" s="245"/>
+      <c r="T4" s="245"/>
+      <c r="U4" s="245"/>
+      <c r="V4" s="245"/>
+      <c r="W4" s="245"/>
+      <c r="X4" s="245"/>
+      <c r="Y4" s="245"/>
+      <c r="Z4" s="245"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15936,32 +15936,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="238" t="s">
+      <c r="C9" s="243" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="E9" s="238"/>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
-      <c r="K9" s="238"/>
-      <c r="L9" s="238"/>
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="243"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="243"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="240" t="s">
+      <c r="P9" s="245" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="240"/>
-      <c r="R9" s="240"/>
-      <c r="S9" s="240"/>
-      <c r="T9" s="240"/>
-      <c r="U9" s="240"/>
-      <c r="V9" s="240"/>
-      <c r="W9" s="240"/>
-      <c r="X9" s="240"/>
-      <c r="Y9" s="240"/>
-      <c r="Z9" s="240"/>
+      <c r="Q9" s="245"/>
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
+      <c r="U9" s="245"/>
+      <c r="V9" s="245"/>
+      <c r="W9" s="245"/>
+      <c r="X9" s="245"/>
+      <c r="Y9" s="245"/>
+      <c r="Z9" s="245"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -16531,31 +16531,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="243" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
-      <c r="P18" s="240" t="s">
+      <c r="D18" s="243"/>
+      <c r="E18" s="243"/>
+      <c r="F18" s="243"/>
+      <c r="G18" s="243"/>
+      <c r="H18" s="243"/>
+      <c r="I18" s="243"/>
+      <c r="J18" s="243"/>
+      <c r="K18" s="243"/>
+      <c r="L18" s="243"/>
+      <c r="P18" s="245" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="240"/>
-      <c r="R18" s="240"/>
-      <c r="S18" s="240"/>
-      <c r="T18" s="240"/>
-      <c r="U18" s="240"/>
-      <c r="V18" s="240"/>
-      <c r="W18" s="240"/>
-      <c r="X18" s="240"/>
-      <c r="Y18" s="240"/>
-      <c r="Z18" s="240"/>
+      <c r="Q18" s="245"/>
+      <c r="R18" s="245"/>
+      <c r="S18" s="245"/>
+      <c r="T18" s="245"/>
+      <c r="U18" s="245"/>
+      <c r="V18" s="245"/>
+      <c r="W18" s="245"/>
+      <c r="X18" s="245"/>
+      <c r="Y18" s="245"/>
+      <c r="Z18" s="245"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17115,60 +17115,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
+      <c r="G3" s="246"/>
+      <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="243"/>
-      <c r="Q3" s="243"/>
-      <c r="R3" s="243"/>
-      <c r="S3" s="243"/>
-      <c r="T3" s="243"/>
-      <c r="U3" s="243"/>
-      <c r="V3" s="243"/>
-      <c r="W3" s="243"/>
-      <c r="X3" s="243"/>
-      <c r="Y3" s="243"/>
-      <c r="Z3" s="243"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
+      <c r="P3" s="248"/>
+      <c r="Q3" s="248"/>
+      <c r="R3" s="248"/>
+      <c r="S3" s="248"/>
+      <c r="T3" s="248"/>
+      <c r="U3" s="248"/>
+      <c r="V3" s="248"/>
+      <c r="W3" s="248"/>
+      <c r="X3" s="248"/>
+      <c r="Y3" s="248"/>
+      <c r="Z3" s="248"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="243" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="243"/>
-      <c r="R5" s="243"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="243"/>
-      <c r="U5" s="243"/>
-      <c r="V5" s="243"/>
-      <c r="W5" s="243"/>
-      <c r="X5" s="243"/>
-      <c r="Y5" s="243"/>
-      <c r="Z5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="P5" s="248"/>
+      <c r="Q5" s="248"/>
+      <c r="R5" s="248"/>
+      <c r="S5" s="248"/>
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
+      <c r="V5" s="248"/>
+      <c r="W5" s="248"/>
+      <c r="X5" s="248"/>
+      <c r="Y5" s="248"/>
+      <c r="Z5" s="248"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17354,30 +17354,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="238" t="s">
+      <c r="C11" s="243" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="E11" s="238"/>
-      <c r="F11" s="238"/>
-      <c r="G11" s="238"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="238"/>
-      <c r="L11" s="238"/>
+      <c r="D11" s="243"/>
+      <c r="E11" s="243"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="243"/>
+      <c r="I11" s="243"/>
+      <c r="J11" s="243"/>
+      <c r="K11" s="243"/>
+      <c r="L11" s="243"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="243"/>
-      <c r="Q11" s="243"/>
-      <c r="R11" s="243"/>
-      <c r="S11" s="243"/>
-      <c r="T11" s="243"/>
-      <c r="U11" s="243"/>
-      <c r="V11" s="243"/>
-      <c r="W11" s="243"/>
-      <c r="X11" s="243"/>
-      <c r="Y11" s="243"/>
-      <c r="Z11" s="243"/>
+      <c r="P11" s="248"/>
+      <c r="Q11" s="248"/>
+      <c r="R11" s="248"/>
+      <c r="S11" s="248"/>
+      <c r="T11" s="248"/>
+      <c r="U11" s="248"/>
+      <c r="V11" s="248"/>
+      <c r="W11" s="248"/>
+      <c r="X11" s="248"/>
+      <c r="Y11" s="248"/>
+      <c r="Z11" s="248"/>
       <c r="AB11" s="109"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17619,18 +17619,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="243" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
+      <c r="D18" s="243"/>
+      <c r="E18" s="243"/>
+      <c r="F18" s="243"/>
+      <c r="G18" s="243"/>
+      <c r="H18" s="243"/>
+      <c r="I18" s="243"/>
+      <c r="J18" s="243"/>
+      <c r="K18" s="243"/>
+      <c r="L18" s="243"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17843,23 +17843,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="243"/>
-      <c r="C25" s="243"/>
+      <c r="B25" s="248"/>
+      <c r="C25" s="248"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="238" t="s">
+      <c r="C26" s="243" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238"/>
-      <c r="L26" s="238"/>
+      <c r="D26" s="243"/>
+      <c r="E26" s="243"/>
+      <c r="F26" s="243"/>
+      <c r="G26" s="243"/>
+      <c r="H26" s="243"/>
+      <c r="I26" s="243"/>
+      <c r="J26" s="243"/>
+      <c r="K26" s="243"/>
+      <c r="L26" s="243"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18051,18 +18051,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="238" t="s">
+      <c r="C33" s="243" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="E33" s="238"/>
-      <c r="F33" s="238"/>
-      <c r="G33" s="238"/>
-      <c r="H33" s="238"/>
-      <c r="I33" s="238"/>
-      <c r="J33" s="238"/>
-      <c r="K33" s="238"/>
-      <c r="L33" s="238"/>
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="243"/>
+      <c r="I33" s="243"/>
+      <c r="J33" s="243"/>
+      <c r="K33" s="243"/>
+      <c r="L33" s="243"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18246,18 +18246,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="238" t="s">
+      <c r="C40" s="243" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="238"/>
-      <c r="E40" s="238"/>
-      <c r="F40" s="238"/>
-      <c r="G40" s="238"/>
-      <c r="H40" s="238"/>
-      <c r="I40" s="238"/>
-      <c r="J40" s="238"/>
-      <c r="K40" s="238"/>
-      <c r="L40" s="238"/>
+      <c r="D40" s="243"/>
+      <c r="E40" s="243"/>
+      <c r="F40" s="243"/>
+      <c r="G40" s="243"/>
+      <c r="H40" s="243"/>
+      <c r="I40" s="243"/>
+      <c r="J40" s="243"/>
+      <c r="K40" s="243"/>
+      <c r="L40" s="243"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18571,60 +18571,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243"/>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
+      <c r="S2" s="248"/>
+      <c r="T2" s="248"/>
+      <c r="U2" s="248"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="248"/>
+      <c r="X2" s="248"/>
+      <c r="Y2" s="248"/>
+      <c r="Z2" s="248"/>
+      <c r="AA2" s="248"/>
+      <c r="AB2" s="248"/>
+      <c r="AC2" s="248"/>
       <c r="AE2" s="108"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="243" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
-      <c r="AA4" s="243"/>
-      <c r="AB4" s="243"/>
-      <c r="AC4" s="243"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="243"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
+      <c r="AA4" s="248"/>
+      <c r="AB4" s="248"/>
+      <c r="AC4" s="248"/>
       <c r="AE4" s="109"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -18987,18 +18987,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="238" t="s">
+      <c r="C13" s="243" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="E13" s="238"/>
-      <c r="F13" s="238"/>
-      <c r="G13" s="238"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="238"/>
-      <c r="L13" s="238"/>
+      <c r="D13" s="243"/>
+      <c r="E13" s="243"/>
+      <c r="F13" s="243"/>
+      <c r="G13" s="243"/>
+      <c r="H13" s="243"/>
+      <c r="I13" s="243"/>
+      <c r="J13" s="243"/>
+      <c r="K13" s="243"/>
+      <c r="L13" s="243"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19091,18 +19091,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="243" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
+      <c r="D18" s="243"/>
+      <c r="E18" s="243"/>
+      <c r="F18" s="243"/>
+      <c r="G18" s="243"/>
+      <c r="H18" s="243"/>
+      <c r="I18" s="243"/>
+      <c r="J18" s="243"/>
+      <c r="K18" s="243"/>
+      <c r="L18" s="243"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19294,18 +19294,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="238" t="s">
+      <c r="C25" s="243" t="s">
         <v>262</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="E25" s="238"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="238"/>
-      <c r="H25" s="238"/>
-      <c r="I25" s="238"/>
-      <c r="J25" s="238"/>
-      <c r="K25" s="238"/>
-      <c r="L25" s="238"/>
+      <c r="D25" s="243"/>
+      <c r="E25" s="243"/>
+      <c r="F25" s="243"/>
+      <c r="G25" s="243"/>
+      <c r="H25" s="243"/>
+      <c r="I25" s="243"/>
+      <c r="J25" s="243"/>
+      <c r="K25" s="243"/>
+      <c r="L25" s="243"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19443,18 +19443,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="238" t="s">
+      <c r="C31" s="243" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="E31" s="238"/>
-      <c r="F31" s="238"/>
-      <c r="G31" s="238"/>
-      <c r="H31" s="238"/>
-      <c r="I31" s="238"/>
-      <c r="J31" s="238"/>
-      <c r="K31" s="238"/>
-      <c r="L31" s="238"/>
+      <c r="D31" s="243"/>
+      <c r="E31" s="243"/>
+      <c r="F31" s="243"/>
+      <c r="G31" s="243"/>
+      <c r="H31" s="243"/>
+      <c r="I31" s="243"/>
+      <c r="J31" s="243"/>
+      <c r="K31" s="243"/>
+      <c r="L31" s="243"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19665,10 +19665,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="237" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="237"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>109.84</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>552055.84</v>
+        <v>453345.2</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.1977000000000002</v>
+        <v>2.2986</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19753,10 +19753,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="237" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="237"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.5417840393199764E-2</v>
+        <v>9.0355438321492884E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92458215960680024</v>
+        <v>0.90964456167850716</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14458650000000001</v>
+        <v>0.15006700000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13689942349116252</v>
+        <v>0.14036219343620343</v>
       </c>
     </row>
   </sheetData>
@@ -19845,60 +19845,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
+      <c r="G3" s="246"/>
+      <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="243"/>
-      <c r="Q3" s="243"/>
-      <c r="R3" s="243"/>
-      <c r="S3" s="243"/>
-      <c r="T3" s="243"/>
-      <c r="U3" s="243"/>
-      <c r="V3" s="243"/>
-      <c r="W3" s="243"/>
-      <c r="X3" s="243"/>
-      <c r="Y3" s="243"/>
-      <c r="Z3" s="243"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
+      <c r="P3" s="248"/>
+      <c r="Q3" s="248"/>
+      <c r="R3" s="248"/>
+      <c r="S3" s="248"/>
+      <c r="T3" s="248"/>
+      <c r="U3" s="248"/>
+      <c r="V3" s="248"/>
+      <c r="W3" s="248"/>
+      <c r="X3" s="248"/>
+      <c r="Y3" s="248"/>
+      <c r="Z3" s="248"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="243" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="243"/>
-      <c r="R5" s="243"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="243"/>
-      <c r="U5" s="243"/>
-      <c r="V5" s="243"/>
-      <c r="W5" s="243"/>
-      <c r="X5" s="243"/>
-      <c r="Y5" s="243"/>
-      <c r="Z5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="P5" s="248"/>
+      <c r="Q5" s="248"/>
+      <c r="R5" s="248"/>
+      <c r="S5" s="248"/>
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
+      <c r="V5" s="248"/>
+      <c r="W5" s="248"/>
+      <c r="X5" s="248"/>
+      <c r="Y5" s="248"/>
+      <c r="Z5" s="248"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-23383.084881215414</v>
+        <v>-22710.363312777641</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20105,23 +20105,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-6496.9172558363534</v>
+        <v>-6477.1890239303684</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5061.9404947247322</v>
+        <v>-5031.2454705438458</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3569.4055936547038</v>
+        <v>-3536.9881654360802</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3269.8020670695473</v>
+        <v>-3230.2668936688319</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1410.9244923529491</v>
+        <v>-1389.6324611747609</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20140,14 +20140,14 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-12310.950210193347</v>
+        <v>-11776.331669707777</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="237" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="237"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20163,14 +20163,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13689942349116252</v>
+        <v>0.14036219343620343</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="237" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="237"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-19808.989903638285</v>
+        <v>-19665.322014753889</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20187,7 +20187,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-12310.950210193347</v>
+        <v>-11776.331669707777</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-32119.940113831632</v>
+        <v>-31441.653684461664</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-35880.940113831632</v>
+        <v>-35202.653684461664</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C26" s="141">
         <f ca="1">C24/C25</f>
-        <v>-7.1390648853624414</v>
+        <v>-7.0041093681778079</v>
       </c>
     </row>
   </sheetData>
@@ -20284,37 +20284,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="243" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="243"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20503,18 +20503,18 @@
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="238" t="s">
+      <c r="C10" s="243" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="238"/>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="243"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="243"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="243"/>
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20708,18 +20708,18 @@
       <c r="N15" s="90"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="238" t="s">
+      <c r="C16" s="243" t="s">
         <v>191</v>
       </c>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="238"/>
-      <c r="L16" s="238"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="243"/>
+      <c r="I16" s="243"/>
+      <c r="J16" s="243"/>
+      <c r="K16" s="243"/>
+      <c r="L16" s="243"/>
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20853,18 +20853,18 @@
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="238" t="s">
+      <c r="C21" s="243" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="E21" s="238"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
-      <c r="H21" s="238"/>
-      <c r="I21" s="238"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="238"/>
-      <c r="L21" s="238"/>
+      <c r="D21" s="243"/>
+      <c r="E21" s="243"/>
+      <c r="F21" s="243"/>
+      <c r="G21" s="243"/>
+      <c r="H21" s="243"/>
+      <c r="I21" s="243"/>
+      <c r="J21" s="243"/>
+      <c r="K21" s="243"/>
+      <c r="L21" s="243"/>
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -20948,18 +20948,18 @@
       <c r="N25" s="90"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="238" t="s">
+      <c r="C26" s="243" t="s">
         <v>195</v>
       </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="238"/>
-      <c r="L26" s="238"/>
+      <c r="D26" s="243"/>
+      <c r="E26" s="243"/>
+      <c r="F26" s="243"/>
+      <c r="G26" s="243"/>
+      <c r="H26" s="243"/>
+      <c r="I26" s="243"/>
+      <c r="J26" s="243"/>
+      <c r="K26" s="243"/>
+      <c r="L26" s="243"/>
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21229,10 +21229,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="237" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="237"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13689942349116252</v>
+        <v>0.14036219343620343</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>184435.92067451426</v>
+        <v>181642.71362536069</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21303,7 +21303,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>180674.92067451426</v>
+        <v>177881.71362536069</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21321,14 +21321,14 @@
       </c>
       <c r="C47" s="141">
         <f ca="1">C45/C46</f>
-        <v>35.948054252788353</v>
+        <v>35.392302750768145</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="232" t="s">
+      <c r="B49" s="237" t="s">
         <v>205</v>
       </c>
-      <c r="C49" s="232"/>
+      <c r="C49" s="237"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21384,10 +21384,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="232" t="s">
+      <c r="B57" s="237" t="s">
         <v>322</v>
       </c>
-      <c r="C57" s="232"/>
+      <c r="C57" s="237"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21404,7 +21404,7 @@
       </c>
       <c r="C59" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13689942349116252</v>
+        <v>0.14036219343620343</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="C62" s="63">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>-57439.883338961445</v>
+        <v>-56582.982116398955</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>-61200.883338961445</v>
+        <v>-60343.982116398955</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="C67" s="141">
         <f ca="1">C65/C66</f>
-        <v>-12.176857011333356</v>
+        <v>-12.006363333943286</v>
       </c>
     </row>
   </sheetData>
@@ -21527,10 +21527,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="237" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="237"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-7.1390648853624414</v>
+        <v>-7.0041093681778079</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C47</f>
-        <v>35.948054252788353</v>
+        <v>35.392302750768145</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C67</f>
-        <v>-12.176857011333356</v>
+        <v>-12.006363333943286</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C9" s="141">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>14.007842773786702</v>
+        <v>13.945267196925325</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>109.84</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="C11" s="153">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.8724704772961881</v>
+        <v>-0.84539615081014052</v>
       </c>
     </row>
   </sheetData>
@@ -21649,37 +21649,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="238" t="s">
+      <c r="C4" s="243" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="243"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21730,23 +21730,23 @@
       <c r="B6" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="247">
+      <c r="C6" s="229">
         <f>Statement!M26</f>
         <v>4.8600000000000003</v>
       </c>
-      <c r="D6" s="247">
+      <c r="D6" s="229">
         <f>Statement!N26</f>
         <v>1.94</v>
       </c>
-      <c r="E6" s="247">
+      <c r="E6" s="229">
         <f>Statement!O26</f>
         <v>0.4</v>
       </c>
-      <c r="F6" s="247">
+      <c r="F6" s="229">
         <f>Statement!P26</f>
         <v>-4.38</v>
       </c>
-      <c r="G6" s="248">
+      <c r="G6" s="230">
         <f>Statement!Q26</f>
         <v>-0.06</v>
       </c>
@@ -21761,23 +21761,23 @@
       <c r="B7" s="16" t="s">
         <v>406</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="229">
         <f>Statement!M82</f>
         <v>1.39</v>
       </c>
-      <c r="D7" s="247">
+      <c r="D7" s="229">
         <f>Statement!N82</f>
         <v>1.46</v>
       </c>
-      <c r="E7" s="247">
+      <c r="E7" s="229">
         <f>Statement!O82</f>
         <v>0.74</v>
       </c>
-      <c r="F7" s="247">
+      <c r="F7" s="229">
         <f>Statement!P82</f>
         <v>0.38</v>
       </c>
-      <c r="G7" s="248">
+      <c r="G7" s="230">
         <f>Statement!Q82</f>
         <v>0</v>
       </c>
@@ -21792,18 +21792,18 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="238" t="s">
+      <c r="C9" s="243" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="E9" s="238"/>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
-      <c r="K9" s="238"/>
-      <c r="L9" s="238"/>
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="243"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="243"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21924,18 +21924,18 @@
       <c r="N13" s="90"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="238" t="s">
+      <c r="C14" s="243" t="s">
         <v>407</v>
       </c>
-      <c r="D14" s="238"/>
-      <c r="E14" s="238"/>
-      <c r="F14" s="238"/>
-      <c r="G14" s="238"/>
-      <c r="H14" s="238"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="238"/>
-      <c r="L14" s="238"/>
+      <c r="D14" s="243"/>
+      <c r="E14" s="243"/>
+      <c r="F14" s="243"/>
+      <c r="G14" s="243"/>
+      <c r="H14" s="243"/>
+      <c r="I14" s="243"/>
+      <c r="J14" s="243"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="243"/>
       <c r="N14" s="90"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22025,17 +22025,17 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="232" t="s">
+      <c r="B20" s="237" t="s">
         <v>409</v>
       </c>
-      <c r="C20" s="232"/>
+      <c r="C20" s="237"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C21" s="249">
+      <c r="C21" s="231">
         <f>G7</f>
         <v>0</v>
       </c>
@@ -22044,7 +22044,7 @@
       <c r="B22" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C22" s="250">
+      <c r="C22" s="232">
         <v>0</v>
       </c>
     </row>
@@ -22052,7 +22052,7 @@
       <c r="B23" s="39" t="s">
         <v>412</v>
       </c>
-      <c r="C23" s="251">
+      <c r="C23" s="233">
         <f>C21*(1+C22)</f>
         <v>0</v>
       </c>
@@ -22070,7 +22070,7 @@
       <c r="B25" s="39" t="s">
         <v>413</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="232">
         <v>0</v>
       </c>
     </row>
@@ -22085,12 +22085,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C9:L9"/>
     <mergeCell ref="C14:L14"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22129,60 +22129,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="241"/>
-      <c r="H3" s="242" t="s">
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
+      <c r="G3" s="246"/>
+      <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="243"/>
-      <c r="Q3" s="243"/>
-      <c r="R3" s="243"/>
-      <c r="S3" s="243"/>
-      <c r="T3" s="243"/>
-      <c r="U3" s="243"/>
-      <c r="V3" s="243"/>
-      <c r="W3" s="243"/>
-      <c r="X3" s="243"/>
-      <c r="Y3" s="243"/>
-      <c r="Z3" s="243"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
+      <c r="P3" s="248"/>
+      <c r="Q3" s="248"/>
+      <c r="R3" s="248"/>
+      <c r="S3" s="248"/>
+      <c r="T3" s="248"/>
+      <c r="U3" s="248"/>
+      <c r="V3" s="248"/>
+      <c r="W3" s="248"/>
+      <c r="X3" s="248"/>
+      <c r="Y3" s="248"/>
+      <c r="Z3" s="248"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="238" t="s">
+      <c r="C5" s="243" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="238"/>
-      <c r="E5" s="238"/>
-      <c r="F5" s="238"/>
-      <c r="G5" s="238"/>
-      <c r="H5" s="238"/>
-      <c r="I5" s="238"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="238"/>
-      <c r="L5" s="238"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="243"/>
-      <c r="R5" s="243"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="243"/>
-      <c r="U5" s="243"/>
-      <c r="V5" s="243"/>
-      <c r="W5" s="243"/>
-      <c r="X5" s="243"/>
-      <c r="Y5" s="243"/>
-      <c r="Z5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="P5" s="248"/>
+      <c r="Q5" s="248"/>
+      <c r="R5" s="248"/>
+      <c r="S5" s="248"/>
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
+      <c r="V5" s="248"/>
+      <c r="W5" s="248"/>
+      <c r="X5" s="248"/>
+      <c r="Y5" s="248"/>
+      <c r="Z5" s="248"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22317,7 +22317,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-968721.82537113957</v>
+        <v>-940852.10377306689</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22371,23 +22371,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13175.086008808861</v>
+        <v>-13135.079165266319</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19121.209374686256</v>
+        <v>-19005.26056321061</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27750.911660548987</v>
+        <v>-27498.877207429832</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40275.334206167594</v>
+        <v>-39788.365182064052</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58452.225471370461</v>
+        <v>-57570.132479210835</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22406,15 +22406,15 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-510021.93338708114</v>
+        <v>-487873.58764710219</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="244" t="s">
+      <c r="B14" s="249" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="245"/>
+      <c r="C14" s="250"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="154" t="s">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>109.84</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="C16" s="155">
         <f ca="1">C36</f>
-        <v>-133.81569839010413</v>
+        <v>-129.05537251179544</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22441,20 +22441,20 @@
       <c r="C17" s="157">
         <v>0.65</v>
       </c>
-      <c r="E17" s="246" t="s">
+      <c r="E17" s="251" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="244" t="s">
+      <c r="B19" s="249" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="245"/>
+      <c r="C19" s="250"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="158" t="s">
@@ -22470,7 +22470,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13689942349116252</v>
+        <v>0.14036219343620343</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>552055.84</v>
+        <v>453345.2</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22515,15 +22515,15 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>555816.84</v>
+        <v>457106.2</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="244" t="s">
+      <c r="B28" s="249" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="245"/>
+      <c r="C28" s="250"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="158" t="s">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="C29" s="160">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158774.76672158216</v>
+        <v>-156997.71459718165</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22540,7 +22540,7 @@
       </c>
       <c r="C30" s="160">
         <f ca="1">L11</f>
-        <v>-510021.93338708114</v>
+        <v>-487873.58764710219</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="C31" s="163">
         <f ca="1">C29+C30</f>
-        <v>-668796.7001086633</v>
+        <v>-644871.30224428384</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="C34" s="163">
         <f ca="1">C31+C32-C33</f>
-        <v>-672557.7001086633</v>
+        <v>-648632.30224428384</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22594,22 +22594,22 @@
       </c>
       <c r="C36" s="166">
         <f ca="1">C34/C35</f>
-        <v>-133.81569839010413</v>
+        <v>-129.05537251179544</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="238" t="s">
+      <c r="C39" s="243" t="s">
         <v>224</v>
       </c>
-      <c r="D39" s="238"/>
-      <c r="E39" s="238"/>
-      <c r="F39" s="238"/>
-      <c r="G39" s="238"/>
-      <c r="H39" s="238"/>
-      <c r="I39" s="238"/>
-      <c r="J39" s="238"/>
-      <c r="K39" s="238"/>
-      <c r="L39" s="238"/>
+      <c r="D39" s="243"/>
+      <c r="E39" s="243"/>
+      <c r="F39" s="243"/>
+      <c r="G39" s="243"/>
+      <c r="H39" s="243"/>
+      <c r="I39" s="243"/>
+      <c r="J39" s="243"/>
+      <c r="K39" s="243"/>
+      <c r="L39" s="243"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -29593,17 +29593,33 @@
       <c r="Q116" s="62">
         <v>36.200000000000003</v>
       </c>
-      <c r="T116" s="67"/>
-      <c r="U116" s="67"/>
-      <c r="V116" s="67"/>
-      <c r="W116" s="67"/>
-      <c r="X116" s="67"/>
-      <c r="Y116" s="67"/>
-      <c r="Z116" s="67"/>
-      <c r="AA116" s="67"/>
+      <c r="T116" s="62">
+        <v>30.97</v>
+      </c>
+      <c r="U116" s="62">
+        <v>23.91</v>
+      </c>
+      <c r="V116" s="62">
+        <v>20.3</v>
+      </c>
+      <c r="W116" s="62">
+        <v>22.71</v>
+      </c>
+      <c r="X116" s="62">
+        <v>22.69</v>
+      </c>
+      <c r="Y116" s="62">
+        <v>35.5</v>
+      </c>
+      <c r="Z116" s="62">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="AA116" s="62">
+        <v>43.23</v>
+      </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>109.84</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29640,17 +29656,41 @@
         <f>Q116/Q85</f>
         <v>36.200000000000003</v>
       </c>
-      <c r="T117" s="67"/>
-      <c r="U117" s="67"/>
-      <c r="V117" s="67"/>
-      <c r="W117" s="67"/>
-      <c r="X117" s="67"/>
-      <c r="Y117" s="67"/>
-      <c r="Z117" s="67"/>
-      <c r="AA117" s="67"/>
+      <c r="T117" s="64">
+        <f t="shared" ref="T117:AA117" si="74">T116/T85</f>
+        <v>30.97</v>
+      </c>
+      <c r="U117" s="64">
+        <f t="shared" si="74"/>
+        <v>23.91</v>
+      </c>
+      <c r="V117" s="64">
+        <f t="shared" si="74"/>
+        <v>20.3</v>
+      </c>
+      <c r="W117" s="64">
+        <f t="shared" si="74"/>
+        <v>22.71</v>
+      </c>
+      <c r="X117" s="64">
+        <f t="shared" si="74"/>
+        <v>22.69</v>
+      </c>
+      <c r="Y117" s="64">
+        <f t="shared" si="74"/>
+        <v>35.5</v>
+      </c>
+      <c r="Z117" s="64">
+        <f t="shared" si="74"/>
+        <v>36.200000000000003</v>
+      </c>
+      <c r="AA117" s="64">
+        <f t="shared" si="74"/>
+        <v>43.23</v>
+      </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>109.84</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -29764,19 +29804,19 @@
         <v>97</v>
       </c>
       <c r="M123" s="75">
-        <f t="shared" ref="M123:P123" si="74">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="75">M121*M122</f>
         <v>0.11797679417597948</v>
       </c>
       <c r="N123" s="75">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>4.4024535565037361E-2</v>
       </c>
       <c r="O123" s="75">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>8.7434489382581995E-3</v>
       </c>
       <c r="P123" s="75">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>-9.7885334758378503E-2</v>
       </c>
       <c r="Q123" s="75">
@@ -29838,19 +29878,19 @@
         <v>99</v>
       </c>
       <c r="M125" s="75">
-        <f t="shared" ref="M125:P125" si="75">M123*M124</f>
+        <f t="shared" ref="M125:P125" si="76">M123*M124</f>
         <v>0.20827960709081569</v>
       </c>
       <c r="N125" s="75">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>7.904518698914445E-2</v>
       </c>
       <c r="O125" s="75">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>1.5863244625438012E-2</v>
       </c>
       <c r="P125" s="75">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>-0.19374433363553945</v>
       </c>
       <c r="Q125" s="75">
@@ -30012,35 +30052,35 @@
       <c r="P131" s="49"/>
       <c r="Q131" s="49"/>
       <c r="T131" s="25">
-        <f t="shared" ref="T131:AA131" si="76">U5</f>
+        <f t="shared" ref="T131:AA131" si="77">U5</f>
         <v>13284</v>
       </c>
       <c r="U131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>14260</v>
       </c>
       <c r="V131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>12667</v>
       </c>
       <c r="W131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>12859</v>
       </c>
       <c r="X131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>13653</v>
       </c>
       <c r="Y131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>13674</v>
       </c>
       <c r="Z131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>13577</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
@@ -30065,31 +30105,31 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="227" t="str">
-        <f t="shared" ref="T132:Z132" si="77">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Z132" si="78">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="V132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="W132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="X132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="Y132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>MET</v>
       </c>
       <c r="Z132" s="227" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>BEAT</v>
       </c>
       <c r="AA132" s="227" t="str">
@@ -30208,35 +30248,35 @@
       <c r="P135" s="49"/>
       <c r="Q135" s="49"/>
       <c r="T135" s="73">
-        <f t="shared" ref="T135:AA135" si="78">U101</f>
+        <f t="shared" ref="T135:AA135" si="79">U101</f>
         <v>0.15033122553447756</v>
       </c>
       <c r="U135" s="73">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.39158485273492288</v>
       </c>
       <c r="V135" s="73">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.36883239914739085</v>
       </c>
       <c r="W135" s="73">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.27544910179640719</v>
       </c>
       <c r="X135" s="73">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.38218706511389439</v>
       </c>
       <c r="Y135" s="73">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.36148895714494661</v>
       </c>
       <c r="Z135" s="73">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.39382779700964865</v>
       </c>
       <c r="AA135" s="73">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
@@ -30261,31 +30301,31 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="227" t="str">
-        <f t="shared" ref="T136:Z136" si="79">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Z136" si="80">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U136" s="227" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="V136" s="227" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="W136" s="227" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>MISSED</v>
       </c>
       <c r="X136" s="227" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="Y136" s="227" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="Z136" s="227" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>BEAT</v>
       </c>
       <c r="AA136" s="227" t="str">
@@ -30378,55 +30418,55 @@
         <v>134</v>
       </c>
       <c r="M141" s="117">
-        <f t="shared" ref="M141:Q142" si="80">M30/M5*365</f>
+        <f t="shared" ref="M141:Q142" si="81">M30/M5*365</f>
         <v>43.680464162785988</v>
       </c>
       <c r="N141" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>23.924651885685286</v>
       </c>
       <c r="O141" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>22.898318211993807</v>
       </c>
       <c r="P141" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>23.906706088397584</v>
       </c>
       <c r="Q141" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>26.511929313378616</v>
       </c>
       <c r="T141" s="117">
-        <f t="shared" ref="T141:AA141" si="81">T30/T5*90</f>
+        <f t="shared" ref="T141:AA141" si="82">T30/T5*90</f>
         <v>21.958232681368347</v>
       </c>
       <c r="U141" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>21.144986449864501</v>
       </c>
       <c r="V141" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>21.950911640953716</v>
       </c>
       <c r="W141" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>21.769953422278363</v>
       </c>
       <c r="X141" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>16.517614122404542</v>
       </c>
       <c r="Y141" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>21.107448912326962</v>
       </c>
       <c r="Z141" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>25.267661254936375</v>
       </c>
       <c r="AA141" s="117">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>26.952935110849229</v>
       </c>
       <c r="AC141" s="117">
@@ -30439,55 +30479,55 @@
         <v>135</v>
       </c>
       <c r="M142" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>111.71121020193701</v>
       </c>
       <c r="N142" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>133.38012600862163</v>
       </c>
       <c r="O142" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>124.89943721745549</v>
       </c>
       <c r="P142" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>124.51812283253162</v>
       </c>
       <c r="Q142" s="117">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>122.99350310342828</v>
       </c>
       <c r="T142" s="117">
-        <f t="shared" ref="T142:AA142" si="82">T31/T6*365</f>
+        <f t="shared" ref="T142:AA142" si="83">T31/T6*365</f>
         <v>495.30050687907317</v>
       </c>
       <c r="U142" s="117">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>390.06201825108536</v>
       </c>
       <c r="V142" s="117">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>513.17081604425994</v>
       </c>
       <c r="W142" s="117">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>560.6710444027517</v>
       </c>
       <c r="X142" s="117">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>445.70194268541377</v>
       </c>
       <c r="Y142" s="117">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>497.15293420272673</v>
       </c>
       <c r="Z142" s="117">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>485.6912152101707</v>
       </c>
       <c r="AA142" s="117">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>551.09234507897929</v>
       </c>
       <c r="AC142" s="117">
@@ -30520,35 +30560,35 @@
         <v>104.6154069261558</v>
       </c>
       <c r="T143" s="117">
-        <f t="shared" ref="T143:AA143" si="83">T38/T6*90</f>
+        <f t="shared" ref="T143:AA143" si="84">T38/T6*90</f>
         <v>104.46777697320782</v>
       </c>
       <c r="U143" s="117">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>88.301585895277753</v>
       </c>
       <c r="V143" s="117">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>130.24896265560164</v>
       </c>
       <c r="W143" s="117">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>122.65666041275797</v>
       </c>
       <c r="X143" s="117">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>103.03101856820865</v>
       </c>
       <c r="Y143" s="117">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>109.55779490219324</v>
       </c>
       <c r="Z143" s="117">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>101.86462031840568</v>
       </c>
       <c r="AA143" s="117">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>78.287970838396106</v>
       </c>
       <c r="AC143" s="117">
@@ -30565,55 +30605,55 @@
         <v>95.814435590545941</v>
       </c>
       <c r="N144" s="117">
-        <f t="shared" ref="N144:Q144" si="84">N141+N142-N143</f>
+        <f t="shared" ref="N144:Q144" si="85">N141+N142-N143</f>
         <v>60.527531293223674</v>
       </c>
       <c r="O144" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>51.577931952498773</v>
       </c>
       <c r="P144" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>20.252214534532527</v>
       </c>
       <c r="Q144" s="117">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>44.890025490651112</v>
       </c>
       <c r="T144" s="117">
-        <f t="shared" ref="T144" si="85">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="86">T141+T142-T143</f>
         <v>412.79096258723371</v>
       </c>
       <c r="U144" s="117">
-        <f t="shared" ref="U144" si="86">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="87">U141+U142-U143</f>
         <v>322.90541880567213</v>
       </c>
       <c r="V144" s="117">
-        <f t="shared" ref="V144" si="87">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="88">V141+V142-V143</f>
         <v>404.87276502961197</v>
       </c>
       <c r="W144" s="117">
-        <f t="shared" ref="W144" si="88">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="89">W141+W142-W143</f>
         <v>459.78433741227212</v>
       </c>
       <c r="X144" s="117">
-        <f t="shared" ref="X144" si="89">X141+X142-X143</f>
+        <f t="shared" ref="X144" si="90">X141+X142-X143</f>
         <v>359.18853823960967</v>
       </c>
       <c r="Y144" s="117">
-        <f t="shared" ref="Y144" si="90">Y141+Y142-Y143</f>
+        <f t="shared" ref="Y144" si="91">Y141+Y142-Y143</f>
         <v>408.70258821286052</v>
       </c>
       <c r="Z144" s="117">
-        <f t="shared" ref="Z144:AA144" si="91">Z141+Z142-Z143</f>
+        <f t="shared" ref="Z144:AA144" si="92">Z141+Z142-Z143</f>
         <v>409.09425614670141</v>
       </c>
       <c r="AA144" s="117">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>499.75730935143241</v>
       </c>
       <c r="AC144" s="117">
-        <f t="shared" ref="AC144" si="92">AC141+AC142-AC143</f>
+        <f t="shared" ref="AC144" si="93">AC141+AC142-AC143</f>
         <v>82.9857136586363</v>
       </c>
     </row>
@@ -30642,35 +30682,35 @@
         <v>0.40763556496705489</v>
       </c>
       <c r="T145" s="117">
-        <f t="shared" ref="T145:AA145" si="93">T108/T49</f>
+        <f t="shared" ref="T145:AA145" si="94">T108/T49</f>
         <v>0.46020533025540444</v>
       </c>
       <c r="U145" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.50472209942531043</v>
       </c>
       <c r="V145" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.50378764984386015</v>
       </c>
       <c r="W145" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.50273667749308315</v>
       </c>
       <c r="X145" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.51854765383161527</v>
       </c>
       <c r="Y145" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.43762690832518614</v>
       </c>
       <c r="Z145" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.40763556496705489</v>
       </c>
       <c r="AA145" s="117">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.40424978005996731</v>
       </c>
       <c r="AC145" s="117">
@@ -30703,35 +30743,35 @@
         <v>5.7489871457197606E-3</v>
       </c>
       <c r="T146" s="178">
-        <f t="shared" ref="T146:AA146" si="94">(T108-T107)/T49</f>
+        <f t="shared" ref="T146:AA146" si="95">(T108-T107)/T49</f>
         <v>0.15562054691093388</v>
       </c>
       <c r="U146" s="178">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.20751115219225977</v>
       </c>
       <c r="V146" s="178">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.22731943185252343</v>
       </c>
       <c r="W146" s="178">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.2413488912947592</v>
       </c>
       <c r="X146" s="178">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.24690702164829439</v>
       </c>
       <c r="Y146" s="178">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>6.5343686545837401E-2</v>
       </c>
       <c r="Z146" s="178">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>5.7489871457197606E-3</v>
       </c>
       <c r="AA146" s="178">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>3.3763039301937268E-2</v>
       </c>
       <c r="AC146" s="178">
@@ -30764,35 +30804,35 @@
         <v>1.5761520190023752</v>
       </c>
       <c r="T147" s="117">
-        <f t="shared" ref="T147:AA147" si="95">(T107+T30)/T40</f>
+        <f t="shared" ref="T147:AA147" si="96">(T107+T30)/T40</f>
         <v>1.1936178849096075</v>
       </c>
       <c r="U147" s="117">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.93014590858670609</v>
       </c>
       <c r="V147" s="117">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.86701620591039086</v>
       </c>
       <c r="W147" s="117">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.90566917386709767</v>
       </c>
       <c r="X147" s="117">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.82791854944803522</v>
       </c>
       <c r="Y147" s="117">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.32532433352943</v>
       </c>
       <c r="Z147" s="117">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.5761520190023752</v>
       </c>
       <c r="AA147" s="117">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>1.686293472196392</v>
       </c>
       <c r="AC147" s="117">
@@ -30825,35 +30865,35 @@
         <v>2.0170387965162311</v>
       </c>
       <c r="T148" s="117">
-        <f t="shared" ref="T148:AA148" si="96">T32/T40</f>
+        <f t="shared" ref="T148:AA148" si="97">T32/T40</f>
         <v>1.5870671620819934</v>
       </c>
       <c r="U148" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.3122386871071419</v>
       </c>
       <c r="V148" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.3268659227275277</v>
       </c>
       <c r="W148" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.3095667309007273</v>
       </c>
       <c r="X148" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.2404907624549562</v>
       </c>
       <c r="Y148" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>1.6017277146484195</v>
       </c>
       <c r="Z148" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0170387965162311</v>
       </c>
       <c r="AA148" s="117">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.3119583410823878</v>
       </c>
       <c r="AC148" s="117">
@@ -30886,35 +30926,35 @@
         <v>N/A</v>
       </c>
       <c r="T149" s="180" t="str">
-        <f t="shared" ref="T149:AA149" si="97">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
+        <f t="shared" ref="T149:AA149" si="98">IF(T13&gt;=0,"N/A",IF(T12&lt;=0,"N/A",T12/-T13))</f>
         <v>N/A</v>
       </c>
       <c r="U149" s="180" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="V149" s="180" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="W149" s="180" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="X149" s="180" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="Y149" s="180" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="Z149" s="180">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>5.9793814432989691</v>
       </c>
       <c r="AA149" s="180" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>N/A</v>
       </c>
       <c r="AC149" s="180" t="str">
@@ -30956,7 +30996,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-177.16129032258064</v>
+        <v>-145.48387096774195</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30993,7 +31033,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>9.6135282629317569</v>
+        <v>7.8945761955248033</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31020,17 +31060,41 @@
         <f>Q117/(Statement!Q49/Statement!Q75)</f>
         <v>1.5822315170500785</v>
       </c>
-      <c r="T152" s="49"/>
-      <c r="U152" s="49"/>
-      <c r="V152" s="49"/>
-      <c r="W152" s="49"/>
-      <c r="X152" s="49"/>
-      <c r="Y152" s="49"/>
-      <c r="Z152" s="49"/>
-      <c r="AA152" s="49"/>
+      <c r="T152" s="71">
+        <f>T117/(Statement!T49/Statement!T75)</f>
+        <v>1.149256871100157</v>
+      </c>
+      <c r="U152" s="71">
+        <f>U117/(Statement!U49/Statement!U75)</f>
+        <v>1.0360871880400273</v>
+      </c>
+      <c r="V152" s="71">
+        <f>V117/(Statement!V49/Statement!V75)</f>
+        <v>0.88545381283368585</v>
+      </c>
+      <c r="W152" s="71">
+        <f>W117/(Statement!W49/Statement!W75)</f>
+        <v>0.99303320101046555</v>
+      </c>
+      <c r="X152" s="71">
+        <f>X117/(Statement!X49/Statement!X75)</f>
+        <v>1.0146208228190801</v>
+      </c>
+      <c r="Y152" s="71">
+        <f>Y117/(Statement!Y49/Statement!Y75)</f>
+        <v>1.5918534255847183</v>
+      </c>
+      <c r="Z152" s="71">
+        <f>Z117/(Statement!Z49/Statement!Z75)</f>
+        <v>1.5822315170500785</v>
+      </c>
+      <c r="AA152" s="71">
+        <f>AA117/(Statement!AA49/Statement!AA75)</f>
+        <v>1.9504998473885484</v>
+      </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.9558848771028963</v>
+        <v>4.0697452286478626</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31057,17 +31121,41 @@
         <f>Statement!Q117*Statement!Q78</f>
         <v>180819</v>
       </c>
-      <c r="T153" s="49"/>
-      <c r="U153" s="49"/>
-      <c r="V153" s="49"/>
-      <c r="W153" s="49"/>
-      <c r="X153" s="49"/>
-      <c r="Y153" s="49"/>
-      <c r="Z153" s="49"/>
-      <c r="AA153" s="49"/>
+      <c r="T153" s="142">
+        <f>Statement!T117*Statement!T78</f>
+        <v>132427.72</v>
+      </c>
+      <c r="U153" s="142">
+        <f>Statement!U117*Statement!U78</f>
+        <v>103123.83</v>
+      </c>
+      <c r="V153" s="142">
+        <f>Statement!V117*Statement!V78</f>
+        <v>87899</v>
+      </c>
+      <c r="W153" s="142">
+        <f>Statement!W117*Statement!W78</f>
+        <v>99061.02</v>
+      </c>
+      <c r="X153" s="142">
+        <f>Statement!X117*Statement!X78</f>
+        <v>99314.13</v>
+      </c>
+      <c r="Y153" s="142">
+        <f>Statement!Y117*Statement!Y78</f>
+        <v>169335</v>
+      </c>
+      <c r="Z153" s="142">
+        <f>Statement!Z117*Statement!Z78</f>
+        <v>180819</v>
+      </c>
+      <c r="AA153" s="142">
+        <f>Statement!AA117*Statement!AA78</f>
+        <v>217273.97999999998</v>
+      </c>
       <c r="AC153" s="142">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>552055.84</v>
+        <v>453345.2</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31094,17 +31182,41 @@
         <f>Q153+Q108-Q107+Q48+Q45</f>
         <v>193555</v>
       </c>
-      <c r="T154" s="49"/>
-      <c r="U154" s="49"/>
-      <c r="V154" s="49"/>
-      <c r="W154" s="49"/>
-      <c r="X154" s="49"/>
-      <c r="Y154" s="49"/>
-      <c r="Z154" s="49"/>
-      <c r="AA154" s="49"/>
+      <c r="T154" s="142">
+        <f t="shared" ref="T154:AA154" si="99">T153+T108-T107+T48+T45</f>
+        <v>155564.72</v>
+      </c>
+      <c r="U154" s="142">
+        <f t="shared" si="99"/>
+        <v>129109.83000000002</v>
+      </c>
+      <c r="V154" s="142">
+        <f t="shared" si="99"/>
+        <v>116227</v>
+      </c>
+      <c r="W154" s="142">
+        <f t="shared" si="99"/>
+        <v>129794.02000000002</v>
+      </c>
+      <c r="X154" s="142">
+        <f t="shared" si="99"/>
+        <v>131350.13</v>
+      </c>
+      <c r="Y154" s="142">
+        <f t="shared" si="99"/>
+        <v>186640</v>
+      </c>
+      <c r="Z154" s="142">
+        <f t="shared" si="99"/>
+        <v>193555</v>
+      </c>
+      <c r="AA154" s="142">
+        <f t="shared" si="99"/>
+        <v>234629.97999999998</v>
+      </c>
       <c r="AC154" s="142">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>569411.83999999997</v>
+        <v>470701.2</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31141,7 +31253,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="182">
         <f ca="1">AC154/AC5</f>
-        <v>10.591147071405985</v>
+        <v>8.7551141119357183</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31178,7 +31290,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="182">
         <f ca="1">AC154/AC12</f>
-        <v>-112.77715191126956</v>
+        <v>-93.226619132501483</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31206,35 +31318,35 @@
         <v>-7383</v>
       </c>
       <c r="T157" s="63">
-        <f t="shared" ref="T157:AA157" si="98">T59-T54+T110+T65</f>
+        <f t="shared" ref="T157:AA157" si="100">T59-T54+T110+T65</f>
         <v>0</v>
       </c>
       <c r="U157" s="63">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="V157" s="63">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="W157" s="63">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>-5054</v>
       </c>
       <c r="X157" s="63">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>-2164</v>
       </c>
       <c r="Y157" s="63">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>-427</v>
       </c>
       <c r="Z157" s="63">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>262</v>
       </c>
       <c r="AA157" s="63">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>-3161</v>
       </c>
       <c r="AC157" s="63">
@@ -31288,19 +31400,19 @@
         <v>24.234480257856571</v>
       </c>
       <c r="N159" s="71">
-        <f t="shared" ref="N159:Q159" si="99">N153/N157</f>
+        <f t="shared" ref="N159:Q159" si="101">N153/N157</f>
         <v>-8.7516835473323233</v>
       </c>
       <c r="O159" s="71">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-12.197995202193283</v>
       </c>
       <c r="P159" s="71">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-4.6102486100912623</v>
       </c>
       <c r="Q159" s="71">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>-24.491263713937425</v>
       </c>
       <c r="T159" s="49"/>
@@ -31312,8 +31424,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
-        <f t="shared" ref="AC159:AC160" ca="1" si="100">AC153/AC157</f>
-        <v>-100.55661930783242</v>
+        <f t="shared" ref="AC159:AC160" ca="1" si="102">AC153/AC157</f>
+        <v>-82.576539162112937</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31325,19 +31437,19 @@
         <v>39.164320117414455</v>
       </c>
       <c r="N160" s="71">
-        <f t="shared" ref="N160:Q160" si="101">N154/N158</f>
+        <f t="shared" ref="N160:Q160" si="103">N154/N158</f>
         <v>-8.5390374025602505</v>
       </c>
       <c r="O160" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>-14.216825072184793</v>
       </c>
       <c r="P160" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>-5.0227744165946415</v>
       </c>
       <c r="Q160" s="71">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>-28.047384437038112</v>
       </c>
       <c r="T160" s="49"/>
@@ -31349,8 +31461,8 @@
       <c r="Z160" s="49"/>
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
-        <f t="shared" ca="1" si="100"/>
-        <v>-66.419204479178816</v>
+        <f t="shared" ca="1" si="102"/>
+        <v>-54.90507406975388</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31362,19 +31474,19 @@
         <v>4.1263521617131038E-2</v>
       </c>
       <c r="N161" s="73">
-        <f t="shared" ref="N161:Q161" si="102">N157/N153</f>
+        <f t="shared" ref="N161:Q161" si="104">N157/N153</f>
         <v>-0.11426372932609277</v>
       </c>
       <c r="O161" s="73">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-8.1980684811237922E-2</v>
       </c>
       <c r="P161" s="73">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-0.21690804218478027</v>
       </c>
       <c r="Q161" s="73">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-4.0830886134753538E-2</v>
       </c>
       <c r="T161" s="49"/>
@@ -31386,8 +31498,8 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
-        <f t="shared" ref="AC161" ca="1" si="103">AC157/AC153</f>
-        <v>-9.9446461792705616E-3</v>
+        <f t="shared" ref="AC161" ca="1" si="105">AC157/AC153</f>
+        <v>-1.2109977121187122E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31424,7 +31536,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-5.644573925710124E-3</v>
+        <v>-6.873614190687361E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31785,35 +31897,35 @@
         <v>9.1947947947947952</v>
       </c>
       <c r="T172" s="71">
-        <f t="shared" ref="T172:AA172" si="104">T107/T75</f>
+        <f t="shared" ref="T172:AA172" si="106">T107/T75</f>
         <v>8.2079045837231064</v>
       </c>
       <c r="U172" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>6.8587989798284257</v>
       </c>
       <c r="V172" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>6.3383371824480372</v>
       </c>
       <c r="W172" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>5.977762494268684</v>
       </c>
       <c r="X172" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>6.0747087045921866</v>
       </c>
       <c r="Y172" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>8.3023060796645698</v>
       </c>
       <c r="Z172" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>9.1947947947947952</v>
       </c>
       <c r="AA172" s="71">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>8.2113012335853561</v>
       </c>
       <c r="AC172" s="71">
@@ -31846,27 +31958,27 @@
         <v>0.25100546560791998</v>
       </c>
       <c r="T173" s="153" t="e">
-        <f t="shared" ref="T173:Y173" si="105">T54/T59</f>
+        <f t="shared" ref="T173:Y173" si="107">T54/T59</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U173" s="153" t="e">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V173" s="153" t="e">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W173" s="153">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.84132841328413288</v>
       </c>
       <c r="X173" s="153">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.32390243902439025</v>
       </c>
       <c r="Y173" s="153">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.2152395915161037</v>
       </c>
       <c r="Z173" s="153">
@@ -31907,27 +32019,27 @@
         <v>4.6052258149963103E-2</v>
       </c>
       <c r="T174" s="153">
-        <f t="shared" ref="T174:Y174" si="106">T54/T5</f>
+        <f t="shared" ref="T174:Y174" si="108">T54/T5</f>
         <v>0</v>
       </c>
       <c r="U174" s="153">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="V174" s="153">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="W174" s="153">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>5.3998578984763561E-2</v>
       </c>
       <c r="X174" s="153">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>5.1636985768722297E-2</v>
       </c>
       <c r="Y174" s="153">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>4.0137698674284038E-2</v>
       </c>
       <c r="Z174" s="153">
@@ -31968,35 +32080,35 @@
         <v>-0.13153153153153152</v>
       </c>
       <c r="T175" s="71">
-        <f t="shared" ref="T175:AA175" si="107">(T107-T108)/T75</f>
+        <f t="shared" ref="T175:AA175" si="109">(T107-T108)/T75</f>
         <v>-4.1936389148737137</v>
       </c>
       <c r="U175" s="71">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-4.7887781126825875</v>
       </c>
       <c r="V175" s="71">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-5.2115473441108549</v>
       </c>
       <c r="W175" s="71">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-5.5194864740944523</v>
       </c>
       <c r="X175" s="71">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-5.5215901302261825</v>
       </c>
       <c r="Y175" s="71">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-1.4572327044025157</v>
       </c>
       <c r="Z175" s="71">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.13153153153153152</v>
       </c>
       <c r="AA175" s="71">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.74830879426979702</v>
       </c>
       <c r="AC175" s="71">
@@ -32038,7 +32150,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="153">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-6.8127166266369003E-3</v>
+        <v>-8.296106366627462E-3</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32066,35 +32178,35 @@
         <v>0.27710820577829071</v>
       </c>
       <c r="T177" s="153">
-        <f t="shared" ref="T177:AA177" si="108">-T110/T5</f>
+        <f t="shared" ref="T177:AA177" si="110">-T110/T5</f>
         <v>0</v>
       </c>
       <c r="U177" s="153">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="V177" s="153">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="W177" s="153">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.40917344280413676</v>
       </c>
       <c r="X177" s="153">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.27607123415506651</v>
       </c>
       <c r="Y177" s="153">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.17761664103127517</v>
       </c>
       <c r="Z177" s="153">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.25508263858417435</v>
       </c>
       <c r="AA177" s="153">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.2678058481255064</v>
       </c>
       <c r="AC177" s="153">
@@ -32127,27 +32239,27 @@
         <v>1.5103640301124059</v>
       </c>
       <c r="T178" s="153" t="e">
-        <f t="shared" ref="T178:Y178" si="109">-(T110/T59)</f>
+        <f t="shared" ref="T178:Y178" si="111">-(T110/T59)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U178" s="153" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V178" s="153" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W178" s="153">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>6.375153751537515</v>
       </c>
       <c r="X178" s="153">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>1.7317073170731707</v>
       </c>
       <c r="Y178" s="153">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.95247446975648076</v>
       </c>
       <c r="Z178" s="153">
@@ -32188,27 +32300,27 @@
         <v>1.2511532547411583</v>
       </c>
       <c r="T179" s="153" t="e">
-        <f t="shared" ref="T179:Y179" si="110">-T110/T53</f>
+        <f t="shared" ref="T179:Y179" si="112">-T110/T53</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U179" s="153" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V179" s="153" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W179" s="153">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>1.9382946896035902</v>
       </c>
       <c r="X179" s="153">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>1.1782276800531033</v>
       </c>
       <c r="Y179" s="153">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>0.81049465240641716</v>
       </c>
       <c r="Z179" s="153">
@@ -32233,19 +32345,19 @@
         <v>0.46924693894516822</v>
       </c>
       <c r="N180" s="71">
-        <f t="shared" ref="N180:Q180" si="111">N5/N37</f>
+        <f t="shared" ref="N180:Q180" si="113">N5/N37</f>
         <v>0.34625459218134791</v>
       </c>
       <c r="O180" s="71">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.2830685068799198</v>
       </c>
       <c r="P180" s="71">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.27025472682393059</v>
       </c>
       <c r="Q180" s="71">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.24997989868939455</v>
       </c>
       <c r="T180" s="49"/>
@@ -32257,7 +32369,7 @@
       <c r="Z180" s="49"/>
       <c r="AA180" s="49"/>
       <c r="AC180" s="71">
-        <f t="shared" ref="AC180" si="112">AC5/AC37</f>
+        <f t="shared" ref="AC180" si="114">AC5/AC37</f>
         <v>0.26183449243176904</v>
       </c>
     </row>
@@ -32270,19 +32382,19 @@
         <v>1.9583162006578947</v>
       </c>
       <c r="N181" s="71">
-        <f t="shared" ref="N181:Q181" si="113">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
+        <f t="shared" ref="N181:Q181" si="115">IF(AND(N12&gt;0,N108&gt;0),N108/N12,"N/A")</f>
         <v>18.016709511568124</v>
       </c>
       <c r="O181" s="71">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>529.74193548387098</v>
       </c>
       <c r="P181" s="180" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>N/A</v>
       </c>
       <c r="Q181" s="180" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>N/A</v>
       </c>
       <c r="T181" s="49"/>
@@ -32294,7 +32406,7 @@
       <c r="Z181" s="49"/>
       <c r="AA181" s="49"/>
       <c r="AC181" s="180" t="str">
-        <f t="shared" ref="AC181" si="114">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
+        <f t="shared" ref="AC181" si="116">IF(AND(AC12&gt;0,AC108&gt;0),AC108/AC12,"N/A")</f>
         <v>N/A</v>
       </c>
     </row>
@@ -32307,19 +32419,19 @@
         <v>0.17423930921052633</v>
       </c>
       <c r="N182" s="71">
-        <f t="shared" ref="N182:Q182" si="115">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
+        <f t="shared" ref="N182:Q182" si="117">IF(AND(N12&gt;0,N108&gt;0),(N108-N107)/N12,"N/A")</f>
         <v>3.342330762639246</v>
       </c>
       <c r="O182" s="71">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>197.88172043010752</v>
       </c>
       <c r="P182" s="180" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>N/A</v>
       </c>
       <c r="Q182" s="180" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>N/A</v>
       </c>
       <c r="T182" s="49"/>
@@ -32331,7 +32443,7 @@
       <c r="Z182" s="49"/>
       <c r="AA182" s="49"/>
       <c r="AC182" s="180" t="str">
-        <f t="shared" ref="AC182" si="116">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
+        <f t="shared" ref="AC182" si="118">IF(AND(AC12&gt;0,AC108&gt;0),(AC108-AC107)/AC12,"N/A")</f>
         <v>N/A</v>
       </c>
     </row>
@@ -32344,19 +32456,19 @@
         <v>0.79999190127656128</v>
       </c>
       <c r="N183" s="71">
-        <f t="shared" ref="N183:Q183" si="117">N5/(N108+N112-N107)</f>
+        <f t="shared" ref="N183:Q183" si="119">N5/(N108+N112-N107)</f>
         <v>0.56760917119014831</v>
       </c>
       <c r="O183" s="71">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.42244173002617474</v>
       </c>
       <c r="P183" s="71">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.41615856047900435</v>
       </c>
       <c r="Q183" s="71">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.41610965461316202</v>
       </c>
       <c r="T183" s="49"/>
@@ -32368,7 +32480,7 @@
       <c r="Z183" s="49"/>
       <c r="AA183" s="49"/>
       <c r="AC183" s="71">
-        <f t="shared" ref="AC183" si="118">AC5/(AC108+AC112-AC107)</f>
+        <f t="shared" ref="AC183" si="120">AC5/(AC108+AC112-AC107)</f>
         <v>0.4175766990291262</v>
       </c>
     </row>
@@ -32501,7 +32613,7 @@
         <v>5052</v>
       </c>
       <c r="AC188" s="61">
-        <f t="shared" ref="AC188:AC197" si="119">SUM(X188:AA188)</f>
+        <f t="shared" ref="AC188:AC197" si="121">SUM(X188:AA188)</f>
         <v>17845</v>
       </c>
     </row>
@@ -32562,7 +32674,7 @@
         <v>12779</v>
       </c>
       <c r="AC189" s="61">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>50171</v>
       </c>
     </row>
@@ -32620,7 +32732,7 @@
         <v>5421</v>
       </c>
       <c r="AC190" s="61">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>18580</v>
       </c>
     </row>
@@ -32681,7 +32793,7 @@
         <v>628</v>
       </c>
       <c r="AC191" s="61">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>3248</v>
       </c>
     </row>
@@ -32768,7 +32880,7 @@
         <v>2516</v>
       </c>
       <c r="AC193" s="61">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>20159</v>
       </c>
     </row>
@@ -32829,7 +32941,7 @@
         <v>3510</v>
       </c>
       <c r="AC194" s="61">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>13456</v>
       </c>
     </row>
@@ -32890,7 +33002,7 @@
         <v>8721</v>
       </c>
       <c r="AC195" s="61">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>36310</v>
       </c>
     </row>
@@ -32951,7 +33063,7 @@
         <v>7858</v>
       </c>
       <c r="AC196" s="61">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>29015</v>
       </c>
     </row>
@@ -33012,7 +33124,7 @@
         <v>526</v>
       </c>
       <c r="AC197" s="61">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>2985</v>
       </c>
     </row>
@@ -33076,61 +33188,61 @@
       <c r="K201" s="80"/>
       <c r="L201" s="80"/>
       <c r="M201" s="80">
-        <f t="shared" ref="M201:Q205" si="120">IF(L187=0,
+        <f t="shared" ref="M201:Q205" si="122">IF(L187=0,
 IF(M187=0,0,IF(M187&gt;0,1,-1)),
 (M187-L187)/ABS(L187)
 )</f>
         <v>1</v>
       </c>
       <c r="N201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.22657676298045326</v>
       </c>
       <c r="O201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-7.9155257608661447E-2</v>
       </c>
       <c r="P201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.139722469068289</v>
       </c>
       <c r="Q201" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-3.3527259641336293E-2</v>
       </c>
       <c r="T201" s="80">
-        <f t="shared" ref="T201:AA205" si="121">IF(S187=0,
+        <f t="shared" ref="T201:AA205" si="123">IF(S187=0,
 IF(T187=0,0,IF(T187&gt;0,1,-1)),
 (T187-S187)/ABS(S187)
 )</f>
         <v>1</v>
       </c>
       <c r="U201" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>2.2104875353063983E-3</v>
       </c>
       <c r="V201" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>7.4500673937017522E-2</v>
       </c>
       <c r="W201" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.13000342114266164</v>
       </c>
       <c r="X201" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>3.1721064359680168E-2</v>
       </c>
       <c r="Y201" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.436030999872951E-2</v>
       </c>
       <c r="Z201" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-4.0070298769771528E-2</v>
       </c>
       <c r="AA201" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-5.687782253142927E-2</v>
       </c>
       <c r="AC201" s="49"/>
@@ -33140,55 +33252,55 @@
         <v>359</v>
       </c>
       <c r="M202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
       <c r="N202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-8.4923946253162061E-2</v>
       </c>
       <c r="O202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.23547784878293962</v>
       </c>
       <c r="P202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.242779995304062</v>
       </c>
       <c r="Q202" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>4.9240310077519382E-2</v>
       </c>
       <c r="T202" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U202" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.8304862023653091E-2</v>
       </c>
       <c r="V202" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>5.0712388312001935E-2</v>
       </c>
       <c r="W202" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-5.1712250057458053E-2</v>
       </c>
       <c r="X202" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-4.5322346097915654E-2</v>
       </c>
       <c r="Y202" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>4.5189134298045192E-2</v>
       </c>
       <c r="Z202" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.15059509351469516</v>
       </c>
       <c r="AA202" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>6.6497783407219763E-2</v>
       </c>
       <c r="AC202" s="49"/>
@@ -33198,55 +33310,55 @@
         <v>360</v>
       </c>
       <c r="M203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
       <c r="N203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.16628914988814317</v>
       </c>
       <c r="O203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.1521793818236705</v>
       </c>
       <c r="P203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-2.1403279726227919E-2</v>
       </c>
       <c r="Q203" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-6.5492915041135214E-3</v>
       </c>
       <c r="T203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>2.9628389688650822E-2</v>
       </c>
       <c r="V203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>6.6493253129572424E-2</v>
       </c>
       <c r="W203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.10403963414634146</v>
       </c>
       <c r="X203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>4.6788600595491277E-3</v>
       </c>
       <c r="Y203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>7.1295512277730733E-2</v>
       </c>
       <c r="Z203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>2.1972810622826432E-2</v>
       </c>
       <c r="AA203" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-1.1678267594740912E-2</v>
       </c>
       <c r="AC203" s="49"/>
@@ -33256,55 +33368,55 @@
         <v>361</v>
       </c>
       <c r="M204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
       <c r="N204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.35158501440922191</v>
       </c>
       <c r="O204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1.0298507462686568</v>
       </c>
       <c r="P204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>17.190126050420169</v>
       </c>
       <c r="Q204" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>2.9393081942599757E-2</v>
       </c>
       <c r="T204" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U204" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1.3311536665109761E-2</v>
       </c>
       <c r="V204" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>2.3046784973496196E-4</v>
       </c>
       <c r="W204" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>7.5345622119815672E-2</v>
       </c>
       <c r="X204" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-5.3567602314120423E-2</v>
       </c>
       <c r="Y204" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-4.1204437400950873E-2</v>
       </c>
       <c r="Z204" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>6.4226682408500588E-2</v>
       </c>
       <c r="AA204" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.2027956512092301</v>
       </c>
       <c r="AC204" s="49"/>
@@ -33314,55 +33426,55 @@
         <v>362</v>
       </c>
       <c r="M205" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1</v>
       </c>
       <c r="N205" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-0.58669833729216148</v>
       </c>
       <c r="O205" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-7.9445571331981074E-2</v>
       </c>
       <c r="P205" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>0.32243848696290855</v>
       </c>
       <c r="Q205" s="80">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-1.0552624271035824E-2</v>
       </c>
       <c r="T205" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1</v>
       </c>
       <c r="U205" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>9.4211123723041995E-2</v>
       </c>
       <c r="V205" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.1545643153526971</v>
       </c>
       <c r="W205" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.1527403414195867</v>
       </c>
       <c r="X205" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.11664899257688228</v>
       </c>
       <c r="Y205" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-5.6980056980056981E-2</v>
       </c>
       <c r="Z205" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.42195367573011078</v>
       </c>
       <c r="AA205" s="80">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>9.4076655052264813E-2</v>
       </c>
       <c r="AC205" s="49"/>
@@ -33502,15 +33614,15 @@
         <v>51.510426817384527</v>
       </c>
       <c r="O213" s="142">
-        <f t="shared" ref="O213:Q213" si="122">100*(1+((O117-$M117)/ABS($M117)))</f>
+        <f t="shared" ref="O213:Q213" si="124">100*(1+((O117-$M117)/ABS($M117)))</f>
         <v>97.934125901383737</v>
       </c>
       <c r="P213" s="142">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>39.563437926330145</v>
       </c>
       <c r="Q213" s="142">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>70.551549405573965</v>
       </c>
       <c r="T213" s="49"/>
@@ -33535,15 +33647,15 @@
         <v>79.790949584936214</v>
       </c>
       <c r="O214" s="142">
-        <f t="shared" ref="O214:Q214" si="123">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O214:Q214" si="125">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>68.6221907268678</v>
       </c>
       <c r="P214" s="142">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>67.196041708847943</v>
       </c>
       <c r="Q214" s="142">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>66.882212998582702</v>
       </c>
       <c r="T214" s="49"/>
@@ -33568,15 +33680,15 @@
         <v>39.917695473251023</v>
       </c>
       <c r="O215" s="142">
-        <f t="shared" ref="O215:Q215" si="124">100*(1+((O26-$M26)/ABS($M26)))</f>
+        <f t="shared" ref="O215:Q215" si="126">100*(1+((O26-$M26)/ABS($M26)))</f>
         <v>8.2304526748971263</v>
       </c>
       <c r="P215" s="142">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>-90.123456790123456</v>
       </c>
       <c r="Q215" s="142">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>-1.2345679012345512</v>
       </c>
       <c r="T215" s="49"/>
@@ -33673,35 +33785,35 @@
         <v>143</v>
       </c>
       <c r="T220" s="61">
-        <f t="shared" ref="T220:AA220" si="125">T190+T219</f>
+        <f t="shared" ref="T220:AA220" si="127">T190+T219</f>
         <v>4</v>
       </c>
       <c r="U220" s="61">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>18</v>
       </c>
       <c r="V220" s="61">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>27</v>
       </c>
       <c r="W220" s="61">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>-31</v>
       </c>
       <c r="X220" s="61">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>-4</v>
       </c>
       <c r="Y220" s="61">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>8</v>
       </c>
       <c r="Z220" s="61">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>170</v>
       </c>
       <c r="AA220" s="61">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>170</v>
       </c>
       <c r="AC220" s="63">
@@ -33763,15 +33875,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="237" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="237"/>
+      <c r="E4" s="237" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33779,7 +33891,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>109.84</v>
+        <v>90.2</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -33795,7 +33907,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>552055.84</v>
+        <v>453345.2</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33815,7 +33927,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>569411.83999999997</v>
+        <v>470701.2</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33835,7 +33947,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC150</f>
-        <v>-177.16129032258064</v>
+        <v>-145.48387096774195</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -33855,7 +33967,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>9.6135282629317569</v>
+        <v>7.8945761955248033</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -33875,7 +33987,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>4.9558848771028963</v>
+        <v>4.0697452286478626</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33895,7 +34007,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC155</f>
-        <v>10.591147071405985</v>
+        <v>8.7551141119357183</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33904,18 +34016,18 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>-112.77715191126956</v>
+        <v>-93.226619132501483</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="237"/>
+      <c r="E15" s="237" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33966,14 +34078,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="237" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="237"/>
+      <c r="E21" s="237" t="s">
         <v>249</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="237"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34042,14 +34154,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="237" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="237"/>
+      <c r="E29" s="237" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="237"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34125,14 +34237,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="237" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="237"/>
+      <c r="E37" s="237" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="237"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34140,7 +34252,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC162</f>
-        <v>-5.644573925710124E-3</v>
+        <v>-6.873614190687361E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -34156,7 +34268,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC161</f>
-        <v>-9.9446461792705616E-3</v>
+        <v>-1.2109977121187122E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -34201,14 +34313,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="237" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="237"/>
+      <c r="E45" s="237" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="237"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34241,18 +34353,18 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC176</f>
-        <v>-6.8127166266369003E-3</v>
+        <v>-8.296106366627462E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="237" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="237"/>
+      <c r="E51" s="237" t="s">
         <v>303</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="237"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34420,7 +34532,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>109.84</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34449,7 +34561,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>552055.84</v>
+        <v>453345.2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34478,7 +34590,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>569411.83999999997</v>
+        <v>470701.2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34507,7 +34619,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC150</f>
-        <v>-177.16129032258064</v>
+        <v>-145.48387096774195</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34536,7 +34648,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>9.6135282629317569</v>
+        <v>7.8945761955248033</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34565,7 +34677,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>4.9558848771028963</v>
+        <v>4.0697452286478626</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34594,7 +34706,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC155</f>
-        <v>10.591147071405985</v>
+        <v>8.7551141119357183</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34623,7 +34735,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>-112.77715191126956</v>
+        <v>-93.226619132501483</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35396,7 +35508,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC162</f>
-        <v>-5.644573925710124E-3</v>
+        <v>-6.873614190687361E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35425,7 +35537,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>-9.9446461792705616E-3</v>
+        <v>-1.2109977121187122E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35748,7 +35860,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC176</f>
-        <v>-6.8127166266369003E-3</v>
+        <v>-8.296106366627462E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36286,14 +36398,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="240" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="236"/>
-      <c r="F3" s="237" t="s">
+      <c r="D3" s="241"/>
+      <c r="F3" s="242" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="236"/>
+      <c r="G3" s="241"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36360,19 +36472,19 @@
       <c r="B7" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="233">
+      <c r="C7" s="238">
         <f>Statement!AA89</f>
         <v>-7.0937545707181514E-3</v>
       </c>
-      <c r="D7" s="234"/>
-      <c r="F7" s="233">
+      <c r="D7" s="239"/>
+      <c r="F7" s="238">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>7.1840214731191288E-2</v>
       </c>
-      <c r="G7" s="234"/>
+      <c r="G7" s="239"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -36399,19 +36511,19 @@
       <c r="B9" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="233">
+      <c r="C9" s="238">
         <f>Statement!AA90</f>
         <v>-5.7381743213835761E-2</v>
       </c>
-      <c r="D9" s="234"/>
-      <c r="F9" s="233">
+      <c r="D9" s="239"/>
+      <c r="F9" s="238">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>2.9393370856785492E-2</v>
       </c>
-      <c r="G9" s="234"/>
+      <c r="G9" s="239"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -36438,19 +36550,19 @@
       <c r="B11" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="233">
+      <c r="C11" s="238">
         <f>Statement!AA91</f>
         <v>8.1731741857171761E-2</v>
       </c>
-      <c r="D11" s="234"/>
-      <c r="F11" s="233">
+      <c r="D11" s="239"/>
+      <c r="F11" s="238">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.1444777397260274</v>
       </c>
-      <c r="G11" s="234"/>
+      <c r="G11" s="239"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -36477,19 +36589,19 @@
       <c r="B13" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="233">
+      <c r="C13" s="238">
         <f>Statement!AA95</f>
         <v>0.94430437772175113</v>
       </c>
-      <c r="D13" s="234"/>
-      <c r="F13" s="233">
+      <c r="D13" s="239"/>
+      <c r="F13" s="238">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.70581138145988342</v>
       </c>
-      <c r="G13" s="234"/>
+      <c r="G13" s="239"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -36516,19 +36628,19 @@
       <c r="B15" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="233">
+      <c r="C15" s="238">
         <f>Statement!AA96</f>
         <v>-6.4068965517241381</v>
       </c>
-      <c r="D15" s="234"/>
-      <c r="F15" s="233">
+      <c r="D15" s="239"/>
+      <c r="F15" s="238">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-9.4186046511627914</v>
       </c>
-      <c r="G15" s="234"/>
+      <c r="G15" s="239"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -36555,19 +36667,19 @@
       <c r="B17" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="233">
+      <c r="C17" s="238">
         <f>Statement!AA98</f>
         <v>-5.3079526226734348</v>
       </c>
-      <c r="D17" s="234"/>
-      <c r="F17" s="233">
+      <c r="D17" s="239"/>
+      <c r="F17" s="238">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-3.5408038976857492</v>
       </c>
-      <c r="G17" s="234"/>
+      <c r="G17" s="239"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -36594,22 +36706,22 @@
       <c r="B19" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="233">
+      <c r="C19" s="238">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.6746293245469521E-2</v>
       </c>
-      <c r="D19" s="234"/>
-      <c r="F19" s="233">
+      <c r="D19" s="239"/>
+      <c r="F19" s="238">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.17038913193644947</v>
       </c>
-      <c r="G19" s="234"/>
+      <c r="G19" s="239"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -36636,22 +36748,22 @@
       <c r="B21" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="233">
+      <c r="C21" s="238">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-5.083333333333333</v>
       </c>
-      <c r="D21" s="234"/>
-      <c r="F21" s="233">
+      <c r="D21" s="239"/>
+      <c r="F21" s="238">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.8421052631578947</v>
       </c>
-      <c r="G21" s="234"/>
+      <c r="G21" s="239"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36699,22 +36811,22 @@
       <c r="B25" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="233">
+      <c r="C25" s="238">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.687782253142927E-2</v>
       </c>
-      <c r="D25" s="234"/>
-      <c r="F25" s="233">
+      <c r="D25" s="239"/>
+      <c r="F25" s="238">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>1.284572027788701E-2</v>
       </c>
-      <c r="G25" s="234"/>
+      <c r="G25" s="239"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36741,22 +36853,22 @@
       <c r="B27" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="233">
+      <c r="C27" s="238">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>6.6497783407219763E-2</v>
       </c>
-      <c r="D27" s="234"/>
-      <c r="F27" s="233">
+      <c r="D27" s="239"/>
+      <c r="F27" s="238">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.22443044110518662</v>
       </c>
-      <c r="G27" s="234"/>
+      <c r="G27" s="239"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36783,22 +36895,22 @@
       <c r="B29" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="233">
+      <c r="C29" s="238">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>-1.1678267594740912E-2</v>
       </c>
-      <c r="D29" s="234"/>
-      <c r="F29" s="233">
+      <c r="D29" s="239"/>
+      <c r="F29" s="238">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.7111867290514677E-2</v>
       </c>
-      <c r="G29" s="234"/>
+      <c r="G29" s="239"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36825,22 +36937,22 @@
       <c r="B31" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C31" s="233">
+      <c r="C31" s="238">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>0.2027956512092301</v>
       </c>
-      <c r="D31" s="234"/>
-      <c r="F31" s="233">
+      <c r="D31" s="239"/>
+      <c r="F31" s="238">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.16155988857938719</v>
       </c>
-      <c r="G31" s="234"/>
+      <c r="G31" s="239"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36867,22 +36979,22 @@
       <c r="B33" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C33" s="233">
+      <c r="C33" s="238">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>9.4076655052264813E-2</v>
       </c>
-      <c r="D33" s="234"/>
-      <c r="F33" s="233">
+      <c r="D33" s="239"/>
+      <c r="F33" s="238">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33404029692470838</v>
       </c>
-      <c r="G33" s="234"/>
+      <c r="G33" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="28">
